--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4196A479-2A99-41DD-A857-D384F0FB0C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20574B73-32BB-4CF4-A1E6-7B37358BA636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
     <sheet name="Promts" sheetId="2" r:id="rId2"/>
     <sheet name="Unit Test" sheetId="3" r:id="rId3"/>
     <sheet name="promt" sheetId="4" r:id="rId4"/>
+    <sheet name="Agentes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suite Test'!$A$1:$J$114</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="832">
   <si>
     <t>Nº</t>
   </si>
@@ -2826,12 +2827,103 @@
   <si>
     <t xml:space="preserve"> apps/api/tests/modules/projects/domain/.</t>
   </si>
+  <si>
+    <t>apps/api/tests/modules/procurement/domain/.</t>
+  </si>
+  <si>
+    <t>SEMANAS 1-4 (S1-S2):</t>
+  </si>
+  <si>
+    <t>├── [Agente 1]  Security Core ────────────────►</t>
+  </si>
+  <si>
+    <t>├── [Agente 10] DTOs ─────►</t>
+  </si>
+  <si>
+    <t>└── [Agente 8]  Event Bus básico ───►</t>
+  </si>
+  <si>
+    <t>SEMANAS 5-8 (S3-S4):</t>
+  </si>
+  <si>
+    <t>└── [Agente 2]  Documents ────────────────────►</t>
+  </si>
+  <si>
+    <t>SEMANAS 9-12 (S5-S6):</t>
+  </si>
+  <si>
+    <t>└── [Agente 6]  Coherence (CRÍTICO) ──────────►</t>
+  </si>
+  <si>
+    <t>SEMANAS 13-16 (S7-S8):</t>
+  </si>
+  <si>
+    <t>├── [Agente 3]  Projects ────────►</t>
+  </si>
+  <si>
+    <t>└── [Agente 4]  Procurement ─────► (después de Projects)</t>
+  </si>
+  <si>
+    <t>SEMANAS 17-20 (S9-S10):</t>
+  </si>
+  <si>
+    <t>├── [Agente 7]  Stakeholders ────►</t>
+  </si>
+  <si>
+    <t>└── [Agente 5]  Analysis ────────►</t>
+  </si>
+  <si>
+    <t>SEMANAS 21-24 (S11-S12):</t>
+  </si>
+  <si>
+    <t>├── [Agente 9]  Observability ───►</t>
+  </si>
+  <si>
+    <t>├── [Agente 10] HTTP Adapters ───►</t>
+  </si>
+  <si>
+    <t>├── [Agente 8]  Celery/DLQ ──────►</t>
+  </si>
+  <si>
+    <t>└── [Agente 11] Integration ─────────────────►</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 1 - SECURITY CORE &amp; GATEKEEPER
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Security Lead** for C2Pro v2.1.
+* **CRITICAL:** Read and internalize `agents.md` immediately. It contains your architectural constraints, directory structure, and TDD protocols.
+* **LATENCY:** Do not explain TDD concepts. Output code directly.
+**2. YOUR ASSIGNED SCOPE**
+You own the "Shield" of the application.
+* **Components:**
+    * MCP Gateway (Allowlist, Rate Limiting, Audit).
+    * Anonymizer Service (PII Detection, Strategies).
+    * Tenant Isolation (ContextVars, RLS enforcement).
+    * JWT Validation (Auth Middleware).
+    * Anti-Gaming Detection (Logic &amp; Rules).
+* **Test Suites (Target 100%):**
+    * `TS-UC-SEC-MCP-001` to `004`
+    * `TS-UC-SEC-ANO-001` to `003`
+    * `TS-UC-SEC-TNT-001`
+    * `TS-UC-SEC-JWT-001`
+    * `TS-UC-SEC-AUD-001`
+    * `TS-UC-SEC-GAM-001`
+    * `TS-INT-*` (Security specific integrations only)
+    * `TS-E2E-SEC-*` (Security specific E2E)
+**3. EXECUTION PROTOCOL**
+When I provide a Suite ID (e.g., `TS-UC-SEC-MCP-001`):
+1.  **Lookup:** Check `C2PRO_TEST_SUITES_INDEX_v1.1.md` for scope.
+2.  **RED:** Generate `tests/core/security/test_*.py`. Assert failure.
+3.  **GREEN:** Generate `src/core/security/*.py`. Use "Fake It" pattern.
+4.  **UPDATE:** Remind me to update `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Please provide a TS-UC-SEC ID.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2880,6 +2972,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -2983,7 +3081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3028,6 +3126,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14292,6 +14396,9 @@
       <c r="G277" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H277" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="I277" t="s">
         <v>810</v>
       </c>
@@ -14318,6 +14425,9 @@
       <c r="G278" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H278" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J278" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
@@ -14341,6 +14451,9 @@
       <c r="G279" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H279" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J279" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
@@ -14364,6 +14477,9 @@
       <c r="G280" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H280" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J280" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
@@ -14387,6 +14503,9 @@
       <c r="G281" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H281" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J281" t="str">
         <f t="shared" ref="J281:J331" si="4">CONCATENATE(A281,C281)</f>
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
@@ -14410,6 +14529,9 @@
       <c r="G282" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H282" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J282" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
@@ -14433,6 +14555,9 @@
       <c r="G283" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H283" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J283" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
@@ -14456,6 +14581,9 @@
       <c r="G284" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H284" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J284" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
@@ -14479,6 +14607,9 @@
       <c r="G285" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H285" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J285" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
@@ -14502,6 +14633,9 @@
       <c r="G286" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H286" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J286" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
@@ -14525,6 +14659,9 @@
       <c r="G287" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H287" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J287" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
@@ -14548,6 +14685,9 @@
       <c r="G288" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H288" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J288" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
@@ -14571,6 +14711,9 @@
       <c r="G289" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H289" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J289" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
@@ -14594,6 +14737,9 @@
       <c r="G290" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H290" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J290" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
@@ -14617,6 +14763,9 @@
       <c r="G291" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H291" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J291" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
@@ -14640,6 +14789,9 @@
       <c r="G292" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H292" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J292" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
@@ -14663,6 +14815,9 @@
       <c r="G293" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="H293" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J293" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
@@ -14685,6 +14840,9 @@
       </c>
       <c r="G294" s="12" t="s">
         <v>771</v>
+      </c>
+      <c r="H294" s="12" t="s">
+        <v>407</v>
       </c>
       <c r="J294" t="str">
         <f t="shared" si="4"/>
@@ -14832,6 +14990,15 @@
       <c r="F302" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G302" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H302" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="I302" t="s">
+        <v>811</v>
+      </c>
       <c r="J302" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
@@ -14852,6 +15019,12 @@
       <c r="F303" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G303" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H303" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J303" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
@@ -14872,6 +15045,12 @@
       <c r="F304" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G304" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H304" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J304" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
@@ -14892,6 +15071,12 @@
       <c r="F305" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G305" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H305" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J305" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
@@ -14912,6 +15097,12 @@
       <c r="F306" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G306" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H306" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J306" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
@@ -14932,6 +15123,12 @@
       <c r="F307" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G307" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H307" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J307" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
@@ -14952,6 +15149,12 @@
       <c r="F308" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G308" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H308" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J308" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
@@ -14972,6 +15175,12 @@
       <c r="F309" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G309" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H309" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J309" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
@@ -14992,6 +15201,12 @@
       <c r="F310" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G310" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H310" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J310" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
@@ -15012,6 +15227,12 @@
       <c r="F311" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G311" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H311" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J311" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
@@ -15032,6 +15253,12 @@
       <c r="F312" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G312" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H312" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J312" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
@@ -15052,6 +15279,12 @@
       <c r="F313" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G313" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H313" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J313" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
@@ -15072,6 +15305,12 @@
       <c r="F314" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G314" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H314" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J314" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
@@ -15092,6 +15331,12 @@
       <c r="F315" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G315" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H315" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J315" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
@@ -15112,6 +15357,12 @@
       <c r="F316" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G316" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H316" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J316" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
@@ -15132,6 +15383,12 @@
       <c r="F317" s="9" t="s">
         <v>720</v>
       </c>
+      <c r="G317" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="H317" s="12" t="s">
+        <v>407</v>
+      </c>
       <c r="J317" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
@@ -15152,6 +15409,9 @@
       <c r="F318" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G318" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J318" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
@@ -15172,6 +15432,9 @@
       <c r="F319" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G319" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J319" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
@@ -15192,6 +15455,9 @@
       <c r="F320" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G320" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J320" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
@@ -15212,6 +15478,9 @@
       <c r="F321" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G321" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J321" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
@@ -15232,6 +15501,9 @@
       <c r="F322" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G322" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J322" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
@@ -15252,6 +15524,9 @@
       <c r="F323" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G323" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J323" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
@@ -15272,6 +15547,9 @@
       <c r="F324" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G324" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J324" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
@@ -15292,6 +15570,9 @@
       <c r="F325" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G325" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J325" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
@@ -15312,6 +15593,9 @@
       <c r="F326" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G326" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J326" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
@@ -15332,6 +15616,9 @@
       <c r="F327" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G327" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J327" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
@@ -15352,6 +15639,9 @@
       <c r="F328" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G328" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J328" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
@@ -15372,6 +15662,9 @@
       <c r="F329" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G329" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J329" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
@@ -15392,6 +15685,9 @@
       <c r="F330" s="9" t="s">
         <v>737</v>
       </c>
+      <c r="G330" s="12" t="s">
+        <v>771</v>
+      </c>
       <c r="J330" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
@@ -15411,6 +15707,9 @@
       <c r="E331" s="7"/>
       <c r="F331" s="9" t="s">
         <v>737</v>
+      </c>
+      <c r="G331" s="12" t="s">
+        <v>771</v>
       </c>
       <c r="J331" t="str">
         <f t="shared" si="4"/>
@@ -16456,4 +16755,131 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAF9D8E-5017-468F-8689-A64B44F82814}">
+  <dimension ref="E5:F28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="85.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:6">
+      <c r="E5" s="16" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="6" spans="5:6" ht="201" customHeight="1">
+      <c r="E6" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="7" spans="5:6">
+      <c r="E7" s="16" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="8" spans="5:6">
+      <c r="E8" s="16" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="9" spans="5:6">
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" spans="5:6">
+      <c r="E10" s="16" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6">
+      <c r="E11" s="16" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="12" spans="5:6">
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" spans="5:6">
+      <c r="E13" s="16" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="14" spans="5:6">
+      <c r="E14" s="16" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="15" spans="5:6">
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" spans="5:6">
+      <c r="E16" s="16" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="16" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="16" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="17"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="16" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="16" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" s="16" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="16" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28" s="16" t="s">
+        <v>830</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20574B73-32BB-4CF4-A1E6-7B37358BA636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA186636-5833-4748-8EC2-640B38F3A73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="862">
   <si>
     <t>Nº</t>
   </si>
@@ -2917,6 +2917,293 @@
 3.  **GREEN:** Generate `src/core/security/*.py`. Use "Fake It" pattern.
 4.  **UPDATE:** Remind me to update `C2PRO_TDD_BACKLOG_v1.0.md`.
 **AWAITING INPUT:** Please provide a TS-UC-SEC ID.</t>
+  </si>
+  <si>
+    <t> Orden | Agente | Tests | Sprint | Bloquea | Crítico |</t>
+  </si>
+  <si>
+    <t>|-------|--------|-------|--------|---------|---------|</t>
+  </si>
+  <si>
+    <t>| 1 | Agente 10 (DTOs) | 40 | S1 | Todos | ✅ |</t>
+  </si>
+  <si>
+    <t>| 2 | Agente 1 (Security) | 156 | S1-S2 | Todos | ✅ |</t>
+  </si>
+  <si>
+    <t>| 3 | Agente 8 (Event Bus básico) | 34 | S2 | Async flows | ✅ |</t>
+  </si>
+  <si>
+    <t>| 4 | Agente 2 (Documents) | 162 | S3-S4 | Analysis, Coherence | ✅ |</t>
+  </si>
+  <si>
+    <t>| 5 | Agente 6 (Coherence) | 206 | S5-S6 | Dashboard, E2E | 🔴 CRÍTICO |</t>
+  </si>
+  <si>
+    <t>| 6 | Agente 3 (Projects) | 116 | S7 | Procurement | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 7 | Agente 4 (Procurement) | 116 | S8 | Coherence rules | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 8 | Agente 7 (Stakeholders) | 112 | S9 | RACI | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 9 | Agente 5 (Analysis) | 78 | S10 | Graph RAG | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 10 | Agente 9 (Observability) | 68 | S11 | Monitoring | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 11 | Agente 11 (Integration) | 184 | S11-S12 | E2E | ✅ |</t>
+  </si>
+  <si>
+    <t>| 12 | Agente 10 (HTTP) | 62 | S12 | API | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 13 | Agente 8 (Celery/DLQ) | 44 | S12 | Workers | ⚠️ |</t>
+  </si>
+  <si>
+    <t>| 14 | Agente 12 (E2E) | 78 | S13-S14 | Release | ✅ |</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 1 - SECURITY CORE SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Security Lead**.
+* **CRITICAL:** Read `agents.md`. Enforce "4-Layer Security" model.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **MCP Gateway:** `TS-UC-SEC-MCP-001` to `004` (Allowlist, Rate Limit, Query Limits, Audit).
+* **Anonymizer:** `TS-UC-SEC-ANO-001` to `003` (PII Detection, Strategies, Config).
+* **Isolation:** `TS-UC-SEC-TNT-001` (Tenant Context).
+* **Auth:** `TS-UC-SEC-JWT-001` (JWT Validation).
+* **Audit:** `TS-UC-SEC-AUD-001` (Core Trail).
+* **Gaming:** `TS-UC-SEC-GAM-001` (Detection Logic).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if the test exists. If yes, validate strict security assertions. If no, generate the test (RED).
+2.  **RED:** Confirm failure (e.g., "Unauthorized Access" or "PII Leak").
+3.  **GREEN:** Implement minimal logic in `src/core/security` or `src/core/auth`. Use "Fake It" pattern initially.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UC-SEC ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 2 - DOCUMENTS DOMAIN SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Documents Module Lead**.
+* **CRITICAL:** Read `agents.md`. `Clause` entity is the Single Source of Truth.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Clauses:** `TS-UD-DOC-CLS-001` to `003` (Entity, Types, Hierarchy).
+* **Entities:** `TS-UD-DOC-ENT-001` to `004` (Dates, Money, Durations, Stakeholders).
+* **Document:** `TS-UD-DOC-DOC-001` (Entity) &amp; `TS-UD-DOC-CNF-001` (Confidence).
+* **Use Cases:** `TS-UA-DOC-UC-*` (Upload, Extract).
+* **Services:** `TS-UA-SVC-EXT-*` (Extraction Services).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Ensure Domain Entities are pure Pydantic.
+2.  **RED:** Generate test in `tests/modules/documents/domain`. Assert validation failure.
+3.  **GREEN:** Implement logic in `src/modules/documents/domain`. No DB imports allowed.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-DOC ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 3 - PROJECTS &amp; WBS SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Projects Module Lead**.
+* **CRITICAL:** Read `agents.md`. Focus on Recursive Hierarchies.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **WBS Logic:** `TS-UD-PRJ-WBS-001` to `004` (Entity, Hierarchy, Validation, CRUD).
+* **Project:** `TS-UD-PRJ-PRJ-001` (Entity).
+* **Contracts:** `TS-UD-PRJ-DTO-001` (DTOs &amp; Ports for Integration).
+* **Use Cases:** `TS-UA-PRJ-UC-*` (Generate WBS).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify recursive parent/child logic tests.
+2.  **RED:** Generate test in `tests/modules/projects`. Assert hierarchy constraint failure.
+3.  **GREEN:** Implement logic in `src/modules/projects`. Ensure strictly typed relationships.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-PRJ ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 4 - PROCUREMENT LOGIC SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Procurement Module Lead**.
+* **CRITICAL:** Read `agents.md`. Focus on Lead Time Logic.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **BOM:** `TS-UD-PROC-BOM-001` &amp; `002` (Entity, Validation).
+* **Lead Time:** `TS-UD-PROC-LTM-001` to `004` (Calc, Incoterms, Customs, Alerts).
+* **Planning:** `TS-UD-PROC-PLN-001` (Plan Generation).
+* **Use Cases:** `TS-UA-PROC-UC-*` (Generate BOM, Calc LTM).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify math/date calculation assertions.
+2.  **RED:** Generate test in `tests/modules/procurement`. Assert wrong date calculation.
+3.  **GREEN:** Implement logic in `src/modules/procurement`. Use standard `datetime` libs.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-PROC ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 5 - ANALYSIS &amp; GRAPH SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Analysis Module Lead**.
+* **CRITICAL:** Read `agents.md`. Focus on Graph Consistency.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Alerts:** `TS-UD-ANA-ALR-001` (Entity).
+* **Graph:** `TS-UD-ANA-GRP-001` &amp; `002` (Node, Relationship).
+* **Search:** `TS-UD-ANA-SRC-001` &amp; `HYB-001` (Semantic, Hybrid).
+* **Use Cases:** `TS-UA-ANA-UC-*`.
+* **Neo4j:** `TS-INT-GRP-NEO-001` (Integration Adapter).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Ensure Node/Edge properties are validated.
+2.  **RED:** Generate test in `tests/modules/analysis`. Assert missing graph label/property.
+3.  **GREEN:** Implement logic in `src/modules/analysis`. Mock Neo4j driver in unit tests.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-ANA ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 6 - COHERENCE ENGINE SPECIALIST (CRITICAL)
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Coherence Module Lead**.
+* **CRITICAL:** Read `agents.md`. Adhere to the 6-Category Model (SCOPE, BUDGET, TIME, TECH, LEGAL, QUALITY).
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Setup:** `TS-UD-COH-CAT-001` (Enums/Weights).
+* **Rules:** `TS-UD-COH-RUL-001` to `006` (All Categories).
+* **Scoring:** `TS-UD-COH-SCR-001` to `003` (Calculator).
+* **Gaming:** `TS-UD-COH-GAM-001` (Anti-Gaming Policy).
+* **Mapping:** `TS-UD-COH-ALR-001` (Alert Mapping).
+* **Use Cases:** `TS-UA-COH-UC-*`.
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify logic for specific Rules (e.g., R11, R6).
+2.  **RED:** Generate test in `tests/modules/coherence`. Assert score calculation error.
+3.  **GREEN:** Implement logic in `src/modules/coherence`. Use pure functions for rules.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-COH ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 7 - STAKEHOLDERS SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Stakeholders Module Lead**.
+* **CRITICAL:** Read `agents.md`.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Entities:** `TS-UD-STK-ENT-001` &amp; `MAP-001`.
+* **Classification:** `TS-UD-STK-CLS-001` &amp; `002` (Power/Interest).
+* **RACI:** `TS-UD-STK-RAC-001` to `003` (Matrix Generation).
+* **Use Cases:** `TS-UA-STK-UC-*`.
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify RACI matrix dimensions/roles.
+2.  **RED:** Generate test in `tests/modules/stakeholders`. Assert invalid RACI assignment.
+3.  **GREEN:** Implement logic in `src/modules/stakeholders`.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UD-STK ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 8 - ASYNC ARCHITECTURE SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Async Infrastructure Lead**.
+* **CRITICAL:** Read `agents.md`.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Event Bus:** `TS-INT-EVT-BUS-001` (Redis Pub/Sub).
+* **Celery:** `TS-INT-EVT-CEL-001` (Jobs).
+* **Resilience:** `TS-INT-EVT-DLQ-001` (Dead Letter Queue).
+* **E2E Async:** `TS-E2E-*` (Specific async flows).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Use `pytest-asyncio` and `testcontainers`.
+2.  **RED:** Generate test in `tests/infrastructure/events`. Assert message not received.
+3.  **GREEN:** Implement adapters in `src/core/events` or `src/adapters`.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-INT-EVT ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 9 - OBSERVABILITY SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Observability Lead**.
+* **CRITICAL:** Read `agents.md`.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Budget:** `TS-UA-SVC-BDG-001` (Tracking &amp; Circuit Breaker).
+* **Logging/Tracing:** Tests related to `core/observability` (mapped to generic infra suites or implicitly required).
+* **Monitoring:** Dashboard Data Logic.
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify Structlog/OpenTelemetry mocks.
+2.  **RED:** Generate test asserting missing trace_id or budget overflow.
+3.  **GREEN:** Implement interceptors/services in `src/core/observability`.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a ID (e.g., TS-UA-SVC-BDG-001).</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 10 - API CONTRACTS SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **API Layer Lead**.
+* **CRITICAL:** Read `agents.md`. Routers must be THIN.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **DTOs:** `TS-UA-DTO-ALL-001` &amp; `SER-001` (Validation).
+* **HTTP:** `TS-UAD-HTTP-RTR-001` (Routers).
+* **Middleware:** `TS-UAD-HTTP-MDW-001` (Auth/Tenant).
+* **Errors:** `TS-UAD-HTTP-ERR-001` (Handlers).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Verify serialization and HTTP codes.
+2.  **RED:** Generate test using `TestClient`. Assert 400/404/422 responses.
+3.  **GREEN:** Implement Routers/DTOs in `src/.../adapters/http` or `application/dtos`.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-UA-DTO or TS-UAD-HTTP ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 11 - INTEGRATION SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **Integration Architect**.
+* **CRITICAL:** Read `agents.md`. Verify Boundaries.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Cross-Module:** `TS-INT-MOD-WBS-001`, `DOC-001`, `ANA-001`, `STK-001`.
+* **External:** `TS-INT-EXT-LLM-001/002` (LLM Clients).
+* **Database:** `TS-INT-DB-*` (Repositories) &amp; `TS-INT-GRP-NEO-001`.
+* **Adapters:** `TS-UAD-PER-*` (Persistence Generic).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Use `Testcontainers` for DB tests.
+2.  **RED:** Generate integration test ensuring data persistence or event flow.
+3.  **GREEN:** Implement Repositories or Integration Adapters.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-INT ID.</t>
+  </si>
+  <si>
+    <t>**SYSTEM ROLE:** AGENT 12 - QA &amp; E2E SPECIALIST
+**1. INITIALIZATION &amp; CONTEXT**
+You are the **QA Lead**.
+* **CRITICAL:** Read `agents.md`. Test the full system.
+* **LATENCY:** Output code directly.
+**2. ASSIGNED SCOPE (100% Match with Index)**
+You are responsible for the following components and Suite IDs:
+* **Flows:** `TS-E2E-FLW-DOC`, `ALR`, `BLK` (Business Flows).
+* **Security E2E:** `TS-E2E-SEC-TNT`, `MCP`.
+* **Errors:** `TS-E2E-ERR-TIM`, `CON`, `REC` (Resilience).
+* **Perf:** `TS-E2E-PER-LRG` (Performance).
+**3. EXECUTION PROTOCOL (SMART TDD)**
+1.  **ANALYZE:** Check if test exists. Simulate real user journeys.
+2.  **RED:** Generate E2E script (Pytest/Playwright). Assert flow completion.
+3.  **GREEN:** Fix underlying system issues or adjust logic to pass E2E.
+4.  **UPDATE:** Request update for `C2PRO_TDD_BACKLOG_v1.0.md`.
+**AWAITING INPUT:** Provide a TS-E2E ID.</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>claude</t>
   </si>
 </sst>
 </file>
@@ -2982,7 +3269,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3004,6 +3291,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3081,7 +3374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3129,8 +3422,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3438,7 +3738,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="19.149999999999999" customHeight="1"/>
   <cols>
@@ -3449,7 +3748,7 @@
     <col min="11" max="11" width="62.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.149999999999999" customHeight="1">
+    <row r="1" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3483,8 +3782,11 @@
       <c r="K1" s="3" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+      <c r="L1" s="20" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3519,7 +3821,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="3" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3554,7 +3856,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="4" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3589,7 +3891,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="5" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3624,7 +3926,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="6" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3659,7 +3961,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="7" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3694,7 +3996,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="8" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3729,7 +4031,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="9" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3764,7 +4066,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="10" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3799,7 +4101,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="11" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3834,7 +4136,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="12" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -3869,7 +4171,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="13" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -3904,7 +4206,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="14" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -3936,7 +4238,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="15" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -3968,7 +4270,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="16" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -4003,7 +4305,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="17" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -4035,7 +4337,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="18" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -4064,7 +4366,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="19" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4093,7 +4395,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="20" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4122,7 +4424,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="21" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4151,7 +4453,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="22" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4180,7 +4482,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="23" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -4215,7 +4517,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="24" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -4247,7 +4549,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="25" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4276,7 +4578,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="26" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -4305,7 +4607,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="27" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -4334,7 +4636,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="28" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -4369,7 +4671,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="29" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -4398,7 +4700,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="30" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -4427,7 +4729,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="31" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -4456,7 +4758,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="32" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4485,7 +4787,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="33" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -4514,7 +4816,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="34" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -4546,7 +4848,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="35" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -4578,7 +4880,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="36" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -4610,7 +4912,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="37" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -4642,7 +4944,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="38" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -4674,7 +4976,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="39" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -4709,7 +5011,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="40" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -4738,7 +5040,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="41" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -4767,7 +5069,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="42" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -4796,7 +5098,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="43" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -4825,7 +5127,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="44" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -4854,7 +5156,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="45" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -4883,7 +5185,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="46" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -4912,7 +5214,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="47" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -4947,7 +5249,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="48" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -4976,7 +5278,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="49" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -5005,7 +5307,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="50" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -5034,7 +5336,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="51" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -5063,7 +5365,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="52" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -5092,7 +5394,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="53" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -5121,7 +5423,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="54" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -5150,7 +5452,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="55" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -5179,7 +5481,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="56" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -5208,7 +5510,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="57" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -5237,7 +5539,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="58" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -5266,7 +5568,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="59" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -5295,7 +5597,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="60" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -5324,7 +5626,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="61" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -5353,7 +5655,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="62" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -5382,7 +5684,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="63" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -5411,7 +5713,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="64" spans="1:9" ht="19.149999999999999" customHeight="1">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -5440,7 +5742,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="65" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -5469,7 +5771,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="66" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -5498,7 +5800,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="67" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -5527,7 +5829,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="68" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -5556,7 +5858,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="69" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -5585,7 +5887,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="70" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -5614,7 +5916,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="71" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -5643,7 +5945,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="72" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -5678,7 +5980,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="73" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -5713,7 +6015,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="74" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -5748,7 +6050,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="75" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -5780,7 +6082,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="76" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -5809,7 +6111,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="77" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -5844,7 +6146,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="78" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -5946,24 +6248,24 @@
         <v>802</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="81" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="B81" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G81" t="s">
         <v>407</v>
@@ -5974,28 +6276,25 @@
       <c r="I81" t="s">
         <v>381</v>
       </c>
-      <c r="J81" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="K81" s="2" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="82" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="D82" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F82" t="s">
         <v>353</v>
@@ -6010,7 +6309,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="83" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -6044,25 +6343,28 @@
       <c r="K83" s="2" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+      <c r="L83" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F84" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G84" t="s">
         <v>407</v>
@@ -6074,7 +6376,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="85" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -6106,24 +6408,24 @@
         <v>794</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="86" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D86" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F86" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G86" t="s">
         <v>407</v>
@@ -6138,7 +6440,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="87" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -6167,24 +6469,24 @@
         <v>381</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="88" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C88" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F88" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G88" t="s">
         <v>407</v>
@@ -6196,24 +6498,24 @@
         <v>381</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="89" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C89" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F89" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G89" t="s">
         <v>407</v>
@@ -6225,7 +6527,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="90" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -6260,7 +6562,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="91" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -6292,7 +6594,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="92" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -6324,7 +6626,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="93" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -6353,7 +6655,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="94" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -6385,7 +6687,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="95" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -6420,21 +6722,21 @@
         <v>408</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="96" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B96" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D96" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F96" t="s">
         <v>353</v>
@@ -6449,24 +6751,24 @@
         <v>381</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="97" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C97" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F97" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G97" t="s">
         <v>407</v>
@@ -6477,22 +6779,28 @@
       <c r="I97" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+      <c r="J97" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="L97" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C98" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F98" t="s">
         <v>353</v>
@@ -6506,8 +6814,11 @@
       <c r="I98" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+      <c r="L98" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -6539,7 +6850,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="100" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -6571,7 +6882,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="101" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -6600,7 +6911,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="102" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -6632,7 +6943,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="103" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -6667,7 +6978,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="104" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -6696,7 +7007,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="105" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -6824,7 +7135,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="109" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -6859,7 +7170,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="110" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -6894,7 +7205,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="111" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -6929,7 +7240,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="112" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -6958,7 +7269,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="19.149999999999999" hidden="1" customHeight="1">
+    <row r="113" spans="1:11" ht="19.149999999999999" customHeight="1">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -7021,9 +7332,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J114" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters blank="1"/>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A81:J98">
+      <sortCondition ref="B1:B114"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7060,7 +7371,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P404"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -7100,7 +7410,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="2" spans="1:9" ht="31.5" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -7125,7 +7435,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="3" spans="1:9" ht="31.5" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>119</v>
       </c>
@@ -7150,7 +7460,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="4" spans="1:9" ht="31.5" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -7175,7 +7485,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="46.5" hidden="1" thickBot="1">
+    <row r="5" spans="1:9" ht="46.5" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -7200,7 +7510,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="6" spans="1:9" ht="31.5" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>119</v>
       </c>
@@ -7225,7 +7535,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="7" spans="1:9" ht="31.5" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -7250,7 +7560,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="8" spans="1:9" ht="31.5" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
@@ -7275,7 +7585,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="9" spans="1:9" ht="31.5" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -7300,7 +7610,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="10" spans="1:9" ht="31.5" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>119</v>
       </c>
@@ -7325,7 +7635,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="11" spans="1:9" ht="31.5" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
@@ -7350,7 +7660,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="12" spans="1:9" ht="31.5" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>119</v>
       </c>
@@ -7375,7 +7685,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="13" spans="1:9" ht="31.5" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>119</v>
       </c>
@@ -7400,7 +7710,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="14" spans="1:9" ht="31.5" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -7425,7 +7735,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="15" spans="1:9" ht="31.5" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
@@ -7450,7 +7760,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="31.5" hidden="1" thickBot="1">
+    <row r="16" spans="1:9" ht="31.5" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>119</v>
       </c>
@@ -7475,7 +7785,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="17" spans="1:16" ht="31.5" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
@@ -7500,7 +7810,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="46.5" hidden="1" thickBot="1">
+    <row r="18" spans="1:16" ht="46.5" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
@@ -7525,7 +7835,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="19" spans="1:16" ht="31.5" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>119</v>
       </c>
@@ -7550,7 +7860,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="20" spans="1:16" ht="31.5" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -7575,7 +7885,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="21" spans="1:16" ht="31.5" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>119</v>
       </c>
@@ -7600,7 +7910,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="22" spans="1:16" ht="31.5" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>119</v>
       </c>
@@ -7625,7 +7935,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="23" spans="1:16" ht="31.5" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -7650,7 +7960,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="24" spans="1:16" ht="31.5" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -7682,7 +7992,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="25" spans="1:16" ht="31.5" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>120</v>
       </c>
@@ -7714,7 +8024,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="26" spans="1:16" ht="31.5" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>120</v>
       </c>
@@ -7746,7 +8056,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="27" spans="1:16" ht="31.5" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>120</v>
       </c>
@@ -7778,7 +8088,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="28" spans="1:16" ht="31.5" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>120</v>
       </c>
@@ -7810,7 +8120,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="29" spans="1:16" ht="31.5" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>120</v>
       </c>
@@ -7842,7 +8152,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="30" spans="1:16" ht="31.5" thickBot="1">
       <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
@@ -7874,7 +8184,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="31" spans="1:16" ht="31.5" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
@@ -7906,7 +8216,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="32" spans="1:16" ht="31.5" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
@@ -7938,7 +8248,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="33" spans="1:16" ht="31.5" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>120</v>
       </c>
@@ -7970,7 +8280,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="34" spans="1:16" ht="31.5" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -8002,7 +8312,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="35" spans="1:16" ht="31.5" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>120</v>
       </c>
@@ -8034,7 +8344,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="36" spans="1:16" ht="31.5" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -8066,7 +8376,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="37" spans="1:16" ht="31.5" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>120</v>
       </c>
@@ -8098,7 +8408,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="38" spans="1:16" ht="31.5" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>120</v>
       </c>
@@ -8130,7 +8440,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="39" spans="1:16" ht="31.5" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
@@ -8162,7 +8472,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="31.5" hidden="1" thickBot="1">
+    <row r="40" spans="1:16" ht="31.5" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>120</v>
       </c>
@@ -16727,11 +17037,7 @@
       <c r="F404" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I404" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
-    <filterColumn colId="7">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I404" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16759,124 +17065,263 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAF9D8E-5017-468F-8689-A64B44F82814}">
-  <dimension ref="E5:F28"/>
+  <dimension ref="B2:D43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="85.140625" customWidth="1"/>
+    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="178.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="5:6">
-      <c r="E5" s="16" t="s">
+    <row r="2" spans="2:3">
+      <c r="B2" s="16" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="6" spans="5:6" ht="201" customHeight="1">
-      <c r="E6" s="16" t="s">
+    <row r="3" spans="2:3" ht="201" customHeight="1">
+      <c r="B3" s="16" t="s">
         <v>813</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="7" spans="5:6">
-      <c r="E7" s="16" t="s">
+    <row r="4" spans="2:3">
+      <c r="B4" s="16" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="8" spans="5:6">
-      <c r="E8" s="16" t="s">
+    <row r="5" spans="2:3">
+      <c r="B5" s="16" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="9" spans="5:6">
-      <c r="E9" s="17"/>
-    </row>
-    <row r="10" spans="5:6">
-      <c r="E10" s="16" t="s">
+    <row r="6" spans="2:3">
+      <c r="B6" s="17"/>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" s="16" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="11" spans="5:6">
-      <c r="E11" s="16" t="s">
+    <row r="8" spans="2:3">
+      <c r="B8" s="16" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="12" spans="5:6">
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" spans="5:6">
-      <c r="E13" s="16" t="s">
+    <row r="9" spans="2:3">
+      <c r="B9" s="17"/>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="16" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="14" spans="5:6">
-      <c r="E14" s="16" t="s">
+    <row r="11" spans="2:3">
+      <c r="B11" s="16" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="15" spans="5:6">
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" spans="5:6">
-      <c r="E16" s="16" t="s">
+    <row r="12" spans="2:3">
+      <c r="B12" s="17"/>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" s="16" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="17" spans="5:5">
-      <c r="E17" s="16" t="s">
+    <row r="14" spans="2:3">
+      <c r="B14" s="16" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="18" spans="5:5">
-      <c r="E18" s="16" t="s">
+    <row r="15" spans="2:3">
+      <c r="B15" s="16" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="19" spans="5:5">
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" spans="5:5">
-      <c r="E20" s="16" t="s">
+    <row r="16" spans="2:3">
+      <c r="B16" s="17"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="16" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="21" spans="5:5">
-      <c r="E21" s="16" t="s">
+    <row r="18" spans="2:4">
+      <c r="B18" s="16" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="22" spans="5:5">
-      <c r="E22" s="16" t="s">
+    <row r="19" spans="2:4">
+      <c r="B19" s="16" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="23" spans="5:5">
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" spans="5:5">
-      <c r="E24" s="16" t="s">
+    <row r="20" spans="2:4">
+      <c r="B20" s="17"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="16" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="25" spans="5:5">
-      <c r="E25" s="16" t="s">
+    <row r="22" spans="2:4">
+      <c r="B22" s="16" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="26" spans="5:5">
-      <c r="E26" s="16" t="s">
+    <row r="23" spans="2:4">
+      <c r="B23" s="16" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="27" spans="5:5">
-      <c r="E27" s="16" t="s">
+    <row r="24" spans="2:4">
+      <c r="B24" s="16" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="28" spans="5:5">
-      <c r="E28" s="16" t="s">
+    <row r="25" spans="2:4">
+      <c r="B25" s="16" t="s">
         <v>830</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B28" s="18" t="s">
+        <v>832</v>
+      </c>
+      <c r="C28" s="19"/>
+    </row>
+    <row r="29" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B29" s="18" t="s">
+        <v>833</v>
+      </c>
+      <c r="C29" s="19"/>
+    </row>
+    <row r="30" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B30" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B31" s="18" t="s">
+        <v>835</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B32" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B33" s="18" t="s">
+        <v>837</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B34" s="18" t="s">
+        <v>838</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B35" s="18" t="s">
+        <v>839</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B36" s="18" t="s">
+        <v>840</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B37" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B38" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B39" s="18" t="s">
+        <v>843</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B40" s="18" t="s">
+        <v>844</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B41" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B42" s="18" t="s">
+        <v>846</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B43" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" s="2" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA186636-5833-4748-8EC2-640B38F3A73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E2ED11-DD88-49A3-AD97-0E4F17FD7B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="863">
   <si>
     <t>Nº</t>
   </si>
@@ -3204,6 +3204,9 @@
   </si>
   <si>
     <t>claude</t>
+  </si>
+  <si>
+    <t>Claude</t>
   </si>
 </sst>
 </file>
@@ -3269,7 +3272,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3297,6 +3300,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3374,7 +3383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3432,6 +3441,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6439,6 +6452,9 @@
       <c r="K86" t="s">
         <v>795</v>
       </c>
+      <c r="L86" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="87" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A87" t="s">
@@ -6947,7 +6963,7 @@
       <c r="A103" t="s">
         <v>107</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="22" t="s">
         <v>220</v>
       </c>
       <c r="C103" t="s">
@@ -6976,6 +6992,9 @@
       </c>
       <c r="K103" s="10" t="s">
         <v>767</v>
+      </c>
+      <c r="L103" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="19.149999999999999" customHeight="1">
@@ -7371,7 +7390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
-  <dimension ref="A1:P404"/>
+  <dimension ref="A1:Q404"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -7381,11 +7400,12 @@
     <col min="5" max="5" width="17.7109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="50.5703125" customWidth="1"/>
     <col min="9" max="9" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" thickBot="1">
+    <row r="1" spans="1:11" ht="16.5" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>760</v>
       </c>
@@ -7409,8 +7429,14 @@
       <c r="I1" s="11" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J1" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="31.5" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -7434,8 +7460,14 @@
       <c r="I2" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="31.5" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>119</v>
       </c>
@@ -7459,8 +7491,11 @@
       <c r="I3" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="31.5" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -7484,8 +7519,11 @@
       <c r="I4" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="46.5" thickBot="1">
+      <c r="J4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="46.5" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -7509,8 +7547,11 @@
       <c r="I5" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="31.5" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>119</v>
       </c>
@@ -7534,8 +7575,11 @@
       <c r="I6" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="31.5" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -7559,8 +7603,11 @@
       <c r="I7" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="31.5" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
@@ -7584,8 +7631,11 @@
       <c r="I8" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="31.5" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -7609,8 +7659,11 @@
       <c r="I9" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J9" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="31.5" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>119</v>
       </c>
@@ -7634,8 +7687,11 @@
       <c r="I10" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="31.5" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
@@ -7659,8 +7715,11 @@
       <c r="I11" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="31.5" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>119</v>
       </c>
@@ -7684,8 +7743,11 @@
       <c r="I12" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="31.5" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>119</v>
       </c>
@@ -7709,8 +7771,11 @@
       <c r="I13" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="31.5" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -7734,8 +7799,11 @@
       <c r="I14" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J14" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="31.5" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
@@ -7759,8 +7827,11 @@
       <c r="I15" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="31.5" thickBot="1">
+      <c r="J15" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="31.5" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>119</v>
       </c>
@@ -7784,8 +7855,11 @@
       <c r="I16" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J16" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="31.5" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
@@ -7809,8 +7883,11 @@
       <c r="I17" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="46.5" thickBot="1">
+      <c r="J17" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="46.5" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
@@ -7834,8 +7911,11 @@
       <c r="I18" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J18" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="31.5" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>119</v>
       </c>
@@ -7859,8 +7939,11 @@
       <c r="I19" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="31.5" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -7884,8 +7967,11 @@
       <c r="I20" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="31.5" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>119</v>
       </c>
@@ -7909,8 +7995,11 @@
       <c r="I21" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J21" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="31.5" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>119</v>
       </c>
@@ -7934,8 +8023,11 @@
       <c r="I22" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J22" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="31.5" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -7959,8 +8051,11 @@
       <c r="I23" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="31.5" thickBot="1">
+      <c r="J23" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="31.5" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -7984,15 +8079,18 @@
       <c r="I24" t="s">
         <v>774</v>
       </c>
-      <c r="J24" t="str">
+      <c r="J24" t="s">
+        <v>404</v>
+      </c>
+      <c r="K24" t="str">
         <f>CONCATENATE(A24,C24)</f>
         <v>TS-UC-SEC-MCP-002test_001_request_under_limit_allowed</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="31.5" thickBot="1">
+    <row r="25" spans="1:17" ht="31.5" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>120</v>
       </c>
@@ -8016,15 +8114,18 @@
       <c r="I25" t="s">
         <v>774</v>
       </c>
-      <c r="J25" t="str">
-        <f t="shared" ref="J25:J88" si="0">CONCATENATE(A25,C25)</f>
+      <c r="J25" t="s">
+        <v>404</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" ref="K25:K88" si="0">CONCATENATE(A25,C25)</f>
         <v>TS-UC-SEC-MCP-002test_002_request_at_limit_59_allowed</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="31.5" thickBot="1">
+    <row r="26" spans="1:17" ht="31.5" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>120</v>
       </c>
@@ -8048,15 +8149,18 @@
       <c r="I26" t="s">
         <v>774</v>
       </c>
-      <c r="J26" t="str">
+      <c r="J26" t="s">
+        <v>404</v>
+      </c>
+      <c r="K26" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_003_request_at_limit_60_allowed</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="31.5" thickBot="1">
+    <row r="27" spans="1:17" ht="31.5" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>120</v>
       </c>
@@ -8080,15 +8184,18 @@
       <c r="I27" t="s">
         <v>774</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J27" t="s">
+        <v>404</v>
+      </c>
+      <c r="K27" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_004_request_over_limit_61_blocked</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="31.5" thickBot="1">
+    <row r="28" spans="1:17" ht="31.5" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>120</v>
       </c>
@@ -8112,15 +8219,18 @@
       <c r="I28" t="s">
         <v>774</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J28" t="s">
+        <v>404</v>
+      </c>
+      <c r="K28" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_005_request_over_limit_100_blocked</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="31.5" thickBot="1">
+    <row r="29" spans="1:17" ht="31.5" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>120</v>
       </c>
@@ -8144,15 +8254,18 @@
       <c r="I29" t="s">
         <v>774</v>
       </c>
-      <c r="J29" t="str">
+      <c r="J29" t="s">
+        <v>404</v>
+      </c>
+      <c r="K29" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_006_window_reset_after_60_seconds</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="31.5" thickBot="1">
+    <row r="30" spans="1:17" ht="31.5" thickBot="1">
       <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
@@ -8176,15 +8289,18 @@
       <c r="I30" t="s">
         <v>774</v>
       </c>
-      <c r="J30" t="str">
+      <c r="J30" t="s">
+        <v>404</v>
+      </c>
+      <c r="K30" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_007_tenant_isolation_separate_counters</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="31.5" thickBot="1">
+    <row r="31" spans="1:17" ht="31.5" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
@@ -8208,15 +8324,18 @@
       <c r="I31" t="s">
         <v>774</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J31" t="s">
+        <v>404</v>
+      </c>
+      <c r="K31" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_008_tenant_a_full_tenant_b_available</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="31.5" thickBot="1">
+    <row r="32" spans="1:17" ht="31.5" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
@@ -8240,15 +8359,18 @@
       <c r="I32" t="s">
         <v>774</v>
       </c>
-      <c r="J32" t="str">
+      <c r="J32" t="s">
+        <v>404</v>
+      </c>
+      <c r="K32" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_009_sliding_window_calculation</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="31.5" thickBot="1">
+    <row r="33" spans="1:17" ht="31.5" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>120</v>
       </c>
@@ -8272,15 +8394,18 @@
       <c r="I33" t="s">
         <v>774</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J33" t="s">
+        <v>404</v>
+      </c>
+      <c r="K33" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_010_rate_limit_result_retry_after_header</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="31.5" thickBot="1">
+    <row r="34" spans="1:17" ht="31.5" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -8304,15 +8429,18 @@
       <c r="I34" t="s">
         <v>774</v>
       </c>
-      <c r="J34" t="str">
+      <c r="J34" t="s">
+        <v>404</v>
+      </c>
+      <c r="K34" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_011_rate_limit_audit_log_on_block</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="31.5" thickBot="1">
+    <row r="35" spans="1:17" ht="31.5" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>120</v>
       </c>
@@ -8336,15 +8464,18 @@
       <c r="I35" t="s">
         <v>774</v>
       </c>
-      <c r="J35" t="str">
+      <c r="J35" t="s">
+        <v>404</v>
+      </c>
+      <c r="K35" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_012_rate_limit_warning_at_80_percent</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="31.5" thickBot="1">
+    <row r="36" spans="1:17" ht="31.5" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -8368,15 +8499,18 @@
       <c r="I36" t="s">
         <v>774</v>
       </c>
-      <c r="J36" t="str">
+      <c r="J36" t="s">
+        <v>404</v>
+      </c>
+      <c r="K36" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_013_concurrent_requests_race_condition</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="31.5" thickBot="1">
+    <row r="37" spans="1:17" ht="31.5" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>120</v>
       </c>
@@ -8400,15 +8534,18 @@
       <c r="I37" t="s">
         <v>774</v>
       </c>
-      <c r="J37" t="str">
+      <c r="J37" t="s">
+        <v>404</v>
+      </c>
+      <c r="K37" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_014_rate_limit_reset_at_midnight</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="31.5" thickBot="1">
+    <row r="38" spans="1:17" ht="31.5" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>120</v>
       </c>
@@ -8432,15 +8569,18 @@
       <c r="I38" t="s">
         <v>774</v>
       </c>
-      <c r="J38" t="str">
+      <c r="J38" t="s">
+        <v>404</v>
+      </c>
+      <c r="K38" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_edge_001_burst_59_requests_simultaneous</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="31.5" thickBot="1">
+    <row r="39" spans="1:17" ht="31.5" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
@@ -8464,15 +8604,18 @@
       <c r="I39" t="s">
         <v>774</v>
       </c>
-      <c r="J39" t="str">
+      <c r="J39" t="s">
+        <v>404</v>
+      </c>
+      <c r="K39" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_edge_002_exactly_60_second_boundary</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="31.5" thickBot="1">
+    <row r="40" spans="1:17" ht="31.5" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>120</v>
       </c>
@@ -8496,15 +8639,18 @@
       <c r="I40" t="s">
         <v>774</v>
       </c>
-      <c r="J40" t="str">
+      <c r="J40" t="s">
+        <v>404</v>
+      </c>
+      <c r="K40" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-002test_edge_003_clock_skew_handling</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="31.5" thickBot="1">
+    <row r="41" spans="1:17" ht="31.5" thickBot="1">
       <c r="A41" s="6" t="s">
         <v>121</v>
       </c>
@@ -8528,12 +8674,15 @@
       <c r="I41" t="s">
         <v>796</v>
       </c>
-      <c r="J41" t="str">
+      <c r="J41" t="s">
+        <v>404</v>
+      </c>
+      <c r="K41" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_001_query_under_5s_allowed</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="31.5" thickBot="1">
+    <row r="42" spans="1:17" ht="31.5" thickBot="1">
       <c r="A42" s="6" t="s">
         <v>121</v>
       </c>
@@ -8557,12 +8706,15 @@
       <c r="I42" t="s">
         <v>796</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J42" t="s">
+        <v>404</v>
+      </c>
+      <c r="K42" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_002_query_at_5s_allowed</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="31.5" thickBot="1">
+    <row r="43" spans="1:17" ht="31.5" thickBot="1">
       <c r="A43" s="6" t="s">
         <v>121</v>
       </c>
@@ -8586,12 +8738,15 @@
       <c r="I43" t="s">
         <v>796</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J43" t="s">
+        <v>404</v>
+      </c>
+      <c r="K43" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_003_query_over_5s_timeout_cancelled</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="31.5" thickBot="1">
+    <row r="44" spans="1:17" ht="31.5" thickBot="1">
       <c r="A44" s="6" t="s">
         <v>121</v>
       </c>
@@ -8615,12 +8770,15 @@
       <c r="I44" t="s">
         <v>796</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J44" t="s">
+        <v>404</v>
+      </c>
+      <c r="K44" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_004_query_result_under_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="31.5" thickBot="1">
+    <row r="45" spans="1:17" ht="31.5" thickBot="1">
       <c r="A45" s="6" t="s">
         <v>121</v>
       </c>
@@ -8644,12 +8802,15 @@
       <c r="I45" t="s">
         <v>796</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J45" t="s">
+        <v>404</v>
+      </c>
+      <c r="K45" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_005_query_result_at_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="31.5" thickBot="1">
+    <row r="46" spans="1:17" ht="31.5" thickBot="1">
       <c r="A46" s="6" t="s">
         <v>121</v>
       </c>
@@ -8673,12 +8834,15 @@
       <c r="I46" t="s">
         <v>796</v>
       </c>
-      <c r="J46" t="str">
+      <c r="J46" t="s">
+        <v>404</v>
+      </c>
+      <c r="K46" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_006_query_result_over_1000_rows_truncated</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="31.5" thickBot="1">
+    <row r="47" spans="1:17" ht="31.5" thickBot="1">
       <c r="A47" s="6" t="s">
         <v>121</v>
       </c>
@@ -8702,12 +8866,15 @@
       <c r="I47" t="s">
         <v>796</v>
       </c>
-      <c r="J47" t="str">
+      <c r="J47" t="s">
+        <v>404</v>
+      </c>
+      <c r="K47" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_007_query_result_truncated_flag_set</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="31.5" thickBot="1">
+    <row r="48" spans="1:17" ht="31.5" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>121</v>
       </c>
@@ -8731,12 +8898,15 @@
       <c r="I48" t="s">
         <v>796</v>
       </c>
-      <c r="J48" t="str">
+      <c r="J48" t="s">
+        <v>404</v>
+      </c>
+      <c r="K48" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_008_timeout_returns_partial_results</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="31.5" thickBot="1">
+    <row r="49" spans="1:11" ht="31.5" thickBot="1">
       <c r="A49" s="6" t="s">
         <v>121</v>
       </c>
@@ -8760,12 +8930,15 @@
       <c r="I49" t="s">
         <v>796</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J49" t="s">
+        <v>404</v>
+      </c>
+      <c r="K49" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_009_timeout_audit_log_created</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="31.5" thickBot="1">
+    <row r="50" spans="1:11" ht="31.5" thickBot="1">
       <c r="A50" s="6" t="s">
         <v>121</v>
       </c>
@@ -8789,12 +8962,15 @@
       <c r="I50" t="s">
         <v>796</v>
       </c>
-      <c r="J50" t="str">
+      <c r="J50" t="s">
+        <v>404</v>
+      </c>
+      <c r="K50" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_010_row_limit_audit_log_created</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="31.5" thickBot="1">
+    <row r="51" spans="1:11" ht="31.5" thickBot="1">
       <c r="A51" s="6" t="s">
         <v>121</v>
       </c>
@@ -8818,12 +8994,15 @@
       <c r="I51" t="s">
         <v>796</v>
       </c>
-      <c r="J51" t="str">
+      <c r="J51" t="s">
+        <v>404</v>
+      </c>
+      <c r="K51" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_011_combined_timeout_and_row_limit</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="31.5" thickBot="1">
+    <row r="52" spans="1:11" ht="31.5" thickBot="1">
       <c r="A52" s="6" t="s">
         <v>121</v>
       </c>
@@ -8847,12 +9026,15 @@
       <c r="I52" t="s">
         <v>796</v>
       </c>
-      <c r="J52" t="str">
+      <c r="J52" t="s">
+        <v>404</v>
+      </c>
+      <c r="K52" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_012_query_limit_config_per_tenant</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="31.5" thickBot="1">
+    <row r="53" spans="1:11" ht="31.5" thickBot="1">
       <c r="A53" s="6" t="s">
         <v>121</v>
       </c>
@@ -8876,12 +9058,15 @@
       <c r="I53" t="s">
         <v>796</v>
       </c>
-      <c r="J53" t="str">
+      <c r="J53" t="s">
+        <v>404</v>
+      </c>
+      <c r="K53" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_edge_001_exactly_1000_rows</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="31.5" thickBot="1">
+    <row r="54" spans="1:11" ht="31.5" thickBot="1">
       <c r="A54" s="6" t="s">
         <v>121</v>
       </c>
@@ -8905,12 +9090,15 @@
       <c r="I54" t="s">
         <v>796</v>
       </c>
-      <c r="J54" t="str">
+      <c r="J54" t="s">
+        <v>404</v>
+      </c>
+      <c r="K54" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_edge_002_empty_result_set</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="31.5" thickBot="1">
+    <row r="55" spans="1:11" ht="31.5" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>121</v>
       </c>
@@ -8934,12 +9122,15 @@
       <c r="I55" t="s">
         <v>796</v>
       </c>
-      <c r="J55" t="str">
+      <c r="J55" t="s">
+        <v>404</v>
+      </c>
+      <c r="K55" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-MCP-003test_edge_003_streaming_query_timeout</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="31.5" thickBot="1">
+    <row r="56" spans="1:11" ht="31.5" thickBot="1">
       <c r="A56" s="6" t="s">
         <v>123</v>
       </c>
@@ -8963,12 +9154,15 @@
       <c r="I56" t="s">
         <v>774</v>
       </c>
-      <c r="J56" t="str">
+      <c r="J56" t="s">
+        <v>404</v>
+      </c>
+      <c r="K56" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_001_detect_dni_valid_12345678Z</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="31.5" thickBot="1">
+    <row r="57" spans="1:11" ht="31.5" thickBot="1">
       <c r="A57" s="6" t="s">
         <v>123</v>
       </c>
@@ -8992,12 +9186,15 @@
       <c r="I57" t="s">
         <v>774</v>
       </c>
-      <c r="J57" t="str">
+      <c r="J57" t="s">
+        <v>404</v>
+      </c>
+      <c r="K57" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_002_detect_dni_valid_87654321X</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="31.5" thickBot="1">
+    <row r="58" spans="1:11" ht="31.5" thickBot="1">
       <c r="A58" s="6" t="s">
         <v>123</v>
       </c>
@@ -9021,12 +9218,15 @@
       <c r="I58" t="s">
         <v>774</v>
       </c>
-      <c r="J58" t="str">
+      <c r="J58" t="s">
+        <v>404</v>
+      </c>
+      <c r="K58" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_003_detect_dni_invalid_length_9_digits</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="31.5" thickBot="1">
+    <row r="59" spans="1:11" ht="31.5" thickBot="1">
       <c r="A59" s="6" t="s">
         <v>123</v>
       </c>
@@ -9050,12 +9250,15 @@
       <c r="I59" t="s">
         <v>774</v>
       </c>
-      <c r="J59" t="str">
+      <c r="J59" t="s">
+        <v>404</v>
+      </c>
+      <c r="K59" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_004_detect_dni_invalid_length_7_digits</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="31.5" thickBot="1">
+    <row r="60" spans="1:11" ht="31.5" thickBot="1">
       <c r="A60" s="6" t="s">
         <v>123</v>
       </c>
@@ -9079,12 +9282,15 @@
       <c r="I60" t="s">
         <v>774</v>
       </c>
-      <c r="J60" t="str">
+      <c r="J60" t="s">
+        <v>404</v>
+      </c>
+      <c r="K60" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_005_detect_dni_invalid_letter_checksum</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="31.5" thickBot="1">
+    <row r="61" spans="1:11" ht="31.5" thickBot="1">
       <c r="A61" s="6" t="s">
         <v>123</v>
       </c>
@@ -9108,12 +9314,15 @@
       <c r="I61" t="s">
         <v>774</v>
       </c>
-      <c r="J61" t="str">
+      <c r="J61" t="s">
+        <v>404</v>
+      </c>
+      <c r="K61" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_006_detect_multiple_dnis_in_text</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="31.5" thickBot="1">
+    <row r="62" spans="1:11" ht="31.5" thickBot="1">
       <c r="A62" s="6" t="s">
         <v>123</v>
       </c>
@@ -9137,12 +9346,15 @@
       <c r="I62" t="s">
         <v>774</v>
       </c>
-      <c r="J62" t="str">
+      <c r="J62" t="s">
+        <v>404</v>
+      </c>
+      <c r="K62" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_007_detect_email_simple</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="31.5" thickBot="1">
+    <row r="63" spans="1:11" ht="31.5" thickBot="1">
       <c r="A63" s="6" t="s">
         <v>123</v>
       </c>
@@ -9166,12 +9378,15 @@
       <c r="I63" t="s">
         <v>774</v>
       </c>
-      <c r="J63" t="str">
+      <c r="J63" t="s">
+        <v>404</v>
+      </c>
+      <c r="K63" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_008_detect_email_with_subdomain</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="31.5" thickBot="1">
+    <row r="64" spans="1:11" ht="31.5" thickBot="1">
       <c r="A64" s="6" t="s">
         <v>123</v>
       </c>
@@ -9195,12 +9410,15 @@
       <c r="I64" t="s">
         <v>774</v>
       </c>
-      <c r="J64" t="str">
+      <c r="J64" t="s">
+        <v>404</v>
+      </c>
+      <c r="K64" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_009_detect_email_with_plus_sign</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="31.5" thickBot="1">
+    <row r="65" spans="1:11" ht="31.5" thickBot="1">
       <c r="A65" s="6" t="s">
         <v>123</v>
       </c>
@@ -9224,12 +9442,15 @@
       <c r="I65" t="s">
         <v>774</v>
       </c>
-      <c r="J65" t="str">
+      <c r="J65" t="s">
+        <v>404</v>
+      </c>
+      <c r="K65" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_010_detect_email_invalid_no_at</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="31.5" thickBot="1">
+    <row r="66" spans="1:11" ht="31.5" thickBot="1">
       <c r="A66" s="6" t="s">
         <v>123</v>
       </c>
@@ -9253,12 +9474,15 @@
       <c r="I66" t="s">
         <v>774</v>
       </c>
-      <c r="J66" t="str">
+      <c r="J66" t="s">
+        <v>404</v>
+      </c>
+      <c r="K66" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_011_detect_multiple_emails_in_text</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="31.5" thickBot="1">
+    <row r="67" spans="1:11" ht="31.5" thickBot="1">
       <c r="A67" s="6" t="s">
         <v>123</v>
       </c>
@@ -9282,12 +9506,15 @@
       <c r="I67" t="s">
         <v>774</v>
       </c>
-      <c r="J67" t="str">
+      <c r="J67" t="s">
+        <v>404</v>
+      </c>
+      <c r="K67" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_012_detect_phone_mobile_612345678</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="31.5" thickBot="1">
+    <row r="68" spans="1:11" ht="31.5" thickBot="1">
       <c r="A68" s="6" t="s">
         <v>123</v>
       </c>
@@ -9311,12 +9538,15 @@
       <c r="I68" t="s">
         <v>774</v>
       </c>
-      <c r="J68" t="str">
+      <c r="J68" t="s">
+        <v>404</v>
+      </c>
+      <c r="K68" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_013_detect_phone_mobile_with_prefix_34</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="31.5" thickBot="1">
+    <row r="69" spans="1:11" ht="31.5" thickBot="1">
       <c r="A69" s="6" t="s">
         <v>123</v>
       </c>
@@ -9340,12 +9570,15 @@
       <c r="I69" t="s">
         <v>774</v>
       </c>
-      <c r="J69" t="str">
+      <c r="J69" t="s">
+        <v>404</v>
+      </c>
+      <c r="K69" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_014_detect_phone_landline_912345678</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="31.5" thickBot="1">
+    <row r="70" spans="1:11" ht="31.5" thickBot="1">
       <c r="A70" s="6" t="s">
         <v>123</v>
       </c>
@@ -9369,12 +9602,15 @@
       <c r="I70" t="s">
         <v>774</v>
       </c>
-      <c r="J70" t="str">
+      <c r="J70" t="s">
+        <v>404</v>
+      </c>
+      <c r="K70" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_015_detect_phone_invalid_short</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="31.5" thickBot="1">
+    <row r="71" spans="1:11" ht="31.5" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>123</v>
       </c>
@@ -9398,12 +9634,15 @@
       <c r="I71" t="s">
         <v>774</v>
       </c>
-      <c r="J71" t="str">
+      <c r="J71" t="s">
+        <v>404</v>
+      </c>
+      <c r="K71" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_016_detect_multiple_phones_in_text</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="31.5" thickBot="1">
+    <row r="72" spans="1:11" ht="31.5" thickBot="1">
       <c r="A72" s="6" t="s">
         <v>123</v>
       </c>
@@ -9427,12 +9666,15 @@
       <c r="I72" t="s">
         <v>774</v>
       </c>
-      <c r="J72" t="str">
+      <c r="J72" t="s">
+        <v>404</v>
+      </c>
+      <c r="K72" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_017_detect_iban_spain_valid</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="31.5" thickBot="1">
+    <row r="73" spans="1:11" ht="31.5" thickBot="1">
       <c r="A73" s="6" t="s">
         <v>123</v>
       </c>
@@ -9456,12 +9698,15 @@
       <c r="I73" t="s">
         <v>774</v>
       </c>
-      <c r="J73" t="str">
+      <c r="J73" t="s">
+        <v>404</v>
+      </c>
+      <c r="K73" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_018_detect_iban_germany_valid</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="31.5" thickBot="1">
+    <row r="74" spans="1:11" ht="31.5" thickBot="1">
       <c r="A74" s="6" t="s">
         <v>123</v>
       </c>
@@ -9485,12 +9730,15 @@
       <c r="I74" t="s">
         <v>774</v>
       </c>
-      <c r="J74" t="str">
+      <c r="J74" t="s">
+        <v>404</v>
+      </c>
+      <c r="K74" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_019_detect_iban_invalid_checksum</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="31.5" thickBot="1">
+    <row r="75" spans="1:11" ht="31.5" thickBot="1">
       <c r="A75" s="6" t="s">
         <v>123</v>
       </c>
@@ -9514,12 +9762,15 @@
       <c r="I75" t="s">
         <v>774</v>
       </c>
-      <c r="J75" t="str">
+      <c r="J75" t="s">
+        <v>404</v>
+      </c>
+      <c r="K75" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_020_detect_iban_invalid_length</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="31.5" thickBot="1">
+    <row r="76" spans="1:11" ht="31.5" thickBot="1">
       <c r="A76" s="6" t="s">
         <v>123</v>
       </c>
@@ -9543,12 +9794,15 @@
       <c r="I76" t="s">
         <v>774</v>
       </c>
-      <c r="J76" t="str">
+      <c r="J76" t="s">
+        <v>404</v>
+      </c>
+      <c r="K76" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_021_detect_all_pii_types_in_document</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="31.5" thickBot="1">
+    <row r="77" spans="1:11" ht="31.5" thickBot="1">
       <c r="A77" s="6" t="s">
         <v>123</v>
       </c>
@@ -9572,12 +9826,15 @@
       <c r="I77" t="s">
         <v>774</v>
       </c>
-      <c r="J77" t="str">
+      <c r="J77" t="s">
+        <v>404</v>
+      </c>
+      <c r="K77" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_022_detect_no_pii_clean_document</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="31.5" thickBot="1">
+    <row r="78" spans="1:11" ht="31.5" thickBot="1">
       <c r="A78" s="6" t="s">
         <v>123</v>
       </c>
@@ -9601,12 +9858,15 @@
       <c r="I78" t="s">
         <v>774</v>
       </c>
-      <c r="J78" t="str">
+      <c r="J78" t="s">
+        <v>404</v>
+      </c>
+      <c r="K78" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_023_detect_pii_positions_returned</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="31.5" thickBot="1">
+    <row r="79" spans="1:11" ht="31.5" thickBot="1">
       <c r="A79" s="6" t="s">
         <v>123</v>
       </c>
@@ -9630,12 +9890,15 @@
       <c r="I79" t="s">
         <v>774</v>
       </c>
-      <c r="J79" t="str">
+      <c r="J79" t="s">
+        <v>404</v>
+      </c>
+      <c r="K79" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_024_detect_pii_counts_by_type</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="31.5" thickBot="1">
+    <row r="80" spans="1:11" ht="31.5" thickBot="1">
       <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
@@ -9659,12 +9922,15 @@
       <c r="I80" t="s">
         <v>774</v>
       </c>
-      <c r="J80" t="str">
+      <c r="J80" t="s">
+        <v>404</v>
+      </c>
+      <c r="K80" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_edge_001_pii_in_different_languages</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="31.5" thickBot="1">
+    <row r="81" spans="1:11" ht="31.5" thickBot="1">
       <c r="A81" s="6" t="s">
         <v>123</v>
       </c>
@@ -9688,12 +9954,15 @@
       <c r="I81" t="s">
         <v>774</v>
       </c>
-      <c r="J81" t="str">
+      <c r="J81" t="s">
+        <v>404</v>
+      </c>
+      <c r="K81" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_edge_002_pii_with_unicode_characters</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="31.5" thickBot="1">
+    <row r="82" spans="1:11" ht="31.5" thickBot="1">
       <c r="A82" s="6" t="s">
         <v>123</v>
       </c>
@@ -9708,12 +9977,15 @@
       <c r="F82" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="J82" t="str">
+      <c r="J82" t="s">
+        <v>404</v>
+      </c>
+      <c r="K82" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-001test_edge_003_pii_in_html_escaped_text</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="31.5" thickBot="1">
+    <row r="83" spans="1:11" ht="31.5" thickBot="1">
       <c r="A83" s="6" t="s">
         <v>124</v>
       </c>
@@ -9734,12 +10006,15 @@
       <c r="H83" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J83" t="str">
+      <c r="J83" t="s">
+        <v>404</v>
+      </c>
+      <c r="K83" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_001_redact_dni_to_redacted</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="31.5" thickBot="1">
+    <row r="84" spans="1:11" ht="31.5" thickBot="1">
       <c r="A84" s="6" t="s">
         <v>124</v>
       </c>
@@ -9760,12 +10035,15 @@
       <c r="H84" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J84" t="str">
+      <c r="J84" t="s">
+        <v>404</v>
+      </c>
+      <c r="K84" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_002_redact_email_to_redacted</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="31.5" thickBot="1">
+    <row r="85" spans="1:11" ht="31.5" thickBot="1">
       <c r="A85" s="6" t="s">
         <v>124</v>
       </c>
@@ -9786,12 +10064,15 @@
       <c r="H85" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J85" t="str">
+      <c r="J85" t="s">
+        <v>404</v>
+      </c>
+      <c r="K85" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_003_redact_phone_to_redacted</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="31.5" thickBot="1">
+    <row r="86" spans="1:11" ht="31.5" thickBot="1">
       <c r="A86" s="6" t="s">
         <v>124</v>
       </c>
@@ -9812,12 +10093,15 @@
       <c r="H86" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J86" t="str">
+      <c r="J86" t="s">
+        <v>404</v>
+      </c>
+      <c r="K86" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_004_redact_multiple_pii_all_redacted</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="31.5" thickBot="1">
+    <row r="87" spans="1:11" ht="31.5" thickBot="1">
       <c r="A87" s="6" t="s">
         <v>124</v>
       </c>
@@ -9838,12 +10122,15 @@
       <c r="H87" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J87" t="str">
+      <c r="J87" t="s">
+        <v>404</v>
+      </c>
+      <c r="K87" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_005_hash_dni_deterministic</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="31.5" thickBot="1">
+    <row r="88" spans="1:11" ht="31.5" thickBot="1">
       <c r="A88" s="6" t="s">
         <v>124</v>
       </c>
@@ -9864,12 +10151,15 @@
       <c r="H88" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J88" t="str">
+      <c r="J88" t="s">
+        <v>404</v>
+      </c>
+      <c r="K88" t="str">
         <f t="shared" si="0"/>
         <v>TS-UC-SEC-ANO-002test_006_hash_same_value_same_hash</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="31.5" thickBot="1">
+    <row r="89" spans="1:11" ht="31.5" thickBot="1">
       <c r="A89" s="6" t="s">
         <v>124</v>
       </c>
@@ -9890,12 +10180,15 @@
       <c r="H89" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J89" t="str">
-        <f t="shared" ref="J89:J152" si="1">CONCATENATE(A89,C89)</f>
+      <c r="J89" t="s">
+        <v>404</v>
+      </c>
+      <c r="K89" t="str">
+        <f t="shared" ref="K89:K152" si="1">CONCATENATE(A89,C89)</f>
         <v>TS-UC-SEC-ANO-002test_007_hash_different_values_different_hash</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="31.5" thickBot="1">
+    <row r="90" spans="1:11" ht="31.5" thickBot="1">
       <c r="A90" s="6" t="s">
         <v>124</v>
       </c>
@@ -9916,12 +10209,15 @@
       <c r="H90" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J90" t="str">
+      <c r="J90" t="s">
+        <v>404</v>
+      </c>
+      <c r="K90" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_008_hash_irreversible_validation</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="31.5" thickBot="1">
+    <row r="91" spans="1:11" ht="31.5" thickBot="1">
       <c r="A91" s="6" t="s">
         <v>124</v>
       </c>
@@ -9942,12 +10238,15 @@
       <c r="H91" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J91" t="str">
+      <c r="J91" t="s">
+        <v>404</v>
+      </c>
+      <c r="K91" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_009_pseudonymize_name_to_persona_001</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="31.5" thickBot="1">
+    <row r="92" spans="1:11" ht="31.5" thickBot="1">
       <c r="A92" s="6" t="s">
         <v>124</v>
       </c>
@@ -9968,12 +10267,15 @@
       <c r="H92" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J92" t="str">
+      <c r="J92" t="s">
+        <v>404</v>
+      </c>
+      <c r="K92" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_010_pseudonymize_consistent_same_name</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="46.5" thickBot="1">
+    <row r="93" spans="1:11" ht="46.5" thickBot="1">
       <c r="A93" s="6" t="s">
         <v>124</v>
       </c>
@@ -9994,12 +10296,15 @@
       <c r="H93" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J93" t="str">
+      <c r="J93" t="s">
+        <v>404</v>
+      </c>
+      <c r="K93" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_011_pseudonymize_different_names_different_ids</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="31.5" thickBot="1">
+    <row r="94" spans="1:11" ht="31.5" thickBot="1">
       <c r="A94" s="6" t="s">
         <v>124</v>
       </c>
@@ -10020,12 +10325,15 @@
       <c r="H94" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J94" t="str">
+      <c r="J94" t="s">
+        <v>404</v>
+      </c>
+      <c r="K94" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_012_pseudonymize_in_context_preserved</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="31.5" thickBot="1">
+    <row r="95" spans="1:11" ht="31.5" thickBot="1">
       <c r="A95" s="6" t="s">
         <v>124</v>
       </c>
@@ -10046,12 +10354,15 @@
       <c r="H95" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J95" t="str">
+      <c r="J95" t="s">
+        <v>404</v>
+      </c>
+      <c r="K95" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_013_strategy_by_pii_type_default</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="31.5" thickBot="1">
+    <row r="96" spans="1:11" ht="31.5" thickBot="1">
       <c r="A96" s="6" t="s">
         <v>124</v>
       </c>
@@ -10072,12 +10383,15 @@
       <c r="H96" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J96" t="str">
+      <c r="J96" t="s">
+        <v>404</v>
+      </c>
+      <c r="K96" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_014_strategy_by_tenant_config</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="31.5" thickBot="1">
+    <row r="97" spans="1:11" ht="31.5" thickBot="1">
       <c r="A97" s="6" t="s">
         <v>124</v>
       </c>
@@ -10098,12 +10412,15 @@
       <c r="H97" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J97" t="str">
+      <c r="J97" t="s">
+        <v>404</v>
+      </c>
+      <c r="K97" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_015_strategy_mixed_per_type</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="31.5" thickBot="1">
+    <row r="98" spans="1:11" ht="31.5" thickBot="1">
       <c r="A98" s="6" t="s">
         <v>124</v>
       </c>
@@ -10124,12 +10441,15 @@
       <c r="H98" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J98" t="str">
+      <c r="J98" t="s">
+        <v>404</v>
+      </c>
+      <c r="K98" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_016_strategy_none_keeps_original</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="31.5" thickBot="1">
+    <row r="99" spans="1:11" ht="31.5" thickBot="1">
       <c r="A99" s="6" t="s">
         <v>124</v>
       </c>
@@ -10150,12 +10470,15 @@
       <c r="H99" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J99" t="str">
+      <c r="J99" t="s">
+        <v>404</v>
+      </c>
+      <c r="K99" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_edge_001_nested_pii_in_pii</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="31.5" thickBot="1">
+    <row r="100" spans="1:11" ht="31.5" thickBot="1">
       <c r="A100" s="6" t="s">
         <v>124</v>
       </c>
@@ -10176,12 +10499,15 @@
       <c r="H100" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J100" t="str">
+      <c r="J100" t="s">
+        <v>404</v>
+      </c>
+      <c r="K100" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_edge_002_overlapping_pii_positions</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="31.5" thickBot="1">
+    <row r="101" spans="1:11" ht="31.5" thickBot="1">
       <c r="A101" s="6" t="s">
         <v>124</v>
       </c>
@@ -10202,12 +10528,15 @@
       <c r="H101" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J101" t="str">
+      <c r="J101" t="s">
+        <v>404</v>
+      </c>
+      <c r="K101" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-002test_edge_003_empty_text_no_error</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16.5" thickBot="1">
+    <row r="102" spans="1:11" ht="16.5" thickBot="1">
       <c r="A102" s="6" t="s">
         <v>125</v>
       </c>
@@ -10228,12 +10557,15 @@
       <c r="H102" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J102" t="str">
+      <c r="J102" t="s">
+        <v>404</v>
+      </c>
+      <c r="K102" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-ANO-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16.5" thickBot="1">
+    <row r="103" spans="1:11" ht="16.5" thickBot="1">
       <c r="A103" s="6" t="s">
         <v>126</v>
       </c>
@@ -10254,12 +10586,15 @@
       <c r="H103" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J103" t="str">
+      <c r="J103" t="s">
+        <v>404</v>
+      </c>
+      <c r="K103" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-TNT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16.5" thickBot="1">
+    <row r="104" spans="1:11" ht="16.5" thickBot="1">
       <c r="A104" s="6" t="s">
         <v>127</v>
       </c>
@@ -10280,12 +10615,12 @@
       <c r="H104" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J104" t="str">
+      <c r="K104" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-JWT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="16.5" thickBot="1">
+    <row r="105" spans="1:11" ht="16.5" thickBot="1">
       <c r="A105" s="6" t="s">
         <v>128</v>
       </c>
@@ -10306,12 +10641,12 @@
       <c r="H105" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J105" t="str">
+      <c r="K105" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-AUD-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="31.5" thickBot="1">
+    <row r="106" spans="1:11" ht="31.5" thickBot="1">
       <c r="A106" s="6" t="s">
         <v>129</v>
       </c>
@@ -10332,12 +10667,15 @@
       <c r="H106" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J106" t="str">
+      <c r="J106" t="s">
+        <v>404</v>
+      </c>
+      <c r="K106" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_001_mass_changes_11_in_hour_detected</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="31.5" thickBot="1">
+    <row r="107" spans="1:11" ht="31.5" thickBot="1">
       <c r="A107" s="6" t="s">
         <v>129</v>
       </c>
@@ -10358,12 +10696,15 @@
       <c r="H107" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J107" t="str">
+      <c r="J107" t="s">
+        <v>404</v>
+      </c>
+      <c r="K107" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_002_mass_changes_10_in_hour_allowed</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="31.5" thickBot="1">
+    <row r="108" spans="1:11" ht="31.5" thickBot="1">
       <c r="A108" s="6" t="s">
         <v>129</v>
       </c>
@@ -10384,12 +10725,15 @@
       <c r="H108" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J108" t="str">
+      <c r="J108" t="s">
+        <v>404</v>
+      </c>
+      <c r="K108" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_003_mass_changes_window_reset</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="31.5" thickBot="1">
+    <row r="109" spans="1:11" ht="31.5" thickBot="1">
       <c r="A109" s="6" t="s">
         <v>129</v>
       </c>
@@ -10410,12 +10754,15 @@
       <c r="H109" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J109" t="str">
+      <c r="J109" t="s">
+        <v>404</v>
+      </c>
+      <c r="K109" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_004_resolve_reintroduce_3_times_detected</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="31.5" thickBot="1">
+    <row r="110" spans="1:11" ht="31.5" thickBot="1">
       <c r="A110" s="6" t="s">
         <v>129</v>
       </c>
@@ -10436,12 +10783,15 @@
       <c r="H110" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J110" t="str">
+      <c r="J110" t="s">
+        <v>404</v>
+      </c>
+      <c r="K110" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_005_resolve_reintroduce_2_times_allowed</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="31.5" thickBot="1">
+    <row r="111" spans="1:11" ht="31.5" thickBot="1">
       <c r="A111" s="6" t="s">
         <v>129</v>
       </c>
@@ -10462,12 +10812,15 @@
       <c r="H111" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J111" t="str">
+      <c r="J111" t="s">
+        <v>404</v>
+      </c>
+      <c r="K111" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_006_resolve_reintroduce_different_hash_allowed</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="31.5" thickBot="1">
+    <row r="112" spans="1:11" ht="31.5" thickBot="1">
       <c r="A112" s="6" t="s">
         <v>129</v>
       </c>
@@ -10488,12 +10841,15 @@
       <c r="H112" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J112" t="str">
+      <c r="J112" t="s">
+        <v>404</v>
+      </c>
+      <c r="K112" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_007_high_score_few_docs_detected</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="31.5" thickBot="1">
+    <row r="113" spans="1:11" ht="31.5" thickBot="1">
       <c r="A113" s="6" t="s">
         <v>129</v>
       </c>
@@ -10514,12 +10870,15 @@
       <c r="H113" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J113" t="str">
+      <c r="J113" t="s">
+        <v>404</v>
+      </c>
+      <c r="K113" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_008_high_score_many_docs_allowed</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="31.5" thickBot="1">
+    <row r="114" spans="1:11" ht="31.5" thickBot="1">
       <c r="A114" s="6" t="s">
         <v>129</v>
       </c>
@@ -10540,12 +10899,15 @@
       <c r="H114" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J114" t="str">
+      <c r="J114" t="s">
+        <v>404</v>
+      </c>
+      <c r="K114" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_009_high_score_threshold_boundary</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="31.5" thickBot="1">
+    <row r="115" spans="1:11" ht="31.5" thickBot="1">
       <c r="A115" s="6" t="s">
         <v>129</v>
       </c>
@@ -10566,12 +10928,15 @@
       <c r="H115" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J115" t="str">
+      <c r="J115" t="s">
+        <v>404</v>
+      </c>
+      <c r="K115" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_010_weight_change_25_percent_detected</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="31.5" thickBot="1">
+    <row r="116" spans="1:11" ht="31.5" thickBot="1">
       <c r="A116" s="6" t="s">
         <v>129</v>
       </c>
@@ -10592,12 +10957,15 @@
       <c r="H116" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J116" t="str">
+      <c r="J116" t="s">
+        <v>404</v>
+      </c>
+      <c r="K116" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_011_weight_change_15_percent_allowed</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="31.5" thickBot="1">
+    <row r="117" spans="1:11" ht="31.5" thickBot="1">
       <c r="A117" s="6" t="s">
         <v>129</v>
       </c>
@@ -10618,12 +10986,15 @@
       <c r="H117" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J117" t="str">
+      <c r="J117" t="s">
+        <v>404</v>
+      </c>
+      <c r="K117" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_012_weight_change_tracking_24h_window</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="31.5" thickBot="1">
+    <row r="118" spans="1:11" ht="31.5" thickBot="1">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -10644,12 +11015,15 @@
       <c r="H118" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J118" t="str">
+      <c r="J118" t="s">
+        <v>404</v>
+      </c>
+      <c r="K118" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_edge_001_multiple_violations_combined</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="31.5" thickBot="1">
+    <row r="119" spans="1:11" ht="31.5" thickBot="1">
       <c r="A119" s="6" t="s">
         <v>129</v>
       </c>
@@ -10670,12 +11044,15 @@
       <c r="H119" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J119" t="str">
+      <c r="J119" t="s">
+        <v>404</v>
+      </c>
+      <c r="K119" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_edge_002_violation_penalty_application</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="31.5" thickBot="1">
+    <row r="120" spans="1:11" ht="31.5" thickBot="1">
       <c r="A120" s="6" t="s">
         <v>129</v>
       </c>
@@ -10696,12 +11073,15 @@
       <c r="H120" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J120" t="str">
+      <c r="J120" t="s">
+        <v>404</v>
+      </c>
+      <c r="K120" t="str">
         <f t="shared" si="1"/>
         <v>TS-UC-SEC-GAM-001test_edge_003_violation_audit_logging</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="31.5" thickBot="1">
+    <row r="121" spans="1:11" ht="31.5" thickBot="1">
       <c r="A121" s="6" t="s">
         <v>130</v>
       </c>
@@ -10725,12 +11105,15 @@
       <c r="I121" t="s">
         <v>803</v>
       </c>
-      <c r="J121" t="str">
+      <c r="J121" t="s">
+        <v>404</v>
+      </c>
+      <c r="K121" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_001_clause_creation_with_all_fields</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="31.5" thickBot="1">
+    <row r="122" spans="1:11" ht="31.5" thickBot="1">
       <c r="A122" s="6" t="s">
         <v>130</v>
       </c>
@@ -10751,12 +11134,15 @@
       <c r="H122" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J122" t="str">
+      <c r="J122" t="s">
+        <v>404</v>
+      </c>
+      <c r="K122" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_002_clause_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="31.5" thickBot="1">
+    <row r="123" spans="1:11" ht="31.5" thickBot="1">
       <c r="A123" s="6" t="s">
         <v>130</v>
       </c>
@@ -10777,12 +11163,15 @@
       <c r="H123" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J123" t="str">
+      <c r="J123" t="s">
+        <v>404</v>
+      </c>
+      <c r="K123" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_003_clause_creation_fails_without_content</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="31.5" thickBot="1">
+    <row r="124" spans="1:11" ht="31.5" thickBot="1">
       <c r="A124" s="6" t="s">
         <v>130</v>
       </c>
@@ -10803,12 +11192,15 @@
       <c r="H124" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J124" t="str">
+      <c r="J124" t="s">
+        <v>404</v>
+      </c>
+      <c r="K124" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_004_clause_creation_fails_without_document_id</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="31.5" thickBot="1">
+    <row r="125" spans="1:11" ht="31.5" thickBot="1">
       <c r="A125" s="6" t="s">
         <v>130</v>
       </c>
@@ -10829,12 +11221,15 @@
       <c r="H125" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J125" t="str">
+      <c r="J125" t="s">
+        <v>404</v>
+      </c>
+      <c r="K125" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_005_clause_creation_fails_without_tenant_id</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="31.5" thickBot="1">
+    <row r="126" spans="1:11" ht="31.5" thickBot="1">
       <c r="A126" s="6" t="s">
         <v>130</v>
       </c>
@@ -10855,12 +11250,15 @@
       <c r="H126" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J126" t="str">
+      <c r="J126" t="s">
+        <v>404</v>
+      </c>
+      <c r="K126" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_006_clause_immutability_after_creation</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="31.5" thickBot="1">
+    <row r="127" spans="1:11" ht="31.5" thickBot="1">
       <c r="A127" s="6" t="s">
         <v>130</v>
       </c>
@@ -10881,12 +11279,15 @@
       <c r="H127" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J127" t="str">
+      <c r="J127" t="s">
+        <v>404</v>
+      </c>
+      <c r="K127" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_007_clause_number_format_primera</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="31.5" thickBot="1">
+    <row r="128" spans="1:11" ht="31.5" thickBot="1">
       <c r="A128" s="6" t="s">
         <v>130</v>
       </c>
@@ -10907,12 +11308,15 @@
       <c r="H128" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J128" t="str">
+      <c r="J128" t="s">
+        <v>404</v>
+      </c>
+      <c r="K128" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_008_clause_number_format_numeric</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="31.5" thickBot="1">
+    <row r="129" spans="1:11" ht="31.5" thickBot="1">
       <c r="A129" s="6" t="s">
         <v>130</v>
       </c>
@@ -10933,12 +11337,15 @@
       <c r="H129" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J129" t="str">
+      <c r="J129" t="s">
+        <v>404</v>
+      </c>
+      <c r="K129" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_009_clause_number_format_decimal</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="31.5" thickBot="1">
+    <row r="130" spans="1:11" ht="31.5" thickBot="1">
       <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
@@ -10959,12 +11366,15 @@
       <c r="H130" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J130" t="str">
+      <c r="J130" t="s">
+        <v>404</v>
+      </c>
+      <c r="K130" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_010_clause_number_normalization</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="31.5" thickBot="1">
+    <row r="131" spans="1:11" ht="31.5" thickBot="1">
       <c r="A131" s="6" t="s">
         <v>130</v>
       </c>
@@ -10985,12 +11395,15 @@
       <c r="H131" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J131" t="str">
+      <c r="J131" t="s">
+        <v>404</v>
+      </c>
+      <c r="K131" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_011_clause_content_max_length</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="31.5" thickBot="1">
+    <row r="132" spans="1:11" ht="31.5" thickBot="1">
       <c r="A132" s="6" t="s">
         <v>130</v>
       </c>
@@ -11011,12 +11424,15 @@
       <c r="H132" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J132" t="str">
+      <c r="J132" t="s">
+        <v>404</v>
+      </c>
+      <c r="K132" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_012_clause_content_empty_rejected</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="31.5" thickBot="1">
+    <row r="133" spans="1:11" ht="31.5" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>130</v>
       </c>
@@ -11037,12 +11453,15 @@
       <c r="H133" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J133" t="str">
+      <c r="J133" t="s">
+        <v>404</v>
+      </c>
+      <c r="K133" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_013_clause_document_fk_valid</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="31.5" thickBot="1">
+    <row r="134" spans="1:11" ht="31.5" thickBot="1">
       <c r="A134" s="6" t="s">
         <v>130</v>
       </c>
@@ -11063,12 +11482,15 @@
       <c r="H134" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J134" t="str">
+      <c r="J134" t="s">
+        <v>404</v>
+      </c>
+      <c r="K134" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_014_clause_document_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="31.5" thickBot="1">
+    <row r="135" spans="1:11" ht="31.5" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>130</v>
       </c>
@@ -11089,12 +11511,15 @@
       <c r="H135" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J135" t="str">
+      <c r="J135" t="s">
+        <v>404</v>
+      </c>
+      <c r="K135" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_015_clause_tenant_fk_valid</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="31.5" thickBot="1">
+    <row r="136" spans="1:11" ht="31.5" thickBot="1">
       <c r="A136" s="6" t="s">
         <v>130</v>
       </c>
@@ -11115,12 +11540,15 @@
       <c r="H136" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J136" t="str">
+      <c r="J136" t="s">
+        <v>404</v>
+      </c>
+      <c r="K136" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_016_clause_tenant_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="31.5" thickBot="1">
+    <row r="137" spans="1:11" ht="31.5" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>130</v>
       </c>
@@ -11141,12 +11569,15 @@
       <c r="H137" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J137" t="str">
+      <c r="J137" t="s">
+        <v>404</v>
+      </c>
+      <c r="K137" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_017_clause_on_delete_restrict_document</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="31.5" thickBot="1">
+    <row r="138" spans="1:11" ht="31.5" thickBot="1">
       <c r="A138" s="6" t="s">
         <v>130</v>
       </c>
@@ -11167,12 +11598,15 @@
       <c r="H138" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J138" t="str">
+      <c r="J138" t="s">
+        <v>404</v>
+      </c>
+      <c r="K138" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_018_clause_on_delete_restrict_tenant</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="31.5" thickBot="1">
+    <row r="139" spans="1:11" ht="31.5" thickBot="1">
       <c r="A139" s="6" t="s">
         <v>130</v>
       </c>
@@ -11193,12 +11627,15 @@
       <c r="H139" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J139" t="str">
+      <c r="J139" t="s">
+        <v>404</v>
+      </c>
+      <c r="K139" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_019_clause_embedding_vector_size</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="31.5" thickBot="1">
+    <row r="140" spans="1:11" ht="31.5" thickBot="1">
       <c r="A140" s="6" t="s">
         <v>130</v>
       </c>
@@ -11219,12 +11656,15 @@
       <c r="H140" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J140" t="str">
+      <c r="J140" t="s">
+        <v>404</v>
+      </c>
+      <c r="K140" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_020_clause_embedding_generation</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="31.5" thickBot="1">
+    <row r="141" spans="1:11" ht="31.5" thickBot="1">
       <c r="A141" s="6" t="s">
         <v>130</v>
       </c>
@@ -11245,12 +11685,15 @@
       <c r="H141" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J141" t="str">
+      <c r="J141" t="s">
+        <v>404</v>
+      </c>
+      <c r="K141" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_021_clause_embedding_null_allowed</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="31.5" thickBot="1">
+    <row r="142" spans="1:11" ht="31.5" thickBot="1">
       <c r="A142" s="6" t="s">
         <v>130</v>
       </c>
@@ -11271,12 +11714,15 @@
       <c r="H142" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J142" t="str">
+      <c r="J142" t="s">
+        <v>404</v>
+      </c>
+      <c r="K142" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-001test_022_clause_embedding_update</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="16.5" thickBot="1">
+    <row r="143" spans="1:11" ht="16.5" thickBot="1">
       <c r="A143" s="6" t="s">
         <v>131</v>
       </c>
@@ -11300,12 +11746,12 @@
       <c r="I143" t="s">
         <v>803</v>
       </c>
-      <c r="J143" t="str">
+      <c r="K143" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="16.5" thickBot="1">
+    <row r="144" spans="1:11" ht="16.5" thickBot="1">
       <c r="A144" s="6" t="s">
         <v>132</v>
       </c>
@@ -11326,12 +11772,12 @@
       <c r="H144" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J144" t="str">
+      <c r="K144" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-CLS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="31.5" thickBot="1">
+    <row r="145" spans="1:11" ht="31.5" thickBot="1">
       <c r="A145" s="6" t="s">
         <v>133</v>
       </c>
@@ -11352,12 +11798,15 @@
       <c r="H145" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J145" t="str">
+      <c r="J145" t="s">
+        <v>404</v>
+      </c>
+      <c r="K145" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_001_date_dd_mm_yyyy_slash</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="31.5" thickBot="1">
+    <row r="146" spans="1:11" ht="31.5" thickBot="1">
       <c r="A146" s="6" t="s">
         <v>133</v>
       </c>
@@ -11378,12 +11827,15 @@
       <c r="H146" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J146" t="str">
+      <c r="J146" t="s">
+        <v>404</v>
+      </c>
+      <c r="K146" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_002_date_yyyy_mm_dd_dash</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="31.5" thickBot="1">
+    <row r="147" spans="1:11" ht="31.5" thickBot="1">
       <c r="A147" s="6" t="s">
         <v>133</v>
       </c>
@@ -11404,12 +11856,15 @@
       <c r="H147" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J147" t="str">
+      <c r="J147" t="s">
+        <v>404</v>
+      </c>
+      <c r="K147" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_003_date_dd_month_yyyy_spanish</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="31.5" thickBot="1">
+    <row r="148" spans="1:11" ht="31.5" thickBot="1">
       <c r="A148" s="6" t="s">
         <v>133</v>
       </c>
@@ -11430,12 +11885,15 @@
       <c r="H148" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J148" t="str">
+      <c r="J148" t="s">
+        <v>404</v>
+      </c>
+      <c r="K148" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_004_date_month_dd_yyyy_english</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="31.5" thickBot="1">
+    <row r="149" spans="1:11" ht="31.5" thickBot="1">
       <c r="A149" s="6" t="s">
         <v>133</v>
       </c>
@@ -11456,12 +11914,15 @@
       <c r="H149" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J149" t="str">
+      <c r="J149" t="s">
+        <v>404</v>
+      </c>
+      <c r="K149" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_005_date_relative_30_days</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="31.5" thickBot="1">
+    <row r="150" spans="1:11" ht="31.5" thickBot="1">
       <c r="A150" s="6" t="s">
         <v>133</v>
       </c>
@@ -11482,12 +11943,15 @@
       <c r="H150" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J150" t="str">
+      <c r="J150" t="s">
+        <v>404</v>
+      </c>
+      <c r="K150" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_006_date_relative_3_months</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="31.5" thickBot="1">
+    <row r="151" spans="1:11" ht="31.5" thickBot="1">
       <c r="A151" s="6" t="s">
         <v>133</v>
       </c>
@@ -11508,12 +11972,15 @@
       <c r="H151" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J151" t="str">
+      <c r="J151" t="s">
+        <v>404</v>
+      </c>
+      <c r="K151" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_007_date_relative_1_year</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="31.5" thickBot="1">
+    <row r="152" spans="1:11" ht="31.5" thickBot="1">
       <c r="A152" s="6" t="s">
         <v>133</v>
       </c>
@@ -11534,12 +12001,15 @@
       <c r="H152" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J152" t="str">
+      <c r="J152" t="s">
+        <v>404</v>
+      </c>
+      <c r="K152" t="str">
         <f t="shared" si="1"/>
         <v>TS-UD-DOC-ENT-001test_008_date_relative_from_date</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="31.5" thickBot="1">
+    <row r="153" spans="1:11" ht="31.5" thickBot="1">
       <c r="A153" s="6" t="s">
         <v>133</v>
       </c>
@@ -11560,12 +12030,15 @@
       <c r="H153" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J153" t="str">
-        <f t="shared" ref="J153:J216" si="2">CONCATENATE(A153,C153)</f>
+      <c r="J153" t="s">
+        <v>404</v>
+      </c>
+      <c r="K153" t="str">
+        <f t="shared" ref="K153:K216" si="2">CONCATENATE(A153,C153)</f>
         <v>TS-UD-DOC-ENT-001test_009_date_context_entrega</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="31.5" thickBot="1">
+    <row r="154" spans="1:11" ht="31.5" thickBot="1">
       <c r="A154" s="6" t="s">
         <v>133</v>
       </c>
@@ -11586,12 +12059,15 @@
       <c r="H154" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J154" t="str">
+      <c r="J154" t="s">
+        <v>404</v>
+      </c>
+      <c r="K154" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_010_date_context_firma</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="31.5" thickBot="1">
+    <row r="155" spans="1:11" ht="31.5" thickBot="1">
       <c r="A155" s="6" t="s">
         <v>133</v>
       </c>
@@ -11612,12 +12088,15 @@
       <c r="H155" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J155" t="str">
+      <c r="J155" t="s">
+        <v>404</v>
+      </c>
+      <c r="K155" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_011_date_context_inicio</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="16.5" thickBot="1">
+    <row r="156" spans="1:11" ht="16.5" thickBot="1">
       <c r="A156" s="6" t="s">
         <v>133</v>
       </c>
@@ -11638,12 +12117,15 @@
       <c r="H156" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J156" t="str">
+      <c r="J156" t="s">
+        <v>404</v>
+      </c>
+      <c r="K156" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_012_date_context_fin</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="31.5" thickBot="1">
+    <row r="157" spans="1:11" ht="31.5" thickBot="1">
       <c r="A157" s="6" t="s">
         <v>133</v>
       </c>
@@ -11664,12 +12146,15 @@
       <c r="H157" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J157" t="str">
+      <c r="J157" t="s">
+        <v>404</v>
+      </c>
+      <c r="K157" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_013_multiple_dates_extraction</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="31.5" thickBot="1">
+    <row r="158" spans="1:11" ht="31.5" thickBot="1">
       <c r="A158" s="6" t="s">
         <v>133</v>
       </c>
@@ -11690,12 +12175,15 @@
       <c r="H158" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J158" t="str">
+      <c r="J158" t="s">
+        <v>404</v>
+      </c>
+      <c r="K158" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_014_multiple_dates_ordering</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="31.5" thickBot="1">
+    <row r="159" spans="1:11" ht="31.5" thickBot="1">
       <c r="A159" s="6" t="s">
         <v>133</v>
       </c>
@@ -11716,12 +12204,15 @@
       <c r="H159" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J159" t="str">
+      <c r="J159" t="s">
+        <v>404</v>
+      </c>
+      <c r="K159" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_015_date_range_extraction</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="31.5" thickBot="1">
+    <row r="160" spans="1:11" ht="31.5" thickBot="1">
       <c r="A160" s="6" t="s">
         <v>133</v>
       </c>
@@ -11742,12 +12233,15 @@
       <c r="H160" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J160" t="str">
+      <c r="J160" t="s">
+        <v>404</v>
+      </c>
+      <c r="K160" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-001test_016_date_invalid_format_ignored</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="31.5" thickBot="1">
+    <row r="161" spans="1:11" ht="31.5" thickBot="1">
       <c r="A161" s="6" t="s">
         <v>134</v>
       </c>
@@ -11768,12 +12262,15 @@
       <c r="H161" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J161" t="str">
+      <c r="J161" t="s">
+        <v>404</v>
+      </c>
+      <c r="K161" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_001_money_eur_symbol_suffix</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="31.5" thickBot="1">
+    <row r="162" spans="1:11" ht="31.5" thickBot="1">
       <c r="A162" s="6" t="s">
         <v>134</v>
       </c>
@@ -11794,12 +12291,15 @@
       <c r="H162" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J162" t="str">
+      <c r="J162" t="s">
+        <v>404</v>
+      </c>
+      <c r="K162" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_002_money_eur_symbol_prefix</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="31.5" thickBot="1">
+    <row r="163" spans="1:11" ht="31.5" thickBot="1">
       <c r="A163" s="6" t="s">
         <v>134</v>
       </c>
@@ -11820,12 +12320,15 @@
       <c r="H163" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J163" t="str">
+      <c r="J163" t="s">
+        <v>404</v>
+      </c>
+      <c r="K163" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_003_money_eur_word_euros</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="31.5" thickBot="1">
+    <row r="164" spans="1:11" ht="31.5" thickBot="1">
       <c r="A164" s="6" t="s">
         <v>134</v>
       </c>
@@ -11846,12 +12349,15 @@
       <c r="H164" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J164" t="str">
+      <c r="J164" t="s">
+        <v>404</v>
+      </c>
+      <c r="K164" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_004_money_eur_thousands_separator</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="31.5" thickBot="1">
+    <row r="165" spans="1:11" ht="31.5" thickBot="1">
       <c r="A165" s="6" t="s">
         <v>134</v>
       </c>
@@ -11872,12 +12378,15 @@
       <c r="H165" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J165" t="str">
+      <c r="J165" t="s">
+        <v>404</v>
+      </c>
+      <c r="K165" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_005_money_usd_symbol</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="31.5" thickBot="1">
+    <row r="166" spans="1:11" ht="31.5" thickBot="1">
       <c r="A166" s="6" t="s">
         <v>134</v>
       </c>
@@ -11898,12 +12407,15 @@
       <c r="H166" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J166" t="str">
+      <c r="J166" t="s">
+        <v>404</v>
+      </c>
+      <c r="K166" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_006_money_usd_word</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="31.5" thickBot="1">
+    <row r="167" spans="1:11" ht="31.5" thickBot="1">
       <c r="A167" s="6" t="s">
         <v>134</v>
       </c>
@@ -11924,12 +12436,15 @@
       <c r="H167" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J167" t="str">
+      <c r="J167" t="s">
+        <v>404</v>
+      </c>
+      <c r="K167" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_007_money_usd_thousands_separator</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="31.5" thickBot="1">
+    <row r="168" spans="1:11" ht="31.5" thickBot="1">
       <c r="A168" s="6" t="s">
         <v>134</v>
       </c>
@@ -11950,12 +12465,15 @@
       <c r="H168" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J168" t="str">
+      <c r="J168" t="s">
+        <v>404</v>
+      </c>
+      <c r="K168" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_008_money_context_anticipo</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="31.5" thickBot="1">
+    <row r="169" spans="1:11" ht="31.5" thickBot="1">
       <c r="A169" s="6" t="s">
         <v>134</v>
       </c>
@@ -11976,12 +12494,15 @@
       <c r="H169" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J169" t="str">
+      <c r="J169" t="s">
+        <v>404</v>
+      </c>
+      <c r="K169" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_009_money_context_pago_final</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="31.5" thickBot="1">
+    <row r="170" spans="1:11" ht="31.5" thickBot="1">
       <c r="A170" s="6" t="s">
         <v>134</v>
       </c>
@@ -12002,12 +12523,15 @@
       <c r="H170" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J170" t="str">
+      <c r="J170" t="s">
+        <v>404</v>
+      </c>
+      <c r="K170" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_010_money_context_penalizacion</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="31.5" thickBot="1">
+    <row r="171" spans="1:11" ht="31.5" thickBot="1">
       <c r="A171" s="6" t="s">
         <v>134</v>
       </c>
@@ -12028,12 +12552,15 @@
       <c r="H171" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J171" t="str">
+      <c r="J171" t="s">
+        <v>404</v>
+      </c>
+      <c r="K171" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_011_money_context_total</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="31.5" thickBot="1">
+    <row r="172" spans="1:11" ht="31.5" thickBot="1">
       <c r="A172" s="6" t="s">
         <v>134</v>
       </c>
@@ -12054,12 +12581,15 @@
       <c r="H172" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J172" t="str">
+      <c r="J172" t="s">
+        <v>404</v>
+      </c>
+      <c r="K172" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_012_multiple_amounts_extraction</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="31.5" thickBot="1">
+    <row r="173" spans="1:11" ht="31.5" thickBot="1">
       <c r="A173" s="6" t="s">
         <v>134</v>
       </c>
@@ -12080,12 +12610,15 @@
       <c r="H173" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J173" t="str">
+      <c r="J173" t="s">
+        <v>404</v>
+      </c>
+      <c r="K173" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_013_money_percentage_extraction</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="31.5" thickBot="1">
+    <row r="174" spans="1:11" ht="31.5" thickBot="1">
       <c r="A174" s="6" t="s">
         <v>134</v>
       </c>
@@ -12106,12 +12639,15 @@
       <c r="H174" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J174" t="str">
+      <c r="J174" t="s">
+        <v>404</v>
+      </c>
+      <c r="K174" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-002test_014_money_negative_amount</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="16.5" thickBot="1">
+    <row r="175" spans="1:11" ht="16.5" thickBot="1">
       <c r="A175" s="6" t="s">
         <v>135</v>
       </c>
@@ -12124,12 +12660,15 @@
       <c r="D175" s="6"/>
       <c r="E175" s="7"/>
       <c r="F175" s="5"/>
-      <c r="J175" t="str">
+      <c r="J175" t="s">
+        <v>404</v>
+      </c>
+      <c r="K175" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="16.5" thickBot="1">
+    <row r="176" spans="1:11" ht="16.5" thickBot="1">
       <c r="A176" s="6" t="s">
         <v>136</v>
       </c>
@@ -12142,12 +12681,15 @@
       <c r="D176" s="6"/>
       <c r="E176" s="7"/>
       <c r="F176" s="5"/>
-      <c r="J176" t="str">
+      <c r="J176" t="s">
+        <v>404</v>
+      </c>
+      <c r="K176" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-ENT-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="16.5" thickBot="1">
+    <row r="177" spans="1:11" ht="16.5" thickBot="1">
       <c r="A177" s="6" t="s">
         <v>137</v>
       </c>
@@ -12160,12 +12702,15 @@
       <c r="D177" s="6"/>
       <c r="E177" s="7"/>
       <c r="F177" s="5"/>
-      <c r="J177" t="str">
+      <c r="J177" t="s">
+        <v>404</v>
+      </c>
+      <c r="K177" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-DOC-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="16.5" thickBot="1">
+    <row r="178" spans="1:11" ht="16.5" thickBot="1">
       <c r="A178" s="6" t="s">
         <v>138</v>
       </c>
@@ -12178,12 +12723,15 @@
       <c r="D178" s="6"/>
       <c r="E178" s="7"/>
       <c r="F178" s="5"/>
-      <c r="J178" t="str">
+      <c r="J178" t="s">
+        <v>404</v>
+      </c>
+      <c r="K178" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-DOC-CNF-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="16.5" thickBot="1">
+    <row r="179" spans="1:11" ht="16.5" thickBot="1">
       <c r="A179" s="6" t="s">
         <v>139</v>
       </c>
@@ -12196,12 +12744,15 @@
       <c r="D179" s="6"/>
       <c r="E179" s="7"/>
       <c r="F179" s="5"/>
-      <c r="J179" t="str">
+      <c r="J179" t="s">
+        <v>404</v>
+      </c>
+      <c r="K179" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-CAT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="31.5" thickBot="1">
+    <row r="180" spans="1:11" ht="31.5" thickBot="1">
       <c r="A180" s="6" t="s">
         <v>140</v>
       </c>
@@ -12225,12 +12776,15 @@
       <c r="I180" t="s">
         <v>809</v>
       </c>
-      <c r="J180" t="str">
+      <c r="J180" t="s">
+        <v>404</v>
+      </c>
+      <c r="K180" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_001_r11_wbs_level4_no_activities_alert</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="31.5" thickBot="1">
+    <row r="181" spans="1:11" ht="31.5" thickBot="1">
       <c r="A181" s="6" t="s">
         <v>140</v>
       </c>
@@ -12251,12 +12805,15 @@
       <c r="H181" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J181" t="str">
+      <c r="J181" t="s">
+        <v>404</v>
+      </c>
+      <c r="K181" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_002_r11_wbs_level4_with_activities_pass</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="31.5" thickBot="1">
+    <row r="182" spans="1:11" ht="31.5" thickBot="1">
       <c r="A182" s="6" t="s">
         <v>140</v>
       </c>
@@ -12277,12 +12834,15 @@
       <c r="H182" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J182" t="str">
+      <c r="J182" t="s">
+        <v>404</v>
+      </c>
+      <c r="K182" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_003_r11_wbs_level3_no_activities_ignored</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="31.5" thickBot="1">
+    <row r="183" spans="1:11" ht="31.5" thickBot="1">
       <c r="A183" s="6" t="s">
         <v>140</v>
       </c>
@@ -12303,12 +12863,15 @@
       <c r="H183" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J183" t="str">
+      <c r="J183" t="s">
+        <v>404</v>
+      </c>
+      <c r="K183" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_004_r11_wbs_level2_no_activities_ignored</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="31.5" thickBot="1">
+    <row r="184" spans="1:11" ht="31.5" thickBot="1">
       <c r="A184" s="6" t="s">
         <v>140</v>
       </c>
@@ -12329,12 +12892,15 @@
       <c r="H184" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J184" t="str">
+      <c r="J184" t="s">
+        <v>404</v>
+      </c>
+      <c r="K184" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_005_r11_multiple_wbs_level4_violations</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="31.5" thickBot="1">
+    <row r="185" spans="1:11" ht="31.5" thickBot="1">
       <c r="A185" s="6" t="s">
         <v>140</v>
       </c>
@@ -12355,12 +12921,15 @@
       <c r="H185" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J185" t="str">
+      <c r="J185" t="s">
+        <v>404</v>
+      </c>
+      <c r="K185" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_006_r11_alert_severity_medium</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="31.5" thickBot="1">
+    <row r="186" spans="1:11" ht="31.5" thickBot="1">
       <c r="A186" s="6" t="s">
         <v>140</v>
       </c>
@@ -12381,12 +12950,15 @@
       <c r="H186" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J186" t="str">
+      <c r="J186" t="s">
+        <v>404</v>
+      </c>
+      <c r="K186" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_007_r12_wbs_no_budget_line_alert</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="31.5" thickBot="1">
+    <row r="187" spans="1:11" ht="31.5" thickBot="1">
       <c r="A187" s="6" t="s">
         <v>140</v>
       </c>
@@ -12407,12 +12979,15 @@
       <c r="H187" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J187" t="str">
+      <c r="J187" t="s">
+        <v>404</v>
+      </c>
+      <c r="K187" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_008_r12_wbs_with_budget_line_pass</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="31.5" thickBot="1">
+    <row r="188" spans="1:11" ht="31.5" thickBot="1">
       <c r="A188" s="6" t="s">
         <v>140</v>
       </c>
@@ -12433,12 +13008,15 @@
       <c r="H188" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J188" t="str">
+      <c r="J188" t="s">
+        <v>404</v>
+      </c>
+      <c r="K188" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_009_r12_wbs_budget_zero_warning</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="31.5" thickBot="1">
+    <row r="189" spans="1:11" ht="31.5" thickBot="1">
       <c r="A189" s="6" t="s">
         <v>140</v>
       </c>
@@ -12459,12 +13037,15 @@
       <c r="H189" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J189" t="str">
+      <c r="J189" t="s">
+        <v>404</v>
+      </c>
+      <c r="K189" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_010_r12_multiple_wbs_violations</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="31.5" thickBot="1">
+    <row r="190" spans="1:11" ht="31.5" thickBot="1">
       <c r="A190" s="6" t="s">
         <v>140</v>
       </c>
@@ -12485,12 +13066,15 @@
       <c r="H190" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J190" t="str">
+      <c r="J190" t="s">
+        <v>404</v>
+      </c>
+      <c r="K190" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_011_r12_alert_severity_high</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="31.5" thickBot="1">
+    <row r="191" spans="1:11" ht="31.5" thickBot="1">
       <c r="A191" s="6" t="s">
         <v>140</v>
       </c>
@@ -12511,12 +13095,15 @@
       <c r="H191" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J191" t="str">
+      <c r="J191" t="s">
+        <v>404</v>
+      </c>
+      <c r="K191" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_012_r12_affected_entities_list</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="31.5" thickBot="1">
+    <row r="192" spans="1:11" ht="31.5" thickBot="1">
       <c r="A192" s="6" t="s">
         <v>140</v>
       </c>
@@ -12537,12 +13124,15 @@
       <c r="H192" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J192" t="str">
+      <c r="J192" t="s">
+        <v>404</v>
+      </c>
+      <c r="K192" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_013_r13_scope_clause_no_wbs_alert</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="31.5" thickBot="1">
+    <row r="193" spans="1:11" ht="31.5" thickBot="1">
       <c r="A193" s="6" t="s">
         <v>140</v>
       </c>
@@ -12563,12 +13153,15 @@
       <c r="H193" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J193" t="str">
+      <c r="J193" t="s">
+        <v>404</v>
+      </c>
+      <c r="K193" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_014_r13_scope_clause_with_wbs_pass</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="31.5" thickBot="1">
+    <row r="194" spans="1:11" ht="31.5" thickBot="1">
       <c r="A194" s="6" t="s">
         <v>140</v>
       </c>
@@ -12589,12 +13182,15 @@
       <c r="H194" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J194" t="str">
+      <c r="J194" t="s">
+        <v>404</v>
+      </c>
+      <c r="K194" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_015_r13_partial_coverage_calculation</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="31.5" thickBot="1">
+    <row r="195" spans="1:11" ht="31.5" thickBot="1">
       <c r="A195" s="6" t="s">
         <v>140</v>
       </c>
@@ -12615,12 +13211,15 @@
       <c r="H195" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J195" t="str">
+      <c r="J195" t="s">
+        <v>404</v>
+      </c>
+      <c r="K195" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_016_r13_coverage_percentage_80</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="31.5" thickBot="1">
+    <row r="196" spans="1:11" ht="31.5" thickBot="1">
       <c r="A196" s="6" t="s">
         <v>140</v>
       </c>
@@ -12641,12 +13240,15 @@
       <c r="H196" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J196" t="str">
+      <c r="J196" t="s">
+        <v>404</v>
+      </c>
+      <c r="K196" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_017_r13_uncovered_clauses_list</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="31.5" thickBot="1">
+    <row r="197" spans="1:11" ht="31.5" thickBot="1">
       <c r="A197" s="6" t="s">
         <v>140</v>
       </c>
@@ -12667,12 +13269,15 @@
       <c r="H197" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J197" t="str">
+      <c r="J197" t="s">
+        <v>404</v>
+      </c>
+      <c r="K197" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-001test_018_r13_alert_severity_high</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="31.5" thickBot="1">
+    <row r="198" spans="1:11" ht="31.5" thickBot="1">
       <c r="A198" s="6" t="s">
         <v>141</v>
       </c>
@@ -12693,12 +13298,15 @@
       <c r="H198" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J198" t="str">
+      <c r="J198" t="s">
+        <v>404</v>
+      </c>
+      <c r="K198" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_001_r6_deviation_10_percent_alert</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="31.5" thickBot="1">
+    <row r="199" spans="1:11" ht="31.5" thickBot="1">
       <c r="A199" s="6" t="s">
         <v>141</v>
       </c>
@@ -12719,12 +13327,12 @@
       <c r="H199" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J199" t="str">
+      <c r="K199" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_002_r6_deviation_5_percent_pass</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="31.5" thickBot="1">
+    <row r="200" spans="1:11" ht="31.5" thickBot="1">
       <c r="A200" s="6" t="s">
         <v>141</v>
       </c>
@@ -12745,12 +13353,12 @@
       <c r="H200" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J200" t="str">
+      <c r="K200" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_003_r6_deviation_4_9_percent_pass</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="31.5" thickBot="1">
+    <row r="201" spans="1:11" ht="31.5" thickBot="1">
       <c r="A201" s="6" t="s">
         <v>141</v>
       </c>
@@ -12771,12 +13379,12 @@
       <c r="H201" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J201" t="str">
+      <c r="K201" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_004_r6_over_budget_critical</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="31.5" thickBot="1">
+    <row r="202" spans="1:11" ht="31.5" thickBot="1">
       <c r="A202" s="6" t="s">
         <v>141</v>
       </c>
@@ -12797,12 +13405,12 @@
       <c r="H202" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J202" t="str">
+      <c r="K202" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_005_r6_under_budget_warning</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="31.5" thickBot="1">
+    <row r="203" spans="1:11" ht="31.5" thickBot="1">
       <c r="A203" s="6" t="s">
         <v>141</v>
       </c>
@@ -12823,12 +13431,12 @@
       <c r="H203" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J203" t="str">
+      <c r="K203" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_006_r6_exact_match_pass</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="31.5" thickBot="1">
+    <row r="204" spans="1:11" ht="31.5" thickBot="1">
       <c r="A204" s="6" t="s">
         <v>141</v>
       </c>
@@ -12849,12 +13457,12 @@
       <c r="H204" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J204" t="str">
+      <c r="K204" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_007_r15_bom_no_budget_alert</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="31.5" thickBot="1">
+    <row r="205" spans="1:11" ht="31.5" thickBot="1">
       <c r="A205" s="6" t="s">
         <v>141</v>
       </c>
@@ -12875,12 +13483,12 @@
       <c r="H205" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J205" t="str">
+      <c r="K205" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_008_r15_bom_with_budget_pass</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="31.5" thickBot="1">
+    <row r="206" spans="1:11" ht="31.5" thickBot="1">
       <c r="A206" s="6" t="s">
         <v>141</v>
       </c>
@@ -12901,12 +13509,12 @@
       <c r="H206" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J206" t="str">
+      <c r="K206" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_009_r15_bom_client_provided_exception</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="31.5" thickBot="1">
+    <row r="207" spans="1:11" ht="31.5" thickBot="1">
       <c r="A207" s="6" t="s">
         <v>141</v>
       </c>
@@ -12927,12 +13535,12 @@
       <c r="H207" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J207" t="str">
+      <c r="K207" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_010_r15_multiple_bom_violations</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="31.5" thickBot="1">
+    <row r="208" spans="1:11" ht="31.5" thickBot="1">
       <c r="A208" s="6" t="s">
         <v>141</v>
       </c>
@@ -12953,12 +13561,12 @@
       <c r="H208" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J208" t="str">
+      <c r="K208" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_011_r15_affected_items_list</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="31.5" thickBot="1">
+    <row r="209" spans="1:11" ht="31.5" thickBot="1">
       <c r="A209" s="6" t="s">
         <v>141</v>
       </c>
@@ -12979,12 +13587,12 @@
       <c r="H209" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J209" t="str">
+      <c r="K209" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_012_r16_deviation_11_percent_alert</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="31.5" thickBot="1">
+    <row r="210" spans="1:11" ht="31.5" thickBot="1">
       <c r="A210" s="6" t="s">
         <v>141</v>
       </c>
@@ -13005,12 +13613,12 @@
       <c r="H210" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J210" t="str">
+      <c r="K210" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_013_r16_deviation_10_percent_pass</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="31.5" thickBot="1">
+    <row r="211" spans="1:11" ht="31.5" thickBot="1">
       <c r="A211" s="6" t="s">
         <v>141</v>
       </c>
@@ -13031,12 +13639,12 @@
       <c r="H211" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J211" t="str">
+      <c r="K211" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_014_r16_over_budget_critical</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="31.5" thickBot="1">
+    <row r="212" spans="1:11" ht="31.5" thickBot="1">
       <c r="A212" s="6" t="s">
         <v>141</v>
       </c>
@@ -13057,12 +13665,12 @@
       <c r="H212" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J212" t="str">
+      <c r="K212" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_015_r16_under_budget_different_severity</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="31.5" thickBot="1">
+    <row r="213" spans="1:11" ht="31.5" thickBot="1">
       <c r="A213" s="6" t="s">
         <v>141</v>
       </c>
@@ -13083,12 +13691,12 @@
       <c r="H213" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J213" t="str">
+      <c r="K213" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_016_r16_trend_calculation</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="31.5" thickBot="1">
+    <row r="214" spans="1:11" ht="31.5" thickBot="1">
       <c r="A214" s="6" t="s">
         <v>142</v>
       </c>
@@ -13112,12 +13720,12 @@
       <c r="I214" t="s">
         <v>809</v>
       </c>
-      <c r="J214" t="str">
+      <c r="K214" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_001_r1_dates_mismatch_alert</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="31.5" thickBot="1">
+    <row r="215" spans="1:11" ht="31.5" thickBot="1">
       <c r="A215" s="6" t="s">
         <v>142</v>
       </c>
@@ -13138,12 +13746,12 @@
       <c r="H215" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J215" t="str">
+      <c r="K215" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_002_r1_dates_match_pass</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="31.5" thickBot="1">
+    <row r="216" spans="1:11" ht="31.5" thickBot="1">
       <c r="A216" s="6" t="s">
         <v>142</v>
       </c>
@@ -13164,12 +13772,12 @@
       <c r="H216" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J216" t="str">
+      <c r="K216" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_003_r1_schedule_late_critical</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="31.5" thickBot="1">
+    <row r="217" spans="1:11" ht="31.5" thickBot="1">
       <c r="A217" s="6" t="s">
         <v>142</v>
       </c>
@@ -13190,12 +13798,12 @@
       <c r="H217" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J217" t="str">
-        <f t="shared" ref="J217:J280" si="3">CONCATENATE(A217,C217)</f>
+      <c r="K217" t="str">
+        <f t="shared" ref="K217:K280" si="3">CONCATENATE(A217,C217)</f>
         <v>TS-UD-COH-RUL-003test_004_r1_schedule_early_warning</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="31.5" thickBot="1">
+    <row r="218" spans="1:11" ht="31.5" thickBot="1">
       <c r="A218" s="6" t="s">
         <v>142</v>
       </c>
@@ -13216,12 +13824,12 @@
       <c r="H218" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J218" t="str">
+      <c r="K218" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_005_r1_delta_days_calculation</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="31.5" thickBot="1">
+    <row r="219" spans="1:11" ht="31.5" thickBot="1">
       <c r="A219" s="6" t="s">
         <v>142</v>
       </c>
@@ -13242,12 +13850,12 @@
       <c r="H219" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J219" t="str">
+      <c r="K219" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_006_r2_milestone_no_activity_alert</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="31.5" thickBot="1">
+    <row r="220" spans="1:11" ht="31.5" thickBot="1">
       <c r="A220" s="6" t="s">
         <v>142</v>
       </c>
@@ -13268,12 +13876,12 @@
       <c r="H220" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J220" t="str">
+      <c r="K220" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_007_r2_milestone_with_activity_pass</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="31.5" thickBot="1">
+    <row r="221" spans="1:11" ht="31.5" thickBot="1">
       <c r="A221" s="6" t="s">
         <v>142</v>
       </c>
@@ -13294,12 +13902,12 @@
       <c r="H221" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J221" t="str">
+      <c r="K221" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_008_r2_milestone_date_mismatch_alert</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="31.5" thickBot="1">
+    <row r="222" spans="1:11" ht="31.5" thickBot="1">
       <c r="A222" s="6" t="s">
         <v>142</v>
       </c>
@@ -13320,12 +13928,12 @@
       <c r="H222" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J222" t="str">
+      <c r="K222" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_009_r2_multiple_milestones_violations</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="31.5" thickBot="1">
+    <row r="223" spans="1:11" ht="31.5" thickBot="1">
       <c r="A223" s="6" t="s">
         <v>142</v>
       </c>
@@ -13346,12 +13954,12 @@
       <c r="H223" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J223" t="str">
+      <c r="K223" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_010_r2_unlinked_milestones_list</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="31.5" thickBot="1">
+    <row r="224" spans="1:11" ht="31.5" thickBot="1">
       <c r="A224" s="6" t="s">
         <v>142</v>
       </c>
@@ -13372,12 +13980,12 @@
       <c r="H224" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J224" t="str">
+      <c r="K224" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_011_r5_activity_exceeds_contract_alert</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="31.5" thickBot="1">
+    <row r="225" spans="1:11" ht="31.5" thickBot="1">
       <c r="A225" s="6" t="s">
         <v>142</v>
       </c>
@@ -13398,12 +14006,12 @@
       <c r="H225" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J225" t="str">
+      <c r="K225" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_012_r5_activity_within_contract_pass</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="31.5" thickBot="1">
+    <row r="226" spans="1:11" ht="31.5" thickBot="1">
       <c r="A226" s="6" t="s">
         <v>142</v>
       </c>
@@ -13424,12 +14032,12 @@
       <c r="H226" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J226" t="str">
+      <c r="K226" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_013_r5_exceeding_activities_list</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="31.5" thickBot="1">
+    <row r="227" spans="1:11" ht="31.5" thickBot="1">
       <c r="A227" s="6" t="s">
         <v>142</v>
       </c>
@@ -13450,12 +14058,12 @@
       <c r="H227" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J227" t="str">
+      <c r="K227" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_014_r5_alert_severity_critical</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="31.5" thickBot="1">
+    <row r="228" spans="1:11" ht="31.5" thickBot="1">
       <c r="A228" s="6" t="s">
         <v>142</v>
       </c>
@@ -13476,12 +14084,12 @@
       <c r="H228" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J228" t="str">
+      <c r="K228" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_015_r14_order_date_passed_critical</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="31.5" thickBot="1">
+    <row r="229" spans="1:11" ht="31.5" thickBot="1">
       <c r="A229" s="6" t="s">
         <v>142</v>
       </c>
@@ -13502,12 +14110,12 @@
       <c r="H229" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J229" t="str">
+      <c r="K229" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_016_r14_order_date_tight_warning</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="16.5" thickBot="1">
+    <row r="230" spans="1:11" ht="16.5" thickBot="1">
       <c r="A230" s="6" t="s">
         <v>143</v>
       </c>
@@ -13520,12 +14128,12 @@
       <c r="D230" s="6"/>
       <c r="E230" s="7"/>
       <c r="F230" s="5"/>
-      <c r="J230" t="str">
+      <c r="K230" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="16.5" thickBot="1">
+    <row r="231" spans="1:11" ht="16.5" thickBot="1">
       <c r="A231" s="6" t="s">
         <v>144</v>
       </c>
@@ -13538,12 +14146,12 @@
       <c r="D231" s="6"/>
       <c r="E231" s="7"/>
       <c r="F231" s="5"/>
-      <c r="J231" t="str">
+      <c r="K231" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-005Tests not individually listed</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="16.5" thickBot="1">
+    <row r="232" spans="1:11" ht="16.5" thickBot="1">
       <c r="A232" s="6" t="s">
         <v>145</v>
       </c>
@@ -13556,12 +14164,12 @@
       <c r="D232" s="6"/>
       <c r="E232" s="7"/>
       <c r="F232" s="5"/>
-      <c r="J232" t="str">
+      <c r="K232" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-006Tests not individually listed</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="31.5" thickBot="1">
+    <row r="233" spans="1:11" ht="31.5" thickBot="1">
       <c r="A233" s="6" t="s">
         <v>146</v>
       </c>
@@ -13585,12 +14193,13 @@
       <c r="I233" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="J233" t="str">
+      <c r="J233" s="21"/>
+      <c r="K233" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_001_subscore_no_alerts_100_percent</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="31.5" thickBot="1">
+    <row r="234" spans="1:11" ht="31.5" thickBot="1">
       <c r="A234" s="6" t="s">
         <v>146</v>
       </c>
@@ -13611,12 +14220,12 @@
       <c r="H234" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J234" t="str">
+      <c r="K234" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_002_subscore_one_alert_penalized</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="31.5" thickBot="1">
+    <row r="235" spans="1:11" ht="31.5" thickBot="1">
       <c r="A235" s="6" t="s">
         <v>146</v>
       </c>
@@ -13637,12 +14246,12 @@
       <c r="H235" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J235" t="str">
+      <c r="K235" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_003_subscore_multiple_alerts_cumulative</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="31.5" thickBot="1">
+    <row r="236" spans="1:11" ht="31.5" thickBot="1">
       <c r="A236" s="6" t="s">
         <v>146</v>
       </c>
@@ -13663,12 +14272,12 @@
       <c r="H236" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J236" t="str">
+      <c r="K236" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_004_subscore_severity_low_penalty_5</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="31.5" thickBot="1">
+    <row r="237" spans="1:11" ht="31.5" thickBot="1">
       <c r="A237" s="6" t="s">
         <v>146</v>
       </c>
@@ -13689,12 +14298,12 @@
       <c r="H237" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J237" t="str">
+      <c r="K237" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_005_subscore_severity_medium_penalty_10</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="31.5" thickBot="1">
+    <row r="238" spans="1:11" ht="31.5" thickBot="1">
       <c r="A238" s="6" t="s">
         <v>146</v>
       </c>
@@ -13715,12 +14324,12 @@
       <c r="H238" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J238" t="str">
+      <c r="K238" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_006_subscore_severity_high_penalty_20</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="31.5" thickBot="1">
+    <row r="239" spans="1:11" ht="31.5" thickBot="1">
       <c r="A239" s="6" t="s">
         <v>146</v>
       </c>
@@ -13741,12 +14350,12 @@
       <c r="H239" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J239" t="str">
+      <c r="K239" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_007_subscore_severity_critical_penalty_30</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="31.5" thickBot="1">
+    <row r="240" spans="1:11" ht="31.5" thickBot="1">
       <c r="A240" s="6" t="s">
         <v>146</v>
       </c>
@@ -13767,12 +14376,12 @@
       <c r="H240" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J240" t="str">
+      <c r="K240" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_008_subscore_scope_calculation</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="31.5" thickBot="1">
+    <row r="241" spans="1:11" ht="31.5" thickBot="1">
       <c r="A241" s="6" t="s">
         <v>146</v>
       </c>
@@ -13793,12 +14402,12 @@
       <c r="H241" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J241" t="str">
+      <c r="K241" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_009_subscore_budget_calculation</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="31.5" thickBot="1">
+    <row r="242" spans="1:11" ht="31.5" thickBot="1">
       <c r="A242" s="6" t="s">
         <v>146</v>
       </c>
@@ -13819,12 +14428,12 @@
       <c r="H242" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J242" t="str">
+      <c r="K242" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_010_subscore_quality_calculation</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="31.5" thickBot="1">
+    <row r="243" spans="1:11" ht="31.5" thickBot="1">
       <c r="A243" s="6" t="s">
         <v>146</v>
       </c>
@@ -13845,12 +14454,12 @@
       <c r="H243" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J243" t="str">
+      <c r="K243" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_011_subscore_technical_calculation</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="31.5" thickBot="1">
+    <row r="244" spans="1:11" ht="31.5" thickBot="1">
       <c r="A244" s="6" t="s">
         <v>146</v>
       </c>
@@ -13871,12 +14480,12 @@
       <c r="H244" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J244" t="str">
+      <c r="K244" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_012_subscore_legal_calculation</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="31.5" thickBot="1">
+    <row r="245" spans="1:11" ht="31.5" thickBot="1">
       <c r="A245" s="6" t="s">
         <v>146</v>
       </c>
@@ -13897,12 +14506,12 @@
       <c r="H245" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J245" t="str">
+      <c r="K245" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_013_subscore_time_calculation</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="31.5" thickBot="1">
+    <row r="246" spans="1:11" ht="31.5" thickBot="1">
       <c r="A246" s="6" t="s">
         <v>146</v>
       </c>
@@ -13923,12 +14532,12 @@
       <c r="H246" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J246" t="str">
+      <c r="K246" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_014_subscore_floor_at_zero</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="31.5" thickBot="1">
+    <row r="247" spans="1:11" ht="31.5" thickBot="1">
       <c r="A247" s="6" t="s">
         <v>147</v>
       </c>
@@ -13949,12 +14558,12 @@
       <c r="H247" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J247" t="str">
+      <c r="K247" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_001_global_score_formula_verification</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="31.5" thickBot="1">
+    <row r="248" spans="1:11" ht="31.5" thickBot="1">
       <c r="A248" s="6" t="s">
         <v>147</v>
       </c>
@@ -13975,12 +14584,12 @@
       <c r="H248" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J248" t="str">
+      <c r="K248" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_002_global_score_default_weights</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="31.5" thickBot="1">
+    <row r="249" spans="1:11" ht="31.5" thickBot="1">
       <c r="A249" s="6" t="s">
         <v>147</v>
       </c>
@@ -14001,12 +14610,12 @@
       <c r="H249" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J249" t="str">
+      <c r="K249" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_003_global_score_all_100_equals_100</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="31.5" thickBot="1">
+    <row r="250" spans="1:11" ht="31.5" thickBot="1">
       <c r="A250" s="6" t="s">
         <v>147</v>
       </c>
@@ -14027,12 +14636,12 @@
       <c r="H250" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J250" t="str">
+      <c r="K250" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_004_global_score_all_0_equals_0</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="31.5" thickBot="1">
+    <row r="251" spans="1:11" ht="31.5" thickBot="1">
       <c r="A251" s="6" t="s">
         <v>147</v>
       </c>
@@ -14053,12 +14662,12 @@
       <c r="H251" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J251" t="str">
+      <c r="K251" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_005_global_score_mixed_subscores</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="31.5" thickBot="1">
+    <row r="252" spans="1:11" ht="31.5" thickBot="1">
       <c r="A252" s="6" t="s">
         <v>147</v>
       </c>
@@ -14079,12 +14688,12 @@
       <c r="H252" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J252" t="str">
+      <c r="K252" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_006_global_score_range_0_to_100</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="31.5" thickBot="1">
+    <row r="253" spans="1:11" ht="31.5" thickBot="1">
       <c r="A253" s="6" t="s">
         <v>147</v>
       </c>
@@ -14105,12 +14714,12 @@
       <c r="H253" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J253" t="str">
+      <c r="K253" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_007_weights_sum_validation</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="31.5" thickBot="1">
+    <row r="254" spans="1:11" ht="31.5" thickBot="1">
       <c r="A254" s="6" t="s">
         <v>147</v>
       </c>
@@ -14131,12 +14740,12 @@
       <c r="H254" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J254" t="str">
+      <c r="K254" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_008_weights_normalization_auto</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="31.5" thickBot="1">
+    <row r="255" spans="1:11" ht="31.5" thickBot="1">
       <c r="A255" s="6" t="s">
         <v>147</v>
       </c>
@@ -14157,12 +14766,12 @@
       <c r="H255" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J255" t="str">
+      <c r="K255" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_009_weights_custom_budget_30</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="31.5" thickBot="1">
+    <row r="256" spans="1:11" ht="31.5" thickBot="1">
       <c r="A256" s="6" t="s">
         <v>147</v>
       </c>
@@ -14183,12 +14792,12 @@
       <c r="H256" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J256" t="str">
+      <c r="K256" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_010_weights_custom_time_25</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="31.5" thickBot="1">
+    <row r="257" spans="1:11" ht="31.5" thickBot="1">
       <c r="A257" s="6" t="s">
         <v>147</v>
       </c>
@@ -14209,12 +14818,12 @@
       <c r="H257" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J257" t="str">
+      <c r="K257" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_011_weights_per_project_type</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="31.5" thickBot="1">
+    <row r="258" spans="1:11" ht="31.5" thickBot="1">
       <c r="A258" s="6" t="s">
         <v>147</v>
       </c>
@@ -14235,12 +14844,12 @@
       <c r="H258" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J258" t="str">
+      <c r="K258" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_012_weights_history_tracking</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="16.5" thickBot="1">
+    <row r="259" spans="1:11" ht="16.5" thickBot="1">
       <c r="A259" s="6" t="s">
         <v>148</v>
       </c>
@@ -14254,7 +14863,7 @@
       <c r="E259" s="7"/>
       <c r="F259" s="5"/>
     </row>
-    <row r="260" spans="1:10" ht="31.5" thickBot="1">
+    <row r="260" spans="1:11" ht="31.5" thickBot="1">
       <c r="A260" s="6" t="s">
         <v>149</v>
       </c>
@@ -14275,12 +14884,12 @@
       <c r="H260" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J260" t="str">
+      <c r="K260" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_001_detect_mass_changes_15_in_30min</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="31.5" thickBot="1">
+    <row r="261" spans="1:11" ht="31.5" thickBot="1">
       <c r="A261" s="6" t="s">
         <v>149</v>
       </c>
@@ -14301,12 +14910,12 @@
       <c r="H261" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J261" t="str">
+      <c r="K261" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_002_no_violation_10_in_60min</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="31.5" thickBot="1">
+    <row r="262" spans="1:11" ht="31.5" thickBot="1">
       <c r="A262" s="6" t="s">
         <v>149</v>
       </c>
@@ -14327,12 +14936,12 @@
       <c r="H262" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J262" t="str">
+      <c r="K262" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_003_mass_changes_window_sliding</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="31.5" thickBot="1">
+    <row r="263" spans="1:11" ht="31.5" thickBot="1">
       <c r="A263" s="6" t="s">
         <v>149</v>
       </c>
@@ -14353,12 +14962,12 @@
       <c r="H263" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J263" t="str">
+      <c r="K263" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_004_mass_changes_flag_for_review</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="31.5" thickBot="1">
+    <row r="264" spans="1:11" ht="31.5" thickBot="1">
       <c r="A264" s="6" t="s">
         <v>149</v>
       </c>
@@ -14379,12 +14988,12 @@
       <c r="H264" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J264" t="str">
+      <c r="K264" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_005_detect_resolve_reintroduce_4_times</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="31.5" thickBot="1">
+    <row r="265" spans="1:11" ht="31.5" thickBot="1">
       <c r="A265" s="6" t="s">
         <v>149</v>
       </c>
@@ -14405,12 +15014,12 @@
       <c r="H265" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J265" t="str">
+      <c r="K265" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_006_no_violation_2_times</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="31.5" thickBot="1">
+    <row r="266" spans="1:11" ht="31.5" thickBot="1">
       <c r="A266" s="6" t="s">
         <v>149</v>
       </c>
@@ -14431,12 +15040,12 @@
       <c r="H266" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J266" t="str">
+      <c r="K266" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_007_hash_comparison_same_content</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="31.5" thickBot="1">
+    <row r="267" spans="1:11" ht="31.5" thickBot="1">
       <c r="A267" s="6" t="s">
         <v>149</v>
       </c>
@@ -14457,12 +15066,12 @@
       <c r="H267" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J267" t="str">
+      <c r="K267" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_008_penalty_minus_5_points</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="31.5" thickBot="1">
+    <row r="268" spans="1:11" ht="31.5" thickBot="1">
       <c r="A268" s="6" t="s">
         <v>149</v>
       </c>
@@ -14483,12 +15092,12 @@
       <c r="H268" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J268" t="str">
+      <c r="K268" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_009_detect_95_percent_3_docs</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="31.5" thickBot="1">
+    <row r="269" spans="1:11" ht="31.5" thickBot="1">
       <c r="A269" s="6" t="s">
         <v>149</v>
       </c>
@@ -14509,12 +15118,12 @@
       <c r="H269" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J269" t="str">
+      <c r="K269" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_010_no_violation_95_percent_50_docs</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="31.5" thickBot="1">
+    <row r="270" spans="1:11" ht="31.5" thickBot="1">
       <c r="A270" s="6" t="s">
         <v>149</v>
       </c>
@@ -14535,12 +15144,12 @@
       <c r="H270" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J270" t="str">
+      <c r="K270" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_011_threshold_90_percent_5_docs</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="31.5" thickBot="1">
+    <row r="271" spans="1:11" ht="31.5" thickBot="1">
       <c r="A271" s="6" t="s">
         <v>149</v>
       </c>
@@ -14561,12 +15170,12 @@
       <c r="H271" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J271" t="str">
+      <c r="K271" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_012_require_audit_action</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="31.5" thickBot="1">
+    <row r="272" spans="1:11" ht="31.5" thickBot="1">
       <c r="A272" s="6" t="s">
         <v>149</v>
       </c>
@@ -14587,12 +15196,12 @@
       <c r="H272" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J272" t="str">
+      <c r="K272" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_013_detect_weight_change_25_percent</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="31.5" thickBot="1">
+    <row r="273" spans="1:11" ht="31.5" thickBot="1">
       <c r="A273" s="6" t="s">
         <v>149</v>
       </c>
@@ -14613,12 +15222,12 @@
       <c r="H273" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J273" t="str">
+      <c r="K273" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_014_no_violation_change_15_percent</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="31.5" thickBot="1">
+    <row r="274" spans="1:11" ht="31.5" thickBot="1">
       <c r="A274" s="6" t="s">
         <v>149</v>
       </c>
@@ -14639,12 +15248,12 @@
       <c r="H274" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J274" t="str">
+      <c r="K274" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_015_24h_window_tracking</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="31.5" thickBot="1">
+    <row r="275" spans="1:11" ht="31.5" thickBot="1">
       <c r="A275" s="6" t="s">
         <v>149</v>
       </c>
@@ -14665,12 +15274,12 @@
       <c r="H275" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J275" t="str">
+      <c r="K275" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_016_notify_admin_action</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="16.5" thickBot="1">
+    <row r="276" spans="1:11" ht="16.5" thickBot="1">
       <c r="A276" s="6" t="s">
         <v>150</v>
       </c>
@@ -14683,12 +15292,12 @@
       <c r="D276" s="6"/>
       <c r="E276" s="7"/>
       <c r="F276" s="5"/>
-      <c r="J276" t="str">
+      <c r="K276" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-ALR-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="31.5" thickBot="1">
+    <row r="277" spans="1:11" ht="31.5" thickBot="1">
       <c r="A277" s="6" t="s">
         <v>151</v>
       </c>
@@ -14712,12 +15321,12 @@
       <c r="I277" t="s">
         <v>810</v>
       </c>
-      <c r="J277" t="str">
+      <c r="K277" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_001_wbs_item_creation_all_fields</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="31.5" thickBot="1">
+    <row r="278" spans="1:11" ht="31.5" thickBot="1">
       <c r="A278" s="6" t="s">
         <v>151</v>
       </c>
@@ -14738,12 +15347,12 @@
       <c r="H278" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J278" t="str">
+      <c r="K278" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="31.5" thickBot="1">
+    <row r="279" spans="1:11" ht="31.5" thickBot="1">
       <c r="A279" s="6" t="s">
         <v>151</v>
       </c>
@@ -14764,12 +15373,12 @@
       <c r="H279" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J279" t="str">
+      <c r="K279" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="31.5" thickBot="1">
+    <row r="280" spans="1:11" ht="31.5" thickBot="1">
       <c r="A280" s="6" t="s">
         <v>151</v>
       </c>
@@ -14790,12 +15399,12 @@
       <c r="H280" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J280" t="str">
+      <c r="K280" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="31.5" thickBot="1">
+    <row r="281" spans="1:11" ht="31.5" thickBot="1">
       <c r="A281" s="6" t="s">
         <v>151</v>
       </c>
@@ -14816,12 +15425,12 @@
       <c r="H281" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J281" t="str">
-        <f t="shared" ref="J281:J331" si="4">CONCATENATE(A281,C281)</f>
+      <c r="K281" t="str">
+        <f t="shared" ref="K281:K331" si="4">CONCATENATE(A281,C281)</f>
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="31.5" thickBot="1">
+    <row r="282" spans="1:11" ht="31.5" thickBot="1">
       <c r="A282" s="6" t="s">
         <v>151</v>
       </c>
@@ -14842,12 +15451,12 @@
       <c r="H282" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J282" t="str">
+      <c r="K282" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="31.5" thickBot="1">
+    <row r="283" spans="1:11" ht="31.5" thickBot="1">
       <c r="A283" s="6" t="s">
         <v>151</v>
       </c>
@@ -14868,12 +15477,12 @@
       <c r="H283" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J283" t="str">
+      <c r="K283" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="31.5" thickBot="1">
+    <row r="284" spans="1:11" ht="31.5" thickBot="1">
       <c r="A284" s="6" t="s">
         <v>151</v>
       </c>
@@ -14894,12 +15503,12 @@
       <c r="H284" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J284" t="str">
+      <c r="K284" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="31.5" thickBot="1">
+    <row r="285" spans="1:11" ht="31.5" thickBot="1">
       <c r="A285" s="6" t="s">
         <v>151</v>
       </c>
@@ -14920,12 +15529,12 @@
       <c r="H285" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J285" t="str">
+      <c r="K285" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="31.5" thickBot="1">
+    <row r="286" spans="1:11" ht="31.5" thickBot="1">
       <c r="A286" s="6" t="s">
         <v>151</v>
       </c>
@@ -14946,12 +15555,12 @@
       <c r="H286" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J286" t="str">
+      <c r="K286" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="31.5" thickBot="1">
+    <row r="287" spans="1:11" ht="31.5" thickBot="1">
       <c r="A287" s="6" t="s">
         <v>151</v>
       </c>
@@ -14972,12 +15581,12 @@
       <c r="H287" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J287" t="str">
+      <c r="K287" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="31.5" thickBot="1">
+    <row r="288" spans="1:11" ht="31.5" thickBot="1">
       <c r="A288" s="6" t="s">
         <v>151</v>
       </c>
@@ -14998,12 +15607,12 @@
       <c r="H288" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J288" t="str">
+      <c r="K288" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="31.5" thickBot="1">
+    <row r="289" spans="1:11" ht="31.5" thickBot="1">
       <c r="A289" s="6" t="s">
         <v>151</v>
       </c>
@@ -15024,12 +15633,12 @@
       <c r="H289" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J289" t="str">
+      <c r="K289" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="31.5" thickBot="1">
+    <row r="290" spans="1:11" ht="31.5" thickBot="1">
       <c r="A290" s="6" t="s">
         <v>151</v>
       </c>
@@ -15050,12 +15659,12 @@
       <c r="H290" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J290" t="str">
+      <c r="K290" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="31.5" thickBot="1">
+    <row r="291" spans="1:11" ht="31.5" thickBot="1">
       <c r="A291" s="6" t="s">
         <v>151</v>
       </c>
@@ -15076,12 +15685,12 @@
       <c r="H291" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J291" t="str">
+      <c r="K291" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="31.5" thickBot="1">
+    <row r="292" spans="1:11" ht="31.5" thickBot="1">
       <c r="A292" s="6" t="s">
         <v>151</v>
       </c>
@@ -15102,12 +15711,12 @@
       <c r="H292" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J292" t="str">
+      <c r="K292" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="31.5" thickBot="1">
+    <row r="293" spans="1:11" ht="31.5" thickBot="1">
       <c r="A293" s="6" t="s">
         <v>151</v>
       </c>
@@ -15128,12 +15737,12 @@
       <c r="H293" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J293" t="str">
+      <c r="K293" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="31.5" thickBot="1">
+    <row r="294" spans="1:11" ht="31.5" thickBot="1">
       <c r="A294" s="6" t="s">
         <v>151</v>
       </c>
@@ -15154,12 +15763,12 @@
       <c r="H294" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J294" t="str">
+      <c r="K294" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_018_wbs_level_parent_child_validation</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="16.5" thickBot="1">
+    <row r="295" spans="1:11" ht="16.5" thickBot="1">
       <c r="A295" s="6" t="s">
         <v>152</v>
       </c>
@@ -15172,12 +15781,12 @@
       <c r="D295" s="6"/>
       <c r="E295" s="7"/>
       <c r="F295" s="5"/>
-      <c r="J295" t="str">
+      <c r="K295" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="16.5" thickBot="1">
+    <row r="296" spans="1:11" ht="16.5" thickBot="1">
       <c r="A296" s="6" t="s">
         <v>153</v>
       </c>
@@ -15190,12 +15799,12 @@
       <c r="D296" s="6"/>
       <c r="E296" s="7"/>
       <c r="F296" s="5"/>
-      <c r="J296" t="str">
+      <c r="K296" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="16.5" thickBot="1">
+    <row r="297" spans="1:11" ht="16.5" thickBot="1">
       <c r="A297" s="6" t="s">
         <v>154</v>
       </c>
@@ -15208,12 +15817,12 @@
       <c r="D297" s="6"/>
       <c r="E297" s="7"/>
       <c r="F297" s="5"/>
-      <c r="J297" t="str">
+      <c r="K297" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="16.5" thickBot="1">
+    <row r="298" spans="1:11" ht="16.5" thickBot="1">
       <c r="A298" s="6" t="s">
         <v>155</v>
       </c>
@@ -15226,12 +15835,12 @@
       <c r="D298" s="6"/>
       <c r="E298" s="7"/>
       <c r="F298" s="5"/>
-      <c r="J298" t="str">
+      <c r="K298" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-PRJ-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="16.5" thickBot="1">
+    <row r="299" spans="1:11" ht="16.5" thickBot="1">
       <c r="A299" s="6" t="s">
         <v>156</v>
       </c>
@@ -15244,12 +15853,12 @@
       <c r="D299" s="6"/>
       <c r="E299" s="7"/>
       <c r="F299" s="5"/>
-      <c r="J299" t="str">
+      <c r="K299" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-DTO-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="16.5" thickBot="1">
+    <row r="300" spans="1:11" ht="16.5" thickBot="1">
       <c r="A300" s="6" t="s">
         <v>157</v>
       </c>
@@ -15262,12 +15871,12 @@
       <c r="D300" s="6"/>
       <c r="E300" s="7"/>
       <c r="F300" s="5"/>
-      <c r="J300" t="str">
+      <c r="K300" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-BOM-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="16.5" thickBot="1">
+    <row r="301" spans="1:11" ht="16.5" thickBot="1">
       <c r="A301" s="6" t="s">
         <v>158</v>
       </c>
@@ -15280,12 +15889,12 @@
       <c r="D301" s="6"/>
       <c r="E301" s="7"/>
       <c r="F301" s="5"/>
-      <c r="J301" t="str">
+      <c r="K301" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-BOM-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="31.5" thickBot="1">
+    <row r="302" spans="1:11" ht="31.5" thickBot="1">
       <c r="A302" s="6" t="s">
         <v>159</v>
       </c>
@@ -15309,12 +15918,12 @@
       <c r="I302" t="s">
         <v>811</v>
       </c>
-      <c r="J302" t="str">
+      <c r="K302" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="31.5" thickBot="1">
+    <row r="303" spans="1:11" ht="31.5" thickBot="1">
       <c r="A303" s="6" t="s">
         <v>159</v>
       </c>
@@ -15335,12 +15944,12 @@
       <c r="H303" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J303" t="str">
+      <c r="K303" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="31.5" thickBot="1">
+    <row r="304" spans="1:11" ht="31.5" thickBot="1">
       <c r="A304" s="6" t="s">
         <v>159</v>
       </c>
@@ -15361,12 +15970,12 @@
       <c r="H304" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J304" t="str">
+      <c r="K304" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="31.5" thickBot="1">
+    <row r="305" spans="1:11" ht="31.5" thickBot="1">
       <c r="A305" s="6" t="s">
         <v>159</v>
       </c>
@@ -15387,12 +15996,12 @@
       <c r="H305" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J305" t="str">
+      <c r="K305" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="31.5" thickBot="1">
+    <row r="306" spans="1:11" ht="31.5" thickBot="1">
       <c r="A306" s="6" t="s">
         <v>159</v>
       </c>
@@ -15413,12 +16022,12 @@
       <c r="H306" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J306" t="str">
+      <c r="K306" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="31.5" thickBot="1">
+    <row r="307" spans="1:11" ht="31.5" thickBot="1">
       <c r="A307" s="6" t="s">
         <v>159</v>
       </c>
@@ -15439,12 +16048,12 @@
       <c r="H307" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J307" t="str">
+      <c r="K307" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="31.5" thickBot="1">
+    <row r="308" spans="1:11" ht="31.5" thickBot="1">
       <c r="A308" s="6" t="s">
         <v>159</v>
       </c>
@@ -15465,12 +16074,12 @@
       <c r="H308" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J308" t="str">
+      <c r="K308" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="31.5" thickBot="1">
+    <row r="309" spans="1:11" ht="31.5" thickBot="1">
       <c r="A309" s="6" t="s">
         <v>159</v>
       </c>
@@ -15491,12 +16100,12 @@
       <c r="H309" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J309" t="str">
+      <c r="K309" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="31.5" thickBot="1">
+    <row r="310" spans="1:11" ht="31.5" thickBot="1">
       <c r="A310" s="6" t="s">
         <v>159</v>
       </c>
@@ -15517,12 +16126,12 @@
       <c r="H310" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J310" t="str">
+      <c r="K310" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="31.5" thickBot="1">
+    <row r="311" spans="1:11" ht="31.5" thickBot="1">
       <c r="A311" s="6" t="s">
         <v>159</v>
       </c>
@@ -15543,12 +16152,12 @@
       <c r="H311" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J311" t="str">
+      <c r="K311" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="31.5" thickBot="1">
+    <row r="312" spans="1:11" ht="31.5" thickBot="1">
       <c r="A312" s="6" t="s">
         <v>159</v>
       </c>
@@ -15569,12 +16178,12 @@
       <c r="H312" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J312" t="str">
+      <c r="K312" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
       </c>
     </row>
-    <row r="313" spans="1:10" ht="31.5" thickBot="1">
+    <row r="313" spans="1:11" ht="31.5" thickBot="1">
       <c r="A313" s="6" t="s">
         <v>159</v>
       </c>
@@ -15595,12 +16204,12 @@
       <c r="H313" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J313" t="str">
+      <c r="K313" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="31.5" thickBot="1">
+    <row r="314" spans="1:11" ht="31.5" thickBot="1">
       <c r="A314" s="6" t="s">
         <v>159</v>
       </c>
@@ -15621,12 +16230,12 @@
       <c r="H314" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J314" t="str">
+      <c r="K314" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="31.5" thickBot="1">
+    <row r="315" spans="1:11" ht="31.5" thickBot="1">
       <c r="A315" s="6" t="s">
         <v>159</v>
       </c>
@@ -15647,12 +16256,12 @@
       <c r="H315" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J315" t="str">
+      <c r="K315" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="31.5" thickBot="1">
+    <row r="316" spans="1:11" ht="31.5" thickBot="1">
       <c r="A316" s="6" t="s">
         <v>159</v>
       </c>
@@ -15673,12 +16282,12 @@
       <c r="H316" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J316" t="str">
+      <c r="K316" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="31.5" thickBot="1">
+    <row r="317" spans="1:11" ht="31.5" thickBot="1">
       <c r="A317" s="6" t="s">
         <v>159</v>
       </c>
@@ -15699,12 +16308,12 @@
       <c r="H317" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J317" t="str">
+      <c r="K317" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="31.5" thickBot="1">
+    <row r="318" spans="1:11" ht="31.5" thickBot="1">
       <c r="A318" s="6" t="s">
         <v>160</v>
       </c>
@@ -15722,12 +16331,12 @@
       <c r="G318" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J318" t="str">
+      <c r="K318" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="31.5" thickBot="1">
+    <row r="319" spans="1:11" ht="31.5" thickBot="1">
       <c r="A319" s="6" t="s">
         <v>160</v>
       </c>
@@ -15745,12 +16354,12 @@
       <c r="G319" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J319" t="str">
+      <c r="K319" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="31.5" thickBot="1">
+    <row r="320" spans="1:11" ht="31.5" thickBot="1">
       <c r="A320" s="6" t="s">
         <v>160</v>
       </c>
@@ -15768,12 +16377,12 @@
       <c r="G320" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J320" t="str">
+      <c r="K320" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="31.5" thickBot="1">
+    <row r="321" spans="1:11" ht="31.5" thickBot="1">
       <c r="A321" s="6" t="s">
         <v>160</v>
       </c>
@@ -15791,12 +16400,12 @@
       <c r="G321" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J321" t="str">
+      <c r="K321" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
       </c>
     </row>
-    <row r="322" spans="1:10" ht="31.5" thickBot="1">
+    <row r="322" spans="1:11" ht="31.5" thickBot="1">
       <c r="A322" s="6" t="s">
         <v>160</v>
       </c>
@@ -15814,12 +16423,12 @@
       <c r="G322" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J322" t="str">
+      <c r="K322" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="31.5" thickBot="1">
+    <row r="323" spans="1:11" ht="31.5" thickBot="1">
       <c r="A323" s="6" t="s">
         <v>160</v>
       </c>
@@ -15837,12 +16446,12 @@
       <c r="G323" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J323" t="str">
+      <c r="K323" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="31.5" thickBot="1">
+    <row r="324" spans="1:11" ht="31.5" thickBot="1">
       <c r="A324" s="6" t="s">
         <v>160</v>
       </c>
@@ -15860,12 +16469,12 @@
       <c r="G324" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J324" t="str">
+      <c r="K324" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
       </c>
     </row>
-    <row r="325" spans="1:10" ht="16.5" thickBot="1">
+    <row r="325" spans="1:11" ht="16.5" thickBot="1">
       <c r="A325" s="6" t="s">
         <v>160</v>
       </c>
@@ -15883,12 +16492,12 @@
       <c r="G325" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J325" t="str">
+      <c r="K325" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
       </c>
     </row>
-    <row r="326" spans="1:10" ht="31.5" thickBot="1">
+    <row r="326" spans="1:11" ht="31.5" thickBot="1">
       <c r="A326" s="6" t="s">
         <v>160</v>
       </c>
@@ -15906,12 +16515,12 @@
       <c r="G326" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J326" t="str">
+      <c r="K326" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="31.5" thickBot="1">
+    <row r="327" spans="1:11" ht="31.5" thickBot="1">
       <c r="A327" s="6" t="s">
         <v>160</v>
       </c>
@@ -15929,12 +16538,12 @@
       <c r="G327" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J327" t="str">
+      <c r="K327" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="31.5" thickBot="1">
+    <row r="328" spans="1:11" ht="31.5" thickBot="1">
       <c r="A328" s="6" t="s">
         <v>160</v>
       </c>
@@ -15952,12 +16561,12 @@
       <c r="G328" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J328" t="str">
+      <c r="K328" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="31.5" thickBot="1">
+    <row r="329" spans="1:11" ht="31.5" thickBot="1">
       <c r="A329" s="6" t="s">
         <v>160</v>
       </c>
@@ -15975,12 +16584,12 @@
       <c r="G329" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J329" t="str">
+      <c r="K329" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="31.5" thickBot="1">
+    <row r="330" spans="1:11" ht="31.5" thickBot="1">
       <c r="A330" s="6" t="s">
         <v>160</v>
       </c>
@@ -15998,12 +16607,12 @@
       <c r="G330" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J330" t="str">
+      <c r="K330" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
       </c>
     </row>
-    <row r="331" spans="1:10" ht="31.5" thickBot="1">
+    <row r="331" spans="1:11" ht="31.5" thickBot="1">
       <c r="A331" s="6" t="s">
         <v>160</v>
       </c>
@@ -16021,12 +16630,12 @@
       <c r="G331" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="J331" t="str">
+      <c r="K331" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_014_incoterm_impact_on_lead_time</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="16.5" thickBot="1">
+    <row r="332" spans="1:11" ht="16.5" thickBot="1">
       <c r="A332" s="6" t="s">
         <v>161</v>
       </c>
@@ -16040,7 +16649,7 @@
       <c r="E332" s="7"/>
       <c r="F332" s="5"/>
     </row>
-    <row r="333" spans="1:10" ht="16.5" thickBot="1">
+    <row r="333" spans="1:11" ht="16.5" thickBot="1">
       <c r="A333" s="6" t="s">
         <v>162</v>
       </c>
@@ -16054,7 +16663,7 @@
       <c r="E333" s="7"/>
       <c r="F333" s="5"/>
     </row>
-    <row r="334" spans="1:10" ht="16.5" thickBot="1">
+    <row r="334" spans="1:11" ht="16.5" thickBot="1">
       <c r="A334" s="6" t="s">
         <v>163</v>
       </c>
@@ -16068,7 +16677,7 @@
       <c r="E334" s="7"/>
       <c r="F334" s="5"/>
     </row>
-    <row r="335" spans="1:10" ht="31.5" thickBot="1">
+    <row r="335" spans="1:11" ht="31.5" thickBot="1">
       <c r="A335" s="6" t="s">
         <v>164</v>
       </c>
@@ -16082,7 +16691,7 @@
       <c r="E335" s="7"/>
       <c r="F335" s="5"/>
     </row>
-    <row r="336" spans="1:10" ht="31.5" thickBot="1">
+    <row r="336" spans="1:11" ht="31.5" thickBot="1">
       <c r="A336" s="6" t="s">
         <v>165</v>
       </c>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E2ED11-DD88-49A3-AD97-0E4F17FD7B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638CA2D0-AAC5-4415-BD7E-DD67DB7B7266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="863">
   <si>
     <t>Nº</t>
   </si>
@@ -3383,7 +3383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3440,9 +3440,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -6963,7 +6960,7 @@
       <c r="A103" t="s">
         <v>107</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="B103" s="21" t="s">
         <v>220</v>
       </c>
       <c r="C103" t="s">
@@ -13327,6 +13324,9 @@
       <c r="H199" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J199" t="s">
+        <v>404</v>
+      </c>
       <c r="K199" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_002_r6_deviation_5_percent_pass</v>
@@ -13353,6 +13353,9 @@
       <c r="H200" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J200" t="s">
+        <v>404</v>
+      </c>
       <c r="K200" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_003_r6_deviation_4_9_percent_pass</v>
@@ -13379,6 +13382,9 @@
       <c r="H201" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J201" t="s">
+        <v>404</v>
+      </c>
       <c r="K201" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_004_r6_over_budget_critical</v>
@@ -13405,6 +13411,9 @@
       <c r="H202" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J202" t="s">
+        <v>404</v>
+      </c>
       <c r="K202" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_005_r6_under_budget_warning</v>
@@ -13431,6 +13440,9 @@
       <c r="H203" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J203" t="s">
+        <v>404</v>
+      </c>
       <c r="K203" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_006_r6_exact_match_pass</v>
@@ -13457,6 +13469,9 @@
       <c r="H204" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J204" t="s">
+        <v>404</v>
+      </c>
       <c r="K204" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_007_r15_bom_no_budget_alert</v>
@@ -13483,6 +13498,9 @@
       <c r="H205" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J205" t="s">
+        <v>404</v>
+      </c>
       <c r="K205" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_008_r15_bom_with_budget_pass</v>
@@ -13509,6 +13527,9 @@
       <c r="H206" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J206" t="s">
+        <v>404</v>
+      </c>
       <c r="K206" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_009_r15_bom_client_provided_exception</v>
@@ -13535,6 +13556,9 @@
       <c r="H207" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J207" t="s">
+        <v>404</v>
+      </c>
       <c r="K207" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_010_r15_multiple_bom_violations</v>
@@ -13561,6 +13585,9 @@
       <c r="H208" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J208" t="s">
+        <v>404</v>
+      </c>
       <c r="K208" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_011_r15_affected_items_list</v>
@@ -13587,6 +13614,9 @@
       <c r="H209" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J209" t="s">
+        <v>404</v>
+      </c>
       <c r="K209" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_012_r16_deviation_11_percent_alert</v>
@@ -13613,6 +13643,9 @@
       <c r="H210" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J210" t="s">
+        <v>404</v>
+      </c>
       <c r="K210" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_013_r16_deviation_10_percent_pass</v>
@@ -13639,6 +13672,9 @@
       <c r="H211" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J211" t="s">
+        <v>404</v>
+      </c>
       <c r="K211" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_014_r16_over_budget_critical</v>
@@ -13665,6 +13701,9 @@
       <c r="H212" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J212" t="s">
+        <v>404</v>
+      </c>
       <c r="K212" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_015_r16_under_budget_different_severity</v>
@@ -13691,6 +13730,9 @@
       <c r="H213" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J213" t="s">
+        <v>404</v>
+      </c>
       <c r="K213" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-002test_016_r16_trend_calculation</v>
@@ -13720,6 +13762,9 @@
       <c r="I214" t="s">
         <v>809</v>
       </c>
+      <c r="J214" t="s">
+        <v>404</v>
+      </c>
       <c r="K214" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_001_r1_dates_mismatch_alert</v>
@@ -13746,6 +13791,9 @@
       <c r="H215" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J215" t="s">
+        <v>404</v>
+      </c>
       <c r="K215" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_002_r1_dates_match_pass</v>
@@ -13772,6 +13820,9 @@
       <c r="H216" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J216" t="s">
+        <v>404</v>
+      </c>
       <c r="K216" t="str">
         <f t="shared" si="2"/>
         <v>TS-UD-COH-RUL-003test_003_r1_schedule_late_critical</v>
@@ -13798,6 +13849,9 @@
       <c r="H217" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J217" t="s">
+        <v>404</v>
+      </c>
       <c r="K217" t="str">
         <f t="shared" ref="K217:K280" si="3">CONCATENATE(A217,C217)</f>
         <v>TS-UD-COH-RUL-003test_004_r1_schedule_early_warning</v>
@@ -13824,6 +13878,9 @@
       <c r="H218" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J218" t="s">
+        <v>404</v>
+      </c>
       <c r="K218" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_005_r1_delta_days_calculation</v>
@@ -13850,6 +13907,9 @@
       <c r="H219" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J219" t="s">
+        <v>404</v>
+      </c>
       <c r="K219" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_006_r2_milestone_no_activity_alert</v>
@@ -13876,6 +13936,9 @@
       <c r="H220" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J220" t="s">
+        <v>404</v>
+      </c>
       <c r="K220" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_007_r2_milestone_with_activity_pass</v>
@@ -13902,6 +13965,9 @@
       <c r="H221" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J221" t="s">
+        <v>404</v>
+      </c>
       <c r="K221" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_008_r2_milestone_date_mismatch_alert</v>
@@ -13928,6 +13994,9 @@
       <c r="H222" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J222" t="s">
+        <v>404</v>
+      </c>
       <c r="K222" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_009_r2_multiple_milestones_violations</v>
@@ -13954,6 +14023,9 @@
       <c r="H223" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J223" t="s">
+        <v>404</v>
+      </c>
       <c r="K223" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_010_r2_unlinked_milestones_list</v>
@@ -13980,6 +14052,9 @@
       <c r="H224" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J224" t="s">
+        <v>404</v>
+      </c>
       <c r="K224" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_011_r5_activity_exceeds_contract_alert</v>
@@ -14006,6 +14081,9 @@
       <c r="H225" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J225" t="s">
+        <v>404</v>
+      </c>
       <c r="K225" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_012_r5_activity_within_contract_pass</v>
@@ -14032,6 +14110,9 @@
       <c r="H226" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J226" t="s">
+        <v>404</v>
+      </c>
       <c r="K226" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_013_r5_exceeding_activities_list</v>
@@ -14058,6 +14139,9 @@
       <c r="H227" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J227" t="s">
+        <v>404</v>
+      </c>
       <c r="K227" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_014_r5_alert_severity_critical</v>
@@ -14084,6 +14168,9 @@
       <c r="H228" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J228" t="s">
+        <v>404</v>
+      </c>
       <c r="K228" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_015_r14_order_date_passed_critical</v>
@@ -14110,6 +14197,9 @@
       <c r="H229" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J229" t="s">
+        <v>404</v>
+      </c>
       <c r="K229" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-003test_016_r14_order_date_tight_warning</v>
@@ -14128,6 +14218,9 @@
       <c r="D230" s="6"/>
       <c r="E230" s="7"/>
       <c r="F230" s="5"/>
+      <c r="J230" t="s">
+        <v>404</v>
+      </c>
       <c r="K230" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-004Tests not individually listed</v>
@@ -14146,6 +14239,9 @@
       <c r="D231" s="6"/>
       <c r="E231" s="7"/>
       <c r="F231" s="5"/>
+      <c r="J231" t="s">
+        <v>404</v>
+      </c>
       <c r="K231" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-005Tests not individually listed</v>
@@ -14164,6 +14260,9 @@
       <c r="D232" s="6"/>
       <c r="E232" s="7"/>
       <c r="F232" s="5"/>
+      <c r="J232" t="s">
+        <v>404</v>
+      </c>
       <c r="K232" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-RUL-006Tests not individually listed</v>
@@ -14193,7 +14292,9 @@
       <c r="I233" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="J233" s="21"/>
+      <c r="J233" t="s">
+        <v>404</v>
+      </c>
       <c r="K233" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_001_subscore_no_alerts_100_percent</v>
@@ -14220,6 +14321,9 @@
       <c r="H234" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J234" t="s">
+        <v>404</v>
+      </c>
       <c r="K234" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_002_subscore_one_alert_penalized</v>
@@ -14246,6 +14350,9 @@
       <c r="H235" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J235" t="s">
+        <v>404</v>
+      </c>
       <c r="K235" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_003_subscore_multiple_alerts_cumulative</v>
@@ -14272,6 +14379,9 @@
       <c r="H236" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J236" t="s">
+        <v>404</v>
+      </c>
       <c r="K236" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_004_subscore_severity_low_penalty_5</v>
@@ -14298,6 +14408,9 @@
       <c r="H237" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J237" t="s">
+        <v>404</v>
+      </c>
       <c r="K237" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_005_subscore_severity_medium_penalty_10</v>
@@ -14324,6 +14437,9 @@
       <c r="H238" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J238" t="s">
+        <v>404</v>
+      </c>
       <c r="K238" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_006_subscore_severity_high_penalty_20</v>
@@ -14350,6 +14466,9 @@
       <c r="H239" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J239" t="s">
+        <v>404</v>
+      </c>
       <c r="K239" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_007_subscore_severity_critical_penalty_30</v>
@@ -14376,6 +14495,9 @@
       <c r="H240" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J240" t="s">
+        <v>404</v>
+      </c>
       <c r="K240" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_008_subscore_scope_calculation</v>
@@ -14402,6 +14524,9 @@
       <c r="H241" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J241" t="s">
+        <v>404</v>
+      </c>
       <c r="K241" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_009_subscore_budget_calculation</v>
@@ -14428,6 +14553,9 @@
       <c r="H242" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J242" t="s">
+        <v>404</v>
+      </c>
       <c r="K242" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_010_subscore_quality_calculation</v>
@@ -14454,6 +14582,9 @@
       <c r="H243" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J243" t="s">
+        <v>404</v>
+      </c>
       <c r="K243" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_011_subscore_technical_calculation</v>
@@ -14480,6 +14611,9 @@
       <c r="H244" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J244" t="s">
+        <v>404</v>
+      </c>
       <c r="K244" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_012_subscore_legal_calculation</v>
@@ -14506,6 +14640,9 @@
       <c r="H245" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J245" t="s">
+        <v>404</v>
+      </c>
       <c r="K245" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_013_subscore_time_calculation</v>
@@ -14532,6 +14669,9 @@
       <c r="H246" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J246" t="s">
+        <v>404</v>
+      </c>
       <c r="K246" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-001test_014_subscore_floor_at_zero</v>
@@ -14558,6 +14698,9 @@
       <c r="H247" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J247" t="s">
+        <v>404</v>
+      </c>
       <c r="K247" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_001_global_score_formula_verification</v>
@@ -14584,6 +14727,9 @@
       <c r="H248" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J248" t="s">
+        <v>404</v>
+      </c>
       <c r="K248" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_002_global_score_default_weights</v>
@@ -14610,6 +14756,9 @@
       <c r="H249" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J249" t="s">
+        <v>404</v>
+      </c>
       <c r="K249" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_003_global_score_all_100_equals_100</v>
@@ -14636,6 +14785,9 @@
       <c r="H250" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J250" t="s">
+        <v>404</v>
+      </c>
       <c r="K250" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_004_global_score_all_0_equals_0</v>
@@ -14662,6 +14814,9 @@
       <c r="H251" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J251" t="s">
+        <v>404</v>
+      </c>
       <c r="K251" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_005_global_score_mixed_subscores</v>
@@ -14688,6 +14843,9 @@
       <c r="H252" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J252" t="s">
+        <v>404</v>
+      </c>
       <c r="K252" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_006_global_score_range_0_to_100</v>
@@ -14714,6 +14872,9 @@
       <c r="H253" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J253" t="s">
+        <v>404</v>
+      </c>
       <c r="K253" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_007_weights_sum_validation</v>
@@ -14740,6 +14901,9 @@
       <c r="H254" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J254" t="s">
+        <v>404</v>
+      </c>
       <c r="K254" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_008_weights_normalization_auto</v>
@@ -14766,6 +14930,9 @@
       <c r="H255" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J255" t="s">
+        <v>404</v>
+      </c>
       <c r="K255" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_009_weights_custom_budget_30</v>
@@ -14792,6 +14959,9 @@
       <c r="H256" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J256" t="s">
+        <v>404</v>
+      </c>
       <c r="K256" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_010_weights_custom_time_25</v>
@@ -14818,6 +14988,9 @@
       <c r="H257" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J257" t="s">
+        <v>404</v>
+      </c>
       <c r="K257" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_011_weights_per_project_type</v>
@@ -14844,6 +15017,9 @@
       <c r="H258" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J258" t="s">
+        <v>404</v>
+      </c>
       <c r="K258" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-SCR-002test_012_weights_history_tracking</v>
@@ -14862,6 +15038,9 @@
       <c r="D259" s="6"/>
       <c r="E259" s="7"/>
       <c r="F259" s="5"/>
+      <c r="J259" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="260" spans="1:11" ht="31.5" thickBot="1">
       <c r="A260" s="6" t="s">
@@ -14884,6 +15063,9 @@
       <c r="H260" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J260" t="s">
+        <v>404</v>
+      </c>
       <c r="K260" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_001_detect_mass_changes_15_in_30min</v>
@@ -14910,6 +15092,9 @@
       <c r="H261" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J261" t="s">
+        <v>404</v>
+      </c>
       <c r="K261" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_002_no_violation_10_in_60min</v>
@@ -14936,6 +15121,9 @@
       <c r="H262" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J262" t="s">
+        <v>404</v>
+      </c>
       <c r="K262" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_003_mass_changes_window_sliding</v>
@@ -14962,6 +15150,9 @@
       <c r="H263" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J263" t="s">
+        <v>404</v>
+      </c>
       <c r="K263" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_004_mass_changes_flag_for_review</v>
@@ -14988,6 +15179,9 @@
       <c r="H264" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J264" t="s">
+        <v>404</v>
+      </c>
       <c r="K264" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_005_detect_resolve_reintroduce_4_times</v>
@@ -15014,6 +15208,9 @@
       <c r="H265" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J265" t="s">
+        <v>404</v>
+      </c>
       <c r="K265" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_006_no_violation_2_times</v>
@@ -15040,6 +15237,9 @@
       <c r="H266" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J266" t="s">
+        <v>404</v>
+      </c>
       <c r="K266" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_007_hash_comparison_same_content</v>
@@ -15066,6 +15266,9 @@
       <c r="H267" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J267" t="s">
+        <v>404</v>
+      </c>
       <c r="K267" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_008_penalty_minus_5_points</v>
@@ -15092,6 +15295,9 @@
       <c r="H268" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J268" t="s">
+        <v>404</v>
+      </c>
       <c r="K268" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_009_detect_95_percent_3_docs</v>
@@ -15118,6 +15324,9 @@
       <c r="H269" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J269" t="s">
+        <v>404</v>
+      </c>
       <c r="K269" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_010_no_violation_95_percent_50_docs</v>
@@ -15144,6 +15353,9 @@
       <c r="H270" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J270" t="s">
+        <v>404</v>
+      </c>
       <c r="K270" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_011_threshold_90_percent_5_docs</v>
@@ -15170,6 +15382,9 @@
       <c r="H271" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J271" t="s">
+        <v>404</v>
+      </c>
       <c r="K271" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_012_require_audit_action</v>
@@ -15196,6 +15411,9 @@
       <c r="H272" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J272" t="s">
+        <v>404</v>
+      </c>
       <c r="K272" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_013_detect_weight_change_25_percent</v>
@@ -15222,6 +15440,9 @@
       <c r="H273" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J273" t="s">
+        <v>404</v>
+      </c>
       <c r="K273" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_014_no_violation_change_15_percent</v>
@@ -15248,6 +15469,9 @@
       <c r="H274" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J274" t="s">
+        <v>404</v>
+      </c>
       <c r="K274" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_015_24h_window_tracking</v>
@@ -15274,6 +15498,9 @@
       <c r="H275" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J275" t="s">
+        <v>404</v>
+      </c>
       <c r="K275" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-GAM-001test_016_notify_admin_action</v>
@@ -15292,6 +15519,9 @@
       <c r="D276" s="6"/>
       <c r="E276" s="7"/>
       <c r="F276" s="5"/>
+      <c r="J276" t="s">
+        <v>404</v>
+      </c>
       <c r="K276" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-COH-ALR-001Tests not individually listed</v>
@@ -15321,6 +15551,9 @@
       <c r="I277" t="s">
         <v>810</v>
       </c>
+      <c r="J277" t="s">
+        <v>404</v>
+      </c>
       <c r="K277" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_001_wbs_item_creation_all_fields</v>
@@ -15347,6 +15580,9 @@
       <c r="H278" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J278" t="s">
+        <v>404</v>
+      </c>
       <c r="K278" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
@@ -15373,6 +15609,9 @@
       <c r="H279" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J279" t="s">
+        <v>404</v>
+      </c>
       <c r="K279" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
@@ -15399,6 +15638,9 @@
       <c r="H280" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J280" t="s">
+        <v>404</v>
+      </c>
       <c r="K280" t="str">
         <f t="shared" si="3"/>
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
@@ -15425,6 +15667,9 @@
       <c r="H281" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J281" t="s">
+        <v>404</v>
+      </c>
       <c r="K281" t="str">
         <f t="shared" ref="K281:K331" si="4">CONCATENATE(A281,C281)</f>
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
@@ -15451,6 +15696,9 @@
       <c r="H282" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J282" t="s">
+        <v>404</v>
+      </c>
       <c r="K282" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
@@ -15477,6 +15725,9 @@
       <c r="H283" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J283" t="s">
+        <v>404</v>
+      </c>
       <c r="K283" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
@@ -15503,6 +15754,9 @@
       <c r="H284" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J284" t="s">
+        <v>404</v>
+      </c>
       <c r="K284" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
@@ -15529,6 +15783,9 @@
       <c r="H285" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J285" t="s">
+        <v>404</v>
+      </c>
       <c r="K285" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
@@ -15555,6 +15812,9 @@
       <c r="H286" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J286" t="s">
+        <v>404</v>
+      </c>
       <c r="K286" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
@@ -15581,6 +15841,9 @@
       <c r="H287" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J287" t="s">
+        <v>404</v>
+      </c>
       <c r="K287" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
@@ -15607,6 +15870,9 @@
       <c r="H288" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J288" t="s">
+        <v>404</v>
+      </c>
       <c r="K288" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
@@ -15633,6 +15899,9 @@
       <c r="H289" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J289" t="s">
+        <v>404</v>
+      </c>
       <c r="K289" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
@@ -15659,6 +15928,9 @@
       <c r="H290" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J290" t="s">
+        <v>404</v>
+      </c>
       <c r="K290" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
@@ -15685,6 +15957,9 @@
       <c r="H291" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J291" t="s">
+        <v>404</v>
+      </c>
       <c r="K291" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
@@ -15711,6 +15986,9 @@
       <c r="H292" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J292" t="s">
+        <v>404</v>
+      </c>
       <c r="K292" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
@@ -15737,6 +16015,9 @@
       <c r="H293" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J293" t="s">
+        <v>404</v>
+      </c>
       <c r="K293" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
@@ -15763,6 +16044,9 @@
       <c r="H294" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J294" t="s">
+        <v>404</v>
+      </c>
       <c r="K294" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-001test_018_wbs_level_parent_child_validation</v>
@@ -15781,6 +16065,9 @@
       <c r="D295" s="6"/>
       <c r="E295" s="7"/>
       <c r="F295" s="5"/>
+      <c r="J295" t="s">
+        <v>404</v>
+      </c>
       <c r="K295" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-002Tests not individually listed</v>
@@ -15799,6 +16086,9 @@
       <c r="D296" s="6"/>
       <c r="E296" s="7"/>
       <c r="F296" s="5"/>
+      <c r="J296" t="s">
+        <v>404</v>
+      </c>
       <c r="K296" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-003Tests not individually listed</v>
@@ -15817,6 +16107,9 @@
       <c r="D297" s="6"/>
       <c r="E297" s="7"/>
       <c r="F297" s="5"/>
+      <c r="J297" t="s">
+        <v>404</v>
+      </c>
       <c r="K297" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-WBS-004Tests not individually listed</v>
@@ -15835,6 +16128,9 @@
       <c r="D298" s="6"/>
       <c r="E298" s="7"/>
       <c r="F298" s="5"/>
+      <c r="J298" t="s">
+        <v>404</v>
+      </c>
       <c r="K298" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-PRJ-001Tests not individually listed</v>
@@ -15853,6 +16149,9 @@
       <c r="D299" s="6"/>
       <c r="E299" s="7"/>
       <c r="F299" s="5"/>
+      <c r="J299" t="s">
+        <v>404</v>
+      </c>
       <c r="K299" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PRJ-DTO-001Tests not individually listed</v>
@@ -15871,6 +16170,9 @@
       <c r="D300" s="6"/>
       <c r="E300" s="7"/>
       <c r="F300" s="5"/>
+      <c r="J300" t="s">
+        <v>404</v>
+      </c>
       <c r="K300" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-BOM-001Tests not individually listed</v>
@@ -15889,6 +16191,9 @@
       <c r="D301" s="6"/>
       <c r="E301" s="7"/>
       <c r="F301" s="5"/>
+      <c r="J301" t="s">
+        <v>404</v>
+      </c>
       <c r="K301" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-BOM-002Tests not individually listed</v>
@@ -15918,6 +16223,9 @@
       <c r="I302" t="s">
         <v>811</v>
       </c>
+      <c r="J302" t="s">
+        <v>404</v>
+      </c>
       <c r="K302" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
@@ -15944,6 +16252,9 @@
       <c r="H303" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J303" t="s">
+        <v>404</v>
+      </c>
       <c r="K303" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
@@ -15970,6 +16281,9 @@
       <c r="H304" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J304" t="s">
+        <v>404</v>
+      </c>
       <c r="K304" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
@@ -15996,6 +16310,9 @@
       <c r="H305" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J305" t="s">
+        <v>404</v>
+      </c>
       <c r="K305" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
@@ -16022,6 +16339,9 @@
       <c r="H306" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J306" t="s">
+        <v>404</v>
+      </c>
       <c r="K306" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
@@ -16048,6 +16368,9 @@
       <c r="H307" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J307" t="s">
+        <v>404</v>
+      </c>
       <c r="K307" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
@@ -16074,6 +16397,9 @@
       <c r="H308" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J308" t="s">
+        <v>404</v>
+      </c>
       <c r="K308" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
@@ -16100,6 +16426,9 @@
       <c r="H309" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J309" t="s">
+        <v>404</v>
+      </c>
       <c r="K309" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
@@ -16126,6 +16455,9 @@
       <c r="H310" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J310" t="s">
+        <v>404</v>
+      </c>
       <c r="K310" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
@@ -16152,6 +16484,9 @@
       <c r="H311" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J311" t="s">
+        <v>404</v>
+      </c>
       <c r="K311" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
@@ -16178,6 +16513,9 @@
       <c r="H312" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J312" t="s">
+        <v>404</v>
+      </c>
       <c r="K312" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
@@ -16204,6 +16542,9 @@
       <c r="H313" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J313" t="s">
+        <v>404</v>
+      </c>
       <c r="K313" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
@@ -16230,6 +16571,9 @@
       <c r="H314" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J314" t="s">
+        <v>404</v>
+      </c>
       <c r="K314" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
@@ -16256,6 +16600,9 @@
       <c r="H315" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J315" t="s">
+        <v>404</v>
+      </c>
       <c r="K315" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
@@ -16282,6 +16629,9 @@
       <c r="H316" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J316" t="s">
+        <v>404</v>
+      </c>
       <c r="K316" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
@@ -16308,6 +16658,9 @@
       <c r="H317" s="12" t="s">
         <v>407</v>
       </c>
+      <c r="J317" t="s">
+        <v>404</v>
+      </c>
       <c r="K317" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
@@ -16331,6 +16684,9 @@
       <c r="G318" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J318" t="s">
+        <v>404</v>
+      </c>
       <c r="K318" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
@@ -16354,6 +16710,9 @@
       <c r="G319" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J319" t="s">
+        <v>404</v>
+      </c>
       <c r="K319" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
@@ -16377,6 +16736,9 @@
       <c r="G320" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J320" t="s">
+        <v>404</v>
+      </c>
       <c r="K320" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
@@ -16400,6 +16762,9 @@
       <c r="G321" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J321" t="s">
+        <v>404</v>
+      </c>
       <c r="K321" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
@@ -16423,6 +16788,9 @@
       <c r="G322" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J322" t="s">
+        <v>404</v>
+      </c>
       <c r="K322" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
@@ -16446,6 +16814,9 @@
       <c r="G323" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J323" t="s">
+        <v>404</v>
+      </c>
       <c r="K323" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
@@ -16469,6 +16840,9 @@
       <c r="G324" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J324" t="s">
+        <v>404</v>
+      </c>
       <c r="K324" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
@@ -16492,6 +16866,9 @@
       <c r="G325" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J325" t="s">
+        <v>404</v>
+      </c>
       <c r="K325" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
@@ -16515,6 +16892,9 @@
       <c r="G326" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J326" t="s">
+        <v>404</v>
+      </c>
       <c r="K326" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
@@ -16538,6 +16918,9 @@
       <c r="G327" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J327" t="s">
+        <v>404</v>
+      </c>
       <c r="K327" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
@@ -16561,6 +16944,9 @@
       <c r="G328" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J328" t="s">
+        <v>404</v>
+      </c>
       <c r="K328" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
@@ -16584,6 +16970,9 @@
       <c r="G329" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J329" t="s">
+        <v>404</v>
+      </c>
       <c r="K329" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
@@ -16607,6 +16996,9 @@
       <c r="G330" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J330" t="s">
+        <v>404</v>
+      </c>
       <c r="K330" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
@@ -16630,6 +17022,9 @@
       <c r="G331" s="12" t="s">
         <v>771</v>
       </c>
+      <c r="J331" t="s">
+        <v>404</v>
+      </c>
       <c r="K331" t="str">
         <f t="shared" si="4"/>
         <v>TS-UD-PROC-LTM-002test_014_incoterm_impact_on_lead_time</v>
@@ -16648,6 +17043,9 @@
       <c r="D332" s="6"/>
       <c r="E332" s="7"/>
       <c r="F332" s="5"/>
+      <c r="J332" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="333" spans="1:11" ht="16.5" thickBot="1">
       <c r="A333" s="6" t="s">

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638CA2D0-AAC5-4415-BD7E-DD67DB7B7266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F8783-740C-46A0-B68E-D247051A3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
     <sheet name="Promts" sheetId="2" r:id="rId2"/>
     <sheet name="Unit Test" sheetId="3" r:id="rId3"/>
-    <sheet name="promt" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja4" sheetId="9" r:id="rId4"/>
     <sheet name="Agentes" sheetId="5" r:id="rId5"/>
+    <sheet name="promt" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suite Test'!$A$1:$J$114</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4280" uniqueCount="1179">
   <si>
     <t>Nº</t>
   </si>
@@ -3208,12 +3209,962 @@
   <si>
     <t>Claude</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Event-driven workflow tests .................... 20 tests               ║
+║  ├── Worker scaling tests ........................... 14 tests               ║
+║  └── TS-E2E-*: E2E ................................... 10 tests   </t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t> AGENTE 1: SECURITY CORE                              ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 100%                                ║</t>
+  </si>
+  <si>
+    <t>╠═══════════════════════════════════════════════════════════════════════════════╣</t>
+  </si>
+  <si>
+    <t>║                                                                               ║</t>
+  </si>
+  <si>
+    <t>║  COMPONENTES ASIGNADOS:                                                       ║</t>
+  </si>
+  <si>
+    <t>║  ├── MCP Gateway (Allowlist, Rate Limit, Query Limits, Audit)                ║</t>
+  </si>
+  <si>
+    <t>║  ├── Anonymizer Service (PII Detection, Strategies, Config)                  ║</t>
+  </si>
+  <si>
+    <t>║  ├── Tenant Isolation                                                        ║</t>
+  </si>
+  <si>
+    <t>║  ├── JWT Validation                                                          ║</t>
+  </si>
+  <si>
+    <t>║  └── Anti-Gaming Detection (compartido con Agente 6)                         ║</t>
+  </si>
+  <si>
+    <t>║  TEST SUITES ASIGNADOS:                                                       ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-MCP-001: MCP Allowlist ............... 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-MCP-002: Rate Limiting ............... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-MCP-003: Query Limits ................ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-MCP-004: MCP Audit ................... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-ANO-001: PII Detection ............... 24 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-ANO-002: Anonymizer Strategies ....... 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-ANO-003: Tenant Config ............... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-TNT-001: Tenant Isolation ............ 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-JWT-001: JWT Validation .............. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-AUD-001: Audit Trail Core ............ 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UC-SEC-GAM-001: Anti-Gaming Detection ....... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-* Integration tests ..................... 30 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-SEC-* E2E tests ......................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║      ─────────────────────────────────────────────────────────               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 1: 188 tests                                               ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S1-S2 (Semanas 1-4)                                      ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Ninguna (puede empezar inmediatamente)                        ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Todos los demás módulos                                         ║</t>
+  </si>
+  <si>
+    <t>╚═══════════════════════════════════════════════════════════════════════════════╝</t>
+  </si>
+  <si>
+    <t>```</t>
+  </si>
+  <si>
+    <t>### 9.2 AGENTE 2: Documents Domain (162 tests)</t>
+  </si>
+  <si>
+    <t>╔═══════════════════════════════════════════════════════════════════════════════╗</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 2: DOCUMENTS DOMAIN                           ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 95%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Clause Entity (creación, validación, FK integrity)                      ║</t>
+  </si>
+  <si>
+    <t>║  ├── Clause Types &amp; Classification                                           ║</t>
+  </si>
+  <si>
+    <t>║  ├── SubClause Hierarchy                                                     ║</t>
+  </si>
+  <si>
+    <t>║  ├── Entity Extraction (Dates, Money, Durations, Stakeholders)               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Document Entity                                                         ║</t>
+  </si>
+  <si>
+    <t>║  └── Confidence Scoring                                                      ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-CLS-001: Clause Entity ............... 22 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-CLS-002: Clause Types ................ 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-CLS-003: SubClause Hierarchy ......... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-ENT-001: Entity Dates ................ 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-ENT-002: Entity Money ................ 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-ENT-003: Entity Durations ............ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-ENT-004: Entity Stakeholders ......... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-DOC-001: Document Entity ............. 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-DOC-CNF-001: Confidence Scoring .......... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-DOC-UC-*: Use Cases ...................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-SVC-EXT-*: Services ...................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-DB-DOC-*: Integration ................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-FLW-DOC-*: E2E .......................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 2: 162 tests                                               ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S3-S4 (Semanas 5-8)                                      ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 1 (Anonymizer para PII en documentos)                  ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Agentes 5, 6, 7 (Analysis, Coherence, Stakeholders)             ║</t>
+  </si>
+  <si>
+    <t>### 9.3 AGENTE 3: Projects &amp; WBS (116 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 3: PROJECTS &amp; WBS                             ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 93%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── WBS Item Entity                                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── WBS Hierarchy &amp; Codes                                                   ║</t>
+  </si>
+  <si>
+    <t>║  ├── WBS Validation Rules                                                    ║</t>
+  </si>
+  <si>
+    <t>║  ├── WBS CRUD Operations                                                     ║</t>
+  </si>
+  <si>
+    <t>║  ├── Project Entity                                                          ║</t>
+  </si>
+  <si>
+    <t>║  └── IWBSQueryPort (interface para otros módulos)                            ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-WBS-001: WBS Item Entity ............. 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-WBS-002: WBS Hierarchy ............... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-WBS-003: WBS Validation .............. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-WBS-004: WBS CRUD .................... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-PRJ-001: Project Entity .............. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PRJ-DTO-001: WBSItemDTO &amp; Port ........... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-PRJ-UC-*: Use Cases ...................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-DB-WBS-*: Integration ................... 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-*: E2E ................................... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 3: 116 tests (ajustado de 130 anterior)                    ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S7 (Semanas 13-14)                                       ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 2 (Clauses para WBS)                                   ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Agente 4 (Procurement), Agente 6 (Reglas SCOPE)                 ║</t>
+  </si>
+  <si>
+    <t>### 9.4 AGENTE 4: Procurement Logic (116 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 4: PROCUREMENT LOGIC                          ║</t>
+  </si>
+  <si>
+    <t>║  ├── BOM Item Entity                                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── BOM Validation Rules                                                    ║</t>
+  </si>
+  <si>
+    <t>║  ├── Lead Time Calculator (Basic, Incoterms, Customs, Alerts)                ║</t>
+  </si>
+  <si>
+    <t>║  └── Procurement Plan Generation                                             ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-BOM-001: BOM Item Entity ............ 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-BOM-002: BOM Validation ............. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-LTM-001: Lead Time Basic ............ 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-LTM-002: Lead Time Incoterms ........ 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-LTM-003: Lead Time Customs .......... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-LTM-004: Lead Time Alerts ........... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-PROC-PLN-001: Procurement Plan ........... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-PROC-UC-*: Use Cases ..................... 22 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-DB-BOM-*: Integration ................... 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-*: E2E ................................... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 4: 116 tests (ajustado)                                    ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S8 (Semanas 15-16)                                       ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 3 (WBS para BOM)                                       ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Agente 6 (Reglas BUDGET, R14)                                   ║</t>
+  </si>
+  <si>
+    <t>### 9.5 AGENTE 5: Analysis &amp; Graph (78 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 5: ANALYSIS &amp; GRAPH                           ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 89%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Alert Entity                                                            ║</t>
+  </si>
+  <si>
+    <t>║  ├── Graph Node Entity                                                       ║</t>
+  </si>
+  <si>
+    <t>║  ├── Graph Relationship Entity                                               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Semantic Search                                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── Hybrid Search                                                           ║</t>
+  </si>
+  <si>
+    <t>║  └── Neo4j Integration                                                       ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-ANA-ALR-001: Alert Entity ................ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-ANA-GRP-001: Graph Node .................. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-ANA-GRP-002: Graph Relationship .......... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-ANA-SRC-001: Semantic Search ............. 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-ANA-HYB-001: Hybrid Search ............... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-ANA-UC-*: Use Cases ...................... 22 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-GRP-NEO-001: Neo4j Integration .......... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-*: E2E ................................... 6 tests                ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 5: 78 tests (ajustado)                                     ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S10 (Semanas 19-20)                                      ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 2 (Clauses para Graph)                                 ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Agente 6 (Coherence necesita Alerts)                            ║</t>
+  </si>
+  <si>
+    <t>### 9.6 AGENTE 6: Coherence Engine - CRÍTICO (206 tests)</t>
+  </si>
+  <si>
+    <t>║                     AGENTE 6: COHERENCE ENGINE (CRÍTICO)                      ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 99%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Category Enum &amp; Default Weights                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── Rules Engine (17 reglas en 6 categorías)                                ║</t>
+  </si>
+  <si>
+    <t>║  │   ├── SCOPE: R11, R12, R13                                                ║</t>
+  </si>
+  <si>
+    <t>║  │   ├── BUDGET: R6, R15, R16                                                ║</t>
+  </si>
+  <si>
+    <t>║  │   ├── TIME: R1, R2, R5, R14                                               ║</t>
+  </si>
+  <si>
+    <t>║  │   ├── TECHNICAL: R3, R4, R7                                               ║</t>
+  </si>
+  <si>
+    <t>║  │   ├── LEGAL: R8, R20                                                      ║</t>
+  </si>
+  <si>
+    <t>║  │   └── QUALITY: R17, R18                                                   ║</t>
+  </si>
+  <si>
+    <t>║  ├── Score Calculator (SubScores, Global, Custom Weights)                    ║</t>
+  </si>
+  <si>
+    <t>║  ├── Anti-Gaming Policy                                                      ║</t>
+  </si>
+  <si>
+    <t>║  └── Alert Entity &amp; Category Mapping                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-CAT-001: Categories .................. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-001: Rules SCOPE ................. 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-002: Rules BUDGET ................ 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-003: Rules TIME .................. 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-004: Rules TECHNICAL ............. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-005: Rules LEGAL ................. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-RUL-006: Rules QUALITY ............... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-SCR-001: SubScores ................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-SCR-002: Global Score ................ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-SCR-003: Custom Weights .............. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-GAM-001: Anti-Gaming ................. 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-COH-ALR-001: Alert Mapping ............... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-COH-UC-*: Use Cases ...................... 26 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-SVC-COH-*: Services ...................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-DB-COH-*: Integration ................... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-*: E2E ................................... 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 6: 206 tests                                               ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S5-S6 (Semanas 9-12) - PRIORIDAD MÁXIMA                  ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agentes 2, 3, 4, 5 (para datos de reglas)                     ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: E2E completo, Dashboard, Release                                ║</t>
+  </si>
+  <si>
+    <t>### 9.7 AGENTE 7: Stakeholders (112 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 7: STAKEHOLDERS                               ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 91%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Stakeholder Entity                                                      ║</t>
+  </si>
+  <si>
+    <t>║  ├── Power/Interest Classification                                           ║</t>
+  </si>
+  <si>
+    <t>║  ├── Quadrant Assignment                                                     ║</t>
+  </si>
+  <si>
+    <t>║  ├── RACI Entry Validation                                                   ║</t>
+  </si>
+  <si>
+    <t>║  ├── RACI Matrix Generation                                                  ║</t>
+  </si>
+  <si>
+    <t>║  ├── RACI from Clauses                                                       ║</t>
+  </si>
+  <si>
+    <t>║  └── Stakeholder Map Data                                                    ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-ENT-001: Stakeholder Entity .......... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-CLS-001: Power/Interest .............. 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-CLS-002: Quadrant Assignment ......... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-RAC-001: RACI Entry .................. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-RAC-002: RACI Matrix ................. 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-RAC-003: RACI from Clauses ........... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UD-STK-MAP-001: Stakeholder Map ............. 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-STK-UC-*: Use Cases ...................... 20 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-*: Integration .......................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 7: 112 tests                                               ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S9 (Semanas 17-18)                                       ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 2 (Clauses para extraction)                            ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Agente 6 (Regla R20)                                            ║</t>
+  </si>
+  <si>
+    <t>### 9.8 AGENTE 8: Async Architecture (78 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 8: ASYNC ARCHITECTURE                         ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 90%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Event Bus (Redis Pub/Sub)                                               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Celery Job Queue                                                        ║</t>
+  </si>
+  <si>
+    <t>║  ├── Dead Letter Queue                                                       ║</t>
+  </si>
+  <si>
+    <t>║  └── Worker Pool Management                                                  ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-EVT-BUS-001: Event Bus .................. 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-EVT-CEL-001: Celery Jobs ................ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-EVT-DLQ-001: Dead Letter Queue .......... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── Event-driven workflow tests .................... 20 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Worker scaling tests ........................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 8: 78 tests                                                ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S11-S12 (Semanas 21-24)                                  ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 1 (Redis adapters)                                     ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Integration flows, E2E                                          ║</t>
+  </si>
+  <si>
+    <t>### 9.9 AGENTE 9: Observability (68 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 9: OBSERVABILITY                              ║</t>
+  </si>
+  <si>
+    <t>║  ├── Logging (Structlog JSON)                                                ║</t>
+  </si>
+  <si>
+    <t>║  ├── Tracing (OpenTelemetry)                                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Budget Circuit Breaker                                                  ║</t>
+  </si>
+  <si>
+    <t>║  └── AI Usage Dashboard                                                      ║</t>
+  </si>
+  <si>
+    <t>║  ├── Logging tests .................................. 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Tracing tests .................................. 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Budget Circuit Breaker ......................... 22 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── AI Usage Dashboard ............................. 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 9: 68 tests                                                ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S11-S12 (paralelo con Agente 8)                          ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Agente 1 (LLM integration para cost tracking)                 ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Monitoring, Alerting                                            ║</t>
+  </si>
+  <si>
+    <t>### 9.10 AGENTE 10: API Contracts (62 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 10: API CONTRACTS                             ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 96%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── DTOs Validation (Pydantic)                                              ║</t>
+  </si>
+  <si>
+    <t>║  ├── Serialization/Deserialization                                           ║</t>
+  </si>
+  <si>
+    <t>║  ├── HTTP Routers                                                            ║</t>
+  </si>
+  <si>
+    <t>║  ├── Middleware (Auth, Tenant, CORS)                                         ║</t>
+  </si>
+  <si>
+    <t>║  └── Error Handlers                                                          ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-DTO-ALL-001: DTOs Validation ............. 24 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UA-DTO-SER-001: Serialization ............... 16 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UAD-HTTP-RTR-0: Routers ................... 32 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-UAD-HTTP-MDW--001: Middleware ................ 18 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-UAD-HTTP-ERR-001: Error Handlers ............ 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 10: 102 tests (ajustado)                                   ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S1-S2 (DTOs), S11-S12 (HTTP)                             ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Ninguna para DTOs                                             ║</t>
+  </si>
+  <si>
+    <t>### 9.11 AGENTE 11: Integration (184 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 11: INTEGRATION                               ║</t>
+  </si>
+  <si>
+    <t>╠═══════════01════════════════════════════════════════════════════════════════════╣</t>
+  </si>
+  <si>
+    <t>║  ├── WBS → Procurement Integration                                           ║</t>
+  </si>
+  <si>
+    <t>║  ├── Documents → Analysis Integration                                        ║</t>
+  </si>
+  <si>
+    <t>║  ├── Analysis → Coherence Integration                                        ║</t>
+  </si>
+  <si>
+    <t>║  ├── Stakeholders → RACI Integration                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── LLM Client Integration (Primary + Fallback)                             ║</t>
+  </si>
+  <si>
+    <t>║  └── All Database Integration                                                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-MOD-WBS-001: WBS → Procurement .......... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-MOD-DOC-001: Documents → Analysis ....... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-MOD-ANA-001: Analysis → Coherence ....... 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-MOD-STK-001: Stakeholders → RACI ........ 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-EXT-LLM-*: LLM Integration .............. 24 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-DB-*: All DB Integration ................ 70 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-INT-GRP-NEO-001: Neo4j ...................... 14 tests               ║</t>
+  </si>
+  <si>
+    <t>║  └── Remaining integration .......................... 34 tests               ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 11: 184 tests                                              ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Todos los módulos de dominio                                  ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: E2E                                                             ║</t>
+  </si>
+  <si>
+    <t>### 9.12 AGENTE 12: QA/E2E (78 tests)</t>
+  </si>
+  <si>
+    <t>║                          AGENTE 12: QA/E2E                                    ║</t>
+  </si>
+  <si>
+    <t>║                          Target Coverage: 83%                                 ║</t>
+  </si>
+  <si>
+    <t>║  ├── Document Upload to Coherence E2E                                        ║</t>
+  </si>
+  <si>
+    <t>║  ├── Alert Review Workflow E2E                                               ║</t>
+  </si>
+  <si>
+    <t>║  ├── Bulk Operations E2E                                                     ║</t>
+  </si>
+  <si>
+    <t>║  ├── Multi-tenant Isolation E2E                                              ║</t>
+  </si>
+  <si>
+    <t>║  ├── MCP Gateway E2E                                                         ║</t>
+  </si>
+  <si>
+    <t>║  ├── Error Scenarios (Timeout, Concurrent, Recovery)                         ║</t>
+  </si>
+  <si>
+    <t>║  └── Performance Tests                                                       ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-FLW-DOC-001: Document Flow .............. 12 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-FLW-ALR-001: Alert Flow ................. 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-FLW-BLK-001: Bulk Operations ............ 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-SEC-TNT-001: Tenant Isolation ........... 10 tests               ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-SEC-MCP-001: MCP Gateway ................ 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-ERR-TIM-001: Timeouts ................... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-ERR-CON-001: Concurrent ................. 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  ├── TS-E2E-ERR-REC-001: Recovery ................... 8 tests                ║</t>
+  </si>
+  <si>
+    <t>║  └── TS-E2E-PER-LRG-001: Performance ................ 6 tests                ║</t>
+  </si>
+  <si>
+    <t>║      TOTAL AGENTE 12: 78 tests                                               ║</t>
+  </si>
+  <si>
+    <t>║  SPRINTS ASIGNADOS: S13-S14 (Semanas 25-28)                                  ║</t>
+  </si>
+  <si>
+    <t>║  DEPENDENCIAS: Todos los módulos + Integration                               ║</t>
+  </si>
+  <si>
+    <t>║  DESBLOQUEA: Release                                                         ║</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>## 10. Dependencias y Orden de Implementación</t>
+  </si>
+  <si>
+    <t>### 10.1 Grafo de Dependencias Completo</t>
+  </si>
+  <si>
+    <t>                              ┌─────────────────┐</t>
+  </si>
+  <si>
+    <t>                              │   NIVEL 0       │</t>
+  </si>
+  <si>
+    <t>                              │  (Sin deps)     │</t>
+  </si>
+  <si>
+    <t>                              └────────┬────────┘</t>
+  </si>
+  <si>
+    <t>                                       │</t>
+  </si>
+  <si>
+    <t>              ┌────────────────────────┼────────────────────────┐</t>
+  </si>
+  <si>
+    <t>              │                        │                        │</t>
+  </si>
+  <si>
+    <t>              ▼                        ▼                        ▼</t>
+  </si>
+  <si>
+    <t>     ┌─────────────────┐     ┌─────────────────┐     ┌─────────────────┐</t>
+  </si>
+  <si>
+    <t>     │   AGENTE 1      │     │   AGENTE 10     │     │   AGENTE 8      │</t>
+  </si>
+  <si>
+    <t>     │ Security Core   │     │ DTOs (parte 1)  │     │ Event Bus       │</t>
+  </si>
+  <si>
+    <t>     │   156 tests     │     │   40 tests      │     │   34 tests      │</t>
+  </si>
+  <si>
+    <t>     └────────┬────────┘     └────────┬────────┘     └────────┬────────┘</t>
+  </si>
+  <si>
+    <t>              └────────────────────────┼────────────────────────┘</t>
+  </si>
+  <si>
+    <t>                              ┌────────┴────────┐</t>
+  </si>
+  <si>
+    <t>                              │    NIVEL 1      │</t>
+  </si>
+  <si>
+    <t>                              │    AGENTE 2     │</t>
+  </si>
+  <si>
+    <t>                              │   Documents     │</t>
+  </si>
+  <si>
+    <t>                              │   162 tests     │</t>
+  </si>
+  <si>
+    <t>     │   AGENTE 3      │     │   AGENTE 5      │     │   AGENTE 7      │</t>
+  </si>
+  <si>
+    <t>     │   Projects      │     │   Analysis      │     │  Stakeholders   │</t>
+  </si>
+  <si>
+    <t>     │   116 tests     │     │   78 tests      │     │   112 tests     │</t>
+  </si>
+  <si>
+    <t>              ▼                        │                        │</t>
+  </si>
+  <si>
+    <t>     ┌─────────────────┐               │                        │</t>
+  </si>
+  <si>
+    <t>     │   AGENTE 4      │               │                        │</t>
+  </si>
+  <si>
+    <t>     │  Procurement    │               │                        │</t>
+  </si>
+  <si>
+    <t>     │   116 tests     │               │                        │</t>
+  </si>
+  <si>
+    <t>     └────────┬────────┘               │                        │</t>
+  </si>
+  <si>
+    <t>                              │    NIVEL 3      │</t>
+  </si>
+  <si>
+    <t>                              │   AGENTE 6      │</t>
+  </si>
+  <si>
+    <t>                              │   Coherence     │</t>
+  </si>
+  <si>
+    <t>                              │   206 tests     │</t>
+  </si>
+  <si>
+    <t>                              │   (CRÍTICO)     │</t>
+  </si>
+  <si>
+    <t>     │   AGENTE 9      │     │   AGENTE 10     │     │   AGENTE 11     │</t>
+  </si>
+  <si>
+    <t>     │ Observability   │     │ HTTP Adapters   │     │  Integration    │</t>
+  </si>
+  <si>
+    <t>     │   68 tests      │     │   62 tests      │     │   184 tests     │</t>
+  </si>
+  <si>
+    <t>                              │    NIVEL 5      │</t>
+  </si>
+  <si>
+    <t>                              │   AGENTE 12     │</t>
+  </si>
+  <si>
+    <t>                              │     E2E         │</t>
+  </si>
+  <si>
+    <t>                              │   78 tests      │</t>
+  </si>
+  <si>
+    <t>                              └─────────────────┘</t>
+  </si>
+  <si>
+    <t>### 10.2 Orden Crítico de Ejecución</t>
+  </si>
+  <si>
+    <t>| Orden | Agente | Tests | Sprint | Bloquea | Crítico |</t>
+  </si>
+  <si>
+    <t>| 14 | Agente 12 (E2E) | 78 | S13-S14 | Release | ✅</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3271,8 +4222,19 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3306,6 +4268,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3383,7 +4363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3442,6 +4422,47 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3748,17 +4769,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="19.149999999999999" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.28515625" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
-    <col min="11" max="11" width="62.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="62.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.149999999999999" customHeight="1">
+    <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3796,7 +4817,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="19.149999999999999" customHeight="1">
+    <row r="2" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3830,8 +4851,12 @@
       <c r="K2" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M2" t="str">
+        <f>VLOOKUP(B2,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3865,8 +4890,12 @@
       <c r="K3" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M3" t="str">
+        <f>VLOOKUP(B3,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3900,8 +4929,12 @@
       <c r="K4" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M4" t="str">
+        <f>VLOOKUP(B4,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3935,8 +4968,15 @@
       <c r="K5" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="L5" t="s">
+        <v>404</v>
+      </c>
+      <c r="M5" t="e">
+        <f>VLOOKUP(B5,'Unit Test'!A:J,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3970,8 +5010,12 @@
       <c r="K6" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M6" t="str">
+        <f>VLOOKUP(B6,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -4005,8 +5049,12 @@
       <c r="K7" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M7" t="str">
+        <f>VLOOKUP(B7,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -4040,8 +5088,12 @@
       <c r="K8" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M8" t="str">
+        <f>VLOOKUP(B8,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -4075,8 +5127,12 @@
       <c r="K9" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M9" t="str">
+        <f>VLOOKUP(B9,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4110,8 +5166,15 @@
       <c r="K10" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="L10" t="s">
+        <v>404</v>
+      </c>
+      <c r="M10">
+        <f>VLOOKUP(B10,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -4145,8 +5208,15 @@
       <c r="K11" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="L11" t="s">
+        <v>404</v>
+      </c>
+      <c r="M11">
+        <f>VLOOKUP(B11,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4180,8 +5250,12 @@
       <c r="K12" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M12" t="str">
+        <f>VLOOKUP(B12,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -4215,12 +5289,16 @@
       <c r="K13" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M13" t="str">
+        <f>VLOOKUP(B13,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="21" t="s">
         <v>131</v>
       </c>
       <c r="C14" t="s">
@@ -4247,8 +5325,12 @@
       <c r="K14" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M14">
+        <f>VLOOKUP(B14,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -4279,8 +5361,12 @@
       <c r="K15" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M15">
+        <f>VLOOKUP(B15,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -4314,8 +5400,12 @@
       <c r="K16" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M16" t="str">
+        <f>VLOOKUP(B16,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -4346,8 +5436,12 @@
       <c r="K17" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M17" t="str">
+        <f>VLOOKUP(B17,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -4375,8 +5469,12 @@
       <c r="I18" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M18" t="str">
+        <f>VLOOKUP(B18,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4404,8 +5502,12 @@
       <c r="I19" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M19" t="str">
+        <f>VLOOKUP(B19,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4433,8 +5535,12 @@
       <c r="I20" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M20" t="str">
+        <f>VLOOKUP(B20,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4462,8 +5568,12 @@
       <c r="I21" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M21" t="str">
+        <f>VLOOKUP(B21,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4491,8 +5601,12 @@
       <c r="I22" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M22" t="str">
+        <f>VLOOKUP(B22,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -4526,8 +5640,12 @@
       <c r="K23" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M23" t="str">
+        <f>VLOOKUP(B23,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -4558,8 +5676,12 @@
       <c r="K24" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M24" t="str">
+        <f>VLOOKUP(B24,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4587,8 +5709,12 @@
       <c r="I25" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M25" t="str">
+        <f>VLOOKUP(B25,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -4616,8 +5742,12 @@
       <c r="I26" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M26" t="str">
+        <f>VLOOKUP(B26,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -4645,8 +5775,12 @@
       <c r="I27" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M27" t="str">
+        <f>VLOOKUP(B27,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -4680,8 +5814,12 @@
       <c r="K28" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M28" t="str">
+        <f>VLOOKUP(B28,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -4709,8 +5847,12 @@
       <c r="I29" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M29" t="str">
+        <f>VLOOKUP(B29,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -4738,8 +5880,12 @@
       <c r="I30" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M30" t="str">
+        <f>VLOOKUP(B30,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -4767,8 +5913,12 @@
       <c r="I31" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M31" t="str">
+        <f>VLOOKUP(B31,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4796,8 +5946,12 @@
       <c r="I32" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M32" t="str">
+        <f>VLOOKUP(B32,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -4825,8 +5979,12 @@
       <c r="I33" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M33" t="str">
+        <f>VLOOKUP(B33,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -4857,8 +6015,12 @@
       <c r="J34" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M34" t="str">
+        <f>VLOOKUP(B34,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -4889,8 +6051,12 @@
       <c r="K35" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M35" t="str">
+        <f>VLOOKUP(B35,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -4921,8 +6087,12 @@
       <c r="K36" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M36" t="str">
+        <f>VLOOKUP(B36,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -4953,8 +6123,12 @@
       <c r="K37" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M37" t="str">
+        <f>VLOOKUP(B37,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -4985,8 +6159,12 @@
       <c r="K38" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M38" t="str">
+        <f>VLOOKUP(B38,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -5020,8 +6198,12 @@
       <c r="K39" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M39" t="str">
+        <f>VLOOKUP(B39,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -5049,8 +6231,12 @@
       <c r="I40" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M40" t="str">
+        <f>VLOOKUP(B40,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -5078,8 +6264,12 @@
       <c r="I41" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M41" t="str">
+        <f>VLOOKUP(B41,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -5107,8 +6297,12 @@
       <c r="I42" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M42" t="str">
+        <f>VLOOKUP(B42,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -5136,8 +6330,12 @@
       <c r="I43" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M43" t="str">
+        <f>VLOOKUP(B43,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -5165,8 +6363,12 @@
       <c r="I44" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M44" t="str">
+        <f>VLOOKUP(B44,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -5194,8 +6396,12 @@
       <c r="I45" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M45" t="str">
+        <f>VLOOKUP(B45,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -5223,8 +6429,12 @@
       <c r="I46" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M46" t="str">
+        <f>VLOOKUP(B46,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -5258,8 +6468,12 @@
       <c r="K47" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M47" t="str">
+        <f>VLOOKUP(B47,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -5287,8 +6501,12 @@
       <c r="I48" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M48" t="str">
+        <f>VLOOKUP(B48,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -5316,8 +6534,12 @@
       <c r="I49" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M49" t="str">
+        <f>VLOOKUP(B49,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -5345,8 +6567,12 @@
       <c r="I50" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M50">
+        <f>VLOOKUP(B50,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -5374,8 +6600,12 @@
       <c r="I51" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M51">
+        <f>VLOOKUP(B51,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -5403,8 +6633,12 @@
       <c r="I52" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M52">
+        <f>VLOOKUP(B52,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -5432,8 +6666,12 @@
       <c r="I53" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M53">
+        <f>VLOOKUP(B53,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -5461,8 +6699,12 @@
       <c r="I54" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M54">
+        <f>VLOOKUP(B54,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -5490,8 +6732,12 @@
       <c r="I55" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M55">
+        <f>VLOOKUP(B55,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -5519,8 +6765,12 @@
       <c r="I56" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M56">
+        <f>VLOOKUP(B56,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -5548,8 +6798,12 @@
       <c r="I57" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M57">
+        <f>VLOOKUP(B57,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -5577,8 +6831,12 @@
       <c r="I58" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M58">
+        <f>VLOOKUP(B58,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -5606,8 +6864,12 @@
       <c r="I59" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M59">
+        <f>VLOOKUP(B59,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -5635,8 +6897,12 @@
       <c r="I60" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M60">
+        <f>VLOOKUP(B60,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -5664,8 +6930,12 @@
       <c r="I61" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M61">
+        <f>VLOOKUP(B61,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -5693,8 +6963,12 @@
       <c r="I62" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M62">
+        <f>VLOOKUP(B62,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -5722,8 +6996,12 @@
       <c r="I63" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="19.149999999999999" customHeight="1">
+      <c r="M63">
+        <f>VLOOKUP(B63,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -5751,8 +7029,12 @@
       <c r="I64" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M64" t="str">
+        <f>VLOOKUP(B64,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -5780,8 +7062,12 @@
       <c r="I65" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M65" t="str">
+        <f>VLOOKUP(B65,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -5809,8 +7095,12 @@
       <c r="I66" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M66">
+        <f>VLOOKUP(B66,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -5838,8 +7128,12 @@
       <c r="I67" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M67">
+        <f>VLOOKUP(B67,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -5867,8 +7161,12 @@
       <c r="I68" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M68">
+        <f>VLOOKUP(B68,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -5896,8 +7194,12 @@
       <c r="I69" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M69">
+        <f>VLOOKUP(B69,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -5925,8 +7227,12 @@
       <c r="I70" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M70">
+        <f>VLOOKUP(B70,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -5954,8 +7260,12 @@
       <c r="I71" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M71">
+        <f>VLOOKUP(B71,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -5989,8 +7299,15 @@
       <c r="K72" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="L72" t="s">
+        <v>404</v>
+      </c>
+      <c r="M72">
+        <f>VLOOKUP(B72,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -6024,8 +7341,12 @@
       <c r="K73" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M73">
+        <f>VLOOKUP(B73,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -6059,8 +7380,12 @@
       <c r="K74" s="2" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M74">
+        <f>VLOOKUP(B74,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -6091,8 +7416,12 @@
       <c r="J75" s="2" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M75">
+        <f>VLOOKUP(B75,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -6120,8 +7449,12 @@
       <c r="I76" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M76">
+        <f>VLOOKUP(B76,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -6155,8 +7488,12 @@
       <c r="K77" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M77">
+        <f>VLOOKUP(B77,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -6190,8 +7527,12 @@
       <c r="K78" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M78">
+        <f>VLOOKUP(B78,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -6225,8 +7566,12 @@
       <c r="K79" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M79">
+        <f>VLOOKUP(B79,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -6257,8 +7602,12 @@
       <c r="K80" s="2" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M80">
+        <f>VLOOKUP(B80,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -6289,8 +7638,12 @@
       <c r="K81" s="2" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M81">
+        <f>VLOOKUP(B81,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -6318,8 +7671,12 @@
       <c r="I82" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M82">
+        <f>VLOOKUP(B82,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -6356,8 +7713,12 @@
       <c r="L83" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M83">
+        <f>VLOOKUP(B83,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A84" t="s">
         <v>102</v>
       </c>
@@ -6385,8 +7746,12 @@
       <c r="I84" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M84">
+        <f>VLOOKUP(B84,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -6417,8 +7782,12 @@
       <c r="K85" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M85" t="str">
+        <f>VLOOKUP(B85,'Unit Test'!A:J,10,FALSE)</f>
+        <v>CODEX</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -6452,8 +7821,12 @@
       <c r="L86" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M86">
+        <f>VLOOKUP(B86,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -6481,8 +7854,12 @@
       <c r="I87" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M87">
+        <f>VLOOKUP(B87,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -6510,8 +7887,12 @@
       <c r="I88" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M88">
+        <f>VLOOKUP(B88,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -6539,8 +7920,12 @@
       <c r="I89" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M89">
+        <f>VLOOKUP(B89,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -6574,8 +7959,12 @@
       <c r="K90" s="2" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M90" t="str">
+        <f>VLOOKUP(B90,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -6606,8 +7995,12 @@
       <c r="K91" s="2" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M91" t="str">
+        <f>VLOOKUP(B91,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -6638,8 +8031,12 @@
       <c r="K92" s="2" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M92" t="str">
+        <f>VLOOKUP(B92,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -6667,8 +8064,12 @@
       <c r="I93" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M93">
+        <f>VLOOKUP(B93,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -6699,8 +8100,12 @@
       <c r="K94" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M94">
+        <f>VLOOKUP(B94,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -6734,8 +8139,12 @@
       <c r="K95" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M95">
+        <f>VLOOKUP(B95,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -6763,8 +8172,12 @@
       <c r="I96" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M96">
+        <f>VLOOKUP(B96,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -6798,8 +8211,12 @@
       <c r="L97" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M97" t="str">
+        <f>VLOOKUP(B97,'Unit Test'!A:J,10,FALSE)</f>
+        <v>CODEX</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A98" t="s">
         <v>86</v>
       </c>
@@ -6830,8 +8247,12 @@
       <c r="L98" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M98" t="str">
+        <f>VLOOKUP(B98,'Unit Test'!A:J,10,FALSE)</f>
+        <v>CODEX</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -6862,8 +8283,12 @@
       <c r="K99" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M99">
+        <f>VLOOKUP(B99,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -6894,8 +8319,12 @@
       <c r="J100" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M100">
+        <f>VLOOKUP(B100,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -6923,8 +8352,12 @@
       <c r="I101" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M101">
+        <f>VLOOKUP(B101,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -6955,8 +8388,12 @@
       <c r="J102" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M102">
+        <f>VLOOKUP(B102,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -6993,8 +8430,12 @@
       <c r="L103" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M103" t="str">
+        <f>VLOOKUP(B103,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -7022,8 +8463,15 @@
       <c r="I104" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="L104" t="s">
+        <v>404</v>
+      </c>
+      <c r="M104" t="str">
+        <f>VLOOKUP(B104,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -7051,8 +8499,15 @@
       <c r="I105" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="L105" t="s">
+        <v>404</v>
+      </c>
+      <c r="M105" t="str">
+        <f>VLOOKUP(B105,'Unit Test'!A:J,10,FALSE)</f>
+        <v>codex</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -7083,8 +8538,12 @@
       <c r="K106" s="2" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M106">
+        <f>VLOOKUP(B106,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -7118,8 +8577,12 @@
       <c r="L107" s="14" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M107">
+        <f>VLOOKUP(B107,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -7150,8 +8613,12 @@
       <c r="K108" s="2" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M108">
+        <f>VLOOKUP(B108,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -7185,8 +8652,12 @@
       <c r="K109" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M109" t="str">
+        <f>VLOOKUP(B109,'Unit Test'!A:J,10,FALSE)</f>
+        <v>claude</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -7220,8 +8691,12 @@
       <c r="K110" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M110">
+        <f>VLOOKUP(B110,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -7255,8 +8730,12 @@
       <c r="K111" s="2" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" ht="19.149999999999999" customHeight="1">
+      <c r="M111">
+        <f>VLOOKUP(B111,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -7284,8 +8763,12 @@
       <c r="I112" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M112">
+        <f>VLOOKUP(B112,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -7313,8 +8796,12 @@
       <c r="I113" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" ht="19.149999999999999" customHeight="1">
+      <c r="M113">
+        <f>VLOOKUP(B113,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -7344,6 +8831,10 @@
       </c>
       <c r="K114" s="2" t="s">
         <v>808</v>
+      </c>
+      <c r="M114">
+        <f>VLOOKUP(B114,'Unit Test'!A:J,10,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7395,8 +8886,9 @@
     <col min="3" max="3" width="29.140625" customWidth="1"/>
     <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5703125" customWidth="1"/>
-    <col min="9" max="9" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5703125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="39.5703125" customWidth="1"/>
     <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -17060,6 +18552,9 @@
       <c r="D333" s="6"/>
       <c r="E333" s="7"/>
       <c r="F333" s="5"/>
+      <c r="J333" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="334" spans="1:11" ht="16.5" thickBot="1">
       <c r="A334" s="6" t="s">
@@ -17074,6 +18569,9 @@
       <c r="D334" s="6"/>
       <c r="E334" s="7"/>
       <c r="F334" s="5"/>
+      <c r="J334" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="335" spans="1:11" ht="31.5" thickBot="1">
       <c r="A335" s="6" t="s">
@@ -17088,6 +18586,9 @@
       <c r="D335" s="6"/>
       <c r="E335" s="7"/>
       <c r="F335" s="5"/>
+      <c r="J335" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="336" spans="1:11" ht="31.5" thickBot="1">
       <c r="A336" s="6" t="s">
@@ -17102,8 +18603,11 @@
       <c r="D336" s="6"/>
       <c r="E336" s="7"/>
       <c r="F336" s="5"/>
-    </row>
-    <row r="337" spans="1:6" ht="31.5" thickBot="1">
+      <c r="J336" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="31.5" thickBot="1">
       <c r="A337" s="6" t="s">
         <v>166</v>
       </c>
@@ -17116,8 +18620,11 @@
       <c r="D337" s="6"/>
       <c r="E337" s="7"/>
       <c r="F337" s="5"/>
-    </row>
-    <row r="338" spans="1:6" ht="31.5" thickBot="1">
+      <c r="J337" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="31.5" thickBot="1">
       <c r="A338" s="6" t="s">
         <v>167</v>
       </c>
@@ -17131,7 +18638,7 @@
       <c r="E338" s="7"/>
       <c r="F338" s="5"/>
     </row>
-    <row r="339" spans="1:6" ht="31.5" thickBot="1">
+    <row r="339" spans="1:10" ht="31.5" thickBot="1">
       <c r="A339" s="6" t="s">
         <v>168</v>
       </c>
@@ -17145,7 +18652,7 @@
       <c r="E339" s="7"/>
       <c r="F339" s="5"/>
     </row>
-    <row r="340" spans="1:6" ht="31.5" thickBot="1">
+    <row r="340" spans="1:10" ht="31.5" thickBot="1">
       <c r="A340" s="6" t="s">
         <v>169</v>
       </c>
@@ -17159,7 +18666,7 @@
       <c r="E340" s="7"/>
       <c r="F340" s="5"/>
     </row>
-    <row r="341" spans="1:6" ht="31.5" thickBot="1">
+    <row r="341" spans="1:10" ht="31.5" thickBot="1">
       <c r="A341" s="6" t="s">
         <v>170</v>
       </c>
@@ -17173,7 +18680,7 @@
       <c r="E341" s="7"/>
       <c r="F341" s="5"/>
     </row>
-    <row r="342" spans="1:6" ht="16.5" thickBot="1">
+    <row r="342" spans="1:10" ht="16.5" thickBot="1">
       <c r="A342" s="6" t="s">
         <v>171</v>
       </c>
@@ -17187,7 +18694,7 @@
       <c r="E342" s="7"/>
       <c r="F342" s="5"/>
     </row>
-    <row r="343" spans="1:6" ht="16.5" thickBot="1">
+    <row r="343" spans="1:10" ht="16.5" thickBot="1">
       <c r="A343" s="6" t="s">
         <v>172</v>
       </c>
@@ -17201,7 +18708,7 @@
       <c r="E343" s="7"/>
       <c r="F343" s="5"/>
     </row>
-    <row r="344" spans="1:6" ht="16.5" thickBot="1">
+    <row r="344" spans="1:10" ht="16.5" thickBot="1">
       <c r="A344" s="6" t="s">
         <v>173</v>
       </c>
@@ -17215,7 +18722,7 @@
       <c r="E344" s="7"/>
       <c r="F344" s="5"/>
     </row>
-    <row r="345" spans="1:6" ht="16.5" thickBot="1">
+    <row r="345" spans="1:10" ht="16.5" thickBot="1">
       <c r="A345" s="6" t="s">
         <v>174</v>
       </c>
@@ -17229,7 +18736,7 @@
       <c r="E345" s="7"/>
       <c r="F345" s="5"/>
     </row>
-    <row r="346" spans="1:6" ht="16.5" thickBot="1">
+    <row r="346" spans="1:10" ht="16.5" thickBot="1">
       <c r="A346" s="6" t="s">
         <v>175</v>
       </c>
@@ -17243,7 +18750,7 @@
       <c r="E346" s="7"/>
       <c r="F346" s="5"/>
     </row>
-    <row r="347" spans="1:6" ht="31.5" thickBot="1">
+    <row r="347" spans="1:10" ht="31.5" thickBot="1">
       <c r="A347" s="6" t="s">
         <v>176</v>
       </c>
@@ -17257,7 +18764,7 @@
       <c r="E347" s="7"/>
       <c r="F347" s="5"/>
     </row>
-    <row r="348" spans="1:6" ht="31.5" thickBot="1">
+    <row r="348" spans="1:10" ht="31.5" thickBot="1">
       <c r="A348" s="6" t="s">
         <v>177</v>
       </c>
@@ -17271,7 +18778,7 @@
       <c r="E348" s="7"/>
       <c r="F348" s="5"/>
     </row>
-    <row r="349" spans="1:6" ht="31.5" thickBot="1">
+    <row r="349" spans="1:10" ht="31.5" thickBot="1">
       <c r="A349" s="6" t="s">
         <v>178</v>
       </c>
@@ -17285,7 +18792,7 @@
       <c r="E349" s="7"/>
       <c r="F349" s="5"/>
     </row>
-    <row r="350" spans="1:6" ht="31.5" thickBot="1">
+    <row r="350" spans="1:10" ht="31.5" thickBot="1">
       <c r="A350" s="6" t="s">
         <v>179</v>
       </c>
@@ -17299,7 +18806,7 @@
       <c r="E350" s="7"/>
       <c r="F350" s="5"/>
     </row>
-    <row r="351" spans="1:6" ht="31.5" thickBot="1">
+    <row r="351" spans="1:10" ht="31.5" thickBot="1">
       <c r="A351" s="6" t="s">
         <v>180</v>
       </c>
@@ -17313,35 +18820,47 @@
       <c r="E351" s="7"/>
       <c r="F351" s="5"/>
     </row>
-    <row r="352" spans="1:6" ht="31.5" thickBot="1">
-      <c r="A352" s="6" t="s">
+    <row r="352" spans="1:10" ht="31.5" thickBot="1">
+      <c r="A352" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="B352" s="6" t="s">
+      <c r="B352" s="33" t="s">
         <v>753</v>
       </c>
-      <c r="C352" s="6" t="s">
+      <c r="C352" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="D352" s="6"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="5"/>
-    </row>
-    <row r="353" spans="1:6" ht="31.5" thickBot="1">
-      <c r="A353" s="6" t="s">
+      <c r="D352" s="33"/>
+      <c r="E352" s="34"/>
+      <c r="F352" s="35"/>
+      <c r="G352" s="36"/>
+      <c r="H352" s="36"/>
+      <c r="I352" s="36"/>
+      <c r="J352" s="36" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" ht="31.5" thickBot="1">
+      <c r="A353" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="B353" s="6" t="s">
+      <c r="B353" s="33" t="s">
         <v>753</v>
       </c>
-      <c r="C353" s="6" t="s">
+      <c r="C353" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="D353" s="6"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="5"/>
-    </row>
-    <row r="354" spans="1:6" ht="31.5" thickBot="1">
+      <c r="D353" s="33"/>
+      <c r="E353" s="34"/>
+      <c r="F353" s="35"/>
+      <c r="G353" s="36"/>
+      <c r="H353" s="36"/>
+      <c r="I353" s="36"/>
+      <c r="J353" s="36" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="31.5" thickBot="1">
       <c r="A354" s="6" t="s">
         <v>183</v>
       </c>
@@ -17355,7 +18874,7 @@
       <c r="E354" s="7"/>
       <c r="F354" s="5"/>
     </row>
-    <row r="355" spans="1:6" ht="31.5" thickBot="1">
+    <row r="355" spans="1:10" ht="31.5" thickBot="1">
       <c r="A355" s="6" t="s">
         <v>184</v>
       </c>
@@ -17369,7 +18888,7 @@
       <c r="E355" s="7"/>
       <c r="F355" s="5"/>
     </row>
-    <row r="356" spans="1:6" ht="31.5" thickBot="1">
+    <row r="356" spans="1:10" ht="31.5" thickBot="1">
       <c r="A356" s="6" t="s">
         <v>185</v>
       </c>
@@ -17383,7 +18902,7 @@
       <c r="E356" s="7"/>
       <c r="F356" s="5"/>
     </row>
-    <row r="357" spans="1:6" ht="31.5" thickBot="1">
+    <row r="357" spans="1:10" ht="31.5" thickBot="1">
       <c r="A357" s="6" t="s">
         <v>186</v>
       </c>
@@ -17397,7 +18916,7 @@
       <c r="E357" s="7"/>
       <c r="F357" s="5"/>
     </row>
-    <row r="358" spans="1:6" ht="31.5" thickBot="1">
+    <row r="358" spans="1:10" ht="31.5" thickBot="1">
       <c r="A358" s="6" t="s">
         <v>187</v>
       </c>
@@ -17411,7 +18930,7 @@
       <c r="E358" s="7"/>
       <c r="F358" s="5"/>
     </row>
-    <row r="359" spans="1:6" ht="31.5" thickBot="1">
+    <row r="359" spans="1:10" ht="31.5" thickBot="1">
       <c r="A359" s="6" t="s">
         <v>188</v>
       </c>
@@ -17425,7 +18944,7 @@
       <c r="E359" s="7"/>
       <c r="F359" s="5"/>
     </row>
-    <row r="360" spans="1:6" ht="31.5" thickBot="1">
+    <row r="360" spans="1:10" ht="31.5" thickBot="1">
       <c r="A360" s="6" t="s">
         <v>189</v>
       </c>
@@ -17439,7 +18958,7 @@
       <c r="E360" s="7"/>
       <c r="F360" s="5"/>
     </row>
-    <row r="361" spans="1:6" ht="31.5" thickBot="1">
+    <row r="361" spans="1:10" ht="31.5" thickBot="1">
       <c r="A361" s="6" t="s">
         <v>190</v>
       </c>
@@ -17453,7 +18972,7 @@
       <c r="E361" s="7"/>
       <c r="F361" s="5"/>
     </row>
-    <row r="362" spans="1:6" ht="16.5" thickBot="1">
+    <row r="362" spans="1:10" ht="16.5" thickBot="1">
       <c r="A362" s="6" t="s">
         <v>191</v>
       </c>
@@ -17467,7 +18986,7 @@
       <c r="E362" s="7"/>
       <c r="F362" s="5"/>
     </row>
-    <row r="363" spans="1:6" ht="16.5" thickBot="1">
+    <row r="363" spans="1:10" ht="16.5" thickBot="1">
       <c r="A363" s="6" t="s">
         <v>192</v>
       </c>
@@ -17481,7 +19000,7 @@
       <c r="E363" s="7"/>
       <c r="F363" s="5"/>
     </row>
-    <row r="364" spans="1:6" ht="16.5" thickBot="1">
+    <row r="364" spans="1:10" ht="16.5" thickBot="1">
       <c r="A364" s="6" t="s">
         <v>193</v>
       </c>
@@ -17495,7 +19014,7 @@
       <c r="E364" s="7"/>
       <c r="F364" s="5"/>
     </row>
-    <row r="365" spans="1:6" ht="16.5" thickBot="1">
+    <row r="365" spans="1:10" ht="16.5" thickBot="1">
       <c r="A365" s="6" t="s">
         <v>194</v>
       </c>
@@ -17509,7 +19028,7 @@
       <c r="E365" s="7"/>
       <c r="F365" s="5"/>
     </row>
-    <row r="366" spans="1:6" ht="16.5" thickBot="1">
+    <row r="366" spans="1:10" ht="16.5" thickBot="1">
       <c r="A366" s="6" t="s">
         <v>195</v>
       </c>
@@ -17523,7 +19042,7 @@
       <c r="E366" s="7"/>
       <c r="F366" s="5"/>
     </row>
-    <row r="367" spans="1:6" ht="16.5" thickBot="1">
+    <row r="367" spans="1:10" ht="16.5" thickBot="1">
       <c r="A367" s="6" t="s">
         <v>196</v>
       </c>
@@ -17537,7 +19056,7 @@
       <c r="E367" s="7"/>
       <c r="F367" s="5"/>
     </row>
-    <row r="368" spans="1:6" ht="16.5" thickBot="1">
+    <row r="368" spans="1:10" ht="16.5" thickBot="1">
       <c r="A368" s="6" t="s">
         <v>197</v>
       </c>
@@ -17551,7 +19070,7 @@
       <c r="E368" s="7"/>
       <c r="F368" s="5"/>
     </row>
-    <row r="369" spans="1:6" ht="16.5" thickBot="1">
+    <row r="369" spans="1:10" ht="16.5" thickBot="1">
       <c r="A369" s="6" t="s">
         <v>198</v>
       </c>
@@ -17564,8 +19083,11 @@
       <c r="D369" s="6"/>
       <c r="E369" s="7"/>
       <c r="F369" s="5"/>
-    </row>
-    <row r="370" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J369" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="16.5" thickBot="1">
       <c r="A370" s="6" t="s">
         <v>199</v>
       </c>
@@ -17578,8 +19100,11 @@
       <c r="D370" s="6"/>
       <c r="E370" s="7"/>
       <c r="F370" s="5"/>
-    </row>
-    <row r="371" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J370" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="16.5" thickBot="1">
       <c r="A371" s="6" t="s">
         <v>200</v>
       </c>
@@ -17593,7 +19118,7 @@
       <c r="E371" s="7"/>
       <c r="F371" s="5"/>
     </row>
-    <row r="372" spans="1:6" ht="16.5" thickBot="1">
+    <row r="372" spans="1:10" ht="16.5" thickBot="1">
       <c r="A372" s="6" t="s">
         <v>201</v>
       </c>
@@ -17607,7 +19132,7 @@
       <c r="E372" s="7"/>
       <c r="F372" s="5"/>
     </row>
-    <row r="373" spans="1:6" ht="16.5" thickBot="1">
+    <row r="373" spans="1:10" ht="16.5" thickBot="1">
       <c r="A373" s="6" t="s">
         <v>202</v>
       </c>
@@ -17620,8 +19145,11 @@
       <c r="D373" s="6"/>
       <c r="E373" s="7"/>
       <c r="F373" s="5"/>
-    </row>
-    <row r="374" spans="1:6" ht="31.5" thickBot="1">
+      <c r="J373" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="31.5" thickBot="1">
       <c r="A374" s="6" t="s">
         <v>203</v>
       </c>
@@ -17635,7 +19163,7 @@
       <c r="E374" s="7"/>
       <c r="F374" s="5"/>
     </row>
-    <row r="375" spans="1:6" ht="31.5" thickBot="1">
+    <row r="375" spans="1:10" ht="31.5" thickBot="1">
       <c r="A375" s="6" t="s">
         <v>204</v>
       </c>
@@ -17649,7 +19177,7 @@
       <c r="E375" s="7"/>
       <c r="F375" s="5"/>
     </row>
-    <row r="376" spans="1:6" ht="31.5" thickBot="1">
+    <row r="376" spans="1:10" ht="31.5" thickBot="1">
       <c r="A376" s="6" t="s">
         <v>205</v>
       </c>
@@ -17663,7 +19191,7 @@
       <c r="E376" s="7"/>
       <c r="F376" s="5"/>
     </row>
-    <row r="377" spans="1:6" ht="31.5" thickBot="1">
+    <row r="377" spans="1:10" ht="31.5" thickBot="1">
       <c r="A377" s="6" t="s">
         <v>206</v>
       </c>
@@ -17677,8 +19205,8 @@
       <c r="E377" s="7"/>
       <c r="F377" s="5"/>
     </row>
-    <row r="378" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A378" s="6" t="s">
+    <row r="378" spans="1:10" ht="16.5" thickBot="1">
+      <c r="A378" s="26" t="s">
         <v>207</v>
       </c>
       <c r="B378" s="6" t="s">
@@ -17690,8 +19218,11 @@
       <c r="D378" s="6"/>
       <c r="E378" s="7"/>
       <c r="F378" s="5"/>
-    </row>
-    <row r="379" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J378" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" ht="16.5" thickBot="1">
       <c r="A379" s="6" t="s">
         <v>208</v>
       </c>
@@ -17704,8 +19235,11 @@
       <c r="D379" s="6"/>
       <c r="E379" s="7"/>
       <c r="F379" s="5"/>
-    </row>
-    <row r="380" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J379" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="16.5" thickBot="1">
       <c r="A380" s="6" t="s">
         <v>209</v>
       </c>
@@ -17718,8 +19252,11 @@
       <c r="D380" s="6"/>
       <c r="E380" s="7"/>
       <c r="F380" s="5"/>
-    </row>
-    <row r="381" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J380" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="16.5" thickBot="1">
       <c r="A381" s="6" t="s">
         <v>210</v>
       </c>
@@ -17733,7 +19270,7 @@
       <c r="E381" s="7"/>
       <c r="F381" s="5"/>
     </row>
-    <row r="382" spans="1:6" ht="16.5" thickBot="1">
+    <row r="382" spans="1:10" ht="16.5" thickBot="1">
       <c r="A382" s="6" t="s">
         <v>211</v>
       </c>
@@ -17747,7 +19284,7 @@
       <c r="E382" s="7"/>
       <c r="F382" s="5"/>
     </row>
-    <row r="383" spans="1:6" ht="16.5" thickBot="1">
+    <row r="383" spans="1:10" ht="16.5" thickBot="1">
       <c r="A383" s="6" t="s">
         <v>212</v>
       </c>
@@ -17761,7 +19298,7 @@
       <c r="E383" s="7"/>
       <c r="F383" s="5"/>
     </row>
-    <row r="384" spans="1:6" ht="16.5" thickBot="1">
+    <row r="384" spans="1:10" ht="16.5" thickBot="1">
       <c r="A384" s="6" t="s">
         <v>213</v>
       </c>
@@ -17775,7 +19312,7 @@
       <c r="E384" s="7"/>
       <c r="F384" s="5"/>
     </row>
-    <row r="385" spans="1:6" ht="16.5" thickBot="1">
+    <row r="385" spans="1:10" ht="16.5" thickBot="1">
       <c r="A385" s="6" t="s">
         <v>214</v>
       </c>
@@ -17789,7 +19326,7 @@
       <c r="E385" s="7"/>
       <c r="F385" s="5"/>
     </row>
-    <row r="386" spans="1:6" ht="16.5" thickBot="1">
+    <row r="386" spans="1:10" ht="16.5" thickBot="1">
       <c r="A386" s="6" t="s">
         <v>215</v>
       </c>
@@ -17803,7 +19340,7 @@
       <c r="E386" s="7"/>
       <c r="F386" s="5"/>
     </row>
-    <row r="387" spans="1:6" ht="16.5" thickBot="1">
+    <row r="387" spans="1:10" ht="16.5" thickBot="1">
       <c r="A387" s="6" t="s">
         <v>216</v>
       </c>
@@ -17817,7 +19354,7 @@
       <c r="E387" s="7"/>
       <c r="F387" s="5"/>
     </row>
-    <row r="388" spans="1:6" ht="16.5" thickBot="1">
+    <row r="388" spans="1:10" ht="16.5" thickBot="1">
       <c r="A388" s="6" t="s">
         <v>217</v>
       </c>
@@ -17831,7 +19368,7 @@
       <c r="E388" s="7"/>
       <c r="F388" s="5"/>
     </row>
-    <row r="389" spans="1:6" ht="16.5" thickBot="1">
+    <row r="389" spans="1:10" ht="16.5" thickBot="1">
       <c r="A389" s="6" t="s">
         <v>218</v>
       </c>
@@ -17845,7 +19382,7 @@
       <c r="E389" s="7"/>
       <c r="F389" s="5"/>
     </row>
-    <row r="390" spans="1:6" ht="16.5" thickBot="1">
+    <row r="390" spans="1:10" ht="16.5" thickBot="1">
       <c r="A390" s="6" t="s">
         <v>219</v>
       </c>
@@ -17859,7 +19396,7 @@
       <c r="E390" s="7"/>
       <c r="F390" s="5"/>
     </row>
-    <row r="391" spans="1:6" ht="16.5" thickBot="1">
+    <row r="391" spans="1:10" ht="16.5" thickBot="1">
       <c r="A391" s="6" t="s">
         <v>220</v>
       </c>
@@ -17872,8 +19409,11 @@
       <c r="D391" s="6"/>
       <c r="E391" s="7"/>
       <c r="F391" s="5"/>
-    </row>
-    <row r="392" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J391" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="16.5" thickBot="1">
       <c r="A392" s="6" t="s">
         <v>221</v>
       </c>
@@ -17886,8 +19426,11 @@
       <c r="D392" s="6"/>
       <c r="E392" s="7"/>
       <c r="F392" s="5"/>
-    </row>
-    <row r="393" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J392" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" ht="16.5" thickBot="1">
       <c r="A393" s="6" t="s">
         <v>222</v>
       </c>
@@ -17900,8 +19443,11 @@
       <c r="D393" s="6"/>
       <c r="E393" s="7"/>
       <c r="F393" s="5"/>
-    </row>
-    <row r="394" spans="1:6" ht="16.5" thickBot="1">
+      <c r="J393" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" ht="16.5" thickBot="1">
       <c r="A394" s="6" t="s">
         <v>223</v>
       </c>
@@ -17915,7 +19461,7 @@
       <c r="E394" s="7"/>
       <c r="F394" s="5"/>
     </row>
-    <row r="395" spans="1:6" ht="16.5" thickBot="1">
+    <row r="395" spans="1:10" ht="16.5" thickBot="1">
       <c r="A395" s="6" t="s">
         <v>224</v>
       </c>
@@ -17929,7 +19475,7 @@
       <c r="E395" s="7"/>
       <c r="F395" s="5"/>
     </row>
-    <row r="396" spans="1:6" ht="16.5" thickBot="1">
+    <row r="396" spans="1:10" ht="16.5" thickBot="1">
       <c r="A396" s="6" t="s">
         <v>225</v>
       </c>
@@ -17943,21 +19489,27 @@
       <c r="E396" s="7"/>
       <c r="F396" s="5"/>
     </row>
-    <row r="397" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A397" s="6" t="s">
+    <row r="397" spans="1:10" ht="16.5" thickBot="1">
+      <c r="A397" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B397" s="6" t="s">
+      <c r="B397" s="22" t="s">
         <v>759</v>
       </c>
-      <c r="C397" s="6" t="s">
+      <c r="C397" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="D397" s="6"/>
-      <c r="E397" s="7"/>
-      <c r="F397" s="5"/>
-    </row>
-    <row r="398" spans="1:6" ht="16.5" thickBot="1">
+      <c r="D397" s="22"/>
+      <c r="E397" s="31"/>
+      <c r="F397" s="32"/>
+      <c r="G397" s="21"/>
+      <c r="H397" s="21"/>
+      <c r="I397" s="21"/>
+      <c r="J397" s="21" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" ht="16.5" thickBot="1">
       <c r="A398" s="6" t="s">
         <v>227</v>
       </c>
@@ -17971,7 +19523,7 @@
       <c r="E398" s="7"/>
       <c r="F398" s="5"/>
     </row>
-    <row r="399" spans="1:6" ht="16.5" thickBot="1">
+    <row r="399" spans="1:10" ht="16.5" thickBot="1">
       <c r="A399" s="6" t="s">
         <v>228</v>
       </c>
@@ -17985,7 +19537,7 @@
       <c r="E399" s="7"/>
       <c r="F399" s="5"/>
     </row>
-    <row r="400" spans="1:6" ht="16.5" thickBot="1">
+    <row r="400" spans="1:10" ht="16.5" thickBot="1">
       <c r="A400" s="6" t="s">
         <v>229</v>
       </c>
@@ -18050,6 +19602,3271 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9447E658-0406-4337-92E7-EF22271613D0}">
+  <dimension ref="A1:I526"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="9" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="23" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="23" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="23" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="23" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="23" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="23" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="23" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="23" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="23" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="23" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="23" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="23" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="23" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="23" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="23" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="23" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="23" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="23" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="23" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="23" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="23" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="23" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="23" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="23" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="25"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="23" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="25"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="23" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="23" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="23" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="23" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="23" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="23" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="23" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="23" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="23" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="23" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="23" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="23" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="23" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="23" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="23" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="23" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="23" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="23" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="23" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="23" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="23" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="23" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="23" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="23" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="23" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="25"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="23" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="25"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="23" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="23" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="23" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="23" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="23" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="23" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="23" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="23" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="27" t="s">
+        <v>932</v>
+      </c>
+      <c r="B93" s="38"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="27" t="s">
+        <v>933</v>
+      </c>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="27" t="s">
+        <v>934</v>
+      </c>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+      <c r="G95" s="38"/>
+      <c r="H95" s="38"/>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="27" t="s">
+        <v>935</v>
+      </c>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38"/>
+      <c r="G96" s="38"/>
+      <c r="H96" s="38"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="27" t="s">
+        <v>936</v>
+      </c>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="27" t="s">
+        <v>937</v>
+      </c>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="27" t="s">
+        <v>938</v>
+      </c>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="27" t="s">
+        <v>939</v>
+      </c>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="23" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="23" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="23" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="23" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="23" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="25"/>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="23" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="25"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="23" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="23" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="23" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="23" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="23" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="23" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="23" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="23" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="23" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="23" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="23" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="23" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="23" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="23" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="23" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="23" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="23" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="23" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="23" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="23" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="25"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="23" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="25"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="23" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="23" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="23" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="23" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="23" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="23" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="23" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="23" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="23" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="23" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="23" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="23" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="23" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="23" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="23" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="23" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="23" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="23" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="23" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="23" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="25"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="23" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="25"/>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="23" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="23" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="23" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="23" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="23" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="23" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="23" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="23" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="23" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="23" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="23" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="23" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="23" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="23" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="23" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="23" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="23" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="23" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="23" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="23" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="23" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="23" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="23" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="23" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="23" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="23" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="23" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="23" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="23" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="23" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="23" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="23" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="23" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="25"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="23" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="25"/>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="23" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="23" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="23" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="23" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="23" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="23" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="23" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="23" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="23" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="23" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="23" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="23" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="23" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="23" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="23" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="23" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="23" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="23" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="23" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="23" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="23" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="23" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="23" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="25"/>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="23" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="25"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="23" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="23" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="23" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="23" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="23" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="23" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="23" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="23" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="23" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="23" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="23" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="23" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="23" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="23" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="23" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="23" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="25"/>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="23" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="25"/>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="23" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="23" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="23" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="23" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="23" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="23" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="23" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="23" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="23" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="23" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="23" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" s="23" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" s="23" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" s="23" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" s="25"/>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="23" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="25"/>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" s="29" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B332" s="30"/>
+      <c r="C332" s="30"/>
+      <c r="D332" s="30"/>
+      <c r="E332" s="30"/>
+      <c r="F332" s="30"/>
+      <c r="G332" s="30"/>
+      <c r="H332" s="30"/>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" s="29" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B333" s="30"/>
+      <c r="C333" s="30"/>
+      <c r="D333" s="30"/>
+      <c r="E333" s="30"/>
+      <c r="F333" s="30"/>
+      <c r="G333" s="30"/>
+      <c r="H333" s="30"/>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" s="29" t="s">
+        <v>867</v>
+      </c>
+      <c r="B334" s="30"/>
+      <c r="C334" s="30"/>
+      <c r="D334" s="30"/>
+      <c r="E334" s="30"/>
+      <c r="F334" s="30"/>
+      <c r="G334" s="30"/>
+      <c r="H334" s="30"/>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+      <c r="D335" s="30"/>
+      <c r="E335" s="30"/>
+      <c r="F335" s="30"/>
+      <c r="G335" s="30"/>
+      <c r="H335" s="30"/>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" s="29" t="s">
+        <v>869</v>
+      </c>
+      <c r="B336" s="30"/>
+      <c r="C336" s="30"/>
+      <c r="D336" s="30"/>
+      <c r="E336" s="30"/>
+      <c r="F336" s="30"/>
+      <c r="G336" s="30"/>
+      <c r="H336" s="30"/>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" s="29" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B337" s="30"/>
+      <c r="C337" s="30"/>
+      <c r="D337" s="30"/>
+      <c r="E337" s="30"/>
+      <c r="F337" s="30"/>
+      <c r="G337" s="30"/>
+      <c r="H337" s="30"/>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" s="29" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B338" s="30"/>
+      <c r="C338" s="30"/>
+      <c r="D338" s="30"/>
+      <c r="E338" s="30"/>
+      <c r="F338" s="30"/>
+      <c r="G338" s="30"/>
+      <c r="H338" s="30"/>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" s="29" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B339" s="30"/>
+      <c r="C339" s="30"/>
+      <c r="D339" s="30"/>
+      <c r="E339" s="30"/>
+      <c r="F339" s="30"/>
+      <c r="G339" s="30"/>
+      <c r="H339" s="30"/>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" s="29" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B340" s="30"/>
+      <c r="C340" s="30"/>
+      <c r="D340" s="30"/>
+      <c r="E340" s="30"/>
+      <c r="F340" s="30"/>
+      <c r="G340" s="30"/>
+      <c r="H340" s="30"/>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" s="29" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+      <c r="D341" s="30"/>
+      <c r="E341" s="30"/>
+      <c r="F341" s="30"/>
+      <c r="G341" s="30"/>
+      <c r="H341" s="30"/>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="B342" s="30"/>
+      <c r="C342" s="30"/>
+      <c r="D342" s="30"/>
+      <c r="E342" s="30"/>
+      <c r="F342" s="30"/>
+      <c r="G342" s="30"/>
+      <c r="H342" s="30"/>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" s="29" t="s">
+        <v>875</v>
+      </c>
+      <c r="B343" s="30"/>
+      <c r="C343" s="30"/>
+      <c r="D343" s="30"/>
+      <c r="E343" s="30"/>
+      <c r="F343" s="30"/>
+      <c r="G343" s="30"/>
+      <c r="H343" s="30"/>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="29" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B344" s="30"/>
+      <c r="C344" s="30"/>
+      <c r="D344" s="30"/>
+      <c r="E344" s="30"/>
+      <c r="F344" s="30"/>
+      <c r="G344" s="30"/>
+      <c r="H344" s="30"/>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="29" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B345" s="30"/>
+      <c r="C345" s="30"/>
+      <c r="D345" s="30"/>
+      <c r="E345" s="30"/>
+      <c r="F345" s="30"/>
+      <c r="G345" s="30"/>
+      <c r="H345" s="30"/>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="29" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B346" s="30"/>
+      <c r="C346" s="30"/>
+      <c r="D346" s="30"/>
+      <c r="E346" s="30"/>
+      <c r="F346" s="30"/>
+      <c r="G346" s="30"/>
+      <c r="H346" s="30"/>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" s="29" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+      <c r="D347" s="30"/>
+      <c r="E347" s="30"/>
+      <c r="F347" s="30"/>
+      <c r="G347" s="30"/>
+      <c r="H347" s="30"/>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" s="29" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B348" s="30"/>
+      <c r="C348" s="30"/>
+      <c r="D348" s="30"/>
+      <c r="E348" s="30"/>
+      <c r="F348" s="30"/>
+      <c r="G348" s="30"/>
+      <c r="H348" s="30"/>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" s="29" t="s">
+        <v>889</v>
+      </c>
+      <c r="B349" s="30"/>
+      <c r="C349" s="30"/>
+      <c r="D349" s="30"/>
+      <c r="E349" s="30"/>
+      <c r="F349" s="30"/>
+      <c r="G349" s="30"/>
+      <c r="H349" s="30"/>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" s="29" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B350" s="30"/>
+      <c r="C350" s="30"/>
+      <c r="D350" s="30"/>
+      <c r="E350" s="30"/>
+      <c r="F350" s="30"/>
+      <c r="G350" s="30"/>
+      <c r="H350" s="30"/>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="B351" s="30"/>
+      <c r="C351" s="30"/>
+      <c r="D351" s="30"/>
+      <c r="E351" s="30"/>
+      <c r="F351" s="30"/>
+      <c r="G351" s="30"/>
+      <c r="H351" s="30"/>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" s="29" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B352" s="30"/>
+      <c r="C352" s="30"/>
+      <c r="D352" s="30"/>
+      <c r="E352" s="30"/>
+      <c r="F352" s="30"/>
+      <c r="G352" s="30"/>
+      <c r="H352" s="30"/>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="29" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B353" s="30"/>
+      <c r="C353" s="30"/>
+      <c r="D353" s="30"/>
+      <c r="E353" s="30"/>
+      <c r="F353" s="30"/>
+      <c r="G353" s="30"/>
+      <c r="H353" s="30"/>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="29" t="s">
+        <v>893</v>
+      </c>
+      <c r="B354" s="30"/>
+      <c r="C354" s="30"/>
+      <c r="D354" s="30"/>
+      <c r="E354" s="30"/>
+      <c r="F354" s="30"/>
+      <c r="G354" s="30"/>
+      <c r="H354" s="30"/>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="B355" s="30"/>
+      <c r="C355" s="30"/>
+      <c r="D355" s="30"/>
+      <c r="E355" s="30"/>
+      <c r="F355" s="30"/>
+      <c r="G355" s="30"/>
+      <c r="H355" s="30"/>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="29" t="s">
+        <v>894</v>
+      </c>
+      <c r="B356" s="30"/>
+      <c r="C356" s="30"/>
+      <c r="D356" s="30"/>
+      <c r="E356" s="30"/>
+      <c r="F356" s="30"/>
+      <c r="G356" s="30"/>
+      <c r="H356" s="30"/>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="25"/>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="23" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="25"/>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="23" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="23" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="23" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="23" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="23" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="23" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="23" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="23" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="23" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="23" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="23" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="23" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="23" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="23" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="23" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="23" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="23" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="23" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="23" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="23" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="23" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="25"/>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="23" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="25"/>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="23" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="23" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="23" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="23" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="23" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="23" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="23" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="23" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="23" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="23" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="23" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="23" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="23" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="23" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="23" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="23" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="23" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="23" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="23" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="23" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="23" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="23" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="23" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="23" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="23" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="23" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="23" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="25"/>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="23" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="25"/>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="23" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="25"/>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="23" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="25"/>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="23" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="23" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="23" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="23" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="23" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="23" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="23" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="23" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="23" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="23" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="23" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="23" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="23" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="23" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="23" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="23" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="23" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="23" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" s="23" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" s="23" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" s="23" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" s="23" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" s="23" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" s="23" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" s="23" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" s="23" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" s="23" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" s="23" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" s="23" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" s="23" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" s="23" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" s="23" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" s="23" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" s="23" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" s="23" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" s="23" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" s="23" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" s="23" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" s="23" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" s="23" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" s="23" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" s="23" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" s="23" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" s="23" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" s="23" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" s="23" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496" s="23" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497" s="23" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498" s="23" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499" s="23" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500" s="23" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501" s="23" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502" s="23" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503" s="23" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504" s="23" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505" s="23" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506" s="23" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507" s="23" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508" s="25"/>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509" s="23" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510" s="25"/>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511" s="23" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" s="23" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" s="23" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" s="23" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" s="23" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" s="23" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" s="23" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" s="23" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" s="23" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" s="23" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" s="23" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" s="23" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" s="23" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" s="23" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" s="23" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" s="23" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAF9D8E-5017-468F-8689-A64B44F82814}">
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="178.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="23" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="23" t="s">
+        <v>833</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="27" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="28" t="s">
+        <v>835</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="23" t="s">
+        <v>836</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="23" t="s">
+        <v>837</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="23" t="s">
+        <v>838</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="28" t="s">
+        <v>839</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="23" t="s">
+        <v>840</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="23" t="s">
+        <v>841</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="23" t="s">
+        <v>842</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="23" t="s">
+        <v>843</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="23" t="s">
+        <v>844</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="23" t="s">
+        <v>846</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="23" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="16" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="409.5">
+      <c r="B19" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="16" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="45">
+      <c r="B21" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="17"/>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="16" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="16" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="17"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="16" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="16" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B28" s="17"/>
+    </row>
+    <row r="29" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B29" s="16" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B30" s="16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B31" s="16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B32" s="17"/>
+    </row>
+    <row r="33" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B33" s="16" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B34" s="16" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B35" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B36" s="17"/>
+    </row>
+    <row r="37" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B37" s="16" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B38" s="16" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B39" s="16" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B40" s="16" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="44.25" customHeight="1">
+      <c r="B41" s="16" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="44.25" customHeight="1"/>
+    <row r="43" spans="2:4" ht="44.25" customHeight="1"/>
+    <row r="44" spans="2:4">
+      <c r="B44" s="18" t="s">
+        <v>832</v>
+      </c>
+      <c r="C44" s="19"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="18" t="s">
+        <v>833</v>
+      </c>
+      <c r="C45" s="19"/>
+    </row>
+    <row r="46" spans="2:4" ht="315">
+      <c r="B46" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="345">
+      <c r="B47" s="18" t="s">
+        <v>835</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="315">
+      <c r="B48" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="330">
+      <c r="B49" s="18" t="s">
+        <v>837</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="345">
+      <c r="B50" s="18" t="s">
+        <v>838</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="315">
+      <c r="B51" s="18" t="s">
+        <v>839</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="315">
+      <c r="B52" s="18" t="s">
+        <v>840</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="315">
+      <c r="B53" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="330">
+      <c r="B54" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="300">
+      <c r="B55" s="18" t="s">
+        <v>843</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="315">
+      <c r="B56" s="18" t="s">
+        <v>844</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="315">
+      <c r="B57" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="315">
+      <c r="B58" s="18" t="s">
+        <v>846</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" ht="315">
+      <c r="B59" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7DD0CD-6695-4D3C-9518-BDB565BCCF21}">
   <dimension ref="B3:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -18068,270 +22885,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FAF9D8E-5017-468F-8689-A64B44F82814}">
-  <dimension ref="B2:D43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="178.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:3">
-      <c r="B2" s="16" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="201" customHeight="1">
-      <c r="B3" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" s="16" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="B5" s="16" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="17"/>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" s="16" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="16" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="16" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="16" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" s="17"/>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="B13" s="16" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="16" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" s="16" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3">
-      <c r="B16" s="17"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="16" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="16" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="16" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="17"/>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" s="16" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="16" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="16" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="16" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="16" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B28" s="18" t="s">
-        <v>832</v>
-      </c>
-      <c r="C28" s="19"/>
-    </row>
-    <row r="29" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B29" s="18" t="s">
-        <v>833</v>
-      </c>
-      <c r="C29" s="19"/>
-    </row>
-    <row r="30" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B30" s="18" t="s">
-        <v>834</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="2" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B31" s="18" t="s">
-        <v>835</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="2" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B32" s="18" t="s">
-        <v>836</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="2" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B33" s="18" t="s">
-        <v>837</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="2" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B34" s="18" t="s">
-        <v>838</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B35" s="18" t="s">
-        <v>839</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="2" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B36" s="18" t="s">
-        <v>840</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="2" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B37" s="18" t="s">
-        <v>841</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B38" s="18" t="s">
-        <v>842</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B39" s="18" t="s">
-        <v>843</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B40" s="18" t="s">
-        <v>844</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="2" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B41" s="18" t="s">
-        <v>845</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="2" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B42" s="18" t="s">
-        <v>846</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="2" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="44.25" customHeight="1">
-      <c r="B43" s="18" t="s">
-        <v>847</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="2" t="s">
-        <v>859</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F8783-740C-46A0-B68E-D247051A3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688FBF51-9951-4660-ACDF-7EFA44BE7ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79CD580-3D6E-41EC-ADBC-0888C41D8202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887C8B13-CE69-4AF6-9C3E-FBB8B4CF3DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20616" windowHeight="11016" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -3930,9 +3930,6 @@
     <t>AGENTE</t>
   </si>
   <si>
-    <t>orden</t>
-  </si>
-  <si>
     <t>7- skateholders</t>
   </si>
   <si>
@@ -3985,6 +3982,9 @@
   </si>
   <si>
     <t>14 - QA/E2E</t>
+  </si>
+  <si>
+    <t>prioridad</t>
   </si>
 </sst>
 </file>
@@ -8708,8 +8708,9 @@
     <col min="4" max="4" width="11.5546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="50.5546875" customWidth="1"/>
-    <col min="7" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="10" width="39.5546875" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5546875" customWidth="1"/>
     <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -18457,7 +18458,7 @@
       <c r="D338" s="6"/>
       <c r="E338" s="7"/>
       <c r="F338" s="5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16.2" thickBot="1">
@@ -18473,7 +18474,7 @@
       <c r="D339" s="6"/>
       <c r="E339" s="7"/>
       <c r="F339" s="5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16.2" thickBot="1">
@@ -18489,7 +18490,7 @@
       <c r="D340" s="6"/>
       <c r="E340" s="7"/>
       <c r="F340" s="5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="16.2" thickBot="1">
@@ -18505,7 +18506,7 @@
       <c r="D341" s="6"/>
       <c r="E341" s="7"/>
       <c r="F341" s="5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="16.2" thickBot="1">
@@ -18521,7 +18522,7 @@
       <c r="D342" s="6"/>
       <c r="E342" s="7"/>
       <c r="F342" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16.2" thickBot="1">
@@ -18537,7 +18538,7 @@
       <c r="D343" s="6"/>
       <c r="E343" s="7"/>
       <c r="F343" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="344" spans="1:10" ht="16.2" thickBot="1">
@@ -18553,7 +18554,7 @@
       <c r="D344" s="6"/>
       <c r="E344" s="7"/>
       <c r="F344" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="345" spans="1:10" ht="16.2" thickBot="1">
@@ -18569,7 +18570,7 @@
       <c r="D345" s="6"/>
       <c r="E345" s="7"/>
       <c r="F345" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="346" spans="1:10" ht="16.2" thickBot="1">
@@ -18585,7 +18586,7 @@
       <c r="D346" s="6"/>
       <c r="E346" s="7"/>
       <c r="F346" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="347" spans="1:10" ht="16.2" thickBot="1">
@@ -18601,7 +18602,7 @@
       <c r="D347" s="6"/>
       <c r="E347" s="7"/>
       <c r="F347" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="348" spans="1:10" ht="16.2" thickBot="1">
@@ -18617,7 +18618,7 @@
       <c r="D348" s="6"/>
       <c r="E348" s="7"/>
       <c r="F348" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="349" spans="1:10" ht="16.2" thickBot="1">
@@ -18633,7 +18634,7 @@
       <c r="D349" s="6"/>
       <c r="E349" s="7"/>
       <c r="F349" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="350" spans="1:10" ht="16.2" thickBot="1">
@@ -18649,7 +18650,7 @@
       <c r="D350" s="6"/>
       <c r="E350" s="7"/>
       <c r="F350" s="5" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="351" spans="1:10" ht="16.2" thickBot="1">
@@ -18665,7 +18666,7 @@
       <c r="D351" s="6"/>
       <c r="E351" s="7"/>
       <c r="F351" s="5" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="352" spans="1:10" ht="16.2" thickBot="1">
@@ -18681,7 +18682,7 @@
       <c r="D352" s="31"/>
       <c r="E352" s="32"/>
       <c r="F352" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="J352" t="s">
         <v>404</v>
@@ -18700,7 +18701,7 @@
       <c r="D353" s="31"/>
       <c r="E353" s="32"/>
       <c r="F353" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="J353" t="s">
         <v>404</v>
@@ -18719,7 +18720,7 @@
       <c r="D354" s="6"/>
       <c r="E354" s="7"/>
       <c r="F354" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="355" spans="1:10" ht="16.2" thickBot="1">
@@ -18735,7 +18736,7 @@
       <c r="D355" s="6"/>
       <c r="E355" s="7"/>
       <c r="F355" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="356" spans="1:10" ht="16.2" thickBot="1">
@@ -18751,7 +18752,7 @@
       <c r="D356" s="6"/>
       <c r="E356" s="7"/>
       <c r="F356" s="5" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="357" spans="1:10" ht="16.2" thickBot="1">
@@ -18767,7 +18768,7 @@
       <c r="D357" s="6"/>
       <c r="E357" s="7"/>
       <c r="F357" s="5" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="358" spans="1:10" ht="16.2" thickBot="1">
@@ -18783,7 +18784,7 @@
       <c r="D358" s="6"/>
       <c r="E358" s="7"/>
       <c r="F358" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="359" spans="1:10" ht="16.2" thickBot="1">
@@ -18799,7 +18800,7 @@
       <c r="D359" s="6"/>
       <c r="E359" s="7"/>
       <c r="F359" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="360" spans="1:10" ht="16.2" thickBot="1">
@@ -18815,7 +18816,7 @@
       <c r="D360" s="6"/>
       <c r="E360" s="7"/>
       <c r="F360" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="361" spans="1:10" ht="16.2" thickBot="1">
@@ -18831,7 +18832,7 @@
       <c r="D361" s="6"/>
       <c r="E361" s="7"/>
       <c r="F361" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="362" spans="1:10" ht="16.2" thickBot="1">
@@ -18847,7 +18848,7 @@
       <c r="D362" s="6"/>
       <c r="E362" s="7"/>
       <c r="F362" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="363" spans="1:10" ht="16.2" thickBot="1">
@@ -18863,7 +18864,7 @@
       <c r="D363" s="6"/>
       <c r="E363" s="7"/>
       <c r="F363" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="364" spans="1:10" ht="16.2" thickBot="1">
@@ -18879,7 +18880,7 @@
       <c r="D364" s="6"/>
       <c r="E364" s="7"/>
       <c r="F364" s="5" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="365" spans="1:10" ht="16.2" thickBot="1">
@@ -18895,7 +18896,7 @@
       <c r="D365" s="6"/>
       <c r="E365" s="7"/>
       <c r="F365" s="5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="366" spans="1:10" ht="16.2" thickBot="1">
@@ -18911,7 +18912,7 @@
       <c r="D366" s="6"/>
       <c r="E366" s="7"/>
       <c r="F366" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="367" spans="1:10" ht="16.2" thickBot="1">
@@ -18927,7 +18928,7 @@
       <c r="D367" s="6"/>
       <c r="E367" s="7"/>
       <c r="F367" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="368" spans="1:10" ht="16.2" thickBot="1">
@@ -18943,7 +18944,7 @@
       <c r="D368" s="6"/>
       <c r="E368" s="7"/>
       <c r="F368" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="369" spans="1:10" ht="16.2" thickBot="1">
@@ -18959,7 +18960,7 @@
       <c r="D369" s="6"/>
       <c r="E369" s="7"/>
       <c r="F369" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J369" t="s">
         <v>851</v>
@@ -18978,7 +18979,7 @@
       <c r="D370" s="6"/>
       <c r="E370" s="7"/>
       <c r="F370" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J370" t="s">
         <v>851</v>
@@ -18997,7 +18998,7 @@
       <c r="D371" s="6"/>
       <c r="E371" s="7"/>
       <c r="F371" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="372" spans="1:10" ht="16.2" thickBot="1">
@@ -19013,7 +19014,7 @@
       <c r="D372" s="6"/>
       <c r="E372" s="7"/>
       <c r="F372" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="373" spans="1:10" ht="16.2" thickBot="1">
@@ -19029,7 +19030,7 @@
       <c r="D373" s="6"/>
       <c r="E373" s="7"/>
       <c r="F373" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="J373" t="s">
         <v>851</v>
@@ -19048,7 +19049,7 @@
       <c r="D374" s="6"/>
       <c r="E374" s="7"/>
       <c r="F374" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="375" spans="1:10" ht="16.2" thickBot="1">
@@ -19064,7 +19065,7 @@
       <c r="D375" s="6"/>
       <c r="E375" s="7"/>
       <c r="F375" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="376" spans="1:10" ht="16.2" thickBot="1">
@@ -19080,7 +19081,7 @@
       <c r="D376" s="6"/>
       <c r="E376" s="7"/>
       <c r="F376" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="377" spans="1:10" ht="16.2" thickBot="1">
@@ -19096,7 +19097,7 @@
       <c r="D377" s="6"/>
       <c r="E377" s="7"/>
       <c r="F377" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="378" spans="1:10" ht="16.2" thickBot="1">
@@ -19112,7 +19113,7 @@
       <c r="D378" s="6"/>
       <c r="E378" s="7"/>
       <c r="F378" s="5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="J378" t="s">
         <v>404</v>
@@ -19131,7 +19132,7 @@
       <c r="D379" s="6"/>
       <c r="E379" s="7"/>
       <c r="F379" s="5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="J379" t="s">
         <v>404</v>
@@ -19150,7 +19151,7 @@
       <c r="D380" s="6"/>
       <c r="E380" s="7"/>
       <c r="F380" s="5" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="J380" t="s">
         <v>404</v>
@@ -19169,7 +19170,7 @@
       <c r="D381" s="6"/>
       <c r="E381" s="7"/>
       <c r="F381" s="5" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="382" spans="1:10" ht="16.2" thickBot="1">
@@ -19185,7 +19186,7 @@
       <c r="D382" s="6"/>
       <c r="E382" s="7"/>
       <c r="F382" s="5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="383" spans="1:10" ht="16.2" thickBot="1">
@@ -19201,7 +19202,7 @@
       <c r="D383" s="6"/>
       <c r="E383" s="7"/>
       <c r="F383" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="384" spans="1:10" ht="16.2" thickBot="1">
@@ -19217,7 +19218,7 @@
       <c r="D384" s="6"/>
       <c r="E384" s="7"/>
       <c r="F384" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="385" spans="1:10" ht="16.2" thickBot="1">
@@ -19233,7 +19234,7 @@
       <c r="D385" s="6"/>
       <c r="E385" s="7"/>
       <c r="F385" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="386" spans="1:10" ht="16.2" thickBot="1">
@@ -19249,7 +19250,7 @@
       <c r="D386" s="6"/>
       <c r="E386" s="7"/>
       <c r="F386" s="5" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="387" spans="1:10" ht="16.2" thickBot="1">
@@ -19265,7 +19266,7 @@
       <c r="D387" s="6"/>
       <c r="E387" s="7"/>
       <c r="F387" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="388" spans="1:10" ht="16.2" thickBot="1">
@@ -19281,7 +19282,7 @@
       <c r="D388" s="6"/>
       <c r="E388" s="7"/>
       <c r="F388" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="389" spans="1:10" ht="16.2" thickBot="1">
@@ -19297,7 +19298,7 @@
       <c r="D389" s="6"/>
       <c r="E389" s="7"/>
       <c r="F389" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="390" spans="1:10" ht="16.2" thickBot="1">
@@ -19313,7 +19314,7 @@
       <c r="D390" s="6"/>
       <c r="E390" s="7"/>
       <c r="F390" s="5" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="391" spans="1:10" ht="16.2" thickBot="1">
@@ -19329,7 +19330,7 @@
       <c r="D391" s="6"/>
       <c r="E391" s="7"/>
       <c r="F391" s="5" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J391" t="s">
         <v>404</v>
@@ -19348,7 +19349,7 @@
       <c r="D392" s="6"/>
       <c r="E392" s="7"/>
       <c r="F392" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="J392" t="s">
         <v>404</v>
@@ -19367,7 +19368,7 @@
       <c r="D393" s="6"/>
       <c r="E393" s="7"/>
       <c r="F393" s="5" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="J393" t="s">
         <v>404</v>
@@ -19386,7 +19387,7 @@
       <c r="D394" s="6"/>
       <c r="E394" s="7"/>
       <c r="F394" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="395" spans="1:10" ht="16.2" thickBot="1">
@@ -19402,7 +19403,7 @@
       <c r="D395" s="6"/>
       <c r="E395" s="7"/>
       <c r="F395" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="396" spans="1:10" ht="16.2" thickBot="1">
@@ -19418,7 +19419,7 @@
       <c r="D396" s="6"/>
       <c r="E396" s="7"/>
       <c r="F396" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="397" spans="1:10" ht="16.2" thickBot="1">
@@ -19434,7 +19435,7 @@
       <c r="D397" s="21"/>
       <c r="E397" s="30"/>
       <c r="F397" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G397" s="20"/>
       <c r="H397" s="20"/>
@@ -19456,7 +19457,7 @@
       <c r="D398" s="6"/>
       <c r="E398" s="7"/>
       <c r="F398" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="399" spans="1:10" ht="16.2" thickBot="1">
@@ -19472,7 +19473,7 @@
       <c r="D399" s="6"/>
       <c r="E399" s="7"/>
       <c r="F399" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="400" spans="1:10" ht="16.2" thickBot="1">
@@ -19488,7 +19489,7 @@
       <c r="D400" s="6"/>
       <c r="E400" s="7"/>
       <c r="F400" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="401" spans="1:6" ht="16.2" thickBot="1">
@@ -19504,7 +19505,7 @@
       <c r="D401" s="6"/>
       <c r="E401" s="7"/>
       <c r="F401" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="402" spans="1:6" ht="16.2" thickBot="1">
@@ -19520,7 +19521,7 @@
       <c r="D402" s="6"/>
       <c r="E402" s="7"/>
       <c r="F402" s="5" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="403" spans="1:6" ht="15" thickBot="1">
@@ -22462,7 +22463,7 @@
         <v>1167</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>1168</v>
+        <v>1186</v>
       </c>
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
@@ -22710,10 +22711,10 @@
       <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="35" t="s">
         <v>875</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="35" t="s">
         <v>852</v>
       </c>
       <c r="C16" s="29">

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE75CE3-DA52-4ED3-AE03-4303D95E33AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CE3207-E29A-40DF-984A-841E56D8C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5788" uniqueCount="1637">
   <si>
     <t>Nº</t>
   </si>
@@ -12905,7 +12905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13080,6 +13080,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13387,16 +13388,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="19.149999999999999" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="19.2" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.28515625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="62.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="62.33203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="1" spans="1:13" ht="19.2" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13434,7 +13435,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="2" spans="1:13" ht="19.2" customHeight="1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13473,7 +13474,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="3" spans="1:13" ht="19.2" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -13512,7 +13513,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="4" spans="1:13" ht="19.2" customHeight="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -13551,7 +13552,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="5" spans="1:13" ht="19.2" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -13593,7 +13594,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="6" spans="1:13" ht="19.2" customHeight="1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -13632,7 +13633,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="7" spans="1:13" ht="19.2" customHeight="1">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -13671,7 +13672,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="8" spans="1:13" ht="19.2" customHeight="1">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -13710,7 +13711,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="9" spans="1:13" ht="19.2" customHeight="1">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -13749,7 +13750,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="10" spans="1:13" ht="19.2" customHeight="1">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -13791,7 +13792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="11" spans="1:13" ht="19.2" customHeight="1">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -13833,7 +13834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="12" spans="1:13" ht="19.2" customHeight="1">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -13872,7 +13873,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="13" spans="1:13" ht="19.2" customHeight="1">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -13911,7 +13912,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="14" spans="1:13" ht="19.2" customHeight="1">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -13947,7 +13948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="15" spans="1:13" ht="19.2" customHeight="1">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -13983,7 +13984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="16" spans="1:13" ht="19.2" customHeight="1">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -14022,7 +14023,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="17" spans="1:13" ht="19.2" customHeight="1">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -14058,7 +14059,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="18" spans="1:13" ht="19.2" customHeight="1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -14091,7 +14092,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="19" spans="1:13" ht="19.2" customHeight="1">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -14124,7 +14125,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="20" spans="1:13" ht="19.2" customHeight="1">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -14157,7 +14158,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="21" spans="1:13" ht="19.2" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -14190,7 +14191,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="22" spans="1:13" ht="19.2" customHeight="1">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -14223,7 +14224,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="23" spans="1:13" ht="19.2" customHeight="1">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -14262,7 +14263,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="24" spans="1:13" ht="19.2" customHeight="1">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -14298,7 +14299,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="25" spans="1:13" ht="19.2" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -14331,7 +14332,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="26" spans="1:13" ht="19.2" customHeight="1">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="27" spans="1:13" ht="19.2" customHeight="1">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -14397,7 +14398,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="28" spans="1:13" ht="19.2" customHeight="1">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -14436,7 +14437,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="29" spans="1:13" ht="19.2" customHeight="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -14469,7 +14470,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="30" spans="1:13" ht="19.2" customHeight="1">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -14502,7 +14503,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="31" spans="1:13" ht="19.2" customHeight="1">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -14535,7 +14536,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="32" spans="1:13" ht="19.2" customHeight="1">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -14568,7 +14569,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="33" spans="1:13" ht="19.2" customHeight="1">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -14601,7 +14602,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="34" spans="1:13" ht="19.2" customHeight="1">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -14637,7 +14638,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="35" spans="1:13" ht="19.2" customHeight="1">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -14673,7 +14674,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="36" spans="1:13" ht="19.2" customHeight="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -14709,7 +14710,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="37" spans="1:13" ht="19.2" customHeight="1">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -14745,7 +14746,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="38" spans="1:13" ht="19.2" customHeight="1">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -14781,7 +14782,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="39" spans="1:13" ht="19.2" customHeight="1">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -14820,7 +14821,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="40" spans="1:13" ht="19.2" customHeight="1">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -14853,7 +14854,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="41" spans="1:13" ht="19.2" customHeight="1">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -14886,7 +14887,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="42" spans="1:13" ht="19.2" customHeight="1">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -14919,7 +14920,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="43" spans="1:13" ht="19.2" customHeight="1">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -14952,7 +14953,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="44" spans="1:13" ht="19.2" customHeight="1">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -14985,7 +14986,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="45" spans="1:13" ht="19.2" customHeight="1">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -15018,7 +15019,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="46" spans="1:13" ht="19.2" customHeight="1">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -15051,7 +15052,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="47" spans="1:13" ht="19.2" customHeight="1">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -15090,7 +15091,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="48" spans="1:13" ht="19.2" customHeight="1">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -15123,7 +15124,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="49" spans="1:13" ht="19.2" customHeight="1">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -15156,7 +15157,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="50" spans="1:13" ht="19.2" customHeight="1">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -15189,7 +15190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="51" spans="1:13" ht="19.2" customHeight="1">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -15222,7 +15223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="52" spans="1:13" ht="19.2" customHeight="1">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -15255,7 +15256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="53" spans="1:13" ht="19.2" customHeight="1">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -15288,7 +15289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="54" spans="1:13" ht="19.2" customHeight="1">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -15321,7 +15322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="55" spans="1:13" ht="19.2" customHeight="1">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -15354,7 +15355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="56" spans="1:13" ht="19.2" customHeight="1">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -15387,7 +15388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="57" spans="1:13" ht="19.2" customHeight="1">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -15420,7 +15421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="58" spans="1:13" ht="19.2" customHeight="1">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -15453,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="59" spans="1:13" ht="19.2" customHeight="1">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -15486,7 +15487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="60" spans="1:13" ht="19.2" customHeight="1">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -15519,7 +15520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="61" spans="1:13" ht="19.2" customHeight="1">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -15552,7 +15553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="62" spans="1:13" ht="19.2" customHeight="1">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -15585,7 +15586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="63" spans="1:13" ht="19.2" customHeight="1">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -15618,7 +15619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="64" spans="1:13" ht="19.2" customHeight="1">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -15651,7 +15652,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="65" spans="1:13" ht="19.2" customHeight="1">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -15684,7 +15685,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="66" spans="1:13" ht="19.2" customHeight="1">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -15717,7 +15718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="67" spans="1:13" ht="19.2" customHeight="1">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -15750,7 +15751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="68" spans="1:13" ht="19.2" customHeight="1">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -15783,7 +15784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="69" spans="1:13" ht="19.2" customHeight="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -15816,7 +15817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="70" spans="1:13" ht="19.2" customHeight="1">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -15849,7 +15850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="71" spans="1:13" ht="19.2" customHeight="1">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -15882,7 +15883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="72" spans="1:13" ht="19.2" customHeight="1">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -15924,7 +15925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="73" spans="1:13" ht="19.2" customHeight="1">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -15963,7 +15964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="74" spans="1:13" ht="19.2" customHeight="1">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -16002,7 +16003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="75" spans="1:13" ht="19.2" customHeight="1">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -16038,7 +16039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="76" spans="1:13" ht="19.2" customHeight="1">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -16071,7 +16072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="77" spans="1:13" ht="19.2" customHeight="1">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -16110,7 +16111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="78" spans="1:13" ht="19.2" customHeight="1">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -16149,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="79" spans="1:13" ht="19.2" customHeight="1">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -16188,7 +16189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="80" spans="1:13" ht="19.2" customHeight="1">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -16224,7 +16225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="81" spans="1:13" ht="19.2" customHeight="1">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -16260,7 +16261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="82" spans="1:13" ht="19.2" customHeight="1">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -16293,7 +16294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="83" spans="1:13" ht="19.2" customHeight="1">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -16335,7 +16336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="84" spans="1:13" ht="19.2" customHeight="1">
       <c r="A84" t="s">
         <v>102</v>
       </c>
@@ -16368,7 +16369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="85" spans="1:13" ht="19.2" customHeight="1">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -16404,7 +16405,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="86" spans="1:13" ht="19.2" customHeight="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -16443,7 +16444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="87" spans="1:13" ht="19.2" customHeight="1">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -16476,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="88" spans="1:13" ht="19.2" customHeight="1">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -16509,7 +16510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="89" spans="1:13" ht="19.2" customHeight="1">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -16542,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="90" spans="1:13" ht="19.2" customHeight="1">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -16581,7 +16582,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="91" spans="1:13" ht="19.2" customHeight="1">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -16617,7 +16618,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="92" spans="1:13" ht="19.2" customHeight="1">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -16653,7 +16654,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="93" spans="1:13" ht="19.2" customHeight="1">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -16686,7 +16687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="94" spans="1:13" ht="19.2" customHeight="1">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="95" spans="1:13" ht="19.2" customHeight="1">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -16761,7 +16762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="96" spans="1:13" ht="19.2" customHeight="1">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -16794,7 +16795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="97" spans="1:13" ht="19.2" customHeight="1">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -16833,7 +16834,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="98" spans="1:13" ht="19.2" customHeight="1">
       <c r="A98" t="s">
         <v>86</v>
       </c>
@@ -16869,7 +16870,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="99" spans="1:13" ht="19.2" customHeight="1">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -16905,7 +16906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="100" spans="1:13" ht="19.2" customHeight="1">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -16941,7 +16942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="101" spans="1:13" ht="19.2" customHeight="1">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -16974,7 +16975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="102" spans="1:13" ht="19.2" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -17010,7 +17011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="103" spans="1:13" ht="19.2" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -17052,7 +17053,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="104" spans="1:13" ht="19.2" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -17088,7 +17089,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="105" spans="1:13" ht="19.2" customHeight="1">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -17124,7 +17125,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="106" spans="1:13" ht="19.2" customHeight="1">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -17160,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="107" spans="1:13" ht="19.2" customHeight="1">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -17199,7 +17200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="108" spans="1:13" ht="19.2" customHeight="1">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -17235,7 +17236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="109" spans="1:13" ht="19.2" customHeight="1">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -17274,7 +17275,7 @@
         <v>claude</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="110" spans="1:13" ht="19.2" customHeight="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -17313,7 +17314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="111" spans="1:13" ht="19.2" customHeight="1">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -17352,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="112" spans="1:13" ht="19.2" customHeight="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -17385,7 +17386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="113" spans="1:13" ht="19.2" customHeight="1">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -17418,7 +17419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="114" spans="1:13" ht="19.2" customHeight="1">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -17467,17 +17468,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16843C28-0155-42BB-A62E-C4CE7C932E1A}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="146.42578125" customWidth="1"/>
+    <col min="1" max="1" width="146.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5">
+    <row r="1" spans="1:1" ht="409.6">
       <c r="A1" s="2" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="90">
+    <row r="3" spans="1:1" ht="86.4">
       <c r="A3" s="2" t="s">
         <v>1340</v>
       </c>
@@ -17491,14 +17492,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1590E3-1708-4563-889F-3AD6ACE1A716}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F236"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="79" customWidth="1"/>
-    <col min="6" max="6" width="67.85546875" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -17530,82 +17531,82 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" hidden="1">
+    <row r="3" spans="1:5" ht="19.2" hidden="1">
       <c r="B3" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="86.25" hidden="1">
+    <row r="4" spans="1:5" ht="96" hidden="1">
       <c r="B4" s="43" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="34.5" hidden="1">
+    <row r="5" spans="1:5" ht="38.4" hidden="1">
       <c r="B5" s="43" t="s">
         <v>1346</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="51.75" hidden="1">
+    <row r="6" spans="1:5" ht="57.6" hidden="1">
       <c r="B6" s="43" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.25" hidden="1">
+    <row r="7" spans="1:5" ht="19.2" hidden="1">
       <c r="B7" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="34.5" hidden="1">
+    <row r="8" spans="1:5" ht="38.4" hidden="1">
       <c r="B8" s="43" t="s">
         <v>1349</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="34.5" hidden="1">
+    <row r="9" spans="1:5" ht="38.4" hidden="1">
       <c r="B9" s="43" t="s">
         <v>1350</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="34.5" hidden="1">
+    <row r="10" spans="1:5" ht="38.4" hidden="1">
       <c r="B10" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51.75" hidden="1">
+    <row r="11" spans="1:5" ht="57.6" hidden="1">
       <c r="B11" s="43" t="s">
         <v>1352</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="51.75" hidden="1">
+    <row r="12" spans="1:5" ht="57.6" hidden="1">
       <c r="B12" s="43" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" hidden="1">
+    <row r="13" spans="1:5" ht="19.2" hidden="1">
       <c r="B13" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="51.75" hidden="1">
+    <row r="14" spans="1:5" ht="57.6" hidden="1">
       <c r="B14" s="43" t="s">
         <v>1355</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="34.5" hidden="1">
+    <row r="15" spans="1:5" ht="38.4" hidden="1">
       <c r="B15" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="69" hidden="1">
+    <row r="16" spans="1:5" ht="57.6" hidden="1">
       <c r="B16" s="43" t="s">
         <v>1357</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="34.5" hidden="1">
+    <row r="17" spans="1:6" ht="38.4" hidden="1">
       <c r="B17" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="69" hidden="1">
+    <row r="18" spans="1:6" ht="57.6" hidden="1">
       <c r="B18" s="43" t="s">
         <v>1359</v>
       </c>
@@ -17631,82 +17632,82 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.25" hidden="1">
+    <row r="20" spans="1:6" ht="19.2" hidden="1">
       <c r="B20" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="51.75" hidden="1">
+    <row r="21" spans="1:6" ht="57.6" hidden="1">
       <c r="B21" s="43" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="69" hidden="1">
+    <row r="22" spans="1:6" ht="76.8" hidden="1">
       <c r="B22" s="43" t="s">
         <v>1362</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="69" hidden="1">
+    <row r="23" spans="1:6" ht="57.6" hidden="1">
       <c r="B23" s="43" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17.25" hidden="1">
+    <row r="24" spans="1:6" ht="19.2" hidden="1">
       <c r="B24" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17.25" hidden="1">
+    <row r="25" spans="1:6" ht="19.2" hidden="1">
       <c r="B25" s="43" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="34.5" hidden="1">
+    <row r="26" spans="1:6" ht="38.4" hidden="1">
       <c r="B26" s="43" t="s">
         <v>1365</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="34.5" hidden="1">
+    <row r="27" spans="1:6" ht="38.4" hidden="1">
       <c r="B27" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="34.5" hidden="1">
+    <row r="28" spans="1:6" ht="38.4" hidden="1">
       <c r="B28" s="43" t="s">
         <v>1366</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="51.75" hidden="1">
+    <row r="29" spans="1:6" ht="38.4" hidden="1">
       <c r="B29" s="43" t="s">
         <v>1367</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17.25" hidden="1">
+    <row r="30" spans="1:6" ht="19.2" hidden="1">
       <c r="B30" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="51.75" hidden="1">
+    <row r="31" spans="1:6" ht="57.6" hidden="1">
       <c r="B31" s="43" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34.5" hidden="1">
+    <row r="32" spans="1:6" ht="38.4" hidden="1">
       <c r="B32" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="51.75" hidden="1">
+    <row r="33" spans="1:5" ht="57.6" hidden="1">
       <c r="B33" s="43" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="34.5" hidden="1">
+    <row r="34" spans="1:5" ht="38.4" hidden="1">
       <c r="B34" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="51.75" hidden="1">
+    <row r="35" spans="1:5" ht="57.6" hidden="1">
       <c r="B35" s="43" t="s">
         <v>1370</v>
       </c>
@@ -17715,7 +17716,7 @@
       <c r="A36" s="44" t="s">
         <v>1371</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="66" t="s">
         <v>1635</v>
       </c>
       <c r="C36" t="s">
@@ -17729,82 +17730,82 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17.25" hidden="1">
+    <row r="37" spans="1:5" ht="19.2" hidden="1">
       <c r="B37" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="51.75" hidden="1">
+    <row r="38" spans="1:5" ht="57.6" hidden="1">
       <c r="B38" s="43" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="51.75" hidden="1">
+    <row r="39" spans="1:5" ht="57.6" hidden="1">
       <c r="B39" s="43" t="s">
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="69" hidden="1">
+    <row r="40" spans="1:5" ht="76.8" hidden="1">
       <c r="B40" s="43" t="s">
         <v>1374</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.25" hidden="1">
+    <row r="41" spans="1:5" ht="19.2" hidden="1">
       <c r="B41" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="51.75" hidden="1">
+    <row r="42" spans="1:5" ht="38.4" hidden="1">
       <c r="B42" s="43" t="s">
         <v>1375</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="34.5" hidden="1">
+    <row r="43" spans="1:5" ht="38.4" hidden="1">
       <c r="B43" s="43" t="s">
         <v>1376</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="34.5" hidden="1">
+    <row r="44" spans="1:5" ht="38.4" hidden="1">
       <c r="B44" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="51.75" hidden="1">
+    <row r="45" spans="1:5" ht="57.6" hidden="1">
       <c r="B45" s="43" t="s">
         <v>1377</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="34.5" hidden="1">
+    <row r="46" spans="1:5" ht="38.4" hidden="1">
       <c r="B46" s="43" t="s">
         <v>1378</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17.25" hidden="1">
+    <row r="47" spans="1:5" ht="19.2" hidden="1">
       <c r="B47" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="34.5" hidden="1">
+    <row r="48" spans="1:5" ht="38.4" hidden="1">
       <c r="B48" s="43" t="s">
         <v>1379</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="34.5" hidden="1">
+    <row r="49" spans="1:5" ht="38.4" hidden="1">
       <c r="B49" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="51.75" hidden="1">
+    <row r="50" spans="1:5" ht="57.6" hidden="1">
       <c r="B50" s="43" t="s">
         <v>1380</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="34.5" hidden="1">
+    <row r="51" spans="1:5" ht="38.4" hidden="1">
       <c r="B51" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="51.75" hidden="1">
+    <row r="52" spans="1:5" ht="57.6" hidden="1">
       <c r="B52" s="43" t="s">
         <v>1381</v>
       </c>
@@ -17813,8 +17814,8 @@
       <c r="A53" s="44" t="s">
         <v>1382</v>
       </c>
-      <c r="B53" t="s">
-        <v>1501</v>
+      <c r="B53" s="20" t="s">
+        <v>1635</v>
       </c>
       <c r="C53" t="s">
         <v>1500</v>
@@ -17827,82 +17828,82 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="17.25" hidden="1">
+    <row r="54" spans="1:5" ht="19.2" hidden="1">
       <c r="B54" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="51.75" hidden="1">
+    <row r="55" spans="1:5" ht="38.4" hidden="1">
       <c r="B55" s="43" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="51.75" hidden="1">
+    <row r="56" spans="1:5" ht="57.6" hidden="1">
       <c r="B56" s="43" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="51.75" hidden="1">
+    <row r="57" spans="1:5" ht="57.6" hidden="1">
       <c r="B57" s="43" t="s">
         <v>1385</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="17.25" hidden="1">
+    <row r="58" spans="1:5" ht="19.2" hidden="1">
       <c r="B58" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="34.5" hidden="1">
+    <row r="59" spans="1:5" ht="38.4" hidden="1">
       <c r="B59" s="43" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="34.5" hidden="1">
+    <row r="60" spans="1:5" ht="38.4" hidden="1">
       <c r="B60" s="43" t="s">
         <v>1387</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="34.5" hidden="1">
+    <row r="61" spans="1:5" ht="38.4" hidden="1">
       <c r="B61" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="51.75" hidden="1">
+    <row r="62" spans="1:5" ht="57.6" hidden="1">
       <c r="B62" s="43" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="34.5" hidden="1">
+    <row r="63" spans="1:5" ht="19.2" hidden="1">
       <c r="B63" s="43" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="17.25" hidden="1">
+    <row r="64" spans="1:5" ht="19.2" hidden="1">
       <c r="B64" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="34.5" hidden="1">
+    <row r="65" spans="1:5" ht="38.4" hidden="1">
       <c r="B65" s="43" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="34.5" hidden="1">
+    <row r="66" spans="1:5" ht="38.4" hidden="1">
       <c r="B66" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="34.5" hidden="1">
+    <row r="67" spans="1:5" ht="38.4" hidden="1">
       <c r="B67" s="43" t="s">
         <v>1391</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="34.5" hidden="1">
+    <row r="68" spans="1:5" ht="38.4" hidden="1">
       <c r="B68" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="69" hidden="1">
+    <row r="69" spans="1:5" ht="57.6" hidden="1">
       <c r="B69" s="43" t="s">
         <v>1392</v>
       </c>
@@ -17925,82 +17926,82 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="17.25" hidden="1">
+    <row r="71" spans="1:5" ht="19.2" hidden="1">
       <c r="B71" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="69" hidden="1">
+    <row r="72" spans="1:5" ht="76.8" hidden="1">
       <c r="B72" s="43" t="s">
         <v>1394</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="51.75" hidden="1">
+    <row r="73" spans="1:5" ht="57.6" hidden="1">
       <c r="B73" s="43" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="51.75" hidden="1">
+    <row r="74" spans="1:5" ht="57.6" hidden="1">
       <c r="B74" s="43" t="s">
         <v>1396</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="17.25" hidden="1">
+    <row r="75" spans="1:5" ht="19.2" hidden="1">
       <c r="B75" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="34.5" hidden="1">
+    <row r="76" spans="1:5" ht="38.4" hidden="1">
       <c r="B76" s="43" t="s">
         <v>1397</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="34.5" hidden="1">
+    <row r="77" spans="1:5" ht="38.4" hidden="1">
       <c r="B77" s="43" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="34.5" hidden="1">
+    <row r="78" spans="1:5" ht="38.4" hidden="1">
       <c r="B78" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="51.75" hidden="1">
+    <row r="79" spans="1:5" ht="57.6" hidden="1">
       <c r="B79" s="43" t="s">
         <v>1399</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="34.5" hidden="1">
+    <row r="80" spans="1:5" ht="38.4" hidden="1">
       <c r="B80" s="43" t="s">
         <v>1400</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="17.25" hidden="1">
+    <row r="81" spans="1:5" ht="19.2" hidden="1">
       <c r="B81" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="51.75" hidden="1">
+    <row r="82" spans="1:5" ht="38.4" hidden="1">
       <c r="B82" s="43" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="34.5" hidden="1">
+    <row r="83" spans="1:5" ht="38.4" hidden="1">
       <c r="B83" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="51.75" hidden="1">
+    <row r="84" spans="1:5" ht="57.6" hidden="1">
       <c r="B84" s="43" t="s">
         <v>1402</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="34.5" hidden="1">
+    <row r="85" spans="1:5" ht="38.4" hidden="1">
       <c r="B85" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="69" hidden="1">
+    <row r="86" spans="1:5" ht="76.8" hidden="1">
       <c r="B86" s="43" t="s">
         <v>1403</v>
       </c>
@@ -18023,77 +18024,77 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="17.25" hidden="1">
+    <row r="88" spans="1:5" ht="19.2" hidden="1">
       <c r="B88" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="69" hidden="1">
+    <row r="89" spans="1:5" ht="76.8" hidden="1">
       <c r="B89" s="43" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="51.75" hidden="1">
+    <row r="90" spans="1:5" ht="38.4" hidden="1">
       <c r="B90" s="43" t="s">
         <v>1406</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="34.5" hidden="1">
+    <row r="91" spans="1:5" ht="38.4" hidden="1">
       <c r="B91" s="43" t="s">
         <v>1407</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="17.25" hidden="1">
+    <row r="92" spans="1:5" ht="19.2" hidden="1">
       <c r="B92" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="34.5" hidden="1">
+    <row r="93" spans="1:5" ht="38.4" hidden="1">
       <c r="B93" s="43" t="s">
         <v>1408</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="17.25" hidden="1">
+    <row r="94" spans="1:5" ht="19.2" hidden="1">
       <c r="B94" s="43" t="s">
         <v>1409</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="34.5" hidden="1">
+    <row r="95" spans="1:5" ht="38.4" hidden="1">
       <c r="B95" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="51.75" hidden="1">
+    <row r="96" spans="1:5" ht="57.6" hidden="1">
       <c r="B96" s="43" t="s">
         <v>1410</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="17.25" hidden="1">
+    <row r="97" spans="1:5" ht="19.2" hidden="1">
       <c r="B97" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="34.5" hidden="1">
+    <row r="98" spans="1:5" ht="38.4" hidden="1">
       <c r="B98" s="43" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="34.5" hidden="1">
+    <row r="99" spans="1:5" ht="38.4" hidden="1">
       <c r="B99" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="34.5" hidden="1">
+    <row r="100" spans="1:5" ht="38.4" hidden="1">
       <c r="B100" s="43" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="34.5" hidden="1">
+    <row r="101" spans="1:5" ht="38.4" hidden="1">
       <c r="B101" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="34.5" hidden="1">
+    <row r="102" spans="1:5" ht="38.4" hidden="1">
       <c r="B102" s="43" t="s">
         <v>1413</v>
       </c>
@@ -18116,77 +18117,77 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17.25" hidden="1">
+    <row r="104" spans="1:5" ht="19.2" hidden="1">
       <c r="B104" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="51.75" hidden="1">
+    <row r="105" spans="1:5" ht="57.6" hidden="1">
       <c r="B105" s="43" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="34.5" hidden="1">
+    <row r="106" spans="1:5" ht="38.4" hidden="1">
       <c r="B106" s="43" t="s">
         <v>1416</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="51.75" hidden="1">
+    <row r="107" spans="1:5" ht="57.6" hidden="1">
       <c r="B107" s="43" t="s">
         <v>1417</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17.25" hidden="1">
+    <row r="108" spans="1:5" ht="19.2" hidden="1">
       <c r="B108" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="34.5" hidden="1">
+    <row r="109" spans="1:5" ht="38.4" hidden="1">
       <c r="B109" s="43" t="s">
         <v>1418</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="34.5" hidden="1">
+    <row r="110" spans="1:5" ht="19.2" hidden="1">
       <c r="B110" s="43" t="s">
         <v>1419</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="34.5" hidden="1">
+    <row r="111" spans="1:5" ht="38.4" hidden="1">
       <c r="B111" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="51.75" hidden="1">
+    <row r="112" spans="1:5" ht="57.6" hidden="1">
       <c r="B112" s="43" t="s">
         <v>1420</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17.25" hidden="1">
+    <row r="113" spans="1:5" ht="19.2" hidden="1">
       <c r="B113" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="34.5" hidden="1">
+    <row r="114" spans="1:5" ht="38.4" hidden="1">
       <c r="B114" s="43" t="s">
         <v>1421</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="34.5" hidden="1">
+    <row r="115" spans="1:5" ht="38.4" hidden="1">
       <c r="B115" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="51.75" hidden="1">
+    <row r="116" spans="1:5" ht="57.6" hidden="1">
       <c r="B116" s="43" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="34.5" hidden="1">
+    <row r="117" spans="1:5" ht="38.4" hidden="1">
       <c r="B117" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="51.75" hidden="1">
+    <row r="118" spans="1:5" ht="57.6" hidden="1">
       <c r="B118" s="43" t="s">
         <v>1423</v>
       </c>
@@ -18209,82 +18210,82 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17.25" hidden="1">
+    <row r="120" spans="1:5" ht="19.2" hidden="1">
       <c r="B120" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="51.75" hidden="1">
+    <row r="121" spans="1:5" ht="57.6" hidden="1">
       <c r="B121" s="43" t="s">
         <v>1425</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="51.75" hidden="1">
+    <row r="122" spans="1:5" ht="57.6" hidden="1">
       <c r="B122" s="43" t="s">
         <v>1426</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="34.5" hidden="1">
+    <row r="123" spans="1:5" ht="38.4" hidden="1">
       <c r="B123" s="43" t="s">
         <v>1427</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17.25" hidden="1">
+    <row r="124" spans="1:5" ht="19.2" hidden="1">
       <c r="B124" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="34.5" hidden="1">
+    <row r="125" spans="1:5" ht="38.4" hidden="1">
       <c r="B125" s="43" t="s">
         <v>1428</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="34.5" hidden="1">
+    <row r="126" spans="1:5" ht="38.4" hidden="1">
       <c r="B126" s="43" t="s">
         <v>1429</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="34.5" hidden="1">
+    <row r="127" spans="1:5" ht="38.4" hidden="1">
       <c r="B127" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="34.5" hidden="1">
+    <row r="128" spans="1:5" ht="38.4" hidden="1">
       <c r="B128" s="43" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="51.75" hidden="1">
+    <row r="129" spans="1:5" ht="57.6" hidden="1">
       <c r="B129" s="43" t="s">
         <v>1431</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17.25" hidden="1">
+    <row r="130" spans="1:5" ht="19.2" hidden="1">
       <c r="B130" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="34.5" hidden="1">
+    <row r="131" spans="1:5" ht="38.4" hidden="1">
       <c r="B131" s="43" t="s">
         <v>1432</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="34.5" hidden="1">
+    <row r="132" spans="1:5" ht="38.4" hidden="1">
       <c r="B132" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="51.75" hidden="1">
+    <row r="133" spans="1:5" ht="57.6" hidden="1">
       <c r="B133" s="43" t="s">
         <v>1433</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="34.5" hidden="1">
+    <row r="134" spans="1:5" ht="38.4" hidden="1">
       <c r="B134" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="69" hidden="1">
+    <row r="135" spans="1:5" ht="76.8" hidden="1">
       <c r="B135" s="43" t="s">
         <v>1434</v>
       </c>
@@ -18307,77 +18308,77 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17.25" hidden="1">
+    <row r="137" spans="1:5" ht="19.2" hidden="1">
       <c r="B137" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="51.75" hidden="1">
+    <row r="138" spans="1:5" ht="57.6" hidden="1">
       <c r="B138" s="43" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="51.75" hidden="1">
+    <row r="139" spans="1:5" ht="57.6" hidden="1">
       <c r="B139" s="43" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="51.75" hidden="1">
+    <row r="140" spans="1:5" ht="57.6" hidden="1">
       <c r="B140" s="43" t="s">
         <v>1438</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17.25" hidden="1">
+    <row r="141" spans="1:5" ht="19.2" hidden="1">
       <c r="B141" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="51.75" hidden="1">
+    <row r="142" spans="1:5" ht="38.4" hidden="1">
       <c r="B142" s="43" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="34.5" hidden="1">
+    <row r="143" spans="1:5" ht="38.4" hidden="1">
       <c r="B143" s="43" t="s">
         <v>1440</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="34.5" hidden="1">
+    <row r="144" spans="1:5" ht="38.4" hidden="1">
       <c r="B144" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="69" hidden="1">
+    <row r="145" spans="1:5" ht="76.8" hidden="1">
       <c r="B145" s="43" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17.25" hidden="1">
+    <row r="146" spans="1:5" ht="19.2" hidden="1">
       <c r="B146" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="51.75" hidden="1">
+    <row r="147" spans="1:5" ht="57.6" hidden="1">
       <c r="B147" s="43" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="34.5" hidden="1">
+    <row r="148" spans="1:5" ht="38.4" hidden="1">
       <c r="B148" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="51.75" hidden="1">
+    <row r="149" spans="1:5" ht="57.6" hidden="1">
       <c r="B149" s="43" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="34.5" hidden="1">
+    <row r="150" spans="1:5" ht="38.4" hidden="1">
       <c r="B150" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="34.5" hidden="1">
+    <row r="151" spans="1:5" ht="38.4" hidden="1">
       <c r="B151" s="43" t="s">
         <v>1444</v>
       </c>
@@ -18400,82 +18401,82 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17.25" hidden="1">
+    <row r="153" spans="1:5" ht="19.2" hidden="1">
       <c r="B153" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="51.75" hidden="1">
+    <row r="154" spans="1:5" ht="57.6" hidden="1">
       <c r="B154" s="43" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="51.75" hidden="1">
+    <row r="155" spans="1:5" ht="57.6" hidden="1">
       <c r="B155" s="43" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="51.75" hidden="1">
+    <row r="156" spans="1:5" ht="57.6" hidden="1">
       <c r="B156" s="43" t="s">
         <v>1448</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17.25" hidden="1">
+    <row r="157" spans="1:5" ht="19.2" hidden="1">
       <c r="B157" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="34.5" hidden="1">
+    <row r="158" spans="1:5" ht="38.4" hidden="1">
       <c r="B158" s="43" t="s">
         <v>1449</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="34.5" hidden="1">
+    <row r="159" spans="1:5" ht="38.4" hidden="1">
       <c r="B159" s="43" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="34.5" hidden="1">
+    <row r="160" spans="1:5" ht="38.4" hidden="1">
       <c r="B160" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="34.5" hidden="1">
+    <row r="161" spans="1:5" ht="38.4" hidden="1">
       <c r="B161" s="43" t="s">
         <v>1451</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="34.5" hidden="1">
+    <row r="162" spans="1:5" ht="38.4" hidden="1">
       <c r="B162" s="43" t="s">
         <v>1452</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17.25" hidden="1">
+    <row r="163" spans="1:5" ht="19.2" hidden="1">
       <c r="B163" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="51.75" hidden="1">
+    <row r="164" spans="1:5" ht="57.6" hidden="1">
       <c r="B164" s="43" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="34.5" hidden="1">
+    <row r="165" spans="1:5" ht="38.4" hidden="1">
       <c r="B165" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="34.5" hidden="1">
+    <row r="166" spans="1:5" ht="38.4" hidden="1">
       <c r="B166" s="43" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="34.5" hidden="1">
+    <row r="167" spans="1:5" ht="38.4" hidden="1">
       <c r="B167" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="51.75" hidden="1">
+    <row r="168" spans="1:5" ht="57.6" hidden="1">
       <c r="B168" s="43" t="s">
         <v>1455</v>
       </c>
@@ -18498,77 +18499,77 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17.25" hidden="1">
+    <row r="170" spans="1:5" ht="19.2" hidden="1">
       <c r="B170" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="34.5" hidden="1">
+    <row r="171" spans="1:5" ht="38.4" hidden="1">
       <c r="B171" s="43" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="51.75" hidden="1">
+    <row r="172" spans="1:5" ht="57.6" hidden="1">
       <c r="B172" s="43" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="34.5" hidden="1">
+    <row r="173" spans="1:5" ht="38.4" hidden="1">
       <c r="B173" s="43" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17.25" hidden="1">
+    <row r="174" spans="1:5" ht="19.2" hidden="1">
       <c r="B174" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="34.5" hidden="1">
+    <row r="175" spans="1:5" ht="38.4" hidden="1">
       <c r="B175" s="43" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="34.5" hidden="1">
+    <row r="176" spans="1:5" ht="38.4" hidden="1">
       <c r="B176" s="43" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="34.5" hidden="1">
+    <row r="177" spans="1:5" ht="38.4" hidden="1">
       <c r="B177" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="51.75" hidden="1">
+    <row r="178" spans="1:5" ht="57.6" hidden="1">
       <c r="B178" s="43" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17.25" hidden="1">
+    <row r="179" spans="1:5" ht="19.2" hidden="1">
       <c r="B179" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="34.5" hidden="1">
+    <row r="180" spans="1:5" ht="38.4" hidden="1">
       <c r="B180" s="43" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="34.5" hidden="1">
+    <row r="181" spans="1:5" ht="38.4" hidden="1">
       <c r="B181" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="51.75" hidden="1">
+    <row r="182" spans="1:5" ht="38.4" hidden="1">
       <c r="B182" s="43" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="34.5" hidden="1">
+    <row r="183" spans="1:5" ht="38.4" hidden="1">
       <c r="B183" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="34.5" hidden="1">
+    <row r="184" spans="1:5" ht="38.4" hidden="1">
       <c r="B184" s="43" t="s">
         <v>1465</v>
       </c>
@@ -18591,77 +18592,77 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17.25" hidden="1">
+    <row r="186" spans="1:5" ht="19.2" hidden="1">
       <c r="B186" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="34.5" hidden="1">
+    <row r="187" spans="1:5" ht="38.4" hidden="1">
       <c r="B187" s="43" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="51.75" hidden="1">
+    <row r="188" spans="1:5" ht="57.6" hidden="1">
       <c r="B188" s="43" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="51.75" hidden="1">
+    <row r="189" spans="1:5" ht="57.6" hidden="1">
       <c r="B189" s="43" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17.25" hidden="1">
+    <row r="190" spans="1:5" ht="19.2" hidden="1">
       <c r="B190" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="34.5" hidden="1">
+    <row r="191" spans="1:5" ht="38.4" hidden="1">
       <c r="B191" s="43" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="34.5" hidden="1">
+    <row r="192" spans="1:5" ht="38.4" hidden="1">
       <c r="B192" s="43" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="34.5" hidden="1">
+    <row r="193" spans="1:5" ht="38.4" hidden="1">
       <c r="B193" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="69" hidden="1">
+    <row r="194" spans="1:5" ht="76.8" hidden="1">
       <c r="B194" s="43" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17.25" hidden="1">
+    <row r="195" spans="1:5" ht="19.2" hidden="1">
       <c r="B195" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="34.5" hidden="1">
+    <row r="196" spans="1:5" ht="38.4" hidden="1">
       <c r="B196" s="43" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="34.5" hidden="1">
+    <row r="197" spans="1:5" ht="38.4" hidden="1">
       <c r="B197" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="51.75" hidden="1">
+    <row r="198" spans="1:5" ht="57.6" hidden="1">
       <c r="B198" s="43" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="34.5" hidden="1">
+    <row r="199" spans="1:5" ht="38.4" hidden="1">
       <c r="B199" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="51.75" hidden="1">
+    <row r="200" spans="1:5" ht="57.6" hidden="1">
       <c r="B200" s="43" t="s">
         <v>1475</v>
       </c>
@@ -18684,77 +18685,77 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17.25" hidden="1">
+    <row r="202" spans="1:5" ht="19.2" hidden="1">
       <c r="B202" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="51.75" hidden="1">
+    <row r="203" spans="1:5" ht="57.6" hidden="1">
       <c r="B203" s="43" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="51.75" hidden="1">
+    <row r="204" spans="1:5" ht="57.6" hidden="1">
       <c r="B204" s="43" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="51.75" hidden="1">
+    <row r="205" spans="1:5" ht="57.6" hidden="1">
       <c r="B205" s="43" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17.25" hidden="1">
+    <row r="206" spans="1:5" ht="19.2" hidden="1">
       <c r="B206" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="34.5" hidden="1">
+    <row r="207" spans="1:5" ht="38.4" hidden="1">
       <c r="B207" s="43" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="51.75" hidden="1">
+    <row r="208" spans="1:5" ht="57.6" hidden="1">
       <c r="B208" s="43" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="34.5" hidden="1">
+    <row r="209" spans="1:5" ht="38.4" hidden="1">
       <c r="B209" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="51.75" hidden="1">
+    <row r="210" spans="1:5" ht="57.6" hidden="1">
       <c r="B210" s="43" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17.25" hidden="1">
+    <row r="211" spans="1:5" ht="19.2" hidden="1">
       <c r="B211" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="34.5" hidden="1">
+    <row r="212" spans="1:5" ht="38.4" hidden="1">
       <c r="B212" s="43" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="34.5" hidden="1">
+    <row r="213" spans="1:5" ht="38.4" hidden="1">
       <c r="B213" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="51.75" hidden="1">
+    <row r="214" spans="1:5" ht="57.6" hidden="1">
       <c r="B214" s="43" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="34.5" hidden="1">
+    <row r="215" spans="1:5" ht="38.4" hidden="1">
       <c r="B215" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="51.75" hidden="1">
+    <row r="216" spans="1:5" ht="57.6" hidden="1">
       <c r="B216" s="43" t="s">
         <v>1485</v>
       </c>
@@ -18777,92 +18778,92 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17.25" hidden="1">
+    <row r="218" spans="1:5" ht="19.2" hidden="1">
       <c r="B218" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="51.75" hidden="1">
+    <row r="219" spans="1:5" ht="57.6" hidden="1">
       <c r="B219" s="43" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="51.75" hidden="1">
+    <row r="220" spans="1:5" ht="57.6" hidden="1">
       <c r="B220" s="43" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="34.5" hidden="1">
+    <row r="221" spans="1:5" ht="38.4" hidden="1">
       <c r="B221" s="43" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="86.25" hidden="1">
+    <row r="222" spans="1:5" ht="76.8" hidden="1">
       <c r="B222" s="43" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="51.75" hidden="1">
+    <row r="223" spans="1:5" ht="57.6" hidden="1">
       <c r="B223" s="43" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17.25" hidden="1">
+    <row r="224" spans="1:5" ht="19.2" hidden="1">
       <c r="B224" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="225" spans="2:2" ht="34.5" hidden="1">
+    <row r="225" spans="2:2" ht="38.4" hidden="1">
       <c r="B225" s="43" t="s">
         <v>1492</v>
       </c>
     </row>
-    <row r="226" spans="2:2" ht="34.5" hidden="1">
+    <row r="226" spans="2:2" ht="38.4" hidden="1">
       <c r="B226" s="43" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="227" spans="2:2" ht="34.5" hidden="1">
+    <row r="227" spans="2:2" ht="38.4" hidden="1">
       <c r="B227" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="228" spans="2:2" ht="51.75" hidden="1">
+    <row r="228" spans="2:2" ht="57.6" hidden="1">
       <c r="B228" s="43" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="229" spans="2:2" ht="34.5" hidden="1">
+    <row r="229" spans="2:2" ht="38.4" hidden="1">
       <c r="B229" s="43" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="230" spans="2:2" ht="17.25" hidden="1">
+    <row r="230" spans="2:2" ht="19.2" hidden="1">
       <c r="B230" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="231" spans="2:2" ht="34.5" hidden="1">
+    <row r="231" spans="2:2" ht="38.4" hidden="1">
       <c r="B231" s="43" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="232" spans="2:2" ht="34.5" hidden="1">
+    <row r="232" spans="2:2" ht="38.4" hidden="1">
       <c r="B232" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="233" spans="2:2" ht="51.75" hidden="1">
+    <row r="233" spans="2:2" ht="57.6" hidden="1">
       <c r="B233" s="43" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="234" spans="2:2" ht="34.5" hidden="1">
+    <row r="234" spans="2:2" ht="38.4" hidden="1">
       <c r="B234" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="235" spans="2:2" ht="51.75" hidden="1">
+    <row r="235" spans="2:2" ht="38.4" hidden="1">
       <c r="B235" s="43" t="s">
         <v>1498</v>
       </c>
@@ -18883,17 +18884,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725EF9E2-7A77-45FF-B8A4-13516A0F9DA0}">
   <dimension ref="A4:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="155.85546875" customWidth="1"/>
+    <col min="1" max="1" width="155.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:1" ht="409.5">
+    <row r="4" spans="1:1" ht="409.6">
       <c r="A4" s="14" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="409.5">
+    <row r="7" spans="1:1" ht="409.6">
       <c r="A7" s="46" t="s">
         <v>1514</v>
       </c>
@@ -18906,12 +18907,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB3911-F8E7-4083-974C-8215A8CA05BB}">
   <dimension ref="A4:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="112.7109375" customWidth="1"/>
+    <col min="2" max="2" width="112.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:2" ht="255">
+    <row r="4" spans="1:2" ht="244.8">
       <c r="A4" t="s">
         <v>400</v>
       </c>
@@ -18919,7 +18920,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="409.5">
+    <row r="10" spans="1:2" ht="409.6">
       <c r="A10" t="s">
         <v>401</v>
       </c>
@@ -18935,22 +18936,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
   <dimension ref="A1:Q404"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5703125" customWidth="1"/>
-    <col min="7" max="8" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="39.5703125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="39.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5546875" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1">
+    <row r="1" spans="1:11" ht="16.2" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>760</v>
       </c>
@@ -18981,7 +18982,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="31.5" thickBot="1">
+    <row r="2" spans="1:11" ht="31.2" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -19012,7 +19013,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="31.5" thickBot="1">
+    <row r="3" spans="1:11" ht="31.2" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>119</v>
       </c>
@@ -19040,7 +19041,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="31.5" thickBot="1">
+    <row r="4" spans="1:11" ht="31.2" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -19068,7 +19069,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="46.5" thickBot="1">
+    <row r="5" spans="1:11" ht="46.2" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -19096,7 +19097,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="31.5" thickBot="1">
+    <row r="6" spans="1:11" ht="31.2" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>119</v>
       </c>
@@ -19124,7 +19125,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="31.5" thickBot="1">
+    <row r="7" spans="1:11" ht="31.2" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -19152,7 +19153,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="31.5" thickBot="1">
+    <row r="8" spans="1:11" ht="31.2" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
@@ -19180,7 +19181,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="31.5" thickBot="1">
+    <row r="9" spans="1:11" ht="31.2" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -19208,7 +19209,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="31.5" thickBot="1">
+    <row r="10" spans="1:11" ht="31.2" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>119</v>
       </c>
@@ -19236,7 +19237,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.5" thickBot="1">
+    <row r="11" spans="1:11" ht="31.2" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
@@ -19264,7 +19265,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="31.5" thickBot="1">
+    <row r="12" spans="1:11" ht="31.2" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>119</v>
       </c>
@@ -19292,7 +19293,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="31.5" thickBot="1">
+    <row r="13" spans="1:11" ht="31.2" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>119</v>
       </c>
@@ -19320,7 +19321,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="31.5" thickBot="1">
+    <row r="14" spans="1:11" ht="31.2" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -19348,7 +19349,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="31.5" thickBot="1">
+    <row r="15" spans="1:11" ht="31.2" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
@@ -19376,7 +19377,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="31.5" thickBot="1">
+    <row r="16" spans="1:11" ht="31.2" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>119</v>
       </c>
@@ -19404,7 +19405,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="31.5" thickBot="1">
+    <row r="17" spans="1:17" ht="31.2" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
@@ -19432,7 +19433,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="46.5" thickBot="1">
+    <row r="18" spans="1:17" ht="31.2" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
@@ -19460,7 +19461,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="31.5" thickBot="1">
+    <row r="19" spans="1:17" ht="31.2" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>119</v>
       </c>
@@ -19488,7 +19489,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="31.5" thickBot="1">
+    <row r="20" spans="1:17" ht="31.2" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -19516,7 +19517,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="31.5" thickBot="1">
+    <row r="21" spans="1:17" ht="31.2" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>119</v>
       </c>
@@ -19544,7 +19545,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="31.5" thickBot="1">
+    <row r="22" spans="1:17" ht="31.2" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>119</v>
       </c>
@@ -19572,7 +19573,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="31.5" thickBot="1">
+    <row r="23" spans="1:17" ht="31.2" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -19600,7 +19601,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="31.5" thickBot="1">
+    <row r="24" spans="1:17" ht="31.2" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -19635,7 +19636,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="31.5" thickBot="1">
+    <row r="25" spans="1:17" ht="31.2" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>120</v>
       </c>
@@ -19670,7 +19671,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="31.5" thickBot="1">
+    <row r="26" spans="1:17" ht="31.2" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>120</v>
       </c>
@@ -19705,7 +19706,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="31.5" thickBot="1">
+    <row r="27" spans="1:17" ht="31.2" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>120</v>
       </c>
@@ -19740,7 +19741,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="31.5" thickBot="1">
+    <row r="28" spans="1:17" ht="31.2" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>120</v>
       </c>
@@ -19775,7 +19776,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="31.5" thickBot="1">
+    <row r="29" spans="1:17" ht="31.2" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>120</v>
       </c>
@@ -19810,7 +19811,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="31.5" thickBot="1">
+    <row r="30" spans="1:17" ht="31.2" thickBot="1">
       <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
@@ -19845,7 +19846,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="31.5" thickBot="1">
+    <row r="31" spans="1:17" ht="31.2" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
@@ -19880,7 +19881,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="31.5" thickBot="1">
+    <row r="32" spans="1:17" ht="31.2" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
@@ -19915,7 +19916,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="31.5" thickBot="1">
+    <row r="33" spans="1:17" ht="31.2" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>120</v>
       </c>
@@ -19950,7 +19951,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="31.5" thickBot="1">
+    <row r="34" spans="1:17" ht="31.2" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -19985,7 +19986,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="31.5" thickBot="1">
+    <row r="35" spans="1:17" ht="31.2" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>120</v>
       </c>
@@ -20020,7 +20021,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="31.5" thickBot="1">
+    <row r="36" spans="1:17" ht="31.2" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -20055,7 +20056,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="31.5" thickBot="1">
+    <row r="37" spans="1:17" ht="31.2" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>120</v>
       </c>
@@ -20090,7 +20091,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="31.5" thickBot="1">
+    <row r="38" spans="1:17" ht="31.2" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>120</v>
       </c>
@@ -20125,7 +20126,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="31.5" thickBot="1">
+    <row r="39" spans="1:17" ht="31.2" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
@@ -20160,7 +20161,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="31.5" thickBot="1">
+    <row r="40" spans="1:17" ht="31.2" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>120</v>
       </c>
@@ -20195,7 +20196,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="31.5" thickBot="1">
+    <row r="41" spans="1:17" ht="31.2" thickBot="1">
       <c r="A41" s="6" t="s">
         <v>121</v>
       </c>
@@ -20227,7 +20228,7 @@
         <v>TS-UC-SEC-MCP-003test_001_query_under_5s_allowed</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="31.5" thickBot="1">
+    <row r="42" spans="1:17" ht="31.2" thickBot="1">
       <c r="A42" s="6" t="s">
         <v>121</v>
       </c>
@@ -20259,7 +20260,7 @@
         <v>TS-UC-SEC-MCP-003test_002_query_at_5s_allowed</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="31.5" thickBot="1">
+    <row r="43" spans="1:17" ht="31.2" thickBot="1">
       <c r="A43" s="6" t="s">
         <v>121</v>
       </c>
@@ -20291,7 +20292,7 @@
         <v>TS-UC-SEC-MCP-003test_003_query_over_5s_timeout_cancelled</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="31.5" thickBot="1">
+    <row r="44" spans="1:17" ht="31.2" thickBot="1">
       <c r="A44" s="6" t="s">
         <v>121</v>
       </c>
@@ -20323,7 +20324,7 @@
         <v>TS-UC-SEC-MCP-003test_004_query_result_under_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="31.5" thickBot="1">
+    <row r="45" spans="1:17" ht="31.2" thickBot="1">
       <c r="A45" s="6" t="s">
         <v>121</v>
       </c>
@@ -20355,7 +20356,7 @@
         <v>TS-UC-SEC-MCP-003test_005_query_result_at_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="31.5" thickBot="1">
+    <row r="46" spans="1:17" ht="31.2" thickBot="1">
       <c r="A46" s="6" t="s">
         <v>121</v>
       </c>
@@ -20387,7 +20388,7 @@
         <v>TS-UC-SEC-MCP-003test_006_query_result_over_1000_rows_truncated</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="31.5" thickBot="1">
+    <row r="47" spans="1:17" ht="31.2" thickBot="1">
       <c r="A47" s="6" t="s">
         <v>121</v>
       </c>
@@ -20419,7 +20420,7 @@
         <v>TS-UC-SEC-MCP-003test_007_query_result_truncated_flag_set</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="31.5" thickBot="1">
+    <row r="48" spans="1:17" ht="31.2" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>121</v>
       </c>
@@ -20451,7 +20452,7 @@
         <v>TS-UC-SEC-MCP-003test_008_timeout_returns_partial_results</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="31.5" thickBot="1">
+    <row r="49" spans="1:11" ht="31.2" thickBot="1">
       <c r="A49" s="6" t="s">
         <v>121</v>
       </c>
@@ -20483,7 +20484,7 @@
         <v>TS-UC-SEC-MCP-003test_009_timeout_audit_log_created</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="31.5" thickBot="1">
+    <row r="50" spans="1:11" ht="31.2" thickBot="1">
       <c r="A50" s="6" t="s">
         <v>121</v>
       </c>
@@ -20515,7 +20516,7 @@
         <v>TS-UC-SEC-MCP-003test_010_row_limit_audit_log_created</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="31.5" thickBot="1">
+    <row r="51" spans="1:11" ht="31.2" thickBot="1">
       <c r="A51" s="6" t="s">
         <v>121</v>
       </c>
@@ -20547,7 +20548,7 @@
         <v>TS-UC-SEC-MCP-003test_011_combined_timeout_and_row_limit</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="31.5" thickBot="1">
+    <row r="52" spans="1:11" ht="31.2" thickBot="1">
       <c r="A52" s="6" t="s">
         <v>121</v>
       </c>
@@ -20579,7 +20580,7 @@
         <v>TS-UC-SEC-MCP-003test_012_query_limit_config_per_tenant</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="31.5" thickBot="1">
+    <row r="53" spans="1:11" ht="31.2" thickBot="1">
       <c r="A53" s="6" t="s">
         <v>121</v>
       </c>
@@ -20611,7 +20612,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_001_exactly_1000_rows</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="31.5" thickBot="1">
+    <row r="54" spans="1:11" ht="31.2" thickBot="1">
       <c r="A54" s="6" t="s">
         <v>121</v>
       </c>
@@ -20643,7 +20644,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_002_empty_result_set</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="31.5" thickBot="1">
+    <row r="55" spans="1:11" ht="31.2" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>121</v>
       </c>
@@ -20675,7 +20676,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_003_streaming_query_timeout</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="31.5" thickBot="1">
+    <row r="56" spans="1:11" ht="31.2" thickBot="1">
       <c r="A56" s="6" t="s">
         <v>123</v>
       </c>
@@ -20707,7 +20708,7 @@
         <v>TS-UC-SEC-ANO-001test_001_detect_dni_valid_12345678Z</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="31.5" thickBot="1">
+    <row r="57" spans="1:11" ht="31.2" thickBot="1">
       <c r="A57" s="6" t="s">
         <v>123</v>
       </c>
@@ -20739,7 +20740,7 @@
         <v>TS-UC-SEC-ANO-001test_002_detect_dni_valid_87654321X</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="31.5" thickBot="1">
+    <row r="58" spans="1:11" ht="31.2" thickBot="1">
       <c r="A58" s="6" t="s">
         <v>123</v>
       </c>
@@ -20771,7 +20772,7 @@
         <v>TS-UC-SEC-ANO-001test_003_detect_dni_invalid_length_9_digits</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="31.5" thickBot="1">
+    <row r="59" spans="1:11" ht="31.2" thickBot="1">
       <c r="A59" s="6" t="s">
         <v>123</v>
       </c>
@@ -20803,7 +20804,7 @@
         <v>TS-UC-SEC-ANO-001test_004_detect_dni_invalid_length_7_digits</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="31.5" thickBot="1">
+    <row r="60" spans="1:11" ht="31.2" thickBot="1">
       <c r="A60" s="6" t="s">
         <v>123</v>
       </c>
@@ -20835,7 +20836,7 @@
         <v>TS-UC-SEC-ANO-001test_005_detect_dni_invalid_letter_checksum</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="31.5" thickBot="1">
+    <row r="61" spans="1:11" ht="31.2" thickBot="1">
       <c r="A61" s="6" t="s">
         <v>123</v>
       </c>
@@ -20867,7 +20868,7 @@
         <v>TS-UC-SEC-ANO-001test_006_detect_multiple_dnis_in_text</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="31.5" thickBot="1">
+    <row r="62" spans="1:11" ht="31.2" thickBot="1">
       <c r="A62" s="6" t="s">
         <v>123</v>
       </c>
@@ -20899,7 +20900,7 @@
         <v>TS-UC-SEC-ANO-001test_007_detect_email_simple</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="31.5" thickBot="1">
+    <row r="63" spans="1:11" ht="31.2" thickBot="1">
       <c r="A63" s="6" t="s">
         <v>123</v>
       </c>
@@ -20931,7 +20932,7 @@
         <v>TS-UC-SEC-ANO-001test_008_detect_email_with_subdomain</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="31.5" thickBot="1">
+    <row r="64" spans="1:11" ht="31.2" thickBot="1">
       <c r="A64" s="6" t="s">
         <v>123</v>
       </c>
@@ -20963,7 +20964,7 @@
         <v>TS-UC-SEC-ANO-001test_009_detect_email_with_plus_sign</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="31.5" thickBot="1">
+    <row r="65" spans="1:11" ht="31.2" thickBot="1">
       <c r="A65" s="6" t="s">
         <v>123</v>
       </c>
@@ -20995,7 +20996,7 @@
         <v>TS-UC-SEC-ANO-001test_010_detect_email_invalid_no_at</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="31.5" thickBot="1">
+    <row r="66" spans="1:11" ht="31.2" thickBot="1">
       <c r="A66" s="6" t="s">
         <v>123</v>
       </c>
@@ -21027,7 +21028,7 @@
         <v>TS-UC-SEC-ANO-001test_011_detect_multiple_emails_in_text</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="31.5" thickBot="1">
+    <row r="67" spans="1:11" ht="31.2" thickBot="1">
       <c r="A67" s="6" t="s">
         <v>123</v>
       </c>
@@ -21059,7 +21060,7 @@
         <v>TS-UC-SEC-ANO-001test_012_detect_phone_mobile_612345678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="31.5" thickBot="1">
+    <row r="68" spans="1:11" ht="31.2" thickBot="1">
       <c r="A68" s="6" t="s">
         <v>123</v>
       </c>
@@ -21091,7 +21092,7 @@
         <v>TS-UC-SEC-ANO-001test_013_detect_phone_mobile_with_prefix_34</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="31.5" thickBot="1">
+    <row r="69" spans="1:11" ht="31.2" thickBot="1">
       <c r="A69" s="6" t="s">
         <v>123</v>
       </c>
@@ -21123,7 +21124,7 @@
         <v>TS-UC-SEC-ANO-001test_014_detect_phone_landline_912345678</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="31.5" thickBot="1">
+    <row r="70" spans="1:11" ht="31.2" thickBot="1">
       <c r="A70" s="6" t="s">
         <v>123</v>
       </c>
@@ -21155,7 +21156,7 @@
         <v>TS-UC-SEC-ANO-001test_015_detect_phone_invalid_short</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="31.5" thickBot="1">
+    <row r="71" spans="1:11" ht="31.2" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>123</v>
       </c>
@@ -21187,7 +21188,7 @@
         <v>TS-UC-SEC-ANO-001test_016_detect_multiple_phones_in_text</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="31.5" thickBot="1">
+    <row r="72" spans="1:11" ht="31.2" thickBot="1">
       <c r="A72" s="6" t="s">
         <v>123</v>
       </c>
@@ -21219,7 +21220,7 @@
         <v>TS-UC-SEC-ANO-001test_017_detect_iban_spain_valid</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="31.5" thickBot="1">
+    <row r="73" spans="1:11" ht="31.2" thickBot="1">
       <c r="A73" s="6" t="s">
         <v>123</v>
       </c>
@@ -21251,7 +21252,7 @@
         <v>TS-UC-SEC-ANO-001test_018_detect_iban_germany_valid</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="31.5" thickBot="1">
+    <row r="74" spans="1:11" ht="31.2" thickBot="1">
       <c r="A74" s="6" t="s">
         <v>123</v>
       </c>
@@ -21283,7 +21284,7 @@
         <v>TS-UC-SEC-ANO-001test_019_detect_iban_invalid_checksum</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="31.5" thickBot="1">
+    <row r="75" spans="1:11" ht="31.2" thickBot="1">
       <c r="A75" s="6" t="s">
         <v>123</v>
       </c>
@@ -21315,7 +21316,7 @@
         <v>TS-UC-SEC-ANO-001test_020_detect_iban_invalid_length</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="31.5" thickBot="1">
+    <row r="76" spans="1:11" ht="31.2" thickBot="1">
       <c r="A76" s="6" t="s">
         <v>123</v>
       </c>
@@ -21347,7 +21348,7 @@
         <v>TS-UC-SEC-ANO-001test_021_detect_all_pii_types_in_document</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="31.5" thickBot="1">
+    <row r="77" spans="1:11" ht="31.2" thickBot="1">
       <c r="A77" s="6" t="s">
         <v>123</v>
       </c>
@@ -21379,7 +21380,7 @@
         <v>TS-UC-SEC-ANO-001test_022_detect_no_pii_clean_document</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="31.5" thickBot="1">
+    <row r="78" spans="1:11" ht="31.2" thickBot="1">
       <c r="A78" s="6" t="s">
         <v>123</v>
       </c>
@@ -21411,7 +21412,7 @@
         <v>TS-UC-SEC-ANO-001test_023_detect_pii_positions_returned</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="31.5" thickBot="1">
+    <row r="79" spans="1:11" ht="31.2" thickBot="1">
       <c r="A79" s="6" t="s">
         <v>123</v>
       </c>
@@ -21443,7 +21444,7 @@
         <v>TS-UC-SEC-ANO-001test_024_detect_pii_counts_by_type</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="31.5" thickBot="1">
+    <row r="80" spans="1:11" ht="31.2" thickBot="1">
       <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
@@ -21475,7 +21476,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_001_pii_in_different_languages</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="31.5" thickBot="1">
+    <row r="81" spans="1:11" ht="31.2" thickBot="1">
       <c r="A81" s="6" t="s">
         <v>123</v>
       </c>
@@ -21507,7 +21508,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_002_pii_with_unicode_characters</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="31.5" thickBot="1">
+    <row r="82" spans="1:11" ht="31.2" thickBot="1">
       <c r="A82" s="6" t="s">
         <v>123</v>
       </c>
@@ -21530,7 +21531,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_003_pii_in_html_escaped_text</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="31.5" thickBot="1">
+    <row r="83" spans="1:11" ht="31.2" thickBot="1">
       <c r="A83" s="6" t="s">
         <v>124</v>
       </c>
@@ -21559,7 +21560,7 @@
         <v>TS-UC-SEC-ANO-002test_001_redact_dni_to_redacted</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="31.5" thickBot="1">
+    <row r="84" spans="1:11" ht="31.2" thickBot="1">
       <c r="A84" s="6" t="s">
         <v>124</v>
       </c>
@@ -21588,7 +21589,7 @@
         <v>TS-UC-SEC-ANO-002test_002_redact_email_to_redacted</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="31.5" thickBot="1">
+    <row r="85" spans="1:11" ht="31.2" thickBot="1">
       <c r="A85" s="6" t="s">
         <v>124</v>
       </c>
@@ -21617,7 +21618,7 @@
         <v>TS-UC-SEC-ANO-002test_003_redact_phone_to_redacted</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="31.5" thickBot="1">
+    <row r="86" spans="1:11" ht="31.2" thickBot="1">
       <c r="A86" s="6" t="s">
         <v>124</v>
       </c>
@@ -21646,7 +21647,7 @@
         <v>TS-UC-SEC-ANO-002test_004_redact_multiple_pii_all_redacted</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="31.5" thickBot="1">
+    <row r="87" spans="1:11" ht="31.2" thickBot="1">
       <c r="A87" s="6" t="s">
         <v>124</v>
       </c>
@@ -21675,7 +21676,7 @@
         <v>TS-UC-SEC-ANO-002test_005_hash_dni_deterministic</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="31.5" thickBot="1">
+    <row r="88" spans="1:11" ht="31.2" thickBot="1">
       <c r="A88" s="6" t="s">
         <v>124</v>
       </c>
@@ -21704,7 +21705,7 @@
         <v>TS-UC-SEC-ANO-002test_006_hash_same_value_same_hash</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="31.5" thickBot="1">
+    <row r="89" spans="1:11" ht="31.2" thickBot="1">
       <c r="A89" s="6" t="s">
         <v>124</v>
       </c>
@@ -21733,7 +21734,7 @@
         <v>TS-UC-SEC-ANO-002test_007_hash_different_values_different_hash</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="31.5" thickBot="1">
+    <row r="90" spans="1:11" ht="31.2" thickBot="1">
       <c r="A90" s="6" t="s">
         <v>124</v>
       </c>
@@ -21762,7 +21763,7 @@
         <v>TS-UC-SEC-ANO-002test_008_hash_irreversible_validation</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="31.5" thickBot="1">
+    <row r="91" spans="1:11" ht="31.2" thickBot="1">
       <c r="A91" s="6" t="s">
         <v>124</v>
       </c>
@@ -21791,7 +21792,7 @@
         <v>TS-UC-SEC-ANO-002test_009_pseudonymize_name_to_persona_001</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="31.5" thickBot="1">
+    <row r="92" spans="1:11" ht="31.2" thickBot="1">
       <c r="A92" s="6" t="s">
         <v>124</v>
       </c>
@@ -21820,7 +21821,7 @@
         <v>TS-UC-SEC-ANO-002test_010_pseudonymize_consistent_same_name</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="46.5" thickBot="1">
+    <row r="93" spans="1:11" ht="31.2" thickBot="1">
       <c r="A93" s="6" t="s">
         <v>124</v>
       </c>
@@ -21849,7 +21850,7 @@
         <v>TS-UC-SEC-ANO-002test_011_pseudonymize_different_names_different_ids</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="31.5" thickBot="1">
+    <row r="94" spans="1:11" ht="31.2" thickBot="1">
       <c r="A94" s="6" t="s">
         <v>124</v>
       </c>
@@ -21878,7 +21879,7 @@
         <v>TS-UC-SEC-ANO-002test_012_pseudonymize_in_context_preserved</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="31.5" thickBot="1">
+    <row r="95" spans="1:11" ht="31.2" thickBot="1">
       <c r="A95" s="6" t="s">
         <v>124</v>
       </c>
@@ -21907,7 +21908,7 @@
         <v>TS-UC-SEC-ANO-002test_013_strategy_by_pii_type_default</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="31.5" thickBot="1">
+    <row r="96" spans="1:11" ht="31.2" thickBot="1">
       <c r="A96" s="6" t="s">
         <v>124</v>
       </c>
@@ -21936,7 +21937,7 @@
         <v>TS-UC-SEC-ANO-002test_014_strategy_by_tenant_config</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="31.5" thickBot="1">
+    <row r="97" spans="1:11" ht="31.2" thickBot="1">
       <c r="A97" s="6" t="s">
         <v>124</v>
       </c>
@@ -21965,7 +21966,7 @@
         <v>TS-UC-SEC-ANO-002test_015_strategy_mixed_per_type</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="31.5" thickBot="1">
+    <row r="98" spans="1:11" ht="31.2" thickBot="1">
       <c r="A98" s="6" t="s">
         <v>124</v>
       </c>
@@ -21994,7 +21995,7 @@
         <v>TS-UC-SEC-ANO-002test_016_strategy_none_keeps_original</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="31.5" thickBot="1">
+    <row r="99" spans="1:11" ht="31.2" thickBot="1">
       <c r="A99" s="6" t="s">
         <v>124</v>
       </c>
@@ -22023,7 +22024,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_001_nested_pii_in_pii</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="31.5" thickBot="1">
+    <row r="100" spans="1:11" ht="31.2" thickBot="1">
       <c r="A100" s="6" t="s">
         <v>124</v>
       </c>
@@ -22052,7 +22053,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_002_overlapping_pii_positions</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="31.5" thickBot="1">
+    <row r="101" spans="1:11" ht="31.2" thickBot="1">
       <c r="A101" s="6" t="s">
         <v>124</v>
       </c>
@@ -22081,7 +22082,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_003_empty_text_no_error</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16.5" thickBot="1">
+    <row r="102" spans="1:11" ht="16.2" thickBot="1">
       <c r="A102" s="6" t="s">
         <v>125</v>
       </c>
@@ -22110,7 +22111,7 @@
         <v>TS-UC-SEC-ANO-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16.5" thickBot="1">
+    <row r="103" spans="1:11" ht="16.2" thickBot="1">
       <c r="A103" s="6" t="s">
         <v>126</v>
       </c>
@@ -22139,7 +22140,7 @@
         <v>TS-UC-SEC-TNT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16.5" thickBot="1">
+    <row r="104" spans="1:11" ht="16.2" thickBot="1">
       <c r="A104" s="6" t="s">
         <v>127</v>
       </c>
@@ -22165,7 +22166,7 @@
         <v>TS-UC-SEC-JWT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16.5" thickBot="1">
+    <row r="105" spans="1:11" ht="16.2" thickBot="1">
       <c r="A105" s="6" t="s">
         <v>128</v>
       </c>
@@ -22191,7 +22192,7 @@
         <v>TS-UC-SEC-AUD-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="31.5" thickBot="1">
+    <row r="106" spans="1:11" ht="31.2" thickBot="1">
       <c r="A106" s="6" t="s">
         <v>129</v>
       </c>
@@ -22220,7 +22221,7 @@
         <v>TS-UC-SEC-GAM-001test_001_mass_changes_11_in_hour_detected</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="31.5" thickBot="1">
+    <row r="107" spans="1:11" ht="31.2" thickBot="1">
       <c r="A107" s="6" t="s">
         <v>129</v>
       </c>
@@ -22249,7 +22250,7 @@
         <v>TS-UC-SEC-GAM-001test_002_mass_changes_10_in_hour_allowed</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="31.5" thickBot="1">
+    <row r="108" spans="1:11" ht="31.2" thickBot="1">
       <c r="A108" s="6" t="s">
         <v>129</v>
       </c>
@@ -22278,7 +22279,7 @@
         <v>TS-UC-SEC-GAM-001test_003_mass_changes_window_reset</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="31.5" thickBot="1">
+    <row r="109" spans="1:11" ht="31.2" thickBot="1">
       <c r="A109" s="6" t="s">
         <v>129</v>
       </c>
@@ -22307,7 +22308,7 @@
         <v>TS-UC-SEC-GAM-001test_004_resolve_reintroduce_3_times_detected</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="31.5" thickBot="1">
+    <row r="110" spans="1:11" ht="31.2" thickBot="1">
       <c r="A110" s="6" t="s">
         <v>129</v>
       </c>
@@ -22336,7 +22337,7 @@
         <v>TS-UC-SEC-GAM-001test_005_resolve_reintroduce_2_times_allowed</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="31.5" thickBot="1">
+    <row r="111" spans="1:11" ht="31.2" thickBot="1">
       <c r="A111" s="6" t="s">
         <v>129</v>
       </c>
@@ -22365,7 +22366,7 @@
         <v>TS-UC-SEC-GAM-001test_006_resolve_reintroduce_different_hash_allowed</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="31.5" thickBot="1">
+    <row r="112" spans="1:11" ht="31.2" thickBot="1">
       <c r="A112" s="6" t="s">
         <v>129</v>
       </c>
@@ -22394,7 +22395,7 @@
         <v>TS-UC-SEC-GAM-001test_007_high_score_few_docs_detected</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="31.5" thickBot="1">
+    <row r="113" spans="1:11" ht="31.2" thickBot="1">
       <c r="A113" s="6" t="s">
         <v>129</v>
       </c>
@@ -22423,7 +22424,7 @@
         <v>TS-UC-SEC-GAM-001test_008_high_score_many_docs_allowed</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="31.5" thickBot="1">
+    <row r="114" spans="1:11" ht="31.2" thickBot="1">
       <c r="A114" s="6" t="s">
         <v>129</v>
       </c>
@@ -22452,7 +22453,7 @@
         <v>TS-UC-SEC-GAM-001test_009_high_score_threshold_boundary</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="31.5" thickBot="1">
+    <row r="115" spans="1:11" ht="31.2" thickBot="1">
       <c r="A115" s="6" t="s">
         <v>129</v>
       </c>
@@ -22481,7 +22482,7 @@
         <v>TS-UC-SEC-GAM-001test_010_weight_change_25_percent_detected</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="31.5" thickBot="1">
+    <row r="116" spans="1:11" ht="31.2" thickBot="1">
       <c r="A116" s="6" t="s">
         <v>129</v>
       </c>
@@ -22510,7 +22511,7 @@
         <v>TS-UC-SEC-GAM-001test_011_weight_change_15_percent_allowed</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="31.5" thickBot="1">
+    <row r="117" spans="1:11" ht="31.2" thickBot="1">
       <c r="A117" s="6" t="s">
         <v>129</v>
       </c>
@@ -22539,7 +22540,7 @@
         <v>TS-UC-SEC-GAM-001test_012_weight_change_tracking_24h_window</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="31.5" thickBot="1">
+    <row r="118" spans="1:11" ht="31.2" thickBot="1">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -22568,7 +22569,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_001_multiple_violations_combined</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="31.5" thickBot="1">
+    <row r="119" spans="1:11" ht="31.2" thickBot="1">
       <c r="A119" s="6" t="s">
         <v>129</v>
       </c>
@@ -22597,7 +22598,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_002_violation_penalty_application</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="31.5" thickBot="1">
+    <row r="120" spans="1:11" ht="31.2" thickBot="1">
       <c r="A120" s="6" t="s">
         <v>129</v>
       </c>
@@ -22626,7 +22627,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_003_violation_audit_logging</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="31.5" thickBot="1">
+    <row r="121" spans="1:11" ht="31.2" thickBot="1">
       <c r="A121" s="6" t="s">
         <v>130</v>
       </c>
@@ -22658,7 +22659,7 @@
         <v>TS-UD-DOC-CLS-001test_001_clause_creation_with_all_fields</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="31.5" thickBot="1">
+    <row r="122" spans="1:11" ht="31.2" thickBot="1">
       <c r="A122" s="6" t="s">
         <v>130</v>
       </c>
@@ -22687,7 +22688,7 @@
         <v>TS-UD-DOC-CLS-001test_002_clause_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="31.5" thickBot="1">
+    <row r="123" spans="1:11" ht="31.2" thickBot="1">
       <c r="A123" s="6" t="s">
         <v>130</v>
       </c>
@@ -22716,7 +22717,7 @@
         <v>TS-UD-DOC-CLS-001test_003_clause_creation_fails_without_content</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="31.5" thickBot="1">
+    <row r="124" spans="1:11" ht="31.2" thickBot="1">
       <c r="A124" s="6" t="s">
         <v>130</v>
       </c>
@@ -22745,7 +22746,7 @@
         <v>TS-UD-DOC-CLS-001test_004_clause_creation_fails_without_document_id</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="31.5" thickBot="1">
+    <row r="125" spans="1:11" ht="31.2" thickBot="1">
       <c r="A125" s="6" t="s">
         <v>130</v>
       </c>
@@ -22774,7 +22775,7 @@
         <v>TS-UD-DOC-CLS-001test_005_clause_creation_fails_without_tenant_id</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="31.5" thickBot="1">
+    <row r="126" spans="1:11" ht="31.2" thickBot="1">
       <c r="A126" s="6" t="s">
         <v>130</v>
       </c>
@@ -22803,7 +22804,7 @@
         <v>TS-UD-DOC-CLS-001test_006_clause_immutability_after_creation</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="31.5" thickBot="1">
+    <row r="127" spans="1:11" ht="31.2" thickBot="1">
       <c r="A127" s="6" t="s">
         <v>130</v>
       </c>
@@ -22832,7 +22833,7 @@
         <v>TS-UD-DOC-CLS-001test_007_clause_number_format_primera</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="31.5" thickBot="1">
+    <row r="128" spans="1:11" ht="31.2" thickBot="1">
       <c r="A128" s="6" t="s">
         <v>130</v>
       </c>
@@ -22861,7 +22862,7 @@
         <v>TS-UD-DOC-CLS-001test_008_clause_number_format_numeric</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="31.5" thickBot="1">
+    <row r="129" spans="1:11" ht="31.2" thickBot="1">
       <c r="A129" s="6" t="s">
         <v>130</v>
       </c>
@@ -22890,7 +22891,7 @@
         <v>TS-UD-DOC-CLS-001test_009_clause_number_format_decimal</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="31.5" thickBot="1">
+    <row r="130" spans="1:11" ht="31.2" thickBot="1">
       <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
@@ -22919,7 +22920,7 @@
         <v>TS-UD-DOC-CLS-001test_010_clause_number_normalization</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="31.5" thickBot="1">
+    <row r="131" spans="1:11" ht="31.2" thickBot="1">
       <c r="A131" s="6" t="s">
         <v>130</v>
       </c>
@@ -22948,7 +22949,7 @@
         <v>TS-UD-DOC-CLS-001test_011_clause_content_max_length</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="31.5" thickBot="1">
+    <row r="132" spans="1:11" ht="31.2" thickBot="1">
       <c r="A132" s="6" t="s">
         <v>130</v>
       </c>
@@ -22977,7 +22978,7 @@
         <v>TS-UD-DOC-CLS-001test_012_clause_content_empty_rejected</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="31.5" thickBot="1">
+    <row r="133" spans="1:11" ht="31.2" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>130</v>
       </c>
@@ -23006,7 +23007,7 @@
         <v>TS-UD-DOC-CLS-001test_013_clause_document_fk_valid</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="31.5" thickBot="1">
+    <row r="134" spans="1:11" ht="31.2" thickBot="1">
       <c r="A134" s="6" t="s">
         <v>130</v>
       </c>
@@ -23035,7 +23036,7 @@
         <v>TS-UD-DOC-CLS-001test_014_clause_document_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="31.5" thickBot="1">
+    <row r="135" spans="1:11" ht="31.2" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>130</v>
       </c>
@@ -23064,7 +23065,7 @@
         <v>TS-UD-DOC-CLS-001test_015_clause_tenant_fk_valid</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="31.5" thickBot="1">
+    <row r="136" spans="1:11" ht="31.2" thickBot="1">
       <c r="A136" s="6" t="s">
         <v>130</v>
       </c>
@@ -23093,7 +23094,7 @@
         <v>TS-UD-DOC-CLS-001test_016_clause_tenant_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="31.5" thickBot="1">
+    <row r="137" spans="1:11" ht="31.2" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>130</v>
       </c>
@@ -23122,7 +23123,7 @@
         <v>TS-UD-DOC-CLS-001test_017_clause_on_delete_restrict_document</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="31.5" thickBot="1">
+    <row r="138" spans="1:11" ht="31.2" thickBot="1">
       <c r="A138" s="6" t="s">
         <v>130</v>
       </c>
@@ -23151,7 +23152,7 @@
         <v>TS-UD-DOC-CLS-001test_018_clause_on_delete_restrict_tenant</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="31.5" thickBot="1">
+    <row r="139" spans="1:11" ht="31.2" thickBot="1">
       <c r="A139" s="6" t="s">
         <v>130</v>
       </c>
@@ -23180,7 +23181,7 @@
         <v>TS-UD-DOC-CLS-001test_019_clause_embedding_vector_size</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="31.5" thickBot="1">
+    <row r="140" spans="1:11" ht="31.2" thickBot="1">
       <c r="A140" s="6" t="s">
         <v>130</v>
       </c>
@@ -23209,7 +23210,7 @@
         <v>TS-UD-DOC-CLS-001test_020_clause_embedding_generation</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="31.5" thickBot="1">
+    <row r="141" spans="1:11" ht="31.2" thickBot="1">
       <c r="A141" s="6" t="s">
         <v>130</v>
       </c>
@@ -23238,7 +23239,7 @@
         <v>TS-UD-DOC-CLS-001test_021_clause_embedding_null_allowed</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="31.5" thickBot="1">
+    <row r="142" spans="1:11" ht="31.2" thickBot="1">
       <c r="A142" s="6" t="s">
         <v>130</v>
       </c>
@@ -23267,7 +23268,7 @@
         <v>TS-UD-DOC-CLS-001test_022_clause_embedding_update</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="16.5" thickBot="1">
+    <row r="143" spans="1:11" ht="16.2" thickBot="1">
       <c r="A143" s="6" t="s">
         <v>131</v>
       </c>
@@ -23296,7 +23297,7 @@
         <v>TS-UD-DOC-CLS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="16.5" thickBot="1">
+    <row r="144" spans="1:11" ht="16.2" thickBot="1">
       <c r="A144" s="6" t="s">
         <v>132</v>
       </c>
@@ -23322,7 +23323,7 @@
         <v>TS-UD-DOC-CLS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="31.5" thickBot="1">
+    <row r="145" spans="1:11" ht="31.2" thickBot="1">
       <c r="A145" s="6" t="s">
         <v>133</v>
       </c>
@@ -23351,7 +23352,7 @@
         <v>TS-UD-DOC-ENT-001test_001_date_dd_mm_yyyy_slash</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="31.5" thickBot="1">
+    <row r="146" spans="1:11" ht="31.2" thickBot="1">
       <c r="A146" s="6" t="s">
         <v>133</v>
       </c>
@@ -23380,7 +23381,7 @@
         <v>TS-UD-DOC-ENT-001test_002_date_yyyy_mm_dd_dash</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="31.5" thickBot="1">
+    <row r="147" spans="1:11" ht="31.2" thickBot="1">
       <c r="A147" s="6" t="s">
         <v>133</v>
       </c>
@@ -23409,7 +23410,7 @@
         <v>TS-UD-DOC-ENT-001test_003_date_dd_month_yyyy_spanish</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="31.5" thickBot="1">
+    <row r="148" spans="1:11" ht="31.2" thickBot="1">
       <c r="A148" s="6" t="s">
         <v>133</v>
       </c>
@@ -23438,7 +23439,7 @@
         <v>TS-UD-DOC-ENT-001test_004_date_month_dd_yyyy_english</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="31.5" thickBot="1">
+    <row r="149" spans="1:11" ht="31.2" thickBot="1">
       <c r="A149" s="6" t="s">
         <v>133</v>
       </c>
@@ -23467,7 +23468,7 @@
         <v>TS-UD-DOC-ENT-001test_005_date_relative_30_days</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="31.5" thickBot="1">
+    <row r="150" spans="1:11" ht="31.2" thickBot="1">
       <c r="A150" s="6" t="s">
         <v>133</v>
       </c>
@@ -23496,7 +23497,7 @@
         <v>TS-UD-DOC-ENT-001test_006_date_relative_3_months</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="31.5" thickBot="1">
+    <row r="151" spans="1:11" ht="31.2" thickBot="1">
       <c r="A151" s="6" t="s">
         <v>133</v>
       </c>
@@ -23525,7 +23526,7 @@
         <v>TS-UD-DOC-ENT-001test_007_date_relative_1_year</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="31.5" thickBot="1">
+    <row r="152" spans="1:11" ht="31.2" thickBot="1">
       <c r="A152" s="6" t="s">
         <v>133</v>
       </c>
@@ -23554,7 +23555,7 @@
         <v>TS-UD-DOC-ENT-001test_008_date_relative_from_date</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="31.5" thickBot="1">
+    <row r="153" spans="1:11" ht="31.2" thickBot="1">
       <c r="A153" s="6" t="s">
         <v>133</v>
       </c>
@@ -23583,7 +23584,7 @@
         <v>TS-UD-DOC-ENT-001test_009_date_context_entrega</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="31.5" thickBot="1">
+    <row r="154" spans="1:11" ht="31.2" thickBot="1">
       <c r="A154" s="6" t="s">
         <v>133</v>
       </c>
@@ -23612,7 +23613,7 @@
         <v>TS-UD-DOC-ENT-001test_010_date_context_firma</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="31.5" thickBot="1">
+    <row r="155" spans="1:11" ht="31.2" thickBot="1">
       <c r="A155" s="6" t="s">
         <v>133</v>
       </c>
@@ -23641,7 +23642,7 @@
         <v>TS-UD-DOC-ENT-001test_011_date_context_inicio</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="16.5" thickBot="1">
+    <row r="156" spans="1:11" ht="16.2" thickBot="1">
       <c r="A156" s="6" t="s">
         <v>133</v>
       </c>
@@ -23670,7 +23671,7 @@
         <v>TS-UD-DOC-ENT-001test_012_date_context_fin</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="31.5" thickBot="1">
+    <row r="157" spans="1:11" ht="31.2" thickBot="1">
       <c r="A157" s="6" t="s">
         <v>133</v>
       </c>
@@ -23699,7 +23700,7 @@
         <v>TS-UD-DOC-ENT-001test_013_multiple_dates_extraction</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="31.5" thickBot="1">
+    <row r="158" spans="1:11" ht="31.2" thickBot="1">
       <c r="A158" s="6" t="s">
         <v>133</v>
       </c>
@@ -23728,7 +23729,7 @@
         <v>TS-UD-DOC-ENT-001test_014_multiple_dates_ordering</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="31.5" thickBot="1">
+    <row r="159" spans="1:11" ht="31.2" thickBot="1">
       <c r="A159" s="6" t="s">
         <v>133</v>
       </c>
@@ -23757,7 +23758,7 @@
         <v>TS-UD-DOC-ENT-001test_015_date_range_extraction</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="31.5" thickBot="1">
+    <row r="160" spans="1:11" ht="31.2" thickBot="1">
       <c r="A160" s="6" t="s">
         <v>133</v>
       </c>
@@ -23786,7 +23787,7 @@
         <v>TS-UD-DOC-ENT-001test_016_date_invalid_format_ignored</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="31.5" thickBot="1">
+    <row r="161" spans="1:11" ht="31.2" thickBot="1">
       <c r="A161" s="6" t="s">
         <v>134</v>
       </c>
@@ -23815,7 +23816,7 @@
         <v>TS-UD-DOC-ENT-002test_001_money_eur_symbol_suffix</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="31.5" thickBot="1">
+    <row r="162" spans="1:11" ht="31.2" thickBot="1">
       <c r="A162" s="6" t="s">
         <v>134</v>
       </c>
@@ -23844,7 +23845,7 @@
         <v>TS-UD-DOC-ENT-002test_002_money_eur_symbol_prefix</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="31.5" thickBot="1">
+    <row r="163" spans="1:11" ht="31.2" thickBot="1">
       <c r="A163" s="6" t="s">
         <v>134</v>
       </c>
@@ -23873,7 +23874,7 @@
         <v>TS-UD-DOC-ENT-002test_003_money_eur_word_euros</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="31.5" thickBot="1">
+    <row r="164" spans="1:11" ht="31.2" thickBot="1">
       <c r="A164" s="6" t="s">
         <v>134</v>
       </c>
@@ -23902,7 +23903,7 @@
         <v>TS-UD-DOC-ENT-002test_004_money_eur_thousands_separator</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="31.5" thickBot="1">
+    <row r="165" spans="1:11" ht="31.2" thickBot="1">
       <c r="A165" s="6" t="s">
         <v>134</v>
       </c>
@@ -23931,7 +23932,7 @@
         <v>TS-UD-DOC-ENT-002test_005_money_usd_symbol</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="31.5" thickBot="1">
+    <row r="166" spans="1:11" ht="16.2" thickBot="1">
       <c r="A166" s="6" t="s">
         <v>134</v>
       </c>
@@ -23960,7 +23961,7 @@
         <v>TS-UD-DOC-ENT-002test_006_money_usd_word</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="31.5" thickBot="1">
+    <row r="167" spans="1:11" ht="31.2" thickBot="1">
       <c r="A167" s="6" t="s">
         <v>134</v>
       </c>
@@ -23989,7 +23990,7 @@
         <v>TS-UD-DOC-ENT-002test_007_money_usd_thousands_separator</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="31.5" thickBot="1">
+    <row r="168" spans="1:11" ht="31.2" thickBot="1">
       <c r="A168" s="6" t="s">
         <v>134</v>
       </c>
@@ -24018,7 +24019,7 @@
         <v>TS-UD-DOC-ENT-002test_008_money_context_anticipo</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="31.5" thickBot="1">
+    <row r="169" spans="1:11" ht="31.2" thickBot="1">
       <c r="A169" s="6" t="s">
         <v>134</v>
       </c>
@@ -24047,7 +24048,7 @@
         <v>TS-UD-DOC-ENT-002test_009_money_context_pago_final</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="31.5" thickBot="1">
+    <row r="170" spans="1:11" ht="31.2" thickBot="1">
       <c r="A170" s="6" t="s">
         <v>134</v>
       </c>
@@ -24076,7 +24077,7 @@
         <v>TS-UD-DOC-ENT-002test_010_money_context_penalizacion</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="31.5" thickBot="1">
+    <row r="171" spans="1:11" ht="31.2" thickBot="1">
       <c r="A171" s="6" t="s">
         <v>134</v>
       </c>
@@ -24105,7 +24106,7 @@
         <v>TS-UD-DOC-ENT-002test_011_money_context_total</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="31.5" thickBot="1">
+    <row r="172" spans="1:11" ht="31.2" thickBot="1">
       <c r="A172" s="6" t="s">
         <v>134</v>
       </c>
@@ -24134,7 +24135,7 @@
         <v>TS-UD-DOC-ENT-002test_012_multiple_amounts_extraction</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="31.5" thickBot="1">
+    <row r="173" spans="1:11" ht="31.2" thickBot="1">
       <c r="A173" s="6" t="s">
         <v>134</v>
       </c>
@@ -24163,7 +24164,7 @@
         <v>TS-UD-DOC-ENT-002test_013_money_percentage_extraction</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="31.5" thickBot="1">
+    <row r="174" spans="1:11" ht="31.2" thickBot="1">
       <c r="A174" s="6" t="s">
         <v>134</v>
       </c>
@@ -24192,7 +24193,7 @@
         <v>TS-UD-DOC-ENT-002test_014_money_negative_amount</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="16.5" thickBot="1">
+    <row r="175" spans="1:11" ht="16.2" thickBot="1">
       <c r="A175" s="6" t="s">
         <v>135</v>
       </c>
@@ -24213,7 +24214,7 @@
         <v>TS-UD-DOC-ENT-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="16.5" thickBot="1">
+    <row r="176" spans="1:11" ht="16.2" thickBot="1">
       <c r="A176" s="6" t="s">
         <v>136</v>
       </c>
@@ -24234,7 +24235,7 @@
         <v>TS-UD-DOC-ENT-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="16.5" thickBot="1">
+    <row r="177" spans="1:11" ht="16.2" thickBot="1">
       <c r="A177" s="6" t="s">
         <v>137</v>
       </c>
@@ -24255,7 +24256,7 @@
         <v>TS-UD-DOC-DOC-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="16.5" thickBot="1">
+    <row r="178" spans="1:11" ht="16.2" thickBot="1">
       <c r="A178" s="6" t="s">
         <v>138</v>
       </c>
@@ -24276,7 +24277,7 @@
         <v>TS-UD-DOC-CNF-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="16.5" thickBot="1">
+    <row r="179" spans="1:11" ht="16.2" thickBot="1">
       <c r="A179" s="6" t="s">
         <v>139</v>
       </c>
@@ -24297,7 +24298,7 @@
         <v>TS-UD-COH-CAT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="31.5" thickBot="1">
+    <row r="180" spans="1:11" ht="31.2" thickBot="1">
       <c r="A180" s="6" t="s">
         <v>140</v>
       </c>
@@ -24329,7 +24330,7 @@
         <v>TS-UD-COH-RUL-001test_001_r11_wbs_level4_no_activities_alert</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="31.5" thickBot="1">
+    <row r="181" spans="1:11" ht="31.2" thickBot="1">
       <c r="A181" s="6" t="s">
         <v>140</v>
       </c>
@@ -24358,7 +24359,7 @@
         <v>TS-UD-COH-RUL-001test_002_r11_wbs_level4_with_activities_pass</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="31.5" thickBot="1">
+    <row r="182" spans="1:11" ht="31.2" thickBot="1">
       <c r="A182" s="6" t="s">
         <v>140</v>
       </c>
@@ -24387,7 +24388,7 @@
         <v>TS-UD-COH-RUL-001test_003_r11_wbs_level3_no_activities_ignored</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="31.5" thickBot="1">
+    <row r="183" spans="1:11" ht="31.2" thickBot="1">
       <c r="A183" s="6" t="s">
         <v>140</v>
       </c>
@@ -24416,7 +24417,7 @@
         <v>TS-UD-COH-RUL-001test_004_r11_wbs_level2_no_activities_ignored</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="31.5" thickBot="1">
+    <row r="184" spans="1:11" ht="31.2" thickBot="1">
       <c r="A184" s="6" t="s">
         <v>140</v>
       </c>
@@ -24445,7 +24446,7 @@
         <v>TS-UD-COH-RUL-001test_005_r11_multiple_wbs_level4_violations</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="31.5" thickBot="1">
+    <row r="185" spans="1:11" ht="31.2" thickBot="1">
       <c r="A185" s="6" t="s">
         <v>140</v>
       </c>
@@ -24474,7 +24475,7 @@
         <v>TS-UD-COH-RUL-001test_006_r11_alert_severity_medium</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="31.5" thickBot="1">
+    <row r="186" spans="1:11" ht="31.2" thickBot="1">
       <c r="A186" s="6" t="s">
         <v>140</v>
       </c>
@@ -24503,7 +24504,7 @@
         <v>TS-UD-COH-RUL-001test_007_r12_wbs_no_budget_line_alert</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="31.5" thickBot="1">
+    <row r="187" spans="1:11" ht="31.2" thickBot="1">
       <c r="A187" s="6" t="s">
         <v>140</v>
       </c>
@@ -24532,7 +24533,7 @@
         <v>TS-UD-COH-RUL-001test_008_r12_wbs_with_budget_line_pass</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="31.5" thickBot="1">
+    <row r="188" spans="1:11" ht="31.2" thickBot="1">
       <c r="A188" s="6" t="s">
         <v>140</v>
       </c>
@@ -24561,7 +24562,7 @@
         <v>TS-UD-COH-RUL-001test_009_r12_wbs_budget_zero_warning</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="31.5" thickBot="1">
+    <row r="189" spans="1:11" ht="31.2" thickBot="1">
       <c r="A189" s="6" t="s">
         <v>140</v>
       </c>
@@ -24590,7 +24591,7 @@
         <v>TS-UD-COH-RUL-001test_010_r12_multiple_wbs_violations</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="31.5" thickBot="1">
+    <row r="190" spans="1:11" ht="31.2" thickBot="1">
       <c r="A190" s="6" t="s">
         <v>140</v>
       </c>
@@ -24619,7 +24620,7 @@
         <v>TS-UD-COH-RUL-001test_011_r12_alert_severity_high</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="31.5" thickBot="1">
+    <row r="191" spans="1:11" ht="31.2" thickBot="1">
       <c r="A191" s="6" t="s">
         <v>140</v>
       </c>
@@ -24648,7 +24649,7 @@
         <v>TS-UD-COH-RUL-001test_012_r12_affected_entities_list</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="31.5" thickBot="1">
+    <row r="192" spans="1:11" ht="31.2" thickBot="1">
       <c r="A192" s="6" t="s">
         <v>140</v>
       </c>
@@ -24677,7 +24678,7 @@
         <v>TS-UD-COH-RUL-001test_013_r13_scope_clause_no_wbs_alert</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="31.5" thickBot="1">
+    <row r="193" spans="1:11" ht="31.2" thickBot="1">
       <c r="A193" s="6" t="s">
         <v>140</v>
       </c>
@@ -24706,7 +24707,7 @@
         <v>TS-UD-COH-RUL-001test_014_r13_scope_clause_with_wbs_pass</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="31.5" thickBot="1">
+    <row r="194" spans="1:11" ht="31.2" thickBot="1">
       <c r="A194" s="6" t="s">
         <v>140</v>
       </c>
@@ -24735,7 +24736,7 @@
         <v>TS-UD-COH-RUL-001test_015_r13_partial_coverage_calculation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="31.5" thickBot="1">
+    <row r="195" spans="1:11" ht="31.2" thickBot="1">
       <c r="A195" s="6" t="s">
         <v>140</v>
       </c>
@@ -24764,7 +24765,7 @@
         <v>TS-UD-COH-RUL-001test_016_r13_coverage_percentage_80</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="31.5" thickBot="1">
+    <row r="196" spans="1:11" ht="31.2" thickBot="1">
       <c r="A196" s="6" t="s">
         <v>140</v>
       </c>
@@ -24793,7 +24794,7 @@
         <v>TS-UD-COH-RUL-001test_017_r13_uncovered_clauses_list</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="31.5" thickBot="1">
+    <row r="197" spans="1:11" ht="31.2" thickBot="1">
       <c r="A197" s="6" t="s">
         <v>140</v>
       </c>
@@ -24822,7 +24823,7 @@
         <v>TS-UD-COH-RUL-001test_018_r13_alert_severity_high</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="31.5" thickBot="1">
+    <row r="198" spans="1:11" ht="31.2" thickBot="1">
       <c r="A198" s="6" t="s">
         <v>141</v>
       </c>
@@ -24851,7 +24852,7 @@
         <v>TS-UD-COH-RUL-002test_001_r6_deviation_10_percent_alert</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="31.5" thickBot="1">
+    <row r="199" spans="1:11" ht="31.2" thickBot="1">
       <c r="A199" s="6" t="s">
         <v>141</v>
       </c>
@@ -24880,7 +24881,7 @@
         <v>TS-UD-COH-RUL-002test_002_r6_deviation_5_percent_pass</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="31.5" thickBot="1">
+    <row r="200" spans="1:11" ht="31.2" thickBot="1">
       <c r="A200" s="6" t="s">
         <v>141</v>
       </c>
@@ -24909,7 +24910,7 @@
         <v>TS-UD-COH-RUL-002test_003_r6_deviation_4_9_percent_pass</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="31.5" thickBot="1">
+    <row r="201" spans="1:11" ht="31.2" thickBot="1">
       <c r="A201" s="6" t="s">
         <v>141</v>
       </c>
@@ -24938,7 +24939,7 @@
         <v>TS-UD-COH-RUL-002test_004_r6_over_budget_critical</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="31.5" thickBot="1">
+    <row r="202" spans="1:11" ht="31.2" thickBot="1">
       <c r="A202" s="6" t="s">
         <v>141</v>
       </c>
@@ -24967,7 +24968,7 @@
         <v>TS-UD-COH-RUL-002test_005_r6_under_budget_warning</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="31.5" thickBot="1">
+    <row r="203" spans="1:11" ht="31.2" thickBot="1">
       <c r="A203" s="6" t="s">
         <v>141</v>
       </c>
@@ -24996,7 +24997,7 @@
         <v>TS-UD-COH-RUL-002test_006_r6_exact_match_pass</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="31.5" thickBot="1">
+    <row r="204" spans="1:11" ht="31.2" thickBot="1">
       <c r="A204" s="6" t="s">
         <v>141</v>
       </c>
@@ -25025,7 +25026,7 @@
         <v>TS-UD-COH-RUL-002test_007_r15_bom_no_budget_alert</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="31.5" thickBot="1">
+    <row r="205" spans="1:11" ht="31.2" thickBot="1">
       <c r="A205" s="6" t="s">
         <v>141</v>
       </c>
@@ -25054,7 +25055,7 @@
         <v>TS-UD-COH-RUL-002test_008_r15_bom_with_budget_pass</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="31.5" thickBot="1">
+    <row r="206" spans="1:11" ht="31.2" thickBot="1">
       <c r="A206" s="6" t="s">
         <v>141</v>
       </c>
@@ -25083,7 +25084,7 @@
         <v>TS-UD-COH-RUL-002test_009_r15_bom_client_provided_exception</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="31.5" thickBot="1">
+    <row r="207" spans="1:11" ht="31.2" thickBot="1">
       <c r="A207" s="6" t="s">
         <v>141</v>
       </c>
@@ -25112,7 +25113,7 @@
         <v>TS-UD-COH-RUL-002test_010_r15_multiple_bom_violations</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="31.5" thickBot="1">
+    <row r="208" spans="1:11" ht="31.2" thickBot="1">
       <c r="A208" s="6" t="s">
         <v>141</v>
       </c>
@@ -25141,7 +25142,7 @@
         <v>TS-UD-COH-RUL-002test_011_r15_affected_items_list</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="31.5" thickBot="1">
+    <row r="209" spans="1:11" ht="31.2" thickBot="1">
       <c r="A209" s="6" t="s">
         <v>141</v>
       </c>
@@ -25170,7 +25171,7 @@
         <v>TS-UD-COH-RUL-002test_012_r16_deviation_11_percent_alert</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="31.5" thickBot="1">
+    <row r="210" spans="1:11" ht="31.2" thickBot="1">
       <c r="A210" s="6" t="s">
         <v>141</v>
       </c>
@@ -25199,7 +25200,7 @@
         <v>TS-UD-COH-RUL-002test_013_r16_deviation_10_percent_pass</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="31.5" thickBot="1">
+    <row r="211" spans="1:11" ht="31.2" thickBot="1">
       <c r="A211" s="6" t="s">
         <v>141</v>
       </c>
@@ -25228,7 +25229,7 @@
         <v>TS-UD-COH-RUL-002test_014_r16_over_budget_critical</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="31.5" thickBot="1">
+    <row r="212" spans="1:11" ht="31.2" thickBot="1">
       <c r="A212" s="6" t="s">
         <v>141</v>
       </c>
@@ -25257,7 +25258,7 @@
         <v>TS-UD-COH-RUL-002test_015_r16_under_budget_different_severity</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="31.5" thickBot="1">
+    <row r="213" spans="1:11" ht="31.2" thickBot="1">
       <c r="A213" s="6" t="s">
         <v>141</v>
       </c>
@@ -25286,7 +25287,7 @@
         <v>TS-UD-COH-RUL-002test_016_r16_trend_calculation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="31.5" thickBot="1">
+    <row r="214" spans="1:11" ht="31.2" thickBot="1">
       <c r="A214" s="6" t="s">
         <v>142</v>
       </c>
@@ -25318,7 +25319,7 @@
         <v>TS-UD-COH-RUL-003test_001_r1_dates_mismatch_alert</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="31.5" thickBot="1">
+    <row r="215" spans="1:11" ht="31.2" thickBot="1">
       <c r="A215" s="6" t="s">
         <v>142</v>
       </c>
@@ -25347,7 +25348,7 @@
         <v>TS-UD-COH-RUL-003test_002_r1_dates_match_pass</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="31.5" thickBot="1">
+    <row r="216" spans="1:11" ht="31.2" thickBot="1">
       <c r="A216" s="6" t="s">
         <v>142</v>
       </c>
@@ -25376,7 +25377,7 @@
         <v>TS-UD-COH-RUL-003test_003_r1_schedule_late_critical</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="31.5" thickBot="1">
+    <row r="217" spans="1:11" ht="31.2" thickBot="1">
       <c r="A217" s="6" t="s">
         <v>142</v>
       </c>
@@ -25405,7 +25406,7 @@
         <v>TS-UD-COH-RUL-003test_004_r1_schedule_early_warning</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="31.5" thickBot="1">
+    <row r="218" spans="1:11" ht="31.2" thickBot="1">
       <c r="A218" s="6" t="s">
         <v>142</v>
       </c>
@@ -25434,7 +25435,7 @@
         <v>TS-UD-COH-RUL-003test_005_r1_delta_days_calculation</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="31.5" thickBot="1">
+    <row r="219" spans="1:11" ht="31.2" thickBot="1">
       <c r="A219" s="6" t="s">
         <v>142</v>
       </c>
@@ -25463,7 +25464,7 @@
         <v>TS-UD-COH-RUL-003test_006_r2_milestone_no_activity_alert</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="31.5" thickBot="1">
+    <row r="220" spans="1:11" ht="31.2" thickBot="1">
       <c r="A220" s="6" t="s">
         <v>142</v>
       </c>
@@ -25492,7 +25493,7 @@
         <v>TS-UD-COH-RUL-003test_007_r2_milestone_with_activity_pass</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="31.5" thickBot="1">
+    <row r="221" spans="1:11" ht="31.2" thickBot="1">
       <c r="A221" s="6" t="s">
         <v>142</v>
       </c>
@@ -25521,7 +25522,7 @@
         <v>TS-UD-COH-RUL-003test_008_r2_milestone_date_mismatch_alert</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="31.5" thickBot="1">
+    <row r="222" spans="1:11" ht="31.2" thickBot="1">
       <c r="A222" s="6" t="s">
         <v>142</v>
       </c>
@@ -25550,7 +25551,7 @@
         <v>TS-UD-COH-RUL-003test_009_r2_multiple_milestones_violations</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="31.5" thickBot="1">
+    <row r="223" spans="1:11" ht="31.2" thickBot="1">
       <c r="A223" s="6" t="s">
         <v>142</v>
       </c>
@@ -25579,7 +25580,7 @@
         <v>TS-UD-COH-RUL-003test_010_r2_unlinked_milestones_list</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="31.5" thickBot="1">
+    <row r="224" spans="1:11" ht="31.2" thickBot="1">
       <c r="A224" s="6" t="s">
         <v>142</v>
       </c>
@@ -25608,7 +25609,7 @@
         <v>TS-UD-COH-RUL-003test_011_r5_activity_exceeds_contract_alert</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="31.5" thickBot="1">
+    <row r="225" spans="1:11" ht="31.2" thickBot="1">
       <c r="A225" s="6" t="s">
         <v>142</v>
       </c>
@@ -25637,7 +25638,7 @@
         <v>TS-UD-COH-RUL-003test_012_r5_activity_within_contract_pass</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="31.5" thickBot="1">
+    <row r="226" spans="1:11" ht="31.2" thickBot="1">
       <c r="A226" s="6" t="s">
         <v>142</v>
       </c>
@@ -25666,7 +25667,7 @@
         <v>TS-UD-COH-RUL-003test_013_r5_exceeding_activities_list</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="31.5" thickBot="1">
+    <row r="227" spans="1:11" ht="31.2" thickBot="1">
       <c r="A227" s="6" t="s">
         <v>142</v>
       </c>
@@ -25695,7 +25696,7 @@
         <v>TS-UD-COH-RUL-003test_014_r5_alert_severity_critical</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="31.5" thickBot="1">
+    <row r="228" spans="1:11" ht="31.2" thickBot="1">
       <c r="A228" s="6" t="s">
         <v>142</v>
       </c>
@@ -25724,7 +25725,7 @@
         <v>TS-UD-COH-RUL-003test_015_r14_order_date_passed_critical</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="31.5" thickBot="1">
+    <row r="229" spans="1:11" ht="31.2" thickBot="1">
       <c r="A229" s="6" t="s">
         <v>142</v>
       </c>
@@ -25753,7 +25754,7 @@
         <v>TS-UD-COH-RUL-003test_016_r14_order_date_tight_warning</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="16.5" thickBot="1">
+    <row r="230" spans="1:11" ht="16.2" thickBot="1">
       <c r="A230" s="6" t="s">
         <v>143</v>
       </c>
@@ -25774,7 +25775,7 @@
         <v>TS-UD-COH-RUL-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="16.5" thickBot="1">
+    <row r="231" spans="1:11" ht="16.2" thickBot="1">
       <c r="A231" s="6" t="s">
         <v>144</v>
       </c>
@@ -25795,7 +25796,7 @@
         <v>TS-UD-COH-RUL-005Tests not individually listed</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="16.5" thickBot="1">
+    <row r="232" spans="1:11" ht="16.2" thickBot="1">
       <c r="A232" s="6" t="s">
         <v>145</v>
       </c>
@@ -25816,7 +25817,7 @@
         <v>TS-UD-COH-RUL-006Tests not individually listed</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="31.5" thickBot="1">
+    <row r="233" spans="1:11" ht="31.2" thickBot="1">
       <c r="A233" s="6" t="s">
         <v>146</v>
       </c>
@@ -25848,7 +25849,7 @@
         <v>TS-UD-COH-SCR-001test_001_subscore_no_alerts_100_percent</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="31.5" thickBot="1">
+    <row r="234" spans="1:11" ht="31.2" thickBot="1">
       <c r="A234" s="6" t="s">
         <v>146</v>
       </c>
@@ -25877,7 +25878,7 @@
         <v>TS-UD-COH-SCR-001test_002_subscore_one_alert_penalized</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="31.5" thickBot="1">
+    <row r="235" spans="1:11" ht="31.2" thickBot="1">
       <c r="A235" s="6" t="s">
         <v>146</v>
       </c>
@@ -25906,7 +25907,7 @@
         <v>TS-UD-COH-SCR-001test_003_subscore_multiple_alerts_cumulative</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="31.5" thickBot="1">
+    <row r="236" spans="1:11" ht="31.2" thickBot="1">
       <c r="A236" s="6" t="s">
         <v>146</v>
       </c>
@@ -25935,7 +25936,7 @@
         <v>TS-UD-COH-SCR-001test_004_subscore_severity_low_penalty_5</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="31.5" thickBot="1">
+    <row r="237" spans="1:11" ht="31.2" thickBot="1">
       <c r="A237" s="6" t="s">
         <v>146</v>
       </c>
@@ -25964,7 +25965,7 @@
         <v>TS-UD-COH-SCR-001test_005_subscore_severity_medium_penalty_10</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="31.5" thickBot="1">
+    <row r="238" spans="1:11" ht="31.2" thickBot="1">
       <c r="A238" s="6" t="s">
         <v>146</v>
       </c>
@@ -25993,7 +25994,7 @@
         <v>TS-UD-COH-SCR-001test_006_subscore_severity_high_penalty_20</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="31.5" thickBot="1">
+    <row r="239" spans="1:11" ht="31.2" thickBot="1">
       <c r="A239" s="6" t="s">
         <v>146</v>
       </c>
@@ -26022,7 +26023,7 @@
         <v>TS-UD-COH-SCR-001test_007_subscore_severity_critical_penalty_30</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="31.5" thickBot="1">
+    <row r="240" spans="1:11" ht="31.2" thickBot="1">
       <c r="A240" s="6" t="s">
         <v>146</v>
       </c>
@@ -26051,7 +26052,7 @@
         <v>TS-UD-COH-SCR-001test_008_subscore_scope_calculation</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="31.5" thickBot="1">
+    <row r="241" spans="1:11" ht="31.2" thickBot="1">
       <c r="A241" s="6" t="s">
         <v>146</v>
       </c>
@@ -26080,7 +26081,7 @@
         <v>TS-UD-COH-SCR-001test_009_subscore_budget_calculation</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="31.5" thickBot="1">
+    <row r="242" spans="1:11" ht="31.2" thickBot="1">
       <c r="A242" s="6" t="s">
         <v>146</v>
       </c>
@@ -26109,7 +26110,7 @@
         <v>TS-UD-COH-SCR-001test_010_subscore_quality_calculation</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="31.5" thickBot="1">
+    <row r="243" spans="1:11" ht="31.2" thickBot="1">
       <c r="A243" s="6" t="s">
         <v>146</v>
       </c>
@@ -26138,7 +26139,7 @@
         <v>TS-UD-COH-SCR-001test_011_subscore_technical_calculation</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="31.5" thickBot="1">
+    <row r="244" spans="1:11" ht="31.2" thickBot="1">
       <c r="A244" s="6" t="s">
         <v>146</v>
       </c>
@@ -26167,7 +26168,7 @@
         <v>TS-UD-COH-SCR-001test_012_subscore_legal_calculation</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="31.5" thickBot="1">
+    <row r="245" spans="1:11" ht="31.2" thickBot="1">
       <c r="A245" s="6" t="s">
         <v>146</v>
       </c>
@@ -26196,7 +26197,7 @@
         <v>TS-UD-COH-SCR-001test_013_subscore_time_calculation</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="31.5" thickBot="1">
+    <row r="246" spans="1:11" ht="31.2" thickBot="1">
       <c r="A246" s="6" t="s">
         <v>146</v>
       </c>
@@ -26225,7 +26226,7 @@
         <v>TS-UD-COH-SCR-001test_014_subscore_floor_at_zero</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="31.5" thickBot="1">
+    <row r="247" spans="1:11" ht="31.2" thickBot="1">
       <c r="A247" s="6" t="s">
         <v>147</v>
       </c>
@@ -26254,7 +26255,7 @@
         <v>TS-UD-COH-SCR-002test_001_global_score_formula_verification</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="31.5" thickBot="1">
+    <row r="248" spans="1:11" ht="31.2" thickBot="1">
       <c r="A248" s="6" t="s">
         <v>147</v>
       </c>
@@ -26283,7 +26284,7 @@
         <v>TS-UD-COH-SCR-002test_002_global_score_default_weights</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="31.5" thickBot="1">
+    <row r="249" spans="1:11" ht="31.2" thickBot="1">
       <c r="A249" s="6" t="s">
         <v>147</v>
       </c>
@@ -26312,7 +26313,7 @@
         <v>TS-UD-COH-SCR-002test_003_global_score_all_100_equals_100</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="31.5" thickBot="1">
+    <row r="250" spans="1:11" ht="31.2" thickBot="1">
       <c r="A250" s="6" t="s">
         <v>147</v>
       </c>
@@ -26341,7 +26342,7 @@
         <v>TS-UD-COH-SCR-002test_004_global_score_all_0_equals_0</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="31.5" thickBot="1">
+    <row r="251" spans="1:11" ht="31.2" thickBot="1">
       <c r="A251" s="6" t="s">
         <v>147</v>
       </c>
@@ -26370,7 +26371,7 @@
         <v>TS-UD-COH-SCR-002test_005_global_score_mixed_subscores</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="31.5" thickBot="1">
+    <row r="252" spans="1:11" ht="31.2" thickBot="1">
       <c r="A252" s="6" t="s">
         <v>147</v>
       </c>
@@ -26399,7 +26400,7 @@
         <v>TS-UD-COH-SCR-002test_006_global_score_range_0_to_100</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="31.5" thickBot="1">
+    <row r="253" spans="1:11" ht="31.2" thickBot="1">
       <c r="A253" s="6" t="s">
         <v>147</v>
       </c>
@@ -26428,7 +26429,7 @@
         <v>TS-UD-COH-SCR-002test_007_weights_sum_validation</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="31.5" thickBot="1">
+    <row r="254" spans="1:11" ht="31.2" thickBot="1">
       <c r="A254" s="6" t="s">
         <v>147</v>
       </c>
@@ -26457,7 +26458,7 @@
         <v>TS-UD-COH-SCR-002test_008_weights_normalization_auto</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="31.5" thickBot="1">
+    <row r="255" spans="1:11" ht="31.2" thickBot="1">
       <c r="A255" s="6" t="s">
         <v>147</v>
       </c>
@@ -26486,7 +26487,7 @@
         <v>TS-UD-COH-SCR-002test_009_weights_custom_budget_30</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="31.5" thickBot="1">
+    <row r="256" spans="1:11" ht="31.2" thickBot="1">
       <c r="A256" s="6" t="s">
         <v>147</v>
       </c>
@@ -26515,7 +26516,7 @@
         <v>TS-UD-COH-SCR-002test_010_weights_custom_time_25</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="31.5" thickBot="1">
+    <row r="257" spans="1:11" ht="31.2" thickBot="1">
       <c r="A257" s="6" t="s">
         <v>147</v>
       </c>
@@ -26544,7 +26545,7 @@
         <v>TS-UD-COH-SCR-002test_011_weights_per_project_type</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="31.5" thickBot="1">
+    <row r="258" spans="1:11" ht="31.2" thickBot="1">
       <c r="A258" s="6" t="s">
         <v>147</v>
       </c>
@@ -26573,7 +26574,7 @@
         <v>TS-UD-COH-SCR-002test_012_weights_history_tracking</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="16.5" thickBot="1">
+    <row r="259" spans="1:11" ht="16.2" thickBot="1">
       <c r="A259" s="6" t="s">
         <v>148</v>
       </c>
@@ -26590,7 +26591,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="31.5" thickBot="1">
+    <row r="260" spans="1:11" ht="31.2" thickBot="1">
       <c r="A260" s="6" t="s">
         <v>149</v>
       </c>
@@ -26619,7 +26620,7 @@
         <v>TS-UD-COH-GAM-001test_001_detect_mass_changes_15_in_30min</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="31.5" thickBot="1">
+    <row r="261" spans="1:11" ht="31.2" thickBot="1">
       <c r="A261" s="6" t="s">
         <v>149</v>
       </c>
@@ -26648,7 +26649,7 @@
         <v>TS-UD-COH-GAM-001test_002_no_violation_10_in_60min</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="31.5" thickBot="1">
+    <row r="262" spans="1:11" ht="31.2" thickBot="1">
       <c r="A262" s="6" t="s">
         <v>149</v>
       </c>
@@ -26677,7 +26678,7 @@
         <v>TS-UD-COH-GAM-001test_003_mass_changes_window_sliding</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="31.5" thickBot="1">
+    <row r="263" spans="1:11" ht="31.2" thickBot="1">
       <c r="A263" s="6" t="s">
         <v>149</v>
       </c>
@@ -26706,7 +26707,7 @@
         <v>TS-UD-COH-GAM-001test_004_mass_changes_flag_for_review</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="31.5" thickBot="1">
+    <row r="264" spans="1:11" ht="31.2" thickBot="1">
       <c r="A264" s="6" t="s">
         <v>149</v>
       </c>
@@ -26735,7 +26736,7 @@
         <v>TS-UD-COH-GAM-001test_005_detect_resolve_reintroduce_4_times</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="31.5" thickBot="1">
+    <row r="265" spans="1:11" ht="31.2" thickBot="1">
       <c r="A265" s="6" t="s">
         <v>149</v>
       </c>
@@ -26764,7 +26765,7 @@
         <v>TS-UD-COH-GAM-001test_006_no_violation_2_times</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="31.5" thickBot="1">
+    <row r="266" spans="1:11" ht="31.2" thickBot="1">
       <c r="A266" s="6" t="s">
         <v>149</v>
       </c>
@@ -26793,7 +26794,7 @@
         <v>TS-UD-COH-GAM-001test_007_hash_comparison_same_content</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="31.5" thickBot="1">
+    <row r="267" spans="1:11" ht="31.2" thickBot="1">
       <c r="A267" s="6" t="s">
         <v>149</v>
       </c>
@@ -26822,7 +26823,7 @@
         <v>TS-UD-COH-GAM-001test_008_penalty_minus_5_points</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="31.5" thickBot="1">
+    <row r="268" spans="1:11" ht="31.2" thickBot="1">
       <c r="A268" s="6" t="s">
         <v>149</v>
       </c>
@@ -26851,7 +26852,7 @@
         <v>TS-UD-COH-GAM-001test_009_detect_95_percent_3_docs</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="31.5" thickBot="1">
+    <row r="269" spans="1:11" ht="31.2" thickBot="1">
       <c r="A269" s="6" t="s">
         <v>149</v>
       </c>
@@ -26880,7 +26881,7 @@
         <v>TS-UD-COH-GAM-001test_010_no_violation_95_percent_50_docs</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="31.5" thickBot="1">
+    <row r="270" spans="1:11" ht="31.2" thickBot="1">
       <c r="A270" s="6" t="s">
         <v>149</v>
       </c>
@@ -26909,7 +26910,7 @@
         <v>TS-UD-COH-GAM-001test_011_threshold_90_percent_5_docs</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="31.5" thickBot="1">
+    <row r="271" spans="1:11" ht="31.2" thickBot="1">
       <c r="A271" s="6" t="s">
         <v>149</v>
       </c>
@@ -26938,7 +26939,7 @@
         <v>TS-UD-COH-GAM-001test_012_require_audit_action</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="31.5" thickBot="1">
+    <row r="272" spans="1:11" ht="31.2" thickBot="1">
       <c r="A272" s="6" t="s">
         <v>149</v>
       </c>
@@ -26967,7 +26968,7 @@
         <v>TS-UD-COH-GAM-001test_013_detect_weight_change_25_percent</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="31.5" thickBot="1">
+    <row r="273" spans="1:11" ht="31.2" thickBot="1">
       <c r="A273" s="6" t="s">
         <v>149</v>
       </c>
@@ -26996,7 +26997,7 @@
         <v>TS-UD-COH-GAM-001test_014_no_violation_change_15_percent</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="31.5" thickBot="1">
+    <row r="274" spans="1:11" ht="31.2" thickBot="1">
       <c r="A274" s="6" t="s">
         <v>149</v>
       </c>
@@ -27025,7 +27026,7 @@
         <v>TS-UD-COH-GAM-001test_015_24h_window_tracking</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="31.5" thickBot="1">
+    <row r="275" spans="1:11" ht="31.2" thickBot="1">
       <c r="A275" s="6" t="s">
         <v>149</v>
       </c>
@@ -27054,7 +27055,7 @@
         <v>TS-UD-COH-GAM-001test_016_notify_admin_action</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="16.5" thickBot="1">
+    <row r="276" spans="1:11" ht="16.2" thickBot="1">
       <c r="A276" s="6" t="s">
         <v>150</v>
       </c>
@@ -27075,7 +27076,7 @@
         <v>TS-UD-COH-ALR-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="31.5" thickBot="1">
+    <row r="277" spans="1:11" ht="31.2" thickBot="1">
       <c r="A277" s="6" t="s">
         <v>151</v>
       </c>
@@ -27107,7 +27108,7 @@
         <v>TS-UD-PRJ-WBS-001test_001_wbs_item_creation_all_fields</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="31.5" thickBot="1">
+    <row r="278" spans="1:11" ht="31.2" thickBot="1">
       <c r="A278" s="6" t="s">
         <v>151</v>
       </c>
@@ -27136,7 +27137,7 @@
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="31.5" thickBot="1">
+    <row r="279" spans="1:11" ht="31.2" thickBot="1">
       <c r="A279" s="6" t="s">
         <v>151</v>
       </c>
@@ -27165,7 +27166,7 @@
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="31.5" thickBot="1">
+    <row r="280" spans="1:11" ht="31.2" thickBot="1">
       <c r="A280" s="6" t="s">
         <v>151</v>
       </c>
@@ -27194,7 +27195,7 @@
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="31.5" thickBot="1">
+    <row r="281" spans="1:11" ht="31.2" thickBot="1">
       <c r="A281" s="6" t="s">
         <v>151</v>
       </c>
@@ -27223,7 +27224,7 @@
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="31.5" thickBot="1">
+    <row r="282" spans="1:11" ht="31.2" thickBot="1">
       <c r="A282" s="6" t="s">
         <v>151</v>
       </c>
@@ -27252,7 +27253,7 @@
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="31.5" thickBot="1">
+    <row r="283" spans="1:11" ht="31.2" thickBot="1">
       <c r="A283" s="6" t="s">
         <v>151</v>
       </c>
@@ -27281,7 +27282,7 @@
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="31.5" thickBot="1">
+    <row r="284" spans="1:11" ht="31.2" thickBot="1">
       <c r="A284" s="6" t="s">
         <v>151</v>
       </c>
@@ -27310,7 +27311,7 @@
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="31.5" thickBot="1">
+    <row r="285" spans="1:11" ht="31.2" thickBot="1">
       <c r="A285" s="6" t="s">
         <v>151</v>
       </c>
@@ -27339,7 +27340,7 @@
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="31.5" thickBot="1">
+    <row r="286" spans="1:11" ht="31.2" thickBot="1">
       <c r="A286" s="6" t="s">
         <v>151</v>
       </c>
@@ -27368,7 +27369,7 @@
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="31.5" thickBot="1">
+    <row r="287" spans="1:11" ht="31.2" thickBot="1">
       <c r="A287" s="6" t="s">
         <v>151</v>
       </c>
@@ -27397,7 +27398,7 @@
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="31.5" thickBot="1">
+    <row r="288" spans="1:11" ht="31.2" thickBot="1">
       <c r="A288" s="6" t="s">
         <v>151</v>
       </c>
@@ -27426,7 +27427,7 @@
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="31.5" thickBot="1">
+    <row r="289" spans="1:11" ht="16.2" thickBot="1">
       <c r="A289" s="6" t="s">
         <v>151</v>
       </c>
@@ -27455,7 +27456,7 @@
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="31.5" thickBot="1">
+    <row r="290" spans="1:11" ht="16.2" thickBot="1">
       <c r="A290" s="6" t="s">
         <v>151</v>
       </c>
@@ -27484,7 +27485,7 @@
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="31.5" thickBot="1">
+    <row r="291" spans="1:11" ht="31.2" thickBot="1">
       <c r="A291" s="6" t="s">
         <v>151</v>
       </c>
@@ -27513,7 +27514,7 @@
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="31.5" thickBot="1">
+    <row r="292" spans="1:11" ht="31.2" thickBot="1">
       <c r="A292" s="6" t="s">
         <v>151</v>
       </c>
@@ -27542,7 +27543,7 @@
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="31.5" thickBot="1">
+    <row r="293" spans="1:11" ht="31.2" thickBot="1">
       <c r="A293" s="6" t="s">
         <v>151</v>
       </c>
@@ -27571,7 +27572,7 @@
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="31.5" thickBot="1">
+    <row r="294" spans="1:11" ht="31.2" thickBot="1">
       <c r="A294" s="6" t="s">
         <v>151</v>
       </c>
@@ -27600,7 +27601,7 @@
         <v>TS-UD-PRJ-WBS-001test_018_wbs_level_parent_child_validation</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="16.5" thickBot="1">
+    <row r="295" spans="1:11" ht="16.2" thickBot="1">
       <c r="A295" s="6" t="s">
         <v>152</v>
       </c>
@@ -27621,7 +27622,7 @@
         <v>TS-UD-PRJ-WBS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="16.5" thickBot="1">
+    <row r="296" spans="1:11" ht="16.2" thickBot="1">
       <c r="A296" s="6" t="s">
         <v>153</v>
       </c>
@@ -27642,7 +27643,7 @@
         <v>TS-UD-PRJ-WBS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="16.5" thickBot="1">
+    <row r="297" spans="1:11" ht="16.2" thickBot="1">
       <c r="A297" s="6" t="s">
         <v>154</v>
       </c>
@@ -27663,7 +27664,7 @@
         <v>TS-UD-PRJ-WBS-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="16.5" thickBot="1">
+    <row r="298" spans="1:11" ht="16.2" thickBot="1">
       <c r="A298" s="6" t="s">
         <v>155</v>
       </c>
@@ -27684,7 +27685,7 @@
         <v>TS-UD-PRJ-PRJ-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="16.5" thickBot="1">
+    <row r="299" spans="1:11" ht="16.2" thickBot="1">
       <c r="A299" s="6" t="s">
         <v>156</v>
       </c>
@@ -27705,7 +27706,7 @@
         <v>TS-UD-PRJ-DTO-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="16.5" thickBot="1">
+    <row r="300" spans="1:11" ht="16.2" thickBot="1">
       <c r="A300" s="6" t="s">
         <v>157</v>
       </c>
@@ -27726,7 +27727,7 @@
         <v>TS-UD-PROC-BOM-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="16.5" thickBot="1">
+    <row r="301" spans="1:11" ht="16.2" thickBot="1">
       <c r="A301" s="6" t="s">
         <v>158</v>
       </c>
@@ -27747,7 +27748,7 @@
         <v>TS-UD-PROC-BOM-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="31.5" thickBot="1">
+    <row r="302" spans="1:11" ht="31.2" thickBot="1">
       <c r="A302" s="6" t="s">
         <v>159</v>
       </c>
@@ -27779,7 +27780,7 @@
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="31.5" thickBot="1">
+    <row r="303" spans="1:11" ht="31.2" thickBot="1">
       <c r="A303" s="6" t="s">
         <v>159</v>
       </c>
@@ -27808,7 +27809,7 @@
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="31.5" thickBot="1">
+    <row r="304" spans="1:11" ht="31.2" thickBot="1">
       <c r="A304" s="6" t="s">
         <v>159</v>
       </c>
@@ -27837,7 +27838,7 @@
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="31.5" thickBot="1">
+    <row r="305" spans="1:11" ht="31.2" thickBot="1">
       <c r="A305" s="6" t="s">
         <v>159</v>
       </c>
@@ -27866,7 +27867,7 @@
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="31.5" thickBot="1">
+    <row r="306" spans="1:11" ht="31.2" thickBot="1">
       <c r="A306" s="6" t="s">
         <v>159</v>
       </c>
@@ -27895,7 +27896,7 @@
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="31.5" thickBot="1">
+    <row r="307" spans="1:11" ht="31.2" thickBot="1">
       <c r="A307" s="6" t="s">
         <v>159</v>
       </c>
@@ -27924,7 +27925,7 @@
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="31.5" thickBot="1">
+    <row r="308" spans="1:11" ht="31.2" thickBot="1">
       <c r="A308" s="6" t="s">
         <v>159</v>
       </c>
@@ -27953,7 +27954,7 @@
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="31.5" thickBot="1">
+    <row r="309" spans="1:11" ht="31.2" thickBot="1">
       <c r="A309" s="6" t="s">
         <v>159</v>
       </c>
@@ -27982,7 +27983,7 @@
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="16.5" thickBot="1">
+    <row r="310" spans="1:11" ht="16.2" thickBot="1">
       <c r="A310" s="6" t="s">
         <v>159</v>
       </c>
@@ -28011,7 +28012,7 @@
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="31.5" thickBot="1">
+    <row r="311" spans="1:11" ht="31.2" thickBot="1">
       <c r="A311" s="6" t="s">
         <v>159</v>
       </c>
@@ -28040,7 +28041,7 @@
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="31.5" thickBot="1">
+    <row r="312" spans="1:11" ht="31.2" thickBot="1">
       <c r="A312" s="6" t="s">
         <v>159</v>
       </c>
@@ -28069,7 +28070,7 @@
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="31.5" thickBot="1">
+    <row r="313" spans="1:11" ht="31.2" thickBot="1">
       <c r="A313" s="6" t="s">
         <v>159</v>
       </c>
@@ -28098,7 +28099,7 @@
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="31.5" thickBot="1">
+    <row r="314" spans="1:11" ht="31.2" thickBot="1">
       <c r="A314" s="6" t="s">
         <v>159</v>
       </c>
@@ -28127,7 +28128,7 @@
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="31.5" thickBot="1">
+    <row r="315" spans="1:11" ht="31.2" thickBot="1">
       <c r="A315" s="6" t="s">
         <v>159</v>
       </c>
@@ -28156,7 +28157,7 @@
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="31.5" thickBot="1">
+    <row r="316" spans="1:11" ht="31.2" thickBot="1">
       <c r="A316" s="6" t="s">
         <v>159</v>
       </c>
@@ -28185,7 +28186,7 @@
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="31.5" thickBot="1">
+    <row r="317" spans="1:11" ht="31.2" thickBot="1">
       <c r="A317" s="6" t="s">
         <v>159</v>
       </c>
@@ -28214,7 +28215,7 @@
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="31.5" thickBot="1">
+    <row r="318" spans="1:11" ht="31.2" thickBot="1">
       <c r="A318" s="6" t="s">
         <v>160</v>
       </c>
@@ -28240,7 +28241,7 @@
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="31.5" thickBot="1">
+    <row r="319" spans="1:11" ht="31.2" thickBot="1">
       <c r="A319" s="6" t="s">
         <v>160</v>
       </c>
@@ -28266,7 +28267,7 @@
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="31.5" thickBot="1">
+    <row r="320" spans="1:11" ht="31.2" thickBot="1">
       <c r="A320" s="6" t="s">
         <v>160</v>
       </c>
@@ -28292,7 +28293,7 @@
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="31.5" thickBot="1">
+    <row r="321" spans="1:11" ht="31.2" thickBot="1">
       <c r="A321" s="6" t="s">
         <v>160</v>
       </c>
@@ -28318,7 +28319,7 @@
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="31.5" thickBot="1">
+    <row r="322" spans="1:11" ht="31.2" thickBot="1">
       <c r="A322" s="6" t="s">
         <v>160</v>
       </c>
@@ -28344,7 +28345,7 @@
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="31.5" thickBot="1">
+    <row r="323" spans="1:11" ht="31.2" thickBot="1">
       <c r="A323" s="6" t="s">
         <v>160</v>
       </c>
@@ -28370,7 +28371,7 @@
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="31.5" thickBot="1">
+    <row r="324" spans="1:11" ht="31.2" thickBot="1">
       <c r="A324" s="6" t="s">
         <v>160</v>
       </c>
@@ -28396,7 +28397,7 @@
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="16.5" thickBot="1">
+    <row r="325" spans="1:11" ht="16.2" thickBot="1">
       <c r="A325" s="6" t="s">
         <v>160</v>
       </c>
@@ -28422,7 +28423,7 @@
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="31.5" thickBot="1">
+    <row r="326" spans="1:11" ht="31.2" thickBot="1">
       <c r="A326" s="6" t="s">
         <v>160</v>
       </c>
@@ -28448,7 +28449,7 @@
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="31.5" thickBot="1">
+    <row r="327" spans="1:11" ht="31.2" thickBot="1">
       <c r="A327" s="6" t="s">
         <v>160</v>
       </c>
@@ -28474,7 +28475,7 @@
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="31.5" thickBot="1">
+    <row r="328" spans="1:11" ht="31.2" thickBot="1">
       <c r="A328" s="6" t="s">
         <v>160</v>
       </c>
@@ -28500,7 +28501,7 @@
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="31.5" thickBot="1">
+    <row r="329" spans="1:11" ht="31.2" thickBot="1">
       <c r="A329" s="6" t="s">
         <v>160</v>
       </c>
@@ -28526,7 +28527,7 @@
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="31.5" thickBot="1">
+    <row r="330" spans="1:11" ht="31.2" thickBot="1">
       <c r="A330" s="6" t="s">
         <v>160</v>
       </c>
@@ -28552,7 +28553,7 @@
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="31.5" thickBot="1">
+    <row r="331" spans="1:11" ht="31.2" thickBot="1">
       <c r="A331" s="6" t="s">
         <v>160</v>
       </c>
@@ -28578,7 +28579,7 @@
         <v>TS-UD-PROC-LTM-002test_014_incoterm_impact_on_lead_time</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="16.5" thickBot="1">
+    <row r="332" spans="1:11" ht="16.2" thickBot="1">
       <c r="A332" s="6" t="s">
         <v>161</v>
       </c>
@@ -28595,7 +28596,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="16.5" thickBot="1">
+    <row r="333" spans="1:11" ht="16.2" thickBot="1">
       <c r="A333" s="6" t="s">
         <v>162</v>
       </c>
@@ -28612,7 +28613,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="16.5" thickBot="1">
+    <row r="334" spans="1:11" ht="16.2" thickBot="1">
       <c r="A334" s="6" t="s">
         <v>163</v>
       </c>
@@ -28629,7 +28630,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="16.5" thickBot="1">
+    <row r="335" spans="1:11" ht="16.2" thickBot="1">
       <c r="A335" s="6" t="s">
         <v>164</v>
       </c>
@@ -28646,7 +28647,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="16.5" thickBot="1">
+    <row r="336" spans="1:11" ht="16.2" thickBot="1">
       <c r="A336" s="6" t="s">
         <v>165</v>
       </c>
@@ -28663,7 +28664,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="16.5" thickBot="1">
+    <row r="337" spans="1:10" ht="16.2" thickBot="1">
       <c r="A337" s="6" t="s">
         <v>166</v>
       </c>
@@ -28680,7 +28681,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="16.5" thickBot="1">
+    <row r="338" spans="1:10" ht="16.2" thickBot="1">
       <c r="A338" s="6" t="s">
         <v>167</v>
       </c>
@@ -28696,7 +28697,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="16.5" thickBot="1">
+    <row r="339" spans="1:10" ht="16.2" thickBot="1">
       <c r="A339" s="6" t="s">
         <v>168</v>
       </c>
@@ -28712,7 +28713,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="16.5" thickBot="1">
+    <row r="340" spans="1:10" ht="16.2" thickBot="1">
       <c r="A340" s="6" t="s">
         <v>169</v>
       </c>
@@ -28728,7 +28729,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="16.5" thickBot="1">
+    <row r="341" spans="1:10" ht="16.2" thickBot="1">
       <c r="A341" s="6" t="s">
         <v>170</v>
       </c>
@@ -28744,7 +28745,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="16.5" thickBot="1">
+    <row r="342" spans="1:10" ht="16.2" thickBot="1">
       <c r="A342" s="6" t="s">
         <v>171</v>
       </c>
@@ -28760,7 +28761,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="16.5" thickBot="1">
+    <row r="343" spans="1:10" ht="16.2" thickBot="1">
       <c r="A343" s="6" t="s">
         <v>172</v>
       </c>
@@ -28776,7 +28777,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="16.5" thickBot="1">
+    <row r="344" spans="1:10" ht="16.2" thickBot="1">
       <c r="A344" s="6" t="s">
         <v>173</v>
       </c>
@@ -28792,7 +28793,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="16.5" thickBot="1">
+    <row r="345" spans="1:10" ht="16.2" thickBot="1">
       <c r="A345" s="6" t="s">
         <v>174</v>
       </c>
@@ -28808,7 +28809,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="16.5" thickBot="1">
+    <row r="346" spans="1:10" ht="16.2" thickBot="1">
       <c r="A346" s="6" t="s">
         <v>175</v>
       </c>
@@ -28824,7 +28825,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="31.5" thickBot="1">
+    <row r="347" spans="1:10" ht="16.2" thickBot="1">
       <c r="A347" s="6" t="s">
         <v>176</v>
       </c>
@@ -28840,7 +28841,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="31.5" thickBot="1">
+    <row r="348" spans="1:10" ht="16.2" thickBot="1">
       <c r="A348" s="6" t="s">
         <v>177</v>
       </c>
@@ -28856,7 +28857,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="31.5" thickBot="1">
+    <row r="349" spans="1:10" ht="16.2" thickBot="1">
       <c r="A349" s="6" t="s">
         <v>178</v>
       </c>
@@ -28872,7 +28873,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="31.5" thickBot="1">
+    <row r="350" spans="1:10" ht="16.2" thickBot="1">
       <c r="A350" s="6" t="s">
         <v>179</v>
       </c>
@@ -28888,7 +28889,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="31.5" thickBot="1">
+    <row r="351" spans="1:10" ht="16.2" thickBot="1">
       <c r="A351" s="6" t="s">
         <v>180</v>
       </c>
@@ -28904,7 +28905,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="31.5" thickBot="1">
+    <row r="352" spans="1:10" ht="16.2" thickBot="1">
       <c r="A352" s="31" t="s">
         <v>181</v>
       </c>
@@ -28923,7 +28924,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="31.5" thickBot="1">
+    <row r="353" spans="1:10" ht="16.2" thickBot="1">
       <c r="A353" s="31" t="s">
         <v>182</v>
       </c>
@@ -28942,7 +28943,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="31.5" thickBot="1">
+    <row r="354" spans="1:10" ht="16.2" thickBot="1">
       <c r="A354" s="6" t="s">
         <v>183</v>
       </c>
@@ -28958,7 +28959,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="31.5" thickBot="1">
+    <row r="355" spans="1:10" ht="16.2" thickBot="1">
       <c r="A355" s="6" t="s">
         <v>184</v>
       </c>
@@ -28974,7 +28975,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="31.5" thickBot="1">
+    <row r="356" spans="1:10" ht="16.2" thickBot="1">
       <c r="A356" s="6" t="s">
         <v>185</v>
       </c>
@@ -28990,7 +28991,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="31.5" thickBot="1">
+    <row r="357" spans="1:10" ht="16.2" thickBot="1">
       <c r="A357" s="6" t="s">
         <v>186</v>
       </c>
@@ -29006,7 +29007,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="31.5" thickBot="1">
+    <row r="358" spans="1:10" ht="16.2" thickBot="1">
       <c r="A358" s="6" t="s">
         <v>187</v>
       </c>
@@ -29022,7 +29023,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="31.5" thickBot="1">
+    <row r="359" spans="1:10" ht="16.2" thickBot="1">
       <c r="A359" s="6" t="s">
         <v>188</v>
       </c>
@@ -29038,7 +29039,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="31.5" thickBot="1">
+    <row r="360" spans="1:10" ht="16.2" thickBot="1">
       <c r="A360" s="6" t="s">
         <v>189</v>
       </c>
@@ -29054,7 +29055,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="31.5" thickBot="1">
+    <row r="361" spans="1:10" ht="16.2" thickBot="1">
       <c r="A361" s="6" t="s">
         <v>190</v>
       </c>
@@ -29070,7 +29071,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="16.5" thickBot="1">
+    <row r="362" spans="1:10" ht="16.2" thickBot="1">
       <c r="A362" s="6" t="s">
         <v>191</v>
       </c>
@@ -29086,7 +29087,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="16.5" thickBot="1">
+    <row r="363" spans="1:10" ht="16.2" thickBot="1">
       <c r="A363" s="6" t="s">
         <v>192</v>
       </c>
@@ -29102,7 +29103,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="16.5" thickBot="1">
+    <row r="364" spans="1:10" ht="16.2" thickBot="1">
       <c r="A364" s="6" t="s">
         <v>193</v>
       </c>
@@ -29118,7 +29119,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="16.5" thickBot="1">
+    <row r="365" spans="1:10" ht="16.2" thickBot="1">
       <c r="A365" s="6" t="s">
         <v>194</v>
       </c>
@@ -29134,7 +29135,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="16.5" thickBot="1">
+    <row r="366" spans="1:10" ht="16.2" thickBot="1">
       <c r="A366" s="6" t="s">
         <v>195</v>
       </c>
@@ -29150,7 +29151,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="16.5" thickBot="1">
+    <row r="367" spans="1:10" ht="16.2" thickBot="1">
       <c r="A367" s="6" t="s">
         <v>196</v>
       </c>
@@ -29166,7 +29167,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="16.5" thickBot="1">
+    <row r="368" spans="1:10" ht="16.2" thickBot="1">
       <c r="A368" s="6" t="s">
         <v>197</v>
       </c>
@@ -29182,7 +29183,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="16.5" thickBot="1">
+    <row r="369" spans="1:10" ht="16.2" thickBot="1">
       <c r="A369" s="6" t="s">
         <v>198</v>
       </c>
@@ -29201,7 +29202,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="16.5" thickBot="1">
+    <row r="370" spans="1:10" ht="16.2" thickBot="1">
       <c r="A370" s="6" t="s">
         <v>199</v>
       </c>
@@ -29220,7 +29221,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="16.5" thickBot="1">
+    <row r="371" spans="1:10" ht="16.2" thickBot="1">
       <c r="A371" s="6" t="s">
         <v>200</v>
       </c>
@@ -29236,7 +29237,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="16.5" thickBot="1">
+    <row r="372" spans="1:10" ht="16.2" thickBot="1">
       <c r="A372" s="6" t="s">
         <v>201</v>
       </c>
@@ -29252,7 +29253,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="16.5" thickBot="1">
+    <row r="373" spans="1:10" ht="16.2" thickBot="1">
       <c r="A373" s="6" t="s">
         <v>202</v>
       </c>
@@ -29271,7 +29272,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="31.5" thickBot="1">
+    <row r="374" spans="1:10" ht="16.2" thickBot="1">
       <c r="A374" s="6" t="s">
         <v>203</v>
       </c>
@@ -29287,7 +29288,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="31.5" thickBot="1">
+    <row r="375" spans="1:10" ht="16.2" thickBot="1">
       <c r="A375" s="6" t="s">
         <v>204</v>
       </c>
@@ -29303,7 +29304,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="31.5" thickBot="1">
+    <row r="376" spans="1:10" ht="16.2" thickBot="1">
       <c r="A376" s="6" t="s">
         <v>205</v>
       </c>
@@ -29319,7 +29320,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="31.5" thickBot="1">
+    <row r="377" spans="1:10" ht="16.2" thickBot="1">
       <c r="A377" s="6" t="s">
         <v>206</v>
       </c>
@@ -29335,7 +29336,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="16.5" thickBot="1">
+    <row r="378" spans="1:10" ht="16.2" thickBot="1">
       <c r="A378" s="25" t="s">
         <v>207</v>
       </c>
@@ -29354,7 +29355,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="16.5" thickBot="1">
+    <row r="379" spans="1:10" ht="16.2" thickBot="1">
       <c r="A379" s="6" t="s">
         <v>208</v>
       </c>
@@ -29373,7 +29374,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="16.5" thickBot="1">
+    <row r="380" spans="1:10" ht="16.2" thickBot="1">
       <c r="A380" s="6" t="s">
         <v>209</v>
       </c>
@@ -29392,7 +29393,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="16.5" thickBot="1">
+    <row r="381" spans="1:10" ht="16.2" thickBot="1">
       <c r="A381" s="6" t="s">
         <v>210</v>
       </c>
@@ -29408,7 +29409,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="16.5" thickBot="1">
+    <row r="382" spans="1:10" ht="16.2" thickBot="1">
       <c r="A382" s="6" t="s">
         <v>211</v>
       </c>
@@ -29424,7 +29425,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="16.5" thickBot="1">
+    <row r="383" spans="1:10" ht="16.2" thickBot="1">
       <c r="A383" s="6" t="s">
         <v>212</v>
       </c>
@@ -29440,7 +29441,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="16.5" thickBot="1">
+    <row r="384" spans="1:10" ht="16.2" thickBot="1">
       <c r="A384" s="6" t="s">
         <v>213</v>
       </c>
@@ -29456,7 +29457,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="16.5" thickBot="1">
+    <row r="385" spans="1:10" ht="16.2" thickBot="1">
       <c r="A385" s="6" t="s">
         <v>214</v>
       </c>
@@ -29472,7 +29473,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="386" spans="1:10" ht="16.5" thickBot="1">
+    <row r="386" spans="1:10" ht="16.2" thickBot="1">
       <c r="A386" s="6" t="s">
         <v>215</v>
       </c>
@@ -29488,7 +29489,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="16.5" thickBot="1">
+    <row r="387" spans="1:10" ht="16.2" thickBot="1">
       <c r="A387" s="6" t="s">
         <v>216</v>
       </c>
@@ -29504,7 +29505,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="388" spans="1:10" ht="16.5" thickBot="1">
+    <row r="388" spans="1:10" ht="16.2" thickBot="1">
       <c r="A388" s="6" t="s">
         <v>217</v>
       </c>
@@ -29520,7 +29521,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="16.5" thickBot="1">
+    <row r="389" spans="1:10" ht="16.2" thickBot="1">
       <c r="A389" s="6" t="s">
         <v>218</v>
       </c>
@@ -29536,7 +29537,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="390" spans="1:10" ht="16.5" thickBot="1">
+    <row r="390" spans="1:10" ht="16.2" thickBot="1">
       <c r="A390" s="6" t="s">
         <v>219</v>
       </c>
@@ -29552,7 +29553,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="391" spans="1:10" ht="16.5" thickBot="1">
+    <row r="391" spans="1:10" ht="16.2" thickBot="1">
       <c r="A391" s="6" t="s">
         <v>220</v>
       </c>
@@ -29571,7 +29572,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="16.5" thickBot="1">
+    <row r="392" spans="1:10" ht="16.2" thickBot="1">
       <c r="A392" s="6" t="s">
         <v>221</v>
       </c>
@@ -29590,7 +29591,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="16.5" thickBot="1">
+    <row r="393" spans="1:10" ht="16.2" thickBot="1">
       <c r="A393" s="6" t="s">
         <v>222</v>
       </c>
@@ -29609,7 +29610,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="394" spans="1:10" ht="16.5" thickBot="1">
+    <row r="394" spans="1:10" ht="16.2" thickBot="1">
       <c r="A394" s="6" t="s">
         <v>223</v>
       </c>
@@ -29625,7 +29626,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="16.5" thickBot="1">
+    <row r="395" spans="1:10" ht="16.2" thickBot="1">
       <c r="A395" s="6" t="s">
         <v>224</v>
       </c>
@@ -29641,7 +29642,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="16.5" thickBot="1">
+    <row r="396" spans="1:10" ht="16.2" thickBot="1">
       <c r="A396" s="6" t="s">
         <v>225</v>
       </c>
@@ -29657,7 +29658,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="16.5" thickBot="1">
+    <row r="397" spans="1:10" ht="16.2" thickBot="1">
       <c r="A397" s="21" t="s">
         <v>226</v>
       </c>
@@ -29679,7 +29680,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="16.5" thickBot="1">
+    <row r="398" spans="1:10" ht="16.2" thickBot="1">
       <c r="A398" s="6" t="s">
         <v>227</v>
       </c>
@@ -29695,7 +29696,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="399" spans="1:10" ht="16.5" thickBot="1">
+    <row r="399" spans="1:10" ht="16.2" thickBot="1">
       <c r="A399" s="6" t="s">
         <v>228</v>
       </c>
@@ -29711,7 +29712,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="16.5" thickBot="1">
+    <row r="400" spans="1:10" ht="16.2" thickBot="1">
       <c r="A400" s="6" t="s">
         <v>229</v>
       </c>
@@ -29727,7 +29728,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="16.5" thickBot="1">
+    <row r="401" spans="1:6" ht="16.2" thickBot="1">
       <c r="A401" s="6" t="s">
         <v>230</v>
       </c>
@@ -29743,7 +29744,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="16.5" thickBot="1">
+    <row r="402" spans="1:6" ht="16.2" thickBot="1">
       <c r="A402" s="6" t="s">
         <v>231</v>
       </c>
@@ -29759,7 +29760,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="15.75" thickBot="1">
+    <row r="403" spans="1:6" ht="15" thickBot="1">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -29767,7 +29768,7 @@
       <c r="E403" s="5"/>
       <c r="F403" s="5"/>
     </row>
-    <row r="404" spans="1:6" ht="15.75" thickBot="1">
+    <row r="404" spans="1:6" ht="15" thickBot="1">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -29784,9 +29785,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9447E658-0406-4337-92E7-EF22271613D0}">
   <dimension ref="A1:I526"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="9" width="11.42578125" style="23"/>
+    <col min="1" max="9" width="11.44140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -32684,10 +32685,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7AC209-399B-46DE-A186-E777887E2AAF}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="91.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -34609,9 +34610,9 @@
   <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="45" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="178.85546875" customWidth="1"/>
+    <col min="2" max="2" width="66.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="178.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="45" customHeight="1">
@@ -34641,7 +34642,7 @@
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" spans="1:10" ht="14.45" customHeight="1">
+    <row r="3" spans="1:10" ht="14.4" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>834</v>
       </c>
@@ -34657,7 +34658,7 @@
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" spans="1:10" ht="14.45" customHeight="1">
+    <row r="4" spans="1:10" ht="14.4" customHeight="1">
       <c r="A4" s="27" t="s">
         <v>835</v>
       </c>
@@ -34673,7 +34674,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" customHeight="1">
+    <row r="5" spans="1:10" ht="14.4" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>836</v>
       </c>
@@ -34689,7 +34690,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" customHeight="1">
+    <row r="6" spans="1:10" ht="14.4" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>837</v>
       </c>
@@ -34705,7 +34706,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="1:10" ht="14.45" customHeight="1">
+    <row r="7" spans="1:10" ht="14.4" customHeight="1">
       <c r="A7" s="22" t="s">
         <v>838</v>
       </c>
@@ -34721,7 +34722,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10" ht="14.45" customHeight="1">
+    <row r="8" spans="1:10" ht="14.4" customHeight="1">
       <c r="A8" s="27" t="s">
         <v>839</v>
       </c>
@@ -34737,7 +34738,7 @@
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
     </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
+    <row r="9" spans="1:10" ht="14.4" customHeight="1">
       <c r="A9" s="22" t="s">
         <v>840</v>
       </c>
@@ -34753,7 +34754,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
     </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
+    <row r="10" spans="1:10" ht="14.4" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>841</v>
       </c>
@@ -34769,7 +34770,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    <row r="11" spans="1:10" ht="14.4" customHeight="1">
       <c r="A11" s="22" t="s">
         <v>842</v>
       </c>
@@ -34785,7 +34786,7 @@
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
     </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    <row r="12" spans="1:10" ht="14.4" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>843</v>
       </c>
@@ -34801,7 +34802,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
     </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    <row r="13" spans="1:10" ht="14.4" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>844</v>
       </c>
@@ -34817,7 +34818,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    <row r="14" spans="1:10" ht="14.4" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>845</v>
       </c>
@@ -34833,7 +34834,7 @@
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
     </row>
-    <row r="15" spans="1:10" ht="14.45" customHeight="1">
+    <row r="15" spans="1:10" ht="14.4" customHeight="1">
       <c r="A15" s="35" t="s">
         <v>846</v>
       </c>
@@ -34849,7 +34850,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" spans="1:10" ht="14.45" customHeight="1">
+    <row r="16" spans="1:10" ht="14.4" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>1165</v>
       </c>
@@ -34865,7 +34866,7 @@
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
     </row>
-    <row r="17" spans="2:10" ht="14.45" customHeight="1">
+    <row r="17" spans="2:10" ht="14.4" customHeight="1">
       <c r="D17" s="22" t="s">
         <v>1135</v>
       </c>
@@ -34876,7 +34877,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:10" ht="14.45" customHeight="1">
+    <row r="18" spans="2:10" ht="14.4" customHeight="1">
       <c r="B18" s="16" t="s">
         <v>812</v>
       </c>
@@ -34890,7 +34891,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:10" ht="14.45" customHeight="1">
+    <row r="19" spans="2:10" ht="14.4" customHeight="1">
       <c r="B19" s="16" t="s">
         <v>813</v>
       </c>
@@ -34907,7 +34908,7 @@
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:10" ht="14.45" customHeight="1">
+    <row r="20" spans="2:10" ht="14.4" customHeight="1">
       <c r="B20" s="16" t="s">
         <v>814</v>
       </c>
@@ -34921,7 +34922,7 @@
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:10" ht="14.45" customHeight="1">
+    <row r="21" spans="2:10" ht="14.4" customHeight="1">
       <c r="B21" s="16" t="s">
         <v>815</v>
       </c>
@@ -34935,7 +34936,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
     </row>
-    <row r="22" spans="2:10" ht="14.45" customHeight="1">
+    <row r="22" spans="2:10" ht="14.4" customHeight="1">
       <c r="B22" s="17"/>
       <c r="D22" s="22" t="s">
         <v>1126</v>
@@ -34947,7 +34948,7 @@
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
     </row>
-    <row r="23" spans="2:10" ht="14.45" customHeight="1">
+    <row r="23" spans="2:10" ht="14.4" customHeight="1">
       <c r="B23" s="16" t="s">
         <v>816</v>
       </c>
@@ -34961,7 +34962,7 @@
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:10" ht="14.45" customHeight="1">
+    <row r="24" spans="2:10" ht="14.4" customHeight="1">
       <c r="B24" s="16" t="s">
         <v>817</v>
       </c>
@@ -34975,7 +34976,7 @@
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:10" ht="14.45" customHeight="1">
+    <row r="25" spans="2:10" ht="14.4" customHeight="1">
       <c r="B25" s="17"/>
       <c r="D25" s="22" t="s">
         <v>1139</v>
@@ -34987,7 +34988,7 @@
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:10" ht="14.45" customHeight="1">
+    <row r="26" spans="2:10" ht="14.4" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>818</v>
       </c>
@@ -35001,7 +35002,7 @@
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
     </row>
-    <row r="27" spans="2:10" ht="14.45" customHeight="1">
+    <row r="27" spans="2:10" ht="14.4" customHeight="1">
       <c r="B27" s="16" t="s">
         <v>819</v>
       </c>
@@ -35015,7 +35016,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="2:10" ht="14.45" customHeight="1">
+    <row r="28" spans="2:10" ht="14.4" customHeight="1">
       <c r="B28" s="17"/>
       <c r="D28" s="22" t="s">
         <v>1126</v>
@@ -35027,7 +35028,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:10" ht="14.45" customHeight="1">
+    <row r="29" spans="2:10" ht="14.4" customHeight="1">
       <c r="B29" s="16" t="s">
         <v>820</v>
       </c>
@@ -35041,7 +35042,7 @@
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:10" ht="14.45" customHeight="1">
+    <row r="30" spans="2:10" ht="14.4" customHeight="1">
       <c r="B30" s="16" t="s">
         <v>821</v>
       </c>
@@ -35055,7 +35056,7 @@
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
     </row>
-    <row r="31" spans="2:10" ht="14.45" customHeight="1">
+    <row r="31" spans="2:10" ht="14.4" customHeight="1">
       <c r="B31" s="16" t="s">
         <v>822</v>
       </c>
@@ -35069,7 +35070,7 @@
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
     </row>
-    <row r="32" spans="2:10" ht="14.45" customHeight="1">
+    <row r="32" spans="2:10" ht="14.4" customHeight="1">
       <c r="B32" s="17"/>
       <c r="D32" s="22" t="s">
         <v>1130</v>
@@ -35081,7 +35082,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:10" ht="14.45" customHeight="1">
+    <row r="33" spans="2:10" ht="14.4" customHeight="1">
       <c r="B33" s="16" t="s">
         <v>823</v>
       </c>
@@ -35095,7 +35096,7 @@
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:10" ht="14.45" customHeight="1">
+    <row r="34" spans="2:10" ht="14.4" customHeight="1">
       <c r="B34" s="16" t="s">
         <v>824</v>
       </c>
@@ -35109,7 +35110,7 @@
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:10" ht="14.45" customHeight="1">
+    <row r="35" spans="2:10" ht="14.4" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>825</v>
       </c>
@@ -35123,7 +35124,7 @@
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
     </row>
-    <row r="36" spans="2:10" ht="14.45" customHeight="1">
+    <row r="36" spans="2:10" ht="14.4" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="22" t="s">
         <v>1134</v>
@@ -35135,7 +35136,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:10" ht="14.45" customHeight="1">
+    <row r="37" spans="2:10" ht="14.4" customHeight="1">
       <c r="B37" s="16" t="s">
         <v>826</v>
       </c>
@@ -35149,7 +35150,7 @@
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:10" ht="14.45" customHeight="1">
+    <row r="38" spans="2:10" ht="14.4" customHeight="1">
       <c r="B38" s="16" t="s">
         <v>827</v>
       </c>
@@ -35163,7 +35164,7 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="2:10" ht="14.45" customHeight="1">
+    <row r="39" spans="2:10" ht="14.4" customHeight="1">
       <c r="B39" s="16" t="s">
         <v>828</v>
       </c>
@@ -35177,7 +35178,7 @@
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="2:10" ht="14.45" customHeight="1">
+    <row r="40" spans="2:10" ht="14.4" customHeight="1">
       <c r="B40" s="16" t="s">
         <v>829</v>
       </c>
@@ -35191,7 +35192,7 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="2:10" ht="14.45" customHeight="1">
+    <row r="41" spans="2:10" ht="14.4" customHeight="1">
       <c r="B41" s="16" t="s">
         <v>830</v>
       </c>
@@ -35205,7 +35206,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="2:10" ht="14.45" customHeight="1">
+    <row r="42" spans="2:10" ht="14.4" customHeight="1">
       <c r="D42" s="22" t="s">
         <v>1148</v>
       </c>
@@ -35216,7 +35217,7 @@
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
     </row>
-    <row r="43" spans="2:10" ht="14.45" customHeight="1">
+    <row r="43" spans="2:10" ht="14.4" customHeight="1">
       <c r="D43" s="22" t="s">
         <v>1149</v>
       </c>
@@ -35227,7 +35228,7 @@
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
     </row>
-    <row r="44" spans="2:10" ht="14.45" customHeight="1">
+    <row r="44" spans="2:10" ht="14.4" customHeight="1">
       <c r="B44" s="18" t="s">
         <v>832</v>
       </c>
@@ -35242,7 +35243,7 @@
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
     </row>
-    <row r="45" spans="2:10" ht="14.45" customHeight="1">
+    <row r="45" spans="2:10" ht="14.4" customHeight="1">
       <c r="B45" s="18" t="s">
         <v>833</v>
       </c>
@@ -35257,7 +35258,7 @@
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:10" ht="14.45" customHeight="1">
+    <row r="46" spans="2:10" ht="14.4" customHeight="1">
       <c r="B46" s="18" t="s">
         <v>834</v>
       </c>
@@ -35272,7 +35273,7 @@
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
     </row>
-    <row r="47" spans="2:10" ht="14.45" customHeight="1">
+    <row r="47" spans="2:10" ht="14.4" customHeight="1">
       <c r="B47" s="18" t="s">
         <v>835</v>
       </c>
@@ -35287,7 +35288,7 @@
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
     </row>
-    <row r="48" spans="2:10" ht="14.45" customHeight="1">
+    <row r="48" spans="2:10" ht="14.4" customHeight="1">
       <c r="B48" s="18" t="s">
         <v>836</v>
       </c>
@@ -35302,7 +35303,7 @@
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
     </row>
-    <row r="49" spans="2:10" ht="14.45" customHeight="1">
+    <row r="49" spans="2:10" ht="14.4" customHeight="1">
       <c r="B49" s="18" t="s">
         <v>837</v>
       </c>
@@ -35317,7 +35318,7 @@
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
     </row>
-    <row r="50" spans="2:10" ht="14.45" customHeight="1">
+    <row r="50" spans="2:10" ht="14.4" customHeight="1">
       <c r="B50" s="18" t="s">
         <v>838</v>
       </c>
@@ -35332,7 +35333,7 @@
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
     </row>
-    <row r="51" spans="2:10" ht="14.45" customHeight="1">
+    <row r="51" spans="2:10" ht="14.4" customHeight="1">
       <c r="B51" s="18" t="s">
         <v>839</v>
       </c>
@@ -35347,7 +35348,7 @@
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
     </row>
-    <row r="52" spans="2:10" ht="14.45" customHeight="1">
+    <row r="52" spans="2:10" ht="14.4" customHeight="1">
       <c r="B52" s="18" t="s">
         <v>840</v>
       </c>
@@ -35362,7 +35363,7 @@
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
     </row>
-    <row r="53" spans="2:10" ht="14.45" customHeight="1">
+    <row r="53" spans="2:10" ht="14.4" customHeight="1">
       <c r="B53" s="18" t="s">
         <v>841</v>
       </c>
@@ -35377,7 +35378,7 @@
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
     </row>
-    <row r="54" spans="2:10" ht="14.45" customHeight="1">
+    <row r="54" spans="2:10" ht="14.4" customHeight="1">
       <c r="B54" s="18" t="s">
         <v>842</v>
       </c>
@@ -35392,7 +35393,7 @@
       <c r="I54" s="23"/>
       <c r="J54" s="23"/>
     </row>
-    <row r="55" spans="2:10" ht="14.45" customHeight="1">
+    <row r="55" spans="2:10" ht="14.4" customHeight="1">
       <c r="B55" s="18" t="s">
         <v>843</v>
       </c>
@@ -35407,7 +35408,7 @@
       <c r="I55" s="23"/>
       <c r="J55" s="23"/>
     </row>
-    <row r="56" spans="2:10" ht="14.45" customHeight="1">
+    <row r="56" spans="2:10" ht="14.4" customHeight="1">
       <c r="B56" s="18" t="s">
         <v>844</v>
       </c>
@@ -35422,7 +35423,7 @@
       <c r="I56" s="23"/>
       <c r="J56" s="23"/>
     </row>
-    <row r="57" spans="2:10" ht="14.45" customHeight="1">
+    <row r="57" spans="2:10" ht="14.4" customHeight="1">
       <c r="B57" s="18" t="s">
         <v>845</v>
       </c>
@@ -35437,7 +35438,7 @@
       <c r="I57" s="23"/>
       <c r="J57" s="23"/>
     </row>
-    <row r="58" spans="2:10" ht="14.45" customHeight="1">
+    <row r="58" spans="2:10" ht="14.4" customHeight="1">
       <c r="B58" s="18" t="s">
         <v>846</v>
       </c>
@@ -35452,7 +35453,7 @@
       <c r="I58" s="23"/>
       <c r="J58" s="23"/>
     </row>
-    <row r="59" spans="2:10" ht="14.45" customHeight="1">
+    <row r="59" spans="2:10" ht="14.4" customHeight="1">
       <c r="B59" s="18" t="s">
         <v>847</v>
       </c>
@@ -35467,7 +35468,7 @@
       <c r="I59" s="23"/>
       <c r="J59" s="23"/>
     </row>
-    <row r="60" spans="2:10" ht="14.45" customHeight="1">
+    <row r="60" spans="2:10" ht="14.4" customHeight="1">
       <c r="D60" s="22" t="s">
         <v>1156</v>
       </c>
@@ -35478,7 +35479,7 @@
       <c r="I60" s="23"/>
       <c r="J60" s="23"/>
     </row>
-    <row r="61" spans="2:10" ht="14.45" customHeight="1">
+    <row r="61" spans="2:10" ht="14.4" customHeight="1">
       <c r="D61" s="22" t="s">
         <v>1157</v>
       </c>
@@ -35489,7 +35490,7 @@
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
     </row>
-    <row r="62" spans="2:10" ht="14.45" customHeight="1">
+    <row r="62" spans="2:10" ht="14.4" customHeight="1">
       <c r="D62" s="22" t="s">
         <v>1134</v>
       </c>
@@ -35500,7 +35501,7 @@
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
     </row>
-    <row r="63" spans="2:10" ht="14.45" customHeight="1">
+    <row r="63" spans="2:10" ht="14.4" customHeight="1">
       <c r="D63" s="22" t="s">
         <v>1128</v>
       </c>
@@ -35511,7 +35512,7 @@
       <c r="I63" s="23"/>
       <c r="J63" s="23"/>
     </row>
-    <row r="64" spans="2:10" ht="14.45" customHeight="1">
+    <row r="64" spans="2:10" ht="14.4" customHeight="1">
       <c r="D64" s="22" t="s">
         <v>1135</v>
       </c>
@@ -35522,7 +35523,7 @@
       <c r="I64" s="23"/>
       <c r="J64" s="23"/>
     </row>
-    <row r="65" spans="4:10" ht="14.45" customHeight="1">
+    <row r="65" spans="4:10" ht="14.4" customHeight="1">
       <c r="D65" s="22" t="s">
         <v>1126</v>
       </c>
@@ -35533,7 +35534,7 @@
       <c r="I65" s="23"/>
       <c r="J65" s="23"/>
     </row>
-    <row r="66" spans="4:10" ht="14.45" customHeight="1">
+    <row r="66" spans="4:10" ht="14.4" customHeight="1">
       <c r="D66" s="22" t="s">
         <v>1136</v>
       </c>
@@ -35544,7 +35545,7 @@
       <c r="I66" s="23"/>
       <c r="J66" s="23"/>
     </row>
-    <row r="67" spans="4:10" ht="14.45" customHeight="1">
+    <row r="67" spans="4:10" ht="14.4" customHeight="1">
       <c r="D67" s="22" t="s">
         <v>1158</v>
       </c>
@@ -35555,7 +35556,7 @@
       <c r="I67" s="23"/>
       <c r="J67" s="23"/>
     </row>
-    <row r="68" spans="4:10" ht="14.45" customHeight="1">
+    <row r="68" spans="4:10" ht="14.4" customHeight="1">
       <c r="D68" s="22" t="s">
         <v>1159</v>
       </c>
@@ -35566,7 +35567,7 @@
       <c r="I68" s="23"/>
       <c r="J68" s="23"/>
     </row>
-    <row r="69" spans="4:10" ht="14.45" customHeight="1">
+    <row r="69" spans="4:10" ht="14.4" customHeight="1">
       <c r="D69" s="22" t="s">
         <v>1160</v>
       </c>
@@ -35577,7 +35578,7 @@
       <c r="I69" s="23"/>
       <c r="J69" s="23"/>
     </row>
-    <row r="70" spans="4:10" ht="14.45" customHeight="1">
+    <row r="70" spans="4:10" ht="14.4" customHeight="1">
       <c r="D70" s="22" t="s">
         <v>1161</v>
       </c>
@@ -35588,7 +35589,7 @@
       <c r="I70" s="23"/>
       <c r="J70" s="23"/>
     </row>
-    <row r="71" spans="4:10" ht="14.45" customHeight="1">
+    <row r="71" spans="4:10" ht="14.4" customHeight="1">
       <c r="D71" s="22" t="s">
         <v>1162</v>
       </c>
@@ -35599,7 +35600,7 @@
       <c r="I71" s="23"/>
       <c r="J71" s="23"/>
     </row>
-    <row r="72" spans="4:10" ht="14.45" customHeight="1">
+    <row r="72" spans="4:10" ht="14.4" customHeight="1">
       <c r="E72" s="23"/>
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
@@ -35607,7 +35608,7 @@
       <c r="I72" s="23"/>
       <c r="J72" s="23"/>
     </row>
-    <row r="73" spans="4:10" ht="15">
+    <row r="73" spans="4:10" ht="14.4">
       <c r="E73" s="23"/>
       <c r="F73" s="23"/>
       <c r="G73" s="23"/>
@@ -35615,99 +35616,99 @@
       <c r="I73" s="23"/>
       <c r="J73" s="23"/>
     </row>
-    <row r="74" spans="4:10" ht="15"/>
-    <row r="75" spans="4:10" ht="15"/>
-    <row r="76" spans="4:10" ht="15"/>
-    <row r="77" spans="4:10" ht="15"/>
-    <row r="78" spans="4:10" ht="15"/>
-    <row r="79" spans="4:10" ht="15"/>
-    <row r="80" spans="4:10" ht="15"/>
-    <row r="81" ht="15"/>
-    <row r="82" ht="15"/>
-    <row r="83" ht="15"/>
-    <row r="84" ht="15"/>
-    <row r="85" ht="15"/>
-    <row r="86" ht="15"/>
-    <row r="87" ht="15"/>
-    <row r="88" ht="15"/>
-    <row r="89" ht="15"/>
-    <row r="90" ht="15"/>
-    <row r="91" ht="15"/>
-    <row r="92" ht="15"/>
-    <row r="93" ht="15"/>
-    <row r="94" ht="15"/>
-    <row r="95" ht="15"/>
-    <row r="96" ht="15"/>
-    <row r="97" ht="15"/>
-    <row r="98" ht="15"/>
-    <row r="99" ht="15"/>
-    <row r="100" ht="15"/>
-    <row r="101" ht="15"/>
-    <row r="102" ht="15"/>
-    <row r="103" ht="15"/>
-    <row r="104" ht="15"/>
-    <row r="105" ht="15"/>
-    <row r="106" ht="15"/>
-    <row r="107" ht="15"/>
-    <row r="108" ht="15"/>
-    <row r="109" ht="15"/>
-    <row r="110" ht="15"/>
-    <row r="111" ht="15"/>
-    <row r="112" ht="15"/>
-    <row r="113" ht="15"/>
-    <row r="114" ht="15"/>
-    <row r="115" ht="15"/>
-    <row r="116" ht="15"/>
-    <row r="117" ht="15"/>
-    <row r="118" ht="15"/>
-    <row r="119" ht="15"/>
-    <row r="120" ht="15"/>
-    <row r="121" ht="15"/>
-    <row r="122" ht="15"/>
-    <row r="123" ht="15"/>
-    <row r="124" ht="15"/>
-    <row r="125" ht="15"/>
-    <row r="126" ht="15"/>
-    <row r="127" ht="15"/>
-    <row r="128" ht="15"/>
-    <row r="129" ht="15"/>
-    <row r="130" ht="15"/>
-    <row r="131" ht="15"/>
-    <row r="132" ht="15"/>
-    <row r="133" ht="15"/>
-    <row r="134" ht="15"/>
-    <row r="135" ht="15"/>
-    <row r="136" ht="15"/>
-    <row r="137" ht="15"/>
-    <row r="138" ht="15"/>
-    <row r="139" ht="15"/>
-    <row r="140" ht="15"/>
-    <row r="141" ht="15"/>
-    <row r="142" ht="15"/>
-    <row r="143" ht="15"/>
-    <row r="144" ht="15"/>
-    <row r="145" ht="15"/>
-    <row r="146" ht="15"/>
-    <row r="147" ht="15"/>
-    <row r="148" ht="15"/>
-    <row r="149" ht="15"/>
-    <row r="150" ht="15"/>
-    <row r="151" ht="15"/>
-    <row r="152" ht="15"/>
-    <row r="153" ht="15"/>
-    <row r="154" ht="15"/>
-    <row r="155" ht="15"/>
-    <row r="156" ht="15"/>
-    <row r="157" ht="15"/>
-    <row r="158" ht="15"/>
-    <row r="159" ht="15"/>
-    <row r="160" ht="15"/>
-    <row r="161" ht="15"/>
-    <row r="162" ht="15"/>
-    <row r="163" ht="15"/>
-    <row r="164" ht="15"/>
-    <row r="165" ht="15"/>
-    <row r="166" ht="15"/>
+    <row r="74" spans="4:10" ht="14.4"/>
+    <row r="75" spans="4:10" ht="14.4"/>
+    <row r="76" spans="4:10" ht="14.4"/>
+    <row r="77" spans="4:10" ht="14.4"/>
+    <row r="78" spans="4:10" ht="14.4"/>
+    <row r="79" spans="4:10" ht="14.4"/>
+    <row r="80" spans="4:10" ht="14.4"/>
+    <row r="81" ht="14.4"/>
+    <row r="82" ht="14.4"/>
+    <row r="83" ht="14.4"/>
+    <row r="84" ht="14.4"/>
+    <row r="85" ht="14.4"/>
+    <row r="86" ht="14.4"/>
+    <row r="87" ht="14.4"/>
+    <row r="88" ht="14.4"/>
+    <row r="89" ht="14.4"/>
+    <row r="90" ht="14.4"/>
+    <row r="91" ht="14.4"/>
+    <row r="92" ht="14.4"/>
+    <row r="93" ht="14.4"/>
+    <row r="94" ht="14.4"/>
+    <row r="95" ht="14.4"/>
+    <row r="96" ht="14.4"/>
+    <row r="97" ht="14.4"/>
+    <row r="98" ht="14.4"/>
+    <row r="99" ht="14.4"/>
+    <row r="100" ht="14.4"/>
+    <row r="101" ht="14.4"/>
+    <row r="102" ht="14.4"/>
+    <row r="103" ht="14.4"/>
+    <row r="104" ht="14.4"/>
+    <row r="105" ht="14.4"/>
+    <row r="106" ht="14.4"/>
+    <row r="107" ht="14.4"/>
+    <row r="108" ht="14.4"/>
+    <row r="109" ht="14.4"/>
+    <row r="110" ht="14.4"/>
+    <row r="111" ht="14.4"/>
+    <row r="112" ht="14.4"/>
+    <row r="113" ht="14.4"/>
+    <row r="114" ht="14.4"/>
+    <row r="115" ht="14.4"/>
+    <row r="116" ht="14.4"/>
+    <row r="117" ht="14.4"/>
+    <row r="118" ht="14.4"/>
+    <row r="119" ht="14.4"/>
+    <row r="120" ht="14.4"/>
+    <row r="121" ht="14.4"/>
+    <row r="122" ht="14.4"/>
+    <row r="123" ht="14.4"/>
+    <row r="124" ht="14.4"/>
+    <row r="125" ht="14.4"/>
+    <row r="126" ht="14.4"/>
+    <row r="127" ht="14.4"/>
+    <row r="128" ht="14.4"/>
+    <row r="129" ht="14.4"/>
+    <row r="130" ht="14.4"/>
+    <row r="131" ht="14.4"/>
+    <row r="132" ht="14.4"/>
+    <row r="133" ht="14.4"/>
+    <row r="134" ht="14.4"/>
+    <row r="135" ht="14.4"/>
+    <row r="136" ht="14.4"/>
+    <row r="137" ht="14.4"/>
+    <row r="138" ht="14.4"/>
+    <row r="139" ht="14.4"/>
+    <row r="140" ht="14.4"/>
+    <row r="141" ht="14.4"/>
+    <row r="142" ht="14.4"/>
+    <row r="143" ht="14.4"/>
+    <row r="144" ht="14.4"/>
+    <row r="145" ht="14.4"/>
+    <row r="146" ht="14.4"/>
+    <row r="147" ht="14.4"/>
+    <row r="148" ht="14.4"/>
+    <row r="149" ht="14.4"/>
+    <row r="150" ht="14.4"/>
+    <row r="151" ht="14.4"/>
+    <row r="152" ht="14.4"/>
+    <row r="153" ht="14.4"/>
+    <row r="154" ht="14.4"/>
+    <row r="155" ht="14.4"/>
+    <row r="156" ht="14.4"/>
+    <row r="157" ht="14.4"/>
+    <row r="158" ht="14.4"/>
+    <row r="159" ht="14.4"/>
+    <row r="160" ht="14.4"/>
+    <row r="161" ht="14.4"/>
+    <row r="162" ht="14.4"/>
+    <row r="163" ht="14.4"/>
+    <row r="164" ht="14.4"/>
+    <row r="165" ht="14.4"/>
+    <row r="166" ht="14.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35716,15 +35717,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7DD0CD-6695-4D3C-9518-BDB565BCCF21}">
   <dimension ref="B3:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="101.42578125" customWidth="1"/>
+    <col min="2" max="2" width="101.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" s="2"/>
     </row>
-    <row r="5" spans="2:2" ht="409.5">
+    <row r="5" spans="2:2" ht="409.6">
       <c r="B5" s="2" t="s">
         <v>769</v>
       </c>
@@ -35740,17 +35741,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L150"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="65"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="65"/>
     <col min="7" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="48" thickBot="1">
+    <row r="1" spans="1:12" ht="31.8" thickBot="1">
       <c r="A1" t="s">
         <v>760</v>
       </c>
@@ -36646,7 +36647,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1">
+    <row r="42" spans="1:12" ht="15" thickBot="1">
       <c r="A42" s="49">
         <v>41</v>
       </c>
@@ -36669,7 +36670,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="16.5" thickBot="1">
+    <row r="43" spans="1:12" ht="16.2" thickBot="1">
       <c r="A43" s="49">
         <v>42</v>
       </c>
@@ -36692,7 +36693,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="16.5" thickBot="1">
+    <row r="44" spans="1:12" ht="16.2" thickBot="1">
       <c r="A44" s="49">
         <v>42</v>
       </c>
@@ -37378,7 +37379,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1">
+    <row r="75" spans="1:12" ht="15" thickBot="1">
       <c r="A75" s="49">
         <v>71</v>
       </c>
@@ -37401,7 +37402,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="16.5" thickBot="1">
+    <row r="76" spans="1:12" ht="16.2" thickBot="1">
       <c r="A76" s="49">
         <v>72</v>
       </c>
@@ -37424,7 +37425,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="16.5" thickBot="1">
+    <row r="77" spans="1:12" ht="16.2" thickBot="1">
       <c r="A77" s="49">
         <v>73</v>
       </c>
@@ -37737,7 +37738,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" thickBot="1">
+    <row r="94" spans="1:12" ht="15" thickBot="1">
       <c r="A94" s="49">
         <v>89</v>
       </c>
@@ -37760,7 +37761,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="16.5" thickBot="1">
+    <row r="95" spans="1:12" ht="16.2" thickBot="1">
       <c r="A95" s="49">
         <v>72</v>
       </c>
@@ -37823,7 +37824,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.75" thickBot="1">
+    <row r="98" spans="1:12" ht="15" thickBot="1">
       <c r="A98" s="49"/>
       <c r="B98" s="22" t="s">
         <v>214</v>
@@ -37842,7 +37843,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="16.5" thickBot="1">
+    <row r="99" spans="1:12" ht="16.2" thickBot="1">
       <c r="A99" s="49">
         <v>92</v>
       </c>
@@ -37865,7 +37866,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="16.5" thickBot="1">
+    <row r="100" spans="1:12" ht="16.2" thickBot="1">
       <c r="A100" s="49">
         <v>92</v>
       </c>
@@ -37888,7 +37889,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="16.5" thickBot="1">
+    <row r="101" spans="1:12" ht="16.2" thickBot="1">
       <c r="A101" s="49">
         <v>92</v>
       </c>
@@ -37911,7 +37912,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="16.5" thickBot="1">
+    <row r="102" spans="1:12" ht="16.2" thickBot="1">
       <c r="A102" s="49">
         <v>92</v>
       </c>
@@ -37932,7 +37933,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.75" thickBot="1">
+    <row r="103" spans="1:12" ht="15" thickBot="1">
       <c r="A103" s="49">
         <v>92</v>
       </c>
@@ -37950,7 +37951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.75" thickBot="1">
+    <row r="104" spans="1:12" ht="15" thickBot="1">
       <c r="A104" s="49">
         <v>93</v>
       </c>
@@ -38274,7 +38275,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.75" thickBot="1">
+    <row r="118" spans="1:12" ht="15" thickBot="1">
       <c r="A118" s="58">
         <v>616</v>
       </c>
@@ -38300,7 +38301,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.75" thickBot="1">
+    <row r="119" spans="1:12" ht="15" thickBot="1">
       <c r="A119" s="49">
         <v>94</v>
       </c>
@@ -38321,7 +38322,7 @@
       <c r="J119" s="57"/>
       <c r="K119" s="57"/>
     </row>
-    <row r="120" spans="1:12" ht="15.75" thickBot="1">
+    <row r="120" spans="1:12" ht="15" thickBot="1">
       <c r="A120" s="49">
         <v>95</v>
       </c>
@@ -38349,7 +38350,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.75" thickBot="1">
+    <row r="121" spans="1:12" ht="15" thickBot="1">
       <c r="A121" s="49">
         <v>96</v>
       </c>
@@ -38377,7 +38378,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.75" thickBot="1">
+    <row r="122" spans="1:12" ht="15" thickBot="1">
       <c r="A122" s="49">
         <v>97</v>
       </c>
@@ -38405,7 +38406,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" thickBot="1">
+    <row r="123" spans="1:12" ht="15" thickBot="1">
       <c r="A123" s="58">
         <v>598</v>
       </c>
@@ -38428,7 +38429,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" thickBot="1">
+    <row r="124" spans="1:12" ht="15" thickBot="1">
       <c r="A124" s="58">
         <v>599</v>
       </c>
@@ -38451,7 +38452,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.75" thickBot="1">
+    <row r="125" spans="1:12" ht="15" thickBot="1">
       <c r="A125" s="58">
         <v>600</v>
       </c>
@@ -38474,7 +38475,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.75" thickBot="1">
+    <row r="126" spans="1:12" ht="15" thickBot="1">
       <c r="A126" s="58">
         <v>607</v>
       </c>
@@ -38497,7 +38498,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.75" thickBot="1">
+    <row r="127" spans="1:12" ht="15" thickBot="1">
       <c r="A127" s="49">
         <v>98</v>
       </c>
@@ -38525,7 +38526,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.75" thickBot="1">
+    <row r="128" spans="1:12" ht="15" thickBot="1">
       <c r="A128" s="49">
         <v>99</v>
       </c>
@@ -38553,7 +38554,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1">
+    <row r="129" spans="1:12" ht="15" thickBot="1">
       <c r="A129" s="49">
         <v>100</v>
       </c>
@@ -38574,7 +38575,7 @@
       <c r="J129" s="57"/>
       <c r="K129" s="57"/>
     </row>
-    <row r="130" spans="1:12" ht="15.75" thickBot="1">
+    <row r="130" spans="1:12" ht="15" thickBot="1">
       <c r="A130" s="49">
         <v>101</v>
       </c>
@@ -38595,7 +38596,7 @@
       <c r="J130" s="57"/>
       <c r="K130" s="57"/>
     </row>
-    <row r="131" spans="1:12" ht="15.75" thickBot="1">
+    <row r="131" spans="1:12" ht="15" thickBot="1">
       <c r="A131" s="49">
         <v>102</v>
       </c>
@@ -38618,7 +38619,7 @@
       <c r="J131" s="57"/>
       <c r="K131" s="57"/>
     </row>
-    <row r="132" spans="1:12" ht="15.75" thickBot="1">
+    <row r="132" spans="1:12" ht="15" thickBot="1">
       <c r="A132" s="49">
         <v>106</v>
       </c>
@@ -38646,7 +38647,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" thickBot="1">
+    <row r="133" spans="1:12" ht="15" thickBot="1">
       <c r="A133" s="49">
         <v>107</v>
       </c>
@@ -38674,7 +38675,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" thickBot="1">
+    <row r="134" spans="1:12" ht="15" thickBot="1">
       <c r="A134" s="49">
         <v>103</v>
       </c>
@@ -38702,7 +38703,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.75" thickBot="1">
+    <row r="135" spans="1:12" ht="15" thickBot="1">
       <c r="B135" s="55" t="s">
         <v>224</v>
       </c>
@@ -38722,7 +38723,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.75" thickBot="1">
+    <row r="136" spans="1:12" ht="15" thickBot="1">
       <c r="B136" s="64" t="s">
         <v>225</v>
       </c>
@@ -38740,7 +38741,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" thickBot="1">
+    <row r="137" spans="1:12" ht="15" thickBot="1">
       <c r="A137" s="49">
         <v>108</v>
       </c>
@@ -38763,7 +38764,7 @@
       <c r="J137" s="57"/>
       <c r="K137" s="57"/>
     </row>
-    <row r="138" spans="1:12" ht="15.75" thickBot="1">
+    <row r="138" spans="1:12" ht="15" thickBot="1">
       <c r="A138" s="49">
         <v>109</v>
       </c>
@@ -38786,7 +38787,7 @@
       <c r="J138" s="57"/>
       <c r="K138" s="57"/>
     </row>
-    <row r="139" spans="1:12" ht="15.75" thickBot="1">
+    <row r="139" spans="1:12" ht="15" thickBot="1">
       <c r="A139" s="49">
         <v>110</v>
       </c>
@@ -38809,7 +38810,7 @@
       <c r="J139" s="57"/>
       <c r="K139" s="57"/>
     </row>
-    <row r="140" spans="1:12" ht="15.75" thickBot="1">
+    <row r="140" spans="1:12" ht="15" thickBot="1">
       <c r="A140" s="49">
         <v>111</v>
       </c>
@@ -38832,7 +38833,7 @@
       <c r="J140" s="57"/>
       <c r="K140" s="57"/>
     </row>
-    <row r="141" spans="1:12" ht="15.75" thickBot="1">
+    <row r="141" spans="1:12" ht="15" thickBot="1">
       <c r="A141" s="58">
         <v>569</v>
       </c>
@@ -38850,7 +38851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.75" thickBot="1">
+    <row r="142" spans="1:12" ht="15" thickBot="1">
       <c r="B142" s="55" t="s">
         <v>1568</v>
       </c>
@@ -38956,11 +38957,11 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -38986,7 +38987,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="55.5">
+    <row r="2" spans="1:7" ht="55.2">
       <c r="A2" s="38" t="s">
         <v>1191</v>
       </c>
@@ -39009,7 +39010,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45">
+    <row r="3" spans="1:7" ht="43.2">
       <c r="A3" s="38" t="s">
         <v>1195</v>
       </c>
@@ -39032,7 +39033,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45">
+    <row r="4" spans="1:7" ht="43.2">
       <c r="A4" s="38" t="s">
         <v>1199</v>
       </c>
@@ -39055,7 +39056,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45">
+    <row r="5" spans="1:7" ht="43.2">
       <c r="A5" s="38" t="s">
         <v>1204</v>
       </c>
@@ -39078,7 +39079,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60">
+    <row r="6" spans="1:7" ht="43.2">
       <c r="A6" s="38" t="s">
         <v>1208</v>
       </c>
@@ -39101,7 +39102,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45">
+    <row r="7" spans="1:7" ht="43.2">
       <c r="A7" s="38" t="s">
         <v>1211</v>
       </c>
@@ -39124,7 +39125,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45">
+    <row r="8" spans="1:7" ht="43.2">
       <c r="A8" s="38" t="s">
         <v>1216</v>
       </c>
@@ -39147,7 +39148,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45">
+    <row r="9" spans="1:7" ht="43.2">
       <c r="A9" s="38" t="s">
         <v>1220</v>
       </c>
@@ -39170,7 +39171,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="75">
+    <row r="10" spans="1:7" ht="57.6">
       <c r="A10" s="38" t="s">
         <v>1223</v>
       </c>
@@ -39193,7 +39194,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="60">
+    <row r="11" spans="1:7" ht="57.6">
       <c r="A11" s="38" t="s">
         <v>1226</v>
       </c>
@@ -39216,7 +39217,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
+    <row r="12" spans="1:7" ht="57.6">
       <c r="A12" s="38" t="s">
         <v>1230</v>
       </c>
@@ -39239,7 +39240,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45">
+    <row r="13" spans="1:7" ht="43.2">
       <c r="A13" s="38" t="s">
         <v>1234</v>
       </c>
@@ -39262,7 +39263,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60">
+    <row r="14" spans="1:7" ht="57.6">
       <c r="A14" s="38" t="s">
         <v>1238</v>
       </c>
@@ -39285,7 +39286,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="75">
+    <row r="15" spans="1:7" ht="72">
       <c r="A15" s="38" t="s">
         <v>1241</v>
       </c>
@@ -39304,8 +39305,11 @@
       <c r="F15" s="38" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="30">
+      <c r="G15" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8">
       <c r="A16" s="38" t="s">
         <v>1244</v>
       </c>
@@ -39321,8 +39325,14 @@
       <c r="E16" s="38" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="45">
+      <c r="F16" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.2">
       <c r="A17" s="38" t="s">
         <v>1249</v>
       </c>
@@ -39338,8 +39348,14 @@
       <c r="E17" s="38" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="60">
+      <c r="F17" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="57.6">
       <c r="A18" s="38" t="s">
         <v>1252</v>
       </c>
@@ -39355,8 +39371,14 @@
       <c r="E18" s="38" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="30">
+      <c r="F18" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8">
       <c r="A19" s="38" t="s">
         <v>1256</v>
       </c>
@@ -39372,8 +39394,14 @@
       <c r="E19" s="38" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="27.75">
+      <c r="F19" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="27.6">
       <c r="A20" s="38" t="s">
         <v>1260</v>
       </c>
@@ -39389,8 +39417,14 @@
       <c r="E20" s="38" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="45">
+      <c r="F20" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2">
       <c r="A21" s="38" t="s">
         <v>1264</v>
       </c>
@@ -39406,8 +39440,14 @@
       <c r="E21" s="38" t="s">
         <v>1266</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="30">
+      <c r="F21" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="28.8">
       <c r="A22" s="38" t="s">
         <v>1267</v>
       </c>
@@ -39423,8 +39463,14 @@
       <c r="E22" s="38" t="s">
         <v>1269</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="45">
+      <c r="F22" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.2">
       <c r="A23" s="38" t="s">
         <v>1270</v>
       </c>
@@ -39440,8 +39486,14 @@
       <c r="E23" s="38" t="s">
         <v>1272</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="45">
+      <c r="F23" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2">
       <c r="A24" s="38" t="s">
         <v>1273</v>
       </c>
@@ -39457,8 +39509,14 @@
       <c r="E24" s="38" t="s">
         <v>1275</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="60">
+      <c r="F24" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="43.2">
       <c r="A25" s="38" t="s">
         <v>1276</v>
       </c>
@@ -39474,8 +39532,11 @@
       <c r="E25" s="38" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="42.75">
+      <c r="F25" s="38" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42">
       <c r="A26" s="38" t="s">
         <v>1279</v>
       </c>
@@ -39492,7 +39553,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30">
+    <row r="27" spans="1:7" ht="28.8">
       <c r="A27" s="38" t="s">
         <v>1283</v>
       </c>
@@ -39509,7 +39570,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="45">
+    <row r="28" spans="1:7" ht="43.2">
       <c r="A28" s="38" t="s">
         <v>1287</v>
       </c>
@@ -39526,7 +39587,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="45">
+    <row r="29" spans="1:7" ht="43.2">
       <c r="A29" s="38" t="s">
         <v>1290</v>
       </c>
@@ -39543,7 +39604,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="60">
+    <row r="30" spans="1:7" ht="43.2">
       <c r="A30" s="38" t="s">
         <v>1293</v>
       </c>
@@ -39560,7 +39621,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="60">
+    <row r="31" spans="1:7" ht="57.6">
       <c r="A31" s="38" t="s">
         <v>1297</v>
       </c>
@@ -39577,7 +39638,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="60">
+    <row r="32" spans="1:7" ht="57.6">
       <c r="A32" s="38" t="s">
         <v>1301</v>
       </c>
@@ -39594,7 +39655,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="45">
+    <row r="33" spans="1:5" ht="43.2">
       <c r="A33" s="38" t="s">
         <v>1304</v>
       </c>
@@ -39611,7 +39672,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="45">
+    <row r="34" spans="1:5" ht="43.2">
       <c r="A34" s="38" t="s">
         <v>1308</v>
       </c>
@@ -39628,7 +39689,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="45">
+    <row r="35" spans="1:5" ht="43.2">
       <c r="A35" s="38" t="s">
         <v>1312</v>
       </c>
@@ -39645,7 +39706,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="30">
+    <row r="36" spans="1:5" ht="28.8">
       <c r="A36" s="38" t="s">
         <v>1315</v>
       </c>
@@ -39662,7 +39723,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="30">
+    <row r="37" spans="1:5" ht="28.8">
       <c r="A37" s="38" t="s">
         <v>1318</v>
       </c>
@@ -39679,7 +39740,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="45">
+    <row r="38" spans="1:5" ht="28.8">
       <c r="A38" s="38" t="s">
         <v>1322</v>
       </c>
@@ -39696,7 +39757,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="45">
+    <row r="39" spans="1:5" ht="43.2">
       <c r="A39" s="38" t="s">
         <v>1326</v>
       </c>
@@ -39713,7 +39774,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="45">
+    <row r="40" spans="1:5" ht="43.2">
       <c r="A40" s="38" t="s">
         <v>1330</v>
       </c>
@@ -39730,7 +39791,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="45">
+    <row r="41" spans="1:5" ht="43.2">
       <c r="A41" s="38" t="s">
         <v>1333</v>
       </c>
@@ -39747,7 +39808,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="38" t="s">
         <v>1336</v>
       </c>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CE3207-E29A-40DF-984A-841E56D8C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E091C-0488-4CD6-A8F3-5226143CCA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5788" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="1658">
   <si>
     <t>Nº</t>
   </si>
@@ -12654,12 +12654,87 @@
   - test_i2_ocr_provider_choice_logged_to_langsmith
   - test_i2_low_confidence_table_routes_to_human_review_conceptually</t>
   </si>
+  <si>
+    <t>detectado issue de seguridad</t>
+  </si>
+  <si>
+    <t>- Coding orchestrator rules live in `agents.md`.</t>
+  </si>
+  <si>
+    <t>- `@planner-agent` rules live in `context/agent_planner.md`.</t>
+  </si>
+  <si>
+    <t>- `@qa-agent` rules live in `context/agent_qa.md`.</t>
+  </si>
+  <si>
+    <t>- `@backend-tdd` agent rules live in `context/agent_backend_tdd.md`.</t>
+  </si>
+  <si>
+    <t>- `@frontend-tdd` agent rules live in `context/agent_frontend_tdd.md`.</t>
+  </si>
+  <si>
+    <t>- `@security-agent` rules live in `context/agent_security.md`.</t>
+  </si>
+  <si>
+    <t>- `@devops-agent` rules live in `context/agent_devops.md`.</t>
+  </si>
+  <si>
+    <t>- `@docs-agent` rules live in `context/agent_doc.md`.</t>
+  </si>
+  <si>
+    <t>- `@product-agent` rules live in `context/agent_product.md`.</t>
+  </si>
+  <si>
+    <t>- Document Upload → Coherence flow (TS-E2E-FLW-DOC-001)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Multi-tenant isolation (TS-E2E-SEC-TNT-001) - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>_In CI but not fully implemented_</t>
+    </r>
+  </si>
+  <si>
+    <t>- Alert review workflow (TS-E2E-FLW-ALR-001)</t>
+  </si>
+  <si>
+    <t>- Error recovery scenarios (TS-E2E-ERR-REC-001)</t>
+  </si>
+  <si>
+    <t>`@qa-agent`</t>
+  </si>
+  <si>
+    <t>`@backend-tdd`</t>
+  </si>
+  <si>
+    <t>`@frontend-tdd`</t>
+  </si>
+  <si>
+    <t>`@security-agent`</t>
+  </si>
+  <si>
+    <t>`@docs-agent`</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @frontend-tdd can then implement GREEN for those new failing tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @qa-agent RED plan for S3-0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12756,6 +12831,13 @@
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="13">
@@ -13388,16 +13470,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="19.2" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="19.149999999999999" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.33203125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="62.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="62.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.2" customHeight="1">
+    <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13435,7 +13517,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.2" customHeight="1">
+    <row r="2" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13474,7 +13556,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="19.2" customHeight="1">
+    <row r="3" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -13513,7 +13595,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="19.2" customHeight="1">
+    <row r="4" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -13552,7 +13634,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="19.2" customHeight="1">
+    <row r="5" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -13594,7 +13676,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="19.2" customHeight="1">
+    <row r="6" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -13633,7 +13715,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="19.2" customHeight="1">
+    <row r="7" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -13672,7 +13754,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="19.2" customHeight="1">
+    <row r="8" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -13711,7 +13793,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="19.2" customHeight="1">
+    <row r="9" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -13750,7 +13832,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="19.2" customHeight="1">
+    <row r="10" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -13792,7 +13874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="19.2" customHeight="1">
+    <row r="11" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -13834,7 +13916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="19.2" customHeight="1">
+    <row r="12" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -13873,7 +13955,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="19.2" customHeight="1">
+    <row r="13" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -13912,7 +13994,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="19.2" customHeight="1">
+    <row r="14" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -13948,7 +14030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="19.2" customHeight="1">
+    <row r="15" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -13984,7 +14066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.2" customHeight="1">
+    <row r="16" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -14023,7 +14105,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="19.2" customHeight="1">
+    <row r="17" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -14059,7 +14141,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="19.2" customHeight="1">
+    <row r="18" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -14092,7 +14174,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="19.2" customHeight="1">
+    <row r="19" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -14125,7 +14207,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="19.2" customHeight="1">
+    <row r="20" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -14158,7 +14240,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="19.2" customHeight="1">
+    <row r="21" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -14191,7 +14273,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="19.2" customHeight="1">
+    <row r="22" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -14224,7 +14306,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="19.2" customHeight="1">
+    <row r="23" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -14263,7 +14345,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="19.2" customHeight="1">
+    <row r="24" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -14299,7 +14381,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="19.2" customHeight="1">
+    <row r="25" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -14332,7 +14414,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="19.2" customHeight="1">
+    <row r="26" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -14365,7 +14447,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="19.2" customHeight="1">
+    <row r="27" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -14398,7 +14480,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="19.2" customHeight="1">
+    <row r="28" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -14437,7 +14519,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="19.2" customHeight="1">
+    <row r="29" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -14470,7 +14552,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="19.2" customHeight="1">
+    <row r="30" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -14503,7 +14585,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="19.2" customHeight="1">
+    <row r="31" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -14536,7 +14618,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="19.2" customHeight="1">
+    <row r="32" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -14569,7 +14651,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="19.2" customHeight="1">
+    <row r="33" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -14602,7 +14684,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="19.2" customHeight="1">
+    <row r="34" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -14638,7 +14720,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="19.2" customHeight="1">
+    <row r="35" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -14674,7 +14756,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="19.2" customHeight="1">
+    <row r="36" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -14710,7 +14792,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="19.2" customHeight="1">
+    <row r="37" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -14746,7 +14828,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="19.2" customHeight="1">
+    <row r="38" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -14782,7 +14864,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="19.2" customHeight="1">
+    <row r="39" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -14821,7 +14903,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="19.2" customHeight="1">
+    <row r="40" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -14854,7 +14936,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="19.2" customHeight="1">
+    <row r="41" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -14887,7 +14969,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="19.2" customHeight="1">
+    <row r="42" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -14920,7 +15002,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="19.2" customHeight="1">
+    <row r="43" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -14953,7 +15035,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="19.2" customHeight="1">
+    <row r="44" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -14986,7 +15068,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="19.2" customHeight="1">
+    <row r="45" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -15019,7 +15101,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="19.2" customHeight="1">
+    <row r="46" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -15052,7 +15134,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="19.2" customHeight="1">
+    <row r="47" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -15091,7 +15173,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="19.2" customHeight="1">
+    <row r="48" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -15124,7 +15206,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="19.2" customHeight="1">
+    <row r="49" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -15157,7 +15239,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="19.2" customHeight="1">
+    <row r="50" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -15190,7 +15272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="19.2" customHeight="1">
+    <row r="51" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -15223,7 +15305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="19.2" customHeight="1">
+    <row r="52" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -15256,7 +15338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="19.2" customHeight="1">
+    <row r="53" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -15289,7 +15371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="19.2" customHeight="1">
+    <row r="54" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -15322,7 +15404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="19.2" customHeight="1">
+    <row r="55" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -15355,7 +15437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="19.2" customHeight="1">
+    <row r="56" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -15388,7 +15470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="19.2" customHeight="1">
+    <row r="57" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -15421,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="19.2" customHeight="1">
+    <row r="58" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -15454,7 +15536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="19.2" customHeight="1">
+    <row r="59" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -15487,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="19.2" customHeight="1">
+    <row r="60" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -15520,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="19.2" customHeight="1">
+    <row r="61" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -15553,7 +15635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="19.2" customHeight="1">
+    <row r="62" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -15586,7 +15668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="19.2" customHeight="1">
+    <row r="63" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -15619,7 +15701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="19.2" customHeight="1">
+    <row r="64" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -15652,7 +15734,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="19.2" customHeight="1">
+    <row r="65" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -15685,7 +15767,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="19.2" customHeight="1">
+    <row r="66" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -15718,7 +15800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="19.2" customHeight="1">
+    <row r="67" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -15751,7 +15833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="19.2" customHeight="1">
+    <row r="68" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -15784,7 +15866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="19.2" customHeight="1">
+    <row r="69" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -15817,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="19.2" customHeight="1">
+    <row r="70" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -15850,7 +15932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="19.2" customHeight="1">
+    <row r="71" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -15883,7 +15965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="19.2" customHeight="1">
+    <row r="72" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -15925,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="19.2" customHeight="1">
+    <row r="73" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -15964,7 +16046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="19.2" customHeight="1">
+    <row r="74" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -16003,7 +16085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="19.2" customHeight="1">
+    <row r="75" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -16039,7 +16121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="19.2" customHeight="1">
+    <row r="76" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -16072,7 +16154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="19.2" customHeight="1">
+    <row r="77" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -16111,7 +16193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="19.2" customHeight="1">
+    <row r="78" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -16150,7 +16232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="19.2" customHeight="1">
+    <row r="79" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -16189,7 +16271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="19.2" customHeight="1">
+    <row r="80" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -16225,7 +16307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="19.2" customHeight="1">
+    <row r="81" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -16261,7 +16343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="19.2" customHeight="1">
+    <row r="82" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -16294,7 +16376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="19.2" customHeight="1">
+    <row r="83" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -16336,7 +16418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="19.2" customHeight="1">
+    <row r="84" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A84" t="s">
         <v>102</v>
       </c>
@@ -16369,7 +16451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="19.2" customHeight="1">
+    <row r="85" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -16405,7 +16487,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="19.2" customHeight="1">
+    <row r="86" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -16444,7 +16526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="19.2" customHeight="1">
+    <row r="87" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -16477,7 +16559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="19.2" customHeight="1">
+    <row r="88" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -16510,7 +16592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="19.2" customHeight="1">
+    <row r="89" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -16543,7 +16625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="19.2" customHeight="1">
+    <row r="90" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -16582,7 +16664,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="19.2" customHeight="1">
+    <row r="91" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -16618,7 +16700,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="19.2" customHeight="1">
+    <row r="92" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -16654,7 +16736,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="19.2" customHeight="1">
+    <row r="93" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -16687,7 +16769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="19.2" customHeight="1">
+    <row r="94" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -16723,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="19.2" customHeight="1">
+    <row r="95" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -16762,7 +16844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="19.2" customHeight="1">
+    <row r="96" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -16795,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="19.2" customHeight="1">
+    <row r="97" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -16834,7 +16916,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="19.2" customHeight="1">
+    <row r="98" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A98" t="s">
         <v>86</v>
       </c>
@@ -16870,7 +16952,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="19.2" customHeight="1">
+    <row r="99" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -16906,7 +16988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="19.2" customHeight="1">
+    <row r="100" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -16942,7 +17024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="19.2" customHeight="1">
+    <row r="101" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -16975,7 +17057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="19.2" customHeight="1">
+    <row r="102" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -17011,7 +17093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="19.2" customHeight="1">
+    <row r="103" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -17053,7 +17135,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="19.2" customHeight="1">
+    <row r="104" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -17089,7 +17171,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="19.2" customHeight="1">
+    <row r="105" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -17125,7 +17207,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="19.2" customHeight="1">
+    <row r="106" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -17161,7 +17243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="19.2" customHeight="1">
+    <row r="107" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -17200,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="19.2" customHeight="1">
+    <row r="108" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -17236,7 +17318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="19.2" customHeight="1">
+    <row r="109" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -17275,7 +17357,7 @@
         <v>claude</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="19.2" customHeight="1">
+    <row r="110" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -17314,7 +17396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="19.2" customHeight="1">
+    <row r="111" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -17353,7 +17435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="19.2" customHeight="1">
+    <row r="112" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -17386,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="19.2" customHeight="1">
+    <row r="113" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -17419,7 +17501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="19.2" customHeight="1">
+    <row r="114" spans="1:13" ht="19.149999999999999" customHeight="1">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -17468,17 +17550,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16843C28-0155-42BB-A62E-C4CE7C932E1A}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="146.44140625" customWidth="1"/>
+    <col min="1" max="1" width="146.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.6">
+    <row r="1" spans="1:1" ht="409.5">
       <c r="A1" s="2" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="86.4">
+    <row r="3" spans="1:1" ht="90">
       <c r="A3" s="2" t="s">
         <v>1340</v>
       </c>
@@ -17491,15 +17573,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1590E3-1708-4563-889F-3AD6ACE1A716}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F236"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:F264"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="77.6640625" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="47.42578125" customWidth="1"/>
     <col min="5" max="5" width="79" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" customWidth="1"/>
+    <col min="6" max="6" width="67.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -17531,82 +17613,82 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19.2" hidden="1">
+    <row r="3" spans="1:5" ht="17.25" hidden="1">
       <c r="B3" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="96" hidden="1">
+    <row r="4" spans="1:5" ht="86.25" hidden="1">
       <c r="B4" s="43" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="38.4" hidden="1">
+    <row r="5" spans="1:5" ht="34.5" hidden="1">
       <c r="B5" s="43" t="s">
         <v>1346</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="57.6" hidden="1">
+    <row r="6" spans="1:5" ht="51.75" hidden="1">
       <c r="B6" s="43" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19.2" hidden="1">
+    <row r="7" spans="1:5" ht="17.25" hidden="1">
       <c r="B7" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="38.4" hidden="1">
+    <row r="8" spans="1:5" ht="34.5" hidden="1">
       <c r="B8" s="43" t="s">
         <v>1349</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="38.4" hidden="1">
+    <row r="9" spans="1:5" ht="34.5" hidden="1">
       <c r="B9" s="43" t="s">
         <v>1350</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="38.4" hidden="1">
+    <row r="10" spans="1:5" ht="34.5" hidden="1">
       <c r="B10" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="57.6" hidden="1">
+    <row r="11" spans="1:5" ht="51.75" hidden="1">
       <c r="B11" s="43" t="s">
         <v>1352</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="57.6" hidden="1">
+    <row r="12" spans="1:5" ht="51.75" hidden="1">
       <c r="B12" s="43" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19.2" hidden="1">
+    <row r="13" spans="1:5" ht="17.25" hidden="1">
       <c r="B13" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="57.6" hidden="1">
+    <row r="14" spans="1:5" ht="51.75" hidden="1">
       <c r="B14" s="43" t="s">
         <v>1355</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="38.4" hidden="1">
+    <row r="15" spans="1:5" ht="34.5" hidden="1">
       <c r="B15" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="57.6" hidden="1">
+    <row r="16" spans="1:5" ht="69" hidden="1">
       <c r="B16" s="43" t="s">
         <v>1357</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="38.4" hidden="1">
+    <row r="17" spans="1:6" ht="34.5" hidden="1">
       <c r="B17" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="57.6" hidden="1">
+    <row r="18" spans="1:6" ht="69" hidden="1">
       <c r="B18" s="43" t="s">
         <v>1359</v>
       </c>
@@ -17632,82 +17714,82 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="19.2" hidden="1">
+    <row r="20" spans="1:6" ht="17.25" hidden="1">
       <c r="B20" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="57.6" hidden="1">
+    <row r="21" spans="1:6" ht="51.75" hidden="1">
       <c r="B21" s="43" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="76.8" hidden="1">
+    <row r="22" spans="1:6" ht="69" hidden="1">
       <c r="B22" s="43" t="s">
         <v>1362</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="57.6" hidden="1">
+    <row r="23" spans="1:6" ht="69" hidden="1">
       <c r="B23" s="43" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="19.2" hidden="1">
+    <row r="24" spans="1:6" ht="17.25" hidden="1">
       <c r="B24" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="19.2" hidden="1">
+    <row r="25" spans="1:6" ht="17.25" hidden="1">
       <c r="B25" s="43" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="38.4" hidden="1">
+    <row r="26" spans="1:6" ht="34.5" hidden="1">
       <c r="B26" s="43" t="s">
         <v>1365</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="38.4" hidden="1">
+    <row r="27" spans="1:6" ht="34.5" hidden="1">
       <c r="B27" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="38.4" hidden="1">
+    <row r="28" spans="1:6" ht="34.5" hidden="1">
       <c r="B28" s="43" t="s">
         <v>1366</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="38.4" hidden="1">
+    <row r="29" spans="1:6" ht="51.75" hidden="1">
       <c r="B29" s="43" t="s">
         <v>1367</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="19.2" hidden="1">
+    <row r="30" spans="1:6" ht="17.25" hidden="1">
       <c r="B30" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="57.6" hidden="1">
+    <row r="31" spans="1:6" ht="51.75" hidden="1">
       <c r="B31" s="43" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="38.4" hidden="1">
+    <row r="32" spans="1:6" ht="34.5" hidden="1">
       <c r="B32" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="57.6" hidden="1">
+    <row r="33" spans="1:5" ht="51.75" hidden="1">
       <c r="B33" s="43" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="38.4" hidden="1">
+    <row r="34" spans="1:5" ht="34.5" hidden="1">
       <c r="B34" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="57.6" hidden="1">
+    <row r="35" spans="1:5" ht="51.75" hidden="1">
       <c r="B35" s="43" t="s">
         <v>1370</v>
       </c>
@@ -17730,82 +17812,82 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19.2" hidden="1">
+    <row r="37" spans="1:5" ht="17.25" hidden="1">
       <c r="B37" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="57.6" hidden="1">
+    <row r="38" spans="1:5" ht="51.75" hidden="1">
       <c r="B38" s="43" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="57.6" hidden="1">
+    <row r="39" spans="1:5" ht="51.75" hidden="1">
       <c r="B39" s="43" t="s">
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="76.8" hidden="1">
+    <row r="40" spans="1:5" ht="69" hidden="1">
       <c r="B40" s="43" t="s">
         <v>1374</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="19.2" hidden="1">
+    <row r="41" spans="1:5" ht="17.25" hidden="1">
       <c r="B41" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="38.4" hidden="1">
+    <row r="42" spans="1:5" ht="51.75" hidden="1">
       <c r="B42" s="43" t="s">
         <v>1375</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="38.4" hidden="1">
+    <row r="43" spans="1:5" ht="34.5" hidden="1">
       <c r="B43" s="43" t="s">
         <v>1376</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="38.4" hidden="1">
+    <row r="44" spans="1:5" ht="34.5" hidden="1">
       <c r="B44" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="57.6" hidden="1">
+    <row r="45" spans="1:5" ht="51.75" hidden="1">
       <c r="B45" s="43" t="s">
         <v>1377</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="38.4" hidden="1">
+    <row r="46" spans="1:5" ht="34.5" hidden="1">
       <c r="B46" s="43" t="s">
         <v>1378</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="19.2" hidden="1">
+    <row r="47" spans="1:5" ht="17.25" hidden="1">
       <c r="B47" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="38.4" hidden="1">
+    <row r="48" spans="1:5" ht="34.5" hidden="1">
       <c r="B48" s="43" t="s">
         <v>1379</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="38.4" hidden="1">
+    <row r="49" spans="1:5" ht="34.5" hidden="1">
       <c r="B49" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="57.6" hidden="1">
+    <row r="50" spans="1:5" ht="51.75" hidden="1">
       <c r="B50" s="43" t="s">
         <v>1380</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="38.4" hidden="1">
+    <row r="51" spans="1:5" ht="34.5" hidden="1">
       <c r="B51" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="57.6" hidden="1">
+    <row r="52" spans="1:5" ht="51.75" hidden="1">
       <c r="B52" s="43" t="s">
         <v>1381</v>
       </c>
@@ -17828,82 +17910,82 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="19.2" hidden="1">
+    <row r="54" spans="1:5" ht="17.25" hidden="1">
       <c r="B54" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="38.4" hidden="1">
+    <row r="55" spans="1:5" ht="51.75" hidden="1">
       <c r="B55" s="43" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="57.6" hidden="1">
+    <row r="56" spans="1:5" ht="51.75" hidden="1">
       <c r="B56" s="43" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="57.6" hidden="1">
+    <row r="57" spans="1:5" ht="51.75" hidden="1">
       <c r="B57" s="43" t="s">
         <v>1385</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="19.2" hidden="1">
+    <row r="58" spans="1:5" ht="17.25" hidden="1">
       <c r="B58" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="38.4" hidden="1">
+    <row r="59" spans="1:5" ht="34.5" hidden="1">
       <c r="B59" s="43" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="38.4" hidden="1">
+    <row r="60" spans="1:5" ht="34.5" hidden="1">
       <c r="B60" s="43" t="s">
         <v>1387</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="38.4" hidden="1">
+    <row r="61" spans="1:5" ht="34.5" hidden="1">
       <c r="B61" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="57.6" hidden="1">
+    <row r="62" spans="1:5" ht="51.75" hidden="1">
       <c r="B62" s="43" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="19.2" hidden="1">
+    <row r="63" spans="1:5" ht="34.5" hidden="1">
       <c r="B63" s="43" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="19.2" hidden="1">
+    <row r="64" spans="1:5" ht="17.25" hidden="1">
       <c r="B64" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="38.4" hidden="1">
+    <row r="65" spans="1:5" ht="34.5" hidden="1">
       <c r="B65" s="43" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="38.4" hidden="1">
+    <row r="66" spans="1:5" ht="34.5" hidden="1">
       <c r="B66" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="38.4" hidden="1">
+    <row r="67" spans="1:5" ht="34.5" hidden="1">
       <c r="B67" s="43" t="s">
         <v>1391</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="38.4" hidden="1">
+    <row r="68" spans="1:5" ht="34.5" hidden="1">
       <c r="B68" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="57.6" hidden="1">
+    <row r="69" spans="1:5" ht="69" hidden="1">
       <c r="B69" s="43" t="s">
         <v>1392</v>
       </c>
@@ -17926,82 +18008,82 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="19.2" hidden="1">
+    <row r="71" spans="1:5" ht="17.25" hidden="1">
       <c r="B71" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="76.8" hidden="1">
+    <row r="72" spans="1:5" ht="69" hidden="1">
       <c r="B72" s="43" t="s">
         <v>1394</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="57.6" hidden="1">
+    <row r="73" spans="1:5" ht="51.75" hidden="1">
       <c r="B73" s="43" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="57.6" hidden="1">
+    <row r="74" spans="1:5" ht="51.75" hidden="1">
       <c r="B74" s="43" t="s">
         <v>1396</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="19.2" hidden="1">
+    <row r="75" spans="1:5" ht="17.25" hidden="1">
       <c r="B75" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="38.4" hidden="1">
+    <row r="76" spans="1:5" ht="34.5" hidden="1">
       <c r="B76" s="43" t="s">
         <v>1397</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="38.4" hidden="1">
+    <row r="77" spans="1:5" ht="34.5" hidden="1">
       <c r="B77" s="43" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="38.4" hidden="1">
+    <row r="78" spans="1:5" ht="34.5" hidden="1">
       <c r="B78" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="57.6" hidden="1">
+    <row r="79" spans="1:5" ht="51.75" hidden="1">
       <c r="B79" s="43" t="s">
         <v>1399</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="38.4" hidden="1">
+    <row r="80" spans="1:5" ht="34.5" hidden="1">
       <c r="B80" s="43" t="s">
         <v>1400</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="19.2" hidden="1">
+    <row r="81" spans="1:5" ht="17.25" hidden="1">
       <c r="B81" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="38.4" hidden="1">
+    <row r="82" spans="1:5" ht="51.75" hidden="1">
       <c r="B82" s="43" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="38.4" hidden="1">
+    <row r="83" spans="1:5" ht="34.5" hidden="1">
       <c r="B83" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="57.6" hidden="1">
+    <row r="84" spans="1:5" ht="51.75" hidden="1">
       <c r="B84" s="43" t="s">
         <v>1402</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="38.4" hidden="1">
+    <row r="85" spans="1:5" ht="34.5" hidden="1">
       <c r="B85" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="76.8" hidden="1">
+    <row r="86" spans="1:5" ht="69" hidden="1">
       <c r="B86" s="43" t="s">
         <v>1403</v>
       </c>
@@ -18024,77 +18106,77 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="19.2" hidden="1">
+    <row r="88" spans="1:5" ht="17.25" hidden="1">
       <c r="B88" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="76.8" hidden="1">
+    <row r="89" spans="1:5" ht="69" hidden="1">
       <c r="B89" s="43" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="38.4" hidden="1">
+    <row r="90" spans="1:5" ht="51.75" hidden="1">
       <c r="B90" s="43" t="s">
         <v>1406</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="38.4" hidden="1">
+    <row r="91" spans="1:5" ht="34.5" hidden="1">
       <c r="B91" s="43" t="s">
         <v>1407</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="19.2" hidden="1">
+    <row r="92" spans="1:5" ht="17.25" hidden="1">
       <c r="B92" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="38.4" hidden="1">
+    <row r="93" spans="1:5" ht="34.5" hidden="1">
       <c r="B93" s="43" t="s">
         <v>1408</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="19.2" hidden="1">
+    <row r="94" spans="1:5" ht="17.25" hidden="1">
       <c r="B94" s="43" t="s">
         <v>1409</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="38.4" hidden="1">
+    <row r="95" spans="1:5" ht="34.5" hidden="1">
       <c r="B95" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="57.6" hidden="1">
+    <row r="96" spans="1:5" ht="51.75" hidden="1">
       <c r="B96" s="43" t="s">
         <v>1410</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="19.2" hidden="1">
+    <row r="97" spans="1:5" ht="17.25" hidden="1">
       <c r="B97" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="38.4" hidden="1">
+    <row r="98" spans="1:5" ht="34.5" hidden="1">
       <c r="B98" s="43" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="38.4" hidden="1">
+    <row r="99" spans="1:5" ht="34.5" hidden="1">
       <c r="B99" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="38.4" hidden="1">
+    <row r="100" spans="1:5" ht="34.5" hidden="1">
       <c r="B100" s="43" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="38.4" hidden="1">
+    <row r="101" spans="1:5" ht="34.5" hidden="1">
       <c r="B101" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="38.4" hidden="1">
+    <row r="102" spans="1:5" ht="34.5" hidden="1">
       <c r="B102" s="43" t="s">
         <v>1413</v>
       </c>
@@ -18117,77 +18199,77 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="19.2" hidden="1">
+    <row r="104" spans="1:5" ht="17.25" hidden="1">
       <c r="B104" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="57.6" hidden="1">
+    <row r="105" spans="1:5" ht="51.75" hidden="1">
       <c r="B105" s="43" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="38.4" hidden="1">
+    <row r="106" spans="1:5" ht="34.5" hidden="1">
       <c r="B106" s="43" t="s">
         <v>1416</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="57.6" hidden="1">
+    <row r="107" spans="1:5" ht="51.75" hidden="1">
       <c r="B107" s="43" t="s">
         <v>1417</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="19.2" hidden="1">
+    <row r="108" spans="1:5" ht="17.25" hidden="1">
       <c r="B108" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="38.4" hidden="1">
+    <row r="109" spans="1:5" ht="34.5" hidden="1">
       <c r="B109" s="43" t="s">
         <v>1418</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="19.2" hidden="1">
+    <row r="110" spans="1:5" ht="34.5" hidden="1">
       <c r="B110" s="43" t="s">
         <v>1419</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="38.4" hidden="1">
+    <row r="111" spans="1:5" ht="34.5" hidden="1">
       <c r="B111" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="57.6" hidden="1">
+    <row r="112" spans="1:5" ht="51.75" hidden="1">
       <c r="B112" s="43" t="s">
         <v>1420</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="19.2" hidden="1">
+    <row r="113" spans="1:5" ht="17.25" hidden="1">
       <c r="B113" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="38.4" hidden="1">
+    <row r="114" spans="1:5" ht="34.5" hidden="1">
       <c r="B114" s="43" t="s">
         <v>1421</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="38.4" hidden="1">
+    <row r="115" spans="1:5" ht="34.5" hidden="1">
       <c r="B115" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="57.6" hidden="1">
+    <row r="116" spans="1:5" ht="51.75" hidden="1">
       <c r="B116" s="43" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="38.4" hidden="1">
+    <row r="117" spans="1:5" ht="34.5" hidden="1">
       <c r="B117" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="57.6" hidden="1">
+    <row r="118" spans="1:5" ht="51.75" hidden="1">
       <c r="B118" s="43" t="s">
         <v>1423</v>
       </c>
@@ -18210,82 +18292,82 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="19.2" hidden="1">
+    <row r="120" spans="1:5" ht="17.25" hidden="1">
       <c r="B120" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="57.6" hidden="1">
+    <row r="121" spans="1:5" ht="51.75" hidden="1">
       <c r="B121" s="43" t="s">
         <v>1425</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="57.6" hidden="1">
+    <row r="122" spans="1:5" ht="51.75" hidden="1">
       <c r="B122" s="43" t="s">
         <v>1426</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="38.4" hidden="1">
+    <row r="123" spans="1:5" ht="34.5" hidden="1">
       <c r="B123" s="43" t="s">
         <v>1427</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="19.2" hidden="1">
+    <row r="124" spans="1:5" ht="17.25" hidden="1">
       <c r="B124" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="38.4" hidden="1">
+    <row r="125" spans="1:5" ht="34.5" hidden="1">
       <c r="B125" s="43" t="s">
         <v>1428</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="38.4" hidden="1">
+    <row r="126" spans="1:5" ht="34.5" hidden="1">
       <c r="B126" s="43" t="s">
         <v>1429</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="38.4" hidden="1">
+    <row r="127" spans="1:5" ht="34.5" hidden="1">
       <c r="B127" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="38.4" hidden="1">
+    <row r="128" spans="1:5" ht="34.5" hidden="1">
       <c r="B128" s="43" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="57.6" hidden="1">
+    <row r="129" spans="1:5" ht="51.75" hidden="1">
       <c r="B129" s="43" t="s">
         <v>1431</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="19.2" hidden="1">
+    <row r="130" spans="1:5" ht="17.25" hidden="1">
       <c r="B130" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="38.4" hidden="1">
+    <row r="131" spans="1:5" ht="34.5" hidden="1">
       <c r="B131" s="43" t="s">
         <v>1432</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="38.4" hidden="1">
+    <row r="132" spans="1:5" ht="34.5" hidden="1">
       <c r="B132" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="57.6" hidden="1">
+    <row r="133" spans="1:5" ht="51.75" hidden="1">
       <c r="B133" s="43" t="s">
         <v>1433</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="38.4" hidden="1">
+    <row r="134" spans="1:5" ht="34.5" hidden="1">
       <c r="B134" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="76.8" hidden="1">
+    <row r="135" spans="1:5" ht="69" hidden="1">
       <c r="B135" s="43" t="s">
         <v>1434</v>
       </c>
@@ -18308,77 +18390,77 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="19.2" hidden="1">
+    <row r="137" spans="1:5" ht="17.25" hidden="1">
       <c r="B137" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="57.6" hidden="1">
+    <row r="138" spans="1:5" ht="51.75" hidden="1">
       <c r="B138" s="43" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="57.6" hidden="1">
+    <row r="139" spans="1:5" ht="51.75" hidden="1">
       <c r="B139" s="43" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="57.6" hidden="1">
+    <row r="140" spans="1:5" ht="51.75" hidden="1">
       <c r="B140" s="43" t="s">
         <v>1438</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="19.2" hidden="1">
+    <row r="141" spans="1:5" ht="17.25" hidden="1">
       <c r="B141" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="38.4" hidden="1">
+    <row r="142" spans="1:5" ht="51.75" hidden="1">
       <c r="B142" s="43" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="38.4" hidden="1">
+    <row r="143" spans="1:5" ht="34.5" hidden="1">
       <c r="B143" s="43" t="s">
         <v>1440</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="38.4" hidden="1">
+    <row r="144" spans="1:5" ht="34.5" hidden="1">
       <c r="B144" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="76.8" hidden="1">
+    <row r="145" spans="1:5" ht="69" hidden="1">
       <c r="B145" s="43" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="19.2" hidden="1">
+    <row r="146" spans="1:5" ht="17.25" hidden="1">
       <c r="B146" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="57.6" hidden="1">
+    <row r="147" spans="1:5" ht="51.75" hidden="1">
       <c r="B147" s="43" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="38.4" hidden="1">
+    <row r="148" spans="1:5" ht="34.5" hidden="1">
       <c r="B148" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="57.6" hidden="1">
+    <row r="149" spans="1:5" ht="51.75" hidden="1">
       <c r="B149" s="43" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="38.4" hidden="1">
+    <row r="150" spans="1:5" ht="34.5" hidden="1">
       <c r="B150" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="38.4" hidden="1">
+    <row r="151" spans="1:5" ht="34.5" hidden="1">
       <c r="B151" s="43" t="s">
         <v>1444</v>
       </c>
@@ -18401,82 +18483,82 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="19.2" hidden="1">
+    <row r="153" spans="1:5" ht="17.25" hidden="1">
       <c r="B153" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="57.6" hidden="1">
+    <row r="154" spans="1:5" ht="51.75" hidden="1">
       <c r="B154" s="43" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="57.6" hidden="1">
+    <row r="155" spans="1:5" ht="51.75" hidden="1">
       <c r="B155" s="43" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="57.6" hidden="1">
+    <row r="156" spans="1:5" ht="51.75" hidden="1">
       <c r="B156" s="43" t="s">
         <v>1448</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="19.2" hidden="1">
+    <row r="157" spans="1:5" ht="17.25" hidden="1">
       <c r="B157" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="38.4" hidden="1">
+    <row r="158" spans="1:5" ht="34.5" hidden="1">
       <c r="B158" s="43" t="s">
         <v>1449</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="38.4" hidden="1">
+    <row r="159" spans="1:5" ht="34.5" hidden="1">
       <c r="B159" s="43" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="38.4" hidden="1">
+    <row r="160" spans="1:5" ht="34.5" hidden="1">
       <c r="B160" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="38.4" hidden="1">
+    <row r="161" spans="1:5" ht="34.5" hidden="1">
       <c r="B161" s="43" t="s">
         <v>1451</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="38.4" hidden="1">
+    <row r="162" spans="1:5" ht="34.5" hidden="1">
       <c r="B162" s="43" t="s">
         <v>1452</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="19.2" hidden="1">
+    <row r="163" spans="1:5" ht="17.25" hidden="1">
       <c r="B163" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="57.6" hidden="1">
+    <row r="164" spans="1:5" ht="51.75" hidden="1">
       <c r="B164" s="43" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="38.4" hidden="1">
+    <row r="165" spans="1:5" ht="34.5" hidden="1">
       <c r="B165" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="38.4" hidden="1">
+    <row r="166" spans="1:5" ht="34.5" hidden="1">
       <c r="B166" s="43" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="38.4" hidden="1">
+    <row r="167" spans="1:5" ht="34.5" hidden="1">
       <c r="B167" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="57.6" hidden="1">
+    <row r="168" spans="1:5" ht="51.75" hidden="1">
       <c r="B168" s="43" t="s">
         <v>1455</v>
       </c>
@@ -18499,77 +18581,77 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="19.2" hidden="1">
+    <row r="170" spans="1:5" ht="17.25" hidden="1">
       <c r="B170" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="38.4" hidden="1">
+    <row r="171" spans="1:5" ht="34.5" hidden="1">
       <c r="B171" s="43" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="57.6" hidden="1">
+    <row r="172" spans="1:5" ht="51.75" hidden="1">
       <c r="B172" s="43" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="38.4" hidden="1">
+    <row r="173" spans="1:5" ht="34.5" hidden="1">
       <c r="B173" s="43" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="19.2" hidden="1">
+    <row r="174" spans="1:5" ht="17.25" hidden="1">
       <c r="B174" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="38.4" hidden="1">
+    <row r="175" spans="1:5" ht="34.5" hidden="1">
       <c r="B175" s="43" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="38.4" hidden="1">
+    <row r="176" spans="1:5" ht="34.5" hidden="1">
       <c r="B176" s="43" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="38.4" hidden="1">
+    <row r="177" spans="1:5" ht="34.5" hidden="1">
       <c r="B177" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="57.6" hidden="1">
+    <row r="178" spans="1:5" ht="51.75" hidden="1">
       <c r="B178" s="43" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="19.2" hidden="1">
+    <row r="179" spans="1:5" ht="17.25" hidden="1">
       <c r="B179" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="38.4" hidden="1">
+    <row r="180" spans="1:5" ht="34.5" hidden="1">
       <c r="B180" s="43" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="38.4" hidden="1">
+    <row r="181" spans="1:5" ht="34.5" hidden="1">
       <c r="B181" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="38.4" hidden="1">
+    <row r="182" spans="1:5" ht="51.75" hidden="1">
       <c r="B182" s="43" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="38.4" hidden="1">
+    <row r="183" spans="1:5" ht="34.5" hidden="1">
       <c r="B183" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="38.4" hidden="1">
+    <row r="184" spans="1:5" ht="34.5" hidden="1">
       <c r="B184" s="43" t="s">
         <v>1465</v>
       </c>
@@ -18592,77 +18674,77 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="19.2" hidden="1">
+    <row r="186" spans="1:5" ht="17.25" hidden="1">
       <c r="B186" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="38.4" hidden="1">
+    <row r="187" spans="1:5" ht="34.5" hidden="1">
       <c r="B187" s="43" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="57.6" hidden="1">
+    <row r="188" spans="1:5" ht="51.75" hidden="1">
       <c r="B188" s="43" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="57.6" hidden="1">
+    <row r="189" spans="1:5" ht="51.75" hidden="1">
       <c r="B189" s="43" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="19.2" hidden="1">
+    <row r="190" spans="1:5" ht="17.25" hidden="1">
       <c r="B190" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="38.4" hidden="1">
+    <row r="191" spans="1:5" ht="34.5" hidden="1">
       <c r="B191" s="43" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="38.4" hidden="1">
+    <row r="192" spans="1:5" ht="34.5" hidden="1">
       <c r="B192" s="43" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="38.4" hidden="1">
+    <row r="193" spans="1:5" ht="34.5" hidden="1">
       <c r="B193" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="76.8" hidden="1">
+    <row r="194" spans="1:5" ht="69" hidden="1">
       <c r="B194" s="43" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="19.2" hidden="1">
+    <row r="195" spans="1:5" ht="17.25" hidden="1">
       <c r="B195" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="38.4" hidden="1">
+    <row r="196" spans="1:5" ht="34.5" hidden="1">
       <c r="B196" s="43" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="38.4" hidden="1">
+    <row r="197" spans="1:5" ht="34.5" hidden="1">
       <c r="B197" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="57.6" hidden="1">
+    <row r="198" spans="1:5" ht="51.75" hidden="1">
       <c r="B198" s="43" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="38.4" hidden="1">
+    <row r="199" spans="1:5" ht="34.5" hidden="1">
       <c r="B199" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="57.6" hidden="1">
+    <row r="200" spans="1:5" ht="51.75" hidden="1">
       <c r="B200" s="43" t="s">
         <v>1475</v>
       </c>
@@ -18685,77 +18767,77 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="19.2" hidden="1">
+    <row r="202" spans="1:5" ht="17.25" hidden="1">
       <c r="B202" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="57.6" hidden="1">
+    <row r="203" spans="1:5" ht="51.75" hidden="1">
       <c r="B203" s="43" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="57.6" hidden="1">
+    <row r="204" spans="1:5" ht="51.75" hidden="1">
       <c r="B204" s="43" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="57.6" hidden="1">
+    <row r="205" spans="1:5" ht="51.75" hidden="1">
       <c r="B205" s="43" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="19.2" hidden="1">
+    <row r="206" spans="1:5" ht="17.25" hidden="1">
       <c r="B206" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="38.4" hidden="1">
+    <row r="207" spans="1:5" ht="34.5" hidden="1">
       <c r="B207" s="43" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="57.6" hidden="1">
+    <row r="208" spans="1:5" ht="51.75" hidden="1">
       <c r="B208" s="43" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="38.4" hidden="1">
+    <row r="209" spans="1:5" ht="34.5" hidden="1">
       <c r="B209" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="57.6" hidden="1">
+    <row r="210" spans="1:5" ht="51.75" hidden="1">
       <c r="B210" s="43" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="19.2" hidden="1">
+    <row r="211" spans="1:5" ht="17.25" hidden="1">
       <c r="B211" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="38.4" hidden="1">
+    <row r="212" spans="1:5" ht="34.5" hidden="1">
       <c r="B212" s="43" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="38.4" hidden="1">
+    <row r="213" spans="1:5" ht="34.5" hidden="1">
       <c r="B213" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="57.6" hidden="1">
+    <row r="214" spans="1:5" ht="51.75" hidden="1">
       <c r="B214" s="43" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="38.4" hidden="1">
+    <row r="215" spans="1:5" ht="34.5" hidden="1">
       <c r="B215" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="57.6" hidden="1">
+    <row r="216" spans="1:5" ht="51.75" hidden="1">
       <c r="B216" s="43" t="s">
         <v>1485</v>
       </c>
@@ -18778,97 +18860,162 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="19.2" hidden="1">
+    <row r="218" spans="1:5" ht="17.25" hidden="1">
       <c r="B218" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="57.6" hidden="1">
+    <row r="219" spans="1:5" ht="51.75" hidden="1">
       <c r="B219" s="43" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="57.6" hidden="1">
+    <row r="220" spans="1:5" ht="51.75" hidden="1">
       <c r="B220" s="43" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="38.4" hidden="1">
+    <row r="221" spans="1:5" ht="34.5" hidden="1">
       <c r="B221" s="43" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="76.8" hidden="1">
+    <row r="222" spans="1:5" ht="86.25" hidden="1">
       <c r="B222" s="43" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="57.6" hidden="1">
+    <row r="223" spans="1:5" ht="51.75" hidden="1">
       <c r="B223" s="43" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="19.2" hidden="1">
+    <row r="224" spans="1:5" ht="17.25" hidden="1">
       <c r="B224" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="225" spans="2:2" ht="38.4" hidden="1">
+    <row r="225" spans="2:2" ht="34.5" hidden="1">
       <c r="B225" s="43" t="s">
         <v>1492</v>
       </c>
     </row>
-    <row r="226" spans="2:2" ht="38.4" hidden="1">
+    <row r="226" spans="2:2" ht="34.5" hidden="1">
       <c r="B226" s="43" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="227" spans="2:2" ht="38.4" hidden="1">
+    <row r="227" spans="2:2" ht="34.5" hidden="1">
       <c r="B227" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="228" spans="2:2" ht="57.6" hidden="1">
+    <row r="228" spans="2:2" ht="51.75" hidden="1">
       <c r="B228" s="43" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="229" spans="2:2" ht="38.4" hidden="1">
+    <row r="229" spans="2:2" ht="34.5" hidden="1">
       <c r="B229" s="43" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="230" spans="2:2" ht="19.2" hidden="1">
+    <row r="230" spans="2:2" ht="17.25" hidden="1">
       <c r="B230" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="231" spans="2:2" ht="38.4" hidden="1">
+    <row r="231" spans="2:2" ht="34.5" hidden="1">
       <c r="B231" s="43" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="232" spans="2:2" ht="38.4" hidden="1">
+    <row r="232" spans="2:2" ht="34.5" hidden="1">
       <c r="B232" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="233" spans="2:2" ht="57.6" hidden="1">
+    <row r="233" spans="2:2" ht="51.75" hidden="1">
       <c r="B233" s="43" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="234" spans="2:2" ht="38.4" hidden="1">
+    <row r="234" spans="2:2" ht="34.5" hidden="1">
       <c r="B234" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="235" spans="2:2" ht="38.4" hidden="1">
+    <row r="235" spans="2:2" ht="51.75" hidden="1">
       <c r="B235" s="43" t="s">
         <v>1498</v>
       </c>
     </row>
     <row r="236" spans="2:2" hidden="1"/>
+    <row r="243" spans="1:1">
+      <c r="A243" s="16" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="16" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="16" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="16" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="16" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="16" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="16" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="16" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="16" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="16" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="16" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="16" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="16" t="s">
+        <v>1650</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B236" xr:uid="{0D1590E3-1708-4563-889F-3AD6ACE1A716}">
     <filterColumn colId="0">
@@ -18884,17 +19031,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725EF9E2-7A77-45FF-B8A4-13516A0F9DA0}">
   <dimension ref="A4:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="155.88671875" customWidth="1"/>
+    <col min="1" max="1" width="155.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:1" ht="409.6">
+    <row r="4" spans="1:1" ht="409.5">
       <c r="A4" s="14" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="409.6">
+    <row r="7" spans="1:1" ht="409.5">
       <c r="A7" s="46" t="s">
         <v>1514</v>
       </c>
@@ -18907,12 +19054,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB3911-F8E7-4083-974C-8215A8CA05BB}">
   <dimension ref="A4:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="112.6640625" customWidth="1"/>
+    <col min="2" max="2" width="112.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:2" ht="244.8">
+    <row r="4" spans="1:2" ht="255">
       <c r="A4" t="s">
         <v>400</v>
       </c>
@@ -18920,7 +19067,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="409.6">
+    <row r="10" spans="1:2" ht="409.5">
       <c r="A10" t="s">
         <v>401</v>
       </c>
@@ -18936,22 +19083,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
   <dimension ref="A1:Q404"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="3" max="3" width="29.109375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5546875" customWidth="1"/>
-    <col min="7" max="8" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="39.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="39.5546875" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" customWidth="1"/>
+    <col min="7" max="8" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.2" thickBot="1">
+    <row r="1" spans="1:11" ht="16.5" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>760</v>
       </c>
@@ -18982,7 +19129,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="31.2" thickBot="1">
+    <row r="2" spans="1:11" ht="31.5" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -19013,7 +19160,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="31.2" thickBot="1">
+    <row r="3" spans="1:11" ht="31.5" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>119</v>
       </c>
@@ -19041,7 +19188,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="31.2" thickBot="1">
+    <row r="4" spans="1:11" ht="31.5" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -19069,7 +19216,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="46.2" thickBot="1">
+    <row r="5" spans="1:11" ht="46.5" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -19097,7 +19244,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="31.2" thickBot="1">
+    <row r="6" spans="1:11" ht="31.5" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>119</v>
       </c>
@@ -19125,7 +19272,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="31.2" thickBot="1">
+    <row r="7" spans="1:11" ht="31.5" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -19153,7 +19300,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="31.2" thickBot="1">
+    <row r="8" spans="1:11" ht="31.5" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
@@ -19181,7 +19328,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="31.2" thickBot="1">
+    <row r="9" spans="1:11" ht="31.5" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -19209,7 +19356,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="31.2" thickBot="1">
+    <row r="10" spans="1:11" ht="31.5" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>119</v>
       </c>
@@ -19237,7 +19384,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.2" thickBot="1">
+    <row r="11" spans="1:11" ht="31.5" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
@@ -19265,7 +19412,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="31.2" thickBot="1">
+    <row r="12" spans="1:11" ht="31.5" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>119</v>
       </c>
@@ -19293,7 +19440,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="31.2" thickBot="1">
+    <row r="13" spans="1:11" ht="31.5" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>119</v>
       </c>
@@ -19321,7 +19468,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="31.2" thickBot="1">
+    <row r="14" spans="1:11" ht="31.5" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -19349,7 +19496,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="31.2" thickBot="1">
+    <row r="15" spans="1:11" ht="31.5" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
@@ -19377,7 +19524,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="31.2" thickBot="1">
+    <row r="16" spans="1:11" ht="31.5" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>119</v>
       </c>
@@ -19405,7 +19552,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="31.2" thickBot="1">
+    <row r="17" spans="1:17" ht="31.5" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
@@ -19433,7 +19580,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="31.2" thickBot="1">
+    <row r="18" spans="1:17" ht="46.5" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
@@ -19461,7 +19608,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="31.2" thickBot="1">
+    <row r="19" spans="1:17" ht="31.5" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>119</v>
       </c>
@@ -19489,7 +19636,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="31.2" thickBot="1">
+    <row r="20" spans="1:17" ht="31.5" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -19517,7 +19664,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="31.2" thickBot="1">
+    <row r="21" spans="1:17" ht="31.5" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>119</v>
       </c>
@@ -19545,7 +19692,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="31.2" thickBot="1">
+    <row r="22" spans="1:17" ht="31.5" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>119</v>
       </c>
@@ -19573,7 +19720,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="31.2" thickBot="1">
+    <row r="23" spans="1:17" ht="31.5" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -19601,7 +19748,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="31.2" thickBot="1">
+    <row r="24" spans="1:17" ht="31.5" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -19636,7 +19783,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="31.2" thickBot="1">
+    <row r="25" spans="1:17" ht="31.5" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>120</v>
       </c>
@@ -19671,7 +19818,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="31.2" thickBot="1">
+    <row r="26" spans="1:17" ht="31.5" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>120</v>
       </c>
@@ -19706,7 +19853,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="31.2" thickBot="1">
+    <row r="27" spans="1:17" ht="31.5" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>120</v>
       </c>
@@ -19741,7 +19888,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="31.2" thickBot="1">
+    <row r="28" spans="1:17" ht="31.5" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>120</v>
       </c>
@@ -19776,7 +19923,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="31.2" thickBot="1">
+    <row r="29" spans="1:17" ht="31.5" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>120</v>
       </c>
@@ -19811,7 +19958,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="31.2" thickBot="1">
+    <row r="30" spans="1:17" ht="31.5" thickBot="1">
       <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
@@ -19846,7 +19993,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="31.2" thickBot="1">
+    <row r="31" spans="1:17" ht="31.5" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
@@ -19881,7 +20028,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="31.2" thickBot="1">
+    <row r="32" spans="1:17" ht="31.5" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
@@ -19916,7 +20063,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="31.2" thickBot="1">
+    <row r="33" spans="1:17" ht="31.5" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>120</v>
       </c>
@@ -19951,7 +20098,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="31.2" thickBot="1">
+    <row r="34" spans="1:17" ht="31.5" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -19986,7 +20133,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="31.2" thickBot="1">
+    <row r="35" spans="1:17" ht="31.5" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>120</v>
       </c>
@@ -20021,7 +20168,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="31.2" thickBot="1">
+    <row r="36" spans="1:17" ht="31.5" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -20056,7 +20203,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="31.2" thickBot="1">
+    <row r="37" spans="1:17" ht="31.5" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>120</v>
       </c>
@@ -20091,7 +20238,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="31.2" thickBot="1">
+    <row r="38" spans="1:17" ht="31.5" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>120</v>
       </c>
@@ -20126,7 +20273,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="31.2" thickBot="1">
+    <row r="39" spans="1:17" ht="31.5" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
@@ -20161,7 +20308,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="31.2" thickBot="1">
+    <row r="40" spans="1:17" ht="31.5" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>120</v>
       </c>
@@ -20196,7 +20343,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="31.2" thickBot="1">
+    <row r="41" spans="1:17" ht="31.5" thickBot="1">
       <c r="A41" s="6" t="s">
         <v>121</v>
       </c>
@@ -20228,7 +20375,7 @@
         <v>TS-UC-SEC-MCP-003test_001_query_under_5s_allowed</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="31.2" thickBot="1">
+    <row r="42" spans="1:17" ht="31.5" thickBot="1">
       <c r="A42" s="6" t="s">
         <v>121</v>
       </c>
@@ -20260,7 +20407,7 @@
         <v>TS-UC-SEC-MCP-003test_002_query_at_5s_allowed</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="31.2" thickBot="1">
+    <row r="43" spans="1:17" ht="31.5" thickBot="1">
       <c r="A43" s="6" t="s">
         <v>121</v>
       </c>
@@ -20292,7 +20439,7 @@
         <v>TS-UC-SEC-MCP-003test_003_query_over_5s_timeout_cancelled</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="31.2" thickBot="1">
+    <row r="44" spans="1:17" ht="31.5" thickBot="1">
       <c r="A44" s="6" t="s">
         <v>121</v>
       </c>
@@ -20324,7 +20471,7 @@
         <v>TS-UC-SEC-MCP-003test_004_query_result_under_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="31.2" thickBot="1">
+    <row r="45" spans="1:17" ht="31.5" thickBot="1">
       <c r="A45" s="6" t="s">
         <v>121</v>
       </c>
@@ -20356,7 +20503,7 @@
         <v>TS-UC-SEC-MCP-003test_005_query_result_at_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="31.2" thickBot="1">
+    <row r="46" spans="1:17" ht="31.5" thickBot="1">
       <c r="A46" s="6" t="s">
         <v>121</v>
       </c>
@@ -20388,7 +20535,7 @@
         <v>TS-UC-SEC-MCP-003test_006_query_result_over_1000_rows_truncated</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="31.2" thickBot="1">
+    <row r="47" spans="1:17" ht="31.5" thickBot="1">
       <c r="A47" s="6" t="s">
         <v>121</v>
       </c>
@@ -20420,7 +20567,7 @@
         <v>TS-UC-SEC-MCP-003test_007_query_result_truncated_flag_set</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="31.2" thickBot="1">
+    <row r="48" spans="1:17" ht="31.5" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>121</v>
       </c>
@@ -20452,7 +20599,7 @@
         <v>TS-UC-SEC-MCP-003test_008_timeout_returns_partial_results</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="31.2" thickBot="1">
+    <row r="49" spans="1:11" ht="31.5" thickBot="1">
       <c r="A49" s="6" t="s">
         <v>121</v>
       </c>
@@ -20484,7 +20631,7 @@
         <v>TS-UC-SEC-MCP-003test_009_timeout_audit_log_created</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="31.2" thickBot="1">
+    <row r="50" spans="1:11" ht="31.5" thickBot="1">
       <c r="A50" s="6" t="s">
         <v>121</v>
       </c>
@@ -20516,7 +20663,7 @@
         <v>TS-UC-SEC-MCP-003test_010_row_limit_audit_log_created</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="31.2" thickBot="1">
+    <row r="51" spans="1:11" ht="31.5" thickBot="1">
       <c r="A51" s="6" t="s">
         <v>121</v>
       </c>
@@ -20548,7 +20695,7 @@
         <v>TS-UC-SEC-MCP-003test_011_combined_timeout_and_row_limit</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="31.2" thickBot="1">
+    <row r="52" spans="1:11" ht="31.5" thickBot="1">
       <c r="A52" s="6" t="s">
         <v>121</v>
       </c>
@@ -20580,7 +20727,7 @@
         <v>TS-UC-SEC-MCP-003test_012_query_limit_config_per_tenant</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="31.2" thickBot="1">
+    <row r="53" spans="1:11" ht="31.5" thickBot="1">
       <c r="A53" s="6" t="s">
         <v>121</v>
       </c>
@@ -20612,7 +20759,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_001_exactly_1000_rows</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="31.2" thickBot="1">
+    <row r="54" spans="1:11" ht="31.5" thickBot="1">
       <c r="A54" s="6" t="s">
         <v>121</v>
       </c>
@@ -20644,7 +20791,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_002_empty_result_set</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="31.2" thickBot="1">
+    <row r="55" spans="1:11" ht="31.5" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>121</v>
       </c>
@@ -20676,7 +20823,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_003_streaming_query_timeout</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="31.2" thickBot="1">
+    <row r="56" spans="1:11" ht="31.5" thickBot="1">
       <c r="A56" s="6" t="s">
         <v>123</v>
       </c>
@@ -20708,7 +20855,7 @@
         <v>TS-UC-SEC-ANO-001test_001_detect_dni_valid_12345678Z</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="31.2" thickBot="1">
+    <row r="57" spans="1:11" ht="31.5" thickBot="1">
       <c r="A57" s="6" t="s">
         <v>123</v>
       </c>
@@ -20740,7 +20887,7 @@
         <v>TS-UC-SEC-ANO-001test_002_detect_dni_valid_87654321X</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="31.2" thickBot="1">
+    <row r="58" spans="1:11" ht="31.5" thickBot="1">
       <c r="A58" s="6" t="s">
         <v>123</v>
       </c>
@@ -20772,7 +20919,7 @@
         <v>TS-UC-SEC-ANO-001test_003_detect_dni_invalid_length_9_digits</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="31.2" thickBot="1">
+    <row r="59" spans="1:11" ht="31.5" thickBot="1">
       <c r="A59" s="6" t="s">
         <v>123</v>
       </c>
@@ -20804,7 +20951,7 @@
         <v>TS-UC-SEC-ANO-001test_004_detect_dni_invalid_length_7_digits</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="31.2" thickBot="1">
+    <row r="60" spans="1:11" ht="31.5" thickBot="1">
       <c r="A60" s="6" t="s">
         <v>123</v>
       </c>
@@ -20836,7 +20983,7 @@
         <v>TS-UC-SEC-ANO-001test_005_detect_dni_invalid_letter_checksum</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="31.2" thickBot="1">
+    <row r="61" spans="1:11" ht="31.5" thickBot="1">
       <c r="A61" s="6" t="s">
         <v>123</v>
       </c>
@@ -20868,7 +21015,7 @@
         <v>TS-UC-SEC-ANO-001test_006_detect_multiple_dnis_in_text</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="31.2" thickBot="1">
+    <row r="62" spans="1:11" ht="31.5" thickBot="1">
       <c r="A62" s="6" t="s">
         <v>123</v>
       </c>
@@ -20900,7 +21047,7 @@
         <v>TS-UC-SEC-ANO-001test_007_detect_email_simple</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="31.2" thickBot="1">
+    <row r="63" spans="1:11" ht="31.5" thickBot="1">
       <c r="A63" s="6" t="s">
         <v>123</v>
       </c>
@@ -20932,7 +21079,7 @@
         <v>TS-UC-SEC-ANO-001test_008_detect_email_with_subdomain</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="31.2" thickBot="1">
+    <row r="64" spans="1:11" ht="31.5" thickBot="1">
       <c r="A64" s="6" t="s">
         <v>123</v>
       </c>
@@ -20964,7 +21111,7 @@
         <v>TS-UC-SEC-ANO-001test_009_detect_email_with_plus_sign</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="31.2" thickBot="1">
+    <row r="65" spans="1:11" ht="31.5" thickBot="1">
       <c r="A65" s="6" t="s">
         <v>123</v>
       </c>
@@ -20996,7 +21143,7 @@
         <v>TS-UC-SEC-ANO-001test_010_detect_email_invalid_no_at</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="31.2" thickBot="1">
+    <row r="66" spans="1:11" ht="31.5" thickBot="1">
       <c r="A66" s="6" t="s">
         <v>123</v>
       </c>
@@ -21028,7 +21175,7 @@
         <v>TS-UC-SEC-ANO-001test_011_detect_multiple_emails_in_text</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="31.2" thickBot="1">
+    <row r="67" spans="1:11" ht="31.5" thickBot="1">
       <c r="A67" s="6" t="s">
         <v>123</v>
       </c>
@@ -21060,7 +21207,7 @@
         <v>TS-UC-SEC-ANO-001test_012_detect_phone_mobile_612345678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="31.2" thickBot="1">
+    <row r="68" spans="1:11" ht="31.5" thickBot="1">
       <c r="A68" s="6" t="s">
         <v>123</v>
       </c>
@@ -21092,7 +21239,7 @@
         <v>TS-UC-SEC-ANO-001test_013_detect_phone_mobile_with_prefix_34</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="31.2" thickBot="1">
+    <row r="69" spans="1:11" ht="31.5" thickBot="1">
       <c r="A69" s="6" t="s">
         <v>123</v>
       </c>
@@ -21124,7 +21271,7 @@
         <v>TS-UC-SEC-ANO-001test_014_detect_phone_landline_912345678</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="31.2" thickBot="1">
+    <row r="70" spans="1:11" ht="31.5" thickBot="1">
       <c r="A70" s="6" t="s">
         <v>123</v>
       </c>
@@ -21156,7 +21303,7 @@
         <v>TS-UC-SEC-ANO-001test_015_detect_phone_invalid_short</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="31.2" thickBot="1">
+    <row r="71" spans="1:11" ht="31.5" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>123</v>
       </c>
@@ -21188,7 +21335,7 @@
         <v>TS-UC-SEC-ANO-001test_016_detect_multiple_phones_in_text</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="31.2" thickBot="1">
+    <row r="72" spans="1:11" ht="31.5" thickBot="1">
       <c r="A72" s="6" t="s">
         <v>123</v>
       </c>
@@ -21220,7 +21367,7 @@
         <v>TS-UC-SEC-ANO-001test_017_detect_iban_spain_valid</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="31.2" thickBot="1">
+    <row r="73" spans="1:11" ht="31.5" thickBot="1">
       <c r="A73" s="6" t="s">
         <v>123</v>
       </c>
@@ -21252,7 +21399,7 @@
         <v>TS-UC-SEC-ANO-001test_018_detect_iban_germany_valid</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="31.2" thickBot="1">
+    <row r="74" spans="1:11" ht="31.5" thickBot="1">
       <c r="A74" s="6" t="s">
         <v>123</v>
       </c>
@@ -21284,7 +21431,7 @@
         <v>TS-UC-SEC-ANO-001test_019_detect_iban_invalid_checksum</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="31.2" thickBot="1">
+    <row r="75" spans="1:11" ht="31.5" thickBot="1">
       <c r="A75" s="6" t="s">
         <v>123</v>
       </c>
@@ -21316,7 +21463,7 @@
         <v>TS-UC-SEC-ANO-001test_020_detect_iban_invalid_length</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="31.2" thickBot="1">
+    <row r="76" spans="1:11" ht="31.5" thickBot="1">
       <c r="A76" s="6" t="s">
         <v>123</v>
       </c>
@@ -21348,7 +21495,7 @@
         <v>TS-UC-SEC-ANO-001test_021_detect_all_pii_types_in_document</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="31.2" thickBot="1">
+    <row r="77" spans="1:11" ht="31.5" thickBot="1">
       <c r="A77" s="6" t="s">
         <v>123</v>
       </c>
@@ -21380,7 +21527,7 @@
         <v>TS-UC-SEC-ANO-001test_022_detect_no_pii_clean_document</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="31.2" thickBot="1">
+    <row r="78" spans="1:11" ht="31.5" thickBot="1">
       <c r="A78" s="6" t="s">
         <v>123</v>
       </c>
@@ -21412,7 +21559,7 @@
         <v>TS-UC-SEC-ANO-001test_023_detect_pii_positions_returned</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="31.2" thickBot="1">
+    <row r="79" spans="1:11" ht="31.5" thickBot="1">
       <c r="A79" s="6" t="s">
         <v>123</v>
       </c>
@@ -21444,7 +21591,7 @@
         <v>TS-UC-SEC-ANO-001test_024_detect_pii_counts_by_type</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="31.2" thickBot="1">
+    <row r="80" spans="1:11" ht="31.5" thickBot="1">
       <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
@@ -21476,7 +21623,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_001_pii_in_different_languages</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="31.2" thickBot="1">
+    <row r="81" spans="1:11" ht="31.5" thickBot="1">
       <c r="A81" s="6" t="s">
         <v>123</v>
       </c>
@@ -21508,7 +21655,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_002_pii_with_unicode_characters</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="31.2" thickBot="1">
+    <row r="82" spans="1:11" ht="31.5" thickBot="1">
       <c r="A82" s="6" t="s">
         <v>123</v>
       </c>
@@ -21531,7 +21678,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_003_pii_in_html_escaped_text</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="31.2" thickBot="1">
+    <row r="83" spans="1:11" ht="31.5" thickBot="1">
       <c r="A83" s="6" t="s">
         <v>124</v>
       </c>
@@ -21560,7 +21707,7 @@
         <v>TS-UC-SEC-ANO-002test_001_redact_dni_to_redacted</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="31.2" thickBot="1">
+    <row r="84" spans="1:11" ht="31.5" thickBot="1">
       <c r="A84" s="6" t="s">
         <v>124</v>
       </c>
@@ -21589,7 +21736,7 @@
         <v>TS-UC-SEC-ANO-002test_002_redact_email_to_redacted</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="31.2" thickBot="1">
+    <row r="85" spans="1:11" ht="31.5" thickBot="1">
       <c r="A85" s="6" t="s">
         <v>124</v>
       </c>
@@ -21618,7 +21765,7 @@
         <v>TS-UC-SEC-ANO-002test_003_redact_phone_to_redacted</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="31.2" thickBot="1">
+    <row r="86" spans="1:11" ht="31.5" thickBot="1">
       <c r="A86" s="6" t="s">
         <v>124</v>
       </c>
@@ -21647,7 +21794,7 @@
         <v>TS-UC-SEC-ANO-002test_004_redact_multiple_pii_all_redacted</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="31.2" thickBot="1">
+    <row r="87" spans="1:11" ht="31.5" thickBot="1">
       <c r="A87" s="6" t="s">
         <v>124</v>
       </c>
@@ -21676,7 +21823,7 @@
         <v>TS-UC-SEC-ANO-002test_005_hash_dni_deterministic</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="31.2" thickBot="1">
+    <row r="88" spans="1:11" ht="31.5" thickBot="1">
       <c r="A88" s="6" t="s">
         <v>124</v>
       </c>
@@ -21705,7 +21852,7 @@
         <v>TS-UC-SEC-ANO-002test_006_hash_same_value_same_hash</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="31.2" thickBot="1">
+    <row r="89" spans="1:11" ht="31.5" thickBot="1">
       <c r="A89" s="6" t="s">
         <v>124</v>
       </c>
@@ -21734,7 +21881,7 @@
         <v>TS-UC-SEC-ANO-002test_007_hash_different_values_different_hash</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="31.2" thickBot="1">
+    <row r="90" spans="1:11" ht="31.5" thickBot="1">
       <c r="A90" s="6" t="s">
         <v>124</v>
       </c>
@@ -21763,7 +21910,7 @@
         <v>TS-UC-SEC-ANO-002test_008_hash_irreversible_validation</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="31.2" thickBot="1">
+    <row r="91" spans="1:11" ht="31.5" thickBot="1">
       <c r="A91" s="6" t="s">
         <v>124</v>
       </c>
@@ -21792,7 +21939,7 @@
         <v>TS-UC-SEC-ANO-002test_009_pseudonymize_name_to_persona_001</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="31.2" thickBot="1">
+    <row r="92" spans="1:11" ht="31.5" thickBot="1">
       <c r="A92" s="6" t="s">
         <v>124</v>
       </c>
@@ -21821,7 +21968,7 @@
         <v>TS-UC-SEC-ANO-002test_010_pseudonymize_consistent_same_name</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="31.2" thickBot="1">
+    <row r="93" spans="1:11" ht="46.5" thickBot="1">
       <c r="A93" s="6" t="s">
         <v>124</v>
       </c>
@@ -21850,7 +21997,7 @@
         <v>TS-UC-SEC-ANO-002test_011_pseudonymize_different_names_different_ids</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="31.2" thickBot="1">
+    <row r="94" spans="1:11" ht="31.5" thickBot="1">
       <c r="A94" s="6" t="s">
         <v>124</v>
       </c>
@@ -21879,7 +22026,7 @@
         <v>TS-UC-SEC-ANO-002test_012_pseudonymize_in_context_preserved</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="31.2" thickBot="1">
+    <row r="95" spans="1:11" ht="31.5" thickBot="1">
       <c r="A95" s="6" t="s">
         <v>124</v>
       </c>
@@ -21908,7 +22055,7 @@
         <v>TS-UC-SEC-ANO-002test_013_strategy_by_pii_type_default</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="31.2" thickBot="1">
+    <row r="96" spans="1:11" ht="31.5" thickBot="1">
       <c r="A96" s="6" t="s">
         <v>124</v>
       </c>
@@ -21937,7 +22084,7 @@
         <v>TS-UC-SEC-ANO-002test_014_strategy_by_tenant_config</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="31.2" thickBot="1">
+    <row r="97" spans="1:11" ht="31.5" thickBot="1">
       <c r="A97" s="6" t="s">
         <v>124</v>
       </c>
@@ -21966,7 +22113,7 @@
         <v>TS-UC-SEC-ANO-002test_015_strategy_mixed_per_type</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="31.2" thickBot="1">
+    <row r="98" spans="1:11" ht="31.5" thickBot="1">
       <c r="A98" s="6" t="s">
         <v>124</v>
       </c>
@@ -21995,7 +22142,7 @@
         <v>TS-UC-SEC-ANO-002test_016_strategy_none_keeps_original</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="31.2" thickBot="1">
+    <row r="99" spans="1:11" ht="31.5" thickBot="1">
       <c r="A99" s="6" t="s">
         <v>124</v>
       </c>
@@ -22024,7 +22171,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_001_nested_pii_in_pii</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="31.2" thickBot="1">
+    <row r="100" spans="1:11" ht="31.5" thickBot="1">
       <c r="A100" s="6" t="s">
         <v>124</v>
       </c>
@@ -22053,7 +22200,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_002_overlapping_pii_positions</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="31.2" thickBot="1">
+    <row r="101" spans="1:11" ht="31.5" thickBot="1">
       <c r="A101" s="6" t="s">
         <v>124</v>
       </c>
@@ -22082,7 +22229,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_003_empty_text_no_error</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16.2" thickBot="1">
+    <row r="102" spans="1:11" ht="16.5" thickBot="1">
       <c r="A102" s="6" t="s">
         <v>125</v>
       </c>
@@ -22111,7 +22258,7 @@
         <v>TS-UC-SEC-ANO-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16.2" thickBot="1">
+    <row r="103" spans="1:11" ht="16.5" thickBot="1">
       <c r="A103" s="6" t="s">
         <v>126</v>
       </c>
@@ -22140,7 +22287,7 @@
         <v>TS-UC-SEC-TNT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16.2" thickBot="1">
+    <row r="104" spans="1:11" ht="16.5" thickBot="1">
       <c r="A104" s="6" t="s">
         <v>127</v>
       </c>
@@ -22166,7 +22313,7 @@
         <v>TS-UC-SEC-JWT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16.2" thickBot="1">
+    <row r="105" spans="1:11" ht="16.5" thickBot="1">
       <c r="A105" s="6" t="s">
         <v>128</v>
       </c>
@@ -22192,7 +22339,7 @@
         <v>TS-UC-SEC-AUD-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="31.2" thickBot="1">
+    <row r="106" spans="1:11" ht="31.5" thickBot="1">
       <c r="A106" s="6" t="s">
         <v>129</v>
       </c>
@@ -22221,7 +22368,7 @@
         <v>TS-UC-SEC-GAM-001test_001_mass_changes_11_in_hour_detected</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="31.2" thickBot="1">
+    <row r="107" spans="1:11" ht="31.5" thickBot="1">
       <c r="A107" s="6" t="s">
         <v>129</v>
       </c>
@@ -22250,7 +22397,7 @@
         <v>TS-UC-SEC-GAM-001test_002_mass_changes_10_in_hour_allowed</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="31.2" thickBot="1">
+    <row r="108" spans="1:11" ht="31.5" thickBot="1">
       <c r="A108" s="6" t="s">
         <v>129</v>
       </c>
@@ -22279,7 +22426,7 @@
         <v>TS-UC-SEC-GAM-001test_003_mass_changes_window_reset</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="31.2" thickBot="1">
+    <row r="109" spans="1:11" ht="31.5" thickBot="1">
       <c r="A109" s="6" t="s">
         <v>129</v>
       </c>
@@ -22308,7 +22455,7 @@
         <v>TS-UC-SEC-GAM-001test_004_resolve_reintroduce_3_times_detected</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="31.2" thickBot="1">
+    <row r="110" spans="1:11" ht="31.5" thickBot="1">
       <c r="A110" s="6" t="s">
         <v>129</v>
       </c>
@@ -22337,7 +22484,7 @@
         <v>TS-UC-SEC-GAM-001test_005_resolve_reintroduce_2_times_allowed</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="31.2" thickBot="1">
+    <row r="111" spans="1:11" ht="31.5" thickBot="1">
       <c r="A111" s="6" t="s">
         <v>129</v>
       </c>
@@ -22366,7 +22513,7 @@
         <v>TS-UC-SEC-GAM-001test_006_resolve_reintroduce_different_hash_allowed</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="31.2" thickBot="1">
+    <row r="112" spans="1:11" ht="31.5" thickBot="1">
       <c r="A112" s="6" t="s">
         <v>129</v>
       </c>
@@ -22395,7 +22542,7 @@
         <v>TS-UC-SEC-GAM-001test_007_high_score_few_docs_detected</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="31.2" thickBot="1">
+    <row r="113" spans="1:11" ht="31.5" thickBot="1">
       <c r="A113" s="6" t="s">
         <v>129</v>
       </c>
@@ -22424,7 +22571,7 @@
         <v>TS-UC-SEC-GAM-001test_008_high_score_many_docs_allowed</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="31.2" thickBot="1">
+    <row r="114" spans="1:11" ht="31.5" thickBot="1">
       <c r="A114" s="6" t="s">
         <v>129</v>
       </c>
@@ -22453,7 +22600,7 @@
         <v>TS-UC-SEC-GAM-001test_009_high_score_threshold_boundary</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="31.2" thickBot="1">
+    <row r="115" spans="1:11" ht="31.5" thickBot="1">
       <c r="A115" s="6" t="s">
         <v>129</v>
       </c>
@@ -22482,7 +22629,7 @@
         <v>TS-UC-SEC-GAM-001test_010_weight_change_25_percent_detected</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="31.2" thickBot="1">
+    <row r="116" spans="1:11" ht="31.5" thickBot="1">
       <c r="A116" s="6" t="s">
         <v>129</v>
       </c>
@@ -22511,7 +22658,7 @@
         <v>TS-UC-SEC-GAM-001test_011_weight_change_15_percent_allowed</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="31.2" thickBot="1">
+    <row r="117" spans="1:11" ht="31.5" thickBot="1">
       <c r="A117" s="6" t="s">
         <v>129</v>
       </c>
@@ -22540,7 +22687,7 @@
         <v>TS-UC-SEC-GAM-001test_012_weight_change_tracking_24h_window</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="31.2" thickBot="1">
+    <row r="118" spans="1:11" ht="31.5" thickBot="1">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -22569,7 +22716,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_001_multiple_violations_combined</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="31.2" thickBot="1">
+    <row r="119" spans="1:11" ht="31.5" thickBot="1">
       <c r="A119" s="6" t="s">
         <v>129</v>
       </c>
@@ -22598,7 +22745,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_002_violation_penalty_application</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="31.2" thickBot="1">
+    <row r="120" spans="1:11" ht="31.5" thickBot="1">
       <c r="A120" s="6" t="s">
         <v>129</v>
       </c>
@@ -22627,7 +22774,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_003_violation_audit_logging</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="31.2" thickBot="1">
+    <row r="121" spans="1:11" ht="31.5" thickBot="1">
       <c r="A121" s="6" t="s">
         <v>130</v>
       </c>
@@ -22659,7 +22806,7 @@
         <v>TS-UD-DOC-CLS-001test_001_clause_creation_with_all_fields</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="31.2" thickBot="1">
+    <row r="122" spans="1:11" ht="31.5" thickBot="1">
       <c r="A122" s="6" t="s">
         <v>130</v>
       </c>
@@ -22688,7 +22835,7 @@
         <v>TS-UD-DOC-CLS-001test_002_clause_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="31.2" thickBot="1">
+    <row r="123" spans="1:11" ht="31.5" thickBot="1">
       <c r="A123" s="6" t="s">
         <v>130</v>
       </c>
@@ -22717,7 +22864,7 @@
         <v>TS-UD-DOC-CLS-001test_003_clause_creation_fails_without_content</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="31.2" thickBot="1">
+    <row r="124" spans="1:11" ht="31.5" thickBot="1">
       <c r="A124" s="6" t="s">
         <v>130</v>
       </c>
@@ -22746,7 +22893,7 @@
         <v>TS-UD-DOC-CLS-001test_004_clause_creation_fails_without_document_id</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="31.2" thickBot="1">
+    <row r="125" spans="1:11" ht="31.5" thickBot="1">
       <c r="A125" s="6" t="s">
         <v>130</v>
       </c>
@@ -22775,7 +22922,7 @@
         <v>TS-UD-DOC-CLS-001test_005_clause_creation_fails_without_tenant_id</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="31.2" thickBot="1">
+    <row r="126" spans="1:11" ht="31.5" thickBot="1">
       <c r="A126" s="6" t="s">
         <v>130</v>
       </c>
@@ -22804,7 +22951,7 @@
         <v>TS-UD-DOC-CLS-001test_006_clause_immutability_after_creation</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="31.2" thickBot="1">
+    <row r="127" spans="1:11" ht="31.5" thickBot="1">
       <c r="A127" s="6" t="s">
         <v>130</v>
       </c>
@@ -22833,7 +22980,7 @@
         <v>TS-UD-DOC-CLS-001test_007_clause_number_format_primera</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="31.2" thickBot="1">
+    <row r="128" spans="1:11" ht="31.5" thickBot="1">
       <c r="A128" s="6" t="s">
         <v>130</v>
       </c>
@@ -22862,7 +23009,7 @@
         <v>TS-UD-DOC-CLS-001test_008_clause_number_format_numeric</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="31.2" thickBot="1">
+    <row r="129" spans="1:11" ht="31.5" thickBot="1">
       <c r="A129" s="6" t="s">
         <v>130</v>
       </c>
@@ -22891,7 +23038,7 @@
         <v>TS-UD-DOC-CLS-001test_009_clause_number_format_decimal</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="31.2" thickBot="1">
+    <row r="130" spans="1:11" ht="31.5" thickBot="1">
       <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
@@ -22920,7 +23067,7 @@
         <v>TS-UD-DOC-CLS-001test_010_clause_number_normalization</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="31.2" thickBot="1">
+    <row r="131" spans="1:11" ht="31.5" thickBot="1">
       <c r="A131" s="6" t="s">
         <v>130</v>
       </c>
@@ -22949,7 +23096,7 @@
         <v>TS-UD-DOC-CLS-001test_011_clause_content_max_length</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="31.2" thickBot="1">
+    <row r="132" spans="1:11" ht="31.5" thickBot="1">
       <c r="A132" s="6" t="s">
         <v>130</v>
       </c>
@@ -22978,7 +23125,7 @@
         <v>TS-UD-DOC-CLS-001test_012_clause_content_empty_rejected</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="31.2" thickBot="1">
+    <row r="133" spans="1:11" ht="31.5" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>130</v>
       </c>
@@ -23007,7 +23154,7 @@
         <v>TS-UD-DOC-CLS-001test_013_clause_document_fk_valid</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="31.2" thickBot="1">
+    <row r="134" spans="1:11" ht="31.5" thickBot="1">
       <c r="A134" s="6" t="s">
         <v>130</v>
       </c>
@@ -23036,7 +23183,7 @@
         <v>TS-UD-DOC-CLS-001test_014_clause_document_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="31.2" thickBot="1">
+    <row r="135" spans="1:11" ht="31.5" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>130</v>
       </c>
@@ -23065,7 +23212,7 @@
         <v>TS-UD-DOC-CLS-001test_015_clause_tenant_fk_valid</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="31.2" thickBot="1">
+    <row r="136" spans="1:11" ht="31.5" thickBot="1">
       <c r="A136" s="6" t="s">
         <v>130</v>
       </c>
@@ -23094,7 +23241,7 @@
         <v>TS-UD-DOC-CLS-001test_016_clause_tenant_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="31.2" thickBot="1">
+    <row r="137" spans="1:11" ht="31.5" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>130</v>
       </c>
@@ -23123,7 +23270,7 @@
         <v>TS-UD-DOC-CLS-001test_017_clause_on_delete_restrict_document</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="31.2" thickBot="1">
+    <row r="138" spans="1:11" ht="31.5" thickBot="1">
       <c r="A138" s="6" t="s">
         <v>130</v>
       </c>
@@ -23152,7 +23299,7 @@
         <v>TS-UD-DOC-CLS-001test_018_clause_on_delete_restrict_tenant</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="31.2" thickBot="1">
+    <row r="139" spans="1:11" ht="31.5" thickBot="1">
       <c r="A139" s="6" t="s">
         <v>130</v>
       </c>
@@ -23181,7 +23328,7 @@
         <v>TS-UD-DOC-CLS-001test_019_clause_embedding_vector_size</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="31.2" thickBot="1">
+    <row r="140" spans="1:11" ht="31.5" thickBot="1">
       <c r="A140" s="6" t="s">
         <v>130</v>
       </c>
@@ -23210,7 +23357,7 @@
         <v>TS-UD-DOC-CLS-001test_020_clause_embedding_generation</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="31.2" thickBot="1">
+    <row r="141" spans="1:11" ht="31.5" thickBot="1">
       <c r="A141" s="6" t="s">
         <v>130</v>
       </c>
@@ -23239,7 +23386,7 @@
         <v>TS-UD-DOC-CLS-001test_021_clause_embedding_null_allowed</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="31.2" thickBot="1">
+    <row r="142" spans="1:11" ht="31.5" thickBot="1">
       <c r="A142" s="6" t="s">
         <v>130</v>
       </c>
@@ -23268,7 +23415,7 @@
         <v>TS-UD-DOC-CLS-001test_022_clause_embedding_update</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="16.2" thickBot="1">
+    <row r="143" spans="1:11" ht="16.5" thickBot="1">
       <c r="A143" s="6" t="s">
         <v>131</v>
       </c>
@@ -23297,7 +23444,7 @@
         <v>TS-UD-DOC-CLS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="16.2" thickBot="1">
+    <row r="144" spans="1:11" ht="16.5" thickBot="1">
       <c r="A144" s="6" t="s">
         <v>132</v>
       </c>
@@ -23323,7 +23470,7 @@
         <v>TS-UD-DOC-CLS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="31.2" thickBot="1">
+    <row r="145" spans="1:11" ht="31.5" thickBot="1">
       <c r="A145" s="6" t="s">
         <v>133</v>
       </c>
@@ -23352,7 +23499,7 @@
         <v>TS-UD-DOC-ENT-001test_001_date_dd_mm_yyyy_slash</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="31.2" thickBot="1">
+    <row r="146" spans="1:11" ht="31.5" thickBot="1">
       <c r="A146" s="6" t="s">
         <v>133</v>
       </c>
@@ -23381,7 +23528,7 @@
         <v>TS-UD-DOC-ENT-001test_002_date_yyyy_mm_dd_dash</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="31.2" thickBot="1">
+    <row r="147" spans="1:11" ht="31.5" thickBot="1">
       <c r="A147" s="6" t="s">
         <v>133</v>
       </c>
@@ -23410,7 +23557,7 @@
         <v>TS-UD-DOC-ENT-001test_003_date_dd_month_yyyy_spanish</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="31.2" thickBot="1">
+    <row r="148" spans="1:11" ht="31.5" thickBot="1">
       <c r="A148" s="6" t="s">
         <v>133</v>
       </c>
@@ -23439,7 +23586,7 @@
         <v>TS-UD-DOC-ENT-001test_004_date_month_dd_yyyy_english</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="31.2" thickBot="1">
+    <row r="149" spans="1:11" ht="31.5" thickBot="1">
       <c r="A149" s="6" t="s">
         <v>133</v>
       </c>
@@ -23468,7 +23615,7 @@
         <v>TS-UD-DOC-ENT-001test_005_date_relative_30_days</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="31.2" thickBot="1">
+    <row r="150" spans="1:11" ht="31.5" thickBot="1">
       <c r="A150" s="6" t="s">
         <v>133</v>
       </c>
@@ -23497,7 +23644,7 @@
         <v>TS-UD-DOC-ENT-001test_006_date_relative_3_months</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="31.2" thickBot="1">
+    <row r="151" spans="1:11" ht="31.5" thickBot="1">
       <c r="A151" s="6" t="s">
         <v>133</v>
       </c>
@@ -23526,7 +23673,7 @@
         <v>TS-UD-DOC-ENT-001test_007_date_relative_1_year</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="31.2" thickBot="1">
+    <row r="152" spans="1:11" ht="31.5" thickBot="1">
       <c r="A152" s="6" t="s">
         <v>133</v>
       </c>
@@ -23555,7 +23702,7 @@
         <v>TS-UD-DOC-ENT-001test_008_date_relative_from_date</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="31.2" thickBot="1">
+    <row r="153" spans="1:11" ht="31.5" thickBot="1">
       <c r="A153" s="6" t="s">
         <v>133</v>
       </c>
@@ -23584,7 +23731,7 @@
         <v>TS-UD-DOC-ENT-001test_009_date_context_entrega</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="31.2" thickBot="1">
+    <row r="154" spans="1:11" ht="31.5" thickBot="1">
       <c r="A154" s="6" t="s">
         <v>133</v>
       </c>
@@ -23613,7 +23760,7 @@
         <v>TS-UD-DOC-ENT-001test_010_date_context_firma</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="31.2" thickBot="1">
+    <row r="155" spans="1:11" ht="31.5" thickBot="1">
       <c r="A155" s="6" t="s">
         <v>133</v>
       </c>
@@ -23642,7 +23789,7 @@
         <v>TS-UD-DOC-ENT-001test_011_date_context_inicio</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="16.2" thickBot="1">
+    <row r="156" spans="1:11" ht="16.5" thickBot="1">
       <c r="A156" s="6" t="s">
         <v>133</v>
       </c>
@@ -23671,7 +23818,7 @@
         <v>TS-UD-DOC-ENT-001test_012_date_context_fin</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="31.2" thickBot="1">
+    <row r="157" spans="1:11" ht="31.5" thickBot="1">
       <c r="A157" s="6" t="s">
         <v>133</v>
       </c>
@@ -23700,7 +23847,7 @@
         <v>TS-UD-DOC-ENT-001test_013_multiple_dates_extraction</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="31.2" thickBot="1">
+    <row r="158" spans="1:11" ht="31.5" thickBot="1">
       <c r="A158" s="6" t="s">
         <v>133</v>
       </c>
@@ -23729,7 +23876,7 @@
         <v>TS-UD-DOC-ENT-001test_014_multiple_dates_ordering</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="31.2" thickBot="1">
+    <row r="159" spans="1:11" ht="31.5" thickBot="1">
       <c r="A159" s="6" t="s">
         <v>133</v>
       </c>
@@ -23758,7 +23905,7 @@
         <v>TS-UD-DOC-ENT-001test_015_date_range_extraction</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="31.2" thickBot="1">
+    <row r="160" spans="1:11" ht="31.5" thickBot="1">
       <c r="A160" s="6" t="s">
         <v>133</v>
       </c>
@@ -23787,7 +23934,7 @@
         <v>TS-UD-DOC-ENT-001test_016_date_invalid_format_ignored</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="31.2" thickBot="1">
+    <row r="161" spans="1:11" ht="31.5" thickBot="1">
       <c r="A161" s="6" t="s">
         <v>134</v>
       </c>
@@ -23816,7 +23963,7 @@
         <v>TS-UD-DOC-ENT-002test_001_money_eur_symbol_suffix</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="31.2" thickBot="1">
+    <row r="162" spans="1:11" ht="31.5" thickBot="1">
       <c r="A162" s="6" t="s">
         <v>134</v>
       </c>
@@ -23845,7 +23992,7 @@
         <v>TS-UD-DOC-ENT-002test_002_money_eur_symbol_prefix</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="31.2" thickBot="1">
+    <row r="163" spans="1:11" ht="31.5" thickBot="1">
       <c r="A163" s="6" t="s">
         <v>134</v>
       </c>
@@ -23874,7 +24021,7 @@
         <v>TS-UD-DOC-ENT-002test_003_money_eur_word_euros</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="31.2" thickBot="1">
+    <row r="164" spans="1:11" ht="31.5" thickBot="1">
       <c r="A164" s="6" t="s">
         <v>134</v>
       </c>
@@ -23903,7 +24050,7 @@
         <v>TS-UD-DOC-ENT-002test_004_money_eur_thousands_separator</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="31.2" thickBot="1">
+    <row r="165" spans="1:11" ht="31.5" thickBot="1">
       <c r="A165" s="6" t="s">
         <v>134</v>
       </c>
@@ -23932,7 +24079,7 @@
         <v>TS-UD-DOC-ENT-002test_005_money_usd_symbol</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="16.2" thickBot="1">
+    <row r="166" spans="1:11" ht="31.5" thickBot="1">
       <c r="A166" s="6" t="s">
         <v>134</v>
       </c>
@@ -23961,7 +24108,7 @@
         <v>TS-UD-DOC-ENT-002test_006_money_usd_word</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="31.2" thickBot="1">
+    <row r="167" spans="1:11" ht="31.5" thickBot="1">
       <c r="A167" s="6" t="s">
         <v>134</v>
       </c>
@@ -23990,7 +24137,7 @@
         <v>TS-UD-DOC-ENT-002test_007_money_usd_thousands_separator</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="31.2" thickBot="1">
+    <row r="168" spans="1:11" ht="31.5" thickBot="1">
       <c r="A168" s="6" t="s">
         <v>134</v>
       </c>
@@ -24019,7 +24166,7 @@
         <v>TS-UD-DOC-ENT-002test_008_money_context_anticipo</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="31.2" thickBot="1">
+    <row r="169" spans="1:11" ht="31.5" thickBot="1">
       <c r="A169" s="6" t="s">
         <v>134</v>
       </c>
@@ -24048,7 +24195,7 @@
         <v>TS-UD-DOC-ENT-002test_009_money_context_pago_final</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="31.2" thickBot="1">
+    <row r="170" spans="1:11" ht="31.5" thickBot="1">
       <c r="A170" s="6" t="s">
         <v>134</v>
       </c>
@@ -24077,7 +24224,7 @@
         <v>TS-UD-DOC-ENT-002test_010_money_context_penalizacion</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="31.2" thickBot="1">
+    <row r="171" spans="1:11" ht="31.5" thickBot="1">
       <c r="A171" s="6" t="s">
         <v>134</v>
       </c>
@@ -24106,7 +24253,7 @@
         <v>TS-UD-DOC-ENT-002test_011_money_context_total</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="31.2" thickBot="1">
+    <row r="172" spans="1:11" ht="31.5" thickBot="1">
       <c r="A172" s="6" t="s">
         <v>134</v>
       </c>
@@ -24135,7 +24282,7 @@
         <v>TS-UD-DOC-ENT-002test_012_multiple_amounts_extraction</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="31.2" thickBot="1">
+    <row r="173" spans="1:11" ht="31.5" thickBot="1">
       <c r="A173" s="6" t="s">
         <v>134</v>
       </c>
@@ -24164,7 +24311,7 @@
         <v>TS-UD-DOC-ENT-002test_013_money_percentage_extraction</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="31.2" thickBot="1">
+    <row r="174" spans="1:11" ht="31.5" thickBot="1">
       <c r="A174" s="6" t="s">
         <v>134</v>
       </c>
@@ -24193,7 +24340,7 @@
         <v>TS-UD-DOC-ENT-002test_014_money_negative_amount</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="16.2" thickBot="1">
+    <row r="175" spans="1:11" ht="16.5" thickBot="1">
       <c r="A175" s="6" t="s">
         <v>135</v>
       </c>
@@ -24214,7 +24361,7 @@
         <v>TS-UD-DOC-ENT-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="16.2" thickBot="1">
+    <row r="176" spans="1:11" ht="16.5" thickBot="1">
       <c r="A176" s="6" t="s">
         <v>136</v>
       </c>
@@ -24235,7 +24382,7 @@
         <v>TS-UD-DOC-ENT-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="16.2" thickBot="1">
+    <row r="177" spans="1:11" ht="16.5" thickBot="1">
       <c r="A177" s="6" t="s">
         <v>137</v>
       </c>
@@ -24256,7 +24403,7 @@
         <v>TS-UD-DOC-DOC-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="16.2" thickBot="1">
+    <row r="178" spans="1:11" ht="16.5" thickBot="1">
       <c r="A178" s="6" t="s">
         <v>138</v>
       </c>
@@ -24277,7 +24424,7 @@
         <v>TS-UD-DOC-CNF-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="16.2" thickBot="1">
+    <row r="179" spans="1:11" ht="16.5" thickBot="1">
       <c r="A179" s="6" t="s">
         <v>139</v>
       </c>
@@ -24298,7 +24445,7 @@
         <v>TS-UD-COH-CAT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="31.2" thickBot="1">
+    <row r="180" spans="1:11" ht="31.5" thickBot="1">
       <c r="A180" s="6" t="s">
         <v>140</v>
       </c>
@@ -24330,7 +24477,7 @@
         <v>TS-UD-COH-RUL-001test_001_r11_wbs_level4_no_activities_alert</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="31.2" thickBot="1">
+    <row r="181" spans="1:11" ht="31.5" thickBot="1">
       <c r="A181" s="6" t="s">
         <v>140</v>
       </c>
@@ -24359,7 +24506,7 @@
         <v>TS-UD-COH-RUL-001test_002_r11_wbs_level4_with_activities_pass</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="31.2" thickBot="1">
+    <row r="182" spans="1:11" ht="31.5" thickBot="1">
       <c r="A182" s="6" t="s">
         <v>140</v>
       </c>
@@ -24388,7 +24535,7 @@
         <v>TS-UD-COH-RUL-001test_003_r11_wbs_level3_no_activities_ignored</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="31.2" thickBot="1">
+    <row r="183" spans="1:11" ht="31.5" thickBot="1">
       <c r="A183" s="6" t="s">
         <v>140</v>
       </c>
@@ -24417,7 +24564,7 @@
         <v>TS-UD-COH-RUL-001test_004_r11_wbs_level2_no_activities_ignored</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="31.2" thickBot="1">
+    <row r="184" spans="1:11" ht="31.5" thickBot="1">
       <c r="A184" s="6" t="s">
         <v>140</v>
       </c>
@@ -24446,7 +24593,7 @@
         <v>TS-UD-COH-RUL-001test_005_r11_multiple_wbs_level4_violations</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="31.2" thickBot="1">
+    <row r="185" spans="1:11" ht="31.5" thickBot="1">
       <c r="A185" s="6" t="s">
         <v>140</v>
       </c>
@@ -24475,7 +24622,7 @@
         <v>TS-UD-COH-RUL-001test_006_r11_alert_severity_medium</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="31.2" thickBot="1">
+    <row r="186" spans="1:11" ht="31.5" thickBot="1">
       <c r="A186" s="6" t="s">
         <v>140</v>
       </c>
@@ -24504,7 +24651,7 @@
         <v>TS-UD-COH-RUL-001test_007_r12_wbs_no_budget_line_alert</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="31.2" thickBot="1">
+    <row r="187" spans="1:11" ht="31.5" thickBot="1">
       <c r="A187" s="6" t="s">
         <v>140</v>
       </c>
@@ -24533,7 +24680,7 @@
         <v>TS-UD-COH-RUL-001test_008_r12_wbs_with_budget_line_pass</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="31.2" thickBot="1">
+    <row r="188" spans="1:11" ht="31.5" thickBot="1">
       <c r="A188" s="6" t="s">
         <v>140</v>
       </c>
@@ -24562,7 +24709,7 @@
         <v>TS-UD-COH-RUL-001test_009_r12_wbs_budget_zero_warning</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="31.2" thickBot="1">
+    <row r="189" spans="1:11" ht="31.5" thickBot="1">
       <c r="A189" s="6" t="s">
         <v>140</v>
       </c>
@@ -24591,7 +24738,7 @@
         <v>TS-UD-COH-RUL-001test_010_r12_multiple_wbs_violations</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="31.2" thickBot="1">
+    <row r="190" spans="1:11" ht="31.5" thickBot="1">
       <c r="A190" s="6" t="s">
         <v>140</v>
       </c>
@@ -24620,7 +24767,7 @@
         <v>TS-UD-COH-RUL-001test_011_r12_alert_severity_high</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="31.2" thickBot="1">
+    <row r="191" spans="1:11" ht="31.5" thickBot="1">
       <c r="A191" s="6" t="s">
         <v>140</v>
       </c>
@@ -24649,7 +24796,7 @@
         <v>TS-UD-COH-RUL-001test_012_r12_affected_entities_list</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="31.2" thickBot="1">
+    <row r="192" spans="1:11" ht="31.5" thickBot="1">
       <c r="A192" s="6" t="s">
         <v>140</v>
       </c>
@@ -24678,7 +24825,7 @@
         <v>TS-UD-COH-RUL-001test_013_r13_scope_clause_no_wbs_alert</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="31.2" thickBot="1">
+    <row r="193" spans="1:11" ht="31.5" thickBot="1">
       <c r="A193" s="6" t="s">
         <v>140</v>
       </c>
@@ -24707,7 +24854,7 @@
         <v>TS-UD-COH-RUL-001test_014_r13_scope_clause_with_wbs_pass</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="31.2" thickBot="1">
+    <row r="194" spans="1:11" ht="31.5" thickBot="1">
       <c r="A194" s="6" t="s">
         <v>140</v>
       </c>
@@ -24736,7 +24883,7 @@
         <v>TS-UD-COH-RUL-001test_015_r13_partial_coverage_calculation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="31.2" thickBot="1">
+    <row r="195" spans="1:11" ht="31.5" thickBot="1">
       <c r="A195" s="6" t="s">
         <v>140</v>
       </c>
@@ -24765,7 +24912,7 @@
         <v>TS-UD-COH-RUL-001test_016_r13_coverage_percentage_80</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="31.2" thickBot="1">
+    <row r="196" spans="1:11" ht="31.5" thickBot="1">
       <c r="A196" s="6" t="s">
         <v>140</v>
       </c>
@@ -24794,7 +24941,7 @@
         <v>TS-UD-COH-RUL-001test_017_r13_uncovered_clauses_list</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="31.2" thickBot="1">
+    <row r="197" spans="1:11" ht="31.5" thickBot="1">
       <c r="A197" s="6" t="s">
         <v>140</v>
       </c>
@@ -24823,7 +24970,7 @@
         <v>TS-UD-COH-RUL-001test_018_r13_alert_severity_high</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="31.2" thickBot="1">
+    <row r="198" spans="1:11" ht="31.5" thickBot="1">
       <c r="A198" s="6" t="s">
         <v>141</v>
       </c>
@@ -24852,7 +24999,7 @@
         <v>TS-UD-COH-RUL-002test_001_r6_deviation_10_percent_alert</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="31.2" thickBot="1">
+    <row r="199" spans="1:11" ht="31.5" thickBot="1">
       <c r="A199" s="6" t="s">
         <v>141</v>
       </c>
@@ -24881,7 +25028,7 @@
         <v>TS-UD-COH-RUL-002test_002_r6_deviation_5_percent_pass</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="31.2" thickBot="1">
+    <row r="200" spans="1:11" ht="31.5" thickBot="1">
       <c r="A200" s="6" t="s">
         <v>141</v>
       </c>
@@ -24910,7 +25057,7 @@
         <v>TS-UD-COH-RUL-002test_003_r6_deviation_4_9_percent_pass</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="31.2" thickBot="1">
+    <row r="201" spans="1:11" ht="31.5" thickBot="1">
       <c r="A201" s="6" t="s">
         <v>141</v>
       </c>
@@ -24939,7 +25086,7 @@
         <v>TS-UD-COH-RUL-002test_004_r6_over_budget_critical</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="31.2" thickBot="1">
+    <row r="202" spans="1:11" ht="31.5" thickBot="1">
       <c r="A202" s="6" t="s">
         <v>141</v>
       </c>
@@ -24968,7 +25115,7 @@
         <v>TS-UD-COH-RUL-002test_005_r6_under_budget_warning</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="31.2" thickBot="1">
+    <row r="203" spans="1:11" ht="31.5" thickBot="1">
       <c r="A203" s="6" t="s">
         <v>141</v>
       </c>
@@ -24997,7 +25144,7 @@
         <v>TS-UD-COH-RUL-002test_006_r6_exact_match_pass</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="31.2" thickBot="1">
+    <row r="204" spans="1:11" ht="31.5" thickBot="1">
       <c r="A204" s="6" t="s">
         <v>141</v>
       </c>
@@ -25026,7 +25173,7 @@
         <v>TS-UD-COH-RUL-002test_007_r15_bom_no_budget_alert</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="31.2" thickBot="1">
+    <row r="205" spans="1:11" ht="31.5" thickBot="1">
       <c r="A205" s="6" t="s">
         <v>141</v>
       </c>
@@ -25055,7 +25202,7 @@
         <v>TS-UD-COH-RUL-002test_008_r15_bom_with_budget_pass</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="31.2" thickBot="1">
+    <row r="206" spans="1:11" ht="31.5" thickBot="1">
       <c r="A206" s="6" t="s">
         <v>141</v>
       </c>
@@ -25084,7 +25231,7 @@
         <v>TS-UD-COH-RUL-002test_009_r15_bom_client_provided_exception</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="31.2" thickBot="1">
+    <row r="207" spans="1:11" ht="31.5" thickBot="1">
       <c r="A207" s="6" t="s">
         <v>141</v>
       </c>
@@ -25113,7 +25260,7 @@
         <v>TS-UD-COH-RUL-002test_010_r15_multiple_bom_violations</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="31.2" thickBot="1">
+    <row r="208" spans="1:11" ht="31.5" thickBot="1">
       <c r="A208" s="6" t="s">
         <v>141</v>
       </c>
@@ -25142,7 +25289,7 @@
         <v>TS-UD-COH-RUL-002test_011_r15_affected_items_list</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="31.2" thickBot="1">
+    <row r="209" spans="1:11" ht="31.5" thickBot="1">
       <c r="A209" s="6" t="s">
         <v>141</v>
       </c>
@@ -25171,7 +25318,7 @@
         <v>TS-UD-COH-RUL-002test_012_r16_deviation_11_percent_alert</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="31.2" thickBot="1">
+    <row r="210" spans="1:11" ht="31.5" thickBot="1">
       <c r="A210" s="6" t="s">
         <v>141</v>
       </c>
@@ -25200,7 +25347,7 @@
         <v>TS-UD-COH-RUL-002test_013_r16_deviation_10_percent_pass</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="31.2" thickBot="1">
+    <row r="211" spans="1:11" ht="31.5" thickBot="1">
       <c r="A211" s="6" t="s">
         <v>141</v>
       </c>
@@ -25229,7 +25376,7 @@
         <v>TS-UD-COH-RUL-002test_014_r16_over_budget_critical</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="31.2" thickBot="1">
+    <row r="212" spans="1:11" ht="31.5" thickBot="1">
       <c r="A212" s="6" t="s">
         <v>141</v>
       </c>
@@ -25258,7 +25405,7 @@
         <v>TS-UD-COH-RUL-002test_015_r16_under_budget_different_severity</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="31.2" thickBot="1">
+    <row r="213" spans="1:11" ht="31.5" thickBot="1">
       <c r="A213" s="6" t="s">
         <v>141</v>
       </c>
@@ -25287,7 +25434,7 @@
         <v>TS-UD-COH-RUL-002test_016_r16_trend_calculation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="31.2" thickBot="1">
+    <row r="214" spans="1:11" ht="31.5" thickBot="1">
       <c r="A214" s="6" t="s">
         <v>142</v>
       </c>
@@ -25319,7 +25466,7 @@
         <v>TS-UD-COH-RUL-003test_001_r1_dates_mismatch_alert</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="31.2" thickBot="1">
+    <row r="215" spans="1:11" ht="31.5" thickBot="1">
       <c r="A215" s="6" t="s">
         <v>142</v>
       </c>
@@ -25348,7 +25495,7 @@
         <v>TS-UD-COH-RUL-003test_002_r1_dates_match_pass</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="31.2" thickBot="1">
+    <row r="216" spans="1:11" ht="31.5" thickBot="1">
       <c r="A216" s="6" t="s">
         <v>142</v>
       </c>
@@ -25377,7 +25524,7 @@
         <v>TS-UD-COH-RUL-003test_003_r1_schedule_late_critical</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="31.2" thickBot="1">
+    <row r="217" spans="1:11" ht="31.5" thickBot="1">
       <c r="A217" s="6" t="s">
         <v>142</v>
       </c>
@@ -25406,7 +25553,7 @@
         <v>TS-UD-COH-RUL-003test_004_r1_schedule_early_warning</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="31.2" thickBot="1">
+    <row r="218" spans="1:11" ht="31.5" thickBot="1">
       <c r="A218" s="6" t="s">
         <v>142</v>
       </c>
@@ -25435,7 +25582,7 @@
         <v>TS-UD-COH-RUL-003test_005_r1_delta_days_calculation</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="31.2" thickBot="1">
+    <row r="219" spans="1:11" ht="31.5" thickBot="1">
       <c r="A219" s="6" t="s">
         <v>142</v>
       </c>
@@ -25464,7 +25611,7 @@
         <v>TS-UD-COH-RUL-003test_006_r2_milestone_no_activity_alert</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="31.2" thickBot="1">
+    <row r="220" spans="1:11" ht="31.5" thickBot="1">
       <c r="A220" s="6" t="s">
         <v>142</v>
       </c>
@@ -25493,7 +25640,7 @@
         <v>TS-UD-COH-RUL-003test_007_r2_milestone_with_activity_pass</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="31.2" thickBot="1">
+    <row r="221" spans="1:11" ht="31.5" thickBot="1">
       <c r="A221" s="6" t="s">
         <v>142</v>
       </c>
@@ -25522,7 +25669,7 @@
         <v>TS-UD-COH-RUL-003test_008_r2_milestone_date_mismatch_alert</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="31.2" thickBot="1">
+    <row r="222" spans="1:11" ht="31.5" thickBot="1">
       <c r="A222" s="6" t="s">
         <v>142</v>
       </c>
@@ -25551,7 +25698,7 @@
         <v>TS-UD-COH-RUL-003test_009_r2_multiple_milestones_violations</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="31.2" thickBot="1">
+    <row r="223" spans="1:11" ht="31.5" thickBot="1">
       <c r="A223" s="6" t="s">
         <v>142</v>
       </c>
@@ -25580,7 +25727,7 @@
         <v>TS-UD-COH-RUL-003test_010_r2_unlinked_milestones_list</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="31.2" thickBot="1">
+    <row r="224" spans="1:11" ht="31.5" thickBot="1">
       <c r="A224" s="6" t="s">
         <v>142</v>
       </c>
@@ -25609,7 +25756,7 @@
         <v>TS-UD-COH-RUL-003test_011_r5_activity_exceeds_contract_alert</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="31.2" thickBot="1">
+    <row r="225" spans="1:11" ht="31.5" thickBot="1">
       <c r="A225" s="6" t="s">
         <v>142</v>
       </c>
@@ -25638,7 +25785,7 @@
         <v>TS-UD-COH-RUL-003test_012_r5_activity_within_contract_pass</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="31.2" thickBot="1">
+    <row r="226" spans="1:11" ht="31.5" thickBot="1">
       <c r="A226" s="6" t="s">
         <v>142</v>
       </c>
@@ -25667,7 +25814,7 @@
         <v>TS-UD-COH-RUL-003test_013_r5_exceeding_activities_list</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="31.2" thickBot="1">
+    <row r="227" spans="1:11" ht="31.5" thickBot="1">
       <c r="A227" s="6" t="s">
         <v>142</v>
       </c>
@@ -25696,7 +25843,7 @@
         <v>TS-UD-COH-RUL-003test_014_r5_alert_severity_critical</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="31.2" thickBot="1">
+    <row r="228" spans="1:11" ht="31.5" thickBot="1">
       <c r="A228" s="6" t="s">
         <v>142</v>
       </c>
@@ -25725,7 +25872,7 @@
         <v>TS-UD-COH-RUL-003test_015_r14_order_date_passed_critical</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="31.2" thickBot="1">
+    <row r="229" spans="1:11" ht="31.5" thickBot="1">
       <c r="A229" s="6" t="s">
         <v>142</v>
       </c>
@@ -25754,7 +25901,7 @@
         <v>TS-UD-COH-RUL-003test_016_r14_order_date_tight_warning</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="16.2" thickBot="1">
+    <row r="230" spans="1:11" ht="16.5" thickBot="1">
       <c r="A230" s="6" t="s">
         <v>143</v>
       </c>
@@ -25775,7 +25922,7 @@
         <v>TS-UD-COH-RUL-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="16.2" thickBot="1">
+    <row r="231" spans="1:11" ht="16.5" thickBot="1">
       <c r="A231" s="6" t="s">
         <v>144</v>
       </c>
@@ -25796,7 +25943,7 @@
         <v>TS-UD-COH-RUL-005Tests not individually listed</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="16.2" thickBot="1">
+    <row r="232" spans="1:11" ht="16.5" thickBot="1">
       <c r="A232" s="6" t="s">
         <v>145</v>
       </c>
@@ -25817,7 +25964,7 @@
         <v>TS-UD-COH-RUL-006Tests not individually listed</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="31.2" thickBot="1">
+    <row r="233" spans="1:11" ht="31.5" thickBot="1">
       <c r="A233" s="6" t="s">
         <v>146</v>
       </c>
@@ -25849,7 +25996,7 @@
         <v>TS-UD-COH-SCR-001test_001_subscore_no_alerts_100_percent</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="31.2" thickBot="1">
+    <row r="234" spans="1:11" ht="31.5" thickBot="1">
       <c r="A234" s="6" t="s">
         <v>146</v>
       </c>
@@ -25878,7 +26025,7 @@
         <v>TS-UD-COH-SCR-001test_002_subscore_one_alert_penalized</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="31.2" thickBot="1">
+    <row r="235" spans="1:11" ht="31.5" thickBot="1">
       <c r="A235" s="6" t="s">
         <v>146</v>
       </c>
@@ -25907,7 +26054,7 @@
         <v>TS-UD-COH-SCR-001test_003_subscore_multiple_alerts_cumulative</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="31.2" thickBot="1">
+    <row r="236" spans="1:11" ht="31.5" thickBot="1">
       <c r="A236" s="6" t="s">
         <v>146</v>
       </c>
@@ -25936,7 +26083,7 @@
         <v>TS-UD-COH-SCR-001test_004_subscore_severity_low_penalty_5</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="31.2" thickBot="1">
+    <row r="237" spans="1:11" ht="31.5" thickBot="1">
       <c r="A237" s="6" t="s">
         <v>146</v>
       </c>
@@ -25965,7 +26112,7 @@
         <v>TS-UD-COH-SCR-001test_005_subscore_severity_medium_penalty_10</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="31.2" thickBot="1">
+    <row r="238" spans="1:11" ht="31.5" thickBot="1">
       <c r="A238" s="6" t="s">
         <v>146</v>
       </c>
@@ -25994,7 +26141,7 @@
         <v>TS-UD-COH-SCR-001test_006_subscore_severity_high_penalty_20</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="31.2" thickBot="1">
+    <row r="239" spans="1:11" ht="31.5" thickBot="1">
       <c r="A239" s="6" t="s">
         <v>146</v>
       </c>
@@ -26023,7 +26170,7 @@
         <v>TS-UD-COH-SCR-001test_007_subscore_severity_critical_penalty_30</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="31.2" thickBot="1">
+    <row r="240" spans="1:11" ht="31.5" thickBot="1">
       <c r="A240" s="6" t="s">
         <v>146</v>
       </c>
@@ -26052,7 +26199,7 @@
         <v>TS-UD-COH-SCR-001test_008_subscore_scope_calculation</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="31.2" thickBot="1">
+    <row r="241" spans="1:11" ht="31.5" thickBot="1">
       <c r="A241" s="6" t="s">
         <v>146</v>
       </c>
@@ -26081,7 +26228,7 @@
         <v>TS-UD-COH-SCR-001test_009_subscore_budget_calculation</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="31.2" thickBot="1">
+    <row r="242" spans="1:11" ht="31.5" thickBot="1">
       <c r="A242" s="6" t="s">
         <v>146</v>
       </c>
@@ -26110,7 +26257,7 @@
         <v>TS-UD-COH-SCR-001test_010_subscore_quality_calculation</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="31.2" thickBot="1">
+    <row r="243" spans="1:11" ht="31.5" thickBot="1">
       <c r="A243" s="6" t="s">
         <v>146</v>
       </c>
@@ -26139,7 +26286,7 @@
         <v>TS-UD-COH-SCR-001test_011_subscore_technical_calculation</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="31.2" thickBot="1">
+    <row r="244" spans="1:11" ht="31.5" thickBot="1">
       <c r="A244" s="6" t="s">
         <v>146</v>
       </c>
@@ -26168,7 +26315,7 @@
         <v>TS-UD-COH-SCR-001test_012_subscore_legal_calculation</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="31.2" thickBot="1">
+    <row r="245" spans="1:11" ht="31.5" thickBot="1">
       <c r="A245" s="6" t="s">
         <v>146</v>
       </c>
@@ -26197,7 +26344,7 @@
         <v>TS-UD-COH-SCR-001test_013_subscore_time_calculation</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="31.2" thickBot="1">
+    <row r="246" spans="1:11" ht="31.5" thickBot="1">
       <c r="A246" s="6" t="s">
         <v>146</v>
       </c>
@@ -26226,7 +26373,7 @@
         <v>TS-UD-COH-SCR-001test_014_subscore_floor_at_zero</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="31.2" thickBot="1">
+    <row r="247" spans="1:11" ht="31.5" thickBot="1">
       <c r="A247" s="6" t="s">
         <v>147</v>
       </c>
@@ -26255,7 +26402,7 @@
         <v>TS-UD-COH-SCR-002test_001_global_score_formula_verification</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="31.2" thickBot="1">
+    <row r="248" spans="1:11" ht="31.5" thickBot="1">
       <c r="A248" s="6" t="s">
         <v>147</v>
       </c>
@@ -26284,7 +26431,7 @@
         <v>TS-UD-COH-SCR-002test_002_global_score_default_weights</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="31.2" thickBot="1">
+    <row r="249" spans="1:11" ht="31.5" thickBot="1">
       <c r="A249" s="6" t="s">
         <v>147</v>
       </c>
@@ -26313,7 +26460,7 @@
         <v>TS-UD-COH-SCR-002test_003_global_score_all_100_equals_100</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="31.2" thickBot="1">
+    <row r="250" spans="1:11" ht="31.5" thickBot="1">
       <c r="A250" s="6" t="s">
         <v>147</v>
       </c>
@@ -26342,7 +26489,7 @@
         <v>TS-UD-COH-SCR-002test_004_global_score_all_0_equals_0</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="31.2" thickBot="1">
+    <row r="251" spans="1:11" ht="31.5" thickBot="1">
       <c r="A251" s="6" t="s">
         <v>147</v>
       </c>
@@ -26371,7 +26518,7 @@
         <v>TS-UD-COH-SCR-002test_005_global_score_mixed_subscores</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="31.2" thickBot="1">
+    <row r="252" spans="1:11" ht="31.5" thickBot="1">
       <c r="A252" s="6" t="s">
         <v>147</v>
       </c>
@@ -26400,7 +26547,7 @@
         <v>TS-UD-COH-SCR-002test_006_global_score_range_0_to_100</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="31.2" thickBot="1">
+    <row r="253" spans="1:11" ht="31.5" thickBot="1">
       <c r="A253" s="6" t="s">
         <v>147</v>
       </c>
@@ -26429,7 +26576,7 @@
         <v>TS-UD-COH-SCR-002test_007_weights_sum_validation</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="31.2" thickBot="1">
+    <row r="254" spans="1:11" ht="31.5" thickBot="1">
       <c r="A254" s="6" t="s">
         <v>147</v>
       </c>
@@ -26458,7 +26605,7 @@
         <v>TS-UD-COH-SCR-002test_008_weights_normalization_auto</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="31.2" thickBot="1">
+    <row r="255" spans="1:11" ht="31.5" thickBot="1">
       <c r="A255" s="6" t="s">
         <v>147</v>
       </c>
@@ -26487,7 +26634,7 @@
         <v>TS-UD-COH-SCR-002test_009_weights_custom_budget_30</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="31.2" thickBot="1">
+    <row r="256" spans="1:11" ht="31.5" thickBot="1">
       <c r="A256" s="6" t="s">
         <v>147</v>
       </c>
@@ -26516,7 +26663,7 @@
         <v>TS-UD-COH-SCR-002test_010_weights_custom_time_25</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="31.2" thickBot="1">
+    <row r="257" spans="1:11" ht="31.5" thickBot="1">
       <c r="A257" s="6" t="s">
         <v>147</v>
       </c>
@@ -26545,7 +26692,7 @@
         <v>TS-UD-COH-SCR-002test_011_weights_per_project_type</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="31.2" thickBot="1">
+    <row r="258" spans="1:11" ht="31.5" thickBot="1">
       <c r="A258" s="6" t="s">
         <v>147</v>
       </c>
@@ -26574,7 +26721,7 @@
         <v>TS-UD-COH-SCR-002test_012_weights_history_tracking</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="16.2" thickBot="1">
+    <row r="259" spans="1:11" ht="16.5" thickBot="1">
       <c r="A259" s="6" t="s">
         <v>148</v>
       </c>
@@ -26591,7 +26738,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="31.2" thickBot="1">
+    <row r="260" spans="1:11" ht="31.5" thickBot="1">
       <c r="A260" s="6" t="s">
         <v>149</v>
       </c>
@@ -26620,7 +26767,7 @@
         <v>TS-UD-COH-GAM-001test_001_detect_mass_changes_15_in_30min</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="31.2" thickBot="1">
+    <row r="261" spans="1:11" ht="31.5" thickBot="1">
       <c r="A261" s="6" t="s">
         <v>149</v>
       </c>
@@ -26649,7 +26796,7 @@
         <v>TS-UD-COH-GAM-001test_002_no_violation_10_in_60min</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="31.2" thickBot="1">
+    <row r="262" spans="1:11" ht="31.5" thickBot="1">
       <c r="A262" s="6" t="s">
         <v>149</v>
       </c>
@@ -26678,7 +26825,7 @@
         <v>TS-UD-COH-GAM-001test_003_mass_changes_window_sliding</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="31.2" thickBot="1">
+    <row r="263" spans="1:11" ht="31.5" thickBot="1">
       <c r="A263" s="6" t="s">
         <v>149</v>
       </c>
@@ -26707,7 +26854,7 @@
         <v>TS-UD-COH-GAM-001test_004_mass_changes_flag_for_review</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="31.2" thickBot="1">
+    <row r="264" spans="1:11" ht="31.5" thickBot="1">
       <c r="A264" s="6" t="s">
         <v>149</v>
       </c>
@@ -26736,7 +26883,7 @@
         <v>TS-UD-COH-GAM-001test_005_detect_resolve_reintroduce_4_times</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="31.2" thickBot="1">
+    <row r="265" spans="1:11" ht="31.5" thickBot="1">
       <c r="A265" s="6" t="s">
         <v>149</v>
       </c>
@@ -26765,7 +26912,7 @@
         <v>TS-UD-COH-GAM-001test_006_no_violation_2_times</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="31.2" thickBot="1">
+    <row r="266" spans="1:11" ht="31.5" thickBot="1">
       <c r="A266" s="6" t="s">
         <v>149</v>
       </c>
@@ -26794,7 +26941,7 @@
         <v>TS-UD-COH-GAM-001test_007_hash_comparison_same_content</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="31.2" thickBot="1">
+    <row r="267" spans="1:11" ht="31.5" thickBot="1">
       <c r="A267" s="6" t="s">
         <v>149</v>
       </c>
@@ -26823,7 +26970,7 @@
         <v>TS-UD-COH-GAM-001test_008_penalty_minus_5_points</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="31.2" thickBot="1">
+    <row r="268" spans="1:11" ht="31.5" thickBot="1">
       <c r="A268" s="6" t="s">
         <v>149</v>
       </c>
@@ -26852,7 +26999,7 @@
         <v>TS-UD-COH-GAM-001test_009_detect_95_percent_3_docs</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="31.2" thickBot="1">
+    <row r="269" spans="1:11" ht="31.5" thickBot="1">
       <c r="A269" s="6" t="s">
         <v>149</v>
       </c>
@@ -26881,7 +27028,7 @@
         <v>TS-UD-COH-GAM-001test_010_no_violation_95_percent_50_docs</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="31.2" thickBot="1">
+    <row r="270" spans="1:11" ht="31.5" thickBot="1">
       <c r="A270" s="6" t="s">
         <v>149</v>
       </c>
@@ -26910,7 +27057,7 @@
         <v>TS-UD-COH-GAM-001test_011_threshold_90_percent_5_docs</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="31.2" thickBot="1">
+    <row r="271" spans="1:11" ht="31.5" thickBot="1">
       <c r="A271" s="6" t="s">
         <v>149</v>
       </c>
@@ -26939,7 +27086,7 @@
         <v>TS-UD-COH-GAM-001test_012_require_audit_action</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="31.2" thickBot="1">
+    <row r="272" spans="1:11" ht="31.5" thickBot="1">
       <c r="A272" s="6" t="s">
         <v>149</v>
       </c>
@@ -26968,7 +27115,7 @@
         <v>TS-UD-COH-GAM-001test_013_detect_weight_change_25_percent</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="31.2" thickBot="1">
+    <row r="273" spans="1:11" ht="31.5" thickBot="1">
       <c r="A273" s="6" t="s">
         <v>149</v>
       </c>
@@ -26997,7 +27144,7 @@
         <v>TS-UD-COH-GAM-001test_014_no_violation_change_15_percent</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="31.2" thickBot="1">
+    <row r="274" spans="1:11" ht="31.5" thickBot="1">
       <c r="A274" s="6" t="s">
         <v>149</v>
       </c>
@@ -27026,7 +27173,7 @@
         <v>TS-UD-COH-GAM-001test_015_24h_window_tracking</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="31.2" thickBot="1">
+    <row r="275" spans="1:11" ht="31.5" thickBot="1">
       <c r="A275" s="6" t="s">
         <v>149</v>
       </c>
@@ -27055,7 +27202,7 @@
         <v>TS-UD-COH-GAM-001test_016_notify_admin_action</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="16.2" thickBot="1">
+    <row r="276" spans="1:11" ht="16.5" thickBot="1">
       <c r="A276" s="6" t="s">
         <v>150</v>
       </c>
@@ -27076,7 +27223,7 @@
         <v>TS-UD-COH-ALR-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="31.2" thickBot="1">
+    <row r="277" spans="1:11" ht="31.5" thickBot="1">
       <c r="A277" s="6" t="s">
         <v>151</v>
       </c>
@@ -27108,7 +27255,7 @@
         <v>TS-UD-PRJ-WBS-001test_001_wbs_item_creation_all_fields</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="31.2" thickBot="1">
+    <row r="278" spans="1:11" ht="31.5" thickBot="1">
       <c r="A278" s="6" t="s">
         <v>151</v>
       </c>
@@ -27137,7 +27284,7 @@
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="31.2" thickBot="1">
+    <row r="279" spans="1:11" ht="31.5" thickBot="1">
       <c r="A279" s="6" t="s">
         <v>151</v>
       </c>
@@ -27166,7 +27313,7 @@
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="31.2" thickBot="1">
+    <row r="280" spans="1:11" ht="31.5" thickBot="1">
       <c r="A280" s="6" t="s">
         <v>151</v>
       </c>
@@ -27195,7 +27342,7 @@
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="31.2" thickBot="1">
+    <row r="281" spans="1:11" ht="31.5" thickBot="1">
       <c r="A281" s="6" t="s">
         <v>151</v>
       </c>
@@ -27224,7 +27371,7 @@
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="31.2" thickBot="1">
+    <row r="282" spans="1:11" ht="31.5" thickBot="1">
       <c r="A282" s="6" t="s">
         <v>151</v>
       </c>
@@ -27253,7 +27400,7 @@
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="31.2" thickBot="1">
+    <row r="283" spans="1:11" ht="31.5" thickBot="1">
       <c r="A283" s="6" t="s">
         <v>151</v>
       </c>
@@ -27282,7 +27429,7 @@
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="31.2" thickBot="1">
+    <row r="284" spans="1:11" ht="31.5" thickBot="1">
       <c r="A284" s="6" t="s">
         <v>151</v>
       </c>
@@ -27311,7 +27458,7 @@
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="31.2" thickBot="1">
+    <row r="285" spans="1:11" ht="31.5" thickBot="1">
       <c r="A285" s="6" t="s">
         <v>151</v>
       </c>
@@ -27340,7 +27487,7 @@
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="31.2" thickBot="1">
+    <row r="286" spans="1:11" ht="31.5" thickBot="1">
       <c r="A286" s="6" t="s">
         <v>151</v>
       </c>
@@ -27369,7 +27516,7 @@
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="31.2" thickBot="1">
+    <row r="287" spans="1:11" ht="31.5" thickBot="1">
       <c r="A287" s="6" t="s">
         <v>151</v>
       </c>
@@ -27398,7 +27545,7 @@
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="31.2" thickBot="1">
+    <row r="288" spans="1:11" ht="31.5" thickBot="1">
       <c r="A288" s="6" t="s">
         <v>151</v>
       </c>
@@ -27427,7 +27574,7 @@
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="16.2" thickBot="1">
+    <row r="289" spans="1:11" ht="31.5" thickBot="1">
       <c r="A289" s="6" t="s">
         <v>151</v>
       </c>
@@ -27456,7 +27603,7 @@
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="16.2" thickBot="1">
+    <row r="290" spans="1:11" ht="31.5" thickBot="1">
       <c r="A290" s="6" t="s">
         <v>151</v>
       </c>
@@ -27485,7 +27632,7 @@
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="31.2" thickBot="1">
+    <row r="291" spans="1:11" ht="31.5" thickBot="1">
       <c r="A291" s="6" t="s">
         <v>151</v>
       </c>
@@ -27514,7 +27661,7 @@
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="31.2" thickBot="1">
+    <row r="292" spans="1:11" ht="31.5" thickBot="1">
       <c r="A292" s="6" t="s">
         <v>151</v>
       </c>
@@ -27543,7 +27690,7 @@
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="31.2" thickBot="1">
+    <row r="293" spans="1:11" ht="31.5" thickBot="1">
       <c r="A293" s="6" t="s">
         <v>151</v>
       </c>
@@ -27572,7 +27719,7 @@
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="31.2" thickBot="1">
+    <row r="294" spans="1:11" ht="31.5" thickBot="1">
       <c r="A294" s="6" t="s">
         <v>151</v>
       </c>
@@ -27601,7 +27748,7 @@
         <v>TS-UD-PRJ-WBS-001test_018_wbs_level_parent_child_validation</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="16.2" thickBot="1">
+    <row r="295" spans="1:11" ht="16.5" thickBot="1">
       <c r="A295" s="6" t="s">
         <v>152</v>
       </c>
@@ -27622,7 +27769,7 @@
         <v>TS-UD-PRJ-WBS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="16.2" thickBot="1">
+    <row r="296" spans="1:11" ht="16.5" thickBot="1">
       <c r="A296" s="6" t="s">
         <v>153</v>
       </c>
@@ -27643,7 +27790,7 @@
         <v>TS-UD-PRJ-WBS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="16.2" thickBot="1">
+    <row r="297" spans="1:11" ht="16.5" thickBot="1">
       <c r="A297" s="6" t="s">
         <v>154</v>
       </c>
@@ -27664,7 +27811,7 @@
         <v>TS-UD-PRJ-WBS-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="16.2" thickBot="1">
+    <row r="298" spans="1:11" ht="16.5" thickBot="1">
       <c r="A298" s="6" t="s">
         <v>155</v>
       </c>
@@ -27685,7 +27832,7 @@
         <v>TS-UD-PRJ-PRJ-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="16.2" thickBot="1">
+    <row r="299" spans="1:11" ht="16.5" thickBot="1">
       <c r="A299" s="6" t="s">
         <v>156</v>
       </c>
@@ -27706,7 +27853,7 @@
         <v>TS-UD-PRJ-DTO-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="16.2" thickBot="1">
+    <row r="300" spans="1:11" ht="16.5" thickBot="1">
       <c r="A300" s="6" t="s">
         <v>157</v>
       </c>
@@ -27727,7 +27874,7 @@
         <v>TS-UD-PROC-BOM-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="16.2" thickBot="1">
+    <row r="301" spans="1:11" ht="16.5" thickBot="1">
       <c r="A301" s="6" t="s">
         <v>158</v>
       </c>
@@ -27748,7 +27895,7 @@
         <v>TS-UD-PROC-BOM-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="31.2" thickBot="1">
+    <row r="302" spans="1:11" ht="31.5" thickBot="1">
       <c r="A302" s="6" t="s">
         <v>159</v>
       </c>
@@ -27780,7 +27927,7 @@
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="31.2" thickBot="1">
+    <row r="303" spans="1:11" ht="31.5" thickBot="1">
       <c r="A303" s="6" t="s">
         <v>159</v>
       </c>
@@ -27809,7 +27956,7 @@
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="31.2" thickBot="1">
+    <row r="304" spans="1:11" ht="31.5" thickBot="1">
       <c r="A304" s="6" t="s">
         <v>159</v>
       </c>
@@ -27838,7 +27985,7 @@
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="31.2" thickBot="1">
+    <row r="305" spans="1:11" ht="31.5" thickBot="1">
       <c r="A305" s="6" t="s">
         <v>159</v>
       </c>
@@ -27867,7 +28014,7 @@
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="31.2" thickBot="1">
+    <row r="306" spans="1:11" ht="31.5" thickBot="1">
       <c r="A306" s="6" t="s">
         <v>159</v>
       </c>
@@ -27896,7 +28043,7 @@
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="31.2" thickBot="1">
+    <row r="307" spans="1:11" ht="31.5" thickBot="1">
       <c r="A307" s="6" t="s">
         <v>159</v>
       </c>
@@ -27925,7 +28072,7 @@
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="31.2" thickBot="1">
+    <row r="308" spans="1:11" ht="31.5" thickBot="1">
       <c r="A308" s="6" t="s">
         <v>159</v>
       </c>
@@ -27954,7 +28101,7 @@
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="31.2" thickBot="1">
+    <row r="309" spans="1:11" ht="31.5" thickBot="1">
       <c r="A309" s="6" t="s">
         <v>159</v>
       </c>
@@ -27983,7 +28130,7 @@
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="16.2" thickBot="1">
+    <row r="310" spans="1:11" ht="16.5" thickBot="1">
       <c r="A310" s="6" t="s">
         <v>159</v>
       </c>
@@ -28012,7 +28159,7 @@
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="31.2" thickBot="1">
+    <row r="311" spans="1:11" ht="31.5" thickBot="1">
       <c r="A311" s="6" t="s">
         <v>159</v>
       </c>
@@ -28041,7 +28188,7 @@
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="31.2" thickBot="1">
+    <row r="312" spans="1:11" ht="31.5" thickBot="1">
       <c r="A312" s="6" t="s">
         <v>159</v>
       </c>
@@ -28070,7 +28217,7 @@
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="31.2" thickBot="1">
+    <row r="313" spans="1:11" ht="31.5" thickBot="1">
       <c r="A313" s="6" t="s">
         <v>159</v>
       </c>
@@ -28099,7 +28246,7 @@
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="31.2" thickBot="1">
+    <row r="314" spans="1:11" ht="31.5" thickBot="1">
       <c r="A314" s="6" t="s">
         <v>159</v>
       </c>
@@ -28128,7 +28275,7 @@
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="31.2" thickBot="1">
+    <row r="315" spans="1:11" ht="31.5" thickBot="1">
       <c r="A315" s="6" t="s">
         <v>159</v>
       </c>
@@ -28157,7 +28304,7 @@
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="31.2" thickBot="1">
+    <row r="316" spans="1:11" ht="31.5" thickBot="1">
       <c r="A316" s="6" t="s">
         <v>159</v>
       </c>
@@ -28186,7 +28333,7 @@
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="31.2" thickBot="1">
+    <row r="317" spans="1:11" ht="31.5" thickBot="1">
       <c r="A317" s="6" t="s">
         <v>159</v>
       </c>
@@ -28215,7 +28362,7 @@
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="31.2" thickBot="1">
+    <row r="318" spans="1:11" ht="31.5" thickBot="1">
       <c r="A318" s="6" t="s">
         <v>160</v>
       </c>
@@ -28241,7 +28388,7 @@
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="31.2" thickBot="1">
+    <row r="319" spans="1:11" ht="31.5" thickBot="1">
       <c r="A319" s="6" t="s">
         <v>160</v>
       </c>
@@ -28267,7 +28414,7 @@
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="31.2" thickBot="1">
+    <row r="320" spans="1:11" ht="31.5" thickBot="1">
       <c r="A320" s="6" t="s">
         <v>160</v>
       </c>
@@ -28293,7 +28440,7 @@
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="31.2" thickBot="1">
+    <row r="321" spans="1:11" ht="31.5" thickBot="1">
       <c r="A321" s="6" t="s">
         <v>160</v>
       </c>
@@ -28319,7 +28466,7 @@
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="31.2" thickBot="1">
+    <row r="322" spans="1:11" ht="31.5" thickBot="1">
       <c r="A322" s="6" t="s">
         <v>160</v>
       </c>
@@ -28345,7 +28492,7 @@
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="31.2" thickBot="1">
+    <row r="323" spans="1:11" ht="31.5" thickBot="1">
       <c r="A323" s="6" t="s">
         <v>160</v>
       </c>
@@ -28371,7 +28518,7 @@
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="31.2" thickBot="1">
+    <row r="324" spans="1:11" ht="31.5" thickBot="1">
       <c r="A324" s="6" t="s">
         <v>160</v>
       </c>
@@ -28397,7 +28544,7 @@
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="16.2" thickBot="1">
+    <row r="325" spans="1:11" ht="16.5" thickBot="1">
       <c r="A325" s="6" t="s">
         <v>160</v>
       </c>
@@ -28423,7 +28570,7 @@
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="31.2" thickBot="1">
+    <row r="326" spans="1:11" ht="31.5" thickBot="1">
       <c r="A326" s="6" t="s">
         <v>160</v>
       </c>
@@ -28449,7 +28596,7 @@
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="31.2" thickBot="1">
+    <row r="327" spans="1:11" ht="31.5" thickBot="1">
       <c r="A327" s="6" t="s">
         <v>160</v>
       </c>
@@ -28475,7 +28622,7 @@
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="31.2" thickBot="1">
+    <row r="328" spans="1:11" ht="31.5" thickBot="1">
       <c r="A328" s="6" t="s">
         <v>160</v>
       </c>
@@ -28501,7 +28648,7 @@
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="31.2" thickBot="1">
+    <row r="329" spans="1:11" ht="31.5" thickBot="1">
       <c r="A329" s="6" t="s">
         <v>160</v>
       </c>
@@ -28527,7 +28674,7 @@
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="31.2" thickBot="1">
+    <row r="330" spans="1:11" ht="31.5" thickBot="1">
       <c r="A330" s="6" t="s">
         <v>160</v>
       </c>
@@ -28553,7 +28700,7 @@
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="31.2" thickBot="1">
+    <row r="331" spans="1:11" ht="31.5" thickBot="1">
       <c r="A331" s="6" t="s">
         <v>160</v>
       </c>
@@ -28579,7 +28726,7 @@
         <v>TS-UD-PROC-LTM-002test_014_incoterm_impact_on_lead_time</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="16.2" thickBot="1">
+    <row r="332" spans="1:11" ht="16.5" thickBot="1">
       <c r="A332" s="6" t="s">
         <v>161</v>
       </c>
@@ -28596,7 +28743,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="16.2" thickBot="1">
+    <row r="333" spans="1:11" ht="16.5" thickBot="1">
       <c r="A333" s="6" t="s">
         <v>162</v>
       </c>
@@ -28613,7 +28760,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="16.2" thickBot="1">
+    <row r="334" spans="1:11" ht="16.5" thickBot="1">
       <c r="A334" s="6" t="s">
         <v>163</v>
       </c>
@@ -28630,7 +28777,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="16.2" thickBot="1">
+    <row r="335" spans="1:11" ht="16.5" thickBot="1">
       <c r="A335" s="6" t="s">
         <v>164</v>
       </c>
@@ -28647,7 +28794,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="16.2" thickBot="1">
+    <row r="336" spans="1:11" ht="16.5" thickBot="1">
       <c r="A336" s="6" t="s">
         <v>165</v>
       </c>
@@ -28664,7 +28811,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="16.2" thickBot="1">
+    <row r="337" spans="1:10" ht="16.5" thickBot="1">
       <c r="A337" s="6" t="s">
         <v>166</v>
       </c>
@@ -28681,7 +28828,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="16.2" thickBot="1">
+    <row r="338" spans="1:10" ht="16.5" thickBot="1">
       <c r="A338" s="6" t="s">
         <v>167</v>
       </c>
@@ -28697,7 +28844,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="16.2" thickBot="1">
+    <row r="339" spans="1:10" ht="16.5" thickBot="1">
       <c r="A339" s="6" t="s">
         <v>168</v>
       </c>
@@ -28713,7 +28860,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="16.2" thickBot="1">
+    <row r="340" spans="1:10" ht="16.5" thickBot="1">
       <c r="A340" s="6" t="s">
         <v>169</v>
       </c>
@@ -28729,7 +28876,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="16.2" thickBot="1">
+    <row r="341" spans="1:10" ht="16.5" thickBot="1">
       <c r="A341" s="6" t="s">
         <v>170</v>
       </c>
@@ -28745,7 +28892,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="16.2" thickBot="1">
+    <row r="342" spans="1:10" ht="16.5" thickBot="1">
       <c r="A342" s="6" t="s">
         <v>171</v>
       </c>
@@ -28761,7 +28908,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="16.2" thickBot="1">
+    <row r="343" spans="1:10" ht="16.5" thickBot="1">
       <c r="A343" s="6" t="s">
         <v>172</v>
       </c>
@@ -28777,7 +28924,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="16.2" thickBot="1">
+    <row r="344" spans="1:10" ht="16.5" thickBot="1">
       <c r="A344" s="6" t="s">
         <v>173</v>
       </c>
@@ -28793,7 +28940,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="16.2" thickBot="1">
+    <row r="345" spans="1:10" ht="16.5" thickBot="1">
       <c r="A345" s="6" t="s">
         <v>174</v>
       </c>
@@ -28809,7 +28956,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="16.2" thickBot="1">
+    <row r="346" spans="1:10" ht="16.5" thickBot="1">
       <c r="A346" s="6" t="s">
         <v>175</v>
       </c>
@@ -28825,7 +28972,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="16.2" thickBot="1">
+    <row r="347" spans="1:10" ht="31.5" thickBot="1">
       <c r="A347" s="6" t="s">
         <v>176</v>
       </c>
@@ -28841,7 +28988,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="16.2" thickBot="1">
+    <row r="348" spans="1:10" ht="31.5" thickBot="1">
       <c r="A348" s="6" t="s">
         <v>177</v>
       </c>
@@ -28857,7 +29004,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="16.2" thickBot="1">
+    <row r="349" spans="1:10" ht="31.5" thickBot="1">
       <c r="A349" s="6" t="s">
         <v>178</v>
       </c>
@@ -28873,7 +29020,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="16.2" thickBot="1">
+    <row r="350" spans="1:10" ht="31.5" thickBot="1">
       <c r="A350" s="6" t="s">
         <v>179</v>
       </c>
@@ -28889,7 +29036,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="16.2" thickBot="1">
+    <row r="351" spans="1:10" ht="31.5" thickBot="1">
       <c r="A351" s="6" t="s">
         <v>180</v>
       </c>
@@ -28905,7 +29052,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="16.2" thickBot="1">
+    <row r="352" spans="1:10" ht="31.5" thickBot="1">
       <c r="A352" s="31" t="s">
         <v>181</v>
       </c>
@@ -28924,7 +29071,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="16.2" thickBot="1">
+    <row r="353" spans="1:10" ht="31.5" thickBot="1">
       <c r="A353" s="31" t="s">
         <v>182</v>
       </c>
@@ -28943,7 +29090,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="16.2" thickBot="1">
+    <row r="354" spans="1:10" ht="31.5" thickBot="1">
       <c r="A354" s="6" t="s">
         <v>183</v>
       </c>
@@ -28959,7 +29106,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="16.2" thickBot="1">
+    <row r="355" spans="1:10" ht="31.5" thickBot="1">
       <c r="A355" s="6" t="s">
         <v>184</v>
       </c>
@@ -28975,7 +29122,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="16.2" thickBot="1">
+    <row r="356" spans="1:10" ht="31.5" thickBot="1">
       <c r="A356" s="6" t="s">
         <v>185</v>
       </c>
@@ -28991,7 +29138,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="16.2" thickBot="1">
+    <row r="357" spans="1:10" ht="31.5" thickBot="1">
       <c r="A357" s="6" t="s">
         <v>186</v>
       </c>
@@ -29007,7 +29154,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="16.2" thickBot="1">
+    <row r="358" spans="1:10" ht="31.5" thickBot="1">
       <c r="A358" s="6" t="s">
         <v>187</v>
       </c>
@@ -29023,7 +29170,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="16.2" thickBot="1">
+    <row r="359" spans="1:10" ht="31.5" thickBot="1">
       <c r="A359" s="6" t="s">
         <v>188</v>
       </c>
@@ -29039,7 +29186,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="16.2" thickBot="1">
+    <row r="360" spans="1:10" ht="31.5" thickBot="1">
       <c r="A360" s="6" t="s">
         <v>189</v>
       </c>
@@ -29055,7 +29202,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="16.2" thickBot="1">
+    <row r="361" spans="1:10" ht="31.5" thickBot="1">
       <c r="A361" s="6" t="s">
         <v>190</v>
       </c>
@@ -29071,7 +29218,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="16.2" thickBot="1">
+    <row r="362" spans="1:10" ht="16.5" thickBot="1">
       <c r="A362" s="6" t="s">
         <v>191</v>
       </c>
@@ -29087,7 +29234,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="16.2" thickBot="1">
+    <row r="363" spans="1:10" ht="16.5" thickBot="1">
       <c r="A363" s="6" t="s">
         <v>192</v>
       </c>
@@ -29103,7 +29250,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="16.2" thickBot="1">
+    <row r="364" spans="1:10" ht="16.5" thickBot="1">
       <c r="A364" s="6" t="s">
         <v>193</v>
       </c>
@@ -29119,7 +29266,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="16.2" thickBot="1">
+    <row r="365" spans="1:10" ht="16.5" thickBot="1">
       <c r="A365" s="6" t="s">
         <v>194</v>
       </c>
@@ -29135,7 +29282,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="16.2" thickBot="1">
+    <row r="366" spans="1:10" ht="16.5" thickBot="1">
       <c r="A366" s="6" t="s">
         <v>195</v>
       </c>
@@ -29151,7 +29298,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="16.2" thickBot="1">
+    <row r="367" spans="1:10" ht="16.5" thickBot="1">
       <c r="A367" s="6" t="s">
         <v>196</v>
       </c>
@@ -29167,7 +29314,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="16.2" thickBot="1">
+    <row r="368" spans="1:10" ht="16.5" thickBot="1">
       <c r="A368" s="6" t="s">
         <v>197</v>
       </c>
@@ -29183,7 +29330,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="16.2" thickBot="1">
+    <row r="369" spans="1:10" ht="16.5" thickBot="1">
       <c r="A369" s="6" t="s">
         <v>198</v>
       </c>
@@ -29202,7 +29349,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="16.2" thickBot="1">
+    <row r="370" spans="1:10" ht="16.5" thickBot="1">
       <c r="A370" s="6" t="s">
         <v>199</v>
       </c>
@@ -29221,7 +29368,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="16.2" thickBot="1">
+    <row r="371" spans="1:10" ht="16.5" thickBot="1">
       <c r="A371" s="6" t="s">
         <v>200</v>
       </c>
@@ -29237,7 +29384,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="16.2" thickBot="1">
+    <row r="372" spans="1:10" ht="16.5" thickBot="1">
       <c r="A372" s="6" t="s">
         <v>201</v>
       </c>
@@ -29253,7 +29400,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="16.2" thickBot="1">
+    <row r="373" spans="1:10" ht="16.5" thickBot="1">
       <c r="A373" s="6" t="s">
         <v>202</v>
       </c>
@@ -29272,7 +29419,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="16.2" thickBot="1">
+    <row r="374" spans="1:10" ht="31.5" thickBot="1">
       <c r="A374" s="6" t="s">
         <v>203</v>
       </c>
@@ -29288,7 +29435,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="16.2" thickBot="1">
+    <row r="375" spans="1:10" ht="31.5" thickBot="1">
       <c r="A375" s="6" t="s">
         <v>204</v>
       </c>
@@ -29304,7 +29451,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="16.2" thickBot="1">
+    <row r="376" spans="1:10" ht="31.5" thickBot="1">
       <c r="A376" s="6" t="s">
         <v>205</v>
       </c>
@@ -29320,7 +29467,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="16.2" thickBot="1">
+    <row r="377" spans="1:10" ht="31.5" thickBot="1">
       <c r="A377" s="6" t="s">
         <v>206</v>
       </c>
@@ -29336,7 +29483,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="16.2" thickBot="1">
+    <row r="378" spans="1:10" ht="16.5" thickBot="1">
       <c r="A378" s="25" t="s">
         <v>207</v>
       </c>
@@ -29355,7 +29502,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="16.2" thickBot="1">
+    <row r="379" spans="1:10" ht="16.5" thickBot="1">
       <c r="A379" s="6" t="s">
         <v>208</v>
       </c>
@@ -29374,7 +29521,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="16.2" thickBot="1">
+    <row r="380" spans="1:10" ht="16.5" thickBot="1">
       <c r="A380" s="6" t="s">
         <v>209</v>
       </c>
@@ -29393,7 +29540,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="16.2" thickBot="1">
+    <row r="381" spans="1:10" ht="16.5" thickBot="1">
       <c r="A381" s="6" t="s">
         <v>210</v>
       </c>
@@ -29409,7 +29556,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="16.2" thickBot="1">
+    <row r="382" spans="1:10" ht="16.5" thickBot="1">
       <c r="A382" s="6" t="s">
         <v>211</v>
       </c>
@@ -29425,7 +29572,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="16.2" thickBot="1">
+    <row r="383" spans="1:10" ht="16.5" thickBot="1">
       <c r="A383" s="6" t="s">
         <v>212</v>
       </c>
@@ -29441,7 +29588,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="16.2" thickBot="1">
+    <row r="384" spans="1:10" ht="16.5" thickBot="1">
       <c r="A384" s="6" t="s">
         <v>213</v>
       </c>
@@ -29457,7 +29604,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="16.2" thickBot="1">
+    <row r="385" spans="1:10" ht="16.5" thickBot="1">
       <c r="A385" s="6" t="s">
         <v>214</v>
       </c>
@@ -29473,7 +29620,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="386" spans="1:10" ht="16.2" thickBot="1">
+    <row r="386" spans="1:10" ht="16.5" thickBot="1">
       <c r="A386" s="6" t="s">
         <v>215</v>
       </c>
@@ -29489,7 +29636,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="16.2" thickBot="1">
+    <row r="387" spans="1:10" ht="16.5" thickBot="1">
       <c r="A387" s="6" t="s">
         <v>216</v>
       </c>
@@ -29505,7 +29652,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="388" spans="1:10" ht="16.2" thickBot="1">
+    <row r="388" spans="1:10" ht="16.5" thickBot="1">
       <c r="A388" s="6" t="s">
         <v>217</v>
       </c>
@@ -29521,7 +29668,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="16.2" thickBot="1">
+    <row r="389" spans="1:10" ht="16.5" thickBot="1">
       <c r="A389" s="6" t="s">
         <v>218</v>
       </c>
@@ -29537,7 +29684,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="390" spans="1:10" ht="16.2" thickBot="1">
+    <row r="390" spans="1:10" ht="16.5" thickBot="1">
       <c r="A390" s="6" t="s">
         <v>219</v>
       </c>
@@ -29553,7 +29700,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="391" spans="1:10" ht="16.2" thickBot="1">
+    <row r="391" spans="1:10" ht="16.5" thickBot="1">
       <c r="A391" s="6" t="s">
         <v>220</v>
       </c>
@@ -29572,7 +29719,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="16.2" thickBot="1">
+    <row r="392" spans="1:10" ht="16.5" thickBot="1">
       <c r="A392" s="6" t="s">
         <v>221</v>
       </c>
@@ -29591,7 +29738,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="16.2" thickBot="1">
+    <row r="393" spans="1:10" ht="16.5" thickBot="1">
       <c r="A393" s="6" t="s">
         <v>222</v>
       </c>
@@ -29610,7 +29757,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="394" spans="1:10" ht="16.2" thickBot="1">
+    <row r="394" spans="1:10" ht="16.5" thickBot="1">
       <c r="A394" s="6" t="s">
         <v>223</v>
       </c>
@@ -29626,7 +29773,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="16.2" thickBot="1">
+    <row r="395" spans="1:10" ht="16.5" thickBot="1">
       <c r="A395" s="6" t="s">
         <v>224</v>
       </c>
@@ -29642,7 +29789,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="16.2" thickBot="1">
+    <row r="396" spans="1:10" ht="16.5" thickBot="1">
       <c r="A396" s="6" t="s">
         <v>225</v>
       </c>
@@ -29658,7 +29805,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="16.2" thickBot="1">
+    <row r="397" spans="1:10" ht="16.5" thickBot="1">
       <c r="A397" s="21" t="s">
         <v>226</v>
       </c>
@@ -29680,7 +29827,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="16.2" thickBot="1">
+    <row r="398" spans="1:10" ht="16.5" thickBot="1">
       <c r="A398" s="6" t="s">
         <v>227</v>
       </c>
@@ -29696,7 +29843,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="399" spans="1:10" ht="16.2" thickBot="1">
+    <row r="399" spans="1:10" ht="16.5" thickBot="1">
       <c r="A399" s="6" t="s">
         <v>228</v>
       </c>
@@ -29712,7 +29859,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="16.2" thickBot="1">
+    <row r="400" spans="1:10" ht="16.5" thickBot="1">
       <c r="A400" s="6" t="s">
         <v>229</v>
       </c>
@@ -29728,7 +29875,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="16.2" thickBot="1">
+    <row r="401" spans="1:6" ht="16.5" thickBot="1">
       <c r="A401" s="6" t="s">
         <v>230</v>
       </c>
@@ -29744,7 +29891,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="16.2" thickBot="1">
+    <row r="402" spans="1:6" ht="16.5" thickBot="1">
       <c r="A402" s="6" t="s">
         <v>231</v>
       </c>
@@ -29760,7 +29907,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="15" thickBot="1">
+    <row r="403" spans="1:6" ht="15.75" thickBot="1">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -29768,7 +29915,7 @@
       <c r="E403" s="5"/>
       <c r="F403" s="5"/>
     </row>
-    <row r="404" spans="1:6" ht="15" thickBot="1">
+    <row r="404" spans="1:6" ht="15.75" thickBot="1">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -29785,9 +29932,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9447E658-0406-4337-92E7-EF22271613D0}">
   <dimension ref="A1:I526"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="11.44140625" style="23"/>
+    <col min="1" max="9" width="11.42578125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -32685,10 +32832,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7AC209-399B-46DE-A186-E777887E2AAF}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="91.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -34610,9 +34757,9 @@
   <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="45" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="66.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.109375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="178.88671875" customWidth="1"/>
+    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="178.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="45" customHeight="1">
@@ -34642,7 +34789,7 @@
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" spans="1:10" ht="14.4" customHeight="1">
+    <row r="3" spans="1:10" ht="14.45" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>834</v>
       </c>
@@ -34658,7 +34805,7 @@
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4" customHeight="1">
+    <row r="4" spans="1:10" ht="14.45" customHeight="1">
       <c r="A4" s="27" t="s">
         <v>835</v>
       </c>
@@ -34674,7 +34821,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="1:10" ht="14.4" customHeight="1">
+    <row r="5" spans="1:10" ht="14.45" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>836</v>
       </c>
@@ -34690,7 +34837,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4" customHeight="1">
+    <row r="6" spans="1:10" ht="14.45" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>837</v>
       </c>
@@ -34706,7 +34853,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="1:10" ht="14.4" customHeight="1">
+    <row r="7" spans="1:10" ht="14.45" customHeight="1">
       <c r="A7" s="22" t="s">
         <v>838</v>
       </c>
@@ -34722,7 +34869,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10" ht="14.4" customHeight="1">
+    <row r="8" spans="1:10" ht="14.45" customHeight="1">
       <c r="A8" s="27" t="s">
         <v>839</v>
       </c>
@@ -34738,7 +34885,7 @@
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
     </row>
-    <row r="9" spans="1:10" ht="14.4" customHeight="1">
+    <row r="9" spans="1:10" ht="14.45" customHeight="1">
       <c r="A9" s="22" t="s">
         <v>840</v>
       </c>
@@ -34754,7 +34901,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
     </row>
-    <row r="10" spans="1:10" ht="14.4" customHeight="1">
+    <row r="10" spans="1:10" ht="14.45" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>841</v>
       </c>
@@ -34770,7 +34917,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
-    <row r="11" spans="1:10" ht="14.4" customHeight="1">
+    <row r="11" spans="1:10" ht="14.45" customHeight="1">
       <c r="A11" s="22" t="s">
         <v>842</v>
       </c>
@@ -34786,7 +34933,7 @@
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
     </row>
-    <row r="12" spans="1:10" ht="14.4" customHeight="1">
+    <row r="12" spans="1:10" ht="14.45" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>843</v>
       </c>
@@ -34802,7 +34949,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4" customHeight="1">
+    <row r="13" spans="1:10" ht="14.45" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>844</v>
       </c>
@@ -34818,7 +34965,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="14.4" customHeight="1">
+    <row r="14" spans="1:10" ht="14.45" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>845</v>
       </c>
@@ -34834,7 +34981,7 @@
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
     </row>
-    <row r="15" spans="1:10" ht="14.4" customHeight="1">
+    <row r="15" spans="1:10" ht="14.45" customHeight="1">
       <c r="A15" s="35" t="s">
         <v>846</v>
       </c>
@@ -34850,7 +34997,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4" customHeight="1">
+    <row r="16" spans="1:10" ht="14.45" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>1165</v>
       </c>
@@ -34866,7 +35013,7 @@
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
     </row>
-    <row r="17" spans="2:10" ht="14.4" customHeight="1">
+    <row r="17" spans="2:10" ht="14.45" customHeight="1">
       <c r="D17" s="22" t="s">
         <v>1135</v>
       </c>
@@ -34877,7 +35024,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:10" ht="14.4" customHeight="1">
+    <row r="18" spans="2:10" ht="14.45" customHeight="1">
       <c r="B18" s="16" t="s">
         <v>812</v>
       </c>
@@ -34891,7 +35038,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:10" ht="14.4" customHeight="1">
+    <row r="19" spans="2:10" ht="14.45" customHeight="1">
       <c r="B19" s="16" t="s">
         <v>813</v>
       </c>
@@ -34908,7 +35055,7 @@
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:10" ht="14.4" customHeight="1">
+    <row r="20" spans="2:10" ht="14.45" customHeight="1">
       <c r="B20" s="16" t="s">
         <v>814</v>
       </c>
@@ -34922,7 +35069,7 @@
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:10" ht="14.4" customHeight="1">
+    <row r="21" spans="2:10" ht="14.45" customHeight="1">
       <c r="B21" s="16" t="s">
         <v>815</v>
       </c>
@@ -34936,7 +35083,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
     </row>
-    <row r="22" spans="2:10" ht="14.4" customHeight="1">
+    <row r="22" spans="2:10" ht="14.45" customHeight="1">
       <c r="B22" s="17"/>
       <c r="D22" s="22" t="s">
         <v>1126</v>
@@ -34948,7 +35095,7 @@
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
     </row>
-    <row r="23" spans="2:10" ht="14.4" customHeight="1">
+    <row r="23" spans="2:10" ht="14.45" customHeight="1">
       <c r="B23" s="16" t="s">
         <v>816</v>
       </c>
@@ -34962,7 +35109,7 @@
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:10" ht="14.4" customHeight="1">
+    <row r="24" spans="2:10" ht="14.45" customHeight="1">
       <c r="B24" s="16" t="s">
         <v>817</v>
       </c>
@@ -34976,7 +35123,7 @@
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:10" ht="14.4" customHeight="1">
+    <row r="25" spans="2:10" ht="14.45" customHeight="1">
       <c r="B25" s="17"/>
       <c r="D25" s="22" t="s">
         <v>1139</v>
@@ -34988,7 +35135,7 @@
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:10" ht="14.4" customHeight="1">
+    <row r="26" spans="2:10" ht="14.45" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>818</v>
       </c>
@@ -35002,7 +35149,7 @@
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
     </row>
-    <row r="27" spans="2:10" ht="14.4" customHeight="1">
+    <row r="27" spans="2:10" ht="14.45" customHeight="1">
       <c r="B27" s="16" t="s">
         <v>819</v>
       </c>
@@ -35016,7 +35163,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="2:10" ht="14.4" customHeight="1">
+    <row r="28" spans="2:10" ht="14.45" customHeight="1">
       <c r="B28" s="17"/>
       <c r="D28" s="22" t="s">
         <v>1126</v>
@@ -35028,7 +35175,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:10" ht="14.4" customHeight="1">
+    <row r="29" spans="2:10" ht="14.45" customHeight="1">
       <c r="B29" s="16" t="s">
         <v>820</v>
       </c>
@@ -35042,7 +35189,7 @@
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:10" ht="14.4" customHeight="1">
+    <row r="30" spans="2:10" ht="14.45" customHeight="1">
       <c r="B30" s="16" t="s">
         <v>821</v>
       </c>
@@ -35056,7 +35203,7 @@
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
     </row>
-    <row r="31" spans="2:10" ht="14.4" customHeight="1">
+    <row r="31" spans="2:10" ht="14.45" customHeight="1">
       <c r="B31" s="16" t="s">
         <v>822</v>
       </c>
@@ -35070,7 +35217,7 @@
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
     </row>
-    <row r="32" spans="2:10" ht="14.4" customHeight="1">
+    <row r="32" spans="2:10" ht="14.45" customHeight="1">
       <c r="B32" s="17"/>
       <c r="D32" s="22" t="s">
         <v>1130</v>
@@ -35082,7 +35229,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:10" ht="14.4" customHeight="1">
+    <row r="33" spans="2:10" ht="14.45" customHeight="1">
       <c r="B33" s="16" t="s">
         <v>823</v>
       </c>
@@ -35096,7 +35243,7 @@
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:10" ht="14.4" customHeight="1">
+    <row r="34" spans="2:10" ht="14.45" customHeight="1">
       <c r="B34" s="16" t="s">
         <v>824</v>
       </c>
@@ -35110,7 +35257,7 @@
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:10" ht="14.4" customHeight="1">
+    <row r="35" spans="2:10" ht="14.45" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>825</v>
       </c>
@@ -35124,7 +35271,7 @@
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
     </row>
-    <row r="36" spans="2:10" ht="14.4" customHeight="1">
+    <row r="36" spans="2:10" ht="14.45" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="22" t="s">
         <v>1134</v>
@@ -35136,7 +35283,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:10" ht="14.4" customHeight="1">
+    <row r="37" spans="2:10" ht="14.45" customHeight="1">
       <c r="B37" s="16" t="s">
         <v>826</v>
       </c>
@@ -35150,7 +35297,7 @@
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:10" ht="14.4" customHeight="1">
+    <row r="38" spans="2:10" ht="14.45" customHeight="1">
       <c r="B38" s="16" t="s">
         <v>827</v>
       </c>
@@ -35164,7 +35311,7 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="2:10" ht="14.4" customHeight="1">
+    <row r="39" spans="2:10" ht="14.45" customHeight="1">
       <c r="B39" s="16" t="s">
         <v>828</v>
       </c>
@@ -35178,7 +35325,7 @@
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="2:10" ht="14.4" customHeight="1">
+    <row r="40" spans="2:10" ht="14.45" customHeight="1">
       <c r="B40" s="16" t="s">
         <v>829</v>
       </c>
@@ -35192,7 +35339,7 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="2:10" ht="14.4" customHeight="1">
+    <row r="41" spans="2:10" ht="14.45" customHeight="1">
       <c r="B41" s="16" t="s">
         <v>830</v>
       </c>
@@ -35206,7 +35353,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="2:10" ht="14.4" customHeight="1">
+    <row r="42" spans="2:10" ht="14.45" customHeight="1">
       <c r="D42" s="22" t="s">
         <v>1148</v>
       </c>
@@ -35217,7 +35364,7 @@
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
     </row>
-    <row r="43" spans="2:10" ht="14.4" customHeight="1">
+    <row r="43" spans="2:10" ht="14.45" customHeight="1">
       <c r="D43" s="22" t="s">
         <v>1149</v>
       </c>
@@ -35228,7 +35375,7 @@
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
     </row>
-    <row r="44" spans="2:10" ht="14.4" customHeight="1">
+    <row r="44" spans="2:10" ht="14.45" customHeight="1">
       <c r="B44" s="18" t="s">
         <v>832</v>
       </c>
@@ -35243,7 +35390,7 @@
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
     </row>
-    <row r="45" spans="2:10" ht="14.4" customHeight="1">
+    <row r="45" spans="2:10" ht="14.45" customHeight="1">
       <c r="B45" s="18" t="s">
         <v>833</v>
       </c>
@@ -35258,7 +35405,7 @@
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:10" ht="14.4" customHeight="1">
+    <row r="46" spans="2:10" ht="14.45" customHeight="1">
       <c r="B46" s="18" t="s">
         <v>834</v>
       </c>
@@ -35273,7 +35420,7 @@
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
     </row>
-    <row r="47" spans="2:10" ht="14.4" customHeight="1">
+    <row r="47" spans="2:10" ht="14.45" customHeight="1">
       <c r="B47" s="18" t="s">
         <v>835</v>
       </c>
@@ -35288,7 +35435,7 @@
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
     </row>
-    <row r="48" spans="2:10" ht="14.4" customHeight="1">
+    <row r="48" spans="2:10" ht="14.45" customHeight="1">
       <c r="B48" s="18" t="s">
         <v>836</v>
       </c>
@@ -35303,7 +35450,7 @@
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
     </row>
-    <row r="49" spans="2:10" ht="14.4" customHeight="1">
+    <row r="49" spans="2:10" ht="14.45" customHeight="1">
       <c r="B49" s="18" t="s">
         <v>837</v>
       </c>
@@ -35318,7 +35465,7 @@
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
     </row>
-    <row r="50" spans="2:10" ht="14.4" customHeight="1">
+    <row r="50" spans="2:10" ht="14.45" customHeight="1">
       <c r="B50" s="18" t="s">
         <v>838</v>
       </c>
@@ -35333,7 +35480,7 @@
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
     </row>
-    <row r="51" spans="2:10" ht="14.4" customHeight="1">
+    <row r="51" spans="2:10" ht="14.45" customHeight="1">
       <c r="B51" s="18" t="s">
         <v>839</v>
       </c>
@@ -35348,7 +35495,7 @@
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
     </row>
-    <row r="52" spans="2:10" ht="14.4" customHeight="1">
+    <row r="52" spans="2:10" ht="14.45" customHeight="1">
       <c r="B52" s="18" t="s">
         <v>840</v>
       </c>
@@ -35363,7 +35510,7 @@
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
     </row>
-    <row r="53" spans="2:10" ht="14.4" customHeight="1">
+    <row r="53" spans="2:10" ht="14.45" customHeight="1">
       <c r="B53" s="18" t="s">
         <v>841</v>
       </c>
@@ -35378,7 +35525,7 @@
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
     </row>
-    <row r="54" spans="2:10" ht="14.4" customHeight="1">
+    <row r="54" spans="2:10" ht="14.45" customHeight="1">
       <c r="B54" s="18" t="s">
         <v>842</v>
       </c>
@@ -35393,7 +35540,7 @@
       <c r="I54" s="23"/>
       <c r="J54" s="23"/>
     </row>
-    <row r="55" spans="2:10" ht="14.4" customHeight="1">
+    <row r="55" spans="2:10" ht="14.45" customHeight="1">
       <c r="B55" s="18" t="s">
         <v>843</v>
       </c>
@@ -35408,7 +35555,7 @@
       <c r="I55" s="23"/>
       <c r="J55" s="23"/>
     </row>
-    <row r="56" spans="2:10" ht="14.4" customHeight="1">
+    <row r="56" spans="2:10" ht="14.45" customHeight="1">
       <c r="B56" s="18" t="s">
         <v>844</v>
       </c>
@@ -35423,7 +35570,7 @@
       <c r="I56" s="23"/>
       <c r="J56" s="23"/>
     </row>
-    <row r="57" spans="2:10" ht="14.4" customHeight="1">
+    <row r="57" spans="2:10" ht="14.45" customHeight="1">
       <c r="B57" s="18" t="s">
         <v>845</v>
       </c>
@@ -35438,7 +35585,7 @@
       <c r="I57" s="23"/>
       <c r="J57" s="23"/>
     </row>
-    <row r="58" spans="2:10" ht="14.4" customHeight="1">
+    <row r="58" spans="2:10" ht="14.45" customHeight="1">
       <c r="B58" s="18" t="s">
         <v>846</v>
       </c>
@@ -35453,7 +35600,7 @@
       <c r="I58" s="23"/>
       <c r="J58" s="23"/>
     </row>
-    <row r="59" spans="2:10" ht="14.4" customHeight="1">
+    <row r="59" spans="2:10" ht="14.45" customHeight="1">
       <c r="B59" s="18" t="s">
         <v>847</v>
       </c>
@@ -35468,7 +35615,7 @@
       <c r="I59" s="23"/>
       <c r="J59" s="23"/>
     </row>
-    <row r="60" spans="2:10" ht="14.4" customHeight="1">
+    <row r="60" spans="2:10" ht="14.45" customHeight="1">
       <c r="D60" s="22" t="s">
         <v>1156</v>
       </c>
@@ -35479,7 +35626,7 @@
       <c r="I60" s="23"/>
       <c r="J60" s="23"/>
     </row>
-    <row r="61" spans="2:10" ht="14.4" customHeight="1">
+    <row r="61" spans="2:10" ht="14.45" customHeight="1">
       <c r="D61" s="22" t="s">
         <v>1157</v>
       </c>
@@ -35490,7 +35637,7 @@
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
     </row>
-    <row r="62" spans="2:10" ht="14.4" customHeight="1">
+    <row r="62" spans="2:10" ht="14.45" customHeight="1">
       <c r="D62" s="22" t="s">
         <v>1134</v>
       </c>
@@ -35501,7 +35648,7 @@
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
     </row>
-    <row r="63" spans="2:10" ht="14.4" customHeight="1">
+    <row r="63" spans="2:10" ht="14.45" customHeight="1">
       <c r="D63" s="22" t="s">
         <v>1128</v>
       </c>
@@ -35512,7 +35659,7 @@
       <c r="I63" s="23"/>
       <c r="J63" s="23"/>
     </row>
-    <row r="64" spans="2:10" ht="14.4" customHeight="1">
+    <row r="64" spans="2:10" ht="14.45" customHeight="1">
       <c r="D64" s="22" t="s">
         <v>1135</v>
       </c>
@@ -35523,7 +35670,7 @@
       <c r="I64" s="23"/>
       <c r="J64" s="23"/>
     </row>
-    <row r="65" spans="4:10" ht="14.4" customHeight="1">
+    <row r="65" spans="4:10" ht="14.45" customHeight="1">
       <c r="D65" s="22" t="s">
         <v>1126</v>
       </c>
@@ -35534,7 +35681,7 @@
       <c r="I65" s="23"/>
       <c r="J65" s="23"/>
     </row>
-    <row r="66" spans="4:10" ht="14.4" customHeight="1">
+    <row r="66" spans="4:10" ht="14.45" customHeight="1">
       <c r="D66" s="22" t="s">
         <v>1136</v>
       </c>
@@ -35545,7 +35692,7 @@
       <c r="I66" s="23"/>
       <c r="J66" s="23"/>
     </row>
-    <row r="67" spans="4:10" ht="14.4" customHeight="1">
+    <row r="67" spans="4:10" ht="14.45" customHeight="1">
       <c r="D67" s="22" t="s">
         <v>1158</v>
       </c>
@@ -35556,7 +35703,7 @@
       <c r="I67" s="23"/>
       <c r="J67" s="23"/>
     </row>
-    <row r="68" spans="4:10" ht="14.4" customHeight="1">
+    <row r="68" spans="4:10" ht="14.45" customHeight="1">
       <c r="D68" s="22" t="s">
         <v>1159</v>
       </c>
@@ -35567,7 +35714,7 @@
       <c r="I68" s="23"/>
       <c r="J68" s="23"/>
     </row>
-    <row r="69" spans="4:10" ht="14.4" customHeight="1">
+    <row r="69" spans="4:10" ht="14.45" customHeight="1">
       <c r="D69" s="22" t="s">
         <v>1160</v>
       </c>
@@ -35578,7 +35725,7 @@
       <c r="I69" s="23"/>
       <c r="J69" s="23"/>
     </row>
-    <row r="70" spans="4:10" ht="14.4" customHeight="1">
+    <row r="70" spans="4:10" ht="14.45" customHeight="1">
       <c r="D70" s="22" t="s">
         <v>1161</v>
       </c>
@@ -35589,7 +35736,7 @@
       <c r="I70" s="23"/>
       <c r="J70" s="23"/>
     </row>
-    <row r="71" spans="4:10" ht="14.4" customHeight="1">
+    <row r="71" spans="4:10" ht="14.45" customHeight="1">
       <c r="D71" s="22" t="s">
         <v>1162</v>
       </c>
@@ -35600,7 +35747,7 @@
       <c r="I71" s="23"/>
       <c r="J71" s="23"/>
     </row>
-    <row r="72" spans="4:10" ht="14.4" customHeight="1">
+    <row r="72" spans="4:10" ht="14.45" customHeight="1">
       <c r="E72" s="23"/>
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
@@ -35608,7 +35755,7 @@
       <c r="I72" s="23"/>
       <c r="J72" s="23"/>
     </row>
-    <row r="73" spans="4:10" ht="14.4">
+    <row r="73" spans="4:10" ht="15">
       <c r="E73" s="23"/>
       <c r="F73" s="23"/>
       <c r="G73" s="23"/>
@@ -35616,99 +35763,99 @@
       <c r="I73" s="23"/>
       <c r="J73" s="23"/>
     </row>
-    <row r="74" spans="4:10" ht="14.4"/>
-    <row r="75" spans="4:10" ht="14.4"/>
-    <row r="76" spans="4:10" ht="14.4"/>
-    <row r="77" spans="4:10" ht="14.4"/>
-    <row r="78" spans="4:10" ht="14.4"/>
-    <row r="79" spans="4:10" ht="14.4"/>
-    <row r="80" spans="4:10" ht="14.4"/>
-    <row r="81" ht="14.4"/>
-    <row r="82" ht="14.4"/>
-    <row r="83" ht="14.4"/>
-    <row r="84" ht="14.4"/>
-    <row r="85" ht="14.4"/>
-    <row r="86" ht="14.4"/>
-    <row r="87" ht="14.4"/>
-    <row r="88" ht="14.4"/>
-    <row r="89" ht="14.4"/>
-    <row r="90" ht="14.4"/>
-    <row r="91" ht="14.4"/>
-    <row r="92" ht="14.4"/>
-    <row r="93" ht="14.4"/>
-    <row r="94" ht="14.4"/>
-    <row r="95" ht="14.4"/>
-    <row r="96" ht="14.4"/>
-    <row r="97" ht="14.4"/>
-    <row r="98" ht="14.4"/>
-    <row r="99" ht="14.4"/>
-    <row r="100" ht="14.4"/>
-    <row r="101" ht="14.4"/>
-    <row r="102" ht="14.4"/>
-    <row r="103" ht="14.4"/>
-    <row r="104" ht="14.4"/>
-    <row r="105" ht="14.4"/>
-    <row r="106" ht="14.4"/>
-    <row r="107" ht="14.4"/>
-    <row r="108" ht="14.4"/>
-    <row r="109" ht="14.4"/>
-    <row r="110" ht="14.4"/>
-    <row r="111" ht="14.4"/>
-    <row r="112" ht="14.4"/>
-    <row r="113" ht="14.4"/>
-    <row r="114" ht="14.4"/>
-    <row r="115" ht="14.4"/>
-    <row r="116" ht="14.4"/>
-    <row r="117" ht="14.4"/>
-    <row r="118" ht="14.4"/>
-    <row r="119" ht="14.4"/>
-    <row r="120" ht="14.4"/>
-    <row r="121" ht="14.4"/>
-    <row r="122" ht="14.4"/>
-    <row r="123" ht="14.4"/>
-    <row r="124" ht="14.4"/>
-    <row r="125" ht="14.4"/>
-    <row r="126" ht="14.4"/>
-    <row r="127" ht="14.4"/>
-    <row r="128" ht="14.4"/>
-    <row r="129" ht="14.4"/>
-    <row r="130" ht="14.4"/>
-    <row r="131" ht="14.4"/>
-    <row r="132" ht="14.4"/>
-    <row r="133" ht="14.4"/>
-    <row r="134" ht="14.4"/>
-    <row r="135" ht="14.4"/>
-    <row r="136" ht="14.4"/>
-    <row r="137" ht="14.4"/>
-    <row r="138" ht="14.4"/>
-    <row r="139" ht="14.4"/>
-    <row r="140" ht="14.4"/>
-    <row r="141" ht="14.4"/>
-    <row r="142" ht="14.4"/>
-    <row r="143" ht="14.4"/>
-    <row r="144" ht="14.4"/>
-    <row r="145" ht="14.4"/>
-    <row r="146" ht="14.4"/>
-    <row r="147" ht="14.4"/>
-    <row r="148" ht="14.4"/>
-    <row r="149" ht="14.4"/>
-    <row r="150" ht="14.4"/>
-    <row r="151" ht="14.4"/>
-    <row r="152" ht="14.4"/>
-    <row r="153" ht="14.4"/>
-    <row r="154" ht="14.4"/>
-    <row r="155" ht="14.4"/>
-    <row r="156" ht="14.4"/>
-    <row r="157" ht="14.4"/>
-    <row r="158" ht="14.4"/>
-    <row r="159" ht="14.4"/>
-    <row r="160" ht="14.4"/>
-    <row r="161" ht="14.4"/>
-    <row r="162" ht="14.4"/>
-    <row r="163" ht="14.4"/>
-    <row r="164" ht="14.4"/>
-    <row r="165" ht="14.4"/>
-    <row r="166" ht="14.4"/>
+    <row r="74" spans="4:10" ht="15"/>
+    <row r="75" spans="4:10" ht="15"/>
+    <row r="76" spans="4:10" ht="15"/>
+    <row r="77" spans="4:10" ht="15"/>
+    <row r="78" spans="4:10" ht="15"/>
+    <row r="79" spans="4:10" ht="15"/>
+    <row r="80" spans="4:10" ht="15"/>
+    <row r="81" ht="15"/>
+    <row r="82" ht="15"/>
+    <row r="83" ht="15"/>
+    <row r="84" ht="15"/>
+    <row r="85" ht="15"/>
+    <row r="86" ht="15"/>
+    <row r="87" ht="15"/>
+    <row r="88" ht="15"/>
+    <row r="89" ht="15"/>
+    <row r="90" ht="15"/>
+    <row r="91" ht="15"/>
+    <row r="92" ht="15"/>
+    <row r="93" ht="15"/>
+    <row r="94" ht="15"/>
+    <row r="95" ht="15"/>
+    <row r="96" ht="15"/>
+    <row r="97" ht="15"/>
+    <row r="98" ht="15"/>
+    <row r="99" ht="15"/>
+    <row r="100" ht="15"/>
+    <row r="101" ht="15"/>
+    <row r="102" ht="15"/>
+    <row r="103" ht="15"/>
+    <row r="104" ht="15"/>
+    <row r="105" ht="15"/>
+    <row r="106" ht="15"/>
+    <row r="107" ht="15"/>
+    <row r="108" ht="15"/>
+    <row r="109" ht="15"/>
+    <row r="110" ht="15"/>
+    <row r="111" ht="15"/>
+    <row r="112" ht="15"/>
+    <row r="113" ht="15"/>
+    <row r="114" ht="15"/>
+    <row r="115" ht="15"/>
+    <row r="116" ht="15"/>
+    <row r="117" ht="15"/>
+    <row r="118" ht="15"/>
+    <row r="119" ht="15"/>
+    <row r="120" ht="15"/>
+    <row r="121" ht="15"/>
+    <row r="122" ht="15"/>
+    <row r="123" ht="15"/>
+    <row r="124" ht="15"/>
+    <row r="125" ht="15"/>
+    <row r="126" ht="15"/>
+    <row r="127" ht="15"/>
+    <row r="128" ht="15"/>
+    <row r="129" ht="15"/>
+    <row r="130" ht="15"/>
+    <row r="131" ht="15"/>
+    <row r="132" ht="15"/>
+    <row r="133" ht="15"/>
+    <row r="134" ht="15"/>
+    <row r="135" ht="15"/>
+    <row r="136" ht="15"/>
+    <row r="137" ht="15"/>
+    <row r="138" ht="15"/>
+    <row r="139" ht="15"/>
+    <row r="140" ht="15"/>
+    <row r="141" ht="15"/>
+    <row r="142" ht="15"/>
+    <row r="143" ht="15"/>
+    <row r="144" ht="15"/>
+    <row r="145" ht="15"/>
+    <row r="146" ht="15"/>
+    <row r="147" ht="15"/>
+    <row r="148" ht="15"/>
+    <row r="149" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="151" ht="15"/>
+    <row r="152" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="154" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
+    <row r="157" ht="15"/>
+    <row r="158" ht="15"/>
+    <row r="159" ht="15"/>
+    <row r="160" ht="15"/>
+    <row r="161" ht="15"/>
+    <row r="162" ht="15"/>
+    <row r="163" ht="15"/>
+    <row r="164" ht="15"/>
+    <row r="165" ht="15"/>
+    <row r="166" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35717,15 +35864,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7DD0CD-6695-4D3C-9518-BDB565BCCF21}">
   <dimension ref="B3:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="101.44140625" customWidth="1"/>
+    <col min="2" max="2" width="101.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" s="2"/>
     </row>
-    <row r="5" spans="2:2" ht="409.6">
+    <row r="5" spans="2:2" ht="409.5">
       <c r="B5" s="2" t="s">
         <v>769</v>
       </c>
@@ -35741,17 +35888,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L150"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="65"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="65"/>
     <col min="7" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.8" thickBot="1">
+    <row r="1" spans="1:12" ht="48" thickBot="1">
       <c r="A1" t="s">
         <v>760</v>
       </c>
@@ -36647,7 +36794,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" thickBot="1">
+    <row r="42" spans="1:12" ht="15.75" thickBot="1">
       <c r="A42" s="49">
         <v>41</v>
       </c>
@@ -36670,7 +36817,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="16.2" thickBot="1">
+    <row r="43" spans="1:12" ht="16.5" thickBot="1">
       <c r="A43" s="49">
         <v>42</v>
       </c>
@@ -36693,7 +36840,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="16.2" thickBot="1">
+    <row r="44" spans="1:12" ht="16.5" thickBot="1">
       <c r="A44" s="49">
         <v>42</v>
       </c>
@@ -37379,7 +37526,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" thickBot="1">
+    <row r="75" spans="1:12" ht="15.75" thickBot="1">
       <c r="A75" s="49">
         <v>71</v>
       </c>
@@ -37402,7 +37549,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="16.2" thickBot="1">
+    <row r="76" spans="1:12" ht="16.5" thickBot="1">
       <c r="A76" s="49">
         <v>72</v>
       </c>
@@ -37425,7 +37572,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="16.2" thickBot="1">
+    <row r="77" spans="1:12" ht="16.5" thickBot="1">
       <c r="A77" s="49">
         <v>73</v>
       </c>
@@ -37738,7 +37885,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" thickBot="1">
+    <row r="94" spans="1:12" ht="15.75" thickBot="1">
       <c r="A94" s="49">
         <v>89</v>
       </c>
@@ -37761,7 +37908,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="16.2" thickBot="1">
+    <row r="95" spans="1:12" ht="16.5" thickBot="1">
       <c r="A95" s="49">
         <v>72</v>
       </c>
@@ -37824,7 +37971,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" thickBot="1">
+    <row r="98" spans="1:12" ht="15.75" thickBot="1">
       <c r="A98" s="49"/>
       <c r="B98" s="22" t="s">
         <v>214</v>
@@ -37843,7 +37990,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="16.2" thickBot="1">
+    <row r="99" spans="1:12" ht="16.5" thickBot="1">
       <c r="A99" s="49">
         <v>92</v>
       </c>
@@ -37866,7 +38013,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="16.2" thickBot="1">
+    <row r="100" spans="1:12" ht="16.5" thickBot="1">
       <c r="A100" s="49">
         <v>92</v>
       </c>
@@ -37889,7 +38036,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="16.2" thickBot="1">
+    <row r="101" spans="1:12" ht="16.5" thickBot="1">
       <c r="A101" s="49">
         <v>92</v>
       </c>
@@ -37912,7 +38059,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="16.2" thickBot="1">
+    <row r="102" spans="1:12" ht="16.5" thickBot="1">
       <c r="A102" s="49">
         <v>92</v>
       </c>
@@ -37933,7 +38080,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" thickBot="1">
+    <row r="103" spans="1:12" ht="15.75" thickBot="1">
       <c r="A103" s="49">
         <v>92</v>
       </c>
@@ -37951,7 +38098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" thickBot="1">
+    <row r="104" spans="1:12" ht="15.75" thickBot="1">
       <c r="A104" s="49">
         <v>93</v>
       </c>
@@ -38275,7 +38422,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" thickBot="1">
+    <row r="118" spans="1:12" ht="15.75" thickBot="1">
       <c r="A118" s="58">
         <v>616</v>
       </c>
@@ -38301,7 +38448,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" thickBot="1">
+    <row r="119" spans="1:12" ht="15.75" thickBot="1">
       <c r="A119" s="49">
         <v>94</v>
       </c>
@@ -38322,7 +38469,7 @@
       <c r="J119" s="57"/>
       <c r="K119" s="57"/>
     </row>
-    <row r="120" spans="1:12" ht="15" thickBot="1">
+    <row r="120" spans="1:12" ht="15.75" thickBot="1">
       <c r="A120" s="49">
         <v>95</v>
       </c>
@@ -38350,7 +38497,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" thickBot="1">
+    <row r="121" spans="1:12" ht="15.75" thickBot="1">
       <c r="A121" s="49">
         <v>96</v>
       </c>
@@ -38378,7 +38525,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" thickBot="1">
+    <row r="122" spans="1:12" ht="15.75" thickBot="1">
       <c r="A122" s="49">
         <v>97</v>
       </c>
@@ -38406,7 +38553,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" thickBot="1">
+    <row r="123" spans="1:12" ht="15.75" thickBot="1">
       <c r="A123" s="58">
         <v>598</v>
       </c>
@@ -38429,7 +38576,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" thickBot="1">
+    <row r="124" spans="1:12" ht="15.75" thickBot="1">
       <c r="A124" s="58">
         <v>599</v>
       </c>
@@ -38452,7 +38599,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" thickBot="1">
+    <row r="125" spans="1:12" ht="15.75" thickBot="1">
       <c r="A125" s="58">
         <v>600</v>
       </c>
@@ -38475,7 +38622,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" thickBot="1">
+    <row r="126" spans="1:12" ht="15.75" thickBot="1">
       <c r="A126" s="58">
         <v>607</v>
       </c>
@@ -38498,7 +38645,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" thickBot="1">
+    <row r="127" spans="1:12" ht="15.75" thickBot="1">
       <c r="A127" s="49">
         <v>98</v>
       </c>
@@ -38526,7 +38673,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" thickBot="1">
+    <row r="128" spans="1:12" ht="15.75" thickBot="1">
       <c r="A128" s="49">
         <v>99</v>
       </c>
@@ -38554,7 +38701,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" thickBot="1">
+    <row r="129" spans="1:12" ht="15.75" thickBot="1">
       <c r="A129" s="49">
         <v>100</v>
       </c>
@@ -38575,7 +38722,7 @@
       <c r="J129" s="57"/>
       <c r="K129" s="57"/>
     </row>
-    <row r="130" spans="1:12" ht="15" thickBot="1">
+    <row r="130" spans="1:12" ht="15.75" thickBot="1">
       <c r="A130" s="49">
         <v>101</v>
       </c>
@@ -38596,7 +38743,7 @@
       <c r="J130" s="57"/>
       <c r="K130" s="57"/>
     </row>
-    <row r="131" spans="1:12" ht="15" thickBot="1">
+    <row r="131" spans="1:12" ht="15.75" thickBot="1">
       <c r="A131" s="49">
         <v>102</v>
       </c>
@@ -38619,7 +38766,7 @@
       <c r="J131" s="57"/>
       <c r="K131" s="57"/>
     </row>
-    <row r="132" spans="1:12" ht="15" thickBot="1">
+    <row r="132" spans="1:12" ht="15.75" thickBot="1">
       <c r="A132" s="49">
         <v>106</v>
       </c>
@@ -38647,7 +38794,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" thickBot="1">
+    <row r="133" spans="1:12" ht="15.75" thickBot="1">
       <c r="A133" s="49">
         <v>107</v>
       </c>
@@ -38675,7 +38822,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" thickBot="1">
+    <row r="134" spans="1:12" ht="15.75" thickBot="1">
       <c r="A134" s="49">
         <v>103</v>
       </c>
@@ -38703,7 +38850,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" thickBot="1">
+    <row r="135" spans="1:12" ht="15.75" thickBot="1">
       <c r="B135" s="55" t="s">
         <v>224</v>
       </c>
@@ -38723,7 +38870,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" thickBot="1">
+    <row r="136" spans="1:12" ht="15.75" thickBot="1">
       <c r="B136" s="64" t="s">
         <v>225</v>
       </c>
@@ -38741,7 +38888,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" thickBot="1">
+    <row r="137" spans="1:12" ht="15.75" thickBot="1">
       <c r="A137" s="49">
         <v>108</v>
       </c>
@@ -38764,7 +38911,7 @@
       <c r="J137" s="57"/>
       <c r="K137" s="57"/>
     </row>
-    <row r="138" spans="1:12" ht="15" thickBot="1">
+    <row r="138" spans="1:12" ht="15.75" thickBot="1">
       <c r="A138" s="49">
         <v>109</v>
       </c>
@@ -38787,7 +38934,7 @@
       <c r="J138" s="57"/>
       <c r="K138" s="57"/>
     </row>
-    <row r="139" spans="1:12" ht="15" thickBot="1">
+    <row r="139" spans="1:12" ht="15.75" thickBot="1">
       <c r="A139" s="49">
         <v>110</v>
       </c>
@@ -38810,7 +38957,7 @@
       <c r="J139" s="57"/>
       <c r="K139" s="57"/>
     </row>
-    <row r="140" spans="1:12" ht="15" thickBot="1">
+    <row r="140" spans="1:12" ht="15.75" thickBot="1">
       <c r="A140" s="49">
         <v>111</v>
       </c>
@@ -38833,7 +38980,7 @@
       <c r="J140" s="57"/>
       <c r="K140" s="57"/>
     </row>
-    <row r="141" spans="1:12" ht="15" thickBot="1">
+    <row r="141" spans="1:12" ht="15.75" thickBot="1">
       <c r="A141" s="58">
         <v>569</v>
       </c>
@@ -38851,7 +38998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15" thickBot="1">
+    <row r="142" spans="1:12" ht="15.75" thickBot="1">
       <c r="B142" s="55" t="s">
         <v>1568</v>
       </c>
@@ -38956,12 +39103,17 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -38987,7 +39139,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="55.2">
+    <row r="2" spans="1:7" ht="55.5">
       <c r="A2" s="38" t="s">
         <v>1191</v>
       </c>
@@ -39010,7 +39162,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.2">
+    <row r="3" spans="1:7" ht="45">
       <c r="A3" s="38" t="s">
         <v>1195</v>
       </c>
@@ -39033,7 +39185,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2">
+    <row r="4" spans="1:7" ht="45">
       <c r="A4" s="38" t="s">
         <v>1199</v>
       </c>
@@ -39056,7 +39208,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.2">
+    <row r="5" spans="1:7" ht="45">
       <c r="A5" s="38" t="s">
         <v>1204</v>
       </c>
@@ -39079,7 +39231,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2">
+    <row r="6" spans="1:7" ht="60">
       <c r="A6" s="38" t="s">
         <v>1208</v>
       </c>
@@ -39102,7 +39254,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2">
+    <row r="7" spans="1:7" ht="45">
       <c r="A7" s="38" t="s">
         <v>1211</v>
       </c>
@@ -39125,7 +39277,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="43.2">
+    <row r="8" spans="1:7" ht="45">
       <c r="A8" s="38" t="s">
         <v>1216</v>
       </c>
@@ -39148,7 +39300,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="43.2">
+    <row r="9" spans="1:7" ht="45">
       <c r="A9" s="38" t="s">
         <v>1220</v>
       </c>
@@ -39171,7 +39323,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="57.6">
+    <row r="10" spans="1:7" ht="75">
       <c r="A10" s="38" t="s">
         <v>1223</v>
       </c>
@@ -39194,7 +39346,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="57.6">
+    <row r="11" spans="1:7" ht="60">
       <c r="A11" s="38" t="s">
         <v>1226</v>
       </c>
@@ -39217,7 +39369,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57.6">
+    <row r="12" spans="1:7" ht="60">
       <c r="A12" s="38" t="s">
         <v>1230</v>
       </c>
@@ -39240,7 +39392,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2">
+    <row r="13" spans="1:7" ht="45">
       <c r="A13" s="38" t="s">
         <v>1234</v>
       </c>
@@ -39263,7 +39415,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="57.6">
+    <row r="14" spans="1:7" ht="60">
       <c r="A14" s="38" t="s">
         <v>1238</v>
       </c>
@@ -39286,7 +39438,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="72">
+    <row r="15" spans="1:7" ht="75">
       <c r="A15" s="38" t="s">
         <v>1241</v>
       </c>
@@ -39309,7 +39461,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28.8">
+    <row r="16" spans="1:7" ht="30">
       <c r="A16" s="38" t="s">
         <v>1244</v>
       </c>
@@ -39332,7 +39484,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="43.2">
+    <row r="17" spans="1:13" ht="45">
       <c r="A17" s="38" t="s">
         <v>1249</v>
       </c>
@@ -39355,7 +39507,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="57.6">
+    <row r="18" spans="1:13" ht="60">
       <c r="A18" s="38" t="s">
         <v>1252</v>
       </c>
@@ -39378,7 +39530,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="28.8">
+    <row r="19" spans="1:13" ht="30">
       <c r="A19" s="38" t="s">
         <v>1256</v>
       </c>
@@ -39401,7 +39553,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.6">
+    <row r="20" spans="1:13" ht="27.75">
       <c r="A20" s="38" t="s">
         <v>1260</v>
       </c>
@@ -39424,7 +39576,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.2">
+    <row r="21" spans="1:13" ht="45">
       <c r="A21" s="38" t="s">
         <v>1264</v>
       </c>
@@ -39447,7 +39599,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28.8">
+    <row r="22" spans="1:13" ht="30">
       <c r="A22" s="38" t="s">
         <v>1267</v>
       </c>
@@ -39470,7 +39622,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="43.2">
+    <row r="23" spans="1:13" ht="45">
       <c r="A23" s="38" t="s">
         <v>1270</v>
       </c>
@@ -39493,7 +39645,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.2">
+    <row r="24" spans="1:13" ht="45">
       <c r="A24" s="38" t="s">
         <v>1273</v>
       </c>
@@ -39516,7 +39668,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.2">
+    <row r="25" spans="1:13" ht="60">
       <c r="A25" s="38" t="s">
         <v>1276</v>
       </c>
@@ -39535,8 +39687,11 @@
       <c r="F25" s="38" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="42">
+      <c r="G25" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="42.75">
       <c r="A26" s="38" t="s">
         <v>1279</v>
       </c>
@@ -39552,8 +39707,14 @@
       <c r="E26" s="38" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.8">
+      <c r="F26" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30">
       <c r="A27" s="38" t="s">
         <v>1283</v>
       </c>
@@ -39569,8 +39730,14 @@
       <c r="E27" s="38" t="s">
         <v>1286</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="43.2">
+      <c r="F27" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="45">
       <c r="A28" s="38" t="s">
         <v>1287</v>
       </c>
@@ -39586,8 +39753,17 @@
       <c r="E28" s="38" t="s">
         <v>1289</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="43.2">
+      <c r="F28" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="45">
       <c r="A29" s="38" t="s">
         <v>1290</v>
       </c>
@@ -39603,8 +39779,14 @@
       <c r="E29" s="38" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="43.2">
+      <c r="F29" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="60">
       <c r="A30" s="38" t="s">
         <v>1293</v>
       </c>
@@ -39620,8 +39802,29 @@
       <c r="E30" s="38" t="s">
         <v>1296</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="57.6">
+      <c r="F30" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>1651</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>1652</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="60">
       <c r="A31" s="38" t="s">
         <v>1297</v>
       </c>
@@ -39637,8 +39840,17 @@
       <c r="E31" s="38" t="s">
         <v>1300</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="57.6">
+      <c r="F31" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="60">
       <c r="A32" s="38" t="s">
         <v>1301</v>
       </c>
@@ -39654,8 +39866,14 @@
       <c r="E32" s="38" t="s">
         <v>1303</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="43.2">
+      <c r="F32" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="45">
       <c r="A33" s="38" t="s">
         <v>1304</v>
       </c>
@@ -39672,7 +39890,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="43.2">
+    <row r="34" spans="1:5" ht="45">
       <c r="A34" s="38" t="s">
         <v>1308</v>
       </c>
@@ -39689,7 +39907,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="43.2">
+    <row r="35" spans="1:5" ht="45">
       <c r="A35" s="38" t="s">
         <v>1312</v>
       </c>
@@ -39706,7 +39924,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="28.8">
+    <row r="36" spans="1:5" ht="30">
       <c r="A36" s="38" t="s">
         <v>1315</v>
       </c>
@@ -39723,7 +39941,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="28.8">
+    <row r="37" spans="1:5" ht="30">
       <c r="A37" s="38" t="s">
         <v>1318</v>
       </c>
@@ -39740,7 +39958,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="28.8">
+    <row r="38" spans="1:5" ht="45">
       <c r="A38" s="38" t="s">
         <v>1322</v>
       </c>
@@ -39757,7 +39975,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="43.2">
+    <row r="39" spans="1:5" ht="45">
       <c r="A39" s="38" t="s">
         <v>1326</v>
       </c>
@@ -39774,7 +39992,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="43.2">
+    <row r="40" spans="1:5" ht="45">
       <c r="A40" s="38" t="s">
         <v>1330</v>
       </c>
@@ -39791,7 +40009,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="43.2">
+    <row r="41" spans="1:5" ht="45">
       <c r="A41" s="38" t="s">
         <v>1333</v>
       </c>
@@ -39808,7 +40026,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="38" t="s">
         <v>1336</v>
       </c>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72E091C-0488-4CD6-A8F3-5226143CCA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6CCB49-8616-4C07-AF9D-87A7743B8679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="1658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5850" uniqueCount="1660">
   <si>
     <t>Nº</t>
   </si>
@@ -12655,6 +12655,9 @@
   - test_i2_low_confidence_table_routes_to_human_review_conceptually</t>
   </si>
   <si>
+    <t>red</t>
+  </si>
+  <si>
     <t>detectado issue de seguridad</t>
   </si>
   <si>
@@ -12727,7 +12730,10 @@
     <t xml:space="preserve"> @frontend-tdd can then implement GREEN for those new failing tests.</t>
   </si>
   <si>
-    <t xml:space="preserve"> @qa-agent RED plan for S3-0</t>
+    <t>E2E pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @qa-agent RED plan for S3-</t>
   </si>
 </sst>
 </file>
@@ -12987,7 +12993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13163,6 +13169,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18953,67 +18962,67 @@
     <row r="236" spans="2:2" hidden="1"/>
     <row r="243" spans="1:1">
       <c r="A243" s="16" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="16" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="16" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="16" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="16" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="16" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="16" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="16" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="16" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="16" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="16" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="16" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="16" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
   </sheetData>
@@ -39484,7 +39493,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="45">
+    <row r="17" spans="1:8" ht="45">
       <c r="A17" s="38" t="s">
         <v>1249</v>
       </c>
@@ -39507,7 +39516,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="60">
+    <row r="18" spans="1:8" ht="60">
       <c r="A18" s="38" t="s">
         <v>1252</v>
       </c>
@@ -39530,7 +39539,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="30">
+    <row r="19" spans="1:8" ht="30">
       <c r="A19" s="38" t="s">
         <v>1256</v>
       </c>
@@ -39553,7 +39562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="27.75">
+    <row r="20" spans="1:8" ht="27.75">
       <c r="A20" s="38" t="s">
         <v>1260</v>
       </c>
@@ -39576,7 +39585,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="45">
+    <row r="21" spans="1:8" ht="45">
       <c r="A21" s="38" t="s">
         <v>1264</v>
       </c>
@@ -39599,7 +39608,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="30">
+    <row r="22" spans="1:8" ht="30">
       <c r="A22" s="38" t="s">
         <v>1267</v>
       </c>
@@ -39622,7 +39631,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="45">
+    <row r="23" spans="1:8" ht="45">
       <c r="A23" s="38" t="s">
         <v>1270</v>
       </c>
@@ -39645,7 +39654,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45">
+    <row r="24" spans="1:8" ht="45">
       <c r="A24" s="38" t="s">
         <v>1273</v>
       </c>
@@ -39668,7 +39677,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="60">
+    <row r="25" spans="1:8" ht="60">
       <c r="A25" s="38" t="s">
         <v>1276</v>
       </c>
@@ -39691,7 +39700,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="42.75">
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="38" t="s">
         <v>1279</v>
       </c>
@@ -39714,7 +39723,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="30">
+    <row r="27" spans="1:8" ht="30">
       <c r="A27" s="38" t="s">
         <v>1283</v>
       </c>
@@ -39737,7 +39746,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="45">
+    <row r="28" spans="1:8" ht="45">
       <c r="A28" s="38" t="s">
         <v>1287</v>
       </c>
@@ -39760,10 +39769,10 @@
         <v>407</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>1637</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="45">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="45">
       <c r="A29" s="38" t="s">
         <v>1290</v>
       </c>
@@ -39786,7 +39795,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="60">
+    <row r="30" spans="1:8" ht="60">
       <c r="A30" s="38" t="s">
         <v>1293</v>
       </c>
@@ -39808,23 +39817,11 @@
       <c r="G30" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="I30" s="16" t="s">
-        <v>1651</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>1653</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>1654</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>1652</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>1655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="60">
+      <c r="H30" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="60">
       <c r="A31" s="38" t="s">
         <v>1297</v>
       </c>
@@ -39846,11 +39843,11 @@
       <c r="G31" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="I31" t="s">
-        <v>1656</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="60">
+      <c r="H31" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="60">
       <c r="A32" s="38" t="s">
         <v>1301</v>
       </c>
@@ -39869,11 +39866,14 @@
       <c r="F32" s="38" t="s">
         <v>404</v>
       </c>
-      <c r="I32" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="45">
+      <c r="G32" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H32" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="45">
       <c r="A33" s="38" t="s">
         <v>1304</v>
       </c>
@@ -39889,8 +39889,17 @@
       <c r="E33" s="38" t="s">
         <v>1307</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="45">
+      <c r="F33" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H33" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="45">
       <c r="A34" s="38" t="s">
         <v>1308</v>
       </c>
@@ -39906,8 +39915,32 @@
       <c r="E34" s="38" t="s">
         <v>1311</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="45">
+      <c r="F34" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H34" s="67" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="45">
       <c r="A35" s="38" t="s">
         <v>1312</v>
       </c>
@@ -39923,8 +39956,17 @@
       <c r="E35" s="38" t="s">
         <v>1314</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="30">
+      <c r="F35" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H35" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="30">
       <c r="A36" s="38" t="s">
         <v>1315</v>
       </c>
@@ -39940,8 +39982,17 @@
       <c r="E36" s="38" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="30">
+      <c r="F36" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H36" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30">
       <c r="A37" s="38" t="s">
         <v>1318</v>
       </c>
@@ -39957,8 +40008,17 @@
       <c r="E37" s="38" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="45">
+      <c r="F37" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H37" s="67" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="45">
       <c r="A38" s="38" t="s">
         <v>1322</v>
       </c>
@@ -39974,8 +40034,20 @@
       <c r="E38" s="38" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="45">
+      <c r="F38" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H38" s="67" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="45">
       <c r="A39" s="38" t="s">
         <v>1326</v>
       </c>
@@ -39991,8 +40063,20 @@
       <c r="E39" s="38" t="s">
         <v>1329</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="45">
+      <c r="F39" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H39" s="67" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="45">
       <c r="A40" s="38" t="s">
         <v>1330</v>
       </c>
@@ -40008,8 +40092,14 @@
       <c r="E40" s="38" t="s">
         <v>1332</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="45">
+      <c r="F40" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="45">
       <c r="A41" s="38" t="s">
         <v>1333</v>
       </c>
@@ -40026,7 +40116,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:13" ht="30">
       <c r="A42" s="38" t="s">
         <v>1336</v>
       </c>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6CCB49-8616-4C07-AF9D-87A7743B8679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3538C1-7E4B-4633-9A8E-494FC07C2B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5850" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="1704">
   <si>
     <t>Nº</t>
   </si>
@@ -12655,9 +12655,6 @@
   - test_i2_low_confidence_table_routes_to_human_review_conceptually</t>
   </si>
   <si>
-    <t>red</t>
-  </si>
-  <si>
     <t>detectado issue de seguridad</t>
   </si>
   <si>
@@ -12734,6 +12731,141 @@
   </si>
   <si>
     <t xml:space="preserve"> @qa-agent RED plan for S3-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. [S3-12-RED-UNIT-01] Landmark semantics on core shell                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-landmarks.a11y.test.tsx       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: missing banner, navigation, main, or contentinfo roles.      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2. [S3-12-RED-UNIT-02] Heading hierarchy integrity                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-headings.a11y.test.tsx        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: skipped levels or non-linear heading order.                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. [S3-12-RED-UNIT-03] Control accessibility + focus-visible contract           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-controls.a11y.test.tsx        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: actionable controls lack accessible name or focus-visible    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     marker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4. [S3-12-RED-UNIT-04] WCAG AA contrast threshold for critical text             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-contrast.a11y.test.tsx        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: contrast ratio for critical badge/text &lt; 4.5:1.              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5. [S3-12-RED-UNIT-05] Modal focus trap + return-focus behavior                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-dialog-focus.a11y.test.tsx    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: focus escapes dialog or trigger focus is not restored on     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     close.                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6. [S3-12-RED-UNIT-06] Live region update discipline                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/accessibility/S3-12-live-regions.a11y.test.tsx    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: status not announced or duplicate spam on single transition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  7. [S3-12-RED-INT-01] Axe critical violations gate (core shell)                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/integration/a11y/S3-12-axe-                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     critical.integration.test.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: endpoint unavailable or criticalViolations !== 0.            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  8. [S3-12-RED-INT-02] Keyboard traversal workflow integrity                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/integration/a11y/S3-12-keyboard-                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     flow.integration.test.tsx                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: traps detected or workflow not completable by keyboard.      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  9. [S3-12-RED-INT-03] Tablet layout clipping/overlap checks                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/integration/responsive/S3-12-tablet-              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     layout.integration.test.tsx                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: clipped content or overlapping panels at 768x1024 and        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     820x1180.                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  10. [S3-12-RED-INT-04] Orientation-change state persistence                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: active context/state lost after portrait↔landscape switch.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  11. [S3-12-RED-INT-05] Reduced-motion + 200% zoom operability                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/integration/a11y/S3-12-accessibility-             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     modes.integration.test.tsx                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: mode toggles degrade readability/operability.                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12. [S3-12-RED-E2E-01] Route-level a11y critical/blocker smoke                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/e2e/S3-12-a11y-tablet.spec.ts                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Fail condition: non-zero critical/blocker counters on dashboard route.       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  13. [S3-12-RED-E2E-02] Tablet portrait/landscape sanity on key flows            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Target: apps/web/src/tests/e2e/S3-12-a11y-tablet.spec.ts </t>
   </si>
 </sst>
 </file>
@@ -18962,67 +19094,67 @@
     <row r="236" spans="2:2" hidden="1"/>
     <row r="243" spans="1:1">
       <c r="A243" s="16" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="16" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="16" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="16" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="16" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="16" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="16" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="16" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="16" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="16" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="16" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="16" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="16" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -39112,13 +39244,13 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="71.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
@@ -39769,7 +39901,7 @@
         <v>407</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45">
@@ -39818,7 +39950,7 @@
         <v>407</v>
       </c>
       <c r="H30" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="60">
@@ -39844,7 +39976,7 @@
         <v>407</v>
       </c>
       <c r="H31" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="60">
@@ -39870,7 +40002,7 @@
         <v>407</v>
       </c>
       <c r="H32" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="45">
@@ -39896,7 +40028,7 @@
         <v>407</v>
       </c>
       <c r="H33" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="45">
@@ -39922,22 +40054,22 @@
         <v>407</v>
       </c>
       <c r="H34" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="I34" s="16" t="s">
+        <v>1651</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="L34" s="16" t="s">
         <v>1652</v>
       </c>
-      <c r="J34" s="16" t="s">
-        <v>1654</v>
-      </c>
-      <c r="K34" s="16" t="s">
+      <c r="M34" s="16" t="s">
         <v>1655</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>1653</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>1656</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45">
@@ -39963,7 +40095,7 @@
         <v>407</v>
       </c>
       <c r="H35" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="30">
@@ -39989,7 +40121,7 @@
         <v>407</v>
       </c>
       <c r="H36" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="30">
@@ -40015,7 +40147,7 @@
         <v>407</v>
       </c>
       <c r="H37" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="45">
@@ -40041,10 +40173,10 @@
         <v>407</v>
       </c>
       <c r="H38" s="67" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="I38" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="45">
@@ -40070,10 +40202,10 @@
         <v>407</v>
       </c>
       <c r="H39" s="67" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I39" t="s">
         <v>1658</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="45">
@@ -40096,7 +40228,7 @@
         <v>404</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>1637</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="45">
@@ -40131,6 +40263,241 @@
       </c>
       <c r="E42" s="38" t="s">
         <v>1338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="I44" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="I45" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="I46" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="I47" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="I48" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="49" spans="9:9">
+      <c r="I49" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="50" spans="9:9">
+      <c r="I50" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="51" spans="9:9">
+      <c r="I51" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="52" spans="9:9">
+      <c r="I52" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="53" spans="9:9">
+      <c r="I53" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="54" spans="9:9">
+      <c r="I54" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="55" spans="9:9">
+      <c r="I55" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="56" spans="9:9">
+      <c r="I56" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="57" spans="9:9">
+      <c r="I57" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="58" spans="9:9">
+      <c r="I58" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="59" spans="9:9">
+      <c r="I59" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="60" spans="9:9">
+      <c r="I60" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="61" spans="9:9">
+      <c r="I61" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="62" spans="9:9">
+      <c r="I62" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="63" spans="9:9">
+      <c r="I63" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="64" spans="9:9">
+      <c r="I64" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="65" spans="9:9">
+      <c r="I65" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="66" spans="9:9">
+      <c r="I66" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="67" spans="9:9">
+      <c r="I67" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="68" spans="9:9">
+      <c r="I68" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="69" spans="9:9">
+      <c r="I69" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="70" spans="9:9">
+      <c r="I70" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="71" spans="9:9">
+      <c r="I71" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="72" spans="9:9">
+      <c r="I72" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="73" spans="9:9">
+      <c r="I73" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="74" spans="9:9">
+      <c r="I74" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="75" spans="9:9">
+      <c r="I75" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="76" spans="9:9">
+      <c r="I76" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="77" spans="9:9">
+      <c r="I77" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="78" spans="9:9">
+      <c r="I78" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="79" spans="9:9">
+      <c r="I79" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="80" spans="9:9">
+      <c r="I80" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="81" spans="9:9">
+      <c r="I81" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="82" spans="9:9">
+      <c r="I82" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="83" spans="9:9">
+      <c r="I83" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="84" spans="9:9">
+      <c r="I84" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="85" spans="9:9">
+      <c r="I85" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="86" spans="9:9">
+      <c r="I86" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="87" spans="9:9">
+      <c r="I87" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="88" spans="9:9">
+      <c r="I88" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="89" spans="9:9">
+      <c r="I89" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="90" spans="9:9">
+      <c r="I90" t="s">
+        <v>1703</v>
       </c>
     </row>
   </sheetData>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3538C1-7E4B-4633-9A8E-494FC07C2B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3D2F9F-36B0-4CB0-8746-E8686747EA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="23280" windowHeight="12480" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suite Test" sheetId="1" r:id="rId1"/>
@@ -22,13 +22,16 @@
     <sheet name="promt" sheetId="4" r:id="rId7"/>
     <sheet name="plan test" sheetId="18" r:id="rId8"/>
     <sheet name="lista frontend" sheetId="13" r:id="rId9"/>
-    <sheet name="Prmot frontend" sheetId="14" r:id="rId10"/>
-    <sheet name="lista IA " sheetId="17" r:id="rId11"/>
-    <sheet name="prmot llm" sheetId="16" r:id="rId12"/>
+    <sheet name="Hoja1" sheetId="19" r:id="rId10"/>
+    <sheet name="Prmot frontend" sheetId="14" r:id="rId11"/>
+    <sheet name="lista IA " sheetId="17" r:id="rId12"/>
+    <sheet name="prmot llm" sheetId="16" r:id="rId13"/>
+    <sheet name="Hoja3" sheetId="20" r:id="rId14"/>
+    <sheet name="Hoja5" sheetId="21" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Hoja2!$A$1:$C$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'lista IA '!$A$1:$B$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'lista IA '!$A$1:$B$236</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suite Test'!$A$1:$J$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Unit Test'!$A$1:$I$404</definedName>
   </definedNames>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6093" uniqueCount="1835">
   <si>
     <t>Nº</t>
   </si>
@@ -12867,6 +12870,399 @@
   <si>
     <t xml:space="preserve">     Target: apps/web/src/tests/e2e/S3-12-a11y-tablet.spec.ts </t>
   </si>
+  <si>
+    <t> `@planner-agent` rules live in `context/agent_planner.md`.</t>
+  </si>
+  <si>
+    <t> `@planner-agent`</t>
+  </si>
+  <si>
+    <t>`@devops-agent`</t>
+  </si>
+  <si>
+    <t>`@product-agent`</t>
+  </si>
+  <si>
+    <t>`@product write-story [feature_idea]`</t>
+  </si>
+  <si>
+    <t>Translates a raw idea into a formal User Story with BDD (Behavior-Driven Development) "Given/When/Then" Acceptance Criteria.</t>
+  </si>
+  <si>
+    <t>`@product review-ux [component/flow]`</t>
+  </si>
+  <si>
+    <t>Evaluates a frontend UI flow or component design for friction, cognitive load, and alignment with the target personas.</t>
+  </si>
+  <si>
+    <t>@product uat [feature_name]</t>
+  </si>
+  <si>
+    <t>Performs a "Business Review" of a completed feature. You will act as a non-technical end-user trying to use the system and point out logical flaws or confusing UI text.</t>
+  </si>
+  <si>
+    <t>`@product groom-backlog`</t>
+  </si>
+  <si>
+    <t>Reviews the current pending features from the Phase 4 Roadmap and suggests prioritization based on Business Value vs. Risk.</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>Order |</t>
+  </si>
+  <si>
+    <t>Test ID                   |</t>
+  </si>
+  <si>
+    <t>----- |</t>
+  </si>
+  <si>
+    <t>------------------------- |</t>
+  </si>
+  <si>
+    <t>1     |</t>
+  </si>
+  <si>
+    <t>**TS-CT-WBS-API-001**     |</t>
+  </si>
+  <si>
+    <t>2     |</t>
+  </si>
+  <si>
+    <t>**TS-UD-WBS-001**         |</t>
+  </si>
+  <si>
+    <t>3     |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-TREE-001**   |</t>
+  </si>
+  <si>
+    <t>4     |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-CARD-001**   |</t>
+  </si>
+  <si>
+    <t>5     |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-DETAIL-001** |</t>
+  </si>
+  <si>
+    <t>6     |</t>
+  </si>
+  <si>
+    <t>**TS-INT-NAV-001**        |</t>
+  </si>
+  <si>
+    <t>7     |</t>
+  </si>
+  <si>
+    <t>**TS-CT-API-001**         |</t>
+  </si>
+  <si>
+    <t>8     |</t>
+  </si>
+  <si>
+    <t>**TS-E2E-J1-001**         |</t>
+  </si>
+  <si>
+    <t>9     |</t>
+  </si>
+  <si>
+    <t>**TS-E2E-J2-001**         |</t>
+  </si>
+  <si>
+    <t>12    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-FILTER-001** |</t>
+  </si>
+  <si>
+    <t>13    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-SEARCH-001** |</t>
+  </si>
+  <si>
+    <t>14    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-COLOR-001**  |</t>
+  </si>
+  <si>
+    <t>15    |</t>
+  </si>
+  <si>
+    <t>**TS-UA-WBS-CRUD-001**    |</t>
+  </si>
+  <si>
+    <t>16    |</t>
+  </si>
+  <si>
+    <t>**TS-UD-WBS-002**         |</t>
+  </si>
+  <si>
+    <t>17    |</t>
+  </si>
+  <si>
+    <t>**TS-UD-WBS-003**         |</t>
+  </si>
+  <si>
+    <t>18    |</t>
+  </si>
+  <si>
+    <t>**TS-MOB-WBS-001**        |</t>
+  </si>
+  <si>
+    <t>19    |</t>
+  </si>
+  <si>
+    <t>**TS-A11Y-WBS-001**       |</t>
+  </si>
+  <si>
+    <t>20    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-WBS-HOOK-001**   |</t>
+  </si>
+  <si>
+    <t>21    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-PROC-TABLE-001** |</t>
+  </si>
+  <si>
+    <t>22    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-PROC-CALC-001**  |</t>
+  </si>
+  <si>
+    <t>23    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-PROC-GANTT-001** |</t>
+  </si>
+  <si>
+    <t>24    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-PROC-HOOK-001**  |</t>
+  </si>
+  <si>
+    <t>25    |</t>
+  </si>
+  <si>
+    <t>**TS-UAD-PERM-HOOK-001**  |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Type        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Owner         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> File Location                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-------------------------------------- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ----------- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ------------- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ------------------------------------------------------------- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBS API Contract Tests                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contract    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @backend-tdd  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/modules/wbs/adapters/test_wbs_api_contract.py`         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBS Item Entity Domain Tests           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unit        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/modules/wbs/domain/test_wbs_item_entity.py`            </t>
+  </si>
+  <si>
+    <t>WBS Tree Component Contract Tests      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Component   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @frontend-tdd </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/wbs/__tests__/WBSTree.contract.test.tsx` </t>
+  </si>
+  <si>
+    <t>WBS Item Card Component Tests          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/wbs/__tests__/WBSItemCard.test.tsx`      </t>
+  </si>
+  <si>
+    <t>WBS Item Detail Component Tests        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/wbs/__tests__/WBSItemDetail.test.tsx`    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Module Navigation Contract Tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @qa-agent     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/tests/integration/navigation.contract.test.tsx`     </t>
+  </si>
+  <si>
+    <t>Global API Contract Tests              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/contract/test_api_contracts.py`                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">First-Time Project Setup Journey       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E2E         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/tests/e2e/journeys/journey-1-setup.spec.ts`         </t>
+  </si>
+  <si>
+    <t>Weekly Project Review Journey          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/tests/e2e/journeys/journey-2-review.spec.ts`        </t>
+  </si>
+  <si>
+    <t>WBS Filter by Status Tests        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hook      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/hooks/__tests__/useWbsFilter.test.ts`                         </t>
+  </si>
+  <si>
+    <t>WBS Search Tests                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/hooks/__tests__/useWbsSearch.test.ts`                         </t>
+  </si>
+  <si>
+    <t>WBS Alert Color Coding Tests      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/wbs/__tests__/WBSAlertBadge.test.tsx`              </t>
+  </si>
+  <si>
+    <t>WBS CRUD Use Cases Tests          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unit      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/modules/wbs/application/test_wbs_crud.py`                        </t>
+  </si>
+  <si>
+    <t>WBS Hierarchy &amp; Code Tests        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/modules/wbs/domain/test_wbs_hierarchy.py`                        </t>
+  </si>
+  <si>
+    <t>WBS Validation Rules Tests        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `tests/modules/wbs/domain/test_wbs_validation.py`                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBS Mobile Contract Tests         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mobile    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/tests/mobile/wbs-mobile.contract.test.tsx`                    </t>
+  </si>
+  <si>
+    <t>WBS Accessibility Contract Tests  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A11y      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/tests/accessibility/wbs-a11y.contract.test.tsx`               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">useWbs Hook Tests                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/hooks/__tests__/useWbs.test.ts`                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM Table Component Tests         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/procurement/__tests__/BOMTable.test.tsx`           </t>
+  </si>
+  <si>
+    <t>Lead Time Calculator Tests        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/procurement/__tests__/LeadTimeCalculator.test.tsx` </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procurement Gantt Component Tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/components/procurement/__tests__/ProcurementGantt.test.tsx`   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">useProcurement Hook Tests         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/hooks/__tests__/useProcurement.test.ts`                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">usePermissions Hook Tests         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `apps/web/hooks/__tests__/usePermissions.test.ts`                       </t>
+  </si>
 </sst>
 </file>
 
@@ -13125,7 +13521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -13294,15 +13690,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13611,16 +14008,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="19.149999999999999" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="19.2" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.28515625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="62.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.33203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="62.33203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="1" spans="1:13" ht="19.2" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13658,7 +14055,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="2" spans="1:13" ht="19.2" customHeight="1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13697,7 +14094,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="3" spans="1:13" ht="19.2" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -13736,7 +14133,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="4" spans="1:13" ht="19.2" customHeight="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -13775,7 +14172,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="5" spans="1:13" ht="19.2" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -13817,7 +14214,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="6" spans="1:13" ht="19.2" customHeight="1">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -13856,7 +14253,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="7" spans="1:13" ht="19.2" customHeight="1">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -13895,7 +14292,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="8" spans="1:13" ht="19.2" customHeight="1">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -13934,7 +14331,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="9" spans="1:13" ht="19.2" customHeight="1">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -13973,7 +14370,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="10" spans="1:13" ht="19.2" customHeight="1">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -14015,7 +14412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="11" spans="1:13" ht="19.2" customHeight="1">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -14057,7 +14454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="12" spans="1:13" ht="19.2" customHeight="1">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -14096,7 +14493,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="13" spans="1:13" ht="19.2" customHeight="1">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -14135,7 +14532,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="14" spans="1:13" ht="19.2" customHeight="1">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -14171,7 +14568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="15" spans="1:13" ht="19.2" customHeight="1">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -14207,7 +14604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="16" spans="1:13" ht="19.2" customHeight="1">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -14246,7 +14643,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="17" spans="1:13" ht="19.2" customHeight="1">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -14282,7 +14679,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="18" spans="1:13" ht="19.2" customHeight="1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -14315,7 +14712,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="19" spans="1:13" ht="19.2" customHeight="1">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -14348,7 +14745,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="20" spans="1:13" ht="19.2" customHeight="1">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -14381,7 +14778,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="21" spans="1:13" ht="19.2" customHeight="1">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -14414,7 +14811,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="22" spans="1:13" ht="19.2" customHeight="1">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -14447,7 +14844,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="23" spans="1:13" ht="19.2" customHeight="1">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -14486,7 +14883,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="24" spans="1:13" ht="19.2" customHeight="1">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -14522,7 +14919,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="25" spans="1:13" ht="19.2" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -14555,7 +14952,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="26" spans="1:13" ht="19.2" customHeight="1">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -14588,7 +14985,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="27" spans="1:13" ht="19.2" customHeight="1">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -14621,7 +15018,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="28" spans="1:13" ht="19.2" customHeight="1">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -14660,7 +15057,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="29" spans="1:13" ht="19.2" customHeight="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -14693,7 +15090,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="30" spans="1:13" ht="19.2" customHeight="1">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -14726,7 +15123,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="31" spans="1:13" ht="19.2" customHeight="1">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -14759,7 +15156,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="32" spans="1:13" ht="19.2" customHeight="1">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -14792,7 +15189,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="33" spans="1:13" ht="19.2" customHeight="1">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -14825,7 +15222,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="34" spans="1:13" ht="19.2" customHeight="1">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -14861,7 +15258,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="35" spans="1:13" ht="19.2" customHeight="1">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -14897,7 +15294,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="36" spans="1:13" ht="19.2" customHeight="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -14933,7 +15330,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="37" spans="1:13" ht="19.2" customHeight="1">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -14969,7 +15366,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="38" spans="1:13" ht="19.2" customHeight="1">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -15005,7 +15402,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="39" spans="1:13" ht="19.2" customHeight="1">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -15044,7 +15441,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="40" spans="1:13" ht="19.2" customHeight="1">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -15077,7 +15474,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="41" spans="1:13" ht="19.2" customHeight="1">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -15110,7 +15507,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="42" spans="1:13" ht="19.2" customHeight="1">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -15143,7 +15540,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="43" spans="1:13" ht="19.2" customHeight="1">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -15176,7 +15573,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="44" spans="1:13" ht="19.2" customHeight="1">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -15209,7 +15606,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="45" spans="1:13" ht="19.2" customHeight="1">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -15242,7 +15639,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="46" spans="1:13" ht="19.2" customHeight="1">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -15275,7 +15672,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="47" spans="1:13" ht="19.2" customHeight="1">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -15314,7 +15711,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="48" spans="1:13" ht="19.2" customHeight="1">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -15347,7 +15744,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="49" spans="1:13" ht="19.2" customHeight="1">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -15380,7 +15777,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="50" spans="1:13" ht="19.2" customHeight="1">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -15413,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="51" spans="1:13" ht="19.2" customHeight="1">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -15446,7 +15843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="52" spans="1:13" ht="19.2" customHeight="1">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -15479,7 +15876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="53" spans="1:13" ht="19.2" customHeight="1">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -15512,7 +15909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="54" spans="1:13" ht="19.2" customHeight="1">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -15545,7 +15942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="55" spans="1:13" ht="19.2" customHeight="1">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -15578,7 +15975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="56" spans="1:13" ht="19.2" customHeight="1">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -15611,7 +16008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="57" spans="1:13" ht="19.2" customHeight="1">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -15644,7 +16041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="58" spans="1:13" ht="19.2" customHeight="1">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -15677,7 +16074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="59" spans="1:13" ht="19.2" customHeight="1">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -15710,7 +16107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="60" spans="1:13" ht="19.2" customHeight="1">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -15743,7 +16140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="61" spans="1:13" ht="19.2" customHeight="1">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -15776,7 +16173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="62" spans="1:13" ht="19.2" customHeight="1">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -15809,7 +16206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="63" spans="1:13" ht="19.2" customHeight="1">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -15842,7 +16239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="64" spans="1:13" ht="19.2" customHeight="1">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -15875,7 +16272,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="65" spans="1:13" ht="19.2" customHeight="1">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -15908,7 +16305,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="66" spans="1:13" ht="19.2" customHeight="1">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -15941,7 +16338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="67" spans="1:13" ht="19.2" customHeight="1">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -15974,7 +16371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="68" spans="1:13" ht="19.2" customHeight="1">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -16007,7 +16404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="69" spans="1:13" ht="19.2" customHeight="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -16040,7 +16437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="70" spans="1:13" ht="19.2" customHeight="1">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -16073,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="71" spans="1:13" ht="19.2" customHeight="1">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -16106,7 +16503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="72" spans="1:13" ht="19.2" customHeight="1">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -16148,7 +16545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="73" spans="1:13" ht="19.2" customHeight="1">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -16187,7 +16584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="74" spans="1:13" ht="19.2" customHeight="1">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -16226,7 +16623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="75" spans="1:13" ht="19.2" customHeight="1">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -16262,7 +16659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="76" spans="1:13" ht="19.2" customHeight="1">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -16295,7 +16692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="77" spans="1:13" ht="19.2" customHeight="1">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -16334,7 +16731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="78" spans="1:13" ht="19.2" customHeight="1">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -16373,7 +16770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="79" spans="1:13" ht="19.2" customHeight="1">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -16412,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="80" spans="1:13" ht="19.2" customHeight="1">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -16448,7 +16845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="81" spans="1:13" ht="19.2" customHeight="1">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -16484,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="82" spans="1:13" ht="19.2" customHeight="1">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -16517,7 +16914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="83" spans="1:13" ht="19.2" customHeight="1">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -16559,7 +16956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="84" spans="1:13" ht="19.2" customHeight="1">
       <c r="A84" t="s">
         <v>102</v>
       </c>
@@ -16592,7 +16989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="85" spans="1:13" ht="19.2" customHeight="1">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -16628,7 +17025,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="86" spans="1:13" ht="19.2" customHeight="1">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -16667,7 +17064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="87" spans="1:13" ht="19.2" customHeight="1">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -16700,7 +17097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="88" spans="1:13" ht="19.2" customHeight="1">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -16733,7 +17130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="89" spans="1:13" ht="19.2" customHeight="1">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -16766,7 +17163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="90" spans="1:13" ht="19.2" customHeight="1">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -16805,7 +17202,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="91" spans="1:13" ht="19.2" customHeight="1">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -16841,7 +17238,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="92" spans="1:13" ht="19.2" customHeight="1">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -16877,7 +17274,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="93" spans="1:13" ht="19.2" customHeight="1">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -16910,7 +17307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="94" spans="1:13" ht="19.2" customHeight="1">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -16946,7 +17343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="95" spans="1:13" ht="19.2" customHeight="1">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -16985,7 +17382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="96" spans="1:13" ht="19.2" customHeight="1">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -17018,7 +17415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="97" spans="1:13" ht="19.2" customHeight="1">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -17057,7 +17454,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="98" spans="1:13" ht="19.2" customHeight="1">
       <c r="A98" t="s">
         <v>86</v>
       </c>
@@ -17093,7 +17490,7 @@
         <v>CODEX</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="99" spans="1:13" ht="19.2" customHeight="1">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -17129,7 +17526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="100" spans="1:13" ht="19.2" customHeight="1">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -17165,7 +17562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="101" spans="1:13" ht="19.2" customHeight="1">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -17198,7 +17595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="102" spans="1:13" ht="19.2" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -17234,7 +17631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="103" spans="1:13" ht="19.2" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -17276,7 +17673,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="104" spans="1:13" ht="19.2" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -17312,7 +17709,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="105" spans="1:13" ht="19.2" customHeight="1">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -17348,7 +17745,7 @@
         <v>codex</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="106" spans="1:13" ht="19.2" customHeight="1">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -17384,7 +17781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="107" spans="1:13" ht="19.2" customHeight="1">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -17423,7 +17820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="108" spans="1:13" ht="19.2" customHeight="1">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -17459,7 +17856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="109" spans="1:13" ht="19.2" customHeight="1">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -17498,7 +17895,7 @@
         <v>claude</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="110" spans="1:13" ht="19.2" customHeight="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -17537,7 +17934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="111" spans="1:13" ht="19.2" customHeight="1">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -17576,7 +17973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="112" spans="1:13" ht="19.2" customHeight="1">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -17609,7 +18006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="113" spans="1:13" ht="19.2" customHeight="1">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -17642,7 +18039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="19.149999999999999" customHeight="1">
+    <row r="114" spans="1:13" ht="19.2" customHeight="1">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -17689,19 +18086,28 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A4CA26-8AA6-4A16-BD76-23D76994F903}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16843C28-0155-42BB-A62E-C4CE7C932E1A}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="146.42578125" customWidth="1"/>
+    <col min="1" max="1" width="146.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5">
+    <row r="1" spans="1:1" ht="409.6">
       <c r="A1" s="2" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="90">
+    <row r="3" spans="1:1" ht="86.4">
       <c r="A3" s="2" t="s">
         <v>1340</v>
       </c>
@@ -17711,18 +18117,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1590E3-1708-4563-889F-3AD6ACE1A716}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F264"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" customWidth="1"/>
+    <col min="1" max="1" width="77.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="47.44140625" customWidth="1"/>
     <col min="5" max="5" width="79" customWidth="1"/>
-    <col min="6" max="6" width="67.85546875" customWidth="1"/>
+    <col min="6" max="6" width="67.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -17754,82 +18160,82 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" hidden="1">
+    <row r="3" spans="1:5" ht="19.2" hidden="1">
       <c r="B3" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="86.25" hidden="1">
+    <row r="4" spans="1:5" ht="96" hidden="1">
       <c r="B4" s="43" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="34.5" hidden="1">
+    <row r="5" spans="1:5" ht="38.4" hidden="1">
       <c r="B5" s="43" t="s">
         <v>1346</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="51.75" hidden="1">
+    <row r="6" spans="1:5" ht="57.6" hidden="1">
       <c r="B6" s="43" t="s">
         <v>1347</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.25" hidden="1">
+    <row r="7" spans="1:5" ht="19.2" hidden="1">
       <c r="B7" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="34.5" hidden="1">
+    <row r="8" spans="1:5" ht="38.4" hidden="1">
       <c r="B8" s="43" t="s">
         <v>1349</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="34.5" hidden="1">
+    <row r="9" spans="1:5" ht="38.4" hidden="1">
       <c r="B9" s="43" t="s">
         <v>1350</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="34.5" hidden="1">
+    <row r="10" spans="1:5" ht="38.4" hidden="1">
       <c r="B10" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51.75" hidden="1">
+    <row r="11" spans="1:5" ht="57.6" hidden="1">
       <c r="B11" s="43" t="s">
         <v>1352</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="51.75" hidden="1">
+    <row r="12" spans="1:5" ht="57.6" hidden="1">
       <c r="B12" s="43" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" hidden="1">
+    <row r="13" spans="1:5" ht="19.2" hidden="1">
       <c r="B13" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="51.75" hidden="1">
+    <row r="14" spans="1:5" ht="57.6" hidden="1">
       <c r="B14" s="43" t="s">
         <v>1355</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="34.5" hidden="1">
+    <row r="15" spans="1:5" ht="38.4" hidden="1">
       <c r="B15" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="69" hidden="1">
+    <row r="16" spans="1:5" ht="57.6" hidden="1">
       <c r="B16" s="43" t="s">
         <v>1357</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="34.5" hidden="1">
+    <row r="17" spans="1:6" ht="38.4" hidden="1">
       <c r="B17" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="69" hidden="1">
+    <row r="18" spans="1:6" ht="57.6" hidden="1">
       <c r="B18" s="43" t="s">
         <v>1359</v>
       </c>
@@ -17855,82 +18261,82 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.25" hidden="1">
+    <row r="20" spans="1:6" ht="19.2" hidden="1">
       <c r="B20" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="51.75" hidden="1">
+    <row r="21" spans="1:6" ht="57.6" hidden="1">
       <c r="B21" s="43" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="69" hidden="1">
+    <row r="22" spans="1:6" ht="76.8" hidden="1">
       <c r="B22" s="43" t="s">
         <v>1362</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="69" hidden="1">
+    <row r="23" spans="1:6" ht="57.6" hidden="1">
       <c r="B23" s="43" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17.25" hidden="1">
+    <row r="24" spans="1:6" ht="19.2" hidden="1">
       <c r="B24" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17.25" hidden="1">
+    <row r="25" spans="1:6" ht="19.2" hidden="1">
       <c r="B25" s="43" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="34.5" hidden="1">
+    <row r="26" spans="1:6" ht="38.4" hidden="1">
       <c r="B26" s="43" t="s">
         <v>1365</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="34.5" hidden="1">
+    <row r="27" spans="1:6" ht="38.4" hidden="1">
       <c r="B27" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="34.5" hidden="1">
+    <row r="28" spans="1:6" ht="38.4" hidden="1">
       <c r="B28" s="43" t="s">
         <v>1366</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="51.75" hidden="1">
+    <row r="29" spans="1:6" ht="38.4" hidden="1">
       <c r="B29" s="43" t="s">
         <v>1367</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17.25" hidden="1">
+    <row r="30" spans="1:6" ht="19.2" hidden="1">
       <c r="B30" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="51.75" hidden="1">
+    <row r="31" spans="1:6" ht="57.6" hidden="1">
       <c r="B31" s="43" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34.5" hidden="1">
+    <row r="32" spans="1:6" ht="38.4" hidden="1">
       <c r="B32" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="51.75" hidden="1">
+    <row r="33" spans="1:5" ht="57.6" hidden="1">
       <c r="B33" s="43" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="34.5" hidden="1">
+    <row r="34" spans="1:5" ht="38.4" hidden="1">
       <c r="B34" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="51.75" hidden="1">
+    <row r="35" spans="1:5" ht="57.6" hidden="1">
       <c r="B35" s="43" t="s">
         <v>1370</v>
       </c>
@@ -17939,7 +18345,7 @@
       <c r="A36" s="44" t="s">
         <v>1371</v>
       </c>
-      <c r="B36" s="66" t="s">
+      <c r="B36" s="65" t="s">
         <v>1635</v>
       </c>
       <c r="C36" t="s">
@@ -17953,82 +18359,82 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17.25" hidden="1">
+    <row r="37" spans="1:5" ht="19.2" hidden="1">
       <c r="B37" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="51.75" hidden="1">
+    <row r="38" spans="1:5" ht="57.6" hidden="1">
       <c r="B38" s="43" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="51.75" hidden="1">
+    <row r="39" spans="1:5" ht="57.6" hidden="1">
       <c r="B39" s="43" t="s">
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="69" hidden="1">
+    <row r="40" spans="1:5" ht="76.8" hidden="1">
       <c r="B40" s="43" t="s">
         <v>1374</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.25" hidden="1">
+    <row r="41" spans="1:5" ht="19.2" hidden="1">
       <c r="B41" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="51.75" hidden="1">
+    <row r="42" spans="1:5" ht="38.4" hidden="1">
       <c r="B42" s="43" t="s">
         <v>1375</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="34.5" hidden="1">
+    <row r="43" spans="1:5" ht="38.4" hidden="1">
       <c r="B43" s="43" t="s">
         <v>1376</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="34.5" hidden="1">
+    <row r="44" spans="1:5" ht="38.4" hidden="1">
       <c r="B44" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="51.75" hidden="1">
+    <row r="45" spans="1:5" ht="57.6" hidden="1">
       <c r="B45" s="43" t="s">
         <v>1377</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="34.5" hidden="1">
+    <row r="46" spans="1:5" ht="38.4" hidden="1">
       <c r="B46" s="43" t="s">
         <v>1378</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17.25" hidden="1">
+    <row r="47" spans="1:5" ht="19.2" hidden="1">
       <c r="B47" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="34.5" hidden="1">
+    <row r="48" spans="1:5" ht="38.4" hidden="1">
       <c r="B48" s="43" t="s">
         <v>1379</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="34.5" hidden="1">
+    <row r="49" spans="1:5" ht="38.4" hidden="1">
       <c r="B49" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="51.75" hidden="1">
+    <row r="50" spans="1:5" ht="57.6" hidden="1">
       <c r="B50" s="43" t="s">
         <v>1380</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="34.5" hidden="1">
+    <row r="51" spans="1:5" ht="38.4" hidden="1">
       <c r="B51" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="51.75" hidden="1">
+    <row r="52" spans="1:5" ht="57.6" hidden="1">
       <c r="B52" s="43" t="s">
         <v>1381</v>
       </c>
@@ -18051,82 +18457,82 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="17.25" hidden="1">
+    <row r="54" spans="1:5" ht="19.2" hidden="1">
       <c r="B54" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="51.75" hidden="1">
+    <row r="55" spans="1:5" ht="38.4" hidden="1">
       <c r="B55" s="43" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="51.75" hidden="1">
+    <row r="56" spans="1:5" ht="57.6" hidden="1">
       <c r="B56" s="43" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="51.75" hidden="1">
+    <row r="57" spans="1:5" ht="57.6" hidden="1">
       <c r="B57" s="43" t="s">
         <v>1385</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="17.25" hidden="1">
+    <row r="58" spans="1:5" ht="19.2" hidden="1">
       <c r="B58" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="34.5" hidden="1">
+    <row r="59" spans="1:5" ht="38.4" hidden="1">
       <c r="B59" s="43" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="34.5" hidden="1">
+    <row r="60" spans="1:5" ht="38.4" hidden="1">
       <c r="B60" s="43" t="s">
         <v>1387</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="34.5" hidden="1">
+    <row r="61" spans="1:5" ht="38.4" hidden="1">
       <c r="B61" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="51.75" hidden="1">
+    <row r="62" spans="1:5" ht="57.6" hidden="1">
       <c r="B62" s="43" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="34.5" hidden="1">
+    <row r="63" spans="1:5" ht="19.2" hidden="1">
       <c r="B63" s="43" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="17.25" hidden="1">
+    <row r="64" spans="1:5" ht="19.2" hidden="1">
       <c r="B64" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="34.5" hidden="1">
+    <row r="65" spans="1:5" ht="38.4" hidden="1">
       <c r="B65" s="43" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="34.5" hidden="1">
+    <row r="66" spans="1:5" ht="38.4" hidden="1">
       <c r="B66" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="34.5" hidden="1">
+    <row r="67" spans="1:5" ht="38.4" hidden="1">
       <c r="B67" s="43" t="s">
         <v>1391</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="34.5" hidden="1">
+    <row r="68" spans="1:5" ht="38.4" hidden="1">
       <c r="B68" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="69" hidden="1">
+    <row r="69" spans="1:5" ht="57.6" hidden="1">
       <c r="B69" s="43" t="s">
         <v>1392</v>
       </c>
@@ -18149,82 +18555,82 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="17.25" hidden="1">
+    <row r="71" spans="1:5" ht="19.2" hidden="1">
       <c r="B71" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="69" hidden="1">
+    <row r="72" spans="1:5" ht="76.8" hidden="1">
       <c r="B72" s="43" t="s">
         <v>1394</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="51.75" hidden="1">
+    <row r="73" spans="1:5" ht="57.6" hidden="1">
       <c r="B73" s="43" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="51.75" hidden="1">
+    <row r="74" spans="1:5" ht="57.6" hidden="1">
       <c r="B74" s="43" t="s">
         <v>1396</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="17.25" hidden="1">
+    <row r="75" spans="1:5" ht="19.2" hidden="1">
       <c r="B75" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="34.5" hidden="1">
+    <row r="76" spans="1:5" ht="38.4" hidden="1">
       <c r="B76" s="43" t="s">
         <v>1397</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="34.5" hidden="1">
+    <row r="77" spans="1:5" ht="38.4" hidden="1">
       <c r="B77" s="43" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="34.5" hidden="1">
+    <row r="78" spans="1:5" ht="38.4" hidden="1">
       <c r="B78" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="51.75" hidden="1">
+    <row r="79" spans="1:5" ht="57.6" hidden="1">
       <c r="B79" s="43" t="s">
         <v>1399</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="34.5" hidden="1">
+    <row r="80" spans="1:5" ht="38.4" hidden="1">
       <c r="B80" s="43" t="s">
         <v>1400</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="17.25" hidden="1">
+    <row r="81" spans="1:5" ht="19.2" hidden="1">
       <c r="B81" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="51.75" hidden="1">
+    <row r="82" spans="1:5" ht="38.4" hidden="1">
       <c r="B82" s="43" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="34.5" hidden="1">
+    <row r="83" spans="1:5" ht="38.4" hidden="1">
       <c r="B83" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="51.75" hidden="1">
+    <row r="84" spans="1:5" ht="57.6" hidden="1">
       <c r="B84" s="43" t="s">
         <v>1402</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="34.5" hidden="1">
+    <row r="85" spans="1:5" ht="38.4" hidden="1">
       <c r="B85" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="69" hidden="1">
+    <row r="86" spans="1:5" ht="76.8" hidden="1">
       <c r="B86" s="43" t="s">
         <v>1403</v>
       </c>
@@ -18247,77 +18653,77 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="17.25" hidden="1">
+    <row r="88" spans="1:5" ht="19.2" hidden="1">
       <c r="B88" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="69" hidden="1">
+    <row r="89" spans="1:5" ht="76.8" hidden="1">
       <c r="B89" s="43" t="s">
         <v>1405</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="51.75" hidden="1">
+    <row r="90" spans="1:5" ht="38.4" hidden="1">
       <c r="B90" s="43" t="s">
         <v>1406</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="34.5" hidden="1">
+    <row r="91" spans="1:5" ht="38.4" hidden="1">
       <c r="B91" s="43" t="s">
         <v>1407</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="17.25" hidden="1">
+    <row r="92" spans="1:5" ht="19.2" hidden="1">
       <c r="B92" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="34.5" hidden="1">
+    <row r="93" spans="1:5" ht="38.4" hidden="1">
       <c r="B93" s="43" t="s">
         <v>1408</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="17.25" hidden="1">
+    <row r="94" spans="1:5" ht="19.2" hidden="1">
       <c r="B94" s="43" t="s">
         <v>1409</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="34.5" hidden="1">
+    <row r="95" spans="1:5" ht="38.4" hidden="1">
       <c r="B95" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="51.75" hidden="1">
+    <row r="96" spans="1:5" ht="57.6" hidden="1">
       <c r="B96" s="43" t="s">
         <v>1410</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="17.25" hidden="1">
+    <row r="97" spans="1:5" ht="19.2" hidden="1">
       <c r="B97" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="34.5" hidden="1">
+    <row r="98" spans="1:5" ht="38.4" hidden="1">
       <c r="B98" s="43" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="34.5" hidden="1">
+    <row r="99" spans="1:5" ht="38.4" hidden="1">
       <c r="B99" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="34.5" hidden="1">
+    <row r="100" spans="1:5" ht="38.4" hidden="1">
       <c r="B100" s="43" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="34.5" hidden="1">
+    <row r="101" spans="1:5" ht="38.4" hidden="1">
       <c r="B101" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="34.5" hidden="1">
+    <row r="102" spans="1:5" ht="38.4" hidden="1">
       <c r="B102" s="43" t="s">
         <v>1413</v>
       </c>
@@ -18340,77 +18746,77 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17.25" hidden="1">
+    <row r="104" spans="1:5" ht="19.2" hidden="1">
       <c r="B104" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="51.75" hidden="1">
+    <row r="105" spans="1:5" ht="57.6" hidden="1">
       <c r="B105" s="43" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="34.5" hidden="1">
+    <row r="106" spans="1:5" ht="38.4" hidden="1">
       <c r="B106" s="43" t="s">
         <v>1416</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="51.75" hidden="1">
+    <row r="107" spans="1:5" ht="57.6" hidden="1">
       <c r="B107" s="43" t="s">
         <v>1417</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17.25" hidden="1">
+    <row r="108" spans="1:5" ht="19.2" hidden="1">
       <c r="B108" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="34.5" hidden="1">
+    <row r="109" spans="1:5" ht="38.4" hidden="1">
       <c r="B109" s="43" t="s">
         <v>1418</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="34.5" hidden="1">
+    <row r="110" spans="1:5" ht="19.2" hidden="1">
       <c r="B110" s="43" t="s">
         <v>1419</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="34.5" hidden="1">
+    <row r="111" spans="1:5" ht="38.4" hidden="1">
       <c r="B111" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="51.75" hidden="1">
+    <row r="112" spans="1:5" ht="57.6" hidden="1">
       <c r="B112" s="43" t="s">
         <v>1420</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17.25" hidden="1">
+    <row r="113" spans="1:5" ht="19.2" hidden="1">
       <c r="B113" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="34.5" hidden="1">
+    <row r="114" spans="1:5" ht="38.4" hidden="1">
       <c r="B114" s="43" t="s">
         <v>1421</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="34.5" hidden="1">
+    <row r="115" spans="1:5" ht="38.4" hidden="1">
       <c r="B115" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="51.75" hidden="1">
+    <row r="116" spans="1:5" ht="57.6" hidden="1">
       <c r="B116" s="43" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="34.5" hidden="1">
+    <row r="117" spans="1:5" ht="38.4" hidden="1">
       <c r="B117" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="51.75" hidden="1">
+    <row r="118" spans="1:5" ht="57.6" hidden="1">
       <c r="B118" s="43" t="s">
         <v>1423</v>
       </c>
@@ -18433,82 +18839,82 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17.25" hidden="1">
+    <row r="120" spans="1:5" ht="19.2" hidden="1">
       <c r="B120" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="51.75" hidden="1">
+    <row r="121" spans="1:5" ht="57.6" hidden="1">
       <c r="B121" s="43" t="s">
         <v>1425</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="51.75" hidden="1">
+    <row r="122" spans="1:5" ht="57.6" hidden="1">
       <c r="B122" s="43" t="s">
         <v>1426</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="34.5" hidden="1">
+    <row r="123" spans="1:5" ht="38.4" hidden="1">
       <c r="B123" s="43" t="s">
         <v>1427</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17.25" hidden="1">
+    <row r="124" spans="1:5" ht="19.2" hidden="1">
       <c r="B124" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="34.5" hidden="1">
+    <row r="125" spans="1:5" ht="38.4" hidden="1">
       <c r="B125" s="43" t="s">
         <v>1428</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="34.5" hidden="1">
+    <row r="126" spans="1:5" ht="38.4" hidden="1">
       <c r="B126" s="43" t="s">
         <v>1429</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="34.5" hidden="1">
+    <row r="127" spans="1:5" ht="38.4" hidden="1">
       <c r="B127" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="34.5" hidden="1">
+    <row r="128" spans="1:5" ht="38.4" hidden="1">
       <c r="B128" s="43" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="51.75" hidden="1">
+    <row r="129" spans="1:5" ht="57.6" hidden="1">
       <c r="B129" s="43" t="s">
         <v>1431</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17.25" hidden="1">
+    <row r="130" spans="1:5" ht="19.2" hidden="1">
       <c r="B130" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="34.5" hidden="1">
+    <row r="131" spans="1:5" ht="38.4" hidden="1">
       <c r="B131" s="43" t="s">
         <v>1432</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="34.5" hidden="1">
+    <row r="132" spans="1:5" ht="38.4" hidden="1">
       <c r="B132" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="51.75" hidden="1">
+    <row r="133" spans="1:5" ht="57.6" hidden="1">
       <c r="B133" s="43" t="s">
         <v>1433</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="34.5" hidden="1">
+    <row r="134" spans="1:5" ht="38.4" hidden="1">
       <c r="B134" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="69" hidden="1">
+    <row r="135" spans="1:5" ht="76.8" hidden="1">
       <c r="B135" s="43" t="s">
         <v>1434</v>
       </c>
@@ -18531,77 +18937,77 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17.25" hidden="1">
+    <row r="137" spans="1:5" ht="19.2" hidden="1">
       <c r="B137" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="51.75" hidden="1">
+    <row r="138" spans="1:5" ht="57.6" hidden="1">
       <c r="B138" s="43" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="51.75" hidden="1">
+    <row r="139" spans="1:5" ht="57.6" hidden="1">
       <c r="B139" s="43" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="51.75" hidden="1">
+    <row r="140" spans="1:5" ht="57.6" hidden="1">
       <c r="B140" s="43" t="s">
         <v>1438</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17.25" hidden="1">
+    <row r="141" spans="1:5" ht="19.2" hidden="1">
       <c r="B141" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="51.75" hidden="1">
+    <row r="142" spans="1:5" ht="38.4" hidden="1">
       <c r="B142" s="43" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="34.5" hidden="1">
+    <row r="143" spans="1:5" ht="38.4" hidden="1">
       <c r="B143" s="43" t="s">
         <v>1440</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="34.5" hidden="1">
+    <row r="144" spans="1:5" ht="38.4" hidden="1">
       <c r="B144" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="69" hidden="1">
+    <row r="145" spans="1:5" ht="76.8" hidden="1">
       <c r="B145" s="43" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17.25" hidden="1">
+    <row r="146" spans="1:5" ht="19.2" hidden="1">
       <c r="B146" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="51.75" hidden="1">
+    <row r="147" spans="1:5" ht="57.6" hidden="1">
       <c r="B147" s="43" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="34.5" hidden="1">
+    <row r="148" spans="1:5" ht="38.4" hidden="1">
       <c r="B148" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="51.75" hidden="1">
+    <row r="149" spans="1:5" ht="57.6" hidden="1">
       <c r="B149" s="43" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="34.5" hidden="1">
+    <row r="150" spans="1:5" ht="38.4" hidden="1">
       <c r="B150" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="34.5" hidden="1">
+    <row r="151" spans="1:5" ht="38.4" hidden="1">
       <c r="B151" s="43" t="s">
         <v>1444</v>
       </c>
@@ -18624,82 +19030,82 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17.25" hidden="1">
+    <row r="153" spans="1:5" ht="19.2" hidden="1">
       <c r="B153" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="51.75" hidden="1">
+    <row r="154" spans="1:5" ht="57.6" hidden="1">
       <c r="B154" s="43" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="51.75" hidden="1">
+    <row r="155" spans="1:5" ht="57.6" hidden="1">
       <c r="B155" s="43" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="51.75" hidden="1">
+    <row r="156" spans="1:5" ht="57.6" hidden="1">
       <c r="B156" s="43" t="s">
         <v>1448</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17.25" hidden="1">
+    <row r="157" spans="1:5" ht="19.2" hidden="1">
       <c r="B157" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="34.5" hidden="1">
+    <row r="158" spans="1:5" ht="38.4" hidden="1">
       <c r="B158" s="43" t="s">
         <v>1449</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="34.5" hidden="1">
+    <row r="159" spans="1:5" ht="38.4" hidden="1">
       <c r="B159" s="43" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="34.5" hidden="1">
+    <row r="160" spans="1:5" ht="38.4" hidden="1">
       <c r="B160" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="34.5" hidden="1">
+    <row r="161" spans="1:5" ht="38.4" hidden="1">
       <c r="B161" s="43" t="s">
         <v>1451</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="34.5" hidden="1">
+    <row r="162" spans="1:5" ht="38.4" hidden="1">
       <c r="B162" s="43" t="s">
         <v>1452</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17.25" hidden="1">
+    <row r="163" spans="1:5" ht="19.2" hidden="1">
       <c r="B163" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="51.75" hidden="1">
+    <row r="164" spans="1:5" ht="57.6" hidden="1">
       <c r="B164" s="43" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="34.5" hidden="1">
+    <row r="165" spans="1:5" ht="38.4" hidden="1">
       <c r="B165" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="34.5" hidden="1">
+    <row r="166" spans="1:5" ht="38.4" hidden="1">
       <c r="B166" s="43" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="34.5" hidden="1">
+    <row r="167" spans="1:5" ht="38.4" hidden="1">
       <c r="B167" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="51.75" hidden="1">
+    <row r="168" spans="1:5" ht="57.6" hidden="1">
       <c r="B168" s="43" t="s">
         <v>1455</v>
       </c>
@@ -18722,77 +19128,77 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17.25" hidden="1">
+    <row r="170" spans="1:5" ht="19.2" hidden="1">
       <c r="B170" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="34.5" hidden="1">
+    <row r="171" spans="1:5" ht="38.4" hidden="1">
       <c r="B171" s="43" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="51.75" hidden="1">
+    <row r="172" spans="1:5" ht="57.6" hidden="1">
       <c r="B172" s="43" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="34.5" hidden="1">
+    <row r="173" spans="1:5" ht="38.4" hidden="1">
       <c r="B173" s="43" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17.25" hidden="1">
+    <row r="174" spans="1:5" ht="19.2" hidden="1">
       <c r="B174" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="34.5" hidden="1">
+    <row r="175" spans="1:5" ht="38.4" hidden="1">
       <c r="B175" s="43" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="34.5" hidden="1">
+    <row r="176" spans="1:5" ht="38.4" hidden="1">
       <c r="B176" s="43" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="34.5" hidden="1">
+    <row r="177" spans="1:5" ht="38.4" hidden="1">
       <c r="B177" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="51.75" hidden="1">
+    <row r="178" spans="1:5" ht="57.6" hidden="1">
       <c r="B178" s="43" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17.25" hidden="1">
+    <row r="179" spans="1:5" ht="19.2" hidden="1">
       <c r="B179" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="34.5" hidden="1">
+    <row r="180" spans="1:5" ht="38.4" hidden="1">
       <c r="B180" s="43" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="34.5" hidden="1">
+    <row r="181" spans="1:5" ht="38.4" hidden="1">
       <c r="B181" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="51.75" hidden="1">
+    <row r="182" spans="1:5" ht="38.4" hidden="1">
       <c r="B182" s="43" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="34.5" hidden="1">
+    <row r="183" spans="1:5" ht="38.4" hidden="1">
       <c r="B183" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="34.5" hidden="1">
+    <row r="184" spans="1:5" ht="38.4" hidden="1">
       <c r="B184" s="43" t="s">
         <v>1465</v>
       </c>
@@ -18815,77 +19221,77 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17.25" hidden="1">
+    <row r="186" spans="1:5" ht="19.2" hidden="1">
       <c r="B186" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="34.5" hidden="1">
+    <row r="187" spans="1:5" ht="38.4" hidden="1">
       <c r="B187" s="43" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="51.75" hidden="1">
+    <row r="188" spans="1:5" ht="57.6" hidden="1">
       <c r="B188" s="43" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="51.75" hidden="1">
+    <row r="189" spans="1:5" ht="57.6" hidden="1">
       <c r="B189" s="43" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17.25" hidden="1">
+    <row r="190" spans="1:5" ht="19.2" hidden="1">
       <c r="B190" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="34.5" hidden="1">
+    <row r="191" spans="1:5" ht="38.4" hidden="1">
       <c r="B191" s="43" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="34.5" hidden="1">
+    <row r="192" spans="1:5" ht="38.4" hidden="1">
       <c r="B192" s="43" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="34.5" hidden="1">
+    <row r="193" spans="1:5" ht="38.4" hidden="1">
       <c r="B193" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="69" hidden="1">
+    <row r="194" spans="1:5" ht="76.8" hidden="1">
       <c r="B194" s="43" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17.25" hidden="1">
+    <row r="195" spans="1:5" ht="19.2" hidden="1">
       <c r="B195" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="34.5" hidden="1">
+    <row r="196" spans="1:5" ht="38.4" hidden="1">
       <c r="B196" s="43" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="34.5" hidden="1">
+    <row r="197" spans="1:5" ht="38.4" hidden="1">
       <c r="B197" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="51.75" hidden="1">
+    <row r="198" spans="1:5" ht="57.6" hidden="1">
       <c r="B198" s="43" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="34.5" hidden="1">
+    <row r="199" spans="1:5" ht="38.4" hidden="1">
       <c r="B199" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="51.75" hidden="1">
+    <row r="200" spans="1:5" ht="57.6" hidden="1">
       <c r="B200" s="43" t="s">
         <v>1475</v>
       </c>
@@ -18908,77 +19314,77 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17.25" hidden="1">
+    <row r="202" spans="1:5" ht="19.2" hidden="1">
       <c r="B202" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="51.75" hidden="1">
+    <row r="203" spans="1:5" ht="57.6" hidden="1">
       <c r="B203" s="43" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="51.75" hidden="1">
+    <row r="204" spans="1:5" ht="57.6" hidden="1">
       <c r="B204" s="43" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="51.75" hidden="1">
+    <row r="205" spans="1:5" ht="57.6" hidden="1">
       <c r="B205" s="43" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17.25" hidden="1">
+    <row r="206" spans="1:5" ht="19.2" hidden="1">
       <c r="B206" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="34.5" hidden="1">
+    <row r="207" spans="1:5" ht="38.4" hidden="1">
       <c r="B207" s="43" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="51.75" hidden="1">
+    <row r="208" spans="1:5" ht="57.6" hidden="1">
       <c r="B208" s="43" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="34.5" hidden="1">
+    <row r="209" spans="1:5" ht="38.4" hidden="1">
       <c r="B209" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="51.75" hidden="1">
+    <row r="210" spans="1:5" ht="57.6" hidden="1">
       <c r="B210" s="43" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17.25" hidden="1">
+    <row r="211" spans="1:5" ht="19.2" hidden="1">
       <c r="B211" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="34.5" hidden="1">
+    <row r="212" spans="1:5" ht="38.4" hidden="1">
       <c r="B212" s="43" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="34.5" hidden="1">
+    <row r="213" spans="1:5" ht="38.4" hidden="1">
       <c r="B213" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="51.75" hidden="1">
+    <row r="214" spans="1:5" ht="57.6" hidden="1">
       <c r="B214" s="43" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="34.5" hidden="1">
+    <row r="215" spans="1:5" ht="38.4" hidden="1">
       <c r="B215" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="51.75" hidden="1">
+    <row r="216" spans="1:5" ht="57.6" hidden="1">
       <c r="B216" s="43" t="s">
         <v>1485</v>
       </c>
@@ -19001,92 +19407,92 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17.25" hidden="1">
+    <row r="218" spans="1:5" ht="19.2" hidden="1">
       <c r="B218" s="42" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="51.75" hidden="1">
+    <row r="219" spans="1:5" ht="57.6" hidden="1">
       <c r="B219" s="43" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="51.75" hidden="1">
+    <row r="220" spans="1:5" ht="57.6" hidden="1">
       <c r="B220" s="43" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="34.5" hidden="1">
+    <row r="221" spans="1:5" ht="38.4" hidden="1">
       <c r="B221" s="43" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="86.25" hidden="1">
+    <row r="222" spans="1:5" ht="76.8" hidden="1">
       <c r="B222" s="43" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="51.75" hidden="1">
+    <row r="223" spans="1:5" ht="57.6" hidden="1">
       <c r="B223" s="43" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17.25" hidden="1">
+    <row r="224" spans="1:5" ht="19.2" hidden="1">
       <c r="B224" s="42" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="225" spans="2:2" ht="34.5" hidden="1">
+    <row r="225" spans="2:2" ht="38.4" hidden="1">
       <c r="B225" s="43" t="s">
         <v>1492</v>
       </c>
     </row>
-    <row r="226" spans="2:2" ht="34.5" hidden="1">
+    <row r="226" spans="2:2" ht="38.4" hidden="1">
       <c r="B226" s="43" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="227" spans="2:2" ht="34.5" hidden="1">
+    <row r="227" spans="2:2" ht="38.4" hidden="1">
       <c r="B227" s="42" t="s">
         <v>1351</v>
       </c>
     </row>
-    <row r="228" spans="2:2" ht="51.75" hidden="1">
+    <row r="228" spans="2:2" ht="57.6" hidden="1">
       <c r="B228" s="43" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="229" spans="2:2" ht="34.5" hidden="1">
+    <row r="229" spans="2:2" ht="38.4" hidden="1">
       <c r="B229" s="43" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="230" spans="2:2" ht="17.25" hidden="1">
+    <row r="230" spans="2:2" ht="19.2" hidden="1">
       <c r="B230" s="42" t="s">
         <v>1354</v>
       </c>
     </row>
-    <row r="231" spans="2:2" ht="34.5" hidden="1">
+    <row r="231" spans="2:2" ht="38.4" hidden="1">
       <c r="B231" s="43" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="232" spans="2:2" ht="34.5" hidden="1">
+    <row r="232" spans="2:2" ht="38.4" hidden="1">
       <c r="B232" s="42" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="233" spans="2:2" ht="51.75" hidden="1">
+    <row r="233" spans="2:2" ht="57.6" hidden="1">
       <c r="B233" s="43" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="234" spans="2:2" ht="34.5" hidden="1">
+    <row r="234" spans="2:2" ht="38.4" hidden="1">
       <c r="B234" s="42" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="235" spans="2:2" ht="51.75" hidden="1">
+    <row r="235" spans="2:2" ht="38.4" hidden="1">
       <c r="B235" s="43" t="s">
         <v>1498</v>
       </c>
@@ -19169,22 +19575,679 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725EF9E2-7A77-45FF-B8A4-13516A0F9DA0}">
   <dimension ref="A4:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="155.85546875" customWidth="1"/>
+    <col min="1" max="1" width="155.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:1" ht="409.5">
+    <row r="4" spans="1:1" ht="409.6">
       <c r="A4" s="14" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="409.5">
+    <row r="7" spans="1:1" ht="409.6">
       <c r="A7" s="46" t="s">
         <v>1514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D02680-D9E7-4812-880A-0D5C634B6A57}">
+  <dimension ref="C3:K15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:11">
+      <c r="C3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11">
+      <c r="C4" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11">
+      <c r="C5" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11">
+      <c r="C6" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11">
+      <c r="C7" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11">
+      <c r="C8" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11">
+      <c r="C9" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11">
+      <c r="C10" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11">
+      <c r="D12" s="67"/>
+      <c r="E12" s="50" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="50" t="s">
+        <v>1709</v>
+      </c>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+    </row>
+    <row r="13" spans="3:11">
+      <c r="D13" s="67"/>
+      <c r="E13" s="50" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="50" t="s">
+        <v>1711</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+    </row>
+    <row r="14" spans="3:11">
+      <c r="E14" s="50" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="50" t="s">
+        <v>1713</v>
+      </c>
+      <c r="J14" s="67"/>
+    </row>
+    <row r="15" spans="3:11">
+      <c r="E15" s="50" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="50" t="s">
+        <v>1715</v>
+      </c>
+      <c r="J15" s="67"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5321348C-2000-48DD-ACC4-9EE2E70CB318}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="67"/>
+    <col min="2" max="2" width="28.109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="67"/>
+    <col min="5" max="5" width="14.21875" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.5546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="67" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G1" s="67" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="67" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="67" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F3" s="67" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="67" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D4" s="67" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F4" s="67" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="67" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C5" s="67" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D5" s="67" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F5" s="67" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="67" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F6" s="67" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="67" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F7" s="67" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="67" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="67" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="67" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="67" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F11" s="67" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="67" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="67" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F13" s="67" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="67" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F14" s="67" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="67" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F15" s="67" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="67" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D16" s="67" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F16" s="67" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="67" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D17" s="67" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F17" s="67" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="67" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="67" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="67" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D20" s="67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E20" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F20" s="67" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="67" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E21" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F21" s="67" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="67" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D22" s="67" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E22" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F22" s="67" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="67" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D23" s="67" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F23" s="67" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="67" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D24" s="67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E24" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F24" s="67" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="67" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E25" s="67" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F25" s="67" t="s">
+        <v>1834</v>
       </c>
     </row>
   </sheetData>
@@ -19195,12 +20258,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB3911-F8E7-4083-974C-8215A8CA05BB}">
   <dimension ref="A4:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="112.7109375" customWidth="1"/>
+    <col min="2" max="2" width="112.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:2" ht="255">
+    <row r="4" spans="1:2" ht="244.8">
       <c r="A4" t="s">
         <v>400</v>
       </c>
@@ -19208,7 +20271,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="409.5">
+    <row r="10" spans="1:2" ht="409.6">
       <c r="A10" t="s">
         <v>401</v>
       </c>
@@ -19224,22 +20287,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FEA767-FEF3-4D23-9143-13AEAC680DA5}">
   <dimension ref="A1:Q404"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5703125" customWidth="1"/>
-    <col min="7" max="8" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="39.5703125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="39.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5546875" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1">
+    <row r="1" spans="1:11" ht="16.2" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>760</v>
       </c>
@@ -19270,7 +20333,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="31.5" thickBot="1">
+    <row r="2" spans="1:11" ht="31.2" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -19301,7 +20364,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="31.5" thickBot="1">
+    <row r="3" spans="1:11" ht="31.2" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>119</v>
       </c>
@@ -19329,7 +20392,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="31.5" thickBot="1">
+    <row r="4" spans="1:11" ht="31.2" thickBot="1">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -19357,7 +20420,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="46.5" thickBot="1">
+    <row r="5" spans="1:11" ht="46.2" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -19385,7 +20448,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="31.5" thickBot="1">
+    <row r="6" spans="1:11" ht="31.2" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>119</v>
       </c>
@@ -19413,7 +20476,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="31.5" thickBot="1">
+    <row r="7" spans="1:11" ht="31.2" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>119</v>
       </c>
@@ -19441,7 +20504,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="31.5" thickBot="1">
+    <row r="8" spans="1:11" ht="31.2" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
@@ -19469,7 +20532,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="31.5" thickBot="1">
+    <row r="9" spans="1:11" ht="31.2" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>119</v>
       </c>
@@ -19497,7 +20560,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="31.5" thickBot="1">
+    <row r="10" spans="1:11" ht="31.2" thickBot="1">
       <c r="A10" s="6" t="s">
         <v>119</v>
       </c>
@@ -19525,7 +20588,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.5" thickBot="1">
+    <row r="11" spans="1:11" ht="31.2" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
@@ -19553,7 +20616,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="31.5" thickBot="1">
+    <row r="12" spans="1:11" ht="31.2" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>119</v>
       </c>
@@ -19581,7 +20644,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="31.5" thickBot="1">
+    <row r="13" spans="1:11" ht="31.2" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>119</v>
       </c>
@@ -19609,7 +20672,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="31.5" thickBot="1">
+    <row r="14" spans="1:11" ht="31.2" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>119</v>
       </c>
@@ -19637,7 +20700,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="31.5" thickBot="1">
+    <row r="15" spans="1:11" ht="31.2" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
@@ -19665,7 +20728,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="31.5" thickBot="1">
+    <row r="16" spans="1:11" ht="31.2" thickBot="1">
       <c r="A16" s="6" t="s">
         <v>119</v>
       </c>
@@ -19693,7 +20756,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="31.5" thickBot="1">
+    <row r="17" spans="1:17" ht="31.2" thickBot="1">
       <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
@@ -19721,7 +20784,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="46.5" thickBot="1">
+    <row r="18" spans="1:17" ht="31.2" thickBot="1">
       <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
@@ -19749,7 +20812,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="31.5" thickBot="1">
+    <row r="19" spans="1:17" ht="31.2" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>119</v>
       </c>
@@ -19777,7 +20840,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="31.5" thickBot="1">
+    <row r="20" spans="1:17" ht="31.2" thickBot="1">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -19805,7 +20868,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="31.5" thickBot="1">
+    <row r="21" spans="1:17" ht="31.2" thickBot="1">
       <c r="A21" s="6" t="s">
         <v>119</v>
       </c>
@@ -19833,7 +20896,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="31.5" thickBot="1">
+    <row r="22" spans="1:17" ht="31.2" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>119</v>
       </c>
@@ -19861,7 +20924,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="31.5" thickBot="1">
+    <row r="23" spans="1:17" ht="31.2" thickBot="1">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -19889,7 +20952,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="31.5" thickBot="1">
+    <row r="24" spans="1:17" ht="31.2" thickBot="1">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -19924,7 +20987,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="31.5" thickBot="1">
+    <row r="25" spans="1:17" ht="31.2" thickBot="1">
       <c r="A25" s="6" t="s">
         <v>120</v>
       </c>
@@ -19959,7 +21022,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="31.5" thickBot="1">
+    <row r="26" spans="1:17" ht="31.2" thickBot="1">
       <c r="A26" s="6" t="s">
         <v>120</v>
       </c>
@@ -19994,7 +21057,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="31.5" thickBot="1">
+    <row r="27" spans="1:17" ht="31.2" thickBot="1">
       <c r="A27" s="6" t="s">
         <v>120</v>
       </c>
@@ -20029,7 +21092,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="31.5" thickBot="1">
+    <row r="28" spans="1:17" ht="31.2" thickBot="1">
       <c r="A28" s="6" t="s">
         <v>120</v>
       </c>
@@ -20064,7 +21127,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="31.5" thickBot="1">
+    <row r="29" spans="1:17" ht="31.2" thickBot="1">
       <c r="A29" s="6" t="s">
         <v>120</v>
       </c>
@@ -20099,7 +21162,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="31.5" thickBot="1">
+    <row r="30" spans="1:17" ht="31.2" thickBot="1">
       <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
@@ -20134,7 +21197,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="31.5" thickBot="1">
+    <row r="31" spans="1:17" ht="31.2" thickBot="1">
       <c r="A31" s="6" t="s">
         <v>120</v>
       </c>
@@ -20169,7 +21232,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="31.5" thickBot="1">
+    <row r="32" spans="1:17" ht="31.2" thickBot="1">
       <c r="A32" s="6" t="s">
         <v>120</v>
       </c>
@@ -20204,7 +21267,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="31.5" thickBot="1">
+    <row r="33" spans="1:17" ht="31.2" thickBot="1">
       <c r="A33" s="6" t="s">
         <v>120</v>
       </c>
@@ -20239,7 +21302,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="31.5" thickBot="1">
+    <row r="34" spans="1:17" ht="31.2" thickBot="1">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -20274,7 +21337,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="31.5" thickBot="1">
+    <row r="35" spans="1:17" ht="31.2" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>120</v>
       </c>
@@ -20309,7 +21372,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="31.5" thickBot="1">
+    <row r="36" spans="1:17" ht="31.2" thickBot="1">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -20344,7 +21407,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="31.5" thickBot="1">
+    <row r="37" spans="1:17" ht="31.2" thickBot="1">
       <c r="A37" s="6" t="s">
         <v>120</v>
       </c>
@@ -20379,7 +21442,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="31.5" thickBot="1">
+    <row r="38" spans="1:17" ht="31.2" thickBot="1">
       <c r="A38" s="6" t="s">
         <v>120</v>
       </c>
@@ -20414,7 +21477,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="31.5" thickBot="1">
+    <row r="39" spans="1:17" ht="31.2" thickBot="1">
       <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
@@ -20449,7 +21512,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="31.5" thickBot="1">
+    <row r="40" spans="1:17" ht="31.2" thickBot="1">
       <c r="A40" s="6" t="s">
         <v>120</v>
       </c>
@@ -20484,7 +21547,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="31.5" thickBot="1">
+    <row r="41" spans="1:17" ht="31.2" thickBot="1">
       <c r="A41" s="6" t="s">
         <v>121</v>
       </c>
@@ -20516,7 +21579,7 @@
         <v>TS-UC-SEC-MCP-003test_001_query_under_5s_allowed</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="31.5" thickBot="1">
+    <row r="42" spans="1:17" ht="31.2" thickBot="1">
       <c r="A42" s="6" t="s">
         <v>121</v>
       </c>
@@ -20548,7 +21611,7 @@
         <v>TS-UC-SEC-MCP-003test_002_query_at_5s_allowed</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="31.5" thickBot="1">
+    <row r="43" spans="1:17" ht="31.2" thickBot="1">
       <c r="A43" s="6" t="s">
         <v>121</v>
       </c>
@@ -20580,7 +21643,7 @@
         <v>TS-UC-SEC-MCP-003test_003_query_over_5s_timeout_cancelled</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="31.5" thickBot="1">
+    <row r="44" spans="1:17" ht="31.2" thickBot="1">
       <c r="A44" s="6" t="s">
         <v>121</v>
       </c>
@@ -20612,7 +21675,7 @@
         <v>TS-UC-SEC-MCP-003test_004_query_result_under_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="31.5" thickBot="1">
+    <row r="45" spans="1:17" ht="31.2" thickBot="1">
       <c r="A45" s="6" t="s">
         <v>121</v>
       </c>
@@ -20644,7 +21707,7 @@
         <v>TS-UC-SEC-MCP-003test_005_query_result_at_1000_rows_allowed</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="31.5" thickBot="1">
+    <row r="46" spans="1:17" ht="31.2" thickBot="1">
       <c r="A46" s="6" t="s">
         <v>121</v>
       </c>
@@ -20676,7 +21739,7 @@
         <v>TS-UC-SEC-MCP-003test_006_query_result_over_1000_rows_truncated</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="31.5" thickBot="1">
+    <row r="47" spans="1:17" ht="31.2" thickBot="1">
       <c r="A47" s="6" t="s">
         <v>121</v>
       </c>
@@ -20708,7 +21771,7 @@
         <v>TS-UC-SEC-MCP-003test_007_query_result_truncated_flag_set</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="31.5" thickBot="1">
+    <row r="48" spans="1:17" ht="31.2" thickBot="1">
       <c r="A48" s="6" t="s">
         <v>121</v>
       </c>
@@ -20740,7 +21803,7 @@
         <v>TS-UC-SEC-MCP-003test_008_timeout_returns_partial_results</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="31.5" thickBot="1">
+    <row r="49" spans="1:11" ht="31.2" thickBot="1">
       <c r="A49" s="6" t="s">
         <v>121</v>
       </c>
@@ -20772,7 +21835,7 @@
         <v>TS-UC-SEC-MCP-003test_009_timeout_audit_log_created</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="31.5" thickBot="1">
+    <row r="50" spans="1:11" ht="31.2" thickBot="1">
       <c r="A50" s="6" t="s">
         <v>121</v>
       </c>
@@ -20804,7 +21867,7 @@
         <v>TS-UC-SEC-MCP-003test_010_row_limit_audit_log_created</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="31.5" thickBot="1">
+    <row r="51" spans="1:11" ht="31.2" thickBot="1">
       <c r="A51" s="6" t="s">
         <v>121</v>
       </c>
@@ -20836,7 +21899,7 @@
         <v>TS-UC-SEC-MCP-003test_011_combined_timeout_and_row_limit</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="31.5" thickBot="1">
+    <row r="52" spans="1:11" ht="31.2" thickBot="1">
       <c r="A52" s="6" t="s">
         <v>121</v>
       </c>
@@ -20868,7 +21931,7 @@
         <v>TS-UC-SEC-MCP-003test_012_query_limit_config_per_tenant</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="31.5" thickBot="1">
+    <row r="53" spans="1:11" ht="31.2" thickBot="1">
       <c r="A53" s="6" t="s">
         <v>121</v>
       </c>
@@ -20900,7 +21963,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_001_exactly_1000_rows</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="31.5" thickBot="1">
+    <row r="54" spans="1:11" ht="31.2" thickBot="1">
       <c r="A54" s="6" t="s">
         <v>121</v>
       </c>
@@ -20932,7 +21995,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_002_empty_result_set</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="31.5" thickBot="1">
+    <row r="55" spans="1:11" ht="31.2" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>121</v>
       </c>
@@ -20964,7 +22027,7 @@
         <v>TS-UC-SEC-MCP-003test_edge_003_streaming_query_timeout</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="31.5" thickBot="1">
+    <row r="56" spans="1:11" ht="31.2" thickBot="1">
       <c r="A56" s="6" t="s">
         <v>123</v>
       </c>
@@ -20996,7 +22059,7 @@
         <v>TS-UC-SEC-ANO-001test_001_detect_dni_valid_12345678Z</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="31.5" thickBot="1">
+    <row r="57" spans="1:11" ht="31.2" thickBot="1">
       <c r="A57" s="6" t="s">
         <v>123</v>
       </c>
@@ -21028,7 +22091,7 @@
         <v>TS-UC-SEC-ANO-001test_002_detect_dni_valid_87654321X</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="31.5" thickBot="1">
+    <row r="58" spans="1:11" ht="31.2" thickBot="1">
       <c r="A58" s="6" t="s">
         <v>123</v>
       </c>
@@ -21060,7 +22123,7 @@
         <v>TS-UC-SEC-ANO-001test_003_detect_dni_invalid_length_9_digits</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="31.5" thickBot="1">
+    <row r="59" spans="1:11" ht="31.2" thickBot="1">
       <c r="A59" s="6" t="s">
         <v>123</v>
       </c>
@@ -21092,7 +22155,7 @@
         <v>TS-UC-SEC-ANO-001test_004_detect_dni_invalid_length_7_digits</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="31.5" thickBot="1">
+    <row r="60" spans="1:11" ht="31.2" thickBot="1">
       <c r="A60" s="6" t="s">
         <v>123</v>
       </c>
@@ -21124,7 +22187,7 @@
         <v>TS-UC-SEC-ANO-001test_005_detect_dni_invalid_letter_checksum</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="31.5" thickBot="1">
+    <row r="61" spans="1:11" ht="31.2" thickBot="1">
       <c r="A61" s="6" t="s">
         <v>123</v>
       </c>
@@ -21156,7 +22219,7 @@
         <v>TS-UC-SEC-ANO-001test_006_detect_multiple_dnis_in_text</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="31.5" thickBot="1">
+    <row r="62" spans="1:11" ht="31.2" thickBot="1">
       <c r="A62" s="6" t="s">
         <v>123</v>
       </c>
@@ -21188,7 +22251,7 @@
         <v>TS-UC-SEC-ANO-001test_007_detect_email_simple</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="31.5" thickBot="1">
+    <row r="63" spans="1:11" ht="31.2" thickBot="1">
       <c r="A63" s="6" t="s">
         <v>123</v>
       </c>
@@ -21220,7 +22283,7 @@
         <v>TS-UC-SEC-ANO-001test_008_detect_email_with_subdomain</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="31.5" thickBot="1">
+    <row r="64" spans="1:11" ht="31.2" thickBot="1">
       <c r="A64" s="6" t="s">
         <v>123</v>
       </c>
@@ -21252,7 +22315,7 @@
         <v>TS-UC-SEC-ANO-001test_009_detect_email_with_plus_sign</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="31.5" thickBot="1">
+    <row r="65" spans="1:11" ht="31.2" thickBot="1">
       <c r="A65" s="6" t="s">
         <v>123</v>
       </c>
@@ -21284,7 +22347,7 @@
         <v>TS-UC-SEC-ANO-001test_010_detect_email_invalid_no_at</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="31.5" thickBot="1">
+    <row r="66" spans="1:11" ht="31.2" thickBot="1">
       <c r="A66" s="6" t="s">
         <v>123</v>
       </c>
@@ -21316,7 +22379,7 @@
         <v>TS-UC-SEC-ANO-001test_011_detect_multiple_emails_in_text</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="31.5" thickBot="1">
+    <row r="67" spans="1:11" ht="31.2" thickBot="1">
       <c r="A67" s="6" t="s">
         <v>123</v>
       </c>
@@ -21348,7 +22411,7 @@
         <v>TS-UC-SEC-ANO-001test_012_detect_phone_mobile_612345678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="31.5" thickBot="1">
+    <row r="68" spans="1:11" ht="31.2" thickBot="1">
       <c r="A68" s="6" t="s">
         <v>123</v>
       </c>
@@ -21380,7 +22443,7 @@
         <v>TS-UC-SEC-ANO-001test_013_detect_phone_mobile_with_prefix_34</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="31.5" thickBot="1">
+    <row r="69" spans="1:11" ht="31.2" thickBot="1">
       <c r="A69" s="6" t="s">
         <v>123</v>
       </c>
@@ -21412,7 +22475,7 @@
         <v>TS-UC-SEC-ANO-001test_014_detect_phone_landline_912345678</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="31.5" thickBot="1">
+    <row r="70" spans="1:11" ht="31.2" thickBot="1">
       <c r="A70" s="6" t="s">
         <v>123</v>
       </c>
@@ -21444,7 +22507,7 @@
         <v>TS-UC-SEC-ANO-001test_015_detect_phone_invalid_short</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="31.5" thickBot="1">
+    <row r="71" spans="1:11" ht="31.2" thickBot="1">
       <c r="A71" s="6" t="s">
         <v>123</v>
       </c>
@@ -21476,7 +22539,7 @@
         <v>TS-UC-SEC-ANO-001test_016_detect_multiple_phones_in_text</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="31.5" thickBot="1">
+    <row r="72" spans="1:11" ht="31.2" thickBot="1">
       <c r="A72" s="6" t="s">
         <v>123</v>
       </c>
@@ -21508,7 +22571,7 @@
         <v>TS-UC-SEC-ANO-001test_017_detect_iban_spain_valid</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="31.5" thickBot="1">
+    <row r="73" spans="1:11" ht="31.2" thickBot="1">
       <c r="A73" s="6" t="s">
         <v>123</v>
       </c>
@@ -21540,7 +22603,7 @@
         <v>TS-UC-SEC-ANO-001test_018_detect_iban_germany_valid</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="31.5" thickBot="1">
+    <row r="74" spans="1:11" ht="31.2" thickBot="1">
       <c r="A74" s="6" t="s">
         <v>123</v>
       </c>
@@ -21572,7 +22635,7 @@
         <v>TS-UC-SEC-ANO-001test_019_detect_iban_invalid_checksum</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="31.5" thickBot="1">
+    <row r="75" spans="1:11" ht="31.2" thickBot="1">
       <c r="A75" s="6" t="s">
         <v>123</v>
       </c>
@@ -21604,7 +22667,7 @@
         <v>TS-UC-SEC-ANO-001test_020_detect_iban_invalid_length</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="31.5" thickBot="1">
+    <row r="76" spans="1:11" ht="31.2" thickBot="1">
       <c r="A76" s="6" t="s">
         <v>123</v>
       </c>
@@ -21636,7 +22699,7 @@
         <v>TS-UC-SEC-ANO-001test_021_detect_all_pii_types_in_document</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="31.5" thickBot="1">
+    <row r="77" spans="1:11" ht="31.2" thickBot="1">
       <c r="A77" s="6" t="s">
         <v>123</v>
       </c>
@@ -21668,7 +22731,7 @@
         <v>TS-UC-SEC-ANO-001test_022_detect_no_pii_clean_document</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="31.5" thickBot="1">
+    <row r="78" spans="1:11" ht="31.2" thickBot="1">
       <c r="A78" s="6" t="s">
         <v>123</v>
       </c>
@@ -21700,7 +22763,7 @@
         <v>TS-UC-SEC-ANO-001test_023_detect_pii_positions_returned</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="31.5" thickBot="1">
+    <row r="79" spans="1:11" ht="31.2" thickBot="1">
       <c r="A79" s="6" t="s">
         <v>123</v>
       </c>
@@ -21732,7 +22795,7 @@
         <v>TS-UC-SEC-ANO-001test_024_detect_pii_counts_by_type</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="31.5" thickBot="1">
+    <row r="80" spans="1:11" ht="31.2" thickBot="1">
       <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
@@ -21764,7 +22827,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_001_pii_in_different_languages</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="31.5" thickBot="1">
+    <row r="81" spans="1:11" ht="31.2" thickBot="1">
       <c r="A81" s="6" t="s">
         <v>123</v>
       </c>
@@ -21796,7 +22859,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_002_pii_with_unicode_characters</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="31.5" thickBot="1">
+    <row r="82" spans="1:11" ht="31.2" thickBot="1">
       <c r="A82" s="6" t="s">
         <v>123</v>
       </c>
@@ -21819,7 +22882,7 @@
         <v>TS-UC-SEC-ANO-001test_edge_003_pii_in_html_escaped_text</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="31.5" thickBot="1">
+    <row r="83" spans="1:11" ht="31.2" thickBot="1">
       <c r="A83" s="6" t="s">
         <v>124</v>
       </c>
@@ -21848,7 +22911,7 @@
         <v>TS-UC-SEC-ANO-002test_001_redact_dni_to_redacted</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="31.5" thickBot="1">
+    <row r="84" spans="1:11" ht="31.2" thickBot="1">
       <c r="A84" s="6" t="s">
         <v>124</v>
       </c>
@@ -21877,7 +22940,7 @@
         <v>TS-UC-SEC-ANO-002test_002_redact_email_to_redacted</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="31.5" thickBot="1">
+    <row r="85" spans="1:11" ht="31.2" thickBot="1">
       <c r="A85" s="6" t="s">
         <v>124</v>
       </c>
@@ -21906,7 +22969,7 @@
         <v>TS-UC-SEC-ANO-002test_003_redact_phone_to_redacted</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="31.5" thickBot="1">
+    <row r="86" spans="1:11" ht="31.2" thickBot="1">
       <c r="A86" s="6" t="s">
         <v>124</v>
       </c>
@@ -21935,7 +22998,7 @@
         <v>TS-UC-SEC-ANO-002test_004_redact_multiple_pii_all_redacted</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="31.5" thickBot="1">
+    <row r="87" spans="1:11" ht="31.2" thickBot="1">
       <c r="A87" s="6" t="s">
         <v>124</v>
       </c>
@@ -21964,7 +23027,7 @@
         <v>TS-UC-SEC-ANO-002test_005_hash_dni_deterministic</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="31.5" thickBot="1">
+    <row r="88" spans="1:11" ht="31.2" thickBot="1">
       <c r="A88" s="6" t="s">
         <v>124</v>
       </c>
@@ -21993,7 +23056,7 @@
         <v>TS-UC-SEC-ANO-002test_006_hash_same_value_same_hash</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="31.5" thickBot="1">
+    <row r="89" spans="1:11" ht="31.2" thickBot="1">
       <c r="A89" s="6" t="s">
         <v>124</v>
       </c>
@@ -22022,7 +23085,7 @@
         <v>TS-UC-SEC-ANO-002test_007_hash_different_values_different_hash</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="31.5" thickBot="1">
+    <row r="90" spans="1:11" ht="31.2" thickBot="1">
       <c r="A90" s="6" t="s">
         <v>124</v>
       </c>
@@ -22051,7 +23114,7 @@
         <v>TS-UC-SEC-ANO-002test_008_hash_irreversible_validation</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="31.5" thickBot="1">
+    <row r="91" spans="1:11" ht="31.2" thickBot="1">
       <c r="A91" s="6" t="s">
         <v>124</v>
       </c>
@@ -22080,7 +23143,7 @@
         <v>TS-UC-SEC-ANO-002test_009_pseudonymize_name_to_persona_001</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="31.5" thickBot="1">
+    <row r="92" spans="1:11" ht="31.2" thickBot="1">
       <c r="A92" s="6" t="s">
         <v>124</v>
       </c>
@@ -22109,7 +23172,7 @@
         <v>TS-UC-SEC-ANO-002test_010_pseudonymize_consistent_same_name</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="46.5" thickBot="1">
+    <row r="93" spans="1:11" ht="31.2" thickBot="1">
       <c r="A93" s="6" t="s">
         <v>124</v>
       </c>
@@ -22138,7 +23201,7 @@
         <v>TS-UC-SEC-ANO-002test_011_pseudonymize_different_names_different_ids</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="31.5" thickBot="1">
+    <row r="94" spans="1:11" ht="31.2" thickBot="1">
       <c r="A94" s="6" t="s">
         <v>124</v>
       </c>
@@ -22167,7 +23230,7 @@
         <v>TS-UC-SEC-ANO-002test_012_pseudonymize_in_context_preserved</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="31.5" thickBot="1">
+    <row r="95" spans="1:11" ht="31.2" thickBot="1">
       <c r="A95" s="6" t="s">
         <v>124</v>
       </c>
@@ -22196,7 +23259,7 @@
         <v>TS-UC-SEC-ANO-002test_013_strategy_by_pii_type_default</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="31.5" thickBot="1">
+    <row r="96" spans="1:11" ht="31.2" thickBot="1">
       <c r="A96" s="6" t="s">
         <v>124</v>
       </c>
@@ -22225,7 +23288,7 @@
         <v>TS-UC-SEC-ANO-002test_014_strategy_by_tenant_config</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="31.5" thickBot="1">
+    <row r="97" spans="1:11" ht="31.2" thickBot="1">
       <c r="A97" s="6" t="s">
         <v>124</v>
       </c>
@@ -22254,7 +23317,7 @@
         <v>TS-UC-SEC-ANO-002test_015_strategy_mixed_per_type</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="31.5" thickBot="1">
+    <row r="98" spans="1:11" ht="31.2" thickBot="1">
       <c r="A98" s="6" t="s">
         <v>124</v>
       </c>
@@ -22283,7 +23346,7 @@
         <v>TS-UC-SEC-ANO-002test_016_strategy_none_keeps_original</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="31.5" thickBot="1">
+    <row r="99" spans="1:11" ht="31.2" thickBot="1">
       <c r="A99" s="6" t="s">
         <v>124</v>
       </c>
@@ -22312,7 +23375,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_001_nested_pii_in_pii</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="31.5" thickBot="1">
+    <row r="100" spans="1:11" ht="31.2" thickBot="1">
       <c r="A100" s="6" t="s">
         <v>124</v>
       </c>
@@ -22341,7 +23404,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_002_overlapping_pii_positions</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="31.5" thickBot="1">
+    <row r="101" spans="1:11" ht="31.2" thickBot="1">
       <c r="A101" s="6" t="s">
         <v>124</v>
       </c>
@@ -22370,7 +23433,7 @@
         <v>TS-UC-SEC-ANO-002test_edge_003_empty_text_no_error</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16.5" thickBot="1">
+    <row r="102" spans="1:11" ht="16.2" thickBot="1">
       <c r="A102" s="6" t="s">
         <v>125</v>
       </c>
@@ -22399,7 +23462,7 @@
         <v>TS-UC-SEC-ANO-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16.5" thickBot="1">
+    <row r="103" spans="1:11" ht="16.2" thickBot="1">
       <c r="A103" s="6" t="s">
         <v>126</v>
       </c>
@@ -22428,7 +23491,7 @@
         <v>TS-UC-SEC-TNT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16.5" thickBot="1">
+    <row r="104" spans="1:11" ht="16.2" thickBot="1">
       <c r="A104" s="6" t="s">
         <v>127</v>
       </c>
@@ -22454,7 +23517,7 @@
         <v>TS-UC-SEC-JWT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16.5" thickBot="1">
+    <row r="105" spans="1:11" ht="16.2" thickBot="1">
       <c r="A105" s="6" t="s">
         <v>128</v>
       </c>
@@ -22480,7 +23543,7 @@
         <v>TS-UC-SEC-AUD-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="31.5" thickBot="1">
+    <row r="106" spans="1:11" ht="31.2" thickBot="1">
       <c r="A106" s="6" t="s">
         <v>129</v>
       </c>
@@ -22509,7 +23572,7 @@
         <v>TS-UC-SEC-GAM-001test_001_mass_changes_11_in_hour_detected</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="31.5" thickBot="1">
+    <row r="107" spans="1:11" ht="31.2" thickBot="1">
       <c r="A107" s="6" t="s">
         <v>129</v>
       </c>
@@ -22538,7 +23601,7 @@
         <v>TS-UC-SEC-GAM-001test_002_mass_changes_10_in_hour_allowed</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="31.5" thickBot="1">
+    <row r="108" spans="1:11" ht="31.2" thickBot="1">
       <c r="A108" s="6" t="s">
         <v>129</v>
       </c>
@@ -22567,7 +23630,7 @@
         <v>TS-UC-SEC-GAM-001test_003_mass_changes_window_reset</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="31.5" thickBot="1">
+    <row r="109" spans="1:11" ht="31.2" thickBot="1">
       <c r="A109" s="6" t="s">
         <v>129</v>
       </c>
@@ -22596,7 +23659,7 @@
         <v>TS-UC-SEC-GAM-001test_004_resolve_reintroduce_3_times_detected</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="31.5" thickBot="1">
+    <row r="110" spans="1:11" ht="31.2" thickBot="1">
       <c r="A110" s="6" t="s">
         <v>129</v>
       </c>
@@ -22625,7 +23688,7 @@
         <v>TS-UC-SEC-GAM-001test_005_resolve_reintroduce_2_times_allowed</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="31.5" thickBot="1">
+    <row r="111" spans="1:11" ht="31.2" thickBot="1">
       <c r="A111" s="6" t="s">
         <v>129</v>
       </c>
@@ -22654,7 +23717,7 @@
         <v>TS-UC-SEC-GAM-001test_006_resolve_reintroduce_different_hash_allowed</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="31.5" thickBot="1">
+    <row r="112" spans="1:11" ht="31.2" thickBot="1">
       <c r="A112" s="6" t="s">
         <v>129</v>
       </c>
@@ -22683,7 +23746,7 @@
         <v>TS-UC-SEC-GAM-001test_007_high_score_few_docs_detected</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="31.5" thickBot="1">
+    <row r="113" spans="1:11" ht="31.2" thickBot="1">
       <c r="A113" s="6" t="s">
         <v>129</v>
       </c>
@@ -22712,7 +23775,7 @@
         <v>TS-UC-SEC-GAM-001test_008_high_score_many_docs_allowed</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="31.5" thickBot="1">
+    <row r="114" spans="1:11" ht="31.2" thickBot="1">
       <c r="A114" s="6" t="s">
         <v>129</v>
       </c>
@@ -22741,7 +23804,7 @@
         <v>TS-UC-SEC-GAM-001test_009_high_score_threshold_boundary</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="31.5" thickBot="1">
+    <row r="115" spans="1:11" ht="31.2" thickBot="1">
       <c r="A115" s="6" t="s">
         <v>129</v>
       </c>
@@ -22770,7 +23833,7 @@
         <v>TS-UC-SEC-GAM-001test_010_weight_change_25_percent_detected</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="31.5" thickBot="1">
+    <row r="116" spans="1:11" ht="31.2" thickBot="1">
       <c r="A116" s="6" t="s">
         <v>129</v>
       </c>
@@ -22799,7 +23862,7 @@
         <v>TS-UC-SEC-GAM-001test_011_weight_change_15_percent_allowed</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="31.5" thickBot="1">
+    <row r="117" spans="1:11" ht="31.2" thickBot="1">
       <c r="A117" s="6" t="s">
         <v>129</v>
       </c>
@@ -22828,7 +23891,7 @@
         <v>TS-UC-SEC-GAM-001test_012_weight_change_tracking_24h_window</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="31.5" thickBot="1">
+    <row r="118" spans="1:11" ht="31.2" thickBot="1">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -22857,7 +23920,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_001_multiple_violations_combined</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="31.5" thickBot="1">
+    <row r="119" spans="1:11" ht="31.2" thickBot="1">
       <c r="A119" s="6" t="s">
         <v>129</v>
       </c>
@@ -22886,7 +23949,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_002_violation_penalty_application</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="31.5" thickBot="1">
+    <row r="120" spans="1:11" ht="31.2" thickBot="1">
       <c r="A120" s="6" t="s">
         <v>129</v>
       </c>
@@ -22915,7 +23978,7 @@
         <v>TS-UC-SEC-GAM-001test_edge_003_violation_audit_logging</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="31.5" thickBot="1">
+    <row r="121" spans="1:11" ht="31.2" thickBot="1">
       <c r="A121" s="6" t="s">
         <v>130</v>
       </c>
@@ -22947,7 +24010,7 @@
         <v>TS-UD-DOC-CLS-001test_001_clause_creation_with_all_fields</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="31.5" thickBot="1">
+    <row r="122" spans="1:11" ht="31.2" thickBot="1">
       <c r="A122" s="6" t="s">
         <v>130</v>
       </c>
@@ -22976,7 +24039,7 @@
         <v>TS-UD-DOC-CLS-001test_002_clause_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="31.5" thickBot="1">
+    <row r="123" spans="1:11" ht="31.2" thickBot="1">
       <c r="A123" s="6" t="s">
         <v>130</v>
       </c>
@@ -23005,7 +24068,7 @@
         <v>TS-UD-DOC-CLS-001test_003_clause_creation_fails_without_content</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="31.5" thickBot="1">
+    <row r="124" spans="1:11" ht="31.2" thickBot="1">
       <c r="A124" s="6" t="s">
         <v>130</v>
       </c>
@@ -23034,7 +24097,7 @@
         <v>TS-UD-DOC-CLS-001test_004_clause_creation_fails_without_document_id</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="31.5" thickBot="1">
+    <row r="125" spans="1:11" ht="31.2" thickBot="1">
       <c r="A125" s="6" t="s">
         <v>130</v>
       </c>
@@ -23063,7 +24126,7 @@
         <v>TS-UD-DOC-CLS-001test_005_clause_creation_fails_without_tenant_id</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="31.5" thickBot="1">
+    <row r="126" spans="1:11" ht="31.2" thickBot="1">
       <c r="A126" s="6" t="s">
         <v>130</v>
       </c>
@@ -23092,7 +24155,7 @@
         <v>TS-UD-DOC-CLS-001test_006_clause_immutability_after_creation</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="31.5" thickBot="1">
+    <row r="127" spans="1:11" ht="31.2" thickBot="1">
       <c r="A127" s="6" t="s">
         <v>130</v>
       </c>
@@ -23121,7 +24184,7 @@
         <v>TS-UD-DOC-CLS-001test_007_clause_number_format_primera</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="31.5" thickBot="1">
+    <row r="128" spans="1:11" ht="31.2" thickBot="1">
       <c r="A128" s="6" t="s">
         <v>130</v>
       </c>
@@ -23150,7 +24213,7 @@
         <v>TS-UD-DOC-CLS-001test_008_clause_number_format_numeric</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="31.5" thickBot="1">
+    <row r="129" spans="1:11" ht="31.2" thickBot="1">
       <c r="A129" s="6" t="s">
         <v>130</v>
       </c>
@@ -23179,7 +24242,7 @@
         <v>TS-UD-DOC-CLS-001test_009_clause_number_format_decimal</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="31.5" thickBot="1">
+    <row r="130" spans="1:11" ht="31.2" thickBot="1">
       <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
@@ -23208,7 +24271,7 @@
         <v>TS-UD-DOC-CLS-001test_010_clause_number_normalization</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="31.5" thickBot="1">
+    <row r="131" spans="1:11" ht="31.2" thickBot="1">
       <c r="A131" s="6" t="s">
         <v>130</v>
       </c>
@@ -23237,7 +24300,7 @@
         <v>TS-UD-DOC-CLS-001test_011_clause_content_max_length</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="31.5" thickBot="1">
+    <row r="132" spans="1:11" ht="31.2" thickBot="1">
       <c r="A132" s="6" t="s">
         <v>130</v>
       </c>
@@ -23266,7 +24329,7 @@
         <v>TS-UD-DOC-CLS-001test_012_clause_content_empty_rejected</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="31.5" thickBot="1">
+    <row r="133" spans="1:11" ht="31.2" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>130</v>
       </c>
@@ -23295,7 +24358,7 @@
         <v>TS-UD-DOC-CLS-001test_013_clause_document_fk_valid</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="31.5" thickBot="1">
+    <row r="134" spans="1:11" ht="31.2" thickBot="1">
       <c r="A134" s="6" t="s">
         <v>130</v>
       </c>
@@ -23324,7 +24387,7 @@
         <v>TS-UD-DOC-CLS-001test_014_clause_document_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="31.5" thickBot="1">
+    <row r="135" spans="1:11" ht="31.2" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>130</v>
       </c>
@@ -23353,7 +24416,7 @@
         <v>TS-UD-DOC-CLS-001test_015_clause_tenant_fk_valid</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="31.5" thickBot="1">
+    <row r="136" spans="1:11" ht="31.2" thickBot="1">
       <c r="A136" s="6" t="s">
         <v>130</v>
       </c>
@@ -23382,7 +24445,7 @@
         <v>TS-UD-DOC-CLS-001test_016_clause_tenant_fk_invalid_rejected</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="31.5" thickBot="1">
+    <row r="137" spans="1:11" ht="31.2" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>130</v>
       </c>
@@ -23411,7 +24474,7 @@
         <v>TS-UD-DOC-CLS-001test_017_clause_on_delete_restrict_document</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="31.5" thickBot="1">
+    <row r="138" spans="1:11" ht="31.2" thickBot="1">
       <c r="A138" s="6" t="s">
         <v>130</v>
       </c>
@@ -23440,7 +24503,7 @@
         <v>TS-UD-DOC-CLS-001test_018_clause_on_delete_restrict_tenant</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="31.5" thickBot="1">
+    <row r="139" spans="1:11" ht="31.2" thickBot="1">
       <c r="A139" s="6" t="s">
         <v>130</v>
       </c>
@@ -23469,7 +24532,7 @@
         <v>TS-UD-DOC-CLS-001test_019_clause_embedding_vector_size</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="31.5" thickBot="1">
+    <row r="140" spans="1:11" ht="31.2" thickBot="1">
       <c r="A140" s="6" t="s">
         <v>130</v>
       </c>
@@ -23498,7 +24561,7 @@
         <v>TS-UD-DOC-CLS-001test_020_clause_embedding_generation</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="31.5" thickBot="1">
+    <row r="141" spans="1:11" ht="31.2" thickBot="1">
       <c r="A141" s="6" t="s">
         <v>130</v>
       </c>
@@ -23527,7 +24590,7 @@
         <v>TS-UD-DOC-CLS-001test_021_clause_embedding_null_allowed</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="31.5" thickBot="1">
+    <row r="142" spans="1:11" ht="31.2" thickBot="1">
       <c r="A142" s="6" t="s">
         <v>130</v>
       </c>
@@ -23556,7 +24619,7 @@
         <v>TS-UD-DOC-CLS-001test_022_clause_embedding_update</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="16.5" thickBot="1">
+    <row r="143" spans="1:11" ht="16.2" thickBot="1">
       <c r="A143" s="6" t="s">
         <v>131</v>
       </c>
@@ -23585,7 +24648,7 @@
         <v>TS-UD-DOC-CLS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="16.5" thickBot="1">
+    <row r="144" spans="1:11" ht="16.2" thickBot="1">
       <c r="A144" s="6" t="s">
         <v>132</v>
       </c>
@@ -23611,7 +24674,7 @@
         <v>TS-UD-DOC-CLS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="31.5" thickBot="1">
+    <row r="145" spans="1:11" ht="31.2" thickBot="1">
       <c r="A145" s="6" t="s">
         <v>133</v>
       </c>
@@ -23640,7 +24703,7 @@
         <v>TS-UD-DOC-ENT-001test_001_date_dd_mm_yyyy_slash</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="31.5" thickBot="1">
+    <row r="146" spans="1:11" ht="31.2" thickBot="1">
       <c r="A146" s="6" t="s">
         <v>133</v>
       </c>
@@ -23669,7 +24732,7 @@
         <v>TS-UD-DOC-ENT-001test_002_date_yyyy_mm_dd_dash</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="31.5" thickBot="1">
+    <row r="147" spans="1:11" ht="31.2" thickBot="1">
       <c r="A147" s="6" t="s">
         <v>133</v>
       </c>
@@ -23698,7 +24761,7 @@
         <v>TS-UD-DOC-ENT-001test_003_date_dd_month_yyyy_spanish</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="31.5" thickBot="1">
+    <row r="148" spans="1:11" ht="31.2" thickBot="1">
       <c r="A148" s="6" t="s">
         <v>133</v>
       </c>
@@ -23727,7 +24790,7 @@
         <v>TS-UD-DOC-ENT-001test_004_date_month_dd_yyyy_english</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="31.5" thickBot="1">
+    <row r="149" spans="1:11" ht="31.2" thickBot="1">
       <c r="A149" s="6" t="s">
         <v>133</v>
       </c>
@@ -23756,7 +24819,7 @@
         <v>TS-UD-DOC-ENT-001test_005_date_relative_30_days</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="31.5" thickBot="1">
+    <row r="150" spans="1:11" ht="31.2" thickBot="1">
       <c r="A150" s="6" t="s">
         <v>133</v>
       </c>
@@ -23785,7 +24848,7 @@
         <v>TS-UD-DOC-ENT-001test_006_date_relative_3_months</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="31.5" thickBot="1">
+    <row r="151" spans="1:11" ht="31.2" thickBot="1">
       <c r="A151" s="6" t="s">
         <v>133</v>
       </c>
@@ -23814,7 +24877,7 @@
         <v>TS-UD-DOC-ENT-001test_007_date_relative_1_year</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="31.5" thickBot="1">
+    <row r="152" spans="1:11" ht="31.2" thickBot="1">
       <c r="A152" s="6" t="s">
         <v>133</v>
       </c>
@@ -23843,7 +24906,7 @@
         <v>TS-UD-DOC-ENT-001test_008_date_relative_from_date</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="31.5" thickBot="1">
+    <row r="153" spans="1:11" ht="31.2" thickBot="1">
       <c r="A153" s="6" t="s">
         <v>133</v>
       </c>
@@ -23872,7 +24935,7 @@
         <v>TS-UD-DOC-ENT-001test_009_date_context_entrega</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="31.5" thickBot="1">
+    <row r="154" spans="1:11" ht="31.2" thickBot="1">
       <c r="A154" s="6" t="s">
         <v>133</v>
       </c>
@@ -23901,7 +24964,7 @@
         <v>TS-UD-DOC-ENT-001test_010_date_context_firma</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="31.5" thickBot="1">
+    <row r="155" spans="1:11" ht="31.2" thickBot="1">
       <c r="A155" s="6" t="s">
         <v>133</v>
       </c>
@@ -23930,7 +24993,7 @@
         <v>TS-UD-DOC-ENT-001test_011_date_context_inicio</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="16.5" thickBot="1">
+    <row r="156" spans="1:11" ht="16.2" thickBot="1">
       <c r="A156" s="6" t="s">
         <v>133</v>
       </c>
@@ -23959,7 +25022,7 @@
         <v>TS-UD-DOC-ENT-001test_012_date_context_fin</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="31.5" thickBot="1">
+    <row r="157" spans="1:11" ht="31.2" thickBot="1">
       <c r="A157" s="6" t="s">
         <v>133</v>
       </c>
@@ -23988,7 +25051,7 @@
         <v>TS-UD-DOC-ENT-001test_013_multiple_dates_extraction</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="31.5" thickBot="1">
+    <row r="158" spans="1:11" ht="31.2" thickBot="1">
       <c r="A158" s="6" t="s">
         <v>133</v>
       </c>
@@ -24017,7 +25080,7 @@
         <v>TS-UD-DOC-ENT-001test_014_multiple_dates_ordering</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="31.5" thickBot="1">
+    <row r="159" spans="1:11" ht="31.2" thickBot="1">
       <c r="A159" s="6" t="s">
         <v>133</v>
       </c>
@@ -24046,7 +25109,7 @@
         <v>TS-UD-DOC-ENT-001test_015_date_range_extraction</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="31.5" thickBot="1">
+    <row r="160" spans="1:11" ht="31.2" thickBot="1">
       <c r="A160" s="6" t="s">
         <v>133</v>
       </c>
@@ -24075,7 +25138,7 @@
         <v>TS-UD-DOC-ENT-001test_016_date_invalid_format_ignored</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="31.5" thickBot="1">
+    <row r="161" spans="1:11" ht="31.2" thickBot="1">
       <c r="A161" s="6" t="s">
         <v>134</v>
       </c>
@@ -24104,7 +25167,7 @@
         <v>TS-UD-DOC-ENT-002test_001_money_eur_symbol_suffix</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="31.5" thickBot="1">
+    <row r="162" spans="1:11" ht="31.2" thickBot="1">
       <c r="A162" s="6" t="s">
         <v>134</v>
       </c>
@@ -24133,7 +25196,7 @@
         <v>TS-UD-DOC-ENT-002test_002_money_eur_symbol_prefix</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="31.5" thickBot="1">
+    <row r="163" spans="1:11" ht="31.2" thickBot="1">
       <c r="A163" s="6" t="s">
         <v>134</v>
       </c>
@@ -24162,7 +25225,7 @@
         <v>TS-UD-DOC-ENT-002test_003_money_eur_word_euros</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="31.5" thickBot="1">
+    <row r="164" spans="1:11" ht="31.2" thickBot="1">
       <c r="A164" s="6" t="s">
         <v>134</v>
       </c>
@@ -24191,7 +25254,7 @@
         <v>TS-UD-DOC-ENT-002test_004_money_eur_thousands_separator</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="31.5" thickBot="1">
+    <row r="165" spans="1:11" ht="31.2" thickBot="1">
       <c r="A165" s="6" t="s">
         <v>134</v>
       </c>
@@ -24220,7 +25283,7 @@
         <v>TS-UD-DOC-ENT-002test_005_money_usd_symbol</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="31.5" thickBot="1">
+    <row r="166" spans="1:11" ht="16.2" thickBot="1">
       <c r="A166" s="6" t="s">
         <v>134</v>
       </c>
@@ -24249,7 +25312,7 @@
         <v>TS-UD-DOC-ENT-002test_006_money_usd_word</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="31.5" thickBot="1">
+    <row r="167" spans="1:11" ht="31.2" thickBot="1">
       <c r="A167" s="6" t="s">
         <v>134</v>
       </c>
@@ -24278,7 +25341,7 @@
         <v>TS-UD-DOC-ENT-002test_007_money_usd_thousands_separator</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="31.5" thickBot="1">
+    <row r="168" spans="1:11" ht="31.2" thickBot="1">
       <c r="A168" s="6" t="s">
         <v>134</v>
       </c>
@@ -24307,7 +25370,7 @@
         <v>TS-UD-DOC-ENT-002test_008_money_context_anticipo</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="31.5" thickBot="1">
+    <row r="169" spans="1:11" ht="31.2" thickBot="1">
       <c r="A169" s="6" t="s">
         <v>134</v>
       </c>
@@ -24336,7 +25399,7 @@
         <v>TS-UD-DOC-ENT-002test_009_money_context_pago_final</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="31.5" thickBot="1">
+    <row r="170" spans="1:11" ht="31.2" thickBot="1">
       <c r="A170" s="6" t="s">
         <v>134</v>
       </c>
@@ -24365,7 +25428,7 @@
         <v>TS-UD-DOC-ENT-002test_010_money_context_penalizacion</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="31.5" thickBot="1">
+    <row r="171" spans="1:11" ht="31.2" thickBot="1">
       <c r="A171" s="6" t="s">
         <v>134</v>
       </c>
@@ -24394,7 +25457,7 @@
         <v>TS-UD-DOC-ENT-002test_011_money_context_total</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="31.5" thickBot="1">
+    <row r="172" spans="1:11" ht="31.2" thickBot="1">
       <c r="A172" s="6" t="s">
         <v>134</v>
       </c>
@@ -24423,7 +25486,7 @@
         <v>TS-UD-DOC-ENT-002test_012_multiple_amounts_extraction</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="31.5" thickBot="1">
+    <row r="173" spans="1:11" ht="31.2" thickBot="1">
       <c r="A173" s="6" t="s">
         <v>134</v>
       </c>
@@ -24452,7 +25515,7 @@
         <v>TS-UD-DOC-ENT-002test_013_money_percentage_extraction</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="31.5" thickBot="1">
+    <row r="174" spans="1:11" ht="31.2" thickBot="1">
       <c r="A174" s="6" t="s">
         <v>134</v>
       </c>
@@ -24481,7 +25544,7 @@
         <v>TS-UD-DOC-ENT-002test_014_money_negative_amount</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="16.5" thickBot="1">
+    <row r="175" spans="1:11" ht="16.2" thickBot="1">
       <c r="A175" s="6" t="s">
         <v>135</v>
       </c>
@@ -24502,7 +25565,7 @@
         <v>TS-UD-DOC-ENT-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="16.5" thickBot="1">
+    <row r="176" spans="1:11" ht="16.2" thickBot="1">
       <c r="A176" s="6" t="s">
         <v>136</v>
       </c>
@@ -24523,7 +25586,7 @@
         <v>TS-UD-DOC-ENT-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="16.5" thickBot="1">
+    <row r="177" spans="1:11" ht="16.2" thickBot="1">
       <c r="A177" s="6" t="s">
         <v>137</v>
       </c>
@@ -24544,7 +25607,7 @@
         <v>TS-UD-DOC-DOC-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="16.5" thickBot="1">
+    <row r="178" spans="1:11" ht="16.2" thickBot="1">
       <c r="A178" s="6" t="s">
         <v>138</v>
       </c>
@@ -24565,7 +25628,7 @@
         <v>TS-UD-DOC-CNF-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="16.5" thickBot="1">
+    <row r="179" spans="1:11" ht="16.2" thickBot="1">
       <c r="A179" s="6" t="s">
         <v>139</v>
       </c>
@@ -24586,7 +25649,7 @@
         <v>TS-UD-COH-CAT-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="31.5" thickBot="1">
+    <row r="180" spans="1:11" ht="31.2" thickBot="1">
       <c r="A180" s="6" t="s">
         <v>140</v>
       </c>
@@ -24618,7 +25681,7 @@
         <v>TS-UD-COH-RUL-001test_001_r11_wbs_level4_no_activities_alert</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="31.5" thickBot="1">
+    <row r="181" spans="1:11" ht="31.2" thickBot="1">
       <c r="A181" s="6" t="s">
         <v>140</v>
       </c>
@@ -24647,7 +25710,7 @@
         <v>TS-UD-COH-RUL-001test_002_r11_wbs_level4_with_activities_pass</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="31.5" thickBot="1">
+    <row r="182" spans="1:11" ht="31.2" thickBot="1">
       <c r="A182" s="6" t="s">
         <v>140</v>
       </c>
@@ -24676,7 +25739,7 @@
         <v>TS-UD-COH-RUL-001test_003_r11_wbs_level3_no_activities_ignored</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="31.5" thickBot="1">
+    <row r="183" spans="1:11" ht="31.2" thickBot="1">
       <c r="A183" s="6" t="s">
         <v>140</v>
       </c>
@@ -24705,7 +25768,7 @@
         <v>TS-UD-COH-RUL-001test_004_r11_wbs_level2_no_activities_ignored</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="31.5" thickBot="1">
+    <row r="184" spans="1:11" ht="31.2" thickBot="1">
       <c r="A184" s="6" t="s">
         <v>140</v>
       </c>
@@ -24734,7 +25797,7 @@
         <v>TS-UD-COH-RUL-001test_005_r11_multiple_wbs_level4_violations</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="31.5" thickBot="1">
+    <row r="185" spans="1:11" ht="31.2" thickBot="1">
       <c r="A185" s="6" t="s">
         <v>140</v>
       </c>
@@ -24763,7 +25826,7 @@
         <v>TS-UD-COH-RUL-001test_006_r11_alert_severity_medium</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="31.5" thickBot="1">
+    <row r="186" spans="1:11" ht="31.2" thickBot="1">
       <c r="A186" s="6" t="s">
         <v>140</v>
       </c>
@@ -24792,7 +25855,7 @@
         <v>TS-UD-COH-RUL-001test_007_r12_wbs_no_budget_line_alert</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="31.5" thickBot="1">
+    <row r="187" spans="1:11" ht="31.2" thickBot="1">
       <c r="A187" s="6" t="s">
         <v>140</v>
       </c>
@@ -24821,7 +25884,7 @@
         <v>TS-UD-COH-RUL-001test_008_r12_wbs_with_budget_line_pass</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="31.5" thickBot="1">
+    <row r="188" spans="1:11" ht="31.2" thickBot="1">
       <c r="A188" s="6" t="s">
         <v>140</v>
       </c>
@@ -24850,7 +25913,7 @@
         <v>TS-UD-COH-RUL-001test_009_r12_wbs_budget_zero_warning</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="31.5" thickBot="1">
+    <row r="189" spans="1:11" ht="31.2" thickBot="1">
       <c r="A189" s="6" t="s">
         <v>140</v>
       </c>
@@ -24879,7 +25942,7 @@
         <v>TS-UD-COH-RUL-001test_010_r12_multiple_wbs_violations</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="31.5" thickBot="1">
+    <row r="190" spans="1:11" ht="31.2" thickBot="1">
       <c r="A190" s="6" t="s">
         <v>140</v>
       </c>
@@ -24908,7 +25971,7 @@
         <v>TS-UD-COH-RUL-001test_011_r12_alert_severity_high</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="31.5" thickBot="1">
+    <row r="191" spans="1:11" ht="31.2" thickBot="1">
       <c r="A191" s="6" t="s">
         <v>140</v>
       </c>
@@ -24937,7 +26000,7 @@
         <v>TS-UD-COH-RUL-001test_012_r12_affected_entities_list</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="31.5" thickBot="1">
+    <row r="192" spans="1:11" ht="31.2" thickBot="1">
       <c r="A192" s="6" t="s">
         <v>140</v>
       </c>
@@ -24966,7 +26029,7 @@
         <v>TS-UD-COH-RUL-001test_013_r13_scope_clause_no_wbs_alert</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="31.5" thickBot="1">
+    <row r="193" spans="1:11" ht="31.2" thickBot="1">
       <c r="A193" s="6" t="s">
         <v>140</v>
       </c>
@@ -24995,7 +26058,7 @@
         <v>TS-UD-COH-RUL-001test_014_r13_scope_clause_with_wbs_pass</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="31.5" thickBot="1">
+    <row r="194" spans="1:11" ht="31.2" thickBot="1">
       <c r="A194" s="6" t="s">
         <v>140</v>
       </c>
@@ -25024,7 +26087,7 @@
         <v>TS-UD-COH-RUL-001test_015_r13_partial_coverage_calculation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="31.5" thickBot="1">
+    <row r="195" spans="1:11" ht="31.2" thickBot="1">
       <c r="A195" s="6" t="s">
         <v>140</v>
       </c>
@@ -25053,7 +26116,7 @@
         <v>TS-UD-COH-RUL-001test_016_r13_coverage_percentage_80</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="31.5" thickBot="1">
+    <row r="196" spans="1:11" ht="31.2" thickBot="1">
       <c r="A196" s="6" t="s">
         <v>140</v>
       </c>
@@ -25082,7 +26145,7 @@
         <v>TS-UD-COH-RUL-001test_017_r13_uncovered_clauses_list</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="31.5" thickBot="1">
+    <row r="197" spans="1:11" ht="31.2" thickBot="1">
       <c r="A197" s="6" t="s">
         <v>140</v>
       </c>
@@ -25111,7 +26174,7 @@
         <v>TS-UD-COH-RUL-001test_018_r13_alert_severity_high</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="31.5" thickBot="1">
+    <row r="198" spans="1:11" ht="31.2" thickBot="1">
       <c r="A198" s="6" t="s">
         <v>141</v>
       </c>
@@ -25140,7 +26203,7 @@
         <v>TS-UD-COH-RUL-002test_001_r6_deviation_10_percent_alert</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="31.5" thickBot="1">
+    <row r="199" spans="1:11" ht="31.2" thickBot="1">
       <c r="A199" s="6" t="s">
         <v>141</v>
       </c>
@@ -25169,7 +26232,7 @@
         <v>TS-UD-COH-RUL-002test_002_r6_deviation_5_percent_pass</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="31.5" thickBot="1">
+    <row r="200" spans="1:11" ht="31.2" thickBot="1">
       <c r="A200" s="6" t="s">
         <v>141</v>
       </c>
@@ -25198,7 +26261,7 @@
         <v>TS-UD-COH-RUL-002test_003_r6_deviation_4_9_percent_pass</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="31.5" thickBot="1">
+    <row r="201" spans="1:11" ht="31.2" thickBot="1">
       <c r="A201" s="6" t="s">
         <v>141</v>
       </c>
@@ -25227,7 +26290,7 @@
         <v>TS-UD-COH-RUL-002test_004_r6_over_budget_critical</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="31.5" thickBot="1">
+    <row r="202" spans="1:11" ht="31.2" thickBot="1">
       <c r="A202" s="6" t="s">
         <v>141</v>
       </c>
@@ -25256,7 +26319,7 @@
         <v>TS-UD-COH-RUL-002test_005_r6_under_budget_warning</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="31.5" thickBot="1">
+    <row r="203" spans="1:11" ht="31.2" thickBot="1">
       <c r="A203" s="6" t="s">
         <v>141</v>
       </c>
@@ -25285,7 +26348,7 @@
         <v>TS-UD-COH-RUL-002test_006_r6_exact_match_pass</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="31.5" thickBot="1">
+    <row r="204" spans="1:11" ht="31.2" thickBot="1">
       <c r="A204" s="6" t="s">
         <v>141</v>
       </c>
@@ -25314,7 +26377,7 @@
         <v>TS-UD-COH-RUL-002test_007_r15_bom_no_budget_alert</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="31.5" thickBot="1">
+    <row r="205" spans="1:11" ht="31.2" thickBot="1">
       <c r="A205" s="6" t="s">
         <v>141</v>
       </c>
@@ -25343,7 +26406,7 @@
         <v>TS-UD-COH-RUL-002test_008_r15_bom_with_budget_pass</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="31.5" thickBot="1">
+    <row r="206" spans="1:11" ht="31.2" thickBot="1">
       <c r="A206" s="6" t="s">
         <v>141</v>
       </c>
@@ -25372,7 +26435,7 @@
         <v>TS-UD-COH-RUL-002test_009_r15_bom_client_provided_exception</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="31.5" thickBot="1">
+    <row r="207" spans="1:11" ht="31.2" thickBot="1">
       <c r="A207" s="6" t="s">
         <v>141</v>
       </c>
@@ -25401,7 +26464,7 @@
         <v>TS-UD-COH-RUL-002test_010_r15_multiple_bom_violations</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="31.5" thickBot="1">
+    <row r="208" spans="1:11" ht="31.2" thickBot="1">
       <c r="A208" s="6" t="s">
         <v>141</v>
       </c>
@@ -25430,7 +26493,7 @@
         <v>TS-UD-COH-RUL-002test_011_r15_affected_items_list</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="31.5" thickBot="1">
+    <row r="209" spans="1:11" ht="31.2" thickBot="1">
       <c r="A209" s="6" t="s">
         <v>141</v>
       </c>
@@ -25459,7 +26522,7 @@
         <v>TS-UD-COH-RUL-002test_012_r16_deviation_11_percent_alert</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="31.5" thickBot="1">
+    <row r="210" spans="1:11" ht="31.2" thickBot="1">
       <c r="A210" s="6" t="s">
         <v>141</v>
       </c>
@@ -25488,7 +26551,7 @@
         <v>TS-UD-COH-RUL-002test_013_r16_deviation_10_percent_pass</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="31.5" thickBot="1">
+    <row r="211" spans="1:11" ht="31.2" thickBot="1">
       <c r="A211" s="6" t="s">
         <v>141</v>
       </c>
@@ -25517,7 +26580,7 @@
         <v>TS-UD-COH-RUL-002test_014_r16_over_budget_critical</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="31.5" thickBot="1">
+    <row r="212" spans="1:11" ht="31.2" thickBot="1">
       <c r="A212" s="6" t="s">
         <v>141</v>
       </c>
@@ -25546,7 +26609,7 @@
         <v>TS-UD-COH-RUL-002test_015_r16_under_budget_different_severity</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="31.5" thickBot="1">
+    <row r="213" spans="1:11" ht="31.2" thickBot="1">
       <c r="A213" s="6" t="s">
         <v>141</v>
       </c>
@@ -25575,7 +26638,7 @@
         <v>TS-UD-COH-RUL-002test_016_r16_trend_calculation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="31.5" thickBot="1">
+    <row r="214" spans="1:11" ht="31.2" thickBot="1">
       <c r="A214" s="6" t="s">
         <v>142</v>
       </c>
@@ -25607,7 +26670,7 @@
         <v>TS-UD-COH-RUL-003test_001_r1_dates_mismatch_alert</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="31.5" thickBot="1">
+    <row r="215" spans="1:11" ht="31.2" thickBot="1">
       <c r="A215" s="6" t="s">
         <v>142</v>
       </c>
@@ -25636,7 +26699,7 @@
         <v>TS-UD-COH-RUL-003test_002_r1_dates_match_pass</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="31.5" thickBot="1">
+    <row r="216" spans="1:11" ht="31.2" thickBot="1">
       <c r="A216" s="6" t="s">
         <v>142</v>
       </c>
@@ -25665,7 +26728,7 @@
         <v>TS-UD-COH-RUL-003test_003_r1_schedule_late_critical</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="31.5" thickBot="1">
+    <row r="217" spans="1:11" ht="31.2" thickBot="1">
       <c r="A217" s="6" t="s">
         <v>142</v>
       </c>
@@ -25694,7 +26757,7 @@
         <v>TS-UD-COH-RUL-003test_004_r1_schedule_early_warning</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="31.5" thickBot="1">
+    <row r="218" spans="1:11" ht="31.2" thickBot="1">
       <c r="A218" s="6" t="s">
         <v>142</v>
       </c>
@@ -25723,7 +26786,7 @@
         <v>TS-UD-COH-RUL-003test_005_r1_delta_days_calculation</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="31.5" thickBot="1">
+    <row r="219" spans="1:11" ht="31.2" thickBot="1">
       <c r="A219" s="6" t="s">
         <v>142</v>
       </c>
@@ -25752,7 +26815,7 @@
         <v>TS-UD-COH-RUL-003test_006_r2_milestone_no_activity_alert</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="31.5" thickBot="1">
+    <row r="220" spans="1:11" ht="31.2" thickBot="1">
       <c r="A220" s="6" t="s">
         <v>142</v>
       </c>
@@ -25781,7 +26844,7 @@
         <v>TS-UD-COH-RUL-003test_007_r2_milestone_with_activity_pass</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="31.5" thickBot="1">
+    <row r="221" spans="1:11" ht="31.2" thickBot="1">
       <c r="A221" s="6" t="s">
         <v>142</v>
       </c>
@@ -25810,7 +26873,7 @@
         <v>TS-UD-COH-RUL-003test_008_r2_milestone_date_mismatch_alert</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="31.5" thickBot="1">
+    <row r="222" spans="1:11" ht="31.2" thickBot="1">
       <c r="A222" s="6" t="s">
         <v>142</v>
       </c>
@@ -25839,7 +26902,7 @@
         <v>TS-UD-COH-RUL-003test_009_r2_multiple_milestones_violations</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="31.5" thickBot="1">
+    <row r="223" spans="1:11" ht="31.2" thickBot="1">
       <c r="A223" s="6" t="s">
         <v>142</v>
       </c>
@@ -25868,7 +26931,7 @@
         <v>TS-UD-COH-RUL-003test_010_r2_unlinked_milestones_list</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="31.5" thickBot="1">
+    <row r="224" spans="1:11" ht="31.2" thickBot="1">
       <c r="A224" s="6" t="s">
         <v>142</v>
       </c>
@@ -25897,7 +26960,7 @@
         <v>TS-UD-COH-RUL-003test_011_r5_activity_exceeds_contract_alert</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="31.5" thickBot="1">
+    <row r="225" spans="1:11" ht="31.2" thickBot="1">
       <c r="A225" s="6" t="s">
         <v>142</v>
       </c>
@@ -25926,7 +26989,7 @@
         <v>TS-UD-COH-RUL-003test_012_r5_activity_within_contract_pass</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="31.5" thickBot="1">
+    <row r="226" spans="1:11" ht="31.2" thickBot="1">
       <c r="A226" s="6" t="s">
         <v>142</v>
       </c>
@@ -25955,7 +27018,7 @@
         <v>TS-UD-COH-RUL-003test_013_r5_exceeding_activities_list</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="31.5" thickBot="1">
+    <row r="227" spans="1:11" ht="31.2" thickBot="1">
       <c r="A227" s="6" t="s">
         <v>142</v>
       </c>
@@ -25984,7 +27047,7 @@
         <v>TS-UD-COH-RUL-003test_014_r5_alert_severity_critical</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="31.5" thickBot="1">
+    <row r="228" spans="1:11" ht="31.2" thickBot="1">
       <c r="A228" s="6" t="s">
         <v>142</v>
       </c>
@@ -26013,7 +27076,7 @@
         <v>TS-UD-COH-RUL-003test_015_r14_order_date_passed_critical</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="31.5" thickBot="1">
+    <row r="229" spans="1:11" ht="31.2" thickBot="1">
       <c r="A229" s="6" t="s">
         <v>142</v>
       </c>
@@ -26042,7 +27105,7 @@
         <v>TS-UD-COH-RUL-003test_016_r14_order_date_tight_warning</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="16.5" thickBot="1">
+    <row r="230" spans="1:11" ht="16.2" thickBot="1">
       <c r="A230" s="6" t="s">
         <v>143</v>
       </c>
@@ -26063,7 +27126,7 @@
         <v>TS-UD-COH-RUL-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="16.5" thickBot="1">
+    <row r="231" spans="1:11" ht="16.2" thickBot="1">
       <c r="A231" s="6" t="s">
         <v>144</v>
       </c>
@@ -26084,7 +27147,7 @@
         <v>TS-UD-COH-RUL-005Tests not individually listed</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="16.5" thickBot="1">
+    <row r="232" spans="1:11" ht="16.2" thickBot="1">
       <c r="A232" s="6" t="s">
         <v>145</v>
       </c>
@@ -26105,7 +27168,7 @@
         <v>TS-UD-COH-RUL-006Tests not individually listed</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="31.5" thickBot="1">
+    <row r="233" spans="1:11" ht="31.2" thickBot="1">
       <c r="A233" s="6" t="s">
         <v>146</v>
       </c>
@@ -26137,7 +27200,7 @@
         <v>TS-UD-COH-SCR-001test_001_subscore_no_alerts_100_percent</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="31.5" thickBot="1">
+    <row r="234" spans="1:11" ht="31.2" thickBot="1">
       <c r="A234" s="6" t="s">
         <v>146</v>
       </c>
@@ -26166,7 +27229,7 @@
         <v>TS-UD-COH-SCR-001test_002_subscore_one_alert_penalized</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="31.5" thickBot="1">
+    <row r="235" spans="1:11" ht="31.2" thickBot="1">
       <c r="A235" s="6" t="s">
         <v>146</v>
       </c>
@@ -26195,7 +27258,7 @@
         <v>TS-UD-COH-SCR-001test_003_subscore_multiple_alerts_cumulative</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="31.5" thickBot="1">
+    <row r="236" spans="1:11" ht="31.2" thickBot="1">
       <c r="A236" s="6" t="s">
         <v>146</v>
       </c>
@@ -26224,7 +27287,7 @@
         <v>TS-UD-COH-SCR-001test_004_subscore_severity_low_penalty_5</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="31.5" thickBot="1">
+    <row r="237" spans="1:11" ht="31.2" thickBot="1">
       <c r="A237" s="6" t="s">
         <v>146</v>
       </c>
@@ -26253,7 +27316,7 @@
         <v>TS-UD-COH-SCR-001test_005_subscore_severity_medium_penalty_10</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="31.5" thickBot="1">
+    <row r="238" spans="1:11" ht="31.2" thickBot="1">
       <c r="A238" s="6" t="s">
         <v>146</v>
       </c>
@@ -26282,7 +27345,7 @@
         <v>TS-UD-COH-SCR-001test_006_subscore_severity_high_penalty_20</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="31.5" thickBot="1">
+    <row r="239" spans="1:11" ht="31.2" thickBot="1">
       <c r="A239" s="6" t="s">
         <v>146</v>
       </c>
@@ -26311,7 +27374,7 @@
         <v>TS-UD-COH-SCR-001test_007_subscore_severity_critical_penalty_30</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="31.5" thickBot="1">
+    <row r="240" spans="1:11" ht="31.2" thickBot="1">
       <c r="A240" s="6" t="s">
         <v>146</v>
       </c>
@@ -26340,7 +27403,7 @@
         <v>TS-UD-COH-SCR-001test_008_subscore_scope_calculation</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="31.5" thickBot="1">
+    <row r="241" spans="1:11" ht="31.2" thickBot="1">
       <c r="A241" s="6" t="s">
         <v>146</v>
       </c>
@@ -26369,7 +27432,7 @@
         <v>TS-UD-COH-SCR-001test_009_subscore_budget_calculation</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="31.5" thickBot="1">
+    <row r="242" spans="1:11" ht="31.2" thickBot="1">
       <c r="A242" s="6" t="s">
         <v>146</v>
       </c>
@@ -26398,7 +27461,7 @@
         <v>TS-UD-COH-SCR-001test_010_subscore_quality_calculation</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="31.5" thickBot="1">
+    <row r="243" spans="1:11" ht="31.2" thickBot="1">
       <c r="A243" s="6" t="s">
         <v>146</v>
       </c>
@@ -26427,7 +27490,7 @@
         <v>TS-UD-COH-SCR-001test_011_subscore_technical_calculation</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="31.5" thickBot="1">
+    <row r="244" spans="1:11" ht="31.2" thickBot="1">
       <c r="A244" s="6" t="s">
         <v>146</v>
       </c>
@@ -26456,7 +27519,7 @@
         <v>TS-UD-COH-SCR-001test_012_subscore_legal_calculation</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="31.5" thickBot="1">
+    <row r="245" spans="1:11" ht="31.2" thickBot="1">
       <c r="A245" s="6" t="s">
         <v>146</v>
       </c>
@@ -26485,7 +27548,7 @@
         <v>TS-UD-COH-SCR-001test_013_subscore_time_calculation</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="31.5" thickBot="1">
+    <row r="246" spans="1:11" ht="31.2" thickBot="1">
       <c r="A246" s="6" t="s">
         <v>146</v>
       </c>
@@ -26514,7 +27577,7 @@
         <v>TS-UD-COH-SCR-001test_014_subscore_floor_at_zero</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="31.5" thickBot="1">
+    <row r="247" spans="1:11" ht="31.2" thickBot="1">
       <c r="A247" s="6" t="s">
         <v>147</v>
       </c>
@@ -26543,7 +27606,7 @@
         <v>TS-UD-COH-SCR-002test_001_global_score_formula_verification</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="31.5" thickBot="1">
+    <row r="248" spans="1:11" ht="31.2" thickBot="1">
       <c r="A248" s="6" t="s">
         <v>147</v>
       </c>
@@ -26572,7 +27635,7 @@
         <v>TS-UD-COH-SCR-002test_002_global_score_default_weights</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="31.5" thickBot="1">
+    <row r="249" spans="1:11" ht="31.2" thickBot="1">
       <c r="A249" s="6" t="s">
         <v>147</v>
       </c>
@@ -26601,7 +27664,7 @@
         <v>TS-UD-COH-SCR-002test_003_global_score_all_100_equals_100</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="31.5" thickBot="1">
+    <row r="250" spans="1:11" ht="31.2" thickBot="1">
       <c r="A250" s="6" t="s">
         <v>147</v>
       </c>
@@ -26630,7 +27693,7 @@
         <v>TS-UD-COH-SCR-002test_004_global_score_all_0_equals_0</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="31.5" thickBot="1">
+    <row r="251" spans="1:11" ht="31.2" thickBot="1">
       <c r="A251" s="6" t="s">
         <v>147</v>
       </c>
@@ -26659,7 +27722,7 @@
         <v>TS-UD-COH-SCR-002test_005_global_score_mixed_subscores</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="31.5" thickBot="1">
+    <row r="252" spans="1:11" ht="31.2" thickBot="1">
       <c r="A252" s="6" t="s">
         <v>147</v>
       </c>
@@ -26688,7 +27751,7 @@
         <v>TS-UD-COH-SCR-002test_006_global_score_range_0_to_100</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="31.5" thickBot="1">
+    <row r="253" spans="1:11" ht="31.2" thickBot="1">
       <c r="A253" s="6" t="s">
         <v>147</v>
       </c>
@@ -26717,7 +27780,7 @@
         <v>TS-UD-COH-SCR-002test_007_weights_sum_validation</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="31.5" thickBot="1">
+    <row r="254" spans="1:11" ht="31.2" thickBot="1">
       <c r="A254" s="6" t="s">
         <v>147</v>
       </c>
@@ -26746,7 +27809,7 @@
         <v>TS-UD-COH-SCR-002test_008_weights_normalization_auto</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="31.5" thickBot="1">
+    <row r="255" spans="1:11" ht="31.2" thickBot="1">
       <c r="A255" s="6" t="s">
         <v>147</v>
       </c>
@@ -26775,7 +27838,7 @@
         <v>TS-UD-COH-SCR-002test_009_weights_custom_budget_30</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="31.5" thickBot="1">
+    <row r="256" spans="1:11" ht="31.2" thickBot="1">
       <c r="A256" s="6" t="s">
         <v>147</v>
       </c>
@@ -26804,7 +27867,7 @@
         <v>TS-UD-COH-SCR-002test_010_weights_custom_time_25</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="31.5" thickBot="1">
+    <row r="257" spans="1:11" ht="31.2" thickBot="1">
       <c r="A257" s="6" t="s">
         <v>147</v>
       </c>
@@ -26833,7 +27896,7 @@
         <v>TS-UD-COH-SCR-002test_011_weights_per_project_type</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="31.5" thickBot="1">
+    <row r="258" spans="1:11" ht="31.2" thickBot="1">
       <c r="A258" s="6" t="s">
         <v>147</v>
       </c>
@@ -26862,7 +27925,7 @@
         <v>TS-UD-COH-SCR-002test_012_weights_history_tracking</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="16.5" thickBot="1">
+    <row r="259" spans="1:11" ht="16.2" thickBot="1">
       <c r="A259" s="6" t="s">
         <v>148</v>
       </c>
@@ -26879,7 +27942,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="31.5" thickBot="1">
+    <row r="260" spans="1:11" ht="31.2" thickBot="1">
       <c r="A260" s="6" t="s">
         <v>149</v>
       </c>
@@ -26908,7 +27971,7 @@
         <v>TS-UD-COH-GAM-001test_001_detect_mass_changes_15_in_30min</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="31.5" thickBot="1">
+    <row r="261" spans="1:11" ht="31.2" thickBot="1">
       <c r="A261" s="6" t="s">
         <v>149</v>
       </c>
@@ -26937,7 +28000,7 @@
         <v>TS-UD-COH-GAM-001test_002_no_violation_10_in_60min</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="31.5" thickBot="1">
+    <row r="262" spans="1:11" ht="31.2" thickBot="1">
       <c r="A262" s="6" t="s">
         <v>149</v>
       </c>
@@ -26966,7 +28029,7 @@
         <v>TS-UD-COH-GAM-001test_003_mass_changes_window_sliding</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="31.5" thickBot="1">
+    <row r="263" spans="1:11" ht="31.2" thickBot="1">
       <c r="A263" s="6" t="s">
         <v>149</v>
       </c>
@@ -26995,7 +28058,7 @@
         <v>TS-UD-COH-GAM-001test_004_mass_changes_flag_for_review</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="31.5" thickBot="1">
+    <row r="264" spans="1:11" ht="31.2" thickBot="1">
       <c r="A264" s="6" t="s">
         <v>149</v>
       </c>
@@ -27024,7 +28087,7 @@
         <v>TS-UD-COH-GAM-001test_005_detect_resolve_reintroduce_4_times</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="31.5" thickBot="1">
+    <row r="265" spans="1:11" ht="31.2" thickBot="1">
       <c r="A265" s="6" t="s">
         <v>149</v>
       </c>
@@ -27053,7 +28116,7 @@
         <v>TS-UD-COH-GAM-001test_006_no_violation_2_times</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="31.5" thickBot="1">
+    <row r="266" spans="1:11" ht="31.2" thickBot="1">
       <c r="A266" s="6" t="s">
         <v>149</v>
       </c>
@@ -27082,7 +28145,7 @@
         <v>TS-UD-COH-GAM-001test_007_hash_comparison_same_content</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="31.5" thickBot="1">
+    <row r="267" spans="1:11" ht="31.2" thickBot="1">
       <c r="A267" s="6" t="s">
         <v>149</v>
       </c>
@@ -27111,7 +28174,7 @@
         <v>TS-UD-COH-GAM-001test_008_penalty_minus_5_points</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="31.5" thickBot="1">
+    <row r="268" spans="1:11" ht="31.2" thickBot="1">
       <c r="A268" s="6" t="s">
         <v>149</v>
       </c>
@@ -27140,7 +28203,7 @@
         <v>TS-UD-COH-GAM-001test_009_detect_95_percent_3_docs</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="31.5" thickBot="1">
+    <row r="269" spans="1:11" ht="31.2" thickBot="1">
       <c r="A269" s="6" t="s">
         <v>149</v>
       </c>
@@ -27169,7 +28232,7 @@
         <v>TS-UD-COH-GAM-001test_010_no_violation_95_percent_50_docs</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="31.5" thickBot="1">
+    <row r="270" spans="1:11" ht="31.2" thickBot="1">
       <c r="A270" s="6" t="s">
         <v>149</v>
       </c>
@@ -27198,7 +28261,7 @@
         <v>TS-UD-COH-GAM-001test_011_threshold_90_percent_5_docs</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="31.5" thickBot="1">
+    <row r="271" spans="1:11" ht="31.2" thickBot="1">
       <c r="A271" s="6" t="s">
         <v>149</v>
       </c>
@@ -27227,7 +28290,7 @@
         <v>TS-UD-COH-GAM-001test_012_require_audit_action</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="31.5" thickBot="1">
+    <row r="272" spans="1:11" ht="31.2" thickBot="1">
       <c r="A272" s="6" t="s">
         <v>149</v>
       </c>
@@ -27256,7 +28319,7 @@
         <v>TS-UD-COH-GAM-001test_013_detect_weight_change_25_percent</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="31.5" thickBot="1">
+    <row r="273" spans="1:11" ht="31.2" thickBot="1">
       <c r="A273" s="6" t="s">
         <v>149</v>
       </c>
@@ -27285,7 +28348,7 @@
         <v>TS-UD-COH-GAM-001test_014_no_violation_change_15_percent</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="31.5" thickBot="1">
+    <row r="274" spans="1:11" ht="31.2" thickBot="1">
       <c r="A274" s="6" t="s">
         <v>149</v>
       </c>
@@ -27314,7 +28377,7 @@
         <v>TS-UD-COH-GAM-001test_015_24h_window_tracking</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="31.5" thickBot="1">
+    <row r="275" spans="1:11" ht="31.2" thickBot="1">
       <c r="A275" s="6" t="s">
         <v>149</v>
       </c>
@@ -27343,7 +28406,7 @@
         <v>TS-UD-COH-GAM-001test_016_notify_admin_action</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="16.5" thickBot="1">
+    <row r="276" spans="1:11" ht="16.2" thickBot="1">
       <c r="A276" s="6" t="s">
         <v>150</v>
       </c>
@@ -27364,7 +28427,7 @@
         <v>TS-UD-COH-ALR-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="31.5" thickBot="1">
+    <row r="277" spans="1:11" ht="31.2" thickBot="1">
       <c r="A277" s="6" t="s">
         <v>151</v>
       </c>
@@ -27396,7 +28459,7 @@
         <v>TS-UD-PRJ-WBS-001test_001_wbs_item_creation_all_fields</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="31.5" thickBot="1">
+    <row r="278" spans="1:11" ht="31.2" thickBot="1">
       <c r="A278" s="6" t="s">
         <v>151</v>
       </c>
@@ -27425,7 +28488,7 @@
         <v>TS-UD-PRJ-WBS-001test_002_wbs_item_creation_minimum_fields</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="31.5" thickBot="1">
+    <row r="279" spans="1:11" ht="31.2" thickBot="1">
       <c r="A279" s="6" t="s">
         <v>151</v>
       </c>
@@ -27454,7 +28517,7 @@
         <v>TS-UD-PRJ-WBS-001test_003_wbs_item_fails_without_code</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="31.5" thickBot="1">
+    <row r="280" spans="1:11" ht="31.2" thickBot="1">
       <c r="A280" s="6" t="s">
         <v>151</v>
       </c>
@@ -27483,7 +28546,7 @@
         <v>TS-UD-PRJ-WBS-001test_004_wbs_item_fails_without_name</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="31.5" thickBot="1">
+    <row r="281" spans="1:11" ht="31.2" thickBot="1">
       <c r="A281" s="6" t="s">
         <v>151</v>
       </c>
@@ -27512,7 +28575,7 @@
         <v>TS-UD-PRJ-WBS-001test_005_wbs_item_fails_invalid_level</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="31.5" thickBot="1">
+    <row r="282" spans="1:11" ht="31.2" thickBot="1">
       <c r="A282" s="6" t="s">
         <v>151</v>
       </c>
@@ -27541,7 +28604,7 @@
         <v>TS-UD-PRJ-WBS-001test_006_wbs_item_immutability</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="31.5" thickBot="1">
+    <row r="283" spans="1:11" ht="31.2" thickBot="1">
       <c r="A283" s="6" t="s">
         <v>151</v>
       </c>
@@ -27570,7 +28633,7 @@
         <v>TS-UD-PRJ-WBS-001test_007_wbs_code_format_1</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="31.5" thickBot="1">
+    <row r="284" spans="1:11" ht="31.2" thickBot="1">
       <c r="A284" s="6" t="s">
         <v>151</v>
       </c>
@@ -27599,7 +28662,7 @@
         <v>TS-UD-PRJ-WBS-001test_008_wbs_code_format_1_1</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="31.5" thickBot="1">
+    <row r="285" spans="1:11" ht="31.2" thickBot="1">
       <c r="A285" s="6" t="s">
         <v>151</v>
       </c>
@@ -27628,7 +28691,7 @@
         <v>TS-UD-PRJ-WBS-001test_009_wbs_code_format_1_1_1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="31.5" thickBot="1">
+    <row r="286" spans="1:11" ht="31.2" thickBot="1">
       <c r="A286" s="6" t="s">
         <v>151</v>
       </c>
@@ -27657,7 +28720,7 @@
         <v>TS-UD-PRJ-WBS-001test_010_wbs_code_format_1_1_1_1</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="31.5" thickBot="1">
+    <row r="287" spans="1:11" ht="31.2" thickBot="1">
       <c r="A287" s="6" t="s">
         <v>151</v>
       </c>
@@ -27686,7 +28749,7 @@
         <v>TS-UD-PRJ-WBS-001test_011_wbs_code_invalid_format_rejected</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="31.5" thickBot="1">
+    <row r="288" spans="1:11" ht="31.2" thickBot="1">
       <c r="A288" s="6" t="s">
         <v>151</v>
       </c>
@@ -27715,7 +28778,7 @@
         <v>TS-UD-PRJ-WBS-001test_012_wbs_code_uniqueness_per_project</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="31.5" thickBot="1">
+    <row r="289" spans="1:11" ht="16.2" thickBot="1">
       <c r="A289" s="6" t="s">
         <v>151</v>
       </c>
@@ -27744,7 +28807,7 @@
         <v>TS-UD-PRJ-WBS-001test_013_wbs_level_1_valid</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="31.5" thickBot="1">
+    <row r="290" spans="1:11" ht="16.2" thickBot="1">
       <c r="A290" s="6" t="s">
         <v>151</v>
       </c>
@@ -27773,7 +28836,7 @@
         <v>TS-UD-PRJ-WBS-001test_014_wbs_level_4_valid</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="31.5" thickBot="1">
+    <row r="291" spans="1:11" ht="31.2" thickBot="1">
       <c r="A291" s="6" t="s">
         <v>151</v>
       </c>
@@ -27802,7 +28865,7 @@
         <v>TS-UD-PRJ-WBS-001test_015_wbs_level_0_invalid</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="31.5" thickBot="1">
+    <row r="292" spans="1:11" ht="31.2" thickBot="1">
       <c r="A292" s="6" t="s">
         <v>151</v>
       </c>
@@ -27831,7 +28894,7 @@
         <v>TS-UD-PRJ-WBS-001test_016_wbs_level_5_invalid</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="31.5" thickBot="1">
+    <row r="293" spans="1:11" ht="31.2" thickBot="1">
       <c r="A293" s="6" t="s">
         <v>151</v>
       </c>
@@ -27860,7 +28923,7 @@
         <v>TS-UD-PRJ-WBS-001test_017_wbs_level_matches_code_depth</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="31.5" thickBot="1">
+    <row r="294" spans="1:11" ht="31.2" thickBot="1">
       <c r="A294" s="6" t="s">
         <v>151</v>
       </c>
@@ -27889,7 +28952,7 @@
         <v>TS-UD-PRJ-WBS-001test_018_wbs_level_parent_child_validation</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="16.5" thickBot="1">
+    <row r="295" spans="1:11" ht="16.2" thickBot="1">
       <c r="A295" s="6" t="s">
         <v>152</v>
       </c>
@@ -27910,7 +28973,7 @@
         <v>TS-UD-PRJ-WBS-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="16.5" thickBot="1">
+    <row r="296" spans="1:11" ht="16.2" thickBot="1">
       <c r="A296" s="6" t="s">
         <v>153</v>
       </c>
@@ -27931,7 +28994,7 @@
         <v>TS-UD-PRJ-WBS-003Tests not individually listed</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="16.5" thickBot="1">
+    <row r="297" spans="1:11" ht="16.2" thickBot="1">
       <c r="A297" s="6" t="s">
         <v>154</v>
       </c>
@@ -27952,7 +29015,7 @@
         <v>TS-UD-PRJ-WBS-004Tests not individually listed</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="16.5" thickBot="1">
+    <row r="298" spans="1:11" ht="16.2" thickBot="1">
       <c r="A298" s="6" t="s">
         <v>155</v>
       </c>
@@ -27973,7 +29036,7 @@
         <v>TS-UD-PRJ-PRJ-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="16.5" thickBot="1">
+    <row r="299" spans="1:11" ht="16.2" thickBot="1">
       <c r="A299" s="6" t="s">
         <v>156</v>
       </c>
@@ -27994,7 +29057,7 @@
         <v>TS-UD-PRJ-DTO-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="16.5" thickBot="1">
+    <row r="300" spans="1:11" ht="16.2" thickBot="1">
       <c r="A300" s="6" t="s">
         <v>157</v>
       </c>
@@ -28015,7 +29078,7 @@
         <v>TS-UD-PROC-BOM-001Tests not individually listed</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="16.5" thickBot="1">
+    <row r="301" spans="1:11" ht="16.2" thickBot="1">
       <c r="A301" s="6" t="s">
         <v>158</v>
       </c>
@@ -28036,7 +29099,7 @@
         <v>TS-UD-PROC-BOM-002Tests not individually listed</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="31.5" thickBot="1">
+    <row r="302" spans="1:11" ht="31.2" thickBot="1">
       <c r="A302" s="6" t="s">
         <v>159</v>
       </c>
@@ -28068,7 +29131,7 @@
         <v>TS-UD-PROC-LTM-001test_001_optimal_date_production_only</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="31.5" thickBot="1">
+    <row r="303" spans="1:11" ht="31.2" thickBot="1">
       <c r="A303" s="6" t="s">
         <v>159</v>
       </c>
@@ -28097,7 +29160,7 @@
         <v>TS-UD-PROC-LTM-001test_002_optimal_date_production_transit</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="31.5" thickBot="1">
+    <row r="304" spans="1:11" ht="31.2" thickBot="1">
       <c r="A304" s="6" t="s">
         <v>159</v>
       </c>
@@ -28126,7 +29189,7 @@
         <v>TS-UD-PROC-LTM-001test_003_optimal_date_production_transit_buffer</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="31.5" thickBot="1">
+    <row r="305" spans="1:11" ht="31.2" thickBot="1">
       <c r="A305" s="6" t="s">
         <v>159</v>
       </c>
@@ -28155,7 +29218,7 @@
         <v>TS-UD-PROC-LTM-001test_004_optimal_date_all_components</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="31.5" thickBot="1">
+    <row r="306" spans="1:11" ht="31.2" thickBot="1">
       <c r="A306" s="6" t="s">
         <v>159</v>
       </c>
@@ -28184,7 +29247,7 @@
         <v>TS-UD-PROC-LTM-001test_005_lead_time_breakdown_returned</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="31.5" thickBot="1">
+    <row r="307" spans="1:11" ht="31.2" thickBot="1">
       <c r="A307" s="6" t="s">
         <v>159</v>
       </c>
@@ -28213,7 +29276,7 @@
         <v>TS-UD-PROC-LTM-001test_006_required_on_site_calculation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="31.5" thickBot="1">
+    <row r="308" spans="1:11" ht="31.2" thickBot="1">
       <c r="A308" s="6" t="s">
         <v>159</v>
       </c>
@@ -28242,7 +29305,7 @@
         <v>TS-UD-PROC-LTM-001test_007_business_days_calculation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="31.5" thickBot="1">
+    <row r="309" spans="1:11" ht="31.2" thickBot="1">
       <c r="A309" s="6" t="s">
         <v>159</v>
       </c>
@@ -28271,7 +29334,7 @@
         <v>TS-UD-PROC-LTM-001test_008_weekend_exclusion</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="16.5" thickBot="1">
+    <row r="310" spans="1:11" ht="16.2" thickBot="1">
       <c r="A310" s="6" t="s">
         <v>159</v>
       </c>
@@ -28300,7 +29363,7 @@
         <v>TS-UD-PROC-LTM-001test_009_holiday_exclusion</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="31.5" thickBot="1">
+    <row r="311" spans="1:11" ht="31.2" thickBot="1">
       <c r="A311" s="6" t="s">
         <v>159</v>
       </c>
@@ -28329,7 +29392,7 @@
         <v>TS-UD-PROC-LTM-001test_010_delivery_on_weekend_adjusted</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="31.5" thickBot="1">
+    <row r="312" spans="1:11" ht="31.2" thickBot="1">
       <c r="A312" s="6" t="s">
         <v>159</v>
       </c>
@@ -28358,7 +29421,7 @@
         <v>TS-UD-PROC-LTM-001test_011_mixed_calendar_business_days</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="31.5" thickBot="1">
+    <row r="313" spans="1:11" ht="31.2" thickBot="1">
       <c r="A313" s="6" t="s">
         <v>159</v>
       </c>
@@ -28387,7 +29450,7 @@
         <v>TS-UD-PROC-LTM-001test_012_alert_r14_date_passed</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="31.5" thickBot="1">
+    <row r="314" spans="1:11" ht="31.2" thickBot="1">
       <c r="A314" s="6" t="s">
         <v>159</v>
       </c>
@@ -28416,7 +29479,7 @@
         <v>TS-UD-PROC-LTM-001test_013_alert_r14_tight_margin_3_days</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="31.5" thickBot="1">
+    <row r="315" spans="1:11" ht="31.2" thickBot="1">
       <c r="A315" s="6" t="s">
         <v>159</v>
       </c>
@@ -28445,7 +29508,7 @@
         <v>TS-UD-PROC-LTM-001test_014_alert_severity_critical_passed</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="31.5" thickBot="1">
+    <row r="316" spans="1:11" ht="31.2" thickBot="1">
       <c r="A316" s="6" t="s">
         <v>159</v>
       </c>
@@ -28474,7 +29537,7 @@
         <v>TS-UD-PROC-LTM-001test_015_alert_severity_warning_tight</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="31.5" thickBot="1">
+    <row r="317" spans="1:11" ht="31.2" thickBot="1">
       <c r="A317" s="6" t="s">
         <v>159</v>
       </c>
@@ -28503,7 +29566,7 @@
         <v>TS-UD-PROC-LTM-001test_016_no_alert_sufficient_margin</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="31.5" thickBot="1">
+    <row r="318" spans="1:11" ht="31.2" thickBot="1">
       <c r="A318" s="6" t="s">
         <v>160</v>
       </c>
@@ -28529,7 +29592,7 @@
         <v>TS-UD-PROC-LTM-002test_001_exw_buyer_full_responsibility</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="31.5" thickBot="1">
+    <row r="319" spans="1:11" ht="31.2" thickBot="1">
       <c r="A319" s="6" t="s">
         <v>160</v>
       </c>
@@ -28555,7 +29618,7 @@
         <v>TS-UD-PROC-LTM-002test_002_exw_transit_time_included</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="31.5" thickBot="1">
+    <row r="320" spans="1:11" ht="31.2" thickBot="1">
       <c r="A320" s="6" t="s">
         <v>160</v>
       </c>
@@ -28581,7 +29644,7 @@
         <v>TS-UD-PROC-LTM-002test_003_exw_customs_included</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="31.5" thickBot="1">
+    <row r="321" spans="1:11" ht="31.2" thickBot="1">
       <c r="A321" s="6" t="s">
         <v>160</v>
       </c>
@@ -28607,7 +29670,7 @@
         <v>TS-UD-PROC-LTM-002test_004_fob_shared_responsibility</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="31.5" thickBot="1">
+    <row r="322" spans="1:11" ht="31.2" thickBot="1">
       <c r="A322" s="6" t="s">
         <v>160</v>
       </c>
@@ -28633,7 +29696,7 @@
         <v>TS-UD-PROC-LTM-002test_005_fob_port_handover</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="31.5" thickBot="1">
+    <row r="323" spans="1:11" ht="31.2" thickBot="1">
       <c r="A323" s="6" t="s">
         <v>160</v>
       </c>
@@ -28659,7 +29722,7 @@
         <v>TS-UD-PROC-LTM-002test_006_fob_insurance_buyer</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="31.5" thickBot="1">
+    <row r="324" spans="1:11" ht="31.2" thickBot="1">
       <c r="A324" s="6" t="s">
         <v>160</v>
       </c>
@@ -28685,7 +29748,7 @@
         <v>TS-UD-PROC-LTM-002test_007_cif_seller_insurance</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="16.5" thickBot="1">
+    <row r="325" spans="1:11" ht="16.2" thickBot="1">
       <c r="A325" s="6" t="s">
         <v>160</v>
       </c>
@@ -28711,7 +29774,7 @@
         <v>TS-UD-PROC-LTM-002test_008_cif_port_to_port</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="31.5" thickBot="1">
+    <row r="326" spans="1:11" ht="31.2" thickBot="1">
       <c r="A326" s="6" t="s">
         <v>160</v>
       </c>
@@ -28737,7 +29800,7 @@
         <v>TS-UD-PROC-LTM-002test_009_cif_customs_buyer</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="31.5" thickBot="1">
+    <row r="327" spans="1:11" ht="31.2" thickBot="1">
       <c r="A327" s="6" t="s">
         <v>160</v>
       </c>
@@ -28763,7 +29826,7 @@
         <v>TS-UD-PROC-LTM-002test_010_ddp_seller_full_responsibility</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="31.5" thickBot="1">
+    <row r="328" spans="1:11" ht="31.2" thickBot="1">
       <c r="A328" s="6" t="s">
         <v>160</v>
       </c>
@@ -28789,7 +29852,7 @@
         <v>TS-UD-PROC-LTM-002test_011_ddp_no_customs_buyer</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="31.5" thickBot="1">
+    <row r="329" spans="1:11" ht="31.2" thickBot="1">
       <c r="A329" s="6" t="s">
         <v>160</v>
       </c>
@@ -28815,7 +29878,7 @@
         <v>TS-UD-PROC-LTM-002test_012_ddp_door_to_door</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="31.5" thickBot="1">
+    <row r="330" spans="1:11" ht="31.2" thickBot="1">
       <c r="A330" s="6" t="s">
         <v>160</v>
       </c>
@@ -28841,7 +29904,7 @@
         <v>TS-UD-PROC-LTM-002test_013_incoterm_comparison_same_route</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="31.5" thickBot="1">
+    <row r="331" spans="1:11" ht="31.2" thickBot="1">
       <c r="A331" s="6" t="s">
         <v>160</v>
       </c>
@@ -28867,7 +29930,7 @@
         <v>TS-UD-PROC-LTM-002test_014_incoterm_impact_on_lead_time</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="16.5" thickBot="1">
+    <row r="332" spans="1:11" ht="16.2" thickBot="1">
       <c r="A332" s="6" t="s">
         <v>161</v>
       </c>
@@ -28884,7 +29947,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="16.5" thickBot="1">
+    <row r="333" spans="1:11" ht="16.2" thickBot="1">
       <c r="A333" s="6" t="s">
         <v>162</v>
       </c>
@@ -28901,7 +29964,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="16.5" thickBot="1">
+    <row r="334" spans="1:11" ht="16.2" thickBot="1">
       <c r="A334" s="6" t="s">
         <v>163</v>
       </c>
@@ -28918,7 +29981,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="16.5" thickBot="1">
+    <row r="335" spans="1:11" ht="16.2" thickBot="1">
       <c r="A335" s="6" t="s">
         <v>164</v>
       </c>
@@ -28935,7 +29998,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="16.5" thickBot="1">
+    <row r="336" spans="1:11" ht="16.2" thickBot="1">
       <c r="A336" s="6" t="s">
         <v>165</v>
       </c>
@@ -28952,7 +30015,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="16.5" thickBot="1">
+    <row r="337" spans="1:10" ht="16.2" thickBot="1">
       <c r="A337" s="6" t="s">
         <v>166</v>
       </c>
@@ -28969,7 +30032,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="16.5" thickBot="1">
+    <row r="338" spans="1:10" ht="16.2" thickBot="1">
       <c r="A338" s="6" t="s">
         <v>167</v>
       </c>
@@ -28985,7 +30048,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="16.5" thickBot="1">
+    <row r="339" spans="1:10" ht="16.2" thickBot="1">
       <c r="A339" s="6" t="s">
         <v>168</v>
       </c>
@@ -29001,7 +30064,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="16.5" thickBot="1">
+    <row r="340" spans="1:10" ht="16.2" thickBot="1">
       <c r="A340" s="6" t="s">
         <v>169</v>
       </c>
@@ -29017,7 +30080,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="16.5" thickBot="1">
+    <row r="341" spans="1:10" ht="16.2" thickBot="1">
       <c r="A341" s="6" t="s">
         <v>170</v>
       </c>
@@ -29033,7 +30096,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="16.5" thickBot="1">
+    <row r="342" spans="1:10" ht="16.2" thickBot="1">
       <c r="A342" s="6" t="s">
         <v>171</v>
       </c>
@@ -29049,7 +30112,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="16.5" thickBot="1">
+    <row r="343" spans="1:10" ht="16.2" thickBot="1">
       <c r="A343" s="6" t="s">
         <v>172</v>
       </c>
@@ -29065,7 +30128,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="16.5" thickBot="1">
+    <row r="344" spans="1:10" ht="16.2" thickBot="1">
       <c r="A344" s="6" t="s">
         <v>173</v>
       </c>
@@ -29081,7 +30144,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="16.5" thickBot="1">
+    <row r="345" spans="1:10" ht="16.2" thickBot="1">
       <c r="A345" s="6" t="s">
         <v>174</v>
       </c>
@@ -29097,7 +30160,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="16.5" thickBot="1">
+    <row r="346" spans="1:10" ht="16.2" thickBot="1">
       <c r="A346" s="6" t="s">
         <v>175</v>
       </c>
@@ -29113,7 +30176,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="31.5" thickBot="1">
+    <row r="347" spans="1:10" ht="16.2" thickBot="1">
       <c r="A347" s="6" t="s">
         <v>176</v>
       </c>
@@ -29129,7 +30192,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="31.5" thickBot="1">
+    <row r="348" spans="1:10" ht="16.2" thickBot="1">
       <c r="A348" s="6" t="s">
         <v>177</v>
       </c>
@@ -29145,7 +30208,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="31.5" thickBot="1">
+    <row r="349" spans="1:10" ht="16.2" thickBot="1">
       <c r="A349" s="6" t="s">
         <v>178</v>
       </c>
@@ -29161,7 +30224,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="31.5" thickBot="1">
+    <row r="350" spans="1:10" ht="16.2" thickBot="1">
       <c r="A350" s="6" t="s">
         <v>179</v>
       </c>
@@ -29177,7 +30240,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="31.5" thickBot="1">
+    <row r="351" spans="1:10" ht="16.2" thickBot="1">
       <c r="A351" s="6" t="s">
         <v>180</v>
       </c>
@@ -29193,7 +30256,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="31.5" thickBot="1">
+    <row r="352" spans="1:10" ht="16.2" thickBot="1">
       <c r="A352" s="31" t="s">
         <v>181</v>
       </c>
@@ -29212,7 +30275,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="31.5" thickBot="1">
+    <row r="353" spans="1:10" ht="16.2" thickBot="1">
       <c r="A353" s="31" t="s">
         <v>182</v>
       </c>
@@ -29231,7 +30294,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="31.5" thickBot="1">
+    <row r="354" spans="1:10" ht="16.2" thickBot="1">
       <c r="A354" s="6" t="s">
         <v>183</v>
       </c>
@@ -29247,7 +30310,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="31.5" thickBot="1">
+    <row r="355" spans="1:10" ht="16.2" thickBot="1">
       <c r="A355" s="6" t="s">
         <v>184</v>
       </c>
@@ -29263,7 +30326,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="31.5" thickBot="1">
+    <row r="356" spans="1:10" ht="16.2" thickBot="1">
       <c r="A356" s="6" t="s">
         <v>185</v>
       </c>
@@ -29279,7 +30342,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="31.5" thickBot="1">
+    <row r="357" spans="1:10" ht="16.2" thickBot="1">
       <c r="A357" s="6" t="s">
         <v>186</v>
       </c>
@@ -29295,7 +30358,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="31.5" thickBot="1">
+    <row r="358" spans="1:10" ht="16.2" thickBot="1">
       <c r="A358" s="6" t="s">
         <v>187</v>
       </c>
@@ -29311,7 +30374,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="31.5" thickBot="1">
+    <row r="359" spans="1:10" ht="16.2" thickBot="1">
       <c r="A359" s="6" t="s">
         <v>188</v>
       </c>
@@ -29327,7 +30390,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="31.5" thickBot="1">
+    <row r="360" spans="1:10" ht="16.2" thickBot="1">
       <c r="A360" s="6" t="s">
         <v>189</v>
       </c>
@@ -29343,7 +30406,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="31.5" thickBot="1">
+    <row r="361" spans="1:10" ht="16.2" thickBot="1">
       <c r="A361" s="6" t="s">
         <v>190</v>
       </c>
@@ -29359,7 +30422,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="16.5" thickBot="1">
+    <row r="362" spans="1:10" ht="16.2" thickBot="1">
       <c r="A362" s="6" t="s">
         <v>191</v>
       </c>
@@ -29375,7 +30438,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="16.5" thickBot="1">
+    <row r="363" spans="1:10" ht="16.2" thickBot="1">
       <c r="A363" s="6" t="s">
         <v>192</v>
       </c>
@@ -29391,7 +30454,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="16.5" thickBot="1">
+    <row r="364" spans="1:10" ht="16.2" thickBot="1">
       <c r="A364" s="6" t="s">
         <v>193</v>
       </c>
@@ -29407,7 +30470,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="16.5" thickBot="1">
+    <row r="365" spans="1:10" ht="16.2" thickBot="1">
       <c r="A365" s="6" t="s">
         <v>194</v>
       </c>
@@ -29423,7 +30486,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="16.5" thickBot="1">
+    <row r="366" spans="1:10" ht="16.2" thickBot="1">
       <c r="A366" s="6" t="s">
         <v>195</v>
       </c>
@@ -29439,7 +30502,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="16.5" thickBot="1">
+    <row r="367" spans="1:10" ht="16.2" thickBot="1">
       <c r="A367" s="6" t="s">
         <v>196</v>
       </c>
@@ -29455,7 +30518,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="16.5" thickBot="1">
+    <row r="368" spans="1:10" ht="16.2" thickBot="1">
       <c r="A368" s="6" t="s">
         <v>197</v>
       </c>
@@ -29471,7 +30534,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="16.5" thickBot="1">
+    <row r="369" spans="1:10" ht="16.2" thickBot="1">
       <c r="A369" s="6" t="s">
         <v>198</v>
       </c>
@@ -29490,7 +30553,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="16.5" thickBot="1">
+    <row r="370" spans="1:10" ht="16.2" thickBot="1">
       <c r="A370" s="6" t="s">
         <v>199</v>
       </c>
@@ -29509,7 +30572,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="16.5" thickBot="1">
+    <row r="371" spans="1:10" ht="16.2" thickBot="1">
       <c r="A371" s="6" t="s">
         <v>200</v>
       </c>
@@ -29525,7 +30588,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="16.5" thickBot="1">
+    <row r="372" spans="1:10" ht="16.2" thickBot="1">
       <c r="A372" s="6" t="s">
         <v>201</v>
       </c>
@@ -29541,7 +30604,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="16.5" thickBot="1">
+    <row r="373" spans="1:10" ht="16.2" thickBot="1">
       <c r="A373" s="6" t="s">
         <v>202</v>
       </c>
@@ -29560,7 +30623,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="31.5" thickBot="1">
+    <row r="374" spans="1:10" ht="16.2" thickBot="1">
       <c r="A374" s="6" t="s">
         <v>203</v>
       </c>
@@ -29576,7 +30639,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="31.5" thickBot="1">
+    <row r="375" spans="1:10" ht="16.2" thickBot="1">
       <c r="A375" s="6" t="s">
         <v>204</v>
       </c>
@@ -29592,7 +30655,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="31.5" thickBot="1">
+    <row r="376" spans="1:10" ht="16.2" thickBot="1">
       <c r="A376" s="6" t="s">
         <v>205</v>
       </c>
@@ -29608,7 +30671,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="31.5" thickBot="1">
+    <row r="377" spans="1:10" ht="16.2" thickBot="1">
       <c r="A377" s="6" t="s">
         <v>206</v>
       </c>
@@ -29624,7 +30687,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="16.5" thickBot="1">
+    <row r="378" spans="1:10" ht="16.2" thickBot="1">
       <c r="A378" s="25" t="s">
         <v>207</v>
       </c>
@@ -29643,7 +30706,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="16.5" thickBot="1">
+    <row r="379" spans="1:10" ht="16.2" thickBot="1">
       <c r="A379" s="6" t="s">
         <v>208</v>
       </c>
@@ -29662,7 +30725,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="16.5" thickBot="1">
+    <row r="380" spans="1:10" ht="16.2" thickBot="1">
       <c r="A380" s="6" t="s">
         <v>209</v>
       </c>
@@ -29681,7 +30744,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="16.5" thickBot="1">
+    <row r="381" spans="1:10" ht="16.2" thickBot="1">
       <c r="A381" s="6" t="s">
         <v>210</v>
       </c>
@@ -29697,7 +30760,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="16.5" thickBot="1">
+    <row r="382" spans="1:10" ht="16.2" thickBot="1">
       <c r="A382" s="6" t="s">
         <v>211</v>
       </c>
@@ -29713,7 +30776,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="16.5" thickBot="1">
+    <row r="383" spans="1:10" ht="16.2" thickBot="1">
       <c r="A383" s="6" t="s">
         <v>212</v>
       </c>
@@ -29729,7 +30792,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="16.5" thickBot="1">
+    <row r="384" spans="1:10" ht="16.2" thickBot="1">
       <c r="A384" s="6" t="s">
         <v>213</v>
       </c>
@@ -29745,7 +30808,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="16.5" thickBot="1">
+    <row r="385" spans="1:10" ht="16.2" thickBot="1">
       <c r="A385" s="6" t="s">
         <v>214</v>
       </c>
@@ -29761,7 +30824,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="386" spans="1:10" ht="16.5" thickBot="1">
+    <row r="386" spans="1:10" ht="16.2" thickBot="1">
       <c r="A386" s="6" t="s">
         <v>215</v>
       </c>
@@ -29777,7 +30840,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="16.5" thickBot="1">
+    <row r="387" spans="1:10" ht="16.2" thickBot="1">
       <c r="A387" s="6" t="s">
         <v>216</v>
       </c>
@@ -29793,7 +30856,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="388" spans="1:10" ht="16.5" thickBot="1">
+    <row r="388" spans="1:10" ht="16.2" thickBot="1">
       <c r="A388" s="6" t="s">
         <v>217</v>
       </c>
@@ -29809,7 +30872,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="16.5" thickBot="1">
+    <row r="389" spans="1:10" ht="16.2" thickBot="1">
       <c r="A389" s="6" t="s">
         <v>218</v>
       </c>
@@ -29825,7 +30888,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="390" spans="1:10" ht="16.5" thickBot="1">
+    <row r="390" spans="1:10" ht="16.2" thickBot="1">
       <c r="A390" s="6" t="s">
         <v>219</v>
       </c>
@@ -29841,7 +30904,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="391" spans="1:10" ht="16.5" thickBot="1">
+    <row r="391" spans="1:10" ht="16.2" thickBot="1">
       <c r="A391" s="6" t="s">
         <v>220</v>
       </c>
@@ -29860,7 +30923,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="16.5" thickBot="1">
+    <row r="392" spans="1:10" ht="16.2" thickBot="1">
       <c r="A392" s="6" t="s">
         <v>221</v>
       </c>
@@ -29879,7 +30942,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="16.5" thickBot="1">
+    <row r="393" spans="1:10" ht="16.2" thickBot="1">
       <c r="A393" s="6" t="s">
         <v>222</v>
       </c>
@@ -29898,7 +30961,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="394" spans="1:10" ht="16.5" thickBot="1">
+    <row r="394" spans="1:10" ht="16.2" thickBot="1">
       <c r="A394" s="6" t="s">
         <v>223</v>
       </c>
@@ -29914,7 +30977,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="16.5" thickBot="1">
+    <row r="395" spans="1:10" ht="16.2" thickBot="1">
       <c r="A395" s="6" t="s">
         <v>224</v>
       </c>
@@ -29930,7 +30993,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="16.5" thickBot="1">
+    <row r="396" spans="1:10" ht="16.2" thickBot="1">
       <c r="A396" s="6" t="s">
         <v>225</v>
       </c>
@@ -29946,7 +31009,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="16.5" thickBot="1">
+    <row r="397" spans="1:10" ht="16.2" thickBot="1">
       <c r="A397" s="21" t="s">
         <v>226</v>
       </c>
@@ -29968,7 +31031,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="16.5" thickBot="1">
+    <row r="398" spans="1:10" ht="16.2" thickBot="1">
       <c r="A398" s="6" t="s">
         <v>227</v>
       </c>
@@ -29984,7 +31047,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="399" spans="1:10" ht="16.5" thickBot="1">
+    <row r="399" spans="1:10" ht="16.2" thickBot="1">
       <c r="A399" s="6" t="s">
         <v>228</v>
       </c>
@@ -30000,7 +31063,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="16.5" thickBot="1">
+    <row r="400" spans="1:10" ht="16.2" thickBot="1">
       <c r="A400" s="6" t="s">
         <v>229</v>
       </c>
@@ -30016,7 +31079,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="16.5" thickBot="1">
+    <row r="401" spans="1:6" ht="16.2" thickBot="1">
       <c r="A401" s="6" t="s">
         <v>230</v>
       </c>
@@ -30032,7 +31095,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="16.5" thickBot="1">
+    <row r="402" spans="1:6" ht="16.2" thickBot="1">
       <c r="A402" s="6" t="s">
         <v>231</v>
       </c>
@@ -30048,7 +31111,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="15.75" thickBot="1">
+    <row r="403" spans="1:6" ht="15" thickBot="1">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -30056,7 +31119,7 @@
       <c r="E403" s="5"/>
       <c r="F403" s="5"/>
     </row>
-    <row r="404" spans="1:6" ht="15.75" thickBot="1">
+    <row r="404" spans="1:6" ht="15" thickBot="1">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -30073,9 +31136,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9447E658-0406-4337-92E7-EF22271613D0}">
   <dimension ref="A1:I526"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="9" width="11.42578125" style="23"/>
+    <col min="1" max="9" width="11.44140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -32973,10 +34036,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7AC209-399B-46DE-A186-E777887E2AAF}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="91.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -34898,9 +35961,9 @@
   <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="45" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="178.85546875" customWidth="1"/>
+    <col min="2" max="2" width="66.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="178.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="45" customHeight="1">
@@ -34930,7 +35993,7 @@
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" spans="1:10" ht="14.45" customHeight="1">
+    <row r="3" spans="1:10" ht="14.4" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>834</v>
       </c>
@@ -34946,7 +36009,7 @@
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" spans="1:10" ht="14.45" customHeight="1">
+    <row r="4" spans="1:10" ht="14.4" customHeight="1">
       <c r="A4" s="27" t="s">
         <v>835</v>
       </c>
@@ -34962,7 +36025,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" customHeight="1">
+    <row r="5" spans="1:10" ht="14.4" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>836</v>
       </c>
@@ -34978,7 +36041,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" customHeight="1">
+    <row r="6" spans="1:10" ht="14.4" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>837</v>
       </c>
@@ -34994,7 +36057,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="1:10" ht="14.45" customHeight="1">
+    <row r="7" spans="1:10" ht="14.4" customHeight="1">
       <c r="A7" s="22" t="s">
         <v>838</v>
       </c>
@@ -35010,7 +36073,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10" ht="14.45" customHeight="1">
+    <row r="8" spans="1:10" ht="14.4" customHeight="1">
       <c r="A8" s="27" t="s">
         <v>839</v>
       </c>
@@ -35026,7 +36089,7 @@
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
     </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
+    <row r="9" spans="1:10" ht="14.4" customHeight="1">
       <c r="A9" s="22" t="s">
         <v>840</v>
       </c>
@@ -35042,7 +36105,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
     </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
+    <row r="10" spans="1:10" ht="14.4" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>841</v>
       </c>
@@ -35058,7 +36121,7 @@
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    <row r="11" spans="1:10" ht="14.4" customHeight="1">
       <c r="A11" s="22" t="s">
         <v>842</v>
       </c>
@@ -35074,7 +36137,7 @@
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
     </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    <row r="12" spans="1:10" ht="14.4" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>843</v>
       </c>
@@ -35090,7 +36153,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
     </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    <row r="13" spans="1:10" ht="14.4" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>844</v>
       </c>
@@ -35106,7 +36169,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    <row r="14" spans="1:10" ht="14.4" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>845</v>
       </c>
@@ -35122,7 +36185,7 @@
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
     </row>
-    <row r="15" spans="1:10" ht="14.45" customHeight="1">
+    <row r="15" spans="1:10" ht="14.4" customHeight="1">
       <c r="A15" s="35" t="s">
         <v>846</v>
       </c>
@@ -35138,7 +36201,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" spans="1:10" ht="14.45" customHeight="1">
+    <row r="16" spans="1:10" ht="14.4" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>1165</v>
       </c>
@@ -35154,7 +36217,7 @@
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
     </row>
-    <row r="17" spans="2:10" ht="14.45" customHeight="1">
+    <row r="17" spans="2:10" ht="14.4" customHeight="1">
       <c r="D17" s="22" t="s">
         <v>1135</v>
       </c>
@@ -35165,7 +36228,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:10" ht="14.45" customHeight="1">
+    <row r="18" spans="2:10" ht="14.4" customHeight="1">
       <c r="B18" s="16" t="s">
         <v>812</v>
       </c>
@@ -35179,7 +36242,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:10" ht="14.45" customHeight="1">
+    <row r="19" spans="2:10" ht="14.4" customHeight="1">
       <c r="B19" s="16" t="s">
         <v>813</v>
       </c>
@@ -35196,7 +36259,7 @@
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:10" ht="14.45" customHeight="1">
+    <row r="20" spans="2:10" ht="14.4" customHeight="1">
       <c r="B20" s="16" t="s">
         <v>814</v>
       </c>
@@ -35210,7 +36273,7 @@
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:10" ht="14.45" customHeight="1">
+    <row r="21" spans="2:10" ht="14.4" customHeight="1">
       <c r="B21" s="16" t="s">
         <v>815</v>
       </c>
@@ -35224,7 +36287,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
     </row>
-    <row r="22" spans="2:10" ht="14.45" customHeight="1">
+    <row r="22" spans="2:10" ht="14.4" customHeight="1">
       <c r="B22" s="17"/>
       <c r="D22" s="22" t="s">
         <v>1126</v>
@@ -35236,7 +36299,7 @@
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
     </row>
-    <row r="23" spans="2:10" ht="14.45" customHeight="1">
+    <row r="23" spans="2:10" ht="14.4" customHeight="1">
       <c r="B23" s="16" t="s">
         <v>816</v>
       </c>
@@ -35250,7 +36313,7 @@
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:10" ht="14.45" customHeight="1">
+    <row r="24" spans="2:10" ht="14.4" customHeight="1">
       <c r="B24" s="16" t="s">
         <v>817</v>
       </c>
@@ -35264,7 +36327,7 @@
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:10" ht="14.45" customHeight="1">
+    <row r="25" spans="2:10" ht="14.4" customHeight="1">
       <c r="B25" s="17"/>
       <c r="D25" s="22" t="s">
         <v>1139</v>
@@ -35276,7 +36339,7 @@
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:10" ht="14.45" customHeight="1">
+    <row r="26" spans="2:10" ht="14.4" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>818</v>
       </c>
@@ -35290,7 +36353,7 @@
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
     </row>
-    <row r="27" spans="2:10" ht="14.45" customHeight="1">
+    <row r="27" spans="2:10" ht="14.4" customHeight="1">
       <c r="B27" s="16" t="s">
         <v>819</v>
       </c>
@@ -35304,7 +36367,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="2:10" ht="14.45" customHeight="1">
+    <row r="28" spans="2:10" ht="14.4" customHeight="1">
       <c r="B28" s="17"/>
       <c r="D28" s="22" t="s">
         <v>1126</v>
@@ -35316,7 +36379,7 @@
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:10" ht="14.45" customHeight="1">
+    <row r="29" spans="2:10" ht="14.4" customHeight="1">
       <c r="B29" s="16" t="s">
         <v>820</v>
       </c>
@@ -35330,7 +36393,7 @@
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:10" ht="14.45" customHeight="1">
+    <row r="30" spans="2:10" ht="14.4" customHeight="1">
       <c r="B30" s="16" t="s">
         <v>821</v>
       </c>
@@ -35344,7 +36407,7 @@
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
     </row>
-    <row r="31" spans="2:10" ht="14.45" customHeight="1">
+    <row r="31" spans="2:10" ht="14.4" customHeight="1">
       <c r="B31" s="16" t="s">
         <v>822</v>
       </c>
@@ -35358,7 +36421,7 @@
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
     </row>
-    <row r="32" spans="2:10" ht="14.45" customHeight="1">
+    <row r="32" spans="2:10" ht="14.4" customHeight="1">
       <c r="B32" s="17"/>
       <c r="D32" s="22" t="s">
         <v>1130</v>
@@ -35370,7 +36433,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:10" ht="14.45" customHeight="1">
+    <row r="33" spans="2:10" ht="14.4" customHeight="1">
       <c r="B33" s="16" t="s">
         <v>823</v>
       </c>
@@ -35384,7 +36447,7 @@
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:10" ht="14.45" customHeight="1">
+    <row r="34" spans="2:10" ht="14.4" customHeight="1">
       <c r="B34" s="16" t="s">
         <v>824</v>
       </c>
@@ -35398,7 +36461,7 @@
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:10" ht="14.45" customHeight="1">
+    <row r="35" spans="2:10" ht="14.4" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>825</v>
       </c>
@@ -35412,7 +36475,7 @@
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
     </row>
-    <row r="36" spans="2:10" ht="14.45" customHeight="1">
+    <row r="36" spans="2:10" ht="14.4" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="22" t="s">
         <v>1134</v>
@@ -35424,7 +36487,7 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:10" ht="14.45" customHeight="1">
+    <row r="37" spans="2:10" ht="14.4" customHeight="1">
       <c r="B37" s="16" t="s">
         <v>826</v>
       </c>
@@ -35438,7 +36501,7 @@
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:10" ht="14.45" customHeight="1">
+    <row r="38" spans="2:10" ht="14.4" customHeight="1">
       <c r="B38" s="16" t="s">
         <v>827</v>
       </c>
@@ -35452,7 +36515,7 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="2:10" ht="14.45" customHeight="1">
+    <row r="39" spans="2:10" ht="14.4" customHeight="1">
       <c r="B39" s="16" t="s">
         <v>828</v>
       </c>
@@ -35466,7 +36529,7 @@
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="2:10" ht="14.45" customHeight="1">
+    <row r="40" spans="2:10" ht="14.4" customHeight="1">
       <c r="B40" s="16" t="s">
         <v>829</v>
       </c>
@@ -35480,7 +36543,7 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="2:10" ht="14.45" customHeight="1">
+    <row r="41" spans="2:10" ht="14.4" customHeight="1">
       <c r="B41" s="16" t="s">
         <v>830</v>
       </c>
@@ -35494,7 +36557,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="2:10" ht="14.45" customHeight="1">
+    <row r="42" spans="2:10" ht="14.4" customHeight="1">
       <c r="D42" s="22" t="s">
         <v>1148</v>
       </c>
@@ -35505,7 +36568,7 @@
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
     </row>
-    <row r="43" spans="2:10" ht="14.45" customHeight="1">
+    <row r="43" spans="2:10" ht="14.4" customHeight="1">
       <c r="D43" s="22" t="s">
         <v>1149</v>
       </c>
@@ -35516,7 +36579,7 @@
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
     </row>
-    <row r="44" spans="2:10" ht="14.45" customHeight="1">
+    <row r="44" spans="2:10" ht="14.4" customHeight="1">
       <c r="B44" s="18" t="s">
         <v>832</v>
       </c>
@@ -35531,7 +36594,7 @@
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
     </row>
-    <row r="45" spans="2:10" ht="14.45" customHeight="1">
+    <row r="45" spans="2:10" ht="14.4" customHeight="1">
       <c r="B45" s="18" t="s">
         <v>833</v>
       </c>
@@ -35546,7 +36609,7 @@
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:10" ht="14.45" customHeight="1">
+    <row r="46" spans="2:10" ht="14.4" customHeight="1">
       <c r="B46" s="18" t="s">
         <v>834</v>
       </c>
@@ -35561,7 +36624,7 @@
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
     </row>
-    <row r="47" spans="2:10" ht="14.45" customHeight="1">
+    <row r="47" spans="2:10" ht="14.4" customHeight="1">
       <c r="B47" s="18" t="s">
         <v>835</v>
       </c>
@@ -35576,7 +36639,7 @@
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
     </row>
-    <row r="48" spans="2:10" ht="14.45" customHeight="1">
+    <row r="48" spans="2:10" ht="14.4" customHeight="1">
       <c r="B48" s="18" t="s">
         <v>836</v>
       </c>
@@ -35591,7 +36654,7 @@
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
     </row>
-    <row r="49" spans="2:10" ht="14.45" customHeight="1">
+    <row r="49" spans="2:10" ht="14.4" customHeight="1">
       <c r="B49" s="18" t="s">
         <v>837</v>
       </c>
@@ -35606,7 +36669,7 @@
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
     </row>
-    <row r="50" spans="2:10" ht="14.45" customHeight="1">
+    <row r="50" spans="2:10" ht="14.4" customHeight="1">
       <c r="B50" s="18" t="s">
         <v>838</v>
       </c>
@@ -35621,7 +36684,7 @@
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
     </row>
-    <row r="51" spans="2:10" ht="14.45" customHeight="1">
+    <row r="51" spans="2:10" ht="14.4" customHeight="1">
       <c r="B51" s="18" t="s">
         <v>839</v>
       </c>
@@ -35636,7 +36699,7 @@
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
     </row>
-    <row r="52" spans="2:10" ht="14.45" customHeight="1">
+    <row r="52" spans="2:10" ht="14.4" customHeight="1">
       <c r="B52" s="18" t="s">
         <v>840</v>
       </c>
@@ -35651,7 +36714,7 @@
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
     </row>
-    <row r="53" spans="2:10" ht="14.45" customHeight="1">
+    <row r="53" spans="2:10" ht="14.4" customHeight="1">
       <c r="B53" s="18" t="s">
         <v>841</v>
       </c>
@@ -35666,7 +36729,7 @@
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
     </row>
-    <row r="54" spans="2:10" ht="14.45" customHeight="1">
+    <row r="54" spans="2:10" ht="14.4" customHeight="1">
       <c r="B54" s="18" t="s">
         <v>842</v>
       </c>
@@ -35681,7 +36744,7 @@
       <c r="I54" s="23"/>
       <c r="J54" s="23"/>
     </row>
-    <row r="55" spans="2:10" ht="14.45" customHeight="1">
+    <row r="55" spans="2:10" ht="14.4" customHeight="1">
       <c r="B55" s="18" t="s">
         <v>843</v>
       </c>
@@ -35696,7 +36759,7 @@
       <c r="I55" s="23"/>
       <c r="J55" s="23"/>
     </row>
-    <row r="56" spans="2:10" ht="14.45" customHeight="1">
+    <row r="56" spans="2:10" ht="14.4" customHeight="1">
       <c r="B56" s="18" t="s">
         <v>844</v>
       </c>
@@ -35711,7 +36774,7 @@
       <c r="I56" s="23"/>
       <c r="J56" s="23"/>
     </row>
-    <row r="57" spans="2:10" ht="14.45" customHeight="1">
+    <row r="57" spans="2:10" ht="14.4" customHeight="1">
       <c r="B57" s="18" t="s">
         <v>845</v>
       </c>
@@ -35726,7 +36789,7 @@
       <c r="I57" s="23"/>
       <c r="J57" s="23"/>
     </row>
-    <row r="58" spans="2:10" ht="14.45" customHeight="1">
+    <row r="58" spans="2:10" ht="14.4" customHeight="1">
       <c r="B58" s="18" t="s">
         <v>846</v>
       </c>
@@ -35741,7 +36804,7 @@
       <c r="I58" s="23"/>
       <c r="J58" s="23"/>
     </row>
-    <row r="59" spans="2:10" ht="14.45" customHeight="1">
+    <row r="59" spans="2:10" ht="14.4" customHeight="1">
       <c r="B59" s="18" t="s">
         <v>847</v>
       </c>
@@ -35756,7 +36819,7 @@
       <c r="I59" s="23"/>
       <c r="J59" s="23"/>
     </row>
-    <row r="60" spans="2:10" ht="14.45" customHeight="1">
+    <row r="60" spans="2:10" ht="14.4" customHeight="1">
       <c r="D60" s="22" t="s">
         <v>1156</v>
       </c>
@@ -35767,7 +36830,7 @@
       <c r="I60" s="23"/>
       <c r="J60" s="23"/>
     </row>
-    <row r="61" spans="2:10" ht="14.45" customHeight="1">
+    <row r="61" spans="2:10" ht="14.4" customHeight="1">
       <c r="D61" s="22" t="s">
         <v>1157</v>
       </c>
@@ -35778,7 +36841,7 @@
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
     </row>
-    <row r="62" spans="2:10" ht="14.45" customHeight="1">
+    <row r="62" spans="2:10" ht="14.4" customHeight="1">
       <c r="D62" s="22" t="s">
         <v>1134</v>
       </c>
@@ -35789,7 +36852,7 @@
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
     </row>
-    <row r="63" spans="2:10" ht="14.45" customHeight="1">
+    <row r="63" spans="2:10" ht="14.4" customHeight="1">
       <c r="D63" s="22" t="s">
         <v>1128</v>
       </c>
@@ -35800,7 +36863,7 @@
       <c r="I63" s="23"/>
       <c r="J63" s="23"/>
     </row>
-    <row r="64" spans="2:10" ht="14.45" customHeight="1">
+    <row r="64" spans="2:10" ht="14.4" customHeight="1">
       <c r="D64" s="22" t="s">
         <v>1135</v>
       </c>
@@ -35811,7 +36874,7 @@
       <c r="I64" s="23"/>
       <c r="J64" s="23"/>
     </row>
-    <row r="65" spans="4:10" ht="14.45" customHeight="1">
+    <row r="65" spans="4:10" ht="14.4" customHeight="1">
       <c r="D65" s="22" t="s">
         <v>1126</v>
       </c>
@@ -35822,7 +36885,7 @@
       <c r="I65" s="23"/>
       <c r="J65" s="23"/>
     </row>
-    <row r="66" spans="4:10" ht="14.45" customHeight="1">
+    <row r="66" spans="4:10" ht="14.4" customHeight="1">
       <c r="D66" s="22" t="s">
         <v>1136</v>
       </c>
@@ -35833,7 +36896,7 @@
       <c r="I66" s="23"/>
       <c r="J66" s="23"/>
     </row>
-    <row r="67" spans="4:10" ht="14.45" customHeight="1">
+    <row r="67" spans="4:10" ht="14.4" customHeight="1">
       <c r="D67" s="22" t="s">
         <v>1158</v>
       </c>
@@ -35844,7 +36907,7 @@
       <c r="I67" s="23"/>
       <c r="J67" s="23"/>
     </row>
-    <row r="68" spans="4:10" ht="14.45" customHeight="1">
+    <row r="68" spans="4:10" ht="14.4" customHeight="1">
       <c r="D68" s="22" t="s">
         <v>1159</v>
       </c>
@@ -35855,7 +36918,7 @@
       <c r="I68" s="23"/>
       <c r="J68" s="23"/>
     </row>
-    <row r="69" spans="4:10" ht="14.45" customHeight="1">
+    <row r="69" spans="4:10" ht="14.4" customHeight="1">
       <c r="D69" s="22" t="s">
         <v>1160</v>
       </c>
@@ -35866,7 +36929,7 @@
       <c r="I69" s="23"/>
       <c r="J69" s="23"/>
     </row>
-    <row r="70" spans="4:10" ht="14.45" customHeight="1">
+    <row r="70" spans="4:10" ht="14.4" customHeight="1">
       <c r="D70" s="22" t="s">
         <v>1161</v>
       </c>
@@ -35877,7 +36940,7 @@
       <c r="I70" s="23"/>
       <c r="J70" s="23"/>
     </row>
-    <row r="71" spans="4:10" ht="14.45" customHeight="1">
+    <row r="71" spans="4:10" ht="14.4" customHeight="1">
       <c r="D71" s="22" t="s">
         <v>1162</v>
       </c>
@@ -35888,7 +36951,7 @@
       <c r="I71" s="23"/>
       <c r="J71" s="23"/>
     </row>
-    <row r="72" spans="4:10" ht="14.45" customHeight="1">
+    <row r="72" spans="4:10" ht="14.4" customHeight="1">
       <c r="E72" s="23"/>
       <c r="F72" s="23"/>
       <c r="G72" s="23"/>
@@ -35896,7 +36959,7 @@
       <c r="I72" s="23"/>
       <c r="J72" s="23"/>
     </row>
-    <row r="73" spans="4:10" ht="15">
+    <row r="73" spans="4:10" ht="14.4">
       <c r="E73" s="23"/>
       <c r="F73" s="23"/>
       <c r="G73" s="23"/>
@@ -35904,99 +36967,99 @@
       <c r="I73" s="23"/>
       <c r="J73" s="23"/>
     </row>
-    <row r="74" spans="4:10" ht="15"/>
-    <row r="75" spans="4:10" ht="15"/>
-    <row r="76" spans="4:10" ht="15"/>
-    <row r="77" spans="4:10" ht="15"/>
-    <row r="78" spans="4:10" ht="15"/>
-    <row r="79" spans="4:10" ht="15"/>
-    <row r="80" spans="4:10" ht="15"/>
-    <row r="81" ht="15"/>
-    <row r="82" ht="15"/>
-    <row r="83" ht="15"/>
-    <row r="84" ht="15"/>
-    <row r="85" ht="15"/>
-    <row r="86" ht="15"/>
-    <row r="87" ht="15"/>
-    <row r="88" ht="15"/>
-    <row r="89" ht="15"/>
-    <row r="90" ht="15"/>
-    <row r="91" ht="15"/>
-    <row r="92" ht="15"/>
-    <row r="93" ht="15"/>
-    <row r="94" ht="15"/>
-    <row r="95" ht="15"/>
-    <row r="96" ht="15"/>
-    <row r="97" ht="15"/>
-    <row r="98" ht="15"/>
-    <row r="99" ht="15"/>
-    <row r="100" ht="15"/>
-    <row r="101" ht="15"/>
-    <row r="102" ht="15"/>
-    <row r="103" ht="15"/>
-    <row r="104" ht="15"/>
-    <row r="105" ht="15"/>
-    <row r="106" ht="15"/>
-    <row r="107" ht="15"/>
-    <row r="108" ht="15"/>
-    <row r="109" ht="15"/>
-    <row r="110" ht="15"/>
-    <row r="111" ht="15"/>
-    <row r="112" ht="15"/>
-    <row r="113" ht="15"/>
-    <row r="114" ht="15"/>
-    <row r="115" ht="15"/>
-    <row r="116" ht="15"/>
-    <row r="117" ht="15"/>
-    <row r="118" ht="15"/>
-    <row r="119" ht="15"/>
-    <row r="120" ht="15"/>
-    <row r="121" ht="15"/>
-    <row r="122" ht="15"/>
-    <row r="123" ht="15"/>
-    <row r="124" ht="15"/>
-    <row r="125" ht="15"/>
-    <row r="126" ht="15"/>
-    <row r="127" ht="15"/>
-    <row r="128" ht="15"/>
-    <row r="129" ht="15"/>
-    <row r="130" ht="15"/>
-    <row r="131" ht="15"/>
-    <row r="132" ht="15"/>
-    <row r="133" ht="15"/>
-    <row r="134" ht="15"/>
-    <row r="135" ht="15"/>
-    <row r="136" ht="15"/>
-    <row r="137" ht="15"/>
-    <row r="138" ht="15"/>
-    <row r="139" ht="15"/>
-    <row r="140" ht="15"/>
-    <row r="141" ht="15"/>
-    <row r="142" ht="15"/>
-    <row r="143" ht="15"/>
-    <row r="144" ht="15"/>
-    <row r="145" ht="15"/>
-    <row r="146" ht="15"/>
-    <row r="147" ht="15"/>
-    <row r="148" ht="15"/>
-    <row r="149" ht="15"/>
-    <row r="150" ht="15"/>
-    <row r="151" ht="15"/>
-    <row r="152" ht="15"/>
-    <row r="153" ht="15"/>
-    <row r="154" ht="15"/>
-    <row r="155" ht="15"/>
-    <row r="156" ht="15"/>
-    <row r="157" ht="15"/>
-    <row r="158" ht="15"/>
-    <row r="159" ht="15"/>
-    <row r="160" ht="15"/>
-    <row r="161" ht="15"/>
-    <row r="162" ht="15"/>
-    <row r="163" ht="15"/>
-    <row r="164" ht="15"/>
-    <row r="165" ht="15"/>
-    <row r="166" ht="15"/>
+    <row r="74" spans="4:10" ht="14.4"/>
+    <row r="75" spans="4:10" ht="14.4"/>
+    <row r="76" spans="4:10" ht="14.4"/>
+    <row r="77" spans="4:10" ht="14.4"/>
+    <row r="78" spans="4:10" ht="14.4"/>
+    <row r="79" spans="4:10" ht="14.4"/>
+    <row r="80" spans="4:10" ht="14.4"/>
+    <row r="81" ht="14.4"/>
+    <row r="82" ht="14.4"/>
+    <row r="83" ht="14.4"/>
+    <row r="84" ht="14.4"/>
+    <row r="85" ht="14.4"/>
+    <row r="86" ht="14.4"/>
+    <row r="87" ht="14.4"/>
+    <row r="88" ht="14.4"/>
+    <row r="89" ht="14.4"/>
+    <row r="90" ht="14.4"/>
+    <row r="91" ht="14.4"/>
+    <row r="92" ht="14.4"/>
+    <row r="93" ht="14.4"/>
+    <row r="94" ht="14.4"/>
+    <row r="95" ht="14.4"/>
+    <row r="96" ht="14.4"/>
+    <row r="97" ht="14.4"/>
+    <row r="98" ht="14.4"/>
+    <row r="99" ht="14.4"/>
+    <row r="100" ht="14.4"/>
+    <row r="101" ht="14.4"/>
+    <row r="102" ht="14.4"/>
+    <row r="103" ht="14.4"/>
+    <row r="104" ht="14.4"/>
+    <row r="105" ht="14.4"/>
+    <row r="106" ht="14.4"/>
+    <row r="107" ht="14.4"/>
+    <row r="108" ht="14.4"/>
+    <row r="109" ht="14.4"/>
+    <row r="110" ht="14.4"/>
+    <row r="111" ht="14.4"/>
+    <row r="112" ht="14.4"/>
+    <row r="113" ht="14.4"/>
+    <row r="114" ht="14.4"/>
+    <row r="115" ht="14.4"/>
+    <row r="116" ht="14.4"/>
+    <row r="117" ht="14.4"/>
+    <row r="118" ht="14.4"/>
+    <row r="119" ht="14.4"/>
+    <row r="120" ht="14.4"/>
+    <row r="121" ht="14.4"/>
+    <row r="122" ht="14.4"/>
+    <row r="123" ht="14.4"/>
+    <row r="124" ht="14.4"/>
+    <row r="125" ht="14.4"/>
+    <row r="126" ht="14.4"/>
+    <row r="127" ht="14.4"/>
+    <row r="128" ht="14.4"/>
+    <row r="129" ht="14.4"/>
+    <row r="130" ht="14.4"/>
+    <row r="131" ht="14.4"/>
+    <row r="132" ht="14.4"/>
+    <row r="133" ht="14.4"/>
+    <row r="134" ht="14.4"/>
+    <row r="135" ht="14.4"/>
+    <row r="136" ht="14.4"/>
+    <row r="137" ht="14.4"/>
+    <row r="138" ht="14.4"/>
+    <row r="139" ht="14.4"/>
+    <row r="140" ht="14.4"/>
+    <row r="141" ht="14.4"/>
+    <row r="142" ht="14.4"/>
+    <row r="143" ht="14.4"/>
+    <row r="144" ht="14.4"/>
+    <row r="145" ht="14.4"/>
+    <row r="146" ht="14.4"/>
+    <row r="147" ht="14.4"/>
+    <row r="148" ht="14.4"/>
+    <row r="149" ht="14.4"/>
+    <row r="150" ht="14.4"/>
+    <row r="151" ht="14.4"/>
+    <row r="152" ht="14.4"/>
+    <row r="153" ht="14.4"/>
+    <row r="154" ht="14.4"/>
+    <row r="155" ht="14.4"/>
+    <row r="156" ht="14.4"/>
+    <row r="157" ht="14.4"/>
+    <row r="158" ht="14.4"/>
+    <row r="159" ht="14.4"/>
+    <row r="160" ht="14.4"/>
+    <row r="161" ht="14.4"/>
+    <row r="162" ht="14.4"/>
+    <row r="163" ht="14.4"/>
+    <row r="164" ht="14.4"/>
+    <row r="165" ht="14.4"/>
+    <row r="166" ht="14.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36005,15 +37068,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7DD0CD-6695-4D3C-9518-BDB565BCCF21}">
   <dimension ref="B3:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="101.42578125" customWidth="1"/>
+    <col min="2" max="2" width="101.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" s="2"/>
     </row>
-    <row r="5" spans="2:2" ht="409.5">
+    <row r="5" spans="2:2" ht="409.6">
       <c r="B5" s="2" t="s">
         <v>769</v>
       </c>
@@ -36028,18 +37091,18 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:N150"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="65"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="64"/>
     <col min="7" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="48" thickBot="1">
+    <row r="1" spans="1:13" ht="31.8" thickBot="1">
       <c r="A1" t="s">
         <v>760</v>
       </c>
@@ -36072,8 +37135,11 @@
       <c r="L1" s="11" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="11" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="49">
         <v>1</v>
       </c>
@@ -36093,7 +37159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="49">
         <v>2</v>
       </c>
@@ -36113,7 +37179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="49">
         <v>3</v>
       </c>
@@ -36133,7 +37199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="49">
         <v>4</v>
       </c>
@@ -36153,7 +37219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="49">
         <v>5</v>
       </c>
@@ -36173,7 +37239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="49">
         <v>6</v>
       </c>
@@ -36193,7 +37259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="49">
         <v>7</v>
       </c>
@@ -36213,7 +37279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="49">
         <v>8</v>
       </c>
@@ -36233,7 +37299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="49">
         <v>9</v>
       </c>
@@ -36253,7 +37319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="49">
         <v>10</v>
       </c>
@@ -36273,7 +37339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="49">
         <v>11</v>
       </c>
@@ -36293,7 +37359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="49">
         <v>12</v>
       </c>
@@ -36313,7 +37379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="49">
         <v>13</v>
       </c>
@@ -36333,7 +37399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="49">
         <v>14</v>
       </c>
@@ -36349,7 +37415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="49">
         <v>15</v>
       </c>
@@ -36935,7 +38001,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1">
+    <row r="42" spans="1:12" ht="15" thickBot="1">
       <c r="A42" s="49">
         <v>41</v>
       </c>
@@ -36958,7 +38024,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="16.5" thickBot="1">
+    <row r="43" spans="1:12" ht="16.2" thickBot="1">
       <c r="A43" s="49">
         <v>42</v>
       </c>
@@ -36981,7 +38047,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="16.5" thickBot="1">
+    <row r="44" spans="1:12" ht="16.2" thickBot="1">
       <c r="A44" s="49">
         <v>42</v>
       </c>
@@ -37667,7 +38733,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1">
+    <row r="75" spans="1:12" ht="15" thickBot="1">
       <c r="A75" s="49">
         <v>71</v>
       </c>
@@ -37690,7 +38756,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="16.5" thickBot="1">
+    <row r="76" spans="1:12" ht="16.2" thickBot="1">
       <c r="A76" s="49">
         <v>72</v>
       </c>
@@ -37713,7 +38779,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="16.5" thickBot="1">
+    <row r="77" spans="1:12" ht="16.2" thickBot="1">
       <c r="A77" s="49">
         <v>73</v>
       </c>
@@ -38026,7 +39092,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" thickBot="1">
+    <row r="94" spans="1:12" ht="15" thickBot="1">
       <c r="A94" s="49">
         <v>89</v>
       </c>
@@ -38049,7 +39115,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="16.5" thickBot="1">
+    <row r="95" spans="1:12" ht="16.2" thickBot="1">
       <c r="A95" s="49">
         <v>72</v>
       </c>
@@ -38112,7 +39178,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.75" thickBot="1">
+    <row r="98" spans="1:12" ht="15" thickBot="1">
       <c r="A98" s="49"/>
       <c r="B98" s="22" t="s">
         <v>214</v>
@@ -38131,7 +39197,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="16.5" thickBot="1">
+    <row r="99" spans="1:12" ht="16.2" thickBot="1">
       <c r="A99" s="49">
         <v>92</v>
       </c>
@@ -38154,7 +39220,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="16.5" thickBot="1">
+    <row r="100" spans="1:12" ht="16.2" thickBot="1">
       <c r="A100" s="49">
         <v>92</v>
       </c>
@@ -38177,7 +39243,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="16.5" thickBot="1">
+    <row r="101" spans="1:12" ht="16.2" thickBot="1">
       <c r="A101" s="49">
         <v>92</v>
       </c>
@@ -38200,7 +39266,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="16.5" thickBot="1">
+    <row r="102" spans="1:12" ht="16.2" thickBot="1">
       <c r="A102" s="49">
         <v>92</v>
       </c>
@@ -38221,7 +39287,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.75" thickBot="1">
+    <row r="103" spans="1:12" ht="15" thickBot="1">
       <c r="A103" s="49">
         <v>92</v>
       </c>
@@ -38239,7 +39305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.75" thickBot="1">
+    <row r="104" spans="1:12" ht="15" thickBot="1">
       <c r="A104" s="49">
         <v>93</v>
       </c>
@@ -38563,7 +39629,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.75" thickBot="1">
+    <row r="118" spans="1:12" ht="15" thickBot="1">
       <c r="A118" s="58">
         <v>616</v>
       </c>
@@ -38589,7 +39655,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.75" thickBot="1">
+    <row r="119" spans="1:12" ht="15" thickBot="1">
       <c r="A119" s="49">
         <v>94</v>
       </c>
@@ -38610,7 +39676,7 @@
       <c r="J119" s="57"/>
       <c r="K119" s="57"/>
     </row>
-    <row r="120" spans="1:12" ht="15.75" thickBot="1">
+    <row r="120" spans="1:12" ht="15" thickBot="1">
       <c r="A120" s="49">
         <v>95</v>
       </c>
@@ -38638,7 +39704,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.75" thickBot="1">
+    <row r="121" spans="1:12" ht="15" thickBot="1">
       <c r="A121" s="49">
         <v>96</v>
       </c>
@@ -38666,7 +39732,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.75" thickBot="1">
+    <row r="122" spans="1:12" ht="15" thickBot="1">
       <c r="A122" s="49">
         <v>97</v>
       </c>
@@ -38694,7 +39760,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" thickBot="1">
+    <row r="123" spans="1:12" ht="15" thickBot="1">
       <c r="A123" s="58">
         <v>598</v>
       </c>
@@ -38717,7 +39783,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" thickBot="1">
+    <row r="124" spans="1:12" ht="15" thickBot="1">
       <c r="A124" s="58">
         <v>599</v>
       </c>
@@ -38740,7 +39806,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.75" thickBot="1">
+    <row r="125" spans="1:12" ht="15" thickBot="1">
       <c r="A125" s="58">
         <v>600</v>
       </c>
@@ -38763,7 +39829,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.75" thickBot="1">
+    <row r="126" spans="1:12" ht="15" thickBot="1">
       <c r="A126" s="58">
         <v>607</v>
       </c>
@@ -38786,7 +39852,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.75" thickBot="1">
+    <row r="127" spans="1:12" ht="15" thickBot="1">
       <c r="A127" s="49">
         <v>98</v>
       </c>
@@ -38814,7 +39880,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.75" thickBot="1">
+    <row r="128" spans="1:12" ht="15" thickBot="1">
       <c r="A128" s="49">
         <v>99</v>
       </c>
@@ -38842,7 +39908,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1">
+    <row r="129" spans="1:14" ht="15" thickBot="1">
       <c r="A129" s="49">
         <v>100</v>
       </c>
@@ -38863,7 +39929,7 @@
       <c r="J129" s="57"/>
       <c r="K129" s="57"/>
     </row>
-    <row r="130" spans="1:12" ht="15.75" thickBot="1">
+    <row r="130" spans="1:14" ht="15" thickBot="1">
       <c r="A130" s="49">
         <v>101</v>
       </c>
@@ -38884,7 +39950,7 @@
       <c r="J130" s="57"/>
       <c r="K130" s="57"/>
     </row>
-    <row r="131" spans="1:12" ht="15.75" thickBot="1">
+    <row r="131" spans="1:14" ht="15" thickBot="1">
       <c r="A131" s="49">
         <v>102</v>
       </c>
@@ -38907,7 +39973,7 @@
       <c r="J131" s="57"/>
       <c r="K131" s="57"/>
     </row>
-    <row r="132" spans="1:12" ht="15.75" thickBot="1">
+    <row r="132" spans="1:14" ht="15" thickBot="1">
       <c r="A132" s="49">
         <v>106</v>
       </c>
@@ -38935,7 +40001,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" thickBot="1">
+    <row r="133" spans="1:14" ht="15" thickBot="1">
       <c r="A133" s="49">
         <v>107</v>
       </c>
@@ -38963,7 +40029,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" thickBot="1">
+    <row r="134" spans="1:14" ht="15" thickBot="1">
       <c r="A134" s="49">
         <v>103</v>
       </c>
@@ -38990,8 +40056,11 @@
       <c r="L134" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" ht="15.75" thickBot="1">
+      <c r="N134" s="50" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="15" thickBot="1">
       <c r="B135" s="55" t="s">
         <v>224</v>
       </c>
@@ -39010,15 +40079,20 @@
       <c r="L135" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" ht="15.75" thickBot="1">
-      <c r="B136" s="64" t="s">
+      <c r="N135" s="50" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="15" thickBot="1">
+      <c r="B136" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="68" t="s">
         <v>1629</v>
       </c>
-      <c r="D136" s="64"/>
+      <c r="D136" s="55" t="s">
+        <v>407</v>
+      </c>
       <c r="E136" s="55" t="s">
         <v>1625</v>
       </c>
@@ -39028,18 +40102,26 @@
       <c r="L136" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" ht="15.75" thickBot="1">
+      <c r="M136" t="s">
+        <v>404</v>
+      </c>
+      <c r="N136" s="50" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" ht="15" thickBot="1">
       <c r="A137" s="49">
         <v>108</v>
       </c>
-      <c r="B137" s="55" t="s">
+      <c r="B137" s="68" t="s">
         <v>228</v>
       </c>
-      <c r="C137" s="55" t="s">
+      <c r="C137" s="68" t="s">
         <v>1630</v>
       </c>
-      <c r="D137" s="55"/>
+      <c r="D137" s="55" t="s">
+        <v>407</v>
+      </c>
       <c r="E137" s="55" t="s">
         <v>1625</v>
       </c>
@@ -39051,8 +40133,14 @@
       <c r="I137" s="57"/>
       <c r="J137" s="57"/>
       <c r="K137" s="57"/>
-    </row>
-    <row r="138" spans="1:12" ht="15.75" thickBot="1">
+      <c r="M137" t="s">
+        <v>404</v>
+      </c>
+      <c r="N137" s="50" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="15" thickBot="1">
       <c r="A138" s="49">
         <v>109</v>
       </c>
@@ -39062,7 +40150,9 @@
       <c r="C138" s="55" t="s">
         <v>1631</v>
       </c>
-      <c r="D138" s="55"/>
+      <c r="D138" s="55" t="s">
+        <v>407</v>
+      </c>
       <c r="E138" s="55" t="s">
         <v>1625</v>
       </c>
@@ -39074,8 +40164,14 @@
       <c r="I138" s="57"/>
       <c r="J138" s="57"/>
       <c r="K138" s="57"/>
-    </row>
-    <row r="139" spans="1:12" ht="15.75" thickBot="1">
+      <c r="M138" t="s">
+        <v>404</v>
+      </c>
+      <c r="N138" s="50" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="15" thickBot="1">
       <c r="A139" s="49">
         <v>110</v>
       </c>
@@ -39097,8 +40193,11 @@
       <c r="I139" s="57"/>
       <c r="J139" s="57"/>
       <c r="K139" s="57"/>
-    </row>
-    <row r="140" spans="1:12" ht="15.75" thickBot="1">
+      <c r="N139" s="50" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="15" thickBot="1">
       <c r="A140" s="49">
         <v>111</v>
       </c>
@@ -39120,8 +40219,11 @@
       <c r="I140" s="57"/>
       <c r="J140" s="57"/>
       <c r="K140" s="57"/>
-    </row>
-    <row r="141" spans="1:12" ht="15.75" thickBot="1">
+      <c r="N140" s="50" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="15" thickBot="1">
       <c r="A141" s="58">
         <v>569</v>
       </c>
@@ -39138,8 +40240,11 @@
         <f>VLOOKUP(B141,'Unit Test'!A:J,10,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" ht="15.75" thickBot="1">
+      <c r="N141" s="50" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="15" thickBot="1">
       <c r="B142" s="55" t="s">
         <v>1568</v>
       </c>
@@ -39154,12 +40259,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="143" spans="1:14">
+      <c r="N143" s="50" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
       <c r="C144" s="15" t="s">
         <v>1634</v>
       </c>
-    </row>
-    <row r="146" spans="2:6">
+      <c r="N144" s="50" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="145" spans="2:14">
+      <c r="N145" s="50" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="146" spans="2:14">
       <c r="B146" s="35" t="s">
         <v>1568</v>
       </c>
@@ -39173,8 +40291,11 @@
       <c r="F146" s="53">
         <v>12</v>
       </c>
-    </row>
-    <row r="147" spans="2:6">
+      <c r="N146" s="50" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="147" spans="2:14">
       <c r="B147" s="35" t="s">
         <v>1568</v>
       </c>
@@ -39189,7 +40310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="2:6">
+    <row r="148" spans="2:14">
       <c r="B148" s="35" t="s">
         <v>1568</v>
       </c>
@@ -39204,7 +40325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
+    <row r="149" spans="2:14">
       <c r="B149" s="35" t="s">
         <v>1568</v>
       </c>
@@ -39219,7 +40340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
+    <row r="150" spans="2:14">
       <c r="B150" s="35" t="s">
         <v>1568</v>
       </c>
@@ -39245,16 +40366,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="71.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="9" max="9" width="71.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -39280,7 +40401,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="55.5">
+    <row r="2" spans="1:7" ht="55.2">
       <c r="A2" s="38" t="s">
         <v>1191</v>
       </c>
@@ -39303,7 +40424,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45">
+    <row r="3" spans="1:7" ht="43.2">
       <c r="A3" s="38" t="s">
         <v>1195</v>
       </c>
@@ -39326,7 +40447,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45">
+    <row r="4" spans="1:7" ht="43.2">
       <c r="A4" s="38" t="s">
         <v>1199</v>
       </c>
@@ -39349,7 +40470,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45">
+    <row r="5" spans="1:7" ht="43.2">
       <c r="A5" s="38" t="s">
         <v>1204</v>
       </c>
@@ -39372,7 +40493,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60">
+    <row r="6" spans="1:7" ht="43.2">
       <c r="A6" s="38" t="s">
         <v>1208</v>
       </c>
@@ -39395,7 +40516,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45">
+    <row r="7" spans="1:7" ht="43.2">
       <c r="A7" s="38" t="s">
         <v>1211</v>
       </c>
@@ -39418,7 +40539,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45">
+    <row r="8" spans="1:7" ht="43.2">
       <c r="A8" s="38" t="s">
         <v>1216</v>
       </c>
@@ -39441,7 +40562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45">
+    <row r="9" spans="1:7" ht="43.2">
       <c r="A9" s="38" t="s">
         <v>1220</v>
       </c>
@@ -39464,7 +40585,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="75">
+    <row r="10" spans="1:7" ht="57.6">
       <c r="A10" s="38" t="s">
         <v>1223</v>
       </c>
@@ -39487,7 +40608,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="60">
+    <row r="11" spans="1:7" ht="57.6">
       <c r="A11" s="38" t="s">
         <v>1226</v>
       </c>
@@ -39510,7 +40631,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
+    <row r="12" spans="1:7" ht="57.6">
       <c r="A12" s="38" t="s">
         <v>1230</v>
       </c>
@@ -39533,7 +40654,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45">
+    <row r="13" spans="1:7" ht="43.2">
       <c r="A13" s="38" t="s">
         <v>1234</v>
       </c>
@@ -39556,7 +40677,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60">
+    <row r="14" spans="1:7" ht="57.6">
       <c r="A14" s="38" t="s">
         <v>1238</v>
       </c>
@@ -39579,7 +40700,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="75">
+    <row r="15" spans="1:7" ht="72">
       <c r="A15" s="38" t="s">
         <v>1241</v>
       </c>
@@ -39602,7 +40723,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30">
+    <row r="16" spans="1:7" ht="28.8">
       <c r="A16" s="38" t="s">
         <v>1244</v>
       </c>
@@ -39625,7 +40746,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="45">
+    <row r="17" spans="1:8" ht="43.2">
       <c r="A17" s="38" t="s">
         <v>1249</v>
       </c>
@@ -39648,7 +40769,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="60">
+    <row r="18" spans="1:8" ht="57.6">
       <c r="A18" s="38" t="s">
         <v>1252</v>
       </c>
@@ -39671,7 +40792,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30">
+    <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="38" t="s">
         <v>1256</v>
       </c>
@@ -39694,7 +40815,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="27.75">
+    <row r="20" spans="1:8" ht="27.6">
       <c r="A20" s="38" t="s">
         <v>1260</v>
       </c>
@@ -39717,7 +40838,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="45">
+    <row r="21" spans="1:8" ht="43.2">
       <c r="A21" s="38" t="s">
         <v>1264</v>
       </c>
@@ -39740,7 +40861,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30">
+    <row r="22" spans="1:8" ht="28.8">
       <c r="A22" s="38" t="s">
         <v>1267</v>
       </c>
@@ -39763,7 +40884,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="45">
+    <row r="23" spans="1:8" ht="43.2">
       <c r="A23" s="38" t="s">
         <v>1270</v>
       </c>
@@ -39786,7 +40907,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="45">
+    <row r="24" spans="1:8" ht="43.2">
       <c r="A24" s="38" t="s">
         <v>1273</v>
       </c>
@@ -39809,7 +40930,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="60">
+    <row r="25" spans="1:8" ht="43.2">
       <c r="A25" s="38" t="s">
         <v>1276</v>
       </c>
@@ -39832,7 +40953,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="42.75">
+    <row r="26" spans="1:8" ht="42">
       <c r="A26" s="38" t="s">
         <v>1279</v>
       </c>
@@ -39855,7 +40976,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30">
+    <row r="27" spans="1:8" ht="28.8">
       <c r="A27" s="38" t="s">
         <v>1283</v>
       </c>
@@ -39878,7 +40999,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="45">
+    <row r="28" spans="1:8" ht="43.2">
       <c r="A28" s="38" t="s">
         <v>1287</v>
       </c>
@@ -39904,7 +41025,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="45">
+    <row r="29" spans="1:8" ht="43.2">
       <c r="A29" s="38" t="s">
         <v>1290</v>
       </c>
@@ -39927,7 +41048,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="60">
+    <row r="30" spans="1:8" ht="43.2">
       <c r="A30" s="38" t="s">
         <v>1293</v>
       </c>
@@ -39949,11 +41070,11 @@
       <c r="G30" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H30" s="67" t="s">
+      <c r="H30" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="60">
+    <row r="31" spans="1:8" ht="57.6">
       <c r="A31" s="38" t="s">
         <v>1297</v>
       </c>
@@ -39975,11 +41096,11 @@
       <c r="G31" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H31" s="67" t="s">
+      <c r="H31" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="60">
+    <row r="32" spans="1:8" ht="57.6">
       <c r="A32" s="38" t="s">
         <v>1301</v>
       </c>
@@ -40001,11 +41122,11 @@
       <c r="G32" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H32" s="67" t="s">
+      <c r="H32" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="45">
+    <row r="33" spans="1:13" ht="43.2">
       <c r="A33" s="38" t="s">
         <v>1304</v>
       </c>
@@ -40027,11 +41148,11 @@
       <c r="G33" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H33" s="67" t="s">
+      <c r="H33" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="45">
+    <row r="34" spans="1:13" ht="43.2">
       <c r="A34" s="38" t="s">
         <v>1308</v>
       </c>
@@ -40053,7 +41174,7 @@
       <c r="G34" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H34" s="67" t="s">
+      <c r="H34" s="66" t="s">
         <v>1657</v>
       </c>
       <c r="I34" s="16" t="s">
@@ -40072,7 +41193,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="45">
+    <row r="35" spans="1:13" ht="43.2">
       <c r="A35" s="38" t="s">
         <v>1312</v>
       </c>
@@ -40094,11 +41215,11 @@
       <c r="G35" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H35" s="67" t="s">
+      <c r="H35" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="30">
+    <row r="36" spans="1:13" ht="28.8">
       <c r="A36" s="38" t="s">
         <v>1315</v>
       </c>
@@ -40120,11 +41241,11 @@
       <c r="G36" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H36" s="67" t="s">
+      <c r="H36" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="30">
+    <row r="37" spans="1:13" ht="28.8">
       <c r="A37" s="38" t="s">
         <v>1318</v>
       </c>
@@ -40146,11 +41267,11 @@
       <c r="G37" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H37" s="67" t="s">
+      <c r="H37" s="66" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="45">
+    <row r="38" spans="1:13" ht="28.8">
       <c r="A38" s="38" t="s">
         <v>1322</v>
       </c>
@@ -40172,14 +41293,14 @@
       <c r="G38" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H38" s="67" t="s">
+      <c r="H38" s="66" t="s">
         <v>1657</v>
       </c>
       <c r="I38" t="s">
         <v>1656</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="45">
+    <row r="39" spans="1:13" ht="43.2">
       <c r="A39" s="38" t="s">
         <v>1326</v>
       </c>
@@ -40201,14 +41322,14 @@
       <c r="G39" s="38" t="s">
         <v>407</v>
       </c>
-      <c r="H39" s="67" t="s">
+      <c r="H39" s="66" t="s">
         <v>1657</v>
       </c>
       <c r="I39" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="45">
+    <row r="40" spans="1:13" ht="43.2">
       <c r="A40" s="38" t="s">
         <v>1330</v>
       </c>
@@ -40231,7 +41352,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="45">
+    <row r="41" spans="1:13" ht="43.2">
       <c r="A41" s="38" t="s">
         <v>1333</v>
       </c>
@@ -40248,7 +41369,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="30">
+    <row r="42" spans="1:13" ht="28.8">
       <c r="A42" s="38" t="s">
         <v>1336</v>
       </c>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B46666C-CAA9-4434-B070-6E15C1C89352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BA404-C096-4972-A667-A55EFE9BEAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plan test" sheetId="18" r:id="rId1"/>

--- a/tests/C2Pro_Test_Suites_Master.xlsx
+++ b/tests/C2Pro_Test_Suites_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esus_\Documents\AI\ZTWQ\c2pro\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BA404-C096-4972-A667-A55EFE9BEAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4264A6AA-EEB6-4CE8-AC15-55F72B1D58D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20616" windowHeight="11016" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plan test" sheetId="18" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6973" uniqueCount="2306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6980" uniqueCount="2306">
   <si>
     <t>Nº</t>
   </si>
@@ -23891,7 +23891,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A136" s="44" t="s">
+      <c r="A136" s="70" t="s">
         <v>1435</v>
       </c>
       <c r="B136" t="s">
@@ -23984,7 +23984,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A152" s="44" t="s">
+      <c r="A152" s="70" t="s">
         <v>1445</v>
       </c>
       <c r="B152" t="s">
@@ -24082,7 +24082,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A169" s="44" t="s">
+      <c r="A169" s="70" t="s">
         <v>1456</v>
       </c>
       <c r="B169" t="s">
@@ -24175,7 +24175,7 @@
       </c>
     </row>
     <row r="185" spans="1:5" ht="24" customHeight="1">
-      <c r="A185" s="44" t="s">
+      <c r="A185" s="70" t="s">
         <v>1466</v>
       </c>
       <c r="B185" t="s">
@@ -24548,21 +24548,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D02680-D9E7-4812-880A-0D5C634B6A57}">
-  <dimension ref="C3:K20"/>
+  <dimension ref="B1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11">
-      <c r="C3" t="s">
+    <row r="1" spans="2:11">
+      <c r="C1" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="B3" t="s">
         <v>1705</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="4" spans="3:11">
+    <row r="4" spans="2:11">
       <c r="C4" t="s">
         <v>1651</v>
       </c>
@@ -24570,55 +24575,54 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="5" spans="3:11">
-      <c r="C5" t="s">
-        <v>1652</v>
-      </c>
+    <row r="5" spans="2:11">
       <c r="E5" s="50" t="s">
         <v>1641</v>
       </c>
     </row>
-    <row r="6" spans="3:11">
+    <row r="6" spans="2:11">
       <c r="C6" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>1642</v>
       </c>
     </row>
-    <row r="7" spans="3:11">
+    <row r="7" spans="2:11">
       <c r="C7" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>1643</v>
       </c>
     </row>
-    <row r="8" spans="3:11">
-      <c r="C8" t="s">
-        <v>1706</v>
-      </c>
+    <row r="8" spans="2:11">
       <c r="E8" s="50" t="s">
         <v>1644</v>
       </c>
     </row>
-    <row r="9" spans="3:11">
+    <row r="9" spans="2:11">
       <c r="C9" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>1645</v>
       </c>
     </row>
-    <row r="10" spans="3:11">
-      <c r="C10" t="s">
-        <v>1707</v>
-      </c>
+    <row r="10" spans="2:11">
       <c r="E10" s="50" t="s">
         <v>1646</v>
       </c>
     </row>
-    <row r="12" spans="3:11">
+    <row r="11" spans="2:11">
+      <c r="C11" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="C12" t="s">
+        <v>1707</v>
+      </c>
       <c r="D12" s="67"/>
       <c r="E12" s="50" t="s">
         <v>1708</v>
@@ -24632,7 +24636,7 @@
       <c r="J12" s="67"/>
       <c r="K12" s="67"/>
     </row>
-    <row r="13" spans="3:11">
+    <row r="13" spans="2:11">
       <c r="D13" s="67"/>
       <c r="E13" s="50" t="s">
         <v>1710</v>
@@ -24646,7 +24650,7 @@
       <c r="J13" s="67"/>
       <c r="K13" s="67"/>
     </row>
-    <row r="14" spans="3:11">
+    <row r="14" spans="2:11">
       <c r="E14" s="50" t="s">
         <v>1712</v>
       </c>
@@ -24658,7 +24662,7 @@
       </c>
       <c r="J14" s="67"/>
     </row>
-    <row r="15" spans="3:11">
+    <row r="15" spans="2:11">
       <c r="E15" s="50" t="s">
         <v>1714</v>
       </c>
@@ -24963,7 +24967,7 @@
         <v>1801</v>
       </c>
       <c r="G11" s="67" t="s">
-        <v>1716</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -24985,6 +24989,9 @@
       <c r="F12" s="67" t="s">
         <v>1804</v>
       </c>
+      <c r="G12" s="67" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="67" t="s">
@@ -25005,6 +25012,9 @@
       <c r="F13" s="67" t="s">
         <v>1806</v>
       </c>
+      <c r="G13" s="67" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="67" t="s">
@@ -25025,6 +25035,9 @@
       <c r="F14" s="67" t="s">
         <v>1809</v>
       </c>
+      <c r="G14" s="67" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="67" t="s">
@@ -25045,6 +25058,9 @@
       <c r="F15" s="67" t="s">
         <v>1812</v>
       </c>
+      <c r="G15" s="67" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="67" t="s">
@@ -25065,8 +25081,11 @@
       <c r="F16" s="67" t="s">
         <v>1814</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="67" t="s">
         <v>1749</v>
       </c>
@@ -25085,8 +25104,11 @@
       <c r="F17" s="67" t="s">
         <v>1816</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="67" t="s">
         <v>1751</v>
       </c>
@@ -25105,8 +25127,11 @@
       <c r="F18" s="67" t="s">
         <v>1819</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="67" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="67" t="s">
         <v>1753</v>
       </c>
@@ -25126,7 +25151,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="67" t="s">
         <v>1755</v>
       </c>
@@ -25146,7 +25171,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="67" t="s">
         <v>1757</v>
       </c>
@@ -25166,7 +25191,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="67" t="s">
         <v>1759</v>
       </c>
@@ -25186,7 +25211,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="67" t="s">
         <v>1761</v>
       </c>
@@ -25206,7 +25231,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="67" t="s">
         <v>1763</v>
       </c>
@@ -25226,7 +25251,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="67" t="s">
         <v>1765</v>
       </c>
@@ -25246,7 +25271,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="67" t="s">
         <v>2236</v>
       </c>
@@ -25266,7 +25291,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="67" t="s">
         <v>2241</v>
       </c>
@@ -25286,7 +25311,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="67" t="s">
         <v>2244</v>
       </c>
@@ -25306,7 +25331,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="67" t="s">
         <v>2247</v>
       </c>
@@ -25326,7 +25351,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="67" t="s">
         <v>2250</v>
       </c>
@@ -25346,7 +25371,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="67" t="s">
         <v>2253</v>
       </c>
@@ -25366,7 +25391,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="67" t="s">
         <v>2256</v>
       </c>
